--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E2" t="n">
         <v>10026</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10025</v>
+        <v>10026</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6205066001663</v>
+        <v>102.610656160649</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5931657179678</v>
+        <v>102.5896691920469</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02734088219847836</v>
+        <v>-0.02098696860207732</v>
       </c>
       <c r="T2" t="n">
-        <v>17.91768909780116</v>
+        <v>17.9155038668804</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0553248564454</v>
+        <v>36.05009345612843</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1401580122222274</v>
+        <v>0.1409931890664702</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7185017679962451</v>
+        <v>-0.7159677077673274</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1401576954494871</v>
+        <v>0.1409923376428469</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.975828943454343</v>
+        <v>2.975681600135594</v>
       </c>
       <c r="Z2" t="n">
-        <v>80.91433054852874</v>
+        <v>95.02088030319564</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.2664412526513</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E3" t="n">
+        <v>14621</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14620</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14619</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908950954237636</v>
+        <v>4.908743604651163</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966491300692143</v>
+        <v>4.966298123086359</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05754034645450718</v>
+        <v>0.05755451843519679</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344678651577674</v>
+        <v>1.344604257897916</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719196561490579</v>
+        <v>1.719132378703679</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813193129006681</v>
+        <v>0.7813394727654076</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5696226494754484</v>
+        <v>0.5696647336036537</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7802836051556702</v>
+        <v>0.7803029433525255</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.150881791483113</v>
+        <v>2.089206338985151</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.225661007061721</v>
+        <v>2.207129567189043</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.331233021292217</v>
+        <v>2.330687820983126</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E4" t="n">
         <v>10253</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.239112466735863</v>
+        <v>7.239024853385637</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3294513919284887</v>
+        <v>0.3293637785782629</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292410023992817</v>
+        <v>1.292382973225675</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682184810210951</v>
+        <v>1.682164199629526</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676885492328213</v>
+        <v>0.8676924368946518</v>
       </c>
       <c r="W4" t="n">
-        <v>0.737547182802971</v>
+        <v>0.7375536140487986</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472055693195504</v>
+        <v>0.8472296644216341</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.181960352422907</v>
+        <v>3.180150403521643</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.304003187825538</v>
+        <v>3.456767148899859</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.496518272400334</v>
+        <v>3.968782098312546</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.75798825256975</v>
+        <v>2.757769625825385</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302284779643362</v>
+        <v>9.30216591702032</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3609821966175324</v>
+        <v>0.3608633339944894</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253989156906</v>
+        <v>1.254014140263419</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750199988890713</v>
+        <v>1.750208620978122</v>
       </c>
       <c r="V5" t="n">
-        <v>0.866204813272385</v>
+        <v>0.8662064762243523</v>
       </c>
       <c r="W5" t="n">
-        <v>0.721294252761383</v>
+        <v>0.7212915035689254</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8602183440303083</v>
+        <v>0.8602248242357605</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.871414572875782</v>
+        <v>4.776907411505261</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.19583926257148</v>
+        <v>5.194475984089943</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.726413692731685</v>
+        <v>5.807229304175822</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E6" t="n">
         <v>8866</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022006934507797</v>
+        <v>7.021977346764491</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2883830906097593</v>
+        <v>0.2883535028664529</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479832553395997</v>
+        <v>1.479848325507466</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908528354104267</v>
+        <v>1.908547406669168</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304557461770588</v>
+        <v>0.3045645988287349</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977638642666655</v>
+        <v>-0.1977877785958579</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2797509018709516</v>
+        <v>0.2797682235677406</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.381102378142341</v>
+        <v>6.367708092874992</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.583618469081034</v>
+        <v>6.555733993981558</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.711995028099045</v>
+        <v>6.712311227725481</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E7" t="n">
         <v>14228</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14227</v>
+        <v>14228</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581147360652281</v>
+        <v>5.58107769890357</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567707221829661</v>
+        <v>5.567644159389283</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01344013882262098</v>
+        <v>-0.01343353951428771</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167084647303406</v>
+        <v>1.167062970173387</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510326062908891</v>
+        <v>1.51030237503732</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047558869009385</v>
+        <v>0.5047570197169796</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05299615225730514</v>
+        <v>0.05298644135783115</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026066851421211</v>
+        <v>0.5026090514116928</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.930685139429564</v>
+        <v>4.911901185076306</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.00339928342277</v>
+        <v>4.992644984145779</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.051737517240016</v>
+        <v>5.051723194369782</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E8" t="n">
         <v>9026</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9025</v>
+        <v>9026</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.876887257617729</v>
+        <v>7.876636106802569</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115837105028387</v>
+        <v>8.11542688243064</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2389498474106584</v>
+        <v>0.2387907756280712</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446516052246957</v>
+        <v>1.446389343105706</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826095366888119</v>
+        <v>1.825997102989003</v>
       </c>
       <c r="V8" t="n">
-        <v>0.807863206912252</v>
+        <v>0.8078809334385413</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274609164852973</v>
+        <v>0.6274834284506714</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797853774270515</v>
+        <v>0.7978925286148745</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.764292458331322</v>
+        <v>4.699703624013628</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.994657804820511</v>
+        <v>4.952161304131803</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.218376753554645</v>
+        <v>5.215031733135461</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E9" t="n">
         <v>13891</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13890</v>
+        <v>13891</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.611813354931606</v>
+        <v>7.611610215247283</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657392629727465</v>
+        <v>7.657158746563804</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04557927479586086</v>
+        <v>0.04554853131652175</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494454068628206</v>
+        <v>1.494403474178203</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942362115990856</v>
+        <v>1.942304635359889</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565871654135065</v>
+        <v>0.7566064381817833</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5246896613534281</v>
+        <v>0.5247178987097768</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551787062391889</v>
+        <v>0.7552002780578599</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.116181955096716</v>
+        <v>5.075627614234958</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.263307288412771</v>
+        <v>5.237953993155882</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.361600587371512</v>
+        <v>5.361939349474199</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61705334931016</v>
+        <v>10.61693768093387</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3119916688177878</v>
+        <v>0.3118760004414978</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052529428273189</v>
+        <v>2.052570776139774</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698204420852664</v>
+        <v>2.698252311890559</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356837871736162</v>
+        <v>0.3568505388140931</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1205267571512865</v>
+        <v>-0.1205665344677969</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3364019047413548</v>
+        <v>0.3364327795021365</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.490076015867068</v>
+        <v>9.489485571553459</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.794306710035501</v>
+        <v>9.661028628929499</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.92479894014703</v>
+        <v>9.983611807071936</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E11" t="n">
         <v>13832</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13831</v>
+        <v>13832</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243540561058492</v>
+        <v>5.24346873192597</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579030837004405</v>
+        <v>0.4578686720469552</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.2170371100722</v>
+        <v>5.216954819575744</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02650345098629179</v>
+        <v>-0.02651391235022364</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161727306651721</v>
+        <v>1.161671624261001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483193481715616</v>
+        <v>1.483155592547925</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4292594939922887</v>
+        <v>0.4292803833545303</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09227911487965712</v>
+        <v>-0.09226357518707506</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4274502578848689</v>
+        <v>0.4274728698913296</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.069848874204602</v>
+        <v>4.069658229395941</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.607848468541699</v>
+        <v>4.420538537606477</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.455567566903852</v>
+        <v>4.944805575935437</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E12" t="n">
         <v>4150</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4149</v>
+        <v>4150</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.472374909616775</v>
+        <v>7.471526144578314</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.20511013215859</v>
+        <v>2.20509904622157</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.645967740067685</v>
+        <v>7.645183705009093</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735928304509096</v>
+        <v>0.1736575604307796</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9135210157863671</v>
+        <v>0.9134262137001391</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195486757749265</v>
+        <v>1.195377508698834</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8314450999029892</v>
+        <v>0.8315527479393762</v>
       </c>
       <c r="W12" t="n">
-        <v>0.658256926424848</v>
+        <v>0.6584811761704317</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8296724632923537</v>
+        <v>0.8297756434583377</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.291847932012725</v>
+        <v>4.289780141476372</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.447259244732281</v>
+        <v>4.382665142311696</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.261474665264195</v>
+        <v>5.194906292848363</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E13" t="n">
         <v>6485</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6484</v>
+        <v>6485</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.605567165330044</v>
+        <v>9.605054356206631</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02653430527363</v>
+        <v>10.02611038346507</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4209671399435899</v>
+        <v>0.4210560272584442</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691594796210649</v>
+        <v>1.691565516550389</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150994788191994</v>
+        <v>2.150938320013887</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231844240901107</v>
+        <v>0.8231942593098103</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648661523915858</v>
+        <v>0.6486712847590157</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8104862542112194</v>
+        <v>0.8104959205077582</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.095916956552648</v>
+        <v>7.734893971690662</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.414631067479345</v>
+        <v>8.362380353842648</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.504605235412651</v>
+        <v>8.524916901728622</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E14" t="n">
         <v>14072</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14071</v>
+        <v>14072</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.129009132257835</v>
+        <v>8.12877043064241</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9075599608418992</v>
+        <v>0.9074492540963561</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199533929339131</v>
+        <v>8.199190564544491</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07052479708129507</v>
+        <v>0.07042013390208088</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756791903163342</v>
+        <v>1.756619432989678</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282800757222165</v>
+        <v>2.282651813681312</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808444975098474</v>
+        <v>0.7808808489690872</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653542535218699</v>
+        <v>0.5654091474027513</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804665355412211</v>
+        <v>0.7805052154884849</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.182085354725964</v>
+        <v>5.170432952914561</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.251798942180962</v>
+        <v>5.25723773084998</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.333237217994927</v>
+        <v>5.541744903459582</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.673348017621145</v>
+        <v>4.672531181217901</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82214649833608</v>
+        <v>11.82201569404232</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1417408846907007</v>
+        <v>-0.1418716889844631</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052342338424996</v>
+        <v>2.052366965071088</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697594903444394</v>
+        <v>2.6976156015866</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949867055369728</v>
+        <v>0.7949895836601116</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096092127111992</v>
+        <v>0.6096032218969221</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863342903167907</v>
+        <v>0.7863453492445148</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.9146802566502</v>
+        <v>8.531783128446474</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.47024104993337</v>
+        <v>11.22091764442863</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.8986089989068</v>
+        <v>11.90285020159987</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E16" t="n">
         <v>9835</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9834</v>
+        <v>9835</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363813199105145</v>
+        <v>8.363633858668022</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624373071903522</v>
+        <v>8.624591243343799</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2605598727983763</v>
+        <v>0.2609573846757762</v>
       </c>
       <c r="T16" t="n">
-        <v>3.59225820027089</v>
+        <v>3.592455325325715</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09231864172644</v>
+        <v>11.09189241294237</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04171001288694214</v>
+        <v>0.04169598518806215</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6099354251380775</v>
+        <v>-0.6099687370268541</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0250462350960402</v>
+        <v>0.02503176609892821</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.67317419041749</v>
+        <v>11.6592702707897</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.84462858314012</v>
+        <v>11.81562759604806</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.29480447072659</v>
+        <v>12.28361682988293</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E17" t="n">
         <v>2379</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.494915895710681</v>
+        <v>6.493152585119798</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.416938325991189</v>
+        <v>1.416731474688188</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.859011435850739</v>
+        <v>6.857310746336936</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3640955401400583</v>
+        <v>0.3641581612171373</v>
       </c>
       <c r="T17" t="n">
-        <v>2.019635178994044</v>
+        <v>2.019008986043468</v>
       </c>
       <c r="U17" t="n">
-        <v>2.555376646656593</v>
+        <v>2.554882684807781</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5324572448836055</v>
+        <v>0.5329405079111519</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04350561296634237</v>
+        <v>0.0445085575133638</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5291037257120532</v>
+        <v>0.5295807142133513</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.42901347388417</v>
+        <v>2.428812436852707</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.109052148873424</v>
+        <v>3.187052261260365</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.373651612063481</v>
+        <v>4.605098930410115</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E18" t="n">
         <v>3238</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.477426320667283</v>
+        <v>6.476630327362569</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.671940610170693</v>
+        <v>6.671110435821966</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1945142895034078</v>
+        <v>0.1944801084593968</v>
       </c>
       <c r="T18" t="n">
-        <v>1.09866568198048</v>
+        <v>1.098342171488396</v>
       </c>
       <c r="U18" t="n">
-        <v>1.486918199494539</v>
+        <v>1.486701148993269</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6058011176596961</v>
+        <v>0.6061048276803712</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2263205890156228</v>
+        <v>0.2268625634243212</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6029108188996035</v>
+        <v>0.6032193851918206</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.065100466388778</v>
+        <v>3.064848621014697</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.427640372361481</v>
+        <v>4.429689299343201</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.851688262856731</v>
+        <v>5.678285833089822</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E19" t="n">
         <v>7192</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7191</v>
+        <v>7192</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33624794882492</v>
+        <v>10.33492477753059</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12812323577417</v>
+        <v>11.12751651751246</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7918752869492509</v>
+        <v>0.792591739981868</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0519559141632</v>
+        <v>2.052597835470644</v>
       </c>
       <c r="U19" t="n">
-        <v>2.775412154571399</v>
+        <v>2.776317554766227</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7271211058638399</v>
+        <v>0.72713513573626</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4709515563977114</v>
+        <v>0.4709902014429682</v>
       </c>
       <c r="X19" t="n">
-        <v>0.678529178107754</v>
+        <v>0.678402222556959</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.373783103762445</v>
+        <v>7.328981900053581</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.641359266893268</v>
+        <v>7.442825134818501</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.483260125984224</v>
+        <v>7.596810587768807</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E20" t="n">
         <v>620</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>45658</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M20" t="n">
-        <v>10.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>15.53037964458805</v>
+        <v>15.52139516129032</v>
       </c>
       <c r="O20" t="n">
         <v>19.03</v>
       </c>
       <c r="P20" t="n">
-        <v>10.80578193832599</v>
+        <v>10.80560161408657</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.36246131691289</v>
+        <v>16.35350743283659</v>
       </c>
       <c r="R20" t="n">
         <v>19.01911469282878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8320816723248445</v>
+        <v>0.8321122715462624</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8853762187692525</v>
+        <v>0.8853214736124554</v>
       </c>
       <c r="U20" t="n">
-        <v>1.261488999175827</v>
+        <v>1.26093391953712</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9375384673387651</v>
+        <v>0.9379701495268326</v>
       </c>
       <c r="W20" t="n">
-        <v>0.785665515605934</v>
+        <v>0.7869442802952729</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9012171840144266</v>
+        <v>0.9016665886112374</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.79127888241834</v>
+        <v>10.79176797337919</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.80724653607479</v>
+        <v>10.82128739375457</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.82395906754772</v>
+        <v>10.85966919563299</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16690</v>
+        <v>16691</v>
       </c>
       <c r="E21" t="n">
         <v>10237</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9753584184409</v>
+        <v>130.9753771703504</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045914945373727</v>
+        <v>0.1046102464468784</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976783616021335</v>
+        <v>0.7976929735280958</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046341146593539</v>
+        <v>1.046356125737014</v>
       </c>
       <c r="V21" t="n">
-        <v>0.864915864325453</v>
+        <v>0.8649119350598818</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7307660521977413</v>
+        <v>0.7307583435784013</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641736514562061</v>
+        <v>0.8641693103538335</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.035504300431</v>
+        <v>128.0329518813868</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.4669467051054</v>
+        <v>128.3418756637311</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.6620647167807</v>
+        <v>129.5435815587171</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.373783103762445</v>
+        <v>7.328981900053581</v>
       </c>
       <c r="G2" t="n">
-        <v>7.641359266893268</v>
+        <v>7.442825134818503</v>
       </c>
       <c r="H2" t="n">
-        <v>9.483260125984224</v>
+        <v>7.596810587768807</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.930685139429564</v>
+        <v>4.911901185076306</v>
       </c>
       <c r="G3" t="n">
-        <v>5.00339928342277</v>
+        <v>4.992644984145779</v>
       </c>
       <c r="H3" t="n">
-        <v>5.051737517240016</v>
+        <v>5.051723194369782</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.069848874204602</v>
+        <v>4.069658229395941</v>
       </c>
       <c r="G4" t="n">
-        <v>4.607848468541699</v>
+        <v>4.420538537606477</v>
       </c>
       <c r="H4" t="n">
-        <v>5.455567566903852</v>
+        <v>4.944805575935437</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67317419041749</v>
+        <v>11.6592702707897</v>
       </c>
       <c r="G5" t="n">
-        <v>11.84462858314012</v>
+        <v>11.81562759604806</v>
       </c>
       <c r="H5" t="n">
-        <v>12.29480447072659</v>
+        <v>12.28361682988293</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.975828943454343</v>
+        <v>2.975681600135594</v>
       </c>
       <c r="G6" t="n">
-        <v>80.91433054852874</v>
+        <v>95.02088030319564</v>
       </c>
       <c r="H6" t="n">
-        <v>110.2664412526513</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>10.9146802566502</v>
+        <v>8.531783128446474</v>
       </c>
       <c r="G7" t="n">
-        <v>11.47024104993337</v>
+        <v>11.22091764442863</v>
       </c>
       <c r="H7" t="n">
-        <v>11.8986089989068</v>
+        <v>11.90285020159987</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.095916956552648</v>
+        <v>7.734893971690662</v>
       </c>
       <c r="G8" t="n">
-        <v>8.414631067479345</v>
+        <v>8.362380353842648</v>
       </c>
       <c r="H8" t="n">
-        <v>8.504605235412651</v>
+        <v>8.524916901728622</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.291847932012725</v>
+        <v>4.289780141476372</v>
       </c>
       <c r="G9" t="n">
-        <v>4.447259244732282</v>
+        <v>4.382665142311696</v>
       </c>
       <c r="H9" t="n">
-        <v>5.261474665264195</v>
+        <v>5.194906292848363</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.764292458331322</v>
+        <v>4.699703624013628</v>
       </c>
       <c r="G10" t="n">
-        <v>4.994657804820511</v>
+        <v>4.952161304131802</v>
       </c>
       <c r="H10" t="n">
-        <v>5.218376753554645</v>
+        <v>5.215031733135461</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.79127888241834</v>
+        <v>10.79176797337919</v>
       </c>
       <c r="G11" t="n">
-        <v>10.80724653607479</v>
+        <v>10.82128739375457</v>
       </c>
       <c r="H11" t="n">
-        <v>10.82395906754772</v>
+        <v>10.85966919563299</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.42901347388417</v>
+        <v>2.428812436852707</v>
       </c>
       <c r="G12" t="n">
-        <v>3.109052148873424</v>
+        <v>3.187052261260365</v>
       </c>
       <c r="H12" t="n">
-        <v>4.373651612063481</v>
+        <v>4.605098930410115</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.182085354725964</v>
+        <v>5.170432952914561</v>
       </c>
       <c r="G13" t="n">
-        <v>5.251798942180962</v>
+        <v>5.25723773084998</v>
       </c>
       <c r="H13" t="n">
-        <v>5.333237217994927</v>
+        <v>5.541744903459582</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.490076015867068</v>
+        <v>9.489485571553459</v>
       </c>
       <c r="G14" t="n">
-        <v>9.794306710035503</v>
+        <v>9.6610286289295</v>
       </c>
       <c r="H14" t="n">
-        <v>10.92479894014703</v>
+        <v>9.983611807071936</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.116181955096716</v>
+        <v>5.075627614234958</v>
       </c>
       <c r="G15" t="n">
-        <v>5.263307288412771</v>
+        <v>5.237953993155882</v>
       </c>
       <c r="H15" t="n">
-        <v>5.361600587371512</v>
+        <v>5.361939349474199</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.381102378142341</v>
+        <v>6.367708092874992</v>
       </c>
       <c r="G16" t="n">
-        <v>6.583618469081034</v>
+        <v>6.555733993981558</v>
       </c>
       <c r="H16" t="n">
-        <v>6.711995028099045</v>
+        <v>6.712311227725481</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.065100466388778</v>
+        <v>3.064848621014697</v>
       </c>
       <c r="G17" t="n">
-        <v>4.427640372361481</v>
+        <v>4.429689299343201</v>
       </c>
       <c r="H17" t="n">
-        <v>5.851688262856731</v>
+        <v>5.678285833089822</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.181960352422907</v>
+        <v>3.180150403521643</v>
       </c>
       <c r="G18" t="n">
-        <v>3.304003187825538</v>
+        <v>3.456767148899859</v>
       </c>
       <c r="H18" t="n">
-        <v>3.496518272400334</v>
+        <v>3.968782098312546</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.150881791483113</v>
+        <v>2.089206338985151</v>
       </c>
       <c r="G19" t="n">
-        <v>2.225661007061721</v>
+        <v>2.207129567189043</v>
       </c>
       <c r="H19" t="n">
-        <v>2.331233021292217</v>
+        <v>2.330687820983126</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.871414572875782</v>
+        <v>4.776907411505261</v>
       </c>
       <c r="G20" t="n">
-        <v>5.19583926257148</v>
+        <v>5.194475984089943</v>
       </c>
       <c r="H20" t="n">
-        <v>5.726413692731685</v>
+        <v>5.807229304175822</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.035504300431</v>
+        <v>128.0329518813868</v>
       </c>
       <c r="G21" t="n">
-        <v>128.4669467051054</v>
+        <v>128.3418756637311</v>
       </c>
       <c r="H21" t="n">
-        <v>129.6620647167807</v>
+        <v>129.5435815587171</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,7 +576,7 @@
         <v>16691</v>
       </c>
       <c r="E2" t="n">
-        <v>10026</v>
+        <v>10028</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -614,34 +614,34 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5896691920469</v>
+        <v>102.5720491719688</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02098696860207732</v>
+        <v>-0.03860698868021081</v>
       </c>
       <c r="T2" t="n">
-        <v>17.9155038668804</v>
+        <v>17.92604162512164</v>
       </c>
       <c r="U2" t="n">
-        <v>36.05009345612843</v>
+        <v>36.06923260879783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1409931890664702</v>
+        <v>0.1411472183716064</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7159677077673274</v>
+        <v>-0.7177902209877256</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1409923376428469</v>
+        <v>0.1411471346090758</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.975681600135594</v>
+        <v>2.976169283246495</v>
       </c>
       <c r="Z2" t="n">
-        <v>95.02088030319564</v>
+        <v>95.01298267219498</v>
       </c>
       <c r="AA2" t="n">
         <v>111.56</v>
@@ -665,7 +665,7 @@
         <v>16691</v>
       </c>
       <c r="E3" t="n">
-        <v>14621</v>
+        <v>14622</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966298123086359</v>
+        <v>4.966343458745827</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05755451843519679</v>
+        <v>0.05759985409466432</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344604257897916</v>
+        <v>1.34459503631689</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719132378703679</v>
+        <v>1.719123981228464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813394727654076</v>
+        <v>0.7813366103959403</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5696647336036537</v>
+        <v>0.5696689377253985</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803029433525255</v>
+        <v>0.780297464296649</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.089206338985151</v>
+        <v>2.088977411136755</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.207129567189043</v>
+        <v>2.206389744505143</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.330687820983126</v>
+        <v>2.330280630961115</v>
       </c>
     </row>
     <row r="4">
@@ -754,13 +754,13 @@
         <v>16691</v>
       </c>
       <c r="E4" t="n">
-        <v>10253</v>
+        <v>10256</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10253</v>
+        <v>10254</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.909661074807374</v>
+        <v>6.90926979715233</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.239024853385637</v>
+        <v>7.238879593366129</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3293637785782629</v>
+        <v>0.3296097962137978</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292382973225675</v>
+        <v>1.292439005830777</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682164199629526</v>
+        <v>1.682134273204272</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676924368946518</v>
+        <v>0.8677015366697989</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375536140487986</v>
+        <v>0.7375754981940627</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472296644216341</v>
+        <v>0.8471735175526196</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.180150403521643</v>
+        <v>3.171155539251651</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.456767148899859</v>
+        <v>3.45287875754136</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.968782098312546</v>
+        <v>3.966008804108584</v>
       </c>
     </row>
     <row r="5">
@@ -843,13 +843,13 @@
         <v>16691</v>
       </c>
       <c r="E5" t="n">
-        <v>2710</v>
+        <v>2722</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2710</v>
+        <v>2721</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,52 +866,52 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46266</v>
+        <v>46277</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.941302583025831</v>
+        <v>8.933439911797134</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.757769625825385</v>
+        <v>2.824935191978479</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.30216591702032</v>
+        <v>9.304073515603294</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3608633339944894</v>
+        <v>0.3706336038061614</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254014140263419</v>
+        <v>1.248616101907637</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750208620978122</v>
+        <v>1.748091848049035</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8662064762243523</v>
+        <v>0.8659452812928096</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212915035689254</v>
+        <v>0.7212474628102197</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8602248242357605</v>
+        <v>0.8594855425489892</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.776907411505261</v>
+        <v>5.430879744483859</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.194475984089943</v>
+        <v>6.006433117488635</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.807229304175822</v>
+        <v>6.555755247419387</v>
       </c>
     </row>
     <row r="6">
@@ -932,13 +932,13 @@
         <v>16691</v>
       </c>
       <c r="E6" t="n">
-        <v>8866</v>
+        <v>8869</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8866</v>
+        <v>8867</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733623843898037</v>
+        <v>6.733654167136573</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021977346764491</v>
+        <v>7.022318259713997</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2883535028664529</v>
+        <v>0.2886640925774234</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479848325507466</v>
+        <v>1.479646171024144</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908547406669168</v>
+        <v>1.908378230764743</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3045645988287349</v>
+        <v>0.3044954816640217</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977877785958579</v>
+        <v>-0.1977081548819253</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2797682235677406</v>
+        <v>0.2796358703613582</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.367708092874992</v>
+        <v>6.373699293722082</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.555733993981558</v>
+        <v>6.564836703222423</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.712311227725481</v>
+        <v>6.718189808280587</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
         <v>16691</v>
       </c>
       <c r="E7" t="n">
-        <v>14228</v>
+        <v>14230</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -1050,7 +1050,7 @@
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.58107769890357</v>
+        <v>5.581078050323306</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567644159389283</v>
+        <v>5.567627347115266</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01343353951428771</v>
+        <v>-0.01345070320803975</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167062970173387</v>
+        <v>1.167024627592115</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51030237503732</v>
+        <v>1.510260913989076</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047570197169796</v>
+        <v>0.5047721387335367</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05298644135783115</v>
+        <v>0.0530381625950106</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026090514116928</v>
+        <v>0.5026217084248237</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.911901185076306</v>
+        <v>4.910143396428452</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.992644984145779</v>
+        <v>4.991117609125702</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.051723194369782</v>
+        <v>5.050453708018097</v>
       </c>
     </row>
     <row r="8">
@@ -1110,7 +1110,7 @@
         <v>16691</v>
       </c>
       <c r="E8" t="n">
-        <v>9026</v>
+        <v>9028</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.876636106802569</v>
+        <v>7.876634167959229</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.11542688243064</v>
+        <v>8.115841609086177</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2387907756280712</v>
+        <v>0.2392074411269477</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446389343105706</v>
+        <v>1.446413252266368</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825997102989003</v>
+        <v>1.826016288081748</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078809334385413</v>
+        <v>0.8078597935412262</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274834284506714</v>
+        <v>0.627475967835992</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978925286148745</v>
+        <v>0.7978101357205185</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.699703624013628</v>
+        <v>4.70659728544517</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.952161304131803</v>
+        <v>4.966618150640928</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.215031733135461</v>
+        <v>5.225116210896313</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1199,7 @@
         <v>16691</v>
       </c>
       <c r="E9" t="n">
-        <v>13891</v>
+        <v>13893</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657158746563804</v>
+        <v>7.657233315385815</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04554853131652175</v>
+        <v>0.0456231001385326</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494403474178203</v>
+        <v>1.494384309402575</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942304635359889</v>
+        <v>1.942293888120434</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566064381817833</v>
+        <v>0.7565986108234594</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5247178987097768</v>
+        <v>0.524723158395952</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552002780578599</v>
+        <v>0.755187140590924</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.075627614234958</v>
+        <v>5.072744235699506</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.237953993155882</v>
+        <v>5.236730202954233</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.361939349474199</v>
+        <v>5.361117632673025</v>
       </c>
     </row>
     <row r="10">
@@ -1347,7 +1347,7 @@
         <v>-0.1205665344677969</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3364327795021365</v>
+        <v>0.3364327795021363</v>
       </c>
       <c r="Y10" t="n">
         <v>9.489485571553459</v>
@@ -1377,7 +1377,7 @@
         <v>16691</v>
       </c>
       <c r="E11" t="n">
-        <v>13832</v>
+        <v>13834</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -1406,46 +1406,46 @@
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.24346873192597</v>
+        <v>5.243460598611914</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578686720469552</v>
+        <v>0.4579479090242113</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216954819575744</v>
+        <v>5.216878908069908</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02651391235022364</v>
+        <v>-0.02658169054200617</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161671624261001</v>
+        <v>1.161648481263994</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483155592547925</v>
+        <v>1.483129429023117</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4292803833545303</v>
+        <v>0.4293136681427173</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09226357518707506</v>
+        <v>-0.09221577906315814</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4274728698913296</v>
+        <v>0.4275069848204408</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.069658229395941</v>
+        <v>4.069263878698949</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.420538537606477</v>
+        <v>4.419002571048312</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.944805575935437</v>
+        <v>4.94419662509171</v>
       </c>
     </row>
     <row r="12">
@@ -1466,7 +1466,7 @@
         <v>16691</v>
       </c>
       <c r="E12" t="n">
-        <v>4150</v>
+        <v>4152</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -1495,46 +1495,46 @@
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.471526144578314</v>
+        <v>7.471526746987951</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.20509904622157</v>
+        <v>2.20518708730741</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.645183705009093</v>
+        <v>7.644895430914917</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1736575604307796</v>
+        <v>0.1733686839269654</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9134262137001391</v>
+        <v>0.9133212445940742</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195377508698834</v>
+        <v>1.195275117831539</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8315527479393762</v>
+        <v>0.8315980783635759</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6584811761704317</v>
+        <v>0.6585393335817828</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8297756434583377</v>
+        <v>0.8298336935053351</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.289780141476372</v>
+        <v>4.27951707911047</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.382665142311696</v>
+        <v>4.370073736742098</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.194906292848363</v>
+        <v>5.187856183768762</v>
       </c>
     </row>
     <row r="13">
@@ -1555,7 +1555,7 @@
         <v>16691</v>
       </c>
       <c r="E13" t="n">
-        <v>6485</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.605054356206631</v>
+        <v>9.605055898226677</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02611038346507</v>
+        <v>10.02658889913596</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4210560272584442</v>
+        <v>0.421533000909285</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691565516550389</v>
+        <v>1.691655074351911</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150938320013887</v>
+        <v>2.150875117360324</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231942593098103</v>
+        <v>0.8231937030877825</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486712847590157</v>
+        <v>0.6486916580159064</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8104959205077582</v>
+        <v>0.8104262559375465</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.734893971690662</v>
+        <v>7.729761635062327</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.362380353842648</v>
+        <v>8.361114476801497</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.524916901728622</v>
+        <v>8.524262664259133</v>
       </c>
     </row>
     <row r="14">
@@ -1644,7 +1644,7 @@
         <v>16691</v>
       </c>
       <c r="E14" t="n">
-        <v>14072</v>
+        <v>14074</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -1679,40 +1679,40 @@
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9074492540963561</v>
+        <v>0.9077182685253118</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199190564544491</v>
+        <v>8.199442254240395</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07042013390208088</v>
+        <v>0.07067182359798403</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756619432989678</v>
+        <v>1.756747580692275</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282651813681312</v>
+        <v>2.282757622965844</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808808489690872</v>
+        <v>0.7808399849004419</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654091474027513</v>
+        <v>0.5653688567086914</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805052154884849</v>
+        <v>0.7804586837002664</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.170432952914561</v>
+        <v>5.169804822589699</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.25723773084998</v>
+        <v>5.255897562255671</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.541744903459582</v>
+        <v>5.539820532080975</v>
       </c>
     </row>
     <row r="15">
@@ -1786,13 +1786,13 @@
         <v>2.6976156015866</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949895836601116</v>
+        <v>0.7949895836601112</v>
       </c>
       <c r="W15" t="n">
         <v>0.6096032218969221</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863453492445148</v>
+        <v>0.7863453492445145</v>
       </c>
       <c r="Y15" t="n">
         <v>8.531783128446474</v>
@@ -1822,7 +1822,7 @@
         <v>16691</v>
       </c>
       <c r="E16" t="n">
-        <v>9835</v>
+        <v>9837</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363633858668022</v>
+        <v>8.363637925775292</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624591243343799</v>
+        <v>8.623990453460641</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2609573846757762</v>
+        <v>0.2603525276853484</v>
       </c>
       <c r="T16" t="n">
-        <v>3.592455325325715</v>
+        <v>3.592662631964989</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09189241294237</v>
+        <v>11.09193142257605</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04169598518806215</v>
+        <v>0.04168027037037705</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6099687370268541</v>
+        <v>-0.6099803602187148</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02503176609892821</v>
+        <v>0.02501745773479902</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.6592702707897</v>
+        <v>11.65313500445666</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.81562759604806</v>
+        <v>11.81355252620689</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.28361682988293</v>
+        <v>12.27567415228556</v>
       </c>
     </row>
     <row r="17">
@@ -1911,7 +1911,7 @@
         <v>16691</v>
       </c>
       <c r="E17" t="n">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -1946,40 +1946,40 @@
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.416731474688188</v>
+        <v>1.419666177549523</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.857310746336936</v>
+        <v>6.856399232413494</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3641581612171373</v>
+        <v>0.3632466472936951</v>
       </c>
       <c r="T17" t="n">
-        <v>2.019008986043468</v>
+        <v>2.018639411499311</v>
       </c>
       <c r="U17" t="n">
-        <v>2.554882684807781</v>
+        <v>2.554662365696587</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5329405079111519</v>
+        <v>0.5331694541715023</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0445085575133638</v>
+        <v>0.04467334312161741</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5295807142133513</v>
+        <v>0.5298227065817138</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.428812436852707</v>
+        <v>2.374443099824393</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.187052261260365</v>
+        <v>3.170136565309023</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.605098930410115</v>
+        <v>4.519172589135704</v>
       </c>
     </row>
     <row r="18">
@@ -2000,7 +2000,7 @@
         <v>16691</v>
       </c>
       <c r="E18" t="n">
-        <v>3238</v>
+        <v>3240</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.476630327362569</v>
+        <v>6.47663959234095</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.671110435821966</v>
+        <v>6.671056436790835</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1944801084593968</v>
+        <v>0.194416844449884</v>
       </c>
       <c r="T18" t="n">
-        <v>1.098342171488396</v>
+        <v>1.098167681515372</v>
       </c>
       <c r="U18" t="n">
-        <v>1.486701148993269</v>
+        <v>1.486504881054543</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6061048276803712</v>
+        <v>0.6061701745812375</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2268625634243212</v>
+        <v>0.2270538489061109</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6032193851918206</v>
+        <v>0.6032775011553289</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.064848621014697</v>
+        <v>3.066619888673478</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.429689299343201</v>
+        <v>4.427625174771611</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.678285833089822</v>
+        <v>5.672796687033919</v>
       </c>
     </row>
     <row r="19">
@@ -2089,7 +2089,7 @@
         <v>16691</v>
       </c>
       <c r="E19" t="n">
-        <v>7192</v>
+        <v>7194</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33492477753059</v>
+        <v>10.33492269187987</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12751651751246</v>
+        <v>11.12692433568649</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.792591739981868</v>
+        <v>0.7920016438066255</v>
       </c>
       <c r="T19" t="n">
-        <v>2.052597835470644</v>
+        <v>2.052548389183963</v>
       </c>
       <c r="U19" t="n">
-        <v>2.776317554766227</v>
+        <v>2.776197787867929</v>
       </c>
       <c r="V19" t="n">
-        <v>0.72713513573626</v>
+        <v>0.7271596023210478</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4709902014429682</v>
+        <v>0.471037284126937</v>
       </c>
       <c r="X19" t="n">
-        <v>0.678402222556959</v>
+        <v>0.6785511392492206</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.328981900053581</v>
+        <v>7.327535179981441</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.442825134818501</v>
+        <v>7.441100373984497</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.596810587768807</v>
+        <v>7.594632687543739</v>
       </c>
     </row>
     <row r="20">
@@ -2178,13 +2178,13 @@
         <v>16691</v>
       </c>
       <c r="E20" t="n">
-        <v>620</v>
+        <v>10644</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>620</v>
+        <v>10642</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2198,55 +2198,55 @@
         <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>45658</v>
+        <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>46277</v>
       </c>
       <c r="M20" t="n">
-        <v>9.960000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>15.52139516129032</v>
+        <v>13.86077637729852</v>
       </c>
       <c r="O20" t="n">
-        <v>19.03</v>
+        <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>10.80560161408657</v>
+        <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.35350743283659</v>
+        <v>14.2373334877879</v>
       </c>
       <c r="R20" t="n">
-        <v>19.01911469282878</v>
+        <v>21.67640869875964</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8321122715462624</v>
+        <v>0.376557110489386</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8853214736124554</v>
+        <v>1.256099554316596</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26093391953712</v>
+        <v>1.64772749714494</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9379701495268326</v>
+        <v>0.893418353958889</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7869442802952729</v>
+        <v>0.7787390333355673</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9016665886112374</v>
+        <v>0.8885968921736751</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.79176797337919</v>
+        <v>9.790304756336552</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.82128739375457</v>
+        <v>10.18189447088567</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.85966919563299</v>
+        <v>10.72229813398619</v>
       </c>
     </row>
     <row r="21">
@@ -2320,13 +2320,13 @@
         <v>1.046356125737014</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649119350598818</v>
+        <v>0.8649119350598822</v>
       </c>
       <c r="W21" t="n">
         <v>0.7307583435784013</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641693103538335</v>
+        <v>0.8641693103538339</v>
       </c>
       <c r="Y21" t="n">
         <v>128.0329518813868</v>
@@ -2413,13 +2413,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.328981900053581</v>
+        <v>7.327535179981441</v>
       </c>
       <c r="G2" t="n">
-        <v>7.442825134818503</v>
+        <v>7.441100373984497</v>
       </c>
       <c r="H2" t="n">
-        <v>7.596810587768807</v>
+        <v>7.594632687543739</v>
       </c>
     </row>
     <row r="3">
@@ -2441,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.911901185076306</v>
+        <v>4.910143396428452</v>
       </c>
       <c r="G3" t="n">
-        <v>4.992644984145779</v>
+        <v>4.9911176091257</v>
       </c>
       <c r="H3" t="n">
-        <v>5.051723194369782</v>
+        <v>5.050453708018097</v>
       </c>
     </row>
     <row r="4">
@@ -2469,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.069658229395941</v>
+        <v>4.069263878698949</v>
       </c>
       <c r="G4" t="n">
-        <v>4.420538537606477</v>
+        <v>4.419002571048312</v>
       </c>
       <c r="H4" t="n">
-        <v>4.944805575935437</v>
+        <v>4.94419662509171</v>
       </c>
     </row>
     <row r="5">
@@ -2497,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.6592702707897</v>
+        <v>11.65313500445666</v>
       </c>
       <c r="G5" t="n">
-        <v>11.81562759604806</v>
+        <v>11.81355252620689</v>
       </c>
       <c r="H5" t="n">
-        <v>12.28361682988293</v>
+        <v>12.27567415228556</v>
       </c>
     </row>
     <row r="6">
@@ -2525,10 +2525,10 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.975681600135594</v>
+        <v>2.976169283246495</v>
       </c>
       <c r="G6" t="n">
-        <v>95.02088030319564</v>
+        <v>95.01298267219499</v>
       </c>
       <c r="H6" t="n">
         <v>111.56</v>
@@ -2581,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.734893971690662</v>
+        <v>7.729761635062327</v>
       </c>
       <c r="G8" t="n">
-        <v>8.362380353842648</v>
+        <v>8.361114476801495</v>
       </c>
       <c r="H8" t="n">
-        <v>8.524916901728622</v>
+        <v>8.524262664259133</v>
       </c>
     </row>
     <row r="9">
@@ -2609,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.289780141476372</v>
+        <v>4.27951707911047</v>
       </c>
       <c r="G9" t="n">
-        <v>4.382665142311696</v>
+        <v>4.370073736742097</v>
       </c>
       <c r="H9" t="n">
-        <v>5.194906292848363</v>
+        <v>5.187856183768762</v>
       </c>
     </row>
     <row r="10">
@@ -2637,13 +2637,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.699703624013628</v>
+        <v>4.70659728544517</v>
       </c>
       <c r="G10" t="n">
-        <v>4.952161304131802</v>
+        <v>4.966618150640929</v>
       </c>
       <c r="H10" t="n">
-        <v>5.215031733135461</v>
+        <v>5.225116210896313</v>
       </c>
     </row>
     <row r="11">
@@ -2665,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.79176797337919</v>
+        <v>9.790304756336552</v>
       </c>
       <c r="G11" t="n">
-        <v>10.82128739375457</v>
+        <v>10.18189447088567</v>
       </c>
       <c r="H11" t="n">
-        <v>10.85966919563299</v>
+        <v>10.72229813398619</v>
       </c>
     </row>
     <row r="12">
@@ -2693,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.428812436852707</v>
+        <v>2.374443099824393</v>
       </c>
       <c r="G12" t="n">
-        <v>3.187052261260365</v>
+        <v>3.170136565309023</v>
       </c>
       <c r="H12" t="n">
-        <v>4.605098930410115</v>
+        <v>4.519172589135704</v>
       </c>
     </row>
     <row r="13">
@@ -2721,13 +2721,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.170432952914561</v>
+        <v>5.169804822589699</v>
       </c>
       <c r="G13" t="n">
-        <v>5.25723773084998</v>
+        <v>5.255897562255671</v>
       </c>
       <c r="H13" t="n">
-        <v>5.541744903459582</v>
+        <v>5.539820532080975</v>
       </c>
     </row>
     <row r="14">
@@ -2777,13 +2777,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.075627614234958</v>
+        <v>5.072744235699506</v>
       </c>
       <c r="G15" t="n">
-        <v>5.237953993155882</v>
+        <v>5.236730202954233</v>
       </c>
       <c r="H15" t="n">
-        <v>5.361939349474199</v>
+        <v>5.361117632673025</v>
       </c>
     </row>
     <row r="16">
@@ -2805,13 +2805,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.367708092874992</v>
+        <v>6.373699293722082</v>
       </c>
       <c r="G16" t="n">
-        <v>6.555733993981558</v>
+        <v>6.564836703222423</v>
       </c>
       <c r="H16" t="n">
-        <v>6.712311227725481</v>
+        <v>6.718189808280587</v>
       </c>
     </row>
     <row r="17">
@@ -2833,13 +2833,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.064848621014697</v>
+        <v>3.066619888673478</v>
       </c>
       <c r="G17" t="n">
-        <v>4.429689299343201</v>
+        <v>4.427625174771611</v>
       </c>
       <c r="H17" t="n">
-        <v>5.678285833089822</v>
+        <v>5.672796687033919</v>
       </c>
     </row>
     <row r="18">
@@ -2861,13 +2861,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.180150403521643</v>
+        <v>3.171155539251651</v>
       </c>
       <c r="G18" t="n">
-        <v>3.456767148899859</v>
+        <v>3.452878757541359</v>
       </c>
       <c r="H18" t="n">
-        <v>3.968782098312546</v>
+        <v>3.966008804108584</v>
       </c>
     </row>
     <row r="19">
@@ -2889,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.089206338985151</v>
+        <v>2.088977411136755</v>
       </c>
       <c r="G19" t="n">
-        <v>2.207129567189043</v>
+        <v>2.206389744505143</v>
       </c>
       <c r="H19" t="n">
-        <v>2.330687820983126</v>
+        <v>2.330280630961115</v>
       </c>
     </row>
     <row r="20">
@@ -2917,13 +2917,13 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.776907411505261</v>
+        <v>5.430879744483859</v>
       </c>
       <c r="G20" t="n">
-        <v>5.194475984089943</v>
+        <v>6.006433117488635</v>
       </c>
       <c r="H20" t="n">
-        <v>5.807229304175822</v>
+        <v>6.555755247419387</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E2" t="n">
         <v>10028</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10026</v>
+        <v>10027</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.610656160649</v>
+        <v>102.6008026993783</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5720491719688</v>
+        <v>102.5661125263422</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03860698868021081</v>
+        <v>-0.03469017303610322</v>
       </c>
       <c r="T2" t="n">
-        <v>17.92604162512164</v>
+        <v>17.92062351338057</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06923260879783</v>
+        <v>36.06172544118274</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1411472183716064</v>
+        <v>0.1423018964492916</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7177902209877256</v>
+        <v>-0.7150419540580664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1411471346090758</v>
+        <v>0.1423018047162534</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.976169283246495</v>
+        <v>57.32052062049925</v>
       </c>
       <c r="Z2" t="n">
-        <v>95.01298267219498</v>
+        <v>106.4695191407171</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.56</v>
+        <v>110.448460446262</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E3" t="n">
         <v>14622</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14620</v>
+        <v>14621</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908743604651163</v>
+        <v>4.908533889610833</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966343458745827</v>
+        <v>4.966107357953438</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05759985409466432</v>
+        <v>0.05757346834260424</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34459503631689</v>
+        <v>1.34452882347733</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719123981228464</v>
+        <v>1.719068393455301</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813366103959403</v>
+        <v>0.7813596484901236</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5696689377253985</v>
+        <v>0.569707623386438</v>
       </c>
       <c r="X3" t="n">
-        <v>0.780297464296649</v>
+        <v>0.7803220722169903</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.088977411136755</v>
+        <v>2.036648661002087</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.206389744505143</v>
+        <v>2.17522151059124</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.330280630961115</v>
+        <v>2.228817204301075</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E4" t="n">
         <v>10256</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10254</v>
+        <v>10255</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.90926979715233</v>
+        <v>6.908868356899075</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.238879593366129</v>
+        <v>7.238418290059066</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3296097962137978</v>
+        <v>0.3295499331599916</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292439005830777</v>
+        <v>1.292336303109692</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682134273204272</v>
+        <v>1.682036653922765</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8677015366697989</v>
+        <v>0.8677264143690028</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375754981940627</v>
+        <v>0.7376205816432269</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471735175526196</v>
+        <v>0.8472128644742083</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.171155539251651</v>
+        <v>3.15798860772544</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45287875754136</v>
+        <v>3.285314402569126</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.966008804108584</v>
+        <v>3.361697499026302</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,52 +866,52 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.933439911797134</v>
+        <v>8.932461425422483</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824935191978479</v>
+        <v>2.824780058651026</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.304073515603294</v>
+        <v>9.302817670073887</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3706336038061614</v>
+        <v>0.3703562446514029</v>
       </c>
       <c r="T5" t="n">
-        <v>1.248616101907637</v>
+        <v>1.248154376069868</v>
       </c>
       <c r="U5" t="n">
-        <v>1.748091848049035</v>
+        <v>1.747739476590839</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8659452812928096</v>
+        <v>0.8659871181067802</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212474628102197</v>
+        <v>0.7213236772658937</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8594855425489892</v>
+        <v>0.8595381197067589</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.430879744483859</v>
+        <v>4.915063008282379</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.006433117488635</v>
+        <v>5.807668283475556</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.555755247419387</v>
+        <v>6.272632793077175</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E6" t="n">
         <v>8869</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8867</v>
+        <v>8868</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733654167136573</v>
+        <v>6.733684765448805</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022318259713997</v>
+        <v>7.022257630841382</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886640925774234</v>
+        <v>0.2885728653925764</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479646171024144</v>
+        <v>1.479526662078843</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908378230764743</v>
+        <v>1.908290396224969</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3044954816640217</v>
+        <v>0.304498424791817</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977081548819253</v>
+        <v>-0.1977296985368531</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2796358703613582</v>
+        <v>0.2796495789753848</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.373699293722082</v>
+        <v>6.367243332408655</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.564836703222423</v>
+        <v>6.528921870605316</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.718189808280587</v>
+        <v>6.710720653518013</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E7" t="n">
         <v>14230</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14228</v>
+        <v>14229</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581078050323306</v>
+        <v>5.581007695551338</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567627347115266</v>
+        <v>5.567564425719734</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01345070320803975</v>
+        <v>-0.01344326983160386</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167024627592115</v>
+        <v>1.167001082387597</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510260913989076</v>
+        <v>1.510236589845986</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047721387335367</v>
+        <v>0.5047738145659413</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0530381625950106</v>
+        <v>0.05302980187738748</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026217084248237</v>
+        <v>0.5026245850594895</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.910143396428452</v>
+        <v>4.878725694076523</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.991117609125702</v>
+        <v>4.971790057274675</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.050453708018097</v>
+        <v>5.028675659824047</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E8" t="n">
         <v>9028</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9026</v>
+        <v>9027</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.876634167959229</v>
+        <v>7.876370610391048</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115841609086177</v>
+        <v>8.115429295351564</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2392074411269477</v>
+        <v>0.2390586849605142</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446413252266368</v>
+        <v>1.44629383232391</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826016288081748</v>
+        <v>1.825921884123296</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078597935412262</v>
+        <v>0.8078778513577739</v>
       </c>
       <c r="W8" t="n">
-        <v>0.627475967835992</v>
+        <v>0.627499312875537</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978101357205185</v>
+        <v>0.7978483504513313</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.70659728544517</v>
+        <v>4.642522655539863</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.966618150640928</v>
+        <v>4.905659603388722</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.225116210896313</v>
+        <v>5.097888214388661</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E9" t="n">
         <v>13893</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13891</v>
+        <v>13892</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.611610215247283</v>
+        <v>7.611406744889146</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657233315385815</v>
+        <v>7.65700118848848</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0456231001385326</v>
+        <v>0.04559444359933561</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494384309402575</v>
+        <v>1.494330729691562</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942293888120434</v>
+        <v>1.942235915519591</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565986108234594</v>
+        <v>0.7566179019618615</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524723158395952</v>
+        <v>0.524751752265348</v>
       </c>
       <c r="X9" t="n">
-        <v>0.755187140590924</v>
+        <v>0.7552086440579195</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.072744235699506</v>
+        <v>5.047129765395894</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.236730202954233</v>
+        <v>5.203807805182032</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.361117632673025</v>
+        <v>5.308761271994134</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61693768093387</v>
+        <v>10.61682678017796</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3118760004414978</v>
+        <v>0.3117650996855837</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052570776139774</v>
+        <v>2.052614923211615</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698252311890559</v>
+        <v>2.698302791819056</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568505388140931</v>
+        <v>0.3568620043110433</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1205665344677969</v>
+        <v>-0.1206084628281776</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3364327795021363</v>
+        <v>0.3364623770576691</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.489485571553459</v>
+        <v>9.575548649984315</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.661028628929499</v>
+        <v>9.659872148405983</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.983611807071936</v>
+        <v>9.891824604095039</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E11" t="n">
         <v>13834</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13832</v>
+        <v>13833</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243460598611914</v>
+        <v>5.243343056459193</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579479090242113</v>
+        <v>0.4579134897360704</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216878908069908</v>
+        <v>5.216795642794859</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02658169054200617</v>
+        <v>-0.02654741366433308</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161648481263994</v>
+        <v>1.161632609468795</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483129429023117</v>
+        <v>1.483104015860813</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293136681427173</v>
+        <v>0.429343082294632</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09221577906315814</v>
+        <v>-0.09215366732678998</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275069848204408</v>
+        <v>0.4275359855361474</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.069263878698949</v>
+        <v>4.231110515828258</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.419002571048312</v>
+        <v>4.460348688367543</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.94419662509171</v>
+        <v>4.769065249266862</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E12" t="n">
         <v>4152</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4150</v>
+        <v>4151</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.471526746987951</v>
+        <v>7.470686822452421</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.20518708730741</v>
+        <v>2.205175953079179</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.644895430914917</v>
+        <v>7.644102422900386</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1733686839269654</v>
+        <v>0.1734156004479656</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9133212445940742</v>
+        <v>0.9132000924465764</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195275117831539</v>
+        <v>1.195160908811708</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8315980783635759</v>
+        <v>0.8317062247157639</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6585393335817828</v>
+        <v>0.6587611541963949</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8298336935053351</v>
+        <v>0.8299384094558884</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.27951707911047</v>
+        <v>4.295449381797899</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.370073736742098</v>
+        <v>4.756518480229799</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.187856183768762</v>
+        <v>5.876832300274501</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E13" t="n">
         <v>6487</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6485</v>
+        <v>6486</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.605055898226677</v>
+        <v>9.604553268578476</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02658889913596</v>
+        <v>10.02614417447024</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.421533000909285</v>
+        <v>0.4215909058917662</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691655074351911</v>
+        <v>1.691586757174874</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150875117360324</v>
+        <v>2.150783580344355</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231937030877825</v>
+        <v>0.8232088945382871</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486916580159064</v>
+        <v>0.6487111030178681</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8104262559375465</v>
+        <v>0.8104443205733073</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.729761635062327</v>
+        <v>7.568465115277675</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.361114476801497</v>
+        <v>8.246544712509211</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.524262664259133</v>
+        <v>8.504316312118211</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E14" t="n">
         <v>14074</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14072</v>
+        <v>14073</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.12877043064241</v>
+        <v>8.128532828821147</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077182685253118</v>
+        <v>0.9076075268817204</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199442254240395</v>
+        <v>8.199098638576451</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07067182359798403</v>
+        <v>0.07056580975530588</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756747580692275</v>
+        <v>1.756571706978795</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282757622965844</v>
+        <v>2.282608864507944</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808399849004419</v>
+        <v>0.7808762437541056</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653688567086914</v>
+        <v>0.5654234165340331</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804586837002664</v>
+        <v>0.7804973077910395</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.169804822589699</v>
+        <v>5.161764416706679</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.255897562255671</v>
+        <v>5.207451280787866</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.539820532080975</v>
+        <v>5.26737997204246</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.672531181217901</v>
+        <v>4.671715542521994</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82201569404232</v>
+        <v>11.82188204726626</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1418716889844631</v>
+        <v>-0.1420053357605198</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052366965071088</v>
+        <v>2.052397269777185</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6976156015866</v>
+        <v>2.697636408996666</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949895836601112</v>
+        <v>0.7949924025011333</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096032218969221</v>
+        <v>0.6095971994101201</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863453492445145</v>
+        <v>0.7863562134736138</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.531783128446474</v>
+        <v>8.13696003863059</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.22091764442863</v>
+        <v>10.74293946873275</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.90285020159987</v>
+        <v>11.89900937412829</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E16" t="n">
         <v>9837</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9835</v>
+        <v>9836</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363637925775292</v>
+        <v>8.363470821472141</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623990453460641</v>
+        <v>8.624200775553028</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2603525276853484</v>
+        <v>0.2607299540808846</v>
       </c>
       <c r="T16" t="n">
-        <v>3.592662631964989</v>
+        <v>3.592827349916453</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09193142257605</v>
+        <v>11.0914885514982</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04168027037037705</v>
+        <v>0.04166824817829683</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6099803602187148</v>
+        <v>-0.6100096977199561</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02501745773479902</v>
+        <v>0.02500497747794639</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.65313500445666</v>
+        <v>11.63818965591508</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.81355252620689</v>
+        <v>11.7429743843984</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.27567415228556</v>
+        <v>11.94223920296088</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E17" t="n">
         <v>2381</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.493152585119798</v>
+        <v>6.491387605042016</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.419666177549523</v>
+        <v>1.419457478005865</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.856399232413494</v>
+        <v>6.854693060451496</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3632466472936951</v>
+        <v>0.3633054554094782</v>
       </c>
       <c r="T17" t="n">
-        <v>2.018639411499311</v>
+        <v>2.018010253235474</v>
       </c>
       <c r="U17" t="n">
-        <v>2.554662365696587</v>
+        <v>2.554170895795325</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5331694541715023</v>
+        <v>0.533652900928599</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04467334312161741</v>
+        <v>0.04567517902319962</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5298227065817138</v>
+        <v>0.5302999643756429</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.374443099824393</v>
+        <v>2.328827949892189</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.170136565309023</v>
+        <v>3.146214679344246</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.519172589135704</v>
+        <v>3.947848611200896</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E18" t="n">
         <v>3240</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.47663959234095</v>
+        <v>6.47586878666255</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.671056436790835</v>
+        <v>6.67022445563808</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.194416844449884</v>
+        <v>0.1943556689755298</v>
       </c>
       <c r="T18" t="n">
-        <v>1.098167681515372</v>
+        <v>1.097859080783746</v>
       </c>
       <c r="U18" t="n">
-        <v>1.486504881054543</v>
+        <v>1.48629587587695</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6061701745812375</v>
+        <v>0.6064585807666943</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2270538489061109</v>
+        <v>0.2275525244860912</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6032775011553289</v>
+        <v>0.6035734308891246</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.066619888673478</v>
+        <v>3.043596613270648</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.427625174771611</v>
+        <v>4.408410408716898</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.672796687033919</v>
+        <v>5.203087330125467</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E19" t="n">
         <v>7194</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7192</v>
+        <v>7193</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33492269187987</v>
+        <v>10.33358772417628</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12692433568649</v>
+        <v>11.12631403233602</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7920016438066255</v>
+        <v>0.7927263081597422</v>
       </c>
       <c r="T19" t="n">
-        <v>2.052548389183963</v>
+        <v>2.053205662177394</v>
       </c>
       <c r="U19" t="n">
-        <v>2.776197787867929</v>
+        <v>2.777130074096686</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7271596023210478</v>
+        <v>0.7271717546915399</v>
       </c>
       <c r="W19" t="n">
-        <v>0.471037284126937</v>
+        <v>0.47107370073076</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6785511392492206</v>
+        <v>0.6784200112303838</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.327535179981441</v>
+        <v>7.331516778787006</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.441100373984497</v>
+        <v>7.413368689383338</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.594632687543739</v>
+        <v>7.439390679466608</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E20" t="n">
         <v>10644</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10642</v>
+        <v>10643</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.86077637729852</v>
+        <v>13.8604011751584</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.2373334877879</v>
+        <v>14.23687666432598</v>
       </c>
       <c r="R20" t="n">
-        <v>21.67640869875964</v>
+        <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.376557110489386</v>
+        <v>0.3764754891675813</v>
       </c>
       <c r="T20" t="n">
-        <v>1.256099554316596</v>
+        <v>1.255988888270577</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64772749714494</v>
+        <v>1.647650433644038</v>
       </c>
       <c r="V20" t="n">
-        <v>0.893418353958889</v>
+        <v>0.8934323929261473</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7787390333355673</v>
+        <v>0.7787659535479647</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8885968921736751</v>
+        <v>0.8886169305658758</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.790304756336552</v>
+        <v>9.787773888515677</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.18189447088567</v>
+        <v>9.978809588796841</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.72229813398619</v>
+        <v>10.08638564233168</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16691</v>
+        <v>16692</v>
       </c>
       <c r="E21" t="n">
         <v>10237</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9753771703504</v>
+        <v>130.9753961029711</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046102464468784</v>
+        <v>0.1046291790676373</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976929735280958</v>
+        <v>0.7977099410259019</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046356125737014</v>
+        <v>1.046373260468207</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649119350598822</v>
+        <v>0.8649074412773652</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7307583435784013</v>
+        <v>0.7307495255076344</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641693103538339</v>
+        <v>0.8641644020939663</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0329518813868</v>
+        <v>128.0734866835564</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.3418756637311</v>
+        <v>128.9315146774917</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5435815587171</v>
+        <v>130.0188375256969</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.327535179981441</v>
+        <v>7.331516778787006</v>
       </c>
       <c r="G2" t="n">
-        <v>7.441100373984497</v>
+        <v>7.413368689383337</v>
       </c>
       <c r="H2" t="n">
-        <v>7.594632687543739</v>
+        <v>7.439390679466608</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.910143396428452</v>
+        <v>4.878725694076523</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9911176091257</v>
+        <v>4.971790057274674</v>
       </c>
       <c r="H3" t="n">
-        <v>5.050453708018097</v>
+        <v>5.028675659824047</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.069263878698949</v>
+        <v>4.231110515828258</v>
       </c>
       <c r="G4" t="n">
-        <v>4.419002571048312</v>
+        <v>4.460348688367544</v>
       </c>
       <c r="H4" t="n">
-        <v>4.94419662509171</v>
+        <v>4.769065249266862</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.65313500445666</v>
+        <v>11.63818965591508</v>
       </c>
       <c r="G5" t="n">
-        <v>11.81355252620689</v>
+        <v>11.7429743843984</v>
       </c>
       <c r="H5" t="n">
-        <v>12.27567415228556</v>
+        <v>11.94223920296088</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.976169283246495</v>
+        <v>57.32052062049925</v>
       </c>
       <c r="G6" t="n">
-        <v>95.01298267219499</v>
+        <v>106.4695191407171</v>
       </c>
       <c r="H6" t="n">
-        <v>111.56</v>
+        <v>110.448460446262</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.531783128446474</v>
+        <v>8.13696003863059</v>
       </c>
       <c r="G7" t="n">
-        <v>11.22091764442863</v>
+        <v>10.74293946873275</v>
       </c>
       <c r="H7" t="n">
-        <v>11.90285020159987</v>
+        <v>11.89900937412829</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.729761635062327</v>
+        <v>7.568465115277675</v>
       </c>
       <c r="G8" t="n">
-        <v>8.361114476801495</v>
+        <v>8.246544712509211</v>
       </c>
       <c r="H8" t="n">
-        <v>8.524262664259133</v>
+        <v>8.504316312118211</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.27951707911047</v>
+        <v>4.295449381797899</v>
       </c>
       <c r="G9" t="n">
-        <v>4.370073736742097</v>
+        <v>4.756518480229799</v>
       </c>
       <c r="H9" t="n">
-        <v>5.187856183768762</v>
+        <v>5.876832300274501</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.70659728544517</v>
+        <v>4.642522655539863</v>
       </c>
       <c r="G10" t="n">
-        <v>4.966618150640929</v>
+        <v>4.905659603388722</v>
       </c>
       <c r="H10" t="n">
-        <v>5.225116210896313</v>
+        <v>5.097888214388661</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.790304756336552</v>
+        <v>9.787773888515677</v>
       </c>
       <c r="G11" t="n">
-        <v>10.18189447088567</v>
+        <v>9.978809588796841</v>
       </c>
       <c r="H11" t="n">
-        <v>10.72229813398619</v>
+        <v>10.08638564233168</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.374443099824393</v>
+        <v>2.328827949892189</v>
       </c>
       <c r="G12" t="n">
-        <v>3.170136565309023</v>
+        <v>3.146214679344246</v>
       </c>
       <c r="H12" t="n">
-        <v>4.519172589135704</v>
+        <v>3.947848611200896</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.169804822589699</v>
+        <v>5.161764416706679</v>
       </c>
       <c r="G13" t="n">
-        <v>5.255897562255671</v>
+        <v>5.207451280787866</v>
       </c>
       <c r="H13" t="n">
-        <v>5.539820532080975</v>
+        <v>5.26737997204246</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.489485571553459</v>
+        <v>9.575548649984315</v>
       </c>
       <c r="G14" t="n">
-        <v>9.6610286289295</v>
+        <v>9.659872148405981</v>
       </c>
       <c r="H14" t="n">
-        <v>9.983611807071936</v>
+        <v>9.891824604095039</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.072744235699506</v>
+        <v>5.047129765395894</v>
       </c>
       <c r="G15" t="n">
-        <v>5.236730202954233</v>
+        <v>5.203807805182032</v>
       </c>
       <c r="H15" t="n">
-        <v>5.361117632673025</v>
+        <v>5.308761271994134</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.373699293722082</v>
+        <v>6.367243332408655</v>
       </c>
       <c r="G16" t="n">
-        <v>6.564836703222423</v>
+        <v>6.528921870605318</v>
       </c>
       <c r="H16" t="n">
-        <v>6.718189808280587</v>
+        <v>6.710720653518013</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.066619888673478</v>
+        <v>3.043596613270648</v>
       </c>
       <c r="G17" t="n">
-        <v>4.427625174771611</v>
+        <v>4.408410408716897</v>
       </c>
       <c r="H17" t="n">
-        <v>5.672796687033919</v>
+        <v>5.203087330125467</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.171155539251651</v>
+        <v>3.15798860772544</v>
       </c>
       <c r="G18" t="n">
-        <v>3.452878757541359</v>
+        <v>3.285314402569126</v>
       </c>
       <c r="H18" t="n">
-        <v>3.966008804108584</v>
+        <v>3.361697499026302</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.088977411136755</v>
+        <v>2.036648661002087</v>
       </c>
       <c r="G19" t="n">
-        <v>2.206389744505143</v>
+        <v>2.17522151059124</v>
       </c>
       <c r="H19" t="n">
-        <v>2.330280630961115</v>
+        <v>2.228817204301075</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.430879744483859</v>
+        <v>4.915063008282379</v>
       </c>
       <c r="G20" t="n">
-        <v>6.006433117488635</v>
+        <v>5.807668283475556</v>
       </c>
       <c r="H20" t="n">
-        <v>6.555755247419387</v>
+        <v>6.272632793077175</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0329518813868</v>
+        <v>128.0734866835564</v>
       </c>
       <c r="G21" t="n">
-        <v>128.3418756637311</v>
+        <v>128.9315146774917</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5435815587171</v>
+        <v>130.0188375256969</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E2" t="n">
+        <v>10029</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10028</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10027</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6008026993783</v>
+        <v>102.5909541949209</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5661125263422</v>
+        <v>102.5543512829361</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03469017303610322</v>
+        <v>-0.03660291198474812</v>
       </c>
       <c r="T2" t="n">
-        <v>17.92062351338057</v>
+        <v>17.93041381406934</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06172544118274</v>
+        <v>36.07538334307606</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1423018964492916</v>
+        <v>0.1427168182870194</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7150419540580664</v>
+        <v>-0.7143134626403118</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1423018047162534</v>
+        <v>0.1427167311742145</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.32052062049925</v>
+        <v>53.1157700277887</v>
       </c>
       <c r="Z2" t="n">
-        <v>106.4695191407171</v>
+        <v>95.11316601334288</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.448460446262</v>
+        <v>109.4326465274823</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E3" t="n">
+        <v>14623</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14622</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14621</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908533889610833</v>
+        <v>4.908326425933525</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966107357953438</v>
+        <v>4.965925040178926</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05757346834260424</v>
+        <v>0.05759861424540109</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34452882347733</v>
+        <v>1.344453410402844</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719068393455301</v>
+        <v>1.719005850166859</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813596484901236</v>
+        <v>0.7813784853499472</v>
       </c>
       <c r="W3" t="n">
-        <v>0.569707623386438</v>
+        <v>0.5697489317549542</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803220722169903</v>
+        <v>0.780339567535566</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.036648661002087</v>
+        <v>1.988215117902707</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.17522151059124</v>
+        <v>2.152210215200745</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.228817204301075</v>
+        <v>2.226944566544566</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E4" t="n">
+        <v>10257</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10256</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10255</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.908868356899075</v>
+        <v>6.908463826053042</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.238418290059066</v>
+        <v>7.238019802176263</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295499331599916</v>
+        <v>0.3295559761232196</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292336303109692</v>
+        <v>1.292273430810388</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682036653922765</v>
+        <v>1.681945383706387</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8677264143690028</v>
+        <v>0.8677496198086201</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7376205816432269</v>
+        <v>0.7376643041649156</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472128644742083</v>
+        <v>0.8472321607249728</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.15798860772544</v>
+        <v>2.967184642857144</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.285314402569126</v>
+        <v>3.239990668669574</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.361697499026302</v>
+        <v>3.359428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824780058651026</v>
+        <v>2.824625152625153</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302817670073887</v>
+        <v>9.302726364737889</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3703562446514029</v>
+        <v>0.3702649393154067</v>
       </c>
       <c r="T5" t="n">
-        <v>1.248154376069868</v>
+        <v>1.248090475678901</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747739476590839</v>
+        <v>1.747670072090551</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8659871181067802</v>
+        <v>0.8660005678861867</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213236772658937</v>
+        <v>0.7213458098630541</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8595381197067589</v>
+        <v>0.8595561157629211</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.915063008282379</v>
+        <v>4.74573494764149</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.807668283475556</v>
+        <v>5.669587888733165</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.272632793077175</v>
+        <v>6.268263046702717</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E6" t="n">
+        <v>8870</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8869</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8868</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733684765448805</v>
+        <v>6.733749182545947</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022257630841382</v>
+        <v>7.022375462375077</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2885728653925764</v>
+        <v>0.2886262798291301</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479526662078843</v>
+        <v>1.479415881102846</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908290396224969</v>
+        <v>1.90819259599411</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304498424791817</v>
+        <v>0.3044825982316209</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977296985368531</v>
+        <v>-0.197727484203009</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2796495789753848</v>
+        <v>0.2796237212449694</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.367243332408655</v>
+        <v>6.368224895752896</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.528921870605316</v>
+        <v>6.502327340893666</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.710720653518013</v>
+        <v>6.714477886690696</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E7" t="n">
+        <v>14231</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14230</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14229</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581007695551338</v>
+        <v>5.580934539704849</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567564425719734</v>
+        <v>5.567494792702547</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01344326983160386</v>
+        <v>-0.01343974700230214</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167001082387597</v>
+        <v>1.166962170024339</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510236589845986</v>
+        <v>1.51019283816638</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047738145659413</v>
+        <v>0.5047825387208995</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05302980187738748</v>
+        <v>0.05304806217859881</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026245850594895</v>
+        <v>0.5026331112401481</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.878725694076523</v>
+        <v>4.861148608843003</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.971790057274675</v>
+        <v>4.95797072720199</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.028675659824047</v>
+        <v>5.028072318002751</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E8" t="n">
+        <v>9029</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9028</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9027</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.876370610391048</v>
+        <v>7.876073327425787</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115429295351564</v>
+        <v>8.115193574541697</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2390586849605142</v>
+        <v>0.2391202471159111</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44629383232391</v>
+        <v>1.446141957345154</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825921884123296</v>
+        <v>1.825820317471667</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078778513577739</v>
+        <v>0.8078928954712887</v>
       </c>
       <c r="W8" t="n">
-        <v>0.627499312875537</v>
+        <v>0.6275326951334816</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978483504513313</v>
+        <v>0.7978529700324556</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.642522655539863</v>
+        <v>4.614520330355905</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.905659603388722</v>
+        <v>4.872519382515501</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.097888214388661</v>
+        <v>5.098574327122153</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E9" t="n">
+        <v>13894</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13893</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13892</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.611406744889146</v>
+        <v>7.611209781904557</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65700118848848</v>
+        <v>7.656820891345428</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04559444359933561</v>
+        <v>0.04561110944087127</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494330729691562</v>
+        <v>1.494257934321045</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942235915519591</v>
+        <v>1.942172101660859</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566179019618615</v>
+        <v>0.7566316779430967</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524751752265348</v>
+        <v>0.5247810414458658</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552086440579195</v>
+        <v>0.7552216526827791</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.047129765395894</v>
+        <v>5.042710622710622</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.203807805182032</v>
+        <v>5.183351829422563</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.308761271994134</v>
+        <v>5.308428937728937</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61682678017796</v>
+        <v>10.61671808092395</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3117650996855837</v>
+        <v>0.3116564004315795</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052614923211615</v>
+        <v>2.05265913478933</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698302791819056</v>
+        <v>2.698354282897013</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568620043110433</v>
+        <v>0.3568730607394258</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1206084628281776</v>
+        <v>-0.1206512318520578</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3364623770576691</v>
+        <v>0.3364915437249053</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.575548649984315</v>
+        <v>9.492744812394813</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.659872148405983</v>
+        <v>9.641669457016365</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.891824604095039</v>
+        <v>9.89225916482464</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E11" t="n">
+        <v>13835</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13834</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13833</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243343056459193</v>
+        <v>5.243229145583345</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579134897360704</v>
+        <v>0.4579186813186814</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216795642794859</v>
+        <v>5.216711947751373</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02654741366433308</v>
+        <v>-0.02651719783197205</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161632609468795</v>
+        <v>1.161586945604562</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483104015860813</v>
+        <v>1.483055974032171</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429343082294632</v>
+        <v>0.4293782263448069</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09215366732678998</v>
+        <v>-0.0920645258503292</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275359855361474</v>
+        <v>0.4275694745173328</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.231110515828258</v>
+        <v>4.062654077237866</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.460348688367543</v>
+        <v>4.408004204810811</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.769065249266862</v>
+        <v>4.768915750915751</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E12" t="n">
+        <v>4153</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4152</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4151</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.470686822452421</v>
+        <v>7.469829841040463</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205175953079179</v>
+        <v>2.205208791208791</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.644102422900386</v>
+        <v>7.64309839908581</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1734156004479656</v>
+        <v>0.1732685580453475</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9132000924465764</v>
+        <v>0.9130638700341051</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195160908811708</v>
+        <v>1.195017309929815</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8317062247157639</v>
+        <v>0.8318406363668258</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6587611541963949</v>
+        <v>0.6590093605930606</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8299384094558884</v>
+        <v>0.8300785450024586</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.295449381797899</v>
+        <v>4.286115474934287</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.756518480229799</v>
+        <v>4.814692895961036</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.876832300274501</v>
+        <v>5.808383794661954</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E13" t="n">
+        <v>6488</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6487</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6486</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.604553268578476</v>
+        <v>9.604057730846307</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02614417447024</v>
+        <v>10.02598320665481</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4215909058917662</v>
+        <v>0.4219254758085073</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691586757174874</v>
+        <v>1.691614051215331</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150783580344355</v>
+        <v>2.150693815799494</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232088945382871</v>
+        <v>0.823217060530793</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6487111030178681</v>
+        <v>0.6487287608000581</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8104443205733073</v>
+        <v>0.8104165434878653</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.568465115277675</v>
+        <v>7.229112651980258</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.246544712509211</v>
+        <v>8.143101036166557</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.504316312118211</v>
+        <v>8.50379774371625</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E14" t="n">
+        <v>14075</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14074</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14073</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.128532828821147</v>
+        <v>8.128300945004973</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9076075268817204</v>
+        <v>0.9076312576312576</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199098638576451</v>
+        <v>8.198895731276474</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07056580975530588</v>
+        <v>0.07059478627150001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756571706978795</v>
+        <v>1.756470107146309</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282608864507944</v>
+        <v>2.282525958749215</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808762437541056</v>
+        <v>0.7808884066857629</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654234165340331</v>
+        <v>0.5654515345832736</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804973077910395</v>
+        <v>0.7805088460623727</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.161764416706679</v>
+        <v>5.156142991269625</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.207451280787866</v>
+        <v>5.194383069963163</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.26737997204246</v>
+        <v>5.25874998222993</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.671715542521994</v>
+        <v>4.670901098901099</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82188204726626</v>
+        <v>11.82174913104437</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1420053357605198</v>
+        <v>-0.1421382519824174</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052397269777185</v>
+        <v>2.052426653513012</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697636408996666</v>
+        <v>2.697659653913385</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949924025011333</v>
+        <v>0.7949949275314747</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095971994101201</v>
+        <v>0.6095904713576263</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863562134736138</v>
+        <v>0.7863669454787632</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.13696003863059</v>
+        <v>7.888653769857086</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.74293946873275</v>
+        <v>10.3920171509085</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89900937412829</v>
+        <v>11.89139092678375</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E16" t="n">
+        <v>9838</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9837</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9836</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363470821472141</v>
+        <v>8.363302734573548</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624200775553028</v>
+        <v>8.624096883204006</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2607299540808846</v>
+        <v>0.2607941486304572</v>
       </c>
       <c r="T16" t="n">
-        <v>3.592827349916453</v>
+        <v>3.593112350950778</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0914885514982</v>
+        <v>11.09107148820075</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04166824817829683</v>
+        <v>0.04164768881072186</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6100096977199561</v>
+        <v>-0.6100464373723504</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02500497747794639</v>
+        <v>0.02498477809945387</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.63818965591508</v>
+        <v>11.63492483321416</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.7429743843984</v>
+        <v>11.73042726421356</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.94223920296088</v>
+        <v>11.9396961951139</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E17" t="n">
+        <v>2382</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2381</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2380</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.491387605042016</v>
+        <v>6.489618857622848</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.419457478005865</v>
+        <v>1.420714285714286</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.854693060451496</v>
+        <v>6.852547372617106</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3633054554094782</v>
+        <v>0.3629285149942579</v>
       </c>
       <c r="T17" t="n">
-        <v>2.018010253235474</v>
+        <v>2.017179091534754</v>
       </c>
       <c r="U17" t="n">
-        <v>2.554170895795325</v>
+        <v>2.55353736646761</v>
       </c>
       <c r="V17" t="n">
-        <v>0.533652900928599</v>
+        <v>0.5342583463879412</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04567517902319962</v>
+        <v>0.04678642839451719</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5302999643756429</v>
+        <v>0.5309052815115041</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.328827949892189</v>
+        <v>2.29399121129713</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.146214679344246</v>
+        <v>3.089555526118033</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.947848611200896</v>
+        <v>3.943509208893979</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E18" t="n">
+        <v>3241</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3240</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3239</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.47586878666255</v>
+        <v>6.475126234567901</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.67022445563808</v>
+        <v>6.669438876549626</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1943556689755298</v>
+        <v>0.1943126419817253</v>
       </c>
       <c r="T18" t="n">
-        <v>1.097859080783746</v>
+        <v>1.097446176081643</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48629587587695</v>
+        <v>1.485976139840927</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6064585807666943</v>
+        <v>0.6067555980326074</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2275525244860912</v>
+        <v>0.228128622295925</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6035734308891246</v>
+        <v>0.6038693036047897</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.043596613270648</v>
+        <v>3.34127451895791</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.408410408716898</v>
+        <v>4.350851636008524</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.203087330125467</v>
+        <v>5.201825584040268</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E19" t="n">
+        <v>7195</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7194</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7193</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33358772417628</v>
+        <v>10.33224791492911</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12631403233602</v>
+        <v>11.12539533031866</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7927263081597422</v>
+        <v>0.7931474153895515</v>
       </c>
       <c r="T19" t="n">
-        <v>2.053205662177394</v>
+        <v>2.053872256050626</v>
       </c>
       <c r="U19" t="n">
-        <v>2.777130074096686</v>
+        <v>2.778020932486261</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7271717546915399</v>
+        <v>0.7271934559077536</v>
       </c>
       <c r="W19" t="n">
-        <v>0.47107370073076</v>
+        <v>0.4711291148740067</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6784200112303838</v>
+        <v>0.6783632569877633</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.331516778787006</v>
+        <v>7.276804658833231</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.413368689383338</v>
+        <v>7.384338561946412</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.439390679466608</v>
+        <v>7.434567649038179</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E20" t="n">
+        <v>10645</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10644</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10643</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8604011751584</v>
+        <v>13.86002040653991</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23687666432598</v>
+        <v>14.23647792930671</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764754891675813</v>
+        <v>0.376457522766794</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255988888270577</v>
+        <v>1.255889795176839</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647650433644038</v>
+        <v>1.647567463488826</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8934323929261473</v>
+        <v>0.8934471558608359</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7787659535479647</v>
+        <v>0.7787952685981459</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8886169305658758</v>
+        <v>0.8886322227497037</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.787773888515677</v>
+        <v>9.703402210519579</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.978809588796841</v>
+        <v>9.921616090696869</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.08638564233168</v>
+        <v>10.08070130340294</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16692</v>
+        <v>16693</v>
       </c>
       <c r="E21" t="n">
-        <v>10237</v>
+        <v>10241</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10237</v>
+        <v>10240</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8707669239035</v>
+        <v>130.8697930664063</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9753961029711</v>
+        <v>130.9741821213284</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046291790676373</v>
+        <v>0.1043890549221336</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7977099410259019</v>
+        <v>0.7976167818951817</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046373260468207</v>
+        <v>1.046256932828051</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649074412773652</v>
+        <v>0.865017878935359</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7307495255076344</v>
+        <v>0.730945063571059</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641644020939663</v>
+        <v>0.8642896633743109</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0734866835564</v>
+        <v>128.0659421023421</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9315146774917</v>
+        <v>128.9868067669487</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.0188375256969</v>
+        <v>129.7960155016064</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.331516778787006</v>
+        <v>7.276804658833231</v>
       </c>
       <c r="G2" t="n">
-        <v>7.413368689383337</v>
+        <v>7.384338561946412</v>
       </c>
       <c r="H2" t="n">
-        <v>7.439390679466608</v>
+        <v>7.434567649038179</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.878725694076523</v>
+        <v>4.861148608843003</v>
       </c>
       <c r="G3" t="n">
-        <v>4.971790057274674</v>
+        <v>4.957970727201991</v>
       </c>
       <c r="H3" t="n">
-        <v>5.028675659824047</v>
+        <v>5.028072318002751</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.231110515828258</v>
+        <v>4.062654077237866</v>
       </c>
       <c r="G4" t="n">
-        <v>4.460348688367544</v>
+        <v>4.408004204810812</v>
       </c>
       <c r="H4" t="n">
-        <v>4.769065249266862</v>
+        <v>4.768915750915751</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.63818965591508</v>
+        <v>11.63492483321416</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7429743843984</v>
+        <v>11.73042726421356</v>
       </c>
       <c r="H5" t="n">
-        <v>11.94223920296088</v>
+        <v>11.9396961951139</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>57.32052062049925</v>
+        <v>53.1157700277887</v>
       </c>
       <c r="G6" t="n">
-        <v>106.4695191407171</v>
+        <v>95.11316601334289</v>
       </c>
       <c r="H6" t="n">
-        <v>110.448460446262</v>
+        <v>109.4326465274823</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.13696003863059</v>
+        <v>7.888653769857086</v>
       </c>
       <c r="G7" t="n">
-        <v>10.74293946873275</v>
+        <v>10.3920171509085</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89900937412829</v>
+        <v>11.89139092678375</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.568465115277675</v>
+        <v>7.229112651980258</v>
       </c>
       <c r="G8" t="n">
-        <v>8.246544712509211</v>
+        <v>8.143101036166557</v>
       </c>
       <c r="H8" t="n">
-        <v>8.504316312118211</v>
+        <v>8.50379774371625</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.295449381797899</v>
+        <v>4.286115474934287</v>
       </c>
       <c r="G9" t="n">
-        <v>4.756518480229799</v>
+        <v>4.814692895961035</v>
       </c>
       <c r="H9" t="n">
-        <v>5.876832300274501</v>
+        <v>5.808383794661954</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.642522655539863</v>
+        <v>4.614520330355905</v>
       </c>
       <c r="G10" t="n">
-        <v>4.905659603388722</v>
+        <v>4.872519382515501</v>
       </c>
       <c r="H10" t="n">
-        <v>5.097888214388661</v>
+        <v>5.098574327122153</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.787773888515677</v>
+        <v>9.703402210519579</v>
       </c>
       <c r="G11" t="n">
-        <v>9.978809588796841</v>
+        <v>9.921616090696869</v>
       </c>
       <c r="H11" t="n">
-        <v>10.08638564233168</v>
+        <v>10.08070130340294</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.328827949892189</v>
+        <v>2.29399121129713</v>
       </c>
       <c r="G12" t="n">
-        <v>3.146214679344246</v>
+        <v>3.089555526118033</v>
       </c>
       <c r="H12" t="n">
-        <v>3.947848611200896</v>
+        <v>3.943509208893979</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.161764416706679</v>
+        <v>5.156142991269625</v>
       </c>
       <c r="G13" t="n">
-        <v>5.207451280787866</v>
+        <v>5.194383069963164</v>
       </c>
       <c r="H13" t="n">
-        <v>5.26737997204246</v>
+        <v>5.25874998222993</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.575548649984315</v>
+        <v>9.492744812394813</v>
       </c>
       <c r="G14" t="n">
-        <v>9.659872148405981</v>
+        <v>9.641669457016363</v>
       </c>
       <c r="H14" t="n">
-        <v>9.891824604095039</v>
+        <v>9.89225916482464</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.047129765395894</v>
+        <v>5.042710622710622</v>
       </c>
       <c r="G15" t="n">
-        <v>5.203807805182032</v>
+        <v>5.183351829422563</v>
       </c>
       <c r="H15" t="n">
-        <v>5.308761271994134</v>
+        <v>5.308428937728937</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.367243332408655</v>
+        <v>6.368224895752896</v>
       </c>
       <c r="G16" t="n">
-        <v>6.528921870605318</v>
+        <v>6.502327340893666</v>
       </c>
       <c r="H16" t="n">
-        <v>6.710720653518013</v>
+        <v>6.714477886690696</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.043596613270648</v>
+        <v>3.34127451895791</v>
       </c>
       <c r="G17" t="n">
-        <v>4.408410408716897</v>
+        <v>4.350851636008524</v>
       </c>
       <c r="H17" t="n">
-        <v>5.203087330125467</v>
+        <v>5.201825584040268</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.15798860772544</v>
+        <v>2.967184642857144</v>
       </c>
       <c r="G18" t="n">
-        <v>3.285314402569126</v>
+        <v>3.239990668669574</v>
       </c>
       <c r="H18" t="n">
-        <v>3.361697499026302</v>
+        <v>3.359428571428571</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.036648661002087</v>
+        <v>1.988215117902707</v>
       </c>
       <c r="G19" t="n">
-        <v>2.17522151059124</v>
+        <v>2.152210215200744</v>
       </c>
       <c r="H19" t="n">
-        <v>2.228817204301075</v>
+        <v>2.226944566544566</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.915063008282379</v>
+        <v>4.74573494764149</v>
       </c>
       <c r="G20" t="n">
-        <v>5.807668283475556</v>
+        <v>5.669587888733165</v>
       </c>
       <c r="H20" t="n">
-        <v>6.272632793077175</v>
+        <v>6.268263046702717</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0734866835564</v>
+        <v>128.0659421023421</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9315146774917</v>
+        <v>128.9868067669487</v>
       </c>
       <c r="H21" t="n">
-        <v>130.0188375256969</v>
+        <v>129.7960155016064</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E2" t="n">
+        <v>10030</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10029</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10028</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5909541949209</v>
+        <v>102.5811086515771</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5543512829361</v>
+        <v>102.5416270350433</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03660291198474812</v>
+        <v>-0.03948161653378208</v>
       </c>
       <c r="T2" t="n">
-        <v>17.93041381406934</v>
+        <v>17.9356551563071</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07538334307606</v>
+        <v>36.08624750433702</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1427168182870194</v>
+        <v>0.1434456989177813</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7143134626403118</v>
+        <v>-0.7133231700225506</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1427167311742145</v>
+        <v>0.1434456034649185</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.1157700277887</v>
+        <v>53.06797224700058</v>
       </c>
       <c r="Z2" t="n">
-        <v>95.11316601334288</v>
+        <v>87.97940267175927</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.4326465274823</v>
+        <v>108.0936829003284</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E3" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14623</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14622</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908326425933525</v>
+        <v>4.908121897011558</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965925040178926</v>
+        <v>4.965748199396312</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05759861424540109</v>
+        <v>0.05762630238475602</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344453410402844</v>
+        <v>1.34437478996458</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719005850166859</v>
+        <v>1.718942873668503</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813784853499472</v>
+        <v>0.7813966422509192</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5697489317549542</v>
+        <v>0.5697893505277447</v>
       </c>
       <c r="X3" t="n">
-        <v>0.780339567535566</v>
+        <v>0.7803562584368032</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.988215117902707</v>
+        <v>1.946166915263543</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.152210215200745</v>
+        <v>2.117352032572563</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.226944566544566</v>
+        <v>2.209625489185321</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E4" t="n">
+        <v>10258</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10257</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10256</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.908463826053042</v>
+        <v>6.908057424198109</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.238019802176263</v>
+        <v>7.237614290452756</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295559761232196</v>
+        <v>0.3295568662546469</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292273430810388</v>
+        <v>1.292206751589175</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681945383706387</v>
+        <v>1.681849025793509</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8677496198086201</v>
+        <v>0.8677738616248784</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7376643041649156</v>
+        <v>0.7377099904053721</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472321607249728</v>
+        <v>0.8472534318344405</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.967184642857144</v>
+        <v>2.903645680819912</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.239990668669574</v>
+        <v>3.200038866781835</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.359428571428571</v>
+        <v>3.35892972181552</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824625152625153</v>
+        <v>2.824470473401659</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302726364737889</v>
+        <v>9.302647034670446</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3702649393154067</v>
+        <v>0.3701856092479639</v>
       </c>
       <c r="T5" t="n">
-        <v>1.248090475678901</v>
+        <v>1.24803040447265</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747670072090551</v>
+        <v>1.747604022532564</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660005678861867</v>
+        <v>0.866013345660223</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213458098630541</v>
+        <v>0.7213668717769641</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8595561157629211</v>
+        <v>0.8595728495151885</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.74573494764149</v>
+        <v>4.438173362946387</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.669587888733165</v>
+        <v>5.562998555277025</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.268263046702717</v>
+        <v>6.279052150979457</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E6" t="n">
+        <v>8871</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8870</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8869</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733749182545947</v>
+        <v>6.733826550169109</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022375462375077</v>
+        <v>7.022494547343361</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886262798291301</v>
+        <v>0.2886679971742511</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479415881102846</v>
+        <v>1.479317538657916</v>
       </c>
       <c r="U6" t="n">
-        <v>1.90819259599411</v>
+        <v>1.908103634839282</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3044825982316209</v>
+        <v>0.3044612661346087</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.197727484203009</v>
+        <v>-0.1977299253521807</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2796237212449694</v>
+        <v>0.2795921650838061</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.368224895752896</v>
+        <v>6.36812469922045</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.502327340893666</v>
+        <v>6.459169544809944</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.714477886690696</v>
+        <v>6.652185773371299</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E7" t="n">
+        <v>14232</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14231</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14230</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580934539704849</v>
+        <v>5.580867015670016</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567494792702547</v>
+        <v>5.567445207855584</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01343974700230214</v>
+        <v>-0.01342180781443205</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166962170024339</v>
+        <v>1.166903495552381</v>
       </c>
       <c r="U7" t="n">
-        <v>1.51019283816638</v>
+        <v>1.510140977563999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047825387208995</v>
+        <v>0.5047915202000473</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05304806217859881</v>
+        <v>0.0530720681329131</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026331112401481</v>
+        <v>0.5026413800264922</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.861148608843003</v>
+        <v>4.828612493899463</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.95797072720199</v>
+        <v>4.933667894097528</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.028072318002751</v>
+        <v>5.009223224622557</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E8" t="n">
+        <v>9030</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9029</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9028</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.876073327425787</v>
+        <v>7.875809613467715</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115193574541697</v>
+        <v>8.115001462792589</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2391202471159111</v>
+        <v>0.2391918493248731</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446141957345154</v>
+        <v>1.446028323866907</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825820317471667</v>
+        <v>1.825735563653098</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078928954712887</v>
+        <v>0.8079001511183116</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275326951334816</v>
+        <v>0.6275521510567117</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978529700324556</v>
+        <v>0.797848561969281</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.614520330355905</v>
+        <v>4.61871868984707</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.872519382515501</v>
+        <v>4.821873304490335</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.098574327122153</v>
+        <v>5.042463288702553</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E9" t="n">
+        <v>13895</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13894</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13893</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.611209781904557</v>
+        <v>7.611019864689795</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.656820891345428</v>
+        <v>7.656637313041189</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04561110944087127</v>
+        <v>0.04561744835139494</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494257934321045</v>
+        <v>1.494179261242186</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942172101660859</v>
+        <v>1.942106808536684</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566316779430967</v>
+        <v>0.75664536853902</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5247810414458658</v>
+        <v>0.5248087914499141</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552216526827791</v>
+        <v>0.7552349664543068</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.042710622710622</v>
+        <v>5.049284692099633</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.183351829422563</v>
+        <v>5.157797684854041</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.308428937728937</v>
+        <v>5.288561493411421</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61671808092395</v>
+        <v>10.61661693095808</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3116564004315795</v>
+        <v>0.3115552504657125</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05265913478933</v>
+        <v>2.052710500658617</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698354282897013</v>
+        <v>2.698412224372817</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568730607394258</v>
+        <v>0.356880221985833</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1206512318520578</v>
+        <v>-0.1206993596192583</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3364915437249053</v>
+        <v>0.3365164140571438</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.492744812394813</v>
+        <v>9.556995459141131</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.641669457016365</v>
+        <v>9.641273159924154</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.89225916482464</v>
+        <v>9.762991350135364</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E11" t="n">
+        <v>13836</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13835</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13834</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243229145583345</v>
+        <v>5.243149765088544</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579186813186814</v>
+        <v>0.4579238653001464</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216711947751373</v>
+        <v>5.216666314869683</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02651719783197205</v>
+        <v>-0.0264834502188602</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161586945604562</v>
+        <v>1.161506965413583</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483055974032171</v>
+        <v>1.482999687885503</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293782263448069</v>
+        <v>0.4293945634027528</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0920645258503292</v>
+        <v>-0.0920133001339678</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275694745173328</v>
+        <v>0.4275843771801608</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.062654077237866</v>
+        <v>4.223123411219237</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.408004204810811</v>
+        <v>4.39185417521629</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.768915750915751</v>
+        <v>4.608910077320688</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E12" t="n">
+        <v>4154</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4153</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4152</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.469829841040463</v>
+        <v>7.468938959788105</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205208791208791</v>
+        <v>2.205241581259151</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.64309839908581</v>
+        <v>7.642093989796388</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732685580453475</v>
+        <v>0.1731550300082826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9130638700341051</v>
+        <v>0.9129536384558204</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195017309929815</v>
+        <v>1.194896887067312</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8318406363668258</v>
+        <v>0.8319751044229403</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6590093605930606</v>
+        <v>0.6592641426745507</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8300785450024586</v>
+        <v>0.8302168388482178</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.286115474934287</v>
+        <v>4.291614664416267</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.814692895961036</v>
+        <v>4.962983297038839</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.808383794661954</v>
+        <v>5.741303811735539</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E13" t="n">
+        <v>6489</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6488</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6487</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.604057730846307</v>
+        <v>9.603578529593094</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02598320665481</v>
+        <v>10.02584931315418</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4219254758085073</v>
+        <v>0.4222707835610801</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691614051215331</v>
+        <v>1.691653641671577</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150693815799494</v>
+        <v>2.150606501828517</v>
       </c>
       <c r="V13" t="n">
-        <v>0.823217060530793</v>
+        <v>0.8232232779415114</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6487287608000581</v>
+        <v>0.6487428791346607</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8104165434878653</v>
+        <v>0.810385550275651</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.229112651980258</v>
+        <v>6.591017974418374</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.143101036166557</v>
+        <v>7.908443883170754</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.50379774371625</v>
+        <v>8.502869834735165</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E14" t="n">
+        <v>14076</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14075</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14074</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.128300945004973</v>
+        <v>8.128080639431616</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9076312576312576</v>
+        <v>0.90765495363592</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198895731276474</v>
+        <v>8.198709027835003</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07059478627150001</v>
+        <v>0.07062838840338521</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756470107146309</v>
+        <v>1.756373311966857</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282525958749215</v>
+        <v>2.282456696108319</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808884066857629</v>
+        <v>0.780896363667404</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654515345832736</v>
+        <v>0.5654717910847038</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805088460623727</v>
+        <v>0.7805161081670825</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.156142991269625</v>
+        <v>5.151922173050823</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.194383069963163</v>
+        <v>5.17990099456299</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.25874998222993</v>
+        <v>5.228145390428562</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.670901098901099</v>
+        <v>4.6700878477306</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82174913104437</v>
+        <v>11.82161601729376</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1421382519824174</v>
+        <v>-0.1422713657330263</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052426653513012</v>
+        <v>2.052455215626318</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697659653913385</v>
+        <v>2.697684392970805</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949949275314747</v>
+        <v>0.7949972427201908</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095904713576263</v>
+        <v>0.609583310774549</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863669454787632</v>
+        <v>0.7863774993451117</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.888653769857086</v>
+        <v>7.75467309882618</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.3920171509085</v>
+        <v>9.840397066151294</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89139092678375</v>
+        <v>11.69131762688143</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E16" t="n">
+        <v>9839</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9838</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9837</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363302734573548</v>
+        <v>8.363121467778003</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624096883204006</v>
+        <v>8.62400077747235</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2607941486304572</v>
+        <v>0.2608793096943464</v>
       </c>
       <c r="T16" t="n">
-        <v>3.593112350950778</v>
+        <v>3.593404404891191</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09107148820075</v>
+        <v>11.09065399305622</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04164768881072186</v>
+        <v>0.04162704563394722</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6100464373723504</v>
+        <v>-0.6100820755135574</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02498477809945387</v>
+        <v>0.02496425414844705</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.63492483321416</v>
+        <v>11.63302082340981</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.73042726421356</v>
+        <v>11.74233621010294</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.9396961951139</v>
+        <v>11.98157227576243</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E17" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2382</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2381</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.489618857622848</v>
+        <v>6.487861041141898</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.420714285714286</v>
+        <v>1.42196925329429</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.852547372617106</v>
+        <v>6.850447941111757</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3629285149942579</v>
+        <v>0.3625868999698595</v>
       </c>
       <c r="T17" t="n">
-        <v>2.017179091534754</v>
+        <v>2.016360152637711</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55353736646761</v>
+        <v>2.552924445256904</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5342583463879412</v>
+        <v>0.5348422117524272</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04678642839451719</v>
+        <v>0.04786827245805469</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5309052815115041</v>
+        <v>0.5314885872737923</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.29399121129713</v>
+        <v>1.508769415775204</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.089555526118033</v>
+        <v>3.141231189144059</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.943509208893979</v>
+        <v>4.390974962256438</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E18" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3241</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3240</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.475126234567901</v>
+        <v>6.474410367170626</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.669438876549626</v>
+        <v>6.668715658983462</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1943126419817253</v>
+        <v>0.1943052918128368</v>
       </c>
       <c r="T18" t="n">
-        <v>1.097446176081643</v>
+        <v>1.097110306412461</v>
       </c>
       <c r="U18" t="n">
-        <v>1.485976139840927</v>
+        <v>1.485661036666961</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6067555980326074</v>
+        <v>0.6070236115894045</v>
       </c>
       <c r="W18" t="n">
-        <v>0.228128622295925</v>
+        <v>0.2286656341695966</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6038693036047897</v>
+        <v>0.6041330498431224</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.34127451895791</v>
+        <v>2.320415079219935</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.350851636008524</v>
+        <v>4.311275071104149</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.201825584040268</v>
+        <v>5.638779929572027</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E19" t="n">
+        <v>7196</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7195</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7194</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33224791492911</v>
+        <v>10.33092237665045</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12539533031866</v>
+        <v>11.12448918583971</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7931474153895515</v>
+        <v>0.7935668091892544</v>
       </c>
       <c r="T19" t="n">
-        <v>2.053872256050626</v>
+        <v>2.054515159992047</v>
       </c>
       <c r="U19" t="n">
-        <v>2.778020932486261</v>
+        <v>2.778873158806734</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7271934559077536</v>
+        <v>0.7272187004484952</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4711291148740067</v>
+        <v>0.4711891520139716</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6783632569877633</v>
+        <v>0.6783109147507698</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.276804658833231</v>
+        <v>7.222211889680199</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.384338561946412</v>
+        <v>7.344587638123021</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.434567649038179</v>
+        <v>7.405234188737659</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E20" t="n">
+        <v>10646</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10645</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10644</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.86002040653991</v>
+        <v>13.85963618668021</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23647792930671</v>
+        <v>14.23607280686205</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.376457522766794</v>
+        <v>0.376436620181843</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255889795176839</v>
+        <v>1.255794343055667</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647567463488826</v>
+        <v>1.647486495045737</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8934471558608359</v>
+        <v>0.8934619119508004</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7787952685981459</v>
+        <v>0.7788245535893162</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8886322227497037</v>
+        <v>0.888647757397759</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.703402210519579</v>
+        <v>9.622869466053919</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.921616090696869</v>
+        <v>9.872009963629878</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.08070130340294</v>
+        <v>10.07865195781571</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16693</v>
+        <v>16694</v>
       </c>
       <c r="E21" t="n">
+        <v>10242</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10241</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10240</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8697930664063</v>
+        <v>130.869444487843</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9741821213284</v>
+        <v>130.9740425692959</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1043890549221336</v>
+        <v>0.1045980814529483</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976167818951817</v>
+        <v>0.7976333615224631</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046256932828051</v>
+        <v>1.046252967523537</v>
       </c>
       <c r="V21" t="n">
-        <v>0.865017878935359</v>
+        <v>0.8650366874905646</v>
       </c>
       <c r="W21" t="n">
-        <v>0.730945063571059</v>
+        <v>0.7310031009086305</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642896633743109</v>
+        <v>0.8642950018075184</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0659421023421</v>
+        <v>128.0918265492647</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9868067669487</v>
+        <v>129.0923085467124</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.7960155016064</v>
+        <v>129.682811020774</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.276804658833231</v>
+        <v>7.222211889680199</v>
       </c>
       <c r="G2" t="n">
-        <v>7.384338561946412</v>
+        <v>7.344587638123021</v>
       </c>
       <c r="H2" t="n">
-        <v>7.434567649038179</v>
+        <v>7.405234188737659</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.861148608843003</v>
+        <v>4.828612493899463</v>
       </c>
       <c r="G3" t="n">
-        <v>4.957970727201991</v>
+        <v>4.933667894097529</v>
       </c>
       <c r="H3" t="n">
-        <v>5.028072318002751</v>
+        <v>5.009223224622557</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.062654077237866</v>
+        <v>4.223123411219237</v>
       </c>
       <c r="G4" t="n">
-        <v>4.408004204810812</v>
+        <v>4.39185417521629</v>
       </c>
       <c r="H4" t="n">
-        <v>4.768915750915751</v>
+        <v>4.608910077320688</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.63492483321416</v>
+        <v>11.63302082340981</v>
       </c>
       <c r="G5" t="n">
-        <v>11.73042726421356</v>
+        <v>11.74233621010294</v>
       </c>
       <c r="H5" t="n">
-        <v>11.9396961951139</v>
+        <v>11.98157227576243</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.1157700277887</v>
+        <v>53.06797224700058</v>
       </c>
       <c r="G6" t="n">
-        <v>95.11316601334289</v>
+        <v>87.97940267175927</v>
       </c>
       <c r="H6" t="n">
-        <v>109.4326465274823</v>
+        <v>108.0936829003284</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.888653769857086</v>
+        <v>7.75467309882618</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3920171509085</v>
+        <v>9.840397066151292</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89139092678375</v>
+        <v>11.69131762688143</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.229112651980258</v>
+        <v>6.591017974418374</v>
       </c>
       <c r="G8" t="n">
-        <v>8.143101036166557</v>
+        <v>7.908443883170754</v>
       </c>
       <c r="H8" t="n">
-        <v>8.50379774371625</v>
+        <v>8.502869834735165</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.286115474934287</v>
+        <v>4.291614664416267</v>
       </c>
       <c r="G9" t="n">
-        <v>4.814692895961035</v>
+        <v>4.962983297038839</v>
       </c>
       <c r="H9" t="n">
-        <v>5.808383794661954</v>
+        <v>5.741303811735539</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.614520330355905</v>
+        <v>4.61871868984707</v>
       </c>
       <c r="G10" t="n">
-        <v>4.872519382515501</v>
+        <v>4.821873304490336</v>
       </c>
       <c r="H10" t="n">
-        <v>5.098574327122153</v>
+        <v>5.042463288702553</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.703402210519579</v>
+        <v>9.622869466053919</v>
       </c>
       <c r="G11" t="n">
-        <v>9.921616090696869</v>
+        <v>9.872009963629878</v>
       </c>
       <c r="H11" t="n">
-        <v>10.08070130340294</v>
+        <v>10.07865195781571</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.29399121129713</v>
+        <v>1.508769415775204</v>
       </c>
       <c r="G12" t="n">
-        <v>3.089555526118033</v>
+        <v>3.141231189144059</v>
       </c>
       <c r="H12" t="n">
-        <v>3.943509208893979</v>
+        <v>4.390974962256438</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.156142991269625</v>
+        <v>5.151922173050823</v>
       </c>
       <c r="G13" t="n">
-        <v>5.194383069963164</v>
+        <v>5.17990099456299</v>
       </c>
       <c r="H13" t="n">
-        <v>5.25874998222993</v>
+        <v>5.228145390428562</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.492744812394813</v>
+        <v>9.556995459141131</v>
       </c>
       <c r="G14" t="n">
-        <v>9.641669457016363</v>
+        <v>9.641273159924154</v>
       </c>
       <c r="H14" t="n">
-        <v>9.89225916482464</v>
+        <v>9.762991350135364</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.042710622710622</v>
+        <v>5.049284692099633</v>
       </c>
       <c r="G15" t="n">
-        <v>5.183351829422563</v>
+        <v>5.157797684854041</v>
       </c>
       <c r="H15" t="n">
-        <v>5.308428937728937</v>
+        <v>5.288561493411421</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.368224895752896</v>
+        <v>6.36812469922045</v>
       </c>
       <c r="G16" t="n">
-        <v>6.502327340893666</v>
+        <v>6.459169544809944</v>
       </c>
       <c r="H16" t="n">
-        <v>6.714477886690696</v>
+        <v>6.652185773371299</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.34127451895791</v>
+        <v>2.320415079219935</v>
       </c>
       <c r="G17" t="n">
-        <v>4.350851636008524</v>
+        <v>4.311275071104149</v>
       </c>
       <c r="H17" t="n">
-        <v>5.201825584040268</v>
+        <v>5.638779929572027</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.967184642857144</v>
+        <v>2.903645680819912</v>
       </c>
       <c r="G18" t="n">
-        <v>3.239990668669574</v>
+        <v>3.200038866781835</v>
       </c>
       <c r="H18" t="n">
-        <v>3.359428571428571</v>
+        <v>3.35892972181552</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.988215117902707</v>
+        <v>1.946166915263543</v>
       </c>
       <c r="G19" t="n">
-        <v>2.152210215200744</v>
+        <v>2.117352032572562</v>
       </c>
       <c r="H19" t="n">
-        <v>2.226944566544566</v>
+        <v>2.209625489185321</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.74573494764149</v>
+        <v>4.438173362946387</v>
       </c>
       <c r="G20" t="n">
-        <v>5.669587888733165</v>
+        <v>5.562998555277025</v>
       </c>
       <c r="H20" t="n">
-        <v>6.268263046702717</v>
+        <v>6.279052150979457</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0659421023421</v>
+        <v>128.0918265492647</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9868067669487</v>
+        <v>129.0923085467124</v>
       </c>
       <c r="H21" t="n">
-        <v>129.7960155016064</v>
+        <v>129.682811020774</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E2" t="n">
+        <v>10031</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10030</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10029</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5811086515771</v>
+        <v>102.5712730475241</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5416270350433</v>
+        <v>102.5376567541587</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03948161653378208</v>
+        <v>-0.03361629336543875</v>
       </c>
       <c r="T2" t="n">
-        <v>17.9356551563071</v>
+        <v>17.9437287749174</v>
       </c>
       <c r="U2" t="n">
-        <v>36.08624750433702</v>
+        <v>36.10162370793839</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1434456989177813</v>
+        <v>0.1435151913630336</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7133231700225506</v>
+        <v>-0.7127680038792352</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1434456034649185</v>
+        <v>0.1435151204508117</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.06797224700058</v>
+        <v>3.250326545208453</v>
       </c>
       <c r="Z2" t="n">
-        <v>87.97940267175927</v>
+        <v>94.49673308824698</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.0936829003284</v>
+        <v>108.1224379235265</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E3" t="n">
+        <v>14625</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14624</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14623</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.908121897011558</v>
+        <v>4.907923208424507</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965748199396312</v>
+        <v>4.965575735517106</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05762630238475602</v>
+        <v>0.05765252709259886</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34437478996458</v>
+        <v>1.344292712690506</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718942873668503</v>
+        <v>1.718881297594369</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813966422509192</v>
+        <v>0.7814134472612516</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5697893505277447</v>
+        <v>0.5698269127702759</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803562584368032</v>
+        <v>0.7803716642285637</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.946166915263543</v>
+        <v>1.924098175749817</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.117352032572563</v>
+        <v>2.087436227229924</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.209625489185321</v>
+        <v>2.208679663733449</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E4" t="n">
+        <v>10259</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10258</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10257</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.908057424198109</v>
+        <v>6.907646471046989</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.237614290452756</v>
+        <v>7.237193151133388</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295568662546469</v>
+        <v>0.3295466800863985</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292206751589175</v>
+        <v>1.292142210066713</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681849025793509</v>
+        <v>1.681750176846982</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8677738616248784</v>
+        <v>0.8677990507513573</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7377099904053721</v>
+        <v>0.7377573791373688</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472534318344405</v>
+        <v>0.8472781514936214</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.903645680819912</v>
+        <v>2.866958751485919</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.200038866781835</v>
+        <v>3.165868342794115</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.35892972181552</v>
+        <v>3.354458105683066</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824470473401659</v>
+        <v>2.824316020482809</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302647034670446</v>
+        <v>9.302572686328995</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3701856092479639</v>
+        <v>0.3701112609065121</v>
       </c>
       <c r="T5" t="n">
-        <v>1.24803040447265</v>
+        <v>1.247970618682973</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747604022532564</v>
+        <v>1.747540678257706</v>
       </c>
       <c r="V5" t="n">
-        <v>0.866013345660223</v>
+        <v>0.8660255927111277</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213668717769641</v>
+        <v>0.7213870702811566</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8595728495151885</v>
+        <v>0.8595887979770026</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.438173362946387</v>
+        <v>4.357974736160558</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.562998555277025</v>
+        <v>5.3591652835686</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.279052150979457</v>
+        <v>5.977495310790235</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E6" t="n">
+        <v>8872</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8871</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8870</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733826550169109</v>
+        <v>6.733910382144065</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022494547343361</v>
+        <v>7.022615805624545</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886679971742511</v>
+        <v>0.2887054234804798</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479317538657916</v>
+        <v>1.479240223364007</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908103634839282</v>
+        <v>1.908029646185656</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3044612661346087</v>
+        <v>0.304430143242963</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977299253521807</v>
+        <v>-0.1977474971115352</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2795921650838061</v>
+        <v>0.279551200661564</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.36812469922045</v>
+        <v>6.364330619821049</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.459169544809944</v>
+        <v>6.436320483747761</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.652185773371299</v>
+        <v>6.598895903773478</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E7" t="n">
+        <v>14233</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14232</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14231</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580867015670016</v>
+        <v>5.580814959246768</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567445207855584</v>
+        <v>5.567405505271054</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01342180781443205</v>
+        <v>-0.01340945397571412</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166903495552381</v>
+        <v>1.166826880349048</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510140977563999</v>
+        <v>1.510083282619764</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047915202000473</v>
+        <v>0.5048001579603397</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0530720681329131</v>
+        <v>0.0530930504586129</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026413800264922</v>
+        <v>0.5026495396467366</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.828612493899463</v>
+        <v>4.82054678784519</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.933667894097528</v>
+        <v>4.915222664263772</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.009223224622557</v>
+        <v>5.008704115466972</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E8" t="n">
+        <v>9031</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9030</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9029</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.875809613467715</v>
+        <v>7.875574473975637</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115001462792589</v>
+        <v>8.114813291995434</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2391918493248731</v>
+        <v>0.2392388180197968</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446028323866907</v>
+        <v>1.445961982575993</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825735563653098</v>
+        <v>1.82566252960804</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079001511183116</v>
+        <v>0.8079018651743509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275521510567117</v>
+        <v>0.6275607639625098</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797848561969281</v>
+        <v>0.7978409415431799</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.61871868984707</v>
+        <v>4.619098686775962</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.821873304490335</v>
+        <v>4.796058855044732</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.042463288702553</v>
+        <v>5.015427065730968</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E9" t="n">
+        <v>13896</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13895</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13894</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.611019864689795</v>
+        <v>7.610827815761065</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.656637313041189</v>
+        <v>7.656446380828074</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04561744835139494</v>
+        <v>0.0456185650670083</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494179261242186</v>
+        <v>1.494102978158369</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942106808536684</v>
+        <v>1.94204183492178</v>
       </c>
       <c r="V9" t="n">
-        <v>0.75664536853902</v>
+        <v>0.7566597271759578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248087914499141</v>
+        <v>0.5248370666943906</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552349664543068</v>
+        <v>0.7552491616551567</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.049284692099633</v>
+        <v>5.046114442112364</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.157797684854041</v>
+        <v>5.148804366375119</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.288561493411421</v>
+        <v>5.265113996586198</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61661693095808</v>
+        <v>10.61651607568101</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3115552504657125</v>
+        <v>0.3114543951886386</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052710500658617</v>
+        <v>2.052765035770288</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698412224372817</v>
+        <v>2.698475234096308</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356880221985833</v>
+        <v>0.3568863325895987</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1206993596192583</v>
+        <v>-0.1207516983839454</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3365164140571438</v>
+        <v>0.3365408592316003</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.556995459141131</v>
+        <v>9.590198168228547</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.641273159924154</v>
+        <v>9.713961798220863</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.762991350135364</v>
+        <v>9.889086181027563</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E11" t="n">
+        <v>13837</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13836</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13835</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243149765088544</v>
+        <v>5.243102377854872</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579238653001464</v>
+        <v>0.457929041697147</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216666314869683</v>
+        <v>5.216668585449281</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0264834502188602</v>
+        <v>-0.02643379240559064</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161506965413583</v>
+        <v>1.16146722379779</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482999687885503</v>
+        <v>1.482961763604883</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293945634027528</v>
+        <v>0.4293822947622866</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0920133001339678</v>
+        <v>-0.09201953011038344</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275843771801608</v>
+        <v>0.4275710343057757</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.223123411219237</v>
+        <v>4.059870049092447</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.39185417521629</v>
+        <v>4.494502026038605</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.608910077320688</v>
+        <v>4.728302765771823</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E12" t="n">
+        <v>4155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4154</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4153</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.468938959788105</v>
+        <v>7.468094848338951</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205241581259151</v>
+        <v>2.205274323335772</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.642093989796388</v>
+        <v>7.641131680484769</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1731550300082826</v>
+        <v>0.1730368321458184</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9129536384558204</v>
+        <v>0.9127738424821926</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194896887067312</v>
+        <v>1.194732951732905</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8319751044229403</v>
+        <v>0.832108821252484</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6592641426745507</v>
+        <v>0.6595161109126593</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8302168388482178</v>
+        <v>0.8303546194139754</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.291614664416267</v>
+        <v>4.291016669533288</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.962983297038839</v>
+        <v>5.097923529223871</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.741303811735539</v>
+        <v>5.734795179932357</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E13" t="n">
+        <v>6490</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6489</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6488</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.603578529593094</v>
+        <v>9.603128371089538</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02584931315418</v>
+        <v>10.02572336343285</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4222707835610801</v>
+        <v>0.4225949923433119</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691653641671577</v>
+        <v>1.6916678460203</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150606501828517</v>
+        <v>2.150505661390535</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232232779415114</v>
+        <v>0.8232295007256334</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6487428791346607</v>
+        <v>0.6487567611290233</v>
       </c>
       <c r="X13" t="n">
-        <v>0.810385550275651</v>
+        <v>0.81035659048001</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.591017974418374</v>
+        <v>6.49272398493428</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.908443883170754</v>
+        <v>7.701536294379308</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.502869834735165</v>
+        <v>8.483630618347727</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E14" t="n">
+        <v>14077</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14076</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14075</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.128080639431616</v>
+        <v>8.127872087240693</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.90765495363592</v>
+        <v>0.9076786149719581</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198709027835003</v>
+        <v>8.198537516310431</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07062838840338521</v>
+        <v>0.07066542906973741</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756373311966857</v>
+        <v>1.756279917912518</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282456696108319</v>
+        <v>2.282397129613397</v>
       </c>
       <c r="V14" t="n">
-        <v>0.780896363667404</v>
+        <v>0.7809010078221763</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654717910847038</v>
+        <v>0.5654857886715066</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805161081670825</v>
+        <v>0.7805200100596006</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.151922173050823</v>
+        <v>5.148620539203142</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.17990099456299</v>
+        <v>5.174056538045216</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.228145390428562</v>
+        <v>5.2125606086342</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.6700878477306</v>
+        <v>4.669831016825165</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82161601729376</v>
+        <v>11.82148527128407</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1422713657330263</v>
+        <v>-0.1424021117427078</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052455215626318</v>
+        <v>2.052484066780174</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697684392970805</v>
+        <v>2.697709495028842</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949972427201908</v>
+        <v>0.7949993922632138</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609583310774549</v>
+        <v>0.6095760450558365</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863774993451117</v>
+        <v>0.7863877360774315</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.75467309882618</v>
+        <v>7.730167248609561</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.840397066151294</v>
+        <v>9.409772607647424</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.69131762688143</v>
+        <v>11.37608843116153</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E16" t="n">
+        <v>9840</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9839</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9838</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.363121467778003</v>
+        <v>8.362970220550869</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.62400077747235</v>
+        <v>8.623943292858096</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2608793096943464</v>
+        <v>0.2609730723072267</v>
       </c>
       <c r="T16" t="n">
-        <v>3.593404404891191</v>
+        <v>3.59361556723871</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09065399305622</v>
+        <v>11.09020686369496</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04162704563394722</v>
+        <v>0.04160980779566085</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6100820755135574</v>
+        <v>-0.6101111570278521</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02496425414844705</v>
+        <v>0.02494693074185461</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.63302082340981</v>
+        <v>11.62893192026038</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.74233621010294</v>
+        <v>11.78421339292341</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.98157227576243</v>
+        <v>12.13259748672215</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E17" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2383</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2382</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.487861041141898</v>
+        <v>6.486168694922367</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.42196925329429</v>
+        <v>1.423222384784199</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.850447941111757</v>
+        <v>6.848650474719577</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3625868999698595</v>
+        <v>0.3624817797972094</v>
       </c>
       <c r="T17" t="n">
-        <v>2.016360152637711</v>
+        <v>2.015489594818516</v>
       </c>
       <c r="U17" t="n">
-        <v>2.552924445256904</v>
+        <v>2.55224976639826</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5348422117524272</v>
+        <v>0.5353563368980708</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04786827245805469</v>
+        <v>0.04892023911763999</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5314885872737923</v>
+        <v>0.5319992135908533</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.508769415775204</v>
+        <v>1.341185229843205</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.141231189144059</v>
+        <v>2.896687473031234</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.390974962256438</v>
+        <v>3.5916164576909</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E18" t="n">
+        <v>3243</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3242</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3241</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.474410367170626</v>
+        <v>6.473718075262185</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.668715658983462</v>
+        <v>6.668103768358217</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1943052918128368</v>
+        <v>0.1943856930960337</v>
       </c>
       <c r="T18" t="n">
-        <v>1.097110306412461</v>
+        <v>1.096843010578398</v>
       </c>
       <c r="U18" t="n">
-        <v>1.485661036666961</v>
+        <v>1.485368958341205</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6070236115894045</v>
+        <v>0.6072443453803363</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2286656341695966</v>
+        <v>0.2291495580358819</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6041330498431224</v>
+        <v>0.6043421717411537</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.320415079219935</v>
+        <v>2.230067989141284</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.311275071104149</v>
+        <v>3.860955833791982</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.638779929572027</v>
+        <v>4.910782742295828</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E19" t="n">
+        <v>7197</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7196</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7195</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33092237665045</v>
+        <v>10.32959025847693</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12448918583971</v>
+        <v>11.12356967283224</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7935668091892544</v>
+        <v>0.7939794143553072</v>
       </c>
       <c r="T19" t="n">
-        <v>2.054515159992047</v>
+        <v>2.055162491313374</v>
       </c>
       <c r="U19" t="n">
-        <v>2.778873158806734</v>
+        <v>2.779717683682504</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272187004484952</v>
+        <v>0.7272480158974435</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4711891520139716</v>
+        <v>0.4712565052634724</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6783109147507698</v>
+        <v>0.67826338084249</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.222211889680199</v>
+        <v>7.207033189161265</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.344587638123021</v>
+        <v>7.320600263017407</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.405234188737659</v>
+        <v>7.400796167401484</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E20" t="n">
+        <v>10647</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10646</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10645</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85963618668021</v>
+        <v>13.8592489862118</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23607280686205</v>
+        <v>14.23566386548668</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.376436620181843</v>
+        <v>0.3764148792748752</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255794343055667</v>
+        <v>1.255700239683608</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647486495045737</v>
+        <v>1.647404351210486</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8934619119508004</v>
+        <v>0.8934770575306525</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7788245535893162</v>
+        <v>0.7788545960448783</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888647757397759</v>
+        <v>0.8886637512825729</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.622869466053919</v>
+        <v>9.563640685800628</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.872009963629878</v>
+        <v>9.829204908013676</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.07865195781571</v>
+        <v>10.04784100410425</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16694</v>
+        <v>16695</v>
       </c>
       <c r="E21" t="n">
+        <v>10243</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10242</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10241</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.869444487843</v>
+        <v>130.8693205428627</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9740425692959</v>
+        <v>130.97389246027</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045980814529483</v>
+        <v>0.104571917407269</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976333615224631</v>
+        <v>0.7977200015750396</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046252967523537</v>
+        <v>1.046327876162776</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650366874905646</v>
+        <v>0.8650092999593094</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7310031009086305</v>
+        <v>0.7309487131616866</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642950018075184</v>
+        <v>0.8642684436278087</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0918265492647</v>
+        <v>128.1967848829078</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.0923085467124</v>
+        <v>129.2189065044129</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.682811020774</v>
+        <v>129.679788627837</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222211889680199</v>
+        <v>7.207033189161265</v>
       </c>
       <c r="G2" t="n">
-        <v>7.344587638123021</v>
+        <v>7.320600263017409</v>
       </c>
       <c r="H2" t="n">
-        <v>7.405234188737659</v>
+        <v>7.400796167401484</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.828612493899463</v>
+        <v>4.82054678784519</v>
       </c>
       <c r="G3" t="n">
-        <v>4.933667894097529</v>
+        <v>4.915222664263772</v>
       </c>
       <c r="H3" t="n">
-        <v>5.009223224622557</v>
+        <v>5.008704115466972</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.223123411219237</v>
+        <v>4.059870049092447</v>
       </c>
       <c r="G4" t="n">
-        <v>4.39185417521629</v>
+        <v>4.494502026038605</v>
       </c>
       <c r="H4" t="n">
-        <v>4.608910077320688</v>
+        <v>4.728302765771823</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.63302082340981</v>
+        <v>11.62893192026038</v>
       </c>
       <c r="G5" t="n">
-        <v>11.74233621010294</v>
+        <v>11.78421339292341</v>
       </c>
       <c r="H5" t="n">
-        <v>11.98157227576243</v>
+        <v>12.13259748672215</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.06797224700058</v>
+        <v>3.250326545208453</v>
       </c>
       <c r="G6" t="n">
-        <v>87.97940267175927</v>
+        <v>94.49673308824698</v>
       </c>
       <c r="H6" t="n">
-        <v>108.0936829003284</v>
+        <v>108.1224379235265</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.75467309882618</v>
+        <v>7.730167248609561</v>
       </c>
       <c r="G7" t="n">
-        <v>9.840397066151292</v>
+        <v>9.409772607647424</v>
       </c>
       <c r="H7" t="n">
-        <v>11.69131762688143</v>
+        <v>11.37608843116153</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.591017974418374</v>
+        <v>6.49272398493428</v>
       </c>
       <c r="G8" t="n">
-        <v>7.908443883170754</v>
+        <v>7.701536294379307</v>
       </c>
       <c r="H8" t="n">
-        <v>8.502869834735165</v>
+        <v>8.483630618347727</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.291614664416267</v>
+        <v>4.291016669533288</v>
       </c>
       <c r="G9" t="n">
-        <v>4.962983297038839</v>
+        <v>5.097923529223871</v>
       </c>
       <c r="H9" t="n">
-        <v>5.741303811735539</v>
+        <v>5.734795179932357</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.61871868984707</v>
+        <v>4.619098686775962</v>
       </c>
       <c r="G10" t="n">
-        <v>4.821873304490336</v>
+        <v>4.796058855044732</v>
       </c>
       <c r="H10" t="n">
-        <v>5.042463288702553</v>
+        <v>5.015427065730968</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.622869466053919</v>
+        <v>9.563640685800628</v>
       </c>
       <c r="G11" t="n">
-        <v>9.872009963629878</v>
+        <v>9.829204908013676</v>
       </c>
       <c r="H11" t="n">
-        <v>10.07865195781571</v>
+        <v>10.04784100410425</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.508769415775204</v>
+        <v>1.341185229843205</v>
       </c>
       <c r="G12" t="n">
-        <v>3.141231189144059</v>
+        <v>2.896687473031233</v>
       </c>
       <c r="H12" t="n">
-        <v>4.390974962256438</v>
+        <v>3.5916164576909</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.151922173050823</v>
+        <v>5.148620539203142</v>
       </c>
       <c r="G13" t="n">
-        <v>5.17990099456299</v>
+        <v>5.174056538045216</v>
       </c>
       <c r="H13" t="n">
-        <v>5.228145390428562</v>
+        <v>5.2125606086342</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.556995459141131</v>
+        <v>9.590198168228547</v>
       </c>
       <c r="G14" t="n">
-        <v>9.641273159924154</v>
+        <v>9.713961798220865</v>
       </c>
       <c r="H14" t="n">
-        <v>9.762991350135364</v>
+        <v>9.889086181027563</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.049284692099633</v>
+        <v>5.046114442112364</v>
       </c>
       <c r="G15" t="n">
-        <v>5.157797684854041</v>
+        <v>5.148804366375119</v>
       </c>
       <c r="H15" t="n">
-        <v>5.288561493411421</v>
+        <v>5.265113996586198</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.36812469922045</v>
+        <v>6.364330619821049</v>
       </c>
       <c r="G16" t="n">
-        <v>6.459169544809944</v>
+        <v>6.436320483747761</v>
       </c>
       <c r="H16" t="n">
-        <v>6.652185773371299</v>
+        <v>6.598895903773478</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.320415079219935</v>
+        <v>2.230067989141284</v>
       </c>
       <c r="G17" t="n">
-        <v>4.311275071104149</v>
+        <v>3.860955833791982</v>
       </c>
       <c r="H17" t="n">
-        <v>5.638779929572027</v>
+        <v>4.910782742295828</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.903645680819912</v>
+        <v>2.866958751485919</v>
       </c>
       <c r="G18" t="n">
-        <v>3.200038866781835</v>
+        <v>3.165868342794115</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35892972181552</v>
+        <v>3.354458105683066</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.946166915263543</v>
+        <v>1.924098175749817</v>
       </c>
       <c r="G19" t="n">
-        <v>2.117352032572562</v>
+        <v>2.087436227229924</v>
       </c>
       <c r="H19" t="n">
-        <v>2.209625489185321</v>
+        <v>2.208679663733449</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.438173362946387</v>
+        <v>4.357974736160558</v>
       </c>
       <c r="G20" t="n">
-        <v>5.562998555277025</v>
+        <v>5.3591652835686</v>
       </c>
       <c r="H20" t="n">
-        <v>6.279052150979457</v>
+        <v>5.977495310790235</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0918265492647</v>
+        <v>128.1967848829078</v>
       </c>
       <c r="G21" t="n">
-        <v>129.0923085467124</v>
+        <v>129.2189065044129</v>
       </c>
       <c r="H21" t="n">
-        <v>129.682811020774</v>
+        <v>129.679788627837</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E2" t="n">
+        <v>10032</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10031</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10030</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5712730475241</v>
+        <v>102.60853590536</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5376567541587</v>
+        <v>102.5953803305956</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03361629336543875</v>
+        <v>-0.01315557476443113</v>
       </c>
       <c r="T2" t="n">
-        <v>17.9437287749174</v>
+        <v>17.93220592869803</v>
       </c>
       <c r="U2" t="n">
-        <v>36.10162370793839</v>
+        <v>36.02967566816417</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1435151913630336</v>
+        <v>0.1388170097419844</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7127680038792352</v>
+        <v>-0.7193408168981215</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1435151204508117</v>
+        <v>0.1388152051587863</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.250326545208453</v>
+        <v>53.13277182770479</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.49673308824698</v>
+        <v>104.1582155019414</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.1224379235265</v>
+        <v>108.8319156924261</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E3" t="n">
+        <v>14626</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14625</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14624</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.907923208424507</v>
+        <v>4.90772864957265</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965575735517106</v>
+        <v>4.965406289102551</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05765252709259886</v>
+        <v>0.05767763952990239</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344292712690506</v>
+        <v>1.344209493842829</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718881297594369</v>
+        <v>1.718820842451268</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814134472612516</v>
+        <v>0.7814293023536948</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5698269127702759</v>
+        <v>0.5698624284002478</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803716642285637</v>
+        <v>0.7803861759720268</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.924098175749817</v>
+        <v>1.926995641447369</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.087436227229924</v>
+        <v>2.059047959624182</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.208679663733449</v>
+        <v>2.198164473684211</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E4" t="n">
+        <v>10260</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10259</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10258</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.907646471046989</v>
+        <v>6.907232430061409</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.237193151133388</v>
+        <v>7.236791741526184</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295466800863985</v>
+        <v>0.3295593114647733</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292142210066713</v>
+        <v>1.292090022110709</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681750176846982</v>
+        <v>1.681662389299484</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8677990507513573</v>
+        <v>0.8678227133262567</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7377573791373688</v>
+        <v>0.7378019510199114</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472781514936214</v>
+        <v>0.8472966658722201</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.866958751485919</v>
+        <v>2.829652474029719</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.165868342794115</v>
+        <v>3.141479514299197</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.354458105683066</v>
+        <v>3.283293128654971</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824316020482809</v>
+        <v>2.82416179337232</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302572686328995</v>
+        <v>9.302499762580844</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3701112609065121</v>
+        <v>0.3700383371583597</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247970618682973</v>
+        <v>1.247914438309483</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747540678257706</v>
+        <v>1.747480620953623</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660255927111277</v>
+        <v>0.8660373029387144</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213870702811566</v>
+        <v>0.7214062199972402</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8595887979770026</v>
+        <v>0.859604155544327</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.357974736160558</v>
+        <v>4.343139340635405</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.3591652835686</v>
+        <v>5.342492262919523</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.977495310790235</v>
+        <v>6.140195595775055</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E6" t="n">
+        <v>8873</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8872</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8871</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733910382144065</v>
+        <v>6.733985741659152</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022615805624545</v>
+        <v>7.022710673011975</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887054234804798</v>
+        <v>0.2887249313528225</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479240223364007</v>
+        <v>1.479159449432692</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908029646185656</v>
+        <v>1.907953021630897</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304430143242963</v>
+        <v>0.3043940876734124</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977474971115352</v>
+        <v>-0.1977664510711579</v>
       </c>
       <c r="X6" t="n">
-        <v>0.279551200661564</v>
+        <v>0.2795047907124621</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.364330619821049</v>
+        <v>6.36944032847321</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.436320483747761</v>
+        <v>6.419187784890648</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.598895903773478</v>
+        <v>6.536811046794437</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E7" t="n">
+        <v>14234</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14233</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14232</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580814959246768</v>
+        <v>5.580770989952927</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567405505271054</v>
+        <v>5.567373807853231</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01340945397571412</v>
+        <v>-0.01339718209969484</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166826880349048</v>
+        <v>1.166745900822392</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510083282619764</v>
+        <v>1.510027585154871</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048001579603397</v>
+        <v>0.5048053384823414</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0530930504586129</v>
+        <v>0.05310719066128478</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026495396467366</v>
+        <v>0.5026542821778719</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.82054678784519</v>
+        <v>4.824168865056753</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.915222664263772</v>
+        <v>4.900288418442055</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.008704115466972</v>
+        <v>4.988846777343804</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E8" t="n">
+        <v>9032</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9031</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9030</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.875574473975637</v>
+        <v>7.875310320008857</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.114813291995434</v>
+        <v>8.114608344361512</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2392388180197968</v>
+        <v>0.2392980243526542</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445961982575993</v>
+        <v>1.445857403286154</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82566252960804</v>
+        <v>1.825573850605839</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079018651743509</v>
+        <v>0.8079102090613952</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275607639625098</v>
+        <v>0.6275819276442263</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978409415431799</v>
+        <v>0.797838792904899</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.619098686775962</v>
+        <v>4.619625538614982</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.796058855044732</v>
+        <v>4.78227838159861</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.015427065730968</v>
+        <v>4.975092481011981</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E9" t="n">
+        <v>13897</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13896</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13895</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610827815761065</v>
+        <v>7.610633815486471</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.656446380828074</v>
+        <v>7.656264163006107</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0456185650670083</v>
+        <v>0.04563034751963686</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494102978158369</v>
+        <v>1.494022531136781</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94204183492178</v>
+        <v>1.941975068002079</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566597271759578</v>
+        <v>0.7566740877719633</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248370666943906</v>
+        <v>0.5248668503191132</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552491616551567</v>
+        <v>0.7552629345070836</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.046114442112364</v>
+        <v>5.041827485380117</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.148804366375119</v>
+        <v>5.145717438749221</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.265113996586198</v>
+        <v>5.288467105263158</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61651607568101</v>
+        <v>10.61641253939939</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3114543951886386</v>
+        <v>0.3113508589070208</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052765035770288</v>
+        <v>2.052824897744368</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698475234096308</v>
+        <v>2.698544012743743</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568863325895987</v>
+        <v>0.3568907875343141</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1207516983839454</v>
+        <v>-0.1208088304763995</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3365408592316003</v>
+        <v>0.3365642675242468</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.590198168228547</v>
+        <v>9.549714188281349</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.713961798220863</v>
+        <v>9.701567103211692</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.889086181027563</v>
+        <v>9.928445160574924</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E11" t="n">
+        <v>13838</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13837</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13836</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243102377854872</v>
+        <v>5.24308607357086</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.457929041697147</v>
+        <v>0.4579342105263158</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216668585449281</v>
+        <v>5.216634396189384</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02643379240559064</v>
+        <v>-0.02645167738147693</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16146722379779</v>
+        <v>1.161436914524357</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482961763604883</v>
+        <v>1.482919674738604</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293822947622866</v>
+        <v>0.4293744554432981</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09201953011038344</v>
+        <v>-0.09203447130259845</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275710343057757</v>
+        <v>0.427563150312487</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.059870049092447</v>
+        <v>3.995995982422611</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.494502026038605</v>
+        <v>4.479531922880748</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.728302765771823</v>
+        <v>4.838975236450073</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E12" t="n">
+        <v>4156</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4155</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4154</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.468094848338951</v>
+        <v>7.467467148014441</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205274323335772</v>
+        <v>2.20530701754386</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.641131680484769</v>
+        <v>7.64098603691138</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1730368321458184</v>
+        <v>0.1735188888969388</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9127738424821926</v>
+        <v>0.9127786451261189</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194732951732905</v>
+        <v>1.194632852596428</v>
       </c>
       <c r="V12" t="n">
-        <v>0.832108821252484</v>
+        <v>0.8321188586634455</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6595161109126593</v>
+        <v>0.6596241306514032</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8303546194139754</v>
+        <v>0.8303376516024925</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.291016669533288</v>
+        <v>4.334646658945474</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.097923529223871</v>
+        <v>5.198350784111268</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.734795179932357</v>
+        <v>5.671282625210923</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E13" t="n">
+        <v>6491</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6490</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6489</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.603128371089538</v>
+        <v>9.602706086286595</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02572336343285</v>
+        <v>10.02559313896982</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4225949923433119</v>
+        <v>0.4228870526832293</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6916678460203</v>
+        <v>1.691642454944692</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150505661390535</v>
+        <v>2.150360688935566</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232295007256334</v>
+        <v>0.8232410492164258</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6487567611290233</v>
+        <v>0.6487808663644843</v>
       </c>
       <c r="X13" t="n">
-        <v>0.81035659048001</v>
+        <v>0.8103352933529753</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.49272398493428</v>
+        <v>6.445768416788887</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.701536294379308</v>
+        <v>7.493389120147667</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.483630618347727</v>
+        <v>8.451278535477748</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E14" t="n">
+        <v>14078</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14077</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14076</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.127872087240693</v>
+        <v>8.127675285927399</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9076786149719581</v>
+        <v>0.9077022417153996</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198537516310431</v>
+        <v>8.198382284167472</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07066542906973741</v>
+        <v>0.0707069982400729</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756279917912518</v>
+        <v>1.756208931793209</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282397129613397</v>
+        <v>2.282345706489632</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809010078221763</v>
+        <v>0.7809026769790948</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654857886715066</v>
+        <v>0.5654942599996915</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805200100596006</v>
+        <v>0.7805208756010451</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.148620539203142</v>
+        <v>5.145017819549524</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.174056538045216</v>
+        <v>5.167339468059261</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2125606086342</v>
+        <v>5.198115845986931</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.669831016825165</v>
+        <v>4.669641812865497</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82148527128407</v>
+        <v>11.82137295518759</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1424021117427078</v>
+        <v>-0.1425144278391915</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052484066780174</v>
+        <v>2.052498019518522</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697709495028842</v>
+        <v>2.697736579483698</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949993922632138</v>
+        <v>0.7950011007089779</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095760450558365</v>
+        <v>0.6095682054622225</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863877360774315</v>
+        <v>0.7863976510854853</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.730167248609561</v>
+        <v>7.722212860499562</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.409772607647424</v>
+        <v>9.010684764125781</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.37608843116153</v>
+        <v>11.0915905947206</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E16" t="n">
+        <v>9841</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9840</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9839</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.362970220550869</v>
+        <v>8.3628418699187</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623943292858096</v>
+        <v>8.623883542750722</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2609730723072267</v>
+        <v>0.2610416728320225</v>
       </c>
       <c r="T16" t="n">
-        <v>3.59361556723871</v>
+        <v>3.593800139133999</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09020686369496</v>
+        <v>11.08974911187125</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04160980779566085</v>
+        <v>0.04159378818061465</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6101111570278521</v>
+        <v>-0.6101384594835322</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02494693074185461</v>
+        <v>0.02493094975694066</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.62893192026038</v>
+        <v>11.62183213205211</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.78421339292341</v>
+        <v>11.85674748734831</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.13259748672215</v>
+        <v>12.42951770141462</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E17" t="n">
+        <v>2385</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2384</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2383</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.486168694922367</v>
+        <v>6.484615142617449</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.423222384784199</v>
+        <v>1.424473684210526</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.848650474719577</v>
+        <v>6.847095679844357</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3624817797972094</v>
+        <v>0.3624805372269074</v>
       </c>
       <c r="T17" t="n">
-        <v>2.015489594818516</v>
+        <v>2.014677789848211</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55224976639826</v>
+        <v>2.551576061500764</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5353563368980708</v>
+        <v>0.5357798076741909</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04892023911763999</v>
+        <v>0.04982161749607295</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5319992135908533</v>
+        <v>0.5324183452043492</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.341185229843205</v>
+        <v>1.500569361422194</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.896687473031234</v>
+        <v>3.07372394114318</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5916164576909</v>
+        <v>3.965805163914089</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E18" t="n">
+        <v>3244</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3243</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3242</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.473718075262185</v>
+        <v>6.473066296638915</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.668103768358217</v>
+        <v>6.66769932762961</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1943856930960337</v>
+        <v>0.1946330309906964</v>
       </c>
       <c r="T18" t="n">
-        <v>1.096843010578398</v>
+        <v>1.096591997846893</v>
       </c>
       <c r="U18" t="n">
-        <v>1.485368958341205</v>
+        <v>1.485105204781221</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6072443453803363</v>
+        <v>0.6073899632088985</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2291495580358819</v>
+        <v>0.2295564468698404</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6043421717411537</v>
+        <v>0.6044626145640888</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.230067989141284</v>
+        <v>2.32749311790645</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.860955833791982</v>
+        <v>4.167306363777119</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.910782742295828</v>
+        <v>4.958705806076221</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E19" t="n">
+        <v>7198</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7197</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7196</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32959025847693</v>
+        <v>10.32825955259136</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12356967283224</v>
+        <v>11.12267003705497</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7939794143553072</v>
+        <v>0.7944104844636133</v>
       </c>
       <c r="T19" t="n">
-        <v>2.055162491313374</v>
+        <v>2.055797753806017</v>
       </c>
       <c r="U19" t="n">
-        <v>2.779717683682504</v>
+        <v>2.78056234098697</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272480158974435</v>
+        <v>0.7272767163785619</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4712565052634724</v>
+        <v>0.4713226538055455</v>
       </c>
       <c r="X19" t="n">
-        <v>0.67826338084249</v>
+        <v>0.6782109545473262</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.207033189161265</v>
+        <v>7.195866456079751</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.320600263017407</v>
+        <v>7.308590034869257</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.400796167401484</v>
+        <v>7.393999915348726</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E20" t="n">
+        <v>10648</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10647</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10646</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8592489862118</v>
+        <v>13.85885927559038</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23566386548668</v>
+        <v>14.23526337868622</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764148792748752</v>
+        <v>0.3764041030958336</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255700239683608</v>
+        <v>1.255607924514889</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647404351210486</v>
+        <v>1.647323685836043</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8934770575306525</v>
+        <v>0.8934921649834366</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7788545960448783</v>
+        <v>0.7788846162910783</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8886637512825729</v>
+        <v>0.8886788857253415</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.563640685800628</v>
+        <v>9.541942414592484</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.829204908013676</v>
+        <v>9.801373797647502</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.04784100410425</v>
+        <v>9.994661942518009</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16695</v>
+        <v>16696</v>
       </c>
       <c r="E21" t="n">
+        <v>10244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10243</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10242</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8693205428627</v>
+        <v>130.8691868593185</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.97389246027</v>
+        <v>130.9737505916297</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.104571917407269</v>
+        <v>0.1045637323111056</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7977200015750396</v>
+        <v>0.7977819466317958</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046327876162776</v>
+        <v>1.046376337251175</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650092999593094</v>
+        <v>0.8649893887480181</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7309487131616866</v>
+        <v>0.730909623753117</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642684436278087</v>
+        <v>0.8642486885256411</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.1967848829078</v>
+        <v>128.5944255672721</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2189065044129</v>
+        <v>129.2361412443899</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.679788627837</v>
+        <v>129.5970531425409</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.207033189161265</v>
+        <v>7.195866456079751</v>
       </c>
       <c r="G2" t="n">
-        <v>7.320600263017409</v>
+        <v>7.308590034869257</v>
       </c>
       <c r="H2" t="n">
-        <v>7.400796167401484</v>
+        <v>7.393999915348726</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82054678784519</v>
+        <v>4.824168865056753</v>
       </c>
       <c r="G3" t="n">
-        <v>4.915222664263772</v>
+        <v>4.900288418442054</v>
       </c>
       <c r="H3" t="n">
-        <v>5.008704115466972</v>
+        <v>4.988846777343804</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.059870049092447</v>
+        <v>3.995995982422611</v>
       </c>
       <c r="G4" t="n">
-        <v>4.494502026038605</v>
+        <v>4.479531922880747</v>
       </c>
       <c r="H4" t="n">
-        <v>4.728302765771823</v>
+        <v>4.838975236450073</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.62893192026038</v>
+        <v>11.62183213205211</v>
       </c>
       <c r="G5" t="n">
-        <v>11.78421339292341</v>
+        <v>11.85674748734831</v>
       </c>
       <c r="H5" t="n">
-        <v>12.13259748672215</v>
+        <v>12.42951770141462</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.250326545208453</v>
+        <v>53.13277182770479</v>
       </c>
       <c r="G6" t="n">
-        <v>94.49673308824698</v>
+        <v>104.1582155019414</v>
       </c>
       <c r="H6" t="n">
-        <v>108.1224379235265</v>
+        <v>108.8319156924261</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.730167248609561</v>
+        <v>7.722212860499562</v>
       </c>
       <c r="G7" t="n">
-        <v>9.409772607647424</v>
+        <v>9.010684764125784</v>
       </c>
       <c r="H7" t="n">
-        <v>11.37608843116153</v>
+        <v>11.0915905947206</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.49272398493428</v>
+        <v>6.445768416788887</v>
       </c>
       <c r="G8" t="n">
-        <v>7.701536294379307</v>
+        <v>7.493389120147668</v>
       </c>
       <c r="H8" t="n">
-        <v>8.483630618347727</v>
+        <v>8.451278535477748</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.291016669533288</v>
+        <v>4.334646658945474</v>
       </c>
       <c r="G9" t="n">
-        <v>5.097923529223871</v>
+        <v>5.198350784111269</v>
       </c>
       <c r="H9" t="n">
-        <v>5.734795179932357</v>
+        <v>5.671282625210923</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.619098686775962</v>
+        <v>4.619625538614982</v>
       </c>
       <c r="G10" t="n">
-        <v>4.796058855044732</v>
+        <v>4.78227838159861</v>
       </c>
       <c r="H10" t="n">
-        <v>5.015427065730968</v>
+        <v>4.975092481011981</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.563640685800628</v>
+        <v>9.541942414592484</v>
       </c>
       <c r="G11" t="n">
-        <v>9.829204908013676</v>
+        <v>9.8013737976475</v>
       </c>
       <c r="H11" t="n">
-        <v>10.04784100410425</v>
+        <v>9.994661942518009</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.341185229843205</v>
+        <v>1.500569361422194</v>
       </c>
       <c r="G12" t="n">
-        <v>2.896687473031233</v>
+        <v>3.07372394114318</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5916164576909</v>
+        <v>3.965805163914089</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.148620539203142</v>
+        <v>5.145017819549524</v>
       </c>
       <c r="G13" t="n">
-        <v>5.174056538045216</v>
+        <v>5.167339468059261</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2125606086342</v>
+        <v>5.198115845986931</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.590198168228547</v>
+        <v>9.549714188281349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.713961798220865</v>
+        <v>9.701567103211692</v>
       </c>
       <c r="H14" t="n">
-        <v>9.889086181027563</v>
+        <v>9.928445160574924</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.046114442112364</v>
+        <v>5.041827485380117</v>
       </c>
       <c r="G15" t="n">
-        <v>5.148804366375119</v>
+        <v>5.145717438749221</v>
       </c>
       <c r="H15" t="n">
-        <v>5.265113996586198</v>
+        <v>5.288467105263158</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.364330619821049</v>
+        <v>6.36944032847321</v>
       </c>
       <c r="G16" t="n">
-        <v>6.436320483747761</v>
+        <v>6.419187784890648</v>
       </c>
       <c r="H16" t="n">
-        <v>6.598895903773478</v>
+        <v>6.536811046794437</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.230067989141284</v>
+        <v>2.32749311790645</v>
       </c>
       <c r="G17" t="n">
-        <v>3.860955833791982</v>
+        <v>4.167306363777119</v>
       </c>
       <c r="H17" t="n">
-        <v>4.910782742295828</v>
+        <v>4.958705806076221</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.866958751485919</v>
+        <v>2.829652474029719</v>
       </c>
       <c r="G18" t="n">
-        <v>3.165868342794115</v>
+        <v>3.141479514299198</v>
       </c>
       <c r="H18" t="n">
-        <v>3.354458105683066</v>
+        <v>3.283293128654971</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.924098175749817</v>
+        <v>1.926995641447369</v>
       </c>
       <c r="G19" t="n">
-        <v>2.087436227229924</v>
+        <v>2.059047959624182</v>
       </c>
       <c r="H19" t="n">
-        <v>2.208679663733449</v>
+        <v>2.198164473684211</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.357974736160558</v>
+        <v>4.343139340635405</v>
       </c>
       <c r="G20" t="n">
-        <v>5.3591652835686</v>
+        <v>5.342492262919523</v>
       </c>
       <c r="H20" t="n">
-        <v>5.977495310790235</v>
+        <v>6.140195595775055</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.1967848829078</v>
+        <v>128.5944255672721</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2189065044129</v>
+        <v>129.2361412443899</v>
       </c>
       <c r="H21" t="n">
-        <v>129.679788627837</v>
+        <v>129.5970531425409</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E2" t="n">
+        <v>10033</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10032</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10031</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.60853590536</v>
+        <v>102.6039522195641</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5953803305956</v>
+        <v>102.5958242625169</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01315557476443113</v>
+        <v>-0.008127957047144738</v>
       </c>
       <c r="T2" t="n">
-        <v>17.93220592869803</v>
+        <v>17.935710671747</v>
       </c>
       <c r="U2" t="n">
-        <v>36.02967566816417</v>
+        <v>36.03155108463373</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1388170097419844</v>
+        <v>0.1387454101702119</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7193408168981215</v>
+        <v>-0.7192112915097884</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1388152051587863</v>
+        <v>0.1387432735961563</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.13277182770479</v>
+        <v>52.95087305144219</v>
       </c>
       <c r="Z2" t="n">
-        <v>104.1582155019414</v>
+        <v>102.7818757537659</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.8319156924261</v>
+        <v>108.9257893896179</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E3" t="n">
+        <v>14627</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14626</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14625</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.90772864957265</v>
+        <v>4.907538561465882</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965406289102551</v>
+        <v>4.965251001003814</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05767763952990239</v>
+        <v>0.05771243953793217</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344209493842829</v>
+        <v>1.344126094706994</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718820842451268</v>
+        <v>1.71876375469577</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814293023536948</v>
+        <v>0.7814427522642758</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5698624284002478</v>
+        <v>0.5698946859071765</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803861759720268</v>
+        <v>0.7803978568951071</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.926995641447369</v>
+        <v>1.927969354912345</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.059047959624182</v>
+        <v>2.042680756099311</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.198164473684211</v>
+        <v>2.204196859021183</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E4" t="n">
+        <v>10261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10260</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10259</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.907232430061409</v>
+        <v>6.906826754385966</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.236791741526184</v>
+        <v>7.236408297356834</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295593114647733</v>
+        <v>0.3295815429708698</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292090022110709</v>
+        <v>1.292037109252373</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681662389299484</v>
+        <v>1.681584679071461</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678227133262567</v>
+        <v>0.8678437865016283</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7378019510199114</v>
+        <v>0.7378416687694556</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472966658722201</v>
+        <v>0.8473107166417688</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.829652474029719</v>
+        <v>2.747476260043828</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.141479514299197</v>
+        <v>3.094543890186649</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.283293128654971</v>
+        <v>3.280226442658875</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82416179337232</v>
+        <v>2.824007791575359</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302499762580844</v>
+        <v>9.302421127448966</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3700383371583597</v>
+        <v>0.3699597020264829</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247914438309483</v>
+        <v>1.24786130532519</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747480620953623</v>
+        <v>1.747423680554833</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660373029387144</v>
+        <v>0.8660484992993296</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214062199972402</v>
+        <v>0.7214243752572156</v>
       </c>
       <c r="X5" t="n">
-        <v>0.859604155544327</v>
+        <v>0.8596192723770117</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.343139340635405</v>
+        <v>4.341741868509302</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.342492262919523</v>
+        <v>5.229613502088382</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.140195595775055</v>
+        <v>6.145526739997051</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E6" t="n">
         <v>8873</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8872</v>
+        <v>8873</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733985741659152</v>
+        <v>6.734056294376197</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022710673011975</v>
+        <v>7.022635604528472</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887249313528225</v>
+        <v>0.2885793101522743</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479159449432692</v>
+        <v>1.479100223179476</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907953021630897</v>
+        <v>1.907886944457932</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3043940876734124</v>
+        <v>0.3043813198387086</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977664510711579</v>
+        <v>-0.1978010782910815</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2795047907124621</v>
+        <v>0.2795033547124275</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.36944032847321</v>
+        <v>6.364754742587006</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.419187784890648</v>
+        <v>6.403682812201706</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.536811046794437</v>
+        <v>6.529671727712269</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E7" t="n">
+        <v>14235</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14234</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14233</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580770989952927</v>
+        <v>5.580732295911199</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567373807853231</v>
+        <v>5.567341501672164</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01339718209969484</v>
+        <v>-0.01339079423903384</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166745900822392</v>
+        <v>1.166665417936366</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510027585154871</v>
+        <v>1.509973306893526</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048053384823414</v>
+        <v>0.504809052816674</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05310719066128478</v>
+        <v>0.05311711873089964</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026542821778719</v>
+        <v>0.5026576991267889</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.824168865056753</v>
+        <v>4.824254906352557</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.900288418442055</v>
+        <v>4.888236240175829</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.988846777343804</v>
+        <v>4.99120542831444</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E8" t="n">
+        <v>9033</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9032</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9031</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.875310320008857</v>
+        <v>7.875048715677591</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.114608344361512</v>
+        <v>8.114425846276951</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2392980243526542</v>
+        <v>0.2393771305993617</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445857403286154</v>
+        <v>1.445763110386684</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825573850605839</v>
+        <v>1.825501835147426</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079102090613952</v>
+        <v>0.8079143994267322</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275819276442263</v>
+        <v>0.6275957978816837</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797838792904899</v>
+        <v>0.7978306842170934</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.619625538614982</v>
+        <v>4.619957326753671</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.78227838159861</v>
+        <v>4.785048311921882</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.975092481011981</v>
+        <v>4.98745875924312</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E9" t="n">
+        <v>13898</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13897</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13896</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610633815486471</v>
+        <v>7.610448478088797</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.656264163006107</v>
+        <v>7.656110841706417</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04563034751963686</v>
+        <v>0.045662363617621</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494022531136781</v>
+        <v>1.493924649974304</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941975068002079</v>
+        <v>1.941904910797003</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566740877719633</v>
+        <v>0.7566865314462325</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248668503191132</v>
+        <v>0.5248955636574641</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552629345070836</v>
+        <v>0.7552740408881552</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.041827485380117</v>
+        <v>5.042406866325785</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.145717438749221</v>
+        <v>5.1508767004283</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.288467105263158</v>
+        <v>5.307924397370344</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61641253939939</v>
+        <v>10.61630764537078</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3113508589070208</v>
+        <v>0.3112459648784043</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052824897744368</v>
+        <v>2.052885207192902</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698544012743743</v>
+        <v>2.698613532196115</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568907875343141</v>
+        <v>0.3568950657385004</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1208088304763995</v>
+        <v>-0.120866579410192</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3365642675242468</v>
+        <v>0.3365876110851956</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.549714188281349</v>
+        <v>9.435413266409938</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.701567103211692</v>
+        <v>9.659484052468869</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.928445160574924</v>
+        <v>9.928850240808252</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E11" t="n">
+        <v>13839</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13838</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13837</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.24308607357086</v>
+        <v>5.243049356843475</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579342105263158</v>
+        <v>0.4579393718042367</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216634396189384</v>
+        <v>5.216624021135274</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02645167738147693</v>
+        <v>-0.02642533570819948</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161436914524357</v>
+        <v>1.161386568446875</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482919674738604</v>
+        <v>1.482877188540336</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293744554432981</v>
+        <v>0.4293665792061002</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09203447130259845</v>
+        <v>-0.09204069787057367</v>
       </c>
       <c r="X11" t="n">
-        <v>0.427563150312487</v>
+        <v>0.4275547306707295</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.995995982422611</v>
+        <v>3.837874108324963</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.479531922880748</v>
+        <v>4.356886429287633</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.838975236450073</v>
+        <v>4.843584743305142</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E12" t="n">
+        <v>4157</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4156</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4155</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.467467148014441</v>
+        <v>7.466937800769971</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.20530701754386</v>
+        <v>2.205339663988313</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.64098603691138</v>
+        <v>7.640456611904739</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735188888969388</v>
+        <v>0.1735188111347672</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9127786451261189</v>
+        <v>0.9128332116991217</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194632852596428</v>
+        <v>1.194591182630715</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8321188586634455</v>
+        <v>0.8321321815647882</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6596241306514032</v>
+        <v>0.6596604893542284</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8303376516024925</v>
+        <v>0.8303492164457906</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.334646658945474</v>
+        <v>4.350707671173137</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.198350784111268</v>
+        <v>5.261129409740339</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.671282625210923</v>
+        <v>5.669327472107493</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E13" t="n">
+        <v>6492</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6491</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6490</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.602706086286595</v>
+        <v>9.602314358342321</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02559313896982</v>
+        <v>10.02550226998659</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4228870526832293</v>
+        <v>0.4231879116442704</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691642454944692</v>
+        <v>1.691617809822761</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150360688935566</v>
+        <v>2.150209052400121</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232410492164258</v>
+        <v>0.82325128012061</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6487808663644843</v>
+        <v>0.6488028587083601</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8103352933529753</v>
+        <v>0.8103112477618677</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.445768416788887</v>
+        <v>6.421740216851885</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.493389120147667</v>
+        <v>7.336806686730894</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.451278535477748</v>
+        <v>8.444725486796344</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E14" t="n">
+        <v>14079</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14078</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14077</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.127675285927399</v>
+        <v>8.127489522659468</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077022417153996</v>
+        <v>0.9077258339420502</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198382284167472</v>
+        <v>8.198227347068306</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0707069982400729</v>
+        <v>0.07073782440883605</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756208931793209</v>
+        <v>1.75615091374471</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282345706489632</v>
+        <v>2.282294918427205</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809026769790948</v>
+        <v>0.7809036012625509</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654942599996915</v>
+        <v>0.5655003394335779</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805208756010451</v>
+        <v>0.7805211579885414</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.145017819549524</v>
+        <v>5.138913958232661</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.167339468059261</v>
+        <v>5.163084376834567</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.198115845986931</v>
+        <v>5.198502935390775</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.669641812865497</v>
+        <v>4.66945288531775</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82137295518759</v>
+        <v>11.82127049055363</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1425144278391915</v>
+        <v>-0.1426168924731481</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052498019518522</v>
+        <v>2.052503612982874</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697736579483698</v>
+        <v>2.697762908452182</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950011007089779</v>
+        <v>0.795002805956967</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095682054622225</v>
+        <v>0.6095605844686425</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863976510854853</v>
+        <v>0.7864075317252538</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.722212860499562</v>
+        <v>7.714527444563539</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.010684764125781</v>
+        <v>8.728383453989965</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.0915905947206</v>
+        <v>11.09079811042947</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E16" t="n">
+        <v>9842</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9841</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9840</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.3628418699187</v>
+        <v>8.362716085763642</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623883542750722</v>
+        <v>8.623813648969698</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2610416728320225</v>
+        <v>0.2610975632060558</v>
       </c>
       <c r="T16" t="n">
-        <v>3.593800139133999</v>
+        <v>3.593996407012671</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08974911187125</v>
+        <v>11.08929666826463</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04159378818061465</v>
+        <v>0.0415772557403965</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6101384594835322</v>
+        <v>-0.6101674164159894</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02493094975694066</v>
+        <v>0.02491461757265667</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.62183213205211</v>
+        <v>11.6148937257598</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.85674748734831</v>
+        <v>11.9354273948127</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.42951770141462</v>
+        <v>12.6251370975914</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E17" t="n">
+        <v>2386</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2385</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2384</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.484615142617449</v>
+        <v>6.483216981132076</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.424473684210526</v>
+        <v>1.425723155588021</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.847095679844357</v>
+        <v>6.845897222741704</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3624805372269074</v>
+        <v>0.3626802416096284</v>
       </c>
       <c r="T17" t="n">
-        <v>2.014677789848211</v>
+        <v>2.013973798329986</v>
       </c>
       <c r="U17" t="n">
-        <v>2.551576061500764</v>
+        <v>2.55089569461494</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5357798076741909</v>
+        <v>0.5360965416824552</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04982161749607295</v>
+        <v>0.05057594781037289</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5324183452043492</v>
+        <v>0.532728502557049</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.500569361422194</v>
+        <v>1.501486886390149</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.07372394114318</v>
+        <v>2.958215001400307</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.965805163914089</v>
+        <v>3.965050520028069</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E18" t="n">
+        <v>3245</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3244</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3243</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.473066296638915</v>
+        <v>6.472544389642417</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66769932762961</v>
+        <v>6.667373549256757</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1946330309906964</v>
+        <v>0.1948291596143407</v>
       </c>
       <c r="T18" t="n">
-        <v>1.096591997846893</v>
+        <v>1.096254345568987</v>
       </c>
       <c r="U18" t="n">
-        <v>1.485105204781221</v>
+        <v>1.484835030320936</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6073899632088985</v>
+        <v>0.607481071258996</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2295564468698404</v>
+        <v>0.2298369847106035</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6044626145640888</v>
+        <v>0.6045329265986719</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.32749311790645</v>
+        <v>2.309149274324748</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.167306363777119</v>
+        <v>3.892613687961822</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.958705806076221</v>
+        <v>4.93946599097553</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E19" t="n">
+        <v>7199</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7198</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7197</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32825955259136</v>
+        <v>10.32697193664907</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12267003705497</v>
+        <v>11.12176626111575</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7944104844636133</v>
+        <v>0.7947943244666841</v>
       </c>
       <c r="T19" t="n">
-        <v>2.055797753806017</v>
+        <v>2.056399567387743</v>
       </c>
       <c r="U19" t="n">
-        <v>2.78056234098697</v>
+        <v>2.781309151345859</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272767163785619</v>
+        <v>0.7273119157907766</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4713226538055455</v>
+        <v>0.4713964913616737</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6782109545473262</v>
+        <v>0.6781770026615803</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.195866456079751</v>
+        <v>7.179448136634774</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.308590034869257</v>
+        <v>7.297404237697608</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.393999915348726</v>
+        <v>7.391316143917949</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E20" t="n">
+        <v>10649</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10648</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10647</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85885927559038</v>
+        <v>13.85847644695819</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23526337868622</v>
+        <v>14.23487396914985</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764041030958336</v>
+        <v>0.3763975221916591</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255607924514889</v>
+        <v>1.255506599496482</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647323685836043</v>
+        <v>1.647243395086532</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8934921649834366</v>
+        <v>0.8935066963307829</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7788846162910783</v>
+        <v>0.7789135168545166</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8886788857253415</v>
+        <v>0.8886931109296291</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.541942414592484</v>
+        <v>9.434033208598962</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.801373797647502</v>
+        <v>9.763177894862286</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.994661942518009</v>
+        <v>9.984572131494325</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16696</v>
+        <v>16697</v>
       </c>
       <c r="E21" t="n">
         <v>10244</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10243</v>
+        <v>10244</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8691868593185</v>
+        <v>130.8690619875049</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9737505916297</v>
+        <v>130.9735008234349</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045637323111056</v>
+        <v>0.1044388359300122</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7977819466317958</v>
+        <v>0.7978079938706576</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046376337251175</v>
+        <v>1.04638104586893</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649893887480181</v>
+        <v>0.8649854974639815</v>
       </c>
       <c r="W21" t="n">
-        <v>0.730909623753117</v>
+        <v>0.7308914955575176</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642486885256411</v>
+        <v>0.8642520056457597</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5944255672721</v>
+        <v>128.24704578748</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2361412443899</v>
+        <v>129.2008364540051</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5970531425409</v>
+        <v>129.5971298020423</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.195866456079751</v>
+        <v>7.179448136634774</v>
       </c>
       <c r="G2" t="n">
-        <v>7.308590034869257</v>
+        <v>7.29740423769761</v>
       </c>
       <c r="H2" t="n">
-        <v>7.393999915348726</v>
+        <v>7.391316143917949</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824168865056753</v>
+        <v>4.824254906352557</v>
       </c>
       <c r="G3" t="n">
-        <v>4.900288418442054</v>
+        <v>4.88823624017583</v>
       </c>
       <c r="H3" t="n">
-        <v>4.988846777343804</v>
+        <v>4.99120542831444</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.995995982422611</v>
+        <v>3.837874108324963</v>
       </c>
       <c r="G4" t="n">
-        <v>4.479531922880747</v>
+        <v>4.356886429287633</v>
       </c>
       <c r="H4" t="n">
-        <v>4.838975236450073</v>
+        <v>4.843584743305142</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.62183213205211</v>
+        <v>11.6148937257598</v>
       </c>
       <c r="G5" t="n">
-        <v>11.85674748734831</v>
+        <v>11.9354273948127</v>
       </c>
       <c r="H5" t="n">
-        <v>12.42951770141462</v>
+        <v>12.6251370975914</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.13277182770479</v>
+        <v>52.95087305144219</v>
       </c>
       <c r="G6" t="n">
-        <v>104.1582155019414</v>
+        <v>102.7818757537659</v>
       </c>
       <c r="H6" t="n">
-        <v>108.8319156924261</v>
+        <v>108.9257893896179</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.722212860499562</v>
+        <v>7.714527444563539</v>
       </c>
       <c r="G7" t="n">
-        <v>9.010684764125784</v>
+        <v>8.728383453989965</v>
       </c>
       <c r="H7" t="n">
-        <v>11.0915905947206</v>
+        <v>11.09079811042947</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.445768416788887</v>
+        <v>6.421740216851885</v>
       </c>
       <c r="G8" t="n">
-        <v>7.493389120147668</v>
+        <v>7.336806686730894</v>
       </c>
       <c r="H8" t="n">
-        <v>8.451278535477748</v>
+        <v>8.444725486796344</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.334646658945474</v>
+        <v>4.350707671173137</v>
       </c>
       <c r="G9" t="n">
-        <v>5.198350784111269</v>
+        <v>5.261129409740339</v>
       </c>
       <c r="H9" t="n">
-        <v>5.671282625210923</v>
+        <v>5.669327472107493</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.619625538614982</v>
+        <v>4.619957326753671</v>
       </c>
       <c r="G10" t="n">
-        <v>4.78227838159861</v>
+        <v>4.785048311921882</v>
       </c>
       <c r="H10" t="n">
-        <v>4.975092481011981</v>
+        <v>4.98745875924312</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.541942414592484</v>
+        <v>9.434033208598962</v>
       </c>
       <c r="G11" t="n">
-        <v>9.8013737976475</v>
+        <v>9.763177894862284</v>
       </c>
       <c r="H11" t="n">
-        <v>9.994661942518009</v>
+        <v>9.984572131494325</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.500569361422194</v>
+        <v>1.501486886390149</v>
       </c>
       <c r="G12" t="n">
-        <v>3.07372394114318</v>
+        <v>2.958215001400307</v>
       </c>
       <c r="H12" t="n">
-        <v>3.965805163914089</v>
+        <v>3.965050520028069</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.145017819549524</v>
+        <v>5.138913958232661</v>
       </c>
       <c r="G13" t="n">
-        <v>5.167339468059261</v>
+        <v>5.163084376834567</v>
       </c>
       <c r="H13" t="n">
-        <v>5.198115845986931</v>
+        <v>5.198502935390775</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.549714188281349</v>
+        <v>9.435413266409938</v>
       </c>
       <c r="G14" t="n">
-        <v>9.701567103211692</v>
+        <v>9.659484052468869</v>
       </c>
       <c r="H14" t="n">
-        <v>9.928445160574924</v>
+        <v>9.928850240808252</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.041827485380117</v>
+        <v>5.042406866325785</v>
       </c>
       <c r="G15" t="n">
-        <v>5.145717438749221</v>
+        <v>5.1508767004283</v>
       </c>
       <c r="H15" t="n">
-        <v>5.288467105263158</v>
+        <v>5.307924397370344</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.36944032847321</v>
+        <v>6.364754742587006</v>
       </c>
       <c r="G16" t="n">
-        <v>6.419187784890648</v>
+        <v>6.403682812201706</v>
       </c>
       <c r="H16" t="n">
-        <v>6.536811046794437</v>
+        <v>6.529671727712269</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.32749311790645</v>
+        <v>2.309149274324748</v>
       </c>
       <c r="G17" t="n">
-        <v>4.167306363777119</v>
+        <v>3.892613687961822</v>
       </c>
       <c r="H17" t="n">
-        <v>4.958705806076221</v>
+        <v>4.93946599097553</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.829652474029719</v>
+        <v>2.747476260043828</v>
       </c>
       <c r="G18" t="n">
-        <v>3.141479514299198</v>
+        <v>3.09454389018665</v>
       </c>
       <c r="H18" t="n">
-        <v>3.283293128654971</v>
+        <v>3.280226442658875</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.926995641447369</v>
+        <v>1.927969354912345</v>
       </c>
       <c r="G19" t="n">
-        <v>2.059047959624182</v>
+        <v>2.042680756099311</v>
       </c>
       <c r="H19" t="n">
-        <v>2.198164473684211</v>
+        <v>2.204196859021183</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.343139340635405</v>
+        <v>4.341741868509302</v>
       </c>
       <c r="G20" t="n">
-        <v>5.342492262919523</v>
+        <v>5.229613502088382</v>
       </c>
       <c r="H20" t="n">
-        <v>6.140195595775055</v>
+        <v>6.145526739997051</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5944255672721</v>
+        <v>128.24704578748</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2361412443899</v>
+        <v>129.200836454005</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5970531425409</v>
+        <v>129.5971298020423</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E2" t="n">
         <v>10033</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10032</v>
+        <v>10033</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6039522195641</v>
+        <v>102.5993749293997</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5958242625169</v>
+        <v>102.5958022086482</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.008127957047144738</v>
+        <v>-0.003572720751491304</v>
       </c>
       <c r="T2" t="n">
-        <v>17.935710671747</v>
+        <v>17.93953491033721</v>
       </c>
       <c r="U2" t="n">
-        <v>36.03155108463373</v>
+        <v>36.0337297987621</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387454101702119</v>
+        <v>0.1387088426481452</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7192112915097884</v>
+        <v>-0.719112065139454</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1387432735961563</v>
+        <v>0.138706480363977</v>
       </c>
       <c r="Y2" t="n">
-        <v>52.95087305144219</v>
+        <v>105.8312308480083</v>
       </c>
       <c r="Z2" t="n">
-        <v>102.7818757537659</v>
+        <v>108.8573164947604</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.9257893896179</v>
+        <v>110.8069785124008</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E3" t="n">
         <v>14627</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14626</v>
+        <v>14627</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.907538561465882</v>
+        <v>4.907355506939222</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965251001003814</v>
+        <v>4.965014804007172</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05771243953793217</v>
+        <v>0.0576592970679502</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344126094706994</v>
+        <v>1.34403484124969</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71876375469577</v>
+        <v>1.718704988281475</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814427522642758</v>
+        <v>0.7814637214785011</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5698946859071765</v>
+        <v>0.5699253824519407</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803978568951071</v>
+        <v>0.7804215902695886</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.927969354912345</v>
+        <v>1.927051739279197</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.042680756099311</v>
+        <v>2.015886030128771</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.204196859021183</v>
+        <v>2.1575</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E4" t="n">
         <v>10261</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10260</v>
+        <v>10261</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.906826754385966</v>
+        <v>6.906425543319365</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.236408297356834</v>
+        <v>7.235947811238645</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295815429708698</v>
+        <v>0.3295222679192809</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292037109252373</v>
+        <v>1.291931372351407</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681584679071461</v>
+        <v>1.681487248628711</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678437865016283</v>
+        <v>0.8678685999966753</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7378416687694556</v>
+        <v>0.7378866356326986</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473107166417688</v>
+        <v>0.8473498942487112</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.747476260043828</v>
+        <v>2.621074475364964</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.094543890186649</v>
+        <v>3.102360796664449</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.280226442658875</v>
+        <v>3.222718051437044</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.824007791575359</v>
+        <v>2.82385401459854</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302421127448966</v>
+        <v>9.30230433287273</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3699597020264829</v>
+        <v>0.3698429074502458</v>
       </c>
       <c r="T5" t="n">
-        <v>1.24786130532519</v>
+        <v>1.247825003546653</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747423680554833</v>
+        <v>1.747389426010649</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660484992993296</v>
+        <v>0.8660562040532129</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214243752572156</v>
+        <v>0.7214352969216321</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596192723770117</v>
+        <v>0.8596328644719342</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.341741868509302</v>
+        <v>4.340435324335251</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.229613502088382</v>
+        <v>5.051887611294424</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.145526739997051</v>
+        <v>6.113616838640548</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E6" t="n">
         <v>8873</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022635604528472</v>
+        <v>7.022621380642222</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2885793101522743</v>
+        <v>0.2885650862660242</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479100223179476</v>
+        <v>1.479117002100318</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907886944457932</v>
+        <v>1.907911713587441</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3043813198387086</v>
+        <v>0.3043835460649784</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1978010782910815</v>
+        <v>-0.1978321793819569</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2795033547124275</v>
+        <v>0.2795148863141869</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.364754742587006</v>
+        <v>6.347791912760331</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.403682812201706</v>
+        <v>6.386245759561239</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.529671727712269</v>
+        <v>6.461006719157965</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E7" t="n">
         <v>14235</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14234</v>
+        <v>14235</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580732295911199</v>
+        <v>5.58069641728135</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567341501672164</v>
+        <v>5.567278269605553</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01339079423903384</v>
+        <v>-0.01341814767579651</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166665417936366</v>
+        <v>1.166619820910831</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509973306893526</v>
+        <v>1.509946180993871</v>
       </c>
       <c r="V7" t="n">
-        <v>0.504809052816674</v>
+        <v>0.5048069434306807</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05311711873089964</v>
+        <v>0.05309182474540686</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026576991267889</v>
+        <v>0.5026577400741448</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.824254906352557</v>
+        <v>4.823587591240876</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.888236240175829</v>
+        <v>4.869819726753482</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.99120542831444</v>
+        <v>4.94687754238899</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E8" t="n">
         <v>9033</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9032</v>
+        <v>9033</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.875048715677591</v>
+        <v>7.874796855972544</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.114425846276951</v>
+        <v>8.114007349470496</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2393771305993617</v>
+        <v>0.2392104934979506</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445763110386684</v>
+        <v>1.445679772948819</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825501835147426</v>
+        <v>1.8254190997424</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079143994267322</v>
+        <v>0.8079290385613992</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275957978816837</v>
+        <v>0.6276121702881874</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978306842170934</v>
+        <v>0.7978674838506692</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.619957326753671</v>
+        <v>4.619667815992807</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.785048311921882</v>
+        <v>4.800083976626115</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.98745875924312</v>
+        <v>5.09807981274386</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E9" t="n">
         <v>13898</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13897</v>
+        <v>13898</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610448478088797</v>
+        <v>7.610280795797958</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.656110841706417</v>
+        <v>7.655877362936618</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.045662363617621</v>
+        <v>0.04559656713866139</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493924649974304</v>
+        <v>1.493836660229504</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941904910797003</v>
+        <v>1.941840927503765</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566865314462325</v>
+        <v>0.7567040736652046</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248955636574641</v>
+        <v>0.5249160760117243</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552740408881552</v>
+        <v>0.7552951482149604</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.042406866325785</v>
+        <v>5.039671532846715</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.1508767004283</v>
+        <v>5.161307758417904</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.307924397370344</v>
+        <v>5.308032846715329</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61630764537078</v>
+        <v>10.61620363143672</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3112459648784043</v>
+        <v>0.3111419509443449</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052885207192902</v>
+        <v>2.052942980956759</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698613532196115</v>
+        <v>2.698681003910047</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568950657385004</v>
+        <v>0.3568992429431737</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.120866579410192</v>
+        <v>-0.120922628736057</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3365876110851956</v>
+        <v>0.3366103532826894</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.435413266409938</v>
+        <v>9.339284958302493</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.659484052468869</v>
+        <v>9.606674198267498</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.928850240808252</v>
+        <v>9.733283701411056</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E11" t="n">
         <v>13839</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13838</v>
+        <v>13839</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243049356843475</v>
+        <v>5.243037574969289</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579393718042367</v>
+        <v>0.4579051094890511</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216624021135274</v>
+        <v>5.216543663201373</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02642533570819948</v>
+        <v>-0.02649391176791836</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161386568446875</v>
+        <v>1.161352129240099</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482877188540336</v>
+        <v>1.482844208035713</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293665792061002</v>
+        <v>0.4293735095192326</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09204069787057367</v>
+        <v>-0.09206999320348719</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275547306707295</v>
+        <v>0.4275645826924808</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.837874108324963</v>
+        <v>3.828550515508997</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.356886429287633</v>
+        <v>4.222420821341825</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.843584743305142</v>
+        <v>4.576317846824662</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E12" t="n">
         <v>4157</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4156</v>
+        <v>4157</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.466937800769971</v>
+        <v>7.466416526341111</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205339663988313</v>
+        <v>2.205328467153285</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.640456611904739</v>
+        <v>7.639679710223705</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735188111347672</v>
+        <v>0.1732631838825933</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9128332116991217</v>
+        <v>0.9128266323621581</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194591182630715</v>
+        <v>1.194533120451592</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8321321815647882</v>
+        <v>0.832171474989296</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6596604893542284</v>
+        <v>0.6597033628628945</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8303492164457906</v>
+        <v>0.8304006410193655</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.350707671173137</v>
+        <v>4.711687065566762</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.261129409740339</v>
+        <v>5.340880140880189</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.669327472107493</v>
+        <v>5.657323703568664</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E13" t="n">
         <v>6492</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6491</v>
+        <v>6492</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.602314358342321</v>
+        <v>9.601956638940235</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02550226998659</v>
+        <v>10.02504168199743</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4231879116442704</v>
+        <v>0.423085043057198</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691617809822761</v>
+        <v>1.691400804210249</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150209052400121</v>
+        <v>2.150017013922283</v>
       </c>
       <c r="V13" t="n">
-        <v>0.82325128012061</v>
+        <v>0.8232713496886161</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6488028587083601</v>
+        <v>0.6488336520485074</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8103112477618677</v>
+        <v>0.8103462380512749</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.421740216851885</v>
+        <v>6.409358831360592</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.336806686730894</v>
+        <v>7.087779953560231</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.444725486796344</v>
+        <v>8.142866447245289</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E14" t="n">
         <v>14079</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14078</v>
+        <v>14079</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.127489522659468</v>
+        <v>8.127303608210809</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077258339420502</v>
+        <v>0.9076155717761557</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198227347068306</v>
+        <v>8.197884843058926</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07073782440883605</v>
+        <v>0.07058123484811565</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75615091374471</v>
+        <v>1.755968476602463</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282294918427205</v>
+        <v>2.282148658447543</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809036012625509</v>
+        <v>0.7809360704653244</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5655003394335779</v>
+        <v>0.5655428029835216</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805211579885414</v>
+        <v>0.780556789236852</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.138913958232661</v>
+        <v>5.118887781055847</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.163084376834567</v>
+        <v>5.152763627136067</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.198502935390775</v>
+        <v>5.178027522949923</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.66945288531775</v>
+        <v>4.669264233576643</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82127049055363</v>
+        <v>11.82117252680077</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1426168924731481</v>
+        <v>-0.1427148562260105</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052503612982874</v>
+        <v>2.052509315578662</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697762908452182</v>
+        <v>2.697789714670597</v>
       </c>
       <c r="V15" t="n">
-        <v>0.795002805956967</v>
+        <v>0.7950043343320162</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095605844686425</v>
+        <v>0.6095528252573224</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864075317252538</v>
+        <v>0.7864171379297104</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.714527444563539</v>
+        <v>7.706544946919777</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.728383453989965</v>
+        <v>8.327641279110193</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.09079811042947</v>
+        <v>10.95878977373747</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E16" t="n">
         <v>9842</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9841</v>
+        <v>9842</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.362716085763642</v>
+        <v>8.36257661044503</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623813648969698</v>
+        <v>8.624016456716458</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2610975632060558</v>
+        <v>0.2614398462714266</v>
       </c>
       <c r="T16" t="n">
-        <v>3.593996407012671</v>
+        <v>3.59412635080395</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08929666826463</v>
+        <v>11.08883578837701</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0415772557403965</v>
+        <v>0.0415673460423573</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6101674164159894</v>
+        <v>-0.6101931475907367</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02491461757265667</v>
+        <v>0.02490435893230714</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.6148937257598</v>
+        <v>11.67301544516199</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.9354273948127</v>
+        <v>12.0796366735907</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.6251370975914</v>
+        <v>12.77832293016288</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E17" t="n">
         <v>2386</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.483216981132076</v>
+        <v>6.48203792958927</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.425723155588021</v>
+        <v>1.425510948905109</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.845897222741704</v>
+        <v>6.844559966333741</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3626802416096284</v>
+        <v>0.3625220367444696</v>
       </c>
       <c r="T17" t="n">
-        <v>2.013973798329986</v>
+        <v>2.013154863739763</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55089569461494</v>
+        <v>2.550385560835112</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5360965416824552</v>
+        <v>0.5363428939768985</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05057594781037289</v>
+        <v>0.05101699481109478</v>
       </c>
       <c r="X17" t="n">
-        <v>0.532728502557049</v>
+        <v>0.5329743520683644</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.501486886390149</v>
+        <v>1.616183575538954</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.958215001400307</v>
+        <v>2.99045536886136</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.965050520028069</v>
+        <v>3.980869413511753</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E18" t="n">
         <v>3245</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.472544389642417</v>
+        <v>6.472072110939906</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.667373549256757</v>
+        <v>6.666794181468972</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948291596143407</v>
+        <v>0.1947220705290632</v>
       </c>
       <c r="T18" t="n">
-        <v>1.096254345568987</v>
+        <v>1.095931423646498</v>
       </c>
       <c r="U18" t="n">
-        <v>1.484835030320936</v>
+        <v>1.484617854843949</v>
       </c>
       <c r="V18" t="n">
-        <v>0.607481071258996</v>
+        <v>0.6076034192898644</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2298369847106035</v>
+        <v>0.230019596077051</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6045329265986719</v>
+        <v>0.6046643951932871</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.309149274324748</v>
+        <v>2.460856027660907</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.892613687961822</v>
+        <v>4.049372873231933</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.93946599097553</v>
+        <v>4.917984420345957</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E19" t="n">
         <v>7199</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7198</v>
+        <v>7199</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32697193664907</v>
+        <v>10.32570551465481</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12176626111575</v>
+        <v>11.12115826886687</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7947943244666841</v>
+        <v>0.7954527542120519</v>
       </c>
       <c r="T19" t="n">
-        <v>2.056399567387743</v>
+        <v>2.056985240858798</v>
       </c>
       <c r="U19" t="n">
-        <v>2.781309151345859</v>
+        <v>2.782074424122339</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7273119157907766</v>
+        <v>0.7273372463938322</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4713964913616737</v>
+        <v>0.4714490954354866</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6781770026615803</v>
+        <v>0.6780758527654316</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.179448136634774</v>
+        <v>7.186723235379398</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.297404237697608</v>
+        <v>7.307010850032457</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.391316143917949</v>
+        <v>7.43659393034788</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E20" t="n">
         <v>10649</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10648</v>
+        <v>10649</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85847644695819</v>
+        <v>13.85809815073817</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23487396914985</v>
+        <v>14.23442114432899</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3763975221916591</v>
+        <v>0.3763229935908091</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255506599496482</v>
+        <v>1.255391554158781</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647243395086532</v>
+        <v>1.64716713411685</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935066963307829</v>
+        <v>0.8935209106944746</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7789135168545166</v>
+        <v>0.7789406751130266</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8886931109296291</v>
+        <v>0.888712907519235</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.434033208598962</v>
+        <v>9.382594220008098</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.763177894862286</v>
+        <v>9.756600453489575</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.984572131494325</v>
+        <v>9.877688959994599</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16697</v>
+        <v>16698</v>
       </c>
       <c r="E21" t="n">
         <v>10244</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9735008234349</v>
+        <v>130.9734594758477</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1044388359300122</v>
+        <v>0.1043974883428019</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7978079938706576</v>
+        <v>0.7978133840261346</v>
       </c>
       <c r="U21" t="n">
-        <v>1.04638104586893</v>
+        <v>1.046390139026719</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649854974639815</v>
+        <v>0.8649860506834949</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7308914955575176</v>
+        <v>0.7308868183766083</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642520056457597</v>
+        <v>0.8642559343942966</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.24704578748</v>
+        <v>128.2484847189327</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2008364540051</v>
+        <v>129.1512371040647</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5971298020423</v>
+        <v>129.5967465162187</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.179448136634774</v>
+        <v>7.186723235379398</v>
       </c>
       <c r="G2" t="n">
-        <v>7.29740423769761</v>
+        <v>7.307010850032457</v>
       </c>
       <c r="H2" t="n">
-        <v>7.391316143917949</v>
+        <v>7.43659393034788</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824254906352557</v>
+        <v>4.823587591240876</v>
       </c>
       <c r="G3" t="n">
-        <v>4.88823624017583</v>
+        <v>4.869819726753482</v>
       </c>
       <c r="H3" t="n">
-        <v>4.99120542831444</v>
+        <v>4.94687754238899</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.837874108324963</v>
+        <v>3.828550515508997</v>
       </c>
       <c r="G4" t="n">
-        <v>4.356886429287633</v>
+        <v>4.222420821341825</v>
       </c>
       <c r="H4" t="n">
-        <v>4.843584743305142</v>
+        <v>4.576317846824662</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.6148937257598</v>
+        <v>11.67301544516199</v>
       </c>
       <c r="G5" t="n">
-        <v>11.9354273948127</v>
+        <v>12.0796366735907</v>
       </c>
       <c r="H5" t="n">
-        <v>12.6251370975914</v>
+        <v>12.77832293016288</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>52.95087305144219</v>
+        <v>105.8312308480083</v>
       </c>
       <c r="G6" t="n">
-        <v>102.7818757537659</v>
+        <v>108.8573164947604</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9257893896179</v>
+        <v>110.8069785124008</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.714527444563539</v>
+        <v>7.706544946919777</v>
       </c>
       <c r="G7" t="n">
-        <v>8.728383453989965</v>
+        <v>8.327641279110193</v>
       </c>
       <c r="H7" t="n">
-        <v>11.09079811042947</v>
+        <v>10.95878977373747</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.421740216851885</v>
+        <v>6.409358831360592</v>
       </c>
       <c r="G8" t="n">
-        <v>7.336806686730894</v>
+        <v>7.087779953560231</v>
       </c>
       <c r="H8" t="n">
-        <v>8.444725486796344</v>
+        <v>8.142866447245289</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.350707671173137</v>
+        <v>4.711687065566762</v>
       </c>
       <c r="G9" t="n">
-        <v>5.261129409740339</v>
+        <v>5.340880140880189</v>
       </c>
       <c r="H9" t="n">
-        <v>5.669327472107493</v>
+        <v>5.657323703568664</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.619957326753671</v>
+        <v>4.619667815992807</v>
       </c>
       <c r="G10" t="n">
-        <v>4.785048311921882</v>
+        <v>4.800083976626116</v>
       </c>
       <c r="H10" t="n">
-        <v>4.98745875924312</v>
+        <v>5.09807981274386</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.434033208598962</v>
+        <v>9.382594220008098</v>
       </c>
       <c r="G11" t="n">
-        <v>9.763177894862284</v>
+        <v>9.756600453489577</v>
       </c>
       <c r="H11" t="n">
-        <v>9.984572131494325</v>
+        <v>9.877688959994599</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.501486886390149</v>
+        <v>1.616183575538954</v>
       </c>
       <c r="G12" t="n">
-        <v>2.958215001400307</v>
+        <v>2.99045536886136</v>
       </c>
       <c r="H12" t="n">
-        <v>3.965050520028069</v>
+        <v>3.980869413511753</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.138913958232661</v>
+        <v>5.118887781055847</v>
       </c>
       <c r="G13" t="n">
-        <v>5.163084376834567</v>
+        <v>5.152763627136067</v>
       </c>
       <c r="H13" t="n">
-        <v>5.198502935390775</v>
+        <v>5.178027522949923</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.435413266409938</v>
+        <v>9.339284958302493</v>
       </c>
       <c r="G14" t="n">
-        <v>9.659484052468869</v>
+        <v>9.606674198267498</v>
       </c>
       <c r="H14" t="n">
-        <v>9.928850240808252</v>
+        <v>9.733283701411056</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.042406866325785</v>
+        <v>5.039671532846715</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1508767004283</v>
+        <v>5.161307758417903</v>
       </c>
       <c r="H15" t="n">
-        <v>5.307924397370344</v>
+        <v>5.308032846715329</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.364754742587006</v>
+        <v>6.347791912760331</v>
       </c>
       <c r="G16" t="n">
-        <v>6.403682812201706</v>
+        <v>6.386245759561239</v>
       </c>
       <c r="H16" t="n">
-        <v>6.529671727712269</v>
+        <v>6.461006719157965</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.309149274324748</v>
+        <v>2.460856027660907</v>
       </c>
       <c r="G17" t="n">
-        <v>3.892613687961822</v>
+        <v>4.049372873231933</v>
       </c>
       <c r="H17" t="n">
-        <v>4.93946599097553</v>
+        <v>4.917984420345957</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.747476260043828</v>
+        <v>2.621074475364964</v>
       </c>
       <c r="G18" t="n">
-        <v>3.09454389018665</v>
+        <v>3.10236079666445</v>
       </c>
       <c r="H18" t="n">
-        <v>3.280226442658875</v>
+        <v>3.222718051437044</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.927969354912345</v>
+        <v>1.927051739279197</v>
       </c>
       <c r="G19" t="n">
-        <v>2.042680756099311</v>
+        <v>2.015886030128771</v>
       </c>
       <c r="H19" t="n">
-        <v>2.204196859021183</v>
+        <v>2.1575</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.341741868509302</v>
+        <v>4.340435324335251</v>
       </c>
       <c r="G20" t="n">
-        <v>5.229613502088382</v>
+        <v>5.051887611294424</v>
       </c>
       <c r="H20" t="n">
-        <v>6.145526739997051</v>
+        <v>6.113616838640548</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.24704578748</v>
+        <v>128.2484847189327</v>
       </c>
       <c r="G21" t="n">
-        <v>129.200836454005</v>
+        <v>129.1512371040647</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5971298020423</v>
+        <v>129.5967465162187</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E2" t="n">
-        <v>10033</v>
+        <v>10035</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10033</v>
+        <v>10034</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5993749293997</v>
+        <v>102.5895942462295</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5958022086482</v>
+        <v>102.5725442819268</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.003572720751491304</v>
+        <v>-0.01704996430272219</v>
       </c>
       <c r="T2" t="n">
-        <v>17.93953491033721</v>
+        <v>17.96200436394647</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0337297987621</v>
+        <v>36.06778817700883</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387088426481452</v>
+        <v>0.1387119574169825</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.719112065139454</v>
+        <v>-0.720348688158871</v>
       </c>
       <c r="X2" t="n">
-        <v>0.138706480363977</v>
+        <v>0.1387109689428808</v>
       </c>
       <c r="Y2" t="n">
-        <v>105.8312308480083</v>
+        <v>105.7889202568853</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.8573164947604</v>
+        <v>108.8456375975896</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.8069785124008</v>
+        <v>110.8066713133277</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E3" t="n">
-        <v>14627</v>
+        <v>14629</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14627</v>
+        <v>14628</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.907355506939222</v>
+        <v>4.907188884331419</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.965014804007172</v>
+        <v>4.964993084969548</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0576592970679502</v>
+        <v>0.0578042006381299</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34403484124969</v>
+        <v>1.343988578434508</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718704988281475</v>
+        <v>1.718665340575093</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814637214785011</v>
+        <v>0.781458961050342</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699253824519407</v>
+        <v>0.5699411901553051</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804215902695886</v>
+        <v>0.7804096488192883</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.927051739279197</v>
+        <v>1.930321478391685</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.015886030128771</v>
+        <v>2.019534557782895</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1575</v>
+        <v>2.159721013438865</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E4" t="n">
-        <v>10261</v>
+        <v>10263</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10261</v>
+        <v>10262</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.906425543319365</v>
+        <v>6.906041950886768</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.235947811238645</v>
+        <v>7.235713762395704</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295222679192809</v>
+        <v>0.3296718115089374</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291931372351407</v>
+        <v>1.291903818062057</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681487248628711</v>
+        <v>1.681445313767066</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678685999966753</v>
+        <v>0.8678804535708247</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7378866356326986</v>
+        <v>0.7379108339549865</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473498942487112</v>
+        <v>0.8473238345943881</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.621074475364964</v>
+        <v>2.625971194611597</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.102360796664449</v>
+        <v>3.099443555202373</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.222718051437044</v>
+        <v>3.21671726129422</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82385401459854</v>
+        <v>2.823700461949915</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.30230433287273</v>
+        <v>9.30219378383728</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3698429074502458</v>
+        <v>0.3697323584147977</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247825003546653</v>
+        <v>1.247787977186182</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747389426010649</v>
+        <v>1.74735673983058</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660562040532129</v>
+        <v>0.8660635947101722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214352969216321</v>
+        <v>0.7214457183317087</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596328644719342</v>
+        <v>0.8596458278553671</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.340435324335251</v>
+        <v>4.339041863121294</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.051887611294424</v>
+        <v>5.045610827224881</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.113616838640548</v>
+        <v>6.09279840387687</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E6" t="n">
-        <v>8873</v>
+        <v>8876</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8873</v>
+        <v>8875</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734056294376197</v>
+        <v>6.734313126760563</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022621380642222</v>
+        <v>7.023218286448627</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2885650862660242</v>
+        <v>0.2889051596880635</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479117002100318</v>
+        <v>1.479187513110513</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907911713587441</v>
+        <v>1.907918432821578</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3043835460649784</v>
+        <v>0.3042120492127053</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1978321793819569</v>
+        <v>-0.1979991789915032</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2795148863141869</v>
+        <v>0.2793015099287002</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.347791912760331</v>
+        <v>6.361361384575396</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.386245759561239</v>
+        <v>6.394071295920277</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.461006719157965</v>
+        <v>6.466952755719532</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E7" t="n">
-        <v>14235</v>
+        <v>14237</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14235</v>
+        <v>14236</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.58069641728135</v>
+        <v>5.580667216914863</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567278269605553</v>
+        <v>5.567292791269217</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01341814767579651</v>
+        <v>-0.01337442564564599</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166619820910831</v>
+        <v>1.16652394553225</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509946180993871</v>
+        <v>1.509869493514042</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048069434306807</v>
+        <v>0.5048104947088485</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05309182474540686</v>
+        <v>0.05312620015389147</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026577400741448</v>
+        <v>0.5026585124850645</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.823587591240876</v>
+        <v>4.824462800875273</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.869819726753482</v>
+        <v>4.871170837948925</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.94687754238899</v>
+        <v>4.950158364395548</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E8" t="n">
-        <v>9033</v>
+        <v>9035</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9033</v>
+        <v>9034</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.874796855972544</v>
+        <v>7.874564423289795</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.114007349470496</v>
+        <v>8.114121798063156</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2392104934979506</v>
+        <v>0.2395573747733604</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445679772948819</v>
+        <v>1.44565861523219</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8254190997424</v>
+        <v>1.825408324418952</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079290385613992</v>
+        <v>0.8079077232581183</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6276121702881874</v>
+        <v>0.6275956225581577</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978674838506692</v>
+        <v>0.797797887362463</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.619667815992807</v>
+        <v>4.631168986045213</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.800083976626115</v>
+        <v>4.814140990153557</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.09807981274386</v>
+        <v>5.099675625605074</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E9" t="n">
-        <v>13898</v>
+        <v>13900</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13898</v>
+        <v>13899</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610280795797958</v>
+        <v>7.610156126340025</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655877362936618</v>
+        <v>7.655901978480639</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04559656713866139</v>
+        <v>0.0457458521406154</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493836660229504</v>
+        <v>1.493770666369443</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941840927503765</v>
+        <v>1.941777525678608</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567040736652046</v>
+        <v>0.7566964114950291</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5249160760117243</v>
+        <v>0.524925385847997</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552951482149604</v>
+        <v>0.7552808179760038</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.039671532846715</v>
+        <v>5.043563092633114</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.161307758417904</v>
+        <v>5.16604022691697</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.308032846715329</v>
+        <v>5.309378555798687</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61620363143672</v>
+        <v>10.61609841360147</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3111419509443449</v>
+        <v>0.3110367331090966</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052942980956759</v>
+        <v>2.052994801029636</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698681003910047</v>
+        <v>2.69874050581274</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568992429431737</v>
+        <v>0.3569061474331628</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.120922628736057</v>
+        <v>-0.1209720586348639</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3366103532826894</v>
+        <v>0.3366352539587926</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.339284958302493</v>
+        <v>9.339028732949975</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.606674198267498</v>
+        <v>9.606302734232628</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.733283701411056</v>
+        <v>9.733467301920601</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E11" t="n">
-        <v>13839</v>
+        <v>13841</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13839</v>
+        <v>13840</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243037574969289</v>
+        <v>5.2430675216763</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579051094890511</v>
+        <v>0.4579496717724289</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216543663201373</v>
+        <v>5.216646718604402</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02649391176791836</v>
+        <v>-0.02642080307189935</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161352129240099</v>
+        <v>1.161393061168545</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482844208035713</v>
+        <v>1.482847582403395</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293735095192326</v>
+        <v>0.4293042442928947</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09206999320348719</v>
+        <v>-0.09215110451742925</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275645826924808</v>
+        <v>0.4274919576724492</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.828550515508997</v>
+        <v>3.829340848251279</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.222420821341825</v>
+        <v>4.224234421166212</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.576317846824662</v>
+        <v>4.581675517445749</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E12" t="n">
-        <v>4157</v>
+        <v>4159</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4157</v>
+        <v>4158</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.466416526341111</v>
+        <v>7.465884078884079</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205328467153285</v>
+        <v>2.205404814004376</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.639679710223705</v>
+        <v>7.639461551444772</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732631838825933</v>
+        <v>0.1735774725606943</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9128266323621581</v>
+        <v>0.9127917371902087</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194533120451592</v>
+        <v>1.194410999294834</v>
       </c>
       <c r="V12" t="n">
-        <v>0.832171474989296</v>
+        <v>0.8321805190952025</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6597033628628945</v>
+        <v>0.6597867323010265</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8304006410193655</v>
+        <v>0.830390459259884</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.711687065566762</v>
+        <v>4.740195763043427</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.340880140880189</v>
+        <v>5.34571804954121</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.657323703568664</v>
+        <v>5.65645980731333</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E13" t="n">
-        <v>6492</v>
+        <v>6494</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6492</v>
+        <v>6493</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.601956638940235</v>
+        <v>9.601654474048976</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02504168199743</v>
+        <v>10.02538948341881</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.423085043057198</v>
+        <v>0.4237350093698365</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691400804210249</v>
+        <v>1.691497838226266</v>
       </c>
       <c r="U13" t="n">
-        <v>2.150017013922283</v>
+        <v>2.149922560818415</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232713496886161</v>
+        <v>0.8232596968169017</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6488336520485074</v>
+        <v>0.6488260582579513</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8103462380512749</v>
+        <v>0.8102541297269191</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.409358831360592</v>
+        <v>6.441146388383139</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.087779953560231</v>
+        <v>7.09437323494272</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.142866447245289</v>
+        <v>8.114901297948345</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E14" t="n">
-        <v>14079</v>
+        <v>14081</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14079</v>
+        <v>14080</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.127303608210809</v>
+        <v>8.127134588068182</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9076155717761557</v>
+        <v>0.9077729151470946</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197884843058926</v>
+        <v>8.197950093815354</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07058123484811565</v>
+        <v>0.07081550574717238</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755968476602463</v>
+        <v>1.756086812287091</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282148658447543</v>
+        <v>2.282219987198102</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809360704653244</v>
+        <v>0.7808981527095085</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5655428029835216</v>
+        <v>0.5654993166904811</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780556789236852</v>
+        <v>0.7805142056284929</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.118887781055847</v>
+        <v>5.129754512785028</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.152763627136067</v>
+        <v>5.155763913688343</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.178027522949923</v>
+        <v>5.182506132845325</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.669264233576643</v>
+        <v>4.669075857038658</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82117252680077</v>
+        <v>11.82104939956475</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1427148562260105</v>
+        <v>-0.1428379834620365</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052509315578662</v>
+        <v>2.052542867833799</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697789714670597</v>
+        <v>2.697817114106664</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950043343320162</v>
+        <v>0.7950060861639328</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095528252573224</v>
+        <v>0.6095448942561253</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864171379297104</v>
+        <v>0.7864270283734884</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.706544946919777</v>
+        <v>7.699055125660172</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.327641279110193</v>
+        <v>8.322934088780272</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.95878977373747</v>
+        <v>10.9566535302847</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E16" t="n">
-        <v>9842</v>
+        <v>9844</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9842</v>
+        <v>9843</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.36257661044503</v>
+        <v>8.362411764705882</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624016456716458</v>
+        <v>8.623609169972383</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2614398462714266</v>
+        <v>0.2611974052664998</v>
       </c>
       <c r="T16" t="n">
-        <v>3.59412635080395</v>
+        <v>3.594520550687041</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08883578837701</v>
+        <v>11.08843353081345</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0415673460423573</v>
+        <v>0.04153899780777998</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6101931475907367</v>
+        <v>-0.61023429478961</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02490435893230714</v>
+        <v>0.02487694572292631</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.67301544516199</v>
+        <v>11.67048045136837</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.0796366735907</v>
+        <v>12.07815025775719</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.77832293016288</v>
+        <v>12.77811569824935</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E17" t="n">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.48203792958927</v>
+        <v>6.480912232928362</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.425510948905109</v>
+        <v>1.428216630196937</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.844559966333741</v>
+        <v>6.843745425337374</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3625220367444696</v>
+        <v>0.3628331924090117</v>
       </c>
       <c r="T17" t="n">
-        <v>2.013154863739763</v>
+        <v>2.012385423307685</v>
       </c>
       <c r="U17" t="n">
-        <v>2.550385560835112</v>
+        <v>2.54956678300939</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5363428939768985</v>
+        <v>0.5365564556465843</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05101699481109478</v>
+        <v>0.05164707168366445</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5329743520683644</v>
+        <v>0.5331808302555638</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.616183575538954</v>
+        <v>1.621410173391252</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99045536886136</v>
+        <v>2.995041200888593</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.980869413511753</v>
+        <v>3.969303723283486</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E18" t="n">
-        <v>3245</v>
+        <v>3247</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.472072110939906</v>
+        <v>6.471618607516943</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.666794181468972</v>
+        <v>6.66676267841773</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1947220705290632</v>
+        <v>0.1951440709007866</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095931423646498</v>
+        <v>1.095569402534545</v>
       </c>
       <c r="U18" t="n">
-        <v>1.484617854843949</v>
+        <v>1.484332670227119</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6076034192898644</v>
+        <v>0.6076031657807747</v>
       </c>
       <c r="W18" t="n">
-        <v>0.230019596077051</v>
+        <v>0.2302577092177571</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6046643951932871</v>
+        <v>0.6046190135900544</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.460856027660907</v>
+        <v>2.464003987287078</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.049372873231933</v>
+        <v>4.05656737480645</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.917984420345957</v>
+        <v>4.923725634523991</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E19" t="n">
-        <v>7199</v>
+        <v>7201</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7199</v>
+        <v>7200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32570551465481</v>
+        <v>10.32444673611111</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12115826886687</v>
+        <v>11.11994659978922</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7954527542120519</v>
+        <v>0.7954998636781069</v>
       </c>
       <c r="T19" t="n">
-        <v>2.056985240858798</v>
+        <v>2.057566711405276</v>
       </c>
       <c r="U19" t="n">
-        <v>2.782074424122339</v>
+        <v>2.782707543150536</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7273372463938322</v>
+        <v>0.7273862791946525</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4714490954354866</v>
+        <v>0.4715467515364361</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780758527654316</v>
+        <v>0.6781297870628653</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.186723235379398</v>
+        <v>7.179642723728252</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.307010850032457</v>
+        <v>7.302773007740521</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.43659393034788</v>
+        <v>7.434091240403312</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E20" t="n">
-        <v>10649</v>
+        <v>10651</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10649</v>
+        <v>10650</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85809815073817</v>
+        <v>13.85773189739069</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23442114432899</v>
+        <v>14.23413689606342</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3763229935908091</v>
+        <v>0.3764049986727345</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255391554158781</v>
+        <v>1.255295034383376</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64716713411685</v>
+        <v>1.647088805692355</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935209106944746</v>
+        <v>0.8935333752760898</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7789406751130266</v>
+        <v>0.7789666643241582</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888712907519235</v>
+        <v>0.8887176306944031</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.382594220008098</v>
+        <v>9.385174339476038</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.756600453489575</v>
+        <v>9.761663793079549</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.877688959994599</v>
+        <v>9.890701938557834</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16698</v>
+        <v>16699</v>
       </c>
       <c r="E21" t="n">
-        <v>10244</v>
+        <v>10247</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10244</v>
+        <v>10246</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8690619875049</v>
+        <v>130.8687752293578</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9734594758477</v>
+        <v>130.973370492334</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1043974883428019</v>
+        <v>0.1045952629762157</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7978133840261346</v>
+        <v>0.7976730715872994</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046390139026719</v>
+        <v>1.046283442818875</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649860506834949</v>
+        <v>0.8649894863162201</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7308868183766083</v>
+        <v>0.7309171560969349</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642559343942966</v>
+        <v>0.8642447439895887</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2484847189327</v>
+        <v>128.2535316377792</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1512371040647</v>
+        <v>129.155594177186</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5967465162187</v>
+        <v>129.5964559649138</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.186723235379398</v>
+        <v>7.179642723728252</v>
       </c>
       <c r="G2" t="n">
-        <v>7.307010850032457</v>
+        <v>7.302773007740521</v>
       </c>
       <c r="H2" t="n">
-        <v>7.43659393034788</v>
+        <v>7.434091240403312</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.823587591240876</v>
+        <v>4.824462800875273</v>
       </c>
       <c r="G3" t="n">
-        <v>4.869819726753482</v>
+        <v>4.871170837948926</v>
       </c>
       <c r="H3" t="n">
-        <v>4.94687754238899</v>
+        <v>4.950158364395548</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.828550515508997</v>
+        <v>3.829340848251279</v>
       </c>
       <c r="G4" t="n">
-        <v>4.222420821341825</v>
+        <v>4.224234421166213</v>
       </c>
       <c r="H4" t="n">
-        <v>4.576317846824662</v>
+        <v>4.581675517445749</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67301544516199</v>
+        <v>11.67048045136837</v>
       </c>
       <c r="G5" t="n">
-        <v>12.0796366735907</v>
+        <v>12.07815025775719</v>
       </c>
       <c r="H5" t="n">
-        <v>12.77832293016288</v>
+        <v>12.77811569824935</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>105.8312308480083</v>
+        <v>105.7889202568853</v>
       </c>
       <c r="G6" t="n">
-        <v>108.8573164947604</v>
+        <v>108.8456375975896</v>
       </c>
       <c r="H6" t="n">
-        <v>110.8069785124008</v>
+        <v>110.8066713133277</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.706544946919777</v>
+        <v>7.699055125660172</v>
       </c>
       <c r="G7" t="n">
-        <v>8.327641279110193</v>
+        <v>8.32293408878027</v>
       </c>
       <c r="H7" t="n">
-        <v>10.95878977373747</v>
+        <v>10.9566535302847</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.409358831360592</v>
+        <v>6.441146388383139</v>
       </c>
       <c r="G8" t="n">
-        <v>7.087779953560231</v>
+        <v>7.094373234942722</v>
       </c>
       <c r="H8" t="n">
-        <v>8.142866447245289</v>
+        <v>8.114901297948345</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.711687065566762</v>
+        <v>4.740195763043427</v>
       </c>
       <c r="G9" t="n">
-        <v>5.340880140880189</v>
+        <v>5.34571804954121</v>
       </c>
       <c r="H9" t="n">
-        <v>5.657323703568664</v>
+        <v>5.65645980731333</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.619667815992807</v>
+        <v>4.631168986045213</v>
       </c>
       <c r="G10" t="n">
-        <v>4.800083976626116</v>
+        <v>4.814140990153557</v>
       </c>
       <c r="H10" t="n">
-        <v>5.09807981274386</v>
+        <v>5.099675625605074</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.382594220008098</v>
+        <v>9.385174339476038</v>
       </c>
       <c r="G11" t="n">
-        <v>9.756600453489577</v>
+        <v>9.761663793079551</v>
       </c>
       <c r="H11" t="n">
-        <v>9.877688959994599</v>
+        <v>9.890701938557834</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.616183575538954</v>
+        <v>1.621410173391252</v>
       </c>
       <c r="G12" t="n">
-        <v>2.99045536886136</v>
+        <v>2.995041200888593</v>
       </c>
       <c r="H12" t="n">
-        <v>3.980869413511753</v>
+        <v>3.969303723283486</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.118887781055847</v>
+        <v>5.129754512785028</v>
       </c>
       <c r="G13" t="n">
-        <v>5.152763627136067</v>
+        <v>5.155763913688344</v>
       </c>
       <c r="H13" t="n">
-        <v>5.178027522949923</v>
+        <v>5.182506132845325</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.339284958302493</v>
+        <v>9.339028732949975</v>
       </c>
       <c r="G14" t="n">
-        <v>9.606674198267498</v>
+        <v>9.60630273423263</v>
       </c>
       <c r="H14" t="n">
-        <v>9.733283701411056</v>
+        <v>9.733467301920601</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.039671532846715</v>
+        <v>5.043563092633114</v>
       </c>
       <c r="G15" t="n">
-        <v>5.161307758417903</v>
+        <v>5.16604022691697</v>
       </c>
       <c r="H15" t="n">
-        <v>5.308032846715329</v>
+        <v>5.309378555798687</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.347791912760331</v>
+        <v>6.361361384575396</v>
       </c>
       <c r="G16" t="n">
-        <v>6.386245759561239</v>
+        <v>6.394071295920277</v>
       </c>
       <c r="H16" t="n">
-        <v>6.461006719157965</v>
+        <v>6.466952755719532</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.460856027660907</v>
+        <v>2.464003987287078</v>
       </c>
       <c r="G17" t="n">
-        <v>4.049372873231933</v>
+        <v>4.05656737480645</v>
       </c>
       <c r="H17" t="n">
-        <v>4.917984420345957</v>
+        <v>4.923725634523991</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.621074475364964</v>
+        <v>2.625971194611597</v>
       </c>
       <c r="G18" t="n">
-        <v>3.10236079666445</v>
+        <v>3.099443555202373</v>
       </c>
       <c r="H18" t="n">
-        <v>3.222718051437044</v>
+        <v>3.21671726129422</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.927051739279197</v>
+        <v>1.930321478391685</v>
       </c>
       <c r="G19" t="n">
-        <v>2.015886030128771</v>
+        <v>2.019534557782895</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1575</v>
+        <v>2.159721013438865</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.340435324335251</v>
+        <v>4.339041863121294</v>
       </c>
       <c r="G20" t="n">
-        <v>5.051887611294424</v>
+        <v>5.045610827224881</v>
       </c>
       <c r="H20" t="n">
-        <v>6.113616838640548</v>
+        <v>6.09279840387687</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.2484847189327</v>
+        <v>128.2535316377792</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1512371040647</v>
+        <v>129.155594177186</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5967465162187</v>
+        <v>129.5964559649138</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E2" t="n">
+        <v>10036</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10035</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10034</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5895942462295</v>
+        <v>102.5798513868128</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5725442819268</v>
+        <v>102.5566916975522</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01704996430272219</v>
+        <v>-0.02315968926066251</v>
       </c>
       <c r="T2" t="n">
-        <v>17.96200436394647</v>
+        <v>17.97557871520354</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06778817700883</v>
+        <v>36.09363189305395</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387119574169825</v>
+        <v>0.1387888260976728</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.720348688158871</v>
+        <v>-0.7208189196297412</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1387109689428808</v>
+        <v>0.1387882923841056</v>
       </c>
       <c r="Y2" t="n">
-        <v>105.7889202568853</v>
+        <v>53.02206158202378</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.8456375975896</v>
+        <v>97.55098656314232</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.8066713133277</v>
+        <v>109.1990930495947</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E3" t="n">
+        <v>14630</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14629</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14628</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.907188884331419</v>
+        <v>4.907034930617267</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964993084969548</v>
+        <v>4.964876326635725</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0578042006381299</v>
+        <v>0.05784139601845792</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343988578434508</v>
+        <v>1.343949916862881</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718665340575093</v>
+        <v>1.718630127681188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.781458961050342</v>
+        <v>0.7814608941969635</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699411901553051</v>
+        <v>0.5699511239183098</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804096488192883</v>
+        <v>0.7804097684940482</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.930321478391685</v>
+        <v>1.930828570432079</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.019534557782895</v>
+        <v>2.009334365436257</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.159721013438865</v>
+        <v>2.187837918673763</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E4" t="n">
+        <v>10264</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10263</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10262</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.906041950886768</v>
+        <v>6.905677677092468</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.235713762395704</v>
+        <v>7.235408429920849</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3296718115089374</v>
+        <v>0.3297307528283797</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291903818062057</v>
+        <v>1.2918087896436</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681445313767066</v>
+        <v>1.68139522314358</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678804535708247</v>
+        <v>0.8678927155415546</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379108339549865</v>
+        <v>0.7379339953470649</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473238345943881</v>
+        <v>0.847321732664052</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.625971194611597</v>
+        <v>2.506516913758967</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.099443555202373</v>
+        <v>3.031955805326518</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.21671726129422</v>
+        <v>3.244331893702296</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.823700461949915</v>
+        <v>2.82354713313897</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.30219378383728</v>
+        <v>9.302125427407207</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3697323584147977</v>
+        <v>0.3696640019847239</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247787977186182</v>
+        <v>1.247744356134443</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74735673983058</v>
+        <v>1.747311220228457</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660635947101722</v>
+        <v>0.8660728156452376</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214457183317087</v>
+        <v>0.7214602311265212</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596458278553671</v>
+        <v>0.8596584976707475</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.339041863121294</v>
+        <v>4.336497900680703</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.045610827224881</v>
+        <v>4.793335240956321</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.09279840387687</v>
+        <v>5.803077538827242</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E6" t="n">
+        <v>8877</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8876</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8875</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734313126760563</v>
+        <v>6.734423332582245</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023218286448627</v>
+        <v>7.023335669845681</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889051596880635</v>
+        <v>0.2889123372634365</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479187513110513</v>
+        <v>1.479168076489154</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907918432821578</v>
+        <v>1.90787305423544</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3042120492127053</v>
+        <v>0.3041647958416371</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979991789915032</v>
+        <v>-0.1980346675445777</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2793015099287002</v>
+        <v>0.2792446820525915</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.361361384575396</v>
+        <v>6.260880647553049</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.394071295920277</v>
+        <v>6.370830984258905</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.466952755719532</v>
+        <v>6.396526784156267</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E7" t="n">
+        <v>14238</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14237</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14236</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580667216914863</v>
+        <v>5.580642586219007</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567292791269217</v>
+        <v>5.56728035631245</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01337442564564599</v>
+        <v>-0.0133622299065567</v>
       </c>
       <c r="T7" t="n">
-        <v>1.16652394553225</v>
+        <v>1.166467775106709</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509869493514042</v>
+        <v>1.509822916083204</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048104947088485</v>
+        <v>0.5048061660310356</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05312620015389147</v>
+        <v>0.05312150715097375</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026585124850645</v>
+        <v>0.5026538581250732</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.824462800875273</v>
+        <v>4.816711612030415</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.871170837948925</v>
+        <v>4.849414727608409</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.950158364395548</v>
+        <v>4.91140728568867</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E8" t="n">
+        <v>9036</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9035</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9034</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.874564423289795</v>
+        <v>7.874348090758161</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.114121798063156</v>
+        <v>8.11401475701488</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2395573747733604</v>
+        <v>0.2396666662567168</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44565861523219</v>
+        <v>1.445675347199092</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825408324418952</v>
+        <v>1.825414057959843</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079077232581183</v>
+        <v>0.8078905155538226</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275956225581577</v>
+        <v>0.6275696603005325</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797797887362463</v>
+        <v>0.7977665079354251</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.631168986045213</v>
+        <v>4.636054517833048</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.814140990153557</v>
+        <v>4.858070756323103</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.099675625605074</v>
+        <v>5.103093429627048</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E9" t="n">
+        <v>13901</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13900</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13899</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610156126340025</v>
+        <v>7.610038129496403</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655901978480639</v>
+        <v>7.655819010055869</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0457458521406154</v>
+        <v>0.04578088055946609</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493770666369443</v>
+        <v>1.49373500750759</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941777525678608</v>
+        <v>1.941733492699927</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566964114950291</v>
+        <v>0.7566935461260516</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524925385847997</v>
+        <v>0.5249243374570114</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552808179760038</v>
+        <v>0.7552766643760885</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.043563092633114</v>
+        <v>5.044139941690962</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.16604022691697</v>
+        <v>5.198613001046214</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.309378555798687</v>
+        <v>5.309855685131195</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61609841360147</v>
+        <v>10.61598731435981</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3110367331090966</v>
+        <v>0.3109256338674348</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052994801029636</v>
+        <v>2.053040171994087</v>
       </c>
       <c r="U10" t="n">
-        <v>2.69874050581274</v>
+        <v>2.698794637718906</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569061474331628</v>
+        <v>0.3569168335829799</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1209720586348639</v>
+        <v>-0.121017028473744</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3366352539587926</v>
+        <v>0.3366644489258112</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.339028732949975</v>
+        <v>9.430073593029617</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.606302734232628</v>
+        <v>9.604655934541919</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.733467301920601</v>
+        <v>9.733679766914483</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E11" t="n">
+        <v>13842</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13841</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13840</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2430675216763</v>
+        <v>5.243038219781807</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579496717724289</v>
+        <v>0.4579548104956269</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216646718604402</v>
+        <v>5.216562274822253</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02642080307189935</v>
+        <v>-0.02647594495955476</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161393061168545</v>
+        <v>1.161317753445624</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482847582403395</v>
+        <v>1.48278891266702</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293042442928947</v>
+        <v>0.4293210437636885</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09215110451742925</v>
+        <v>-0.09213714290763231</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4274919576724492</v>
+        <v>0.4275098624240046</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.829340848251279</v>
+        <v>3.761588921282799</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.224234421166212</v>
+        <v>4.246903895791023</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.581675517445749</v>
+        <v>4.589975665234268</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E12" t="n">
+        <v>4160</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4159</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4158</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.465884078884079</v>
+        <v>7.465353089685021</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205404814004376</v>
+        <v>2.205437317784257</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.639461551444772</v>
+        <v>7.639125772275229</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735774725606943</v>
+        <v>0.1737726825902076</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9127917371902087</v>
+        <v>0.9126503993043076</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194410999294834</v>
+        <v>1.194314216574686</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8321805190952025</v>
+        <v>0.8321978260995102</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6597867323010265</v>
+        <v>0.6598551758055213</v>
       </c>
       <c r="X12" t="n">
-        <v>0.830390459259884</v>
+        <v>0.830396347045115</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.740195763043427</v>
+        <v>4.667493098516746</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.34571804954121</v>
+        <v>5.323286439819958</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.65645980731333</v>
+        <v>5.656112859415579</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E13" t="n">
+        <v>6495</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6494</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6493</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.601654474048976</v>
+        <v>9.601337388358484</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02538948341881</v>
+        <v>10.02522295501518</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4237350093698365</v>
+        <v>0.4238855666566902</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691497838226266</v>
+        <v>1.691304907651733</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149922560818415</v>
+        <v>2.14971857327212</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232596968169017</v>
+        <v>0.8232724503816234</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6488260582579513</v>
+        <v>0.6488560392348219</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102541297269191</v>
+        <v>0.8102428253797391</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.441146388383139</v>
+        <v>6.445518169115286</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.09437323494272</v>
+        <v>6.790869140703242</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.114901297948345</v>
+        <v>7.664598543788477</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E14" t="n">
+        <v>14082</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14081</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14080</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.127134588068182</v>
+        <v>8.126974291598609</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077729151470946</v>
+        <v>0.9077964042759962</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197950093815354</v>
+        <v>8.197824387517819</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07081550574717238</v>
+        <v>0.07085009591921135</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756086812287091</v>
+        <v>1.756086254460124</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282219987198102</v>
+        <v>2.282198901497165</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808981527095085</v>
+        <v>0.7808909677452156</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654993166904811</v>
+        <v>0.5654896012669015</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805142056284929</v>
+        <v>0.7805063402959523</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.129754512785028</v>
+        <v>5.107421149789443</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.155763913688343</v>
+        <v>5.141236383545111</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.182506132845325</v>
+        <v>5.162888788954171</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.669075857038658</v>
+        <v>4.668887755102041</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82104939956475</v>
+        <v>11.82097046417811</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1428379834620365</v>
+        <v>-0.1429169188486725</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052542867833799</v>
+        <v>2.052531828690395</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697817114106664</v>
+        <v>2.69784173381115</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950060861639328</v>
+        <v>0.7950075073025041</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095448942561253</v>
+        <v>0.6095377678033121</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864270283734884</v>
+        <v>0.7864360961378578</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.699055125660172</v>
+        <v>7.694622790697875</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.322934088780272</v>
+        <v>7.932170410628082</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.9566535302847</v>
+        <v>8.406449448550184</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E16" t="n">
+        <v>9845</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9844</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9843</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.362411764705882</v>
+        <v>8.36223527021536</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623609169972383</v>
+        <v>8.623488826099939</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2611974052664998</v>
+        <v>0.2612535558845787</v>
       </c>
       <c r="T16" t="n">
-        <v>3.594520550687041</v>
+        <v>3.594811272814512</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08843353081345</v>
+        <v>11.0880150149165</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04153899780777998</v>
+        <v>0.04151829549862806</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.61023429478961</v>
+        <v>-0.6102698582357564</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02487694572292631</v>
+        <v>0.0248564775357184</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.67048045136837</v>
+        <v>11.74084307744742</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.07815025775719</v>
+        <v>12.30701593800071</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.77811569824935</v>
+        <v>12.82505141031926</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E17" t="n">
+        <v>2389</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2388</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2387</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.480912232928362</v>
+        <v>6.479768634840871</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.428216630196937</v>
+        <v>1.429460641399417</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.843745425337374</v>
+        <v>6.842635599282518</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3628331924090117</v>
+        <v>0.3628669644416472</v>
       </c>
       <c r="T17" t="n">
-        <v>2.012385423307685</v>
+        <v>2.011562808540041</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54956678300939</v>
+        <v>2.54889408960383</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5365564556465843</v>
+        <v>0.5367930560083057</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05164707168366445</v>
+        <v>0.05218221499516995</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5331808302555638</v>
+        <v>0.5334142588867354</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.621410173391252</v>
+        <v>1.288120018553863</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.995041200888593</v>
+        <v>2.839451841729517</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.969303723283486</v>
+        <v>3.687168710437843</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E18" t="n">
+        <v>3248</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3247</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3246</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.471618607516943</v>
+        <v>6.471168463196796</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66676267841773</v>
+        <v>6.666279678920601</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1951440709007866</v>
+        <v>0.1951112157238042</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095569402534545</v>
+        <v>1.095196862652063</v>
       </c>
       <c r="U18" t="n">
-        <v>1.484332670227119</v>
+        <v>1.484030782937756</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6076031657807747</v>
+        <v>0.6077172660475587</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2302577092177571</v>
+        <v>0.230510619392219</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6046190135900544</v>
+        <v>0.6047284195266163</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.464003987287078</v>
+        <v>2.232008202553629</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.05656737480645</v>
+        <v>3.966680549281747</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.923725634523991</v>
+        <v>5.108239398733303</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E19" t="n">
+        <v>7202</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7201</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7200</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32444673611111</v>
+        <v>10.32319559783363</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11994659978922</v>
+        <v>11.11905153251387</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7954998636781069</v>
+        <v>0.7958559346802316</v>
       </c>
       <c r="T19" t="n">
-        <v>2.057566711405276</v>
+        <v>2.058124506089779</v>
       </c>
       <c r="U19" t="n">
-        <v>2.782707543150536</v>
+        <v>2.783371269565381</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7273862791946525</v>
+        <v>0.7274274825709989</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4715467515364361</v>
+        <v>0.471627656050652</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6781297870628653</v>
+        <v>0.678109508805041</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.179642723728252</v>
+        <v>7.146706692602829</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.302773007740521</v>
+        <v>7.274015869152035</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.434091240403312</v>
+        <v>7.359011994431813</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E20" t="n">
+        <v>10652</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10651</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10650</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85773189739069</v>
+        <v>13.85737392800778</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23413689606342</v>
+        <v>14.23379609941064</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764049986727345</v>
+        <v>0.3764221714028634</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255295034383376</v>
+        <v>1.255210428651881</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647088805692355</v>
+        <v>1.647016330997399</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935333752760898</v>
+        <v>0.8935450434403149</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7789666643241582</v>
+        <v>0.7789899394820382</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887176306944031</v>
+        <v>0.8887272460872018</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.385174339476038</v>
+        <v>9.275726441893093</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.761663793079549</v>
+        <v>9.655322423385481</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.890701938557834</v>
+        <v>9.901155435590297</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16699</v>
+        <v>16700</v>
       </c>
       <c r="E21" t="n">
+        <v>10248</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10247</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10246</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8687752293578</v>
+        <v>130.8686357958427</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.973370492334</v>
+        <v>130.9732918239778</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045952629762157</v>
+        <v>0.1046560281351549</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976730715872994</v>
+        <v>0.7976211664646483</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046283442818875</v>
+        <v>1.046242327870104</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649894863162201</v>
+        <v>0.8649912763044802</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7309171560969349</v>
+        <v>0.730925219607556</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642447439895887</v>
+        <v>0.864243150320013</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2535316377792</v>
+        <v>128.250474422916</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.155594177186</v>
+        <v>128.9562131955052</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5964559649138</v>
+        <v>129.5960983981505</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.179642723728252</v>
+        <v>7.146706692602829</v>
       </c>
       <c r="G2" t="n">
-        <v>7.302773007740521</v>
+        <v>7.274015869152033</v>
       </c>
       <c r="H2" t="n">
-        <v>7.434091240403312</v>
+        <v>7.359011994431813</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824462800875273</v>
+        <v>4.816711612030415</v>
       </c>
       <c r="G3" t="n">
-        <v>4.871170837948926</v>
+        <v>4.849414727608409</v>
       </c>
       <c r="H3" t="n">
-        <v>4.950158364395548</v>
+        <v>4.91140728568867</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.829340848251279</v>
+        <v>3.761588921282799</v>
       </c>
       <c r="G4" t="n">
-        <v>4.224234421166213</v>
+        <v>4.246903895791023</v>
       </c>
       <c r="H4" t="n">
-        <v>4.581675517445749</v>
+        <v>4.589975665234268</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67048045136837</v>
+        <v>11.74084307744742</v>
       </c>
       <c r="G5" t="n">
-        <v>12.07815025775719</v>
+        <v>12.30701593800071</v>
       </c>
       <c r="H5" t="n">
-        <v>12.77811569824935</v>
+        <v>12.82505141031926</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>105.7889202568853</v>
+        <v>53.02206158202378</v>
       </c>
       <c r="G6" t="n">
-        <v>108.8456375975896</v>
+        <v>97.5509865631423</v>
       </c>
       <c r="H6" t="n">
-        <v>110.8066713133277</v>
+        <v>109.1990930495947</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.699055125660172</v>
+        <v>7.694622790697875</v>
       </c>
       <c r="G7" t="n">
-        <v>8.32293408878027</v>
+        <v>7.932170410628082</v>
       </c>
       <c r="H7" t="n">
-        <v>10.9566535302847</v>
+        <v>8.406449448550184</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.441146388383139</v>
+        <v>6.445518169115286</v>
       </c>
       <c r="G8" t="n">
-        <v>7.094373234942722</v>
+        <v>6.790869140703242</v>
       </c>
       <c r="H8" t="n">
-        <v>8.114901297948345</v>
+        <v>7.664598543788477</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.740195763043427</v>
+        <v>4.667493098516746</v>
       </c>
       <c r="G9" t="n">
-        <v>5.34571804954121</v>
+        <v>5.323286439819958</v>
       </c>
       <c r="H9" t="n">
-        <v>5.65645980731333</v>
+        <v>5.656112859415579</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.631168986045213</v>
+        <v>4.636054517833048</v>
       </c>
       <c r="G10" t="n">
-        <v>4.814140990153557</v>
+        <v>4.858070756323103</v>
       </c>
       <c r="H10" t="n">
-        <v>5.099675625605074</v>
+        <v>5.103093429627048</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.385174339476038</v>
+        <v>9.275726441893093</v>
       </c>
       <c r="G11" t="n">
-        <v>9.761663793079551</v>
+        <v>9.655322423385481</v>
       </c>
       <c r="H11" t="n">
-        <v>9.890701938557834</v>
+        <v>9.901155435590297</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.621410173391252</v>
+        <v>1.288120018553863</v>
       </c>
       <c r="G12" t="n">
-        <v>2.995041200888593</v>
+        <v>2.839451841729517</v>
       </c>
       <c r="H12" t="n">
-        <v>3.969303723283486</v>
+        <v>3.687168710437843</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.129754512785028</v>
+        <v>5.107421149789443</v>
       </c>
       <c r="G13" t="n">
-        <v>5.155763913688344</v>
+        <v>5.141236383545111</v>
       </c>
       <c r="H13" t="n">
-        <v>5.182506132845325</v>
+        <v>5.162888788954171</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.339028732949975</v>
+        <v>9.430073593029617</v>
       </c>
       <c r="G14" t="n">
-        <v>9.60630273423263</v>
+        <v>9.604655934541919</v>
       </c>
       <c r="H14" t="n">
-        <v>9.733467301920601</v>
+        <v>9.733679766914483</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.043563092633114</v>
+        <v>5.044139941690962</v>
       </c>
       <c r="G15" t="n">
-        <v>5.16604022691697</v>
+        <v>5.198613001046214</v>
       </c>
       <c r="H15" t="n">
-        <v>5.309378555798687</v>
+        <v>5.309855685131195</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.361361384575396</v>
+        <v>6.260880647553049</v>
       </c>
       <c r="G16" t="n">
-        <v>6.394071295920277</v>
+        <v>6.370830984258905</v>
       </c>
       <c r="H16" t="n">
-        <v>6.466952755719532</v>
+        <v>6.396526784156267</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.464003987287078</v>
+        <v>2.232008202553629</v>
       </c>
       <c r="G17" t="n">
-        <v>4.05656737480645</v>
+        <v>3.966680549281746</v>
       </c>
       <c r="H17" t="n">
-        <v>4.923725634523991</v>
+        <v>5.108239398733303</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.625971194611597</v>
+        <v>2.506516913758967</v>
       </c>
       <c r="G18" t="n">
-        <v>3.099443555202373</v>
+        <v>3.031955805326518</v>
       </c>
       <c r="H18" t="n">
-        <v>3.21671726129422</v>
+        <v>3.244331893702296</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.930321478391685</v>
+        <v>1.930828570432079</v>
       </c>
       <c r="G19" t="n">
-        <v>2.019534557782895</v>
+        <v>2.009334365436257</v>
       </c>
       <c r="H19" t="n">
-        <v>2.159721013438865</v>
+        <v>2.187837918673763</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.339041863121294</v>
+        <v>4.336497900680703</v>
       </c>
       <c r="G20" t="n">
-        <v>5.045610827224881</v>
+        <v>4.793335240956322</v>
       </c>
       <c r="H20" t="n">
-        <v>6.09279840387687</v>
+        <v>5.803077538827242</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.2535316377792</v>
+        <v>128.250474422916</v>
       </c>
       <c r="G21" t="n">
-        <v>129.155594177186</v>
+        <v>128.9562131955052</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5964559649138</v>
+        <v>129.5960983981505</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E2" t="n">
+        <v>10037</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10036</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10035</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5798513868128</v>
+        <v>102.585805965192</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5566916975522</v>
+        <v>102.5712906641608</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02315968926066251</v>
+        <v>-0.0145153010311559</v>
       </c>
       <c r="T2" t="n">
-        <v>17.97557871520354</v>
+        <v>17.95770136249036</v>
       </c>
       <c r="U2" t="n">
-        <v>36.09363189305395</v>
+        <v>36.04408232647991</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387888260976728</v>
+        <v>0.1387898046978817</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7208189196297412</v>
+        <v>-0.7192123104637675</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1387882923841056</v>
+        <v>0.1387877742953688</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.02206158202378</v>
+        <v>53.59426973092864</v>
       </c>
       <c r="Z2" t="n">
-        <v>97.55098656314232</v>
+        <v>102.8656263778089</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.1990930495947</v>
+        <v>109.4863723665399</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E3" t="n">
+        <v>14631</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14630</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14629</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.907034930617267</v>
+        <v>4.906896889952153</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964876326635725</v>
+        <v>4.964761395264531</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05784139601845792</v>
+        <v>0.0578645053123782</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343949916862881</v>
+        <v>1.343935476667489</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718630127681188</v>
+        <v>1.718607689179994</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814608941969635</v>
+        <v>0.7814581580393256</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699511239183098</v>
+        <v>0.5699504124756201</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804097684940482</v>
+        <v>0.7804057433342879</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.930828570432079</v>
+        <v>1.932207774945375</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.009334365436257</v>
+        <v>2.017474207127405</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.187837918673763</v>
+        <v>2.192417636058524</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E4" t="n">
+        <v>10265</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10264</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10263</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.905677677092468</v>
+        <v>6.90532760132502</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.235408429920849</v>
+        <v>7.235146487285841</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3297307528283797</v>
+        <v>0.3298188859608215</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2918087896436</v>
+        <v>1.291744287406807</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68139522314358</v>
+        <v>1.681355616302715</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678927155415546</v>
+        <v>0.867901995726603</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379339953470649</v>
+        <v>0.7379513636003336</v>
       </c>
       <c r="X4" t="n">
-        <v>0.847321732664052</v>
+        <v>0.8473111466520342</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.506516913758967</v>
+        <v>2.596618604333576</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.031955805326518</v>
+        <v>3.116944374243713</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.244331893702296</v>
+        <v>3.639885930671887</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82354713313897</v>
+        <v>2.823394027676621</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302125427407207</v>
+        <v>9.302063035736884</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3696640019847239</v>
+        <v>0.3696016103144008</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247744356134443</v>
+        <v>1.247702591359125</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747311220228457</v>
+        <v>1.747264959279868</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660728156452376</v>
+        <v>0.8660820954414126</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214602311265212</v>
+        <v>0.7214749798938884</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596584976707475</v>
+        <v>0.8596709194736587</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.336497900680703</v>
+        <v>4.372946727888787</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.793335240956321</v>
+        <v>4.701185617687043</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.803077538827242</v>
+        <v>5.418340645124445</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E6" t="n">
+        <v>8878</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8877</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8876</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734423332582245</v>
+        <v>6.734515207840486</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023335669845681</v>
+        <v>7.023440735273889</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889123372634365</v>
+        <v>0.2889255274334013</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479168076489154</v>
+        <v>1.479138560753617</v>
       </c>
       <c r="U6" t="n">
-        <v>1.90787305423544</v>
+        <v>1.907821536456064</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3041647958416371</v>
+        <v>0.304116933089991</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980346675445777</v>
+        <v>-0.1980753880207977</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2792446820525915</v>
+        <v>0.2791878972438557</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.260880647553049</v>
+        <v>6.276955735503628</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.370830984258905</v>
+        <v>6.368657088070169</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.396526784156267</v>
+        <v>6.393248037886655</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E7" t="n">
+        <v>14239</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14238</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14237</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580642586219007</v>
+        <v>5.580621470712178</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.56728035631245</v>
+        <v>5.567254715357467</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0133622299065567</v>
+        <v>-0.01336675535471204</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166467775106709</v>
+        <v>1.166412143087539</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509822916083204</v>
+        <v>1.509773086595569</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048061660310356</v>
+        <v>0.5048046918747531</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05312150715097375</v>
+        <v>0.05311999972062509</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026538581250732</v>
+        <v>0.502652245848775</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.816711612030415</v>
+        <v>4.79978238944146</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.849414727608409</v>
+        <v>4.84106704177232</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.91140728568867</v>
+        <v>4.883703568827385</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E8" t="n">
+        <v>9037</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9036</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9035</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.874348090758161</v>
+        <v>7.874153663125276</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.11401475701488</v>
+        <v>8.113919477810777</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2396666662567168</v>
+        <v>0.2397658146854996</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445675347199092</v>
+        <v>1.445734176599154</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825414057959843</v>
+        <v>1.825453969653933</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078905155538226</v>
+        <v>0.8078640583542223</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275696603005325</v>
+        <v>0.6275263718379105</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7977665079354251</v>
+        <v>0.7977268745113714</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.636054517833048</v>
+        <v>4.64163239628711</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.858070756323103</v>
+        <v>4.876670173444181</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.103093429627048</v>
+        <v>5.108499650107966</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E9" t="n">
+        <v>13902</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13901</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13900</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.610038129496403</v>
+        <v>7.609932918495073</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655819010055869</v>
+        <v>7.655745748365053</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04578088055946609</v>
+        <v>0.04581282986998203</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49373500750759</v>
+        <v>1.493731178085504</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941733492699927</v>
+        <v>1.94171232012095</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566935461260516</v>
+        <v>0.7566839665083813</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5249243374570114</v>
+        <v>0.524909731900621</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552766643760885</v>
+        <v>0.7552659667361338</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.044139941690962</v>
+        <v>5.044715950473416</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.198613001046214</v>
+        <v>5.220318160805725</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.309855685131195</v>
+        <v>5.31221898519058</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61598731435981</v>
+        <v>10.61587816672906</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3109256338674348</v>
+        <v>0.3108164862366887</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053040171994087</v>
+        <v>2.053089872749883</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698794637718906</v>
+        <v>2.698851674635909</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569168335829799</v>
+        <v>0.3569250139473067</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.121017028473744</v>
+        <v>-0.1210644126132943</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3366644489258112</v>
+        <v>0.3366907009221114</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.430073593029617</v>
+        <v>9.549470573393533</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.604655934541919</v>
+        <v>9.641440675558098</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.733679766914483</v>
+        <v>9.742005809106782</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E11" t="n">
+        <v>13843</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13842</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13841</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243038219781807</v>
+        <v>5.242950223956075</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579548104956269</v>
+        <v>0.4579599417334305</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216562274822253</v>
+        <v>5.216447451866241</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02647594495955476</v>
+        <v>-0.02650277208983472</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161317753445624</v>
+        <v>1.16126347363717</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48278891266702</v>
+        <v>1.482739596193741</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293210437636885</v>
+        <v>0.4293586589649986</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09213714290763231</v>
+        <v>-0.09208525436422277</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275098624240046</v>
+        <v>0.4275487577827173</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.761588921282799</v>
+        <v>4.027457274975722</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.246903895791023</v>
+        <v>4.425616881087926</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.589975665234268</v>
+        <v>4.77259293979374</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E12" t="n">
+        <v>4161</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4160</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4159</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.465353089685021</v>
+        <v>7.46486983173077</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205437317784257</v>
+        <v>2.205469774217043</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.639125772275229</v>
+        <v>7.638789581283644</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1737726825902076</v>
+        <v>0.1739197495528745</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9126503993043076</v>
+        <v>0.9124679414698499</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194314216574686</v>
+        <v>1.194176738027099</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8321978260995102</v>
+        <v>0.832220467757229</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6598551758055213</v>
+        <v>0.6599304990081217</v>
       </c>
       <c r="X12" t="n">
-        <v>0.830396347045115</v>
+        <v>0.8304093796113621</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.667493098516746</v>
+        <v>4.628026231134951</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.323286439819958</v>
+        <v>5.235386689070188</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.656112859415579</v>
+        <v>5.655782498956404</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E13" t="n">
+        <v>6496</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6495</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6494</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.601337388358484</v>
+        <v>9.600969207082372</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02522295501518</v>
+        <v>10.0250422321488</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4238855666566902</v>
+        <v>0.4240730250664271</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691304907651733</v>
+        <v>1.691160125342666</v>
       </c>
       <c r="U13" t="n">
-        <v>2.14971857327212</v>
+        <v>2.149548781339699</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232724503816234</v>
+        <v>0.8232829070004275</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6488560392348219</v>
+        <v>0.6488809323442126</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102428253797391</v>
+        <v>0.8102267914015432</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.445518169115286</v>
+        <v>6.447918751255917</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.790869140703242</v>
+        <v>6.691780889428138</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.664598543788477</v>
+        <v>7.49943833048157</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E14" t="n">
+        <v>14083</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14082</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14081</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126974291598609</v>
+        <v>8.12682111915921</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077964042759962</v>
+        <v>0.9078198591891236</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197824387517819</v>
+        <v>8.197700615002084</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07085009591921135</v>
+        <v>0.07087949584287509</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756086254460124</v>
+        <v>1.756094957108688</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282198901497165</v>
+        <v>2.282182252208737</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808909677452156</v>
+        <v>0.7808825183503216</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654896012669015</v>
+        <v>0.5654770600688647</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805063402959523</v>
+        <v>0.7804972777281026</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.107421149789443</v>
+        <v>5.10024671202433</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.141236383545111</v>
+        <v>5.135459301693208</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.162888788954171</v>
+        <v>5.158428623452294</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.668887755102041</v>
+        <v>4.668699927166788</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82097046417811</v>
+        <v>11.82088831281187</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1429169188486725</v>
+        <v>-0.1429990702149184</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052531828690395</v>
+        <v>2.052515979927604</v>
       </c>
       <c r="U15" t="n">
-        <v>2.69784173381115</v>
+        <v>2.697864986135522</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950075073025041</v>
+        <v>0.7950093458562845</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095377678033121</v>
+        <v>0.6095310370944718</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864360961378578</v>
+        <v>0.7864458634416551</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.694622790697875</v>
+        <v>7.691268076120418</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.932170410628082</v>
+        <v>7.965518156209041</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.406449448550184</v>
+        <v>8.78240993618941</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E16" t="n">
+        <v>9846</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9845</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9844</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.36223527021536</v>
+        <v>8.362054240731336</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623488826099939</v>
+        <v>8.623383990289474</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2612535558845787</v>
+        <v>0.2613297495581378</v>
       </c>
       <c r="T16" t="n">
-        <v>3.594811272814512</v>
+        <v>3.595101061853132</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0880150149165</v>
+        <v>11.08759716316364</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04151829549862806</v>
+        <v>0.04149755181375155</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6102698582357564</v>
+        <v>-0.6103052562245157</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0248564775357184</v>
+        <v>0.02483584825941065</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.74084307744742</v>
+        <v>11.82153123060682</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.30701593800071</v>
+        <v>12.42839636434594</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.82505141031926</v>
+        <v>12.82532914494112</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E17" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2389</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2388</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.479768634840871</v>
+        <v>6.478580996232733</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.429460641399417</v>
+        <v>1.430702840495266</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.842635599282518</v>
+        <v>6.841334150577703</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3628669644416472</v>
+        <v>0.3627531543449693</v>
       </c>
       <c r="T17" t="n">
-        <v>2.011562808540041</v>
+        <v>2.010619560430589</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54889408960383</v>
+        <v>2.548193121224931</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5367930560083057</v>
+        <v>0.5370814107290774</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05218221499516995</v>
+        <v>0.05277242030680507</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5334142588867354</v>
+        <v>0.5337013938381394</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.288120018553863</v>
+        <v>1.498312651444658</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.839451841729517</v>
+        <v>2.986892605983273</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.687168710437843</v>
+        <v>4.084826507095517</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E18" t="n">
+        <v>3249</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3248</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3247</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.471168463196796</v>
+        <v>6.470613916256157</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.666279678920601</v>
+        <v>6.665591661194987</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1951112157238042</v>
+        <v>0.194977744938829</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095196862652063</v>
+        <v>1.094836516755664</v>
       </c>
       <c r="U18" t="n">
-        <v>1.484030782937756</v>
+        <v>1.483738919665991</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6077172660475587</v>
+        <v>0.6079037896180735</v>
       </c>
       <c r="W18" t="n">
-        <v>0.230510619392219</v>
+        <v>0.2308447932662827</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6047284195266163</v>
+        <v>0.6049208034755922</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.232008202553629</v>
+        <v>2.322535276590938</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.966680549281747</v>
+        <v>4.321878091764352</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.108239398733303</v>
+        <v>5.778248170797372</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E19" t="n">
+        <v>7203</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7202</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7201</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32319559783363</v>
+        <v>10.32194897250764</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11905153251387</v>
+        <v>11.11815691810027</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7958559346802316</v>
+        <v>0.7962079455926371</v>
       </c>
       <c r="T19" t="n">
-        <v>2.058124506089779</v>
+        <v>2.058682319834093</v>
       </c>
       <c r="U19" t="n">
-        <v>2.783371269565381</v>
+        <v>2.784024671108059</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7274274825709989</v>
+        <v>0.727469374156712</v>
       </c>
       <c r="W19" t="n">
-        <v>0.471627656050652</v>
+        <v>0.471709414635227</v>
       </c>
       <c r="X19" t="n">
-        <v>0.678109508805041</v>
+        <v>0.6780908274854934</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.146706692602829</v>
+        <v>7.145680010593922</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.274015869152035</v>
+        <v>7.237901288832179</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.359011994431813</v>
+        <v>7.327472985805019</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E20" t="n">
+        <v>10653</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10652</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10651</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85737392800778</v>
+        <v>13.85702916890826</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23379609941064</v>
+        <v>14.23348292341096</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764221714028634</v>
+        <v>0.3764537545026928</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255210428651881</v>
+        <v>1.255132195529686</v>
       </c>
       <c r="U20" t="n">
-        <v>1.647016330997399</v>
+        <v>1.646946085811966</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935450434403149</v>
+        <v>0.8935555295474544</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7789899394820382</v>
+        <v>0.7790108383594148</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887272460872018</v>
+        <v>0.8887346576307114</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.275726441893093</v>
+        <v>9.314994568540905</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.655322423385481</v>
+        <v>9.67455896812675</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.901155435590297</v>
+        <v>9.911422209903273</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16700</v>
+        <v>16701</v>
       </c>
       <c r="E21" t="n">
+        <v>10249</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10248</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10247</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8686357958427</v>
+        <v>130.8685217603435</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9732918239778</v>
+        <v>130.973180812782</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046560281351549</v>
+        <v>0.1046590524385515</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976211664646483</v>
+        <v>0.7975464091710978</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046242327870104</v>
+        <v>1.046184326187877</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649912763044802</v>
+        <v>0.8649961703404254</v>
       </c>
       <c r="W21" t="n">
-        <v>0.730925219607556</v>
+        <v>0.7309376109498944</v>
       </c>
       <c r="X21" t="n">
-        <v>0.864243150320013</v>
+        <v>0.8642466852974909</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.250474422916</v>
+        <v>128.2245208073215</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9562131955052</v>
+        <v>128.8433508276254</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5960983981505</v>
+        <v>129.4927601520489</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.146706692602829</v>
+        <v>7.145680010593922</v>
       </c>
       <c r="G2" t="n">
-        <v>7.274015869152033</v>
+        <v>7.237901288832179</v>
       </c>
       <c r="H2" t="n">
-        <v>7.359011994431813</v>
+        <v>7.327472985805019</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.816711612030415</v>
+        <v>4.79978238944146</v>
       </c>
       <c r="G3" t="n">
-        <v>4.849414727608409</v>
+        <v>4.841067041772319</v>
       </c>
       <c r="H3" t="n">
-        <v>4.91140728568867</v>
+        <v>4.883703568827385</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.761588921282799</v>
+        <v>4.027457274975722</v>
       </c>
       <c r="G4" t="n">
-        <v>4.246903895791023</v>
+        <v>4.425616881087926</v>
       </c>
       <c r="H4" t="n">
-        <v>4.589975665234268</v>
+        <v>4.77259293979374</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.74084307744742</v>
+        <v>11.82153123060682</v>
       </c>
       <c r="G5" t="n">
-        <v>12.30701593800071</v>
+        <v>12.42839636434594</v>
       </c>
       <c r="H5" t="n">
-        <v>12.82505141031926</v>
+        <v>12.82532914494112</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.02206158202378</v>
+        <v>53.59426973092864</v>
       </c>
       <c r="G6" t="n">
-        <v>97.5509865631423</v>
+        <v>102.8656263778089</v>
       </c>
       <c r="H6" t="n">
-        <v>109.1990930495947</v>
+        <v>109.4863723665399</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.694622790697875</v>
+        <v>7.691268076120418</v>
       </c>
       <c r="G7" t="n">
-        <v>7.932170410628082</v>
+        <v>7.965518156209041</v>
       </c>
       <c r="H7" t="n">
-        <v>8.406449448550184</v>
+        <v>8.78240993618941</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.445518169115286</v>
+        <v>6.447918751255917</v>
       </c>
       <c r="G8" t="n">
-        <v>6.790869140703242</v>
+        <v>6.691780889428138</v>
       </c>
       <c r="H8" t="n">
-        <v>7.664598543788477</v>
+        <v>7.49943833048157</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.667493098516746</v>
+        <v>4.628026231134951</v>
       </c>
       <c r="G9" t="n">
-        <v>5.323286439819958</v>
+        <v>5.235386689070188</v>
       </c>
       <c r="H9" t="n">
-        <v>5.656112859415579</v>
+        <v>5.655782498956404</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.636054517833048</v>
+        <v>4.64163239628711</v>
       </c>
       <c r="G10" t="n">
-        <v>4.858070756323103</v>
+        <v>4.876670173444182</v>
       </c>
       <c r="H10" t="n">
-        <v>5.103093429627048</v>
+        <v>5.108499650107966</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.275726441893093</v>
+        <v>9.314994568540905</v>
       </c>
       <c r="G11" t="n">
-        <v>9.655322423385481</v>
+        <v>9.67455896812675</v>
       </c>
       <c r="H11" t="n">
-        <v>9.901155435590297</v>
+        <v>9.911422209903273</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.288120018553863</v>
+        <v>1.498312651444658</v>
       </c>
       <c r="G12" t="n">
-        <v>2.839451841729517</v>
+        <v>2.986892605983273</v>
       </c>
       <c r="H12" t="n">
-        <v>3.687168710437843</v>
+        <v>4.084826507095517</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.107421149789443</v>
+        <v>5.10024671202433</v>
       </c>
       <c r="G13" t="n">
-        <v>5.141236383545111</v>
+        <v>5.135459301693208</v>
       </c>
       <c r="H13" t="n">
-        <v>5.162888788954171</v>
+        <v>5.158428623452294</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.430073593029617</v>
+        <v>9.549470573393533</v>
       </c>
       <c r="G14" t="n">
-        <v>9.604655934541919</v>
+        <v>9.641440675558098</v>
       </c>
       <c r="H14" t="n">
-        <v>9.733679766914483</v>
+        <v>9.742005809106782</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.044139941690962</v>
+        <v>5.044715950473416</v>
       </c>
       <c r="G15" t="n">
-        <v>5.198613001046214</v>
+        <v>5.220318160805724</v>
       </c>
       <c r="H15" t="n">
-        <v>5.309855685131195</v>
+        <v>5.31221898519058</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.260880647553049</v>
+        <v>6.276955735503628</v>
       </c>
       <c r="G16" t="n">
-        <v>6.370830984258905</v>
+        <v>6.368657088070168</v>
       </c>
       <c r="H16" t="n">
-        <v>6.396526784156267</v>
+        <v>6.393248037886655</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.232008202553629</v>
+        <v>2.322535276590938</v>
       </c>
       <c r="G17" t="n">
-        <v>3.966680549281746</v>
+        <v>4.321878091764352</v>
       </c>
       <c r="H17" t="n">
-        <v>5.108239398733303</v>
+        <v>5.778248170797372</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.506516913758967</v>
+        <v>2.596618604333576</v>
       </c>
       <c r="G18" t="n">
-        <v>3.031955805326518</v>
+        <v>3.116944374243713</v>
       </c>
       <c r="H18" t="n">
-        <v>3.244331893702296</v>
+        <v>3.639885930671887</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.930828570432079</v>
+        <v>1.932207774945375</v>
       </c>
       <c r="G19" t="n">
-        <v>2.009334365436257</v>
+        <v>2.017474207127405</v>
       </c>
       <c r="H19" t="n">
-        <v>2.187837918673763</v>
+        <v>2.192417636058524</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.336497900680703</v>
+        <v>4.372946727888787</v>
       </c>
       <c r="G20" t="n">
-        <v>4.793335240956322</v>
+        <v>4.701185617687043</v>
       </c>
       <c r="H20" t="n">
-        <v>5.803077538827242</v>
+        <v>5.418340645124445</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.250474422916</v>
+        <v>128.2245208073215</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9562131955052</v>
+        <v>128.8433508276254</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5960983981505</v>
+        <v>129.4927601520489</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E2" t="n">
+        <v>10038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10037</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10036</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.585805965192</v>
+        <v>102.5813135066919</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5712906641608</v>
+        <v>102.5684607203311</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0145153010311559</v>
+        <v>-0.01285278636085024</v>
       </c>
       <c r="T2" t="n">
-        <v>17.95770136249036</v>
+        <v>17.9645046867726</v>
       </c>
       <c r="U2" t="n">
-        <v>36.04408232647991</v>
+        <v>36.0483270694043</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387898046978817</v>
+        <v>0.1386748542088767</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7192123104637675</v>
+        <v>-0.7193277216570158</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1387877742953688</v>
+        <v>0.1386726804458608</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.59426973092864</v>
+        <v>52.94474255141647</v>
       </c>
       <c r="Z2" t="n">
-        <v>102.8656263778089</v>
+        <v>98.56528723478114</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.4863723665399</v>
+        <v>109.7639779532781</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E3" t="n">
+        <v>14632</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14631</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14630</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906896889952153</v>
+        <v>4.906767753400314</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964761395264531</v>
+        <v>4.9646486027955</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0578645053123782</v>
+        <v>0.05788084939518579</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343935476667489</v>
+        <v>1.343929581897484</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718607689179994</v>
+        <v>1.718590657685865</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814581580393256</v>
+        <v>0.7814532463279156</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699504124756201</v>
+        <v>0.5699448194218417</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804057433342879</v>
+        <v>0.7803997741852335</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.932207774945375</v>
+        <v>1.933179441582515</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.017474207127405</v>
+        <v>2.02845646298284</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.192417636058524</v>
+        <v>2.193834689384889</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E4" t="n">
+        <v>10266</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10265</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10264</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.90532760132502</v>
+        <v>6.904998051631758</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.235146487285841</v>
+        <v>7.234924197300067</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3298188859608215</v>
+        <v>0.3299261456683092</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291744287406807</v>
+        <v>1.29170928099805</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681355616302715</v>
+        <v>1.681343723907394</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867901995726603</v>
+        <v>0.8679049066260894</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379513636003336</v>
+        <v>0.7379566193465743</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473111466520342</v>
+        <v>0.8472910360000762</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.596618604333576</v>
+        <v>2.556484218841004</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.116944374243713</v>
+        <v>3.083586345275369</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.639885930671887</v>
+        <v>3.303569237321745</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.823394027676621</v>
+        <v>2.823241145075206</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302063035736884</v>
+        <v>9.302013413933594</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3696016103144008</v>
+        <v>0.369551988511109</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247702591359125</v>
+        <v>1.247662325868689</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747264959279868</v>
+        <v>1.747224623568088</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660820954414126</v>
+        <v>0.8660903321577632</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214749798938884</v>
+        <v>0.7214878392775785</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596709194736587</v>
+        <v>0.8596817194300064</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.372946727888787</v>
+        <v>4.424694301365132</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.701185617687043</v>
+        <v>4.682453942799987</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.418340645124445</v>
+        <v>4.961262816975677</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E6" t="n">
         <v>8878</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8877</v>
+        <v>8878</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734515207840486</v>
+        <v>6.734596924983104</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023440735273889</v>
+        <v>7.023355836564033</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889255274334013</v>
+        <v>0.2887589115809281</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479138560753617</v>
+        <v>1.479119733189868</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907821536456064</v>
+        <v>1.907778800432836</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304116933089991</v>
+        <v>0.304087829214342</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980753880207977</v>
+        <v>-0.1981332911831089</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2791878972438557</v>
+        <v>0.2791710674240161</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.276955735503628</v>
+        <v>6.368310812910845</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.368657088070169</v>
+        <v>6.407270917495867</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.393248037886655</v>
+        <v>6.577766389950981</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E7" t="n">
+        <v>14240</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14239</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14238</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580621470712178</v>
+        <v>5.580593335206124</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567254715357467</v>
+        <v>5.567232090977812</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01336675535471204</v>
+        <v>-0.01336124422831208</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166412143087539</v>
+        <v>1.166350652116533</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509773086595569</v>
+        <v>1.509721218239295</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048046918747531</v>
+        <v>0.5048048493915053</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05311999972062509</v>
+        <v>0.05312299327810399</v>
       </c>
       <c r="X7" t="n">
-        <v>0.502652245848775</v>
+        <v>0.5026521348800377</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.79978238944146</v>
+        <v>4.818588457250988</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.84106704177232</v>
+        <v>4.842641164664379</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.883703568827385</v>
+        <v>4.876195887118664</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E8" t="n">
+        <v>9038</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9037</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9036</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.874153663125276</v>
+        <v>7.873980579838443</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113919477810777</v>
+        <v>8.113816521209269</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2397658146854996</v>
+        <v>0.2398359413708278</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445734176599154</v>
+        <v>1.445813297461868</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825453969653933</v>
+        <v>1.825508938403933</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078640583542223</v>
+        <v>0.8078328085749023</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275263718379105</v>
+        <v>0.6274739889541167</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7977268745113714</v>
+        <v>0.7976847973268631</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.64163239628711</v>
+        <v>4.64607011963246</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.876670173444181</v>
+        <v>4.904675797577758</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.108499650107966</v>
+        <v>5.115318127227356</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E9" t="n">
+        <v>13903</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13902</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13901</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609932918495073</v>
+        <v>7.609841030067617</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655745748365053</v>
+        <v>7.65567903569973</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04581282986998203</v>
+        <v>0.0458380056321146</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493731178085504</v>
+        <v>1.493746857050669</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94171232012095</v>
+        <v>1.94170607954255</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566839665083813</v>
+        <v>0.7566696359083213</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524909731900621</v>
+        <v>0.5248856367987349</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552659667361338</v>
+        <v>0.755250641444717</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.044715950473416</v>
+        <v>5.069166666666667</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.220318160805725</v>
+        <v>5.25077984964428</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.31221898519058</v>
+        <v>5.315400291120815</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61587816672906</v>
+        <v>10.61577592486319</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3108164862366887</v>
+        <v>0.3107142443708135</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053089872749883</v>
+        <v>2.053145453122357</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698851674635909</v>
+        <v>2.698910550129174</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569250139473067</v>
+        <v>0.3569304836294133</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1210644126132943</v>
+        <v>-0.1211133252236649</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3366907009221114</v>
+        <v>0.3367133654971221</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.549470573393533</v>
+        <v>9.650541271986445</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.641440675558098</v>
+        <v>9.857501757556067</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.742005809106782</v>
+        <v>10.08547802677411</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E11" t="n">
+        <v>13844</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13843</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13842</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242950223956075</v>
+        <v>5.242845987141516</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579599417334305</v>
+        <v>0.4579650655021834</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216447451866241</v>
+        <v>5.216396164244165</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02650277208983472</v>
+        <v>-0.02644982289734976</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16126347363717</v>
+        <v>1.161222848370546</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482739596193741</v>
+        <v>1.482693245133982</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293586589649986</v>
+        <v>0.4293784406699939</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09208525436422277</v>
+        <v>-0.09201428066713491</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275487577827173</v>
+        <v>0.4275661742358117</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.027457274975722</v>
+        <v>4.328630033964095</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.425616881087926</v>
+        <v>4.757638690640993</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.77259293979374</v>
+        <v>4.997085347878527</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E12" t="n">
+        <v>4162</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4161</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4160</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.46486983173077</v>
+        <v>7.464341744772891</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205469774217043</v>
+        <v>2.205502183406113</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.638789581283644</v>
+        <v>7.638392695615191</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1739197495528745</v>
+        <v>0.1740509508423001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9124679414698499</v>
+        <v>0.9122930969547197</v>
       </c>
       <c r="U12" t="n">
-        <v>1.194176738027099</v>
+        <v>1.193977100509936</v>
       </c>
       <c r="V12" t="n">
-        <v>0.832220467757229</v>
+        <v>0.8322711902764406</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6599304990081217</v>
+        <v>0.66005654101053</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8304093796113621</v>
+        <v>0.8304513710236854</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.628026231134951</v>
+        <v>4.684712604652993</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.235386689070188</v>
+        <v>5.174492882198169</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.655782498956404</v>
+        <v>5.655452513140018</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E13" t="n">
+        <v>6497</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6496</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6495</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.600969207082372</v>
+        <v>9.600612684729063</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.0250422321488</v>
+        <v>10.02484417764907</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4240730250664271</v>
+        <v>0.4242314929200098</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691160125342666</v>
+        <v>1.690995071719789</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149548781339699</v>
+        <v>2.149385884779344</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232829070004275</v>
+        <v>0.8232912598109063</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6488809323442126</v>
+        <v>0.6489021250981357</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102267914015432</v>
+        <v>0.8102111995450377</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.447918751255917</v>
+        <v>6.44998762657168</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.691780889428138</v>
+        <v>6.661617055968421</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.49943833048157</v>
+        <v>7.238990583075687</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E14" t="n">
+        <v>14084</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14083</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14082</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.12682111915921</v>
+        <v>8.126670453738551</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9078198591891236</v>
+        <v>0.907843279961184</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197700615002084</v>
+        <v>8.197572337818947</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07087949584287509</v>
+        <v>0.07090188408039638</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756094957108688</v>
+        <v>1.756101795702999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282182252208737</v>
+        <v>2.282166858822759</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808825183503216</v>
+        <v>0.7808738699520578</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654770600688647</v>
+        <v>0.5654636549725912</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804972777281026</v>
+        <v>0.7804881082907777</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.10024671202433</v>
+        <v>5.095339481950051</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.135459301693208</v>
+        <v>5.129522434364441</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.158428623452294</v>
+        <v>5.155356817460459</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.668699927166788</v>
+        <v>4.668512372634644</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82088831281187</v>
+        <v>11.82079613360036</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1429990702149184</v>
+        <v>-0.1430912494264221</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052515979927604</v>
+        <v>2.052509724866362</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697864986135522</v>
+        <v>2.697887171030062</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950093458562845</v>
+        <v>0.7950115131262243</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095310370944718</v>
+        <v>0.609524615313972</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864458634416551</v>
+        <v>0.7864560393145013</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.691268076120418</v>
+        <v>7.687827815785337</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.965518156209041</v>
+        <v>8.239736427223415</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.78240993618941</v>
+        <v>10.87314901634494</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E16" t="n">
+        <v>9847</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9846</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9845</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.362054240731336</v>
+        <v>8.361888482632542</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623383990289474</v>
+        <v>8.623312037785981</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2613297495581378</v>
+        <v>0.2614235551534413</v>
       </c>
       <c r="T16" t="n">
-        <v>3.595101061853132</v>
+        <v>3.595347132511594</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08759716316364</v>
+        <v>11.08716538734009</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04149755181375155</v>
+        <v>0.04147858646240149</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6103052562245157</v>
+        <v>-0.6103376875827422</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02483584825941065</v>
+        <v>0.02481688256111436</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.82153123060682</v>
+        <v>11.89281064567721</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.42839636434594</v>
+        <v>12.53467116727584</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.82532914494112</v>
+        <v>12.83913461896705</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E17" t="n">
+        <v>2391</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2390</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2389</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.478580996232733</v>
+        <v>6.477317991631799</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.430702840495266</v>
+        <v>1.431943231441048</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.841334150577703</v>
+        <v>6.839836861895468</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3627531543449693</v>
+        <v>0.3625188702636694</v>
       </c>
       <c r="T17" t="n">
-        <v>2.010619560430589</v>
+        <v>2.009642594763036</v>
       </c>
       <c r="U17" t="n">
-        <v>2.548193121224931</v>
+        <v>2.547479973807901</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5370814107290774</v>
+        <v>0.5374275587141994</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05277242030680507</v>
+        <v>0.05343270235501529</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5337013938381394</v>
+        <v>0.5340477268259263</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.498312651444658</v>
+        <v>1.534438538728153</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.986892605983273</v>
+        <v>3.20177572919866</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.084826507095517</v>
+        <v>3.73325700050958</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E18" t="n">
+        <v>3250</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3249</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3248</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.470613916256157</v>
+        <v>6.46997353031702</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.665591661194987</v>
+        <v>6.66483584747597</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.194977744938829</v>
+        <v>0.1948623171589506</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094836516755664</v>
+        <v>1.094479658733578</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483738919665991</v>
+        <v>1.483455525123281</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6079037896180735</v>
+        <v>0.608134803430372</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2308447932662827</v>
+        <v>0.2312597234907777</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6049208034755922</v>
+        <v>0.6051576321743972</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.322535276590938</v>
+        <v>2.354153183676114</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.321878091764352</v>
+        <v>4.55909231411914</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.778248170797372</v>
+        <v>5.591736693920373</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E19" t="n">
+        <v>7204</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7203</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7202</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.32194897250764</v>
+        <v>10.3206853394419</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11815691810027</v>
+        <v>11.11726274335941</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7962079455926371</v>
+        <v>0.7965774039175101</v>
       </c>
       <c r="T19" t="n">
-        <v>2.058682319834093</v>
+        <v>2.05927246075511</v>
       </c>
       <c r="U19" t="n">
-        <v>2.784024671108059</v>
+        <v>2.784712510004971</v>
       </c>
       <c r="V19" t="n">
-        <v>0.727469374156712</v>
+        <v>0.727509421501217</v>
       </c>
       <c r="W19" t="n">
-        <v>0.471709414635227</v>
+        <v>0.4717890321412681</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780908274854934</v>
+        <v>0.678066119508576</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.145680010593922</v>
+        <v>7.139615247554626</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.237901288832179</v>
+        <v>7.196611819495715</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.327472985805019</v>
+        <v>7.289541835056554</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E20" t="n">
+        <v>10654</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10653</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10652</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85702916890826</v>
+        <v>13.8566598335878</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23348292341096</v>
+        <v>14.23312964176918</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764537545026928</v>
+        <v>0.3764698081813824</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255132195529686</v>
+        <v>1.255033368524988</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646946085811966</v>
+        <v>1.646870824496087</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935555295474544</v>
+        <v>0.8935683190758033</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790108383594148</v>
+        <v>0.7790362352930371</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887346576307114</v>
+        <v>0.8887455553635135</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.314994568540905</v>
+        <v>9.280011672581914</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.67455896812675</v>
+        <v>9.589354918428972</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.911422209903273</v>
+        <v>9.918882821745646</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16701</v>
+        <v>16702</v>
       </c>
       <c r="E21" t="n">
+        <v>10250</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10249</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10248</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8685217603435</v>
+        <v>130.8683784759489</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.973180812782</v>
+        <v>130.9729995158457</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046590524385515</v>
+        <v>0.1046210398967895</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7975464091710978</v>
+        <v>0.7974636551234444</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046184326187877</v>
+        <v>1.046116712997288</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8649961703404254</v>
+        <v>0.865007995875208</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7309376109498944</v>
+        <v>0.7309600528195409</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642466852974909</v>
+        <v>0.8642596201956183</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2245208073215</v>
+        <v>128.2780675142593</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.8433508276254</v>
+        <v>128.8013830468991</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.4927601520489</v>
+        <v>129.3740376070158</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.145680010593922</v>
+        <v>7.139615247554626</v>
       </c>
       <c r="G2" t="n">
-        <v>7.237901288832179</v>
+        <v>7.196611819495715</v>
       </c>
       <c r="H2" t="n">
-        <v>7.327472985805019</v>
+        <v>7.289541835056554</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.79978238944146</v>
+        <v>4.818588457250988</v>
       </c>
       <c r="G3" t="n">
-        <v>4.841067041772319</v>
+        <v>4.842641164664379</v>
       </c>
       <c r="H3" t="n">
-        <v>4.883703568827385</v>
+        <v>4.876195887118664</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.027457274975722</v>
+        <v>4.328630033964095</v>
       </c>
       <c r="G4" t="n">
-        <v>4.425616881087926</v>
+        <v>4.757638690640993</v>
       </c>
       <c r="H4" t="n">
-        <v>4.77259293979374</v>
+        <v>4.997085347878527</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.82153123060682</v>
+        <v>11.89281064567721</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42839636434594</v>
+        <v>12.53467116727584</v>
       </c>
       <c r="H5" t="n">
-        <v>12.82532914494112</v>
+        <v>12.83913461896705</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.59426973092864</v>
+        <v>52.94474255141647</v>
       </c>
       <c r="G6" t="n">
-        <v>102.8656263778089</v>
+        <v>98.56528723478115</v>
       </c>
       <c r="H6" t="n">
-        <v>109.4863723665399</v>
+        <v>109.7639779532781</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.691268076120418</v>
+        <v>7.687827815785337</v>
       </c>
       <c r="G7" t="n">
-        <v>7.965518156209041</v>
+        <v>8.239736427223415</v>
       </c>
       <c r="H7" t="n">
-        <v>8.78240993618941</v>
+        <v>10.87314901634494</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.447918751255917</v>
+        <v>6.44998762657168</v>
       </c>
       <c r="G8" t="n">
-        <v>6.691780889428138</v>
+        <v>6.661617055968421</v>
       </c>
       <c r="H8" t="n">
-        <v>7.49943833048157</v>
+        <v>7.238990583075687</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.628026231134951</v>
+        <v>4.684712604652993</v>
       </c>
       <c r="G9" t="n">
-        <v>5.235386689070188</v>
+        <v>5.174492882198168</v>
       </c>
       <c r="H9" t="n">
-        <v>5.655782498956404</v>
+        <v>5.655452513140018</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.64163239628711</v>
+        <v>4.64607011963246</v>
       </c>
       <c r="G10" t="n">
-        <v>4.876670173444182</v>
+        <v>4.904675797577758</v>
       </c>
       <c r="H10" t="n">
-        <v>5.108499650107966</v>
+        <v>5.115318127227356</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.314994568540905</v>
+        <v>9.280011672581914</v>
       </c>
       <c r="G11" t="n">
-        <v>9.67455896812675</v>
+        <v>9.589354918428972</v>
       </c>
       <c r="H11" t="n">
-        <v>9.911422209903273</v>
+        <v>9.918882821745646</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.498312651444658</v>
+        <v>1.534438538728153</v>
       </c>
       <c r="G12" t="n">
-        <v>2.986892605983273</v>
+        <v>3.20177572919866</v>
       </c>
       <c r="H12" t="n">
-        <v>4.084826507095517</v>
+        <v>3.73325700050958</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.10024671202433</v>
+        <v>5.095339481950051</v>
       </c>
       <c r="G13" t="n">
-        <v>5.135459301693208</v>
+        <v>5.129522434364442</v>
       </c>
       <c r="H13" t="n">
-        <v>5.158428623452294</v>
+        <v>5.155356817460459</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.549470573393533</v>
+        <v>9.650541271986445</v>
       </c>
       <c r="G14" t="n">
-        <v>9.641440675558098</v>
+        <v>9.857501757556065</v>
       </c>
       <c r="H14" t="n">
-        <v>9.742005809106782</v>
+        <v>10.08547802677411</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.044715950473416</v>
+        <v>5.069166666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>5.220318160805724</v>
+        <v>5.25077984964428</v>
       </c>
       <c r="H15" t="n">
-        <v>5.31221898519058</v>
+        <v>5.315400291120815</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.276955735503628</v>
+        <v>6.368310812910845</v>
       </c>
       <c r="G16" t="n">
-        <v>6.368657088070168</v>
+        <v>6.407270917495867</v>
       </c>
       <c r="H16" t="n">
-        <v>6.393248037886655</v>
+        <v>6.577766389950981</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.322535276590938</v>
+        <v>2.354153183676114</v>
       </c>
       <c r="G17" t="n">
-        <v>4.321878091764352</v>
+        <v>4.559092314119139</v>
       </c>
       <c r="H17" t="n">
-        <v>5.778248170797372</v>
+        <v>5.591736693920373</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.596618604333576</v>
+        <v>2.556484218841004</v>
       </c>
       <c r="G18" t="n">
-        <v>3.116944374243713</v>
+        <v>3.083586345275369</v>
       </c>
       <c r="H18" t="n">
-        <v>3.639885930671887</v>
+        <v>3.303569237321745</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.932207774945375</v>
+        <v>1.933179441582515</v>
       </c>
       <c r="G19" t="n">
-        <v>2.017474207127405</v>
+        <v>2.02845646298284</v>
       </c>
       <c r="H19" t="n">
-        <v>2.192417636058524</v>
+        <v>2.193834689384889</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.372946727888787</v>
+        <v>4.424694301365132</v>
       </c>
       <c r="G20" t="n">
-        <v>4.701185617687043</v>
+        <v>4.682453942799986</v>
       </c>
       <c r="H20" t="n">
-        <v>5.418340645124445</v>
+        <v>4.961262816975677</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.2245208073215</v>
+        <v>128.2780675142593</v>
       </c>
       <c r="G21" t="n">
-        <v>128.8433508276254</v>
+        <v>128.8013830468991</v>
       </c>
       <c r="H21" t="n">
-        <v>129.4927601520489</v>
+        <v>129.3740376070158</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E2" t="n">
+        <v>10039</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10037</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5813135066919</v>
+        <v>102.5768289167829</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5684607203311</v>
+        <v>102.5575640234277</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01285278636085024</v>
+        <v>-0.01926489335519688</v>
       </c>
       <c r="T2" t="n">
-        <v>17.9645046867726</v>
+        <v>17.97734598839982</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0483270694043</v>
+        <v>36.06201482556495</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1386748542088767</v>
+        <v>0.1387992158698598</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7193277216570158</v>
+        <v>-0.7203455638495926</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1386726804458608</v>
+        <v>0.1387983665817011</v>
       </c>
       <c r="Y2" t="n">
-        <v>52.94474255141647</v>
+        <v>3.824242817050304</v>
       </c>
       <c r="Z2" t="n">
-        <v>98.56528723478114</v>
+        <v>84.81775877199217</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.7639779532781</v>
+        <v>110.1748649314524</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E3" t="n">
+        <v>14633</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14632</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14631</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906767753400314</v>
+        <v>4.906644272826681</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.9646486027955</v>
+        <v>4.964531226885761</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05788084939518579</v>
+        <v>0.05788695405907987</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343929581897484</v>
+        <v>1.34393338159535</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718590657685865</v>
+        <v>1.71857847220793</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814532463279156</v>
+        <v>0.7814470307411125</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699448194218417</v>
+        <v>0.5699354954727348</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803997741852335</v>
+        <v>0.7803928931796008</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.933179441582515</v>
+        <v>1.934036601136364</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02845646298284</v>
+        <v>2.043777407874384</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.193834689384889</v>
+        <v>2.198143285654068</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E4" t="n">
+        <v>10267</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10266</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10265</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.904998051631758</v>
+        <v>6.904684638612896</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.234924197300067</v>
+        <v>7.234710966328839</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3299261456683092</v>
+        <v>0.3300263277159421</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29170928099805</v>
+        <v>1.29170518021792</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681343723907394</v>
+        <v>1.681337190772629</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679049066260894</v>
+        <v>0.8679054950607878</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379566193465743</v>
+        <v>0.7379576225283746</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472910360000762</v>
+        <v>0.8472698401038137</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.556484218841004</v>
+        <v>2.537027878787879</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.083586345275369</v>
+        <v>3.058805094888663</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.303569237321745</v>
+        <v>3.278545454545454</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.823241145075206</v>
+        <v>2.823088484848485</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302013413933594</v>
+        <v>9.301977451910169</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.369551988511109</v>
+        <v>0.3695160264876842</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247662325868689</v>
+        <v>1.247638223414878</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747224623568088</v>
+        <v>1.747198966417851</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660903321577632</v>
+        <v>0.8660960146729957</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214878392775785</v>
+        <v>0.7214960188508144</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596817194300064</v>
+        <v>0.8596893772043684</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.424694301365132</v>
+        <v>4.429690556502942</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.682453942799987</v>
+        <v>4.64962277295129</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.961262816975677</v>
+        <v>4.891986020929666</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E6" t="n">
-        <v>8878</v>
+        <v>8880</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8878</v>
+        <v>8879</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734596924983104</v>
+        <v>6.734672710890866</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023355836564033</v>
+        <v>7.02361730526941</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887589115809281</v>
+        <v>0.2889445943785443</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479119733189868</v>
+        <v>1.47905902306093</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907778800432836</v>
+        <v>1.907700236249394</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304087829214342</v>
+        <v>0.3040236930649115</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981332911831089</v>
+        <v>-0.1981494427099304</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2791710674240161</v>
+        <v>0.2790762143346099</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.368310812910845</v>
+        <v>6.377343024306634</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.407270917495867</v>
+        <v>6.460018740357913</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.577766389950981</v>
+        <v>6.802166771855643</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E7" t="n">
+        <v>14241</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14240</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14239</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580593335206124</v>
+        <v>5.580564325842697</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567232090977812</v>
+        <v>5.567191062688369</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01336124422831208</v>
+        <v>-0.01337326315432661</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166350652116533</v>
+        <v>1.166284395403936</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509721218239295</v>
+        <v>1.50966604590581</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048048493915053</v>
+        <v>0.5048091498318339</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05312299327810399</v>
+        <v>0.05313041859431245</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026521348800377</v>
+        <v>0.502656472439259</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.818588457250988</v>
+        <v>4.824804727272728</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.842641164664379</v>
+        <v>4.840965809894617</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.876195887118664</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E8" t="n">
+        <v>9039</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9038</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9037</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.873980579838443</v>
+        <v>7.873818322637751</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113816521209269</v>
+        <v>8.113709854997511</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2398359413708278</v>
+        <v>0.2398915323597584</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445813297461868</v>
+        <v>1.445909406035899</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825508938403933</v>
+        <v>1.825573144314124</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078328085749023</v>
+        <v>0.8077989544907516</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274739889541167</v>
+        <v>0.6274164691104867</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976847973268631</v>
+        <v>0.797641502963875</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.64607011963246</v>
+        <v>4.70447698923885</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.904675797577758</v>
+        <v>4.933514943355085</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.115318127227356</v>
+        <v>5.122734883969533</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E9" t="n">
+        <v>13904</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13903</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13902</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609841030067617</v>
+        <v>7.609749334675969</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65567903569973</v>
+        <v>7.655589045309596</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0458380056321146</v>
+        <v>0.04583971063362761</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493746857050669</v>
+        <v>1.493740683139916</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94170607954255</v>
+        <v>1.941679809257262</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566696359083213</v>
+        <v>0.7566612602797738</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248856367987349</v>
+        <v>0.5248713169315672</v>
       </c>
       <c r="X9" t="n">
-        <v>0.755250641444717</v>
+        <v>0.7552418173618132</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.069166666666667</v>
+        <v>5.131917090909091</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.25077984964428</v>
+        <v>5.277960340761254</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.315400291120815</v>
+        <v>5.318581818181818</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61577592486319</v>
+        <v>10.61568349157604</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3107142443708135</v>
+        <v>0.3106218110836634</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053145453122357</v>
+        <v>2.053206952601999</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698910550129174</v>
+        <v>2.698972587188463</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569304836294133</v>
+        <v>0.3569328410149006</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1211133252236649</v>
+        <v>-0.1211648655558681</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3367133654971221</v>
+        <v>0.3367320781702318</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.650541271986445</v>
+        <v>9.651079755681819</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.857501757556067</v>
+        <v>9.952273821578263</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.08547802677411</v>
+        <v>10.24455930849478</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E11" t="n">
+        <v>13845</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13844</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13843</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242845987141516</v>
+        <v>5.242789620052008</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579650655021834</v>
+        <v>0.4579701818181818</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216396164244165</v>
+        <v>5.216361477808967</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02644982289734976</v>
+        <v>-0.02642814224304129</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161222848370546</v>
+        <v>1.16114606398535</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482693245133982</v>
+        <v>1.482639212456757</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293784406699939</v>
+        <v>0.4293855287896248</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09201428066713491</v>
+        <v>-0.09198971185567362</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275661742358117</v>
+        <v>0.4275724875081928</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.328630033964095</v>
+        <v>4.247937745738636</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.757638690640993</v>
+        <v>4.812538448105768</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.997085347878527</v>
+        <v>5.17194015625</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E12" t="n">
+        <v>4163</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4162</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4161</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.464341744772891</v>
+        <v>7.463709394521865</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205502183406113</v>
+        <v>2.205534545454546</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.638392695615191</v>
+        <v>7.637846363393764</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1740509508423001</v>
+        <v>0.1741369688718986</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9122930969547197</v>
+        <v>0.9122172586765542</v>
       </c>
       <c r="U12" t="n">
-        <v>1.193977100509936</v>
+        <v>1.19383765886563</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8322711902764406</v>
+        <v>0.8323302709236587</v>
       </c>
       <c r="W12" t="n">
-        <v>0.66005654101053</v>
+        <v>0.6601891159776859</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8304513710236854</v>
+        <v>0.8305046260602174</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.684712604652993</v>
+        <v>4.856322839018202</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.174492882198169</v>
+        <v>5.13002430325225</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.655452513140018</v>
+        <v>5.560948666326228</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E13" t="n">
+        <v>6498</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6497</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6496</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.600612684729063</v>
+        <v>9.600257041711558</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02484417764907</v>
+        <v>10.02463714040462</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4242314929200098</v>
+        <v>0.4243800986930606</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690995071719789</v>
+        <v>1.690829722654695</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149385884779344</v>
+        <v>2.149251291905288</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232912598109063</v>
+        <v>0.8232946225163933</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489021250981357</v>
+        <v>0.6489139788709504</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102111995450377</v>
+        <v>0.8101917540621193</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.44998762657168</v>
+        <v>6.452248147516606</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.661617055968421</v>
+        <v>6.67069158229924</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.238990583075687</v>
+        <v>7.296681512288717</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E14" t="n">
+        <v>14085</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14084</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14083</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126670453738551</v>
+        <v>8.126517147117296</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.907843279961184</v>
+        <v>0.9078666666666667</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197572337818947</v>
+        <v>8.197442474217986</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07090188408039638</v>
+        <v>0.07092532710069015</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756101795702999</v>
+        <v>1.756104604675782</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282166858822759</v>
+        <v>2.282143885684803</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808738699520578</v>
+        <v>0.7808668472043119</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654636549725912</v>
+        <v>0.5654535495185462</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804881082907777</v>
+        <v>0.7804805463134755</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.095339481950051</v>
+        <v>5.088248650977845</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.129522434364441</v>
+        <v>5.123320839761353</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.155356817460459</v>
+        <v>5.152272879083807</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.668512372634644</v>
+        <v>4.668325090909091</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82079613360036</v>
+        <v>11.82070118723857</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1430912494264221</v>
+        <v>-0.1431861957882083</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052509724866362</v>
+        <v>2.052502402544447</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697887171030062</v>
+        <v>2.697906470398924</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950115131262243</v>
+        <v>0.7950141757983503</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609524615313972</v>
+        <v>0.6095190287531138</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864560393145013</v>
+        <v>0.7864667226226277</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.687827815785337</v>
+        <v>7.684417817592457</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.239736427223415</v>
+        <v>8.555651675466887</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.87314901634494</v>
+        <v>10.98148104358864</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E16" t="n">
+        <v>9848</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9847</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9846</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.361888482632542</v>
+        <v>8.361731390271148</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623312037785981</v>
+        <v>8.623225813776211</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2614235551534413</v>
+        <v>0.2614944235050617</v>
       </c>
       <c r="T16" t="n">
-        <v>3.595347132511594</v>
+        <v>3.595603667687857</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08716538734009</v>
+        <v>11.08673292601921</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04147858646240149</v>
+        <v>0.04145953319073255</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6103376875827422</v>
+        <v>-0.6103704789998932</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02481688256111436</v>
+        <v>0.02479796238998899</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.89281064567721</v>
+        <v>11.98744688028864</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.53467116727584</v>
+        <v>12.62716394237402</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.83913461896705</v>
+        <v>12.848382032551</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E17" t="n">
+        <v>2392</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2391</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2390</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.477317991631799</v>
+        <v>6.476008992053535</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.431943231441048</v>
+        <v>1.433181818181818</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.839836861895468</v>
+        <v>6.838311536661664</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3625188702636694</v>
+        <v>0.3623025446081296</v>
       </c>
       <c r="T17" t="n">
-        <v>2.009642594763036</v>
+        <v>2.008800965514839</v>
       </c>
       <c r="U17" t="n">
-        <v>2.547479973807901</v>
+        <v>2.546781706103376</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5374275587141994</v>
+        <v>0.5377859292898063</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05343270235501529</v>
+        <v>0.05412093443222454</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5340477268259263</v>
+        <v>0.5344058294165681</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.534438538728153</v>
+        <v>2.426872481608763</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.20177572919866</v>
+        <v>3.240136341114462</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.73325700050958</v>
+        <v>3.68716391378106</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E18" t="n">
+        <v>3251</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3250</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3249</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.46997353031702</v>
+        <v>6.469318153846154</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66483584747597</v>
+        <v>6.664118739006065</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948623171589506</v>
+        <v>0.1948005851599101</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094479658733578</v>
+        <v>1.094105196247146</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483455525123281</v>
+        <v>1.483167485328721</v>
       </c>
       <c r="V18" t="n">
-        <v>0.608134803430372</v>
+        <v>0.6083643805745566</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2312597234907777</v>
+        <v>0.231696360242638</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6051576321743972</v>
+        <v>0.6053881306268749</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.354153183676114</v>
+        <v>3.374928938237335</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55909231411914</v>
+        <v>4.711662201483851</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.591736693920373</v>
+        <v>6.22021272099166</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E19" t="n">
+        <v>7205</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7204</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.3206853394419</v>
+        <v>10.31940401166019</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11726274335941</v>
+        <v>11.1163651490686</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7965774039175101</v>
+        <v>0.7969611374084107</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05927246075511</v>
+        <v>2.059869945476142</v>
       </c>
       <c r="U19" t="n">
-        <v>2.784712510004971</v>
+        <v>2.785425302235744</v>
       </c>
       <c r="V19" t="n">
-        <v>0.727509421501217</v>
+        <v>0.7275499513728371</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4717890321412681</v>
+        <v>0.4718707015608596</v>
       </c>
       <c r="X19" t="n">
-        <v>0.678066119508576</v>
+        <v>0.6780376901444515</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.139615247554626</v>
+        <v>7.132049217923993</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.196611819495715</v>
+        <v>7.18675376145489</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.289541835056554</v>
+        <v>7.356991575852421</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E20" t="n">
+        <v>10655</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10654</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10653</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8566598335878</v>
+        <v>13.85634383397887</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23312964176918</v>
+        <v>14.23284839716077</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764698081813824</v>
+        <v>0.3765045631819089</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255033368524988</v>
+        <v>1.255001254182402</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646870824496087</v>
+        <v>1.646829130967286</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935683190758033</v>
+        <v>0.8935731014837976</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790362352930371</v>
+        <v>0.7790458334062449</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887455553635135</v>
+        <v>0.8887472048528354</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.280011672581914</v>
+        <v>9.271760937272296</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.589354918428972</v>
+        <v>9.514143433421363</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.918882821745646</v>
+        <v>9.923661816431625</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16702</v>
+        <v>16703</v>
       </c>
       <c r="E21" t="n">
+        <v>10251</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10250</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10249</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8683784759489</v>
+        <v>130.8681669268293</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9729995158457</v>
+        <v>130.9727929241393</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046210398967895</v>
+        <v>0.1046259973100331</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7974636551234444</v>
+        <v>0.7974401011883291</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046116712997288</v>
+        <v>1.046070390325553</v>
       </c>
       <c r="V21" t="n">
-        <v>0.865007995875208</v>
+        <v>0.8650217323380155</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7309600528195409</v>
+        <v>0.7309879678852436</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642596201956183</v>
+        <v>0.8642728268583821</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2780675142593</v>
+        <v>128.5984398337426</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.8013830468991</v>
+        <v>128.8103384211233</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.3740376070158</v>
+        <v>129.1166339977195</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.139615247554626</v>
+        <v>7.132049217923993</v>
       </c>
       <c r="G2" t="n">
-        <v>7.196611819495715</v>
+        <v>7.18675376145489</v>
       </c>
       <c r="H2" t="n">
-        <v>7.289541835056554</v>
+        <v>7.356991575852421</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.818588457250988</v>
+        <v>4.824804727272728</v>
       </c>
       <c r="G3" t="n">
-        <v>4.842641164664379</v>
+        <v>4.840965809894617</v>
       </c>
       <c r="H3" t="n">
-        <v>4.876195887118664</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.328630033964095</v>
+        <v>4.247937745738636</v>
       </c>
       <c r="G4" t="n">
-        <v>4.757638690640993</v>
+        <v>4.812538448105768</v>
       </c>
       <c r="H4" t="n">
-        <v>4.997085347878527</v>
+        <v>5.17194015625</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89281064567721</v>
+        <v>11.98744688028864</v>
       </c>
       <c r="G5" t="n">
-        <v>12.53467116727584</v>
+        <v>12.62716394237402</v>
       </c>
       <c r="H5" t="n">
-        <v>12.83913461896705</v>
+        <v>12.848382032551</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>52.94474255141647</v>
+        <v>3.824242817050304</v>
       </c>
       <c r="G6" t="n">
-        <v>98.56528723478115</v>
+        <v>84.81775877199217</v>
       </c>
       <c r="H6" t="n">
-        <v>109.7639779532781</v>
+        <v>110.1748649314524</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.687827815785337</v>
+        <v>7.684417817592457</v>
       </c>
       <c r="G7" t="n">
-        <v>8.239736427223415</v>
+        <v>8.555651675466887</v>
       </c>
       <c r="H7" t="n">
-        <v>10.87314901634494</v>
+        <v>10.98148104358864</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.44998762657168</v>
+        <v>6.452248147516606</v>
       </c>
       <c r="G8" t="n">
-        <v>6.661617055968421</v>
+        <v>6.67069158229924</v>
       </c>
       <c r="H8" t="n">
-        <v>7.238990583075687</v>
+        <v>7.296681512288717</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.684712604652993</v>
+        <v>4.856322839018202</v>
       </c>
       <c r="G9" t="n">
-        <v>5.174492882198168</v>
+        <v>5.130024303252251</v>
       </c>
       <c r="H9" t="n">
-        <v>5.655452513140018</v>
+        <v>5.560948666326228</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.64607011963246</v>
+        <v>4.70447698923885</v>
       </c>
       <c r="G10" t="n">
-        <v>4.904675797577758</v>
+        <v>4.933514943355085</v>
       </c>
       <c r="H10" t="n">
-        <v>5.115318127227356</v>
+        <v>5.122734883969533</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.280011672581914</v>
+        <v>9.271760937272296</v>
       </c>
       <c r="G11" t="n">
-        <v>9.589354918428972</v>
+        <v>9.514143433421363</v>
       </c>
       <c r="H11" t="n">
-        <v>9.918882821745646</v>
+        <v>9.923661816431625</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.534438538728153</v>
+        <v>2.426872481608763</v>
       </c>
       <c r="G12" t="n">
-        <v>3.20177572919866</v>
+        <v>3.240136341114462</v>
       </c>
       <c r="H12" t="n">
-        <v>3.73325700050958</v>
+        <v>3.68716391378106</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.095339481950051</v>
+        <v>5.088248650977845</v>
       </c>
       <c r="G13" t="n">
-        <v>5.129522434364442</v>
+        <v>5.123320839761353</v>
       </c>
       <c r="H13" t="n">
-        <v>5.155356817460459</v>
+        <v>5.152272879083807</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.650541271986445</v>
+        <v>9.651079755681819</v>
       </c>
       <c r="G14" t="n">
-        <v>9.857501757556065</v>
+        <v>9.952273821578263</v>
       </c>
       <c r="H14" t="n">
-        <v>10.08547802677411</v>
+        <v>10.24455930849478</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.069166666666667</v>
+        <v>5.131917090909091</v>
       </c>
       <c r="G15" t="n">
-        <v>5.25077984964428</v>
+        <v>5.277960340761254</v>
       </c>
       <c r="H15" t="n">
-        <v>5.315400291120815</v>
+        <v>5.318581818181818</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.368310812910845</v>
+        <v>6.377343024306634</v>
       </c>
       <c r="G16" t="n">
-        <v>6.407270917495867</v>
+        <v>6.460018740357912</v>
       </c>
       <c r="H16" t="n">
-        <v>6.577766389950981</v>
+        <v>6.802166771855643</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.354153183676114</v>
+        <v>3.374928938237335</v>
       </c>
       <c r="G17" t="n">
-        <v>4.559092314119139</v>
+        <v>4.711662201483851</v>
       </c>
       <c r="H17" t="n">
-        <v>5.591736693920373</v>
+        <v>6.22021272099166</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.556484218841004</v>
+        <v>2.537027878787879</v>
       </c>
       <c r="G18" t="n">
-        <v>3.083586345275369</v>
+        <v>3.058805094888663</v>
       </c>
       <c r="H18" t="n">
-        <v>3.303569237321745</v>
+        <v>3.278545454545454</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.933179441582515</v>
+        <v>1.934036601136364</v>
       </c>
       <c r="G19" t="n">
-        <v>2.02845646298284</v>
+        <v>2.043777407874384</v>
       </c>
       <c r="H19" t="n">
-        <v>2.193834689384889</v>
+        <v>2.198143285654068</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.424694301365132</v>
+        <v>4.429690556502942</v>
       </c>
       <c r="G20" t="n">
-        <v>4.682453942799986</v>
+        <v>4.649622772951289</v>
       </c>
       <c r="H20" t="n">
-        <v>4.961262816975677</v>
+        <v>4.891986020929666</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.2780675142593</v>
+        <v>128.5984398337426</v>
       </c>
       <c r="G21" t="n">
-        <v>128.8013830468991</v>
+        <v>128.8103384211232</v>
       </c>
       <c r="H21" t="n">
-        <v>129.3740376070158</v>
+        <v>129.1166339977195</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E2" t="n">
+        <v>10040</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10039</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10038</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5768289167829</v>
+        <v>102.5671230866288</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5575640234277</v>
+        <v>102.547344106246</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01926489335519688</v>
+        <v>-0.01977898038281511</v>
       </c>
       <c r="T2" t="n">
-        <v>17.97734598839982</v>
+        <v>17.99628470404945</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06201482556495</v>
+        <v>36.08763769788256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387992158698598</v>
+        <v>0.138494339019387</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7203455638495926</v>
+        <v>-0.7208099438811222</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1387983665817011</v>
+        <v>0.1384933682023282</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.824242817050304</v>
+        <v>107.9033013560735</v>
       </c>
       <c r="Z2" t="n">
-        <v>84.81775877199217</v>
+        <v>110.235278494631</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.1748649314524</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E3" t="n">
+        <v>14634</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14633</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14632</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906644272826681</v>
+        <v>4.906520979976765</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964531226885761</v>
+        <v>4.964414536278232</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05788695405907987</v>
+        <v>0.0578935563014669</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34393338159535</v>
+        <v>1.343940825146346</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71857847220793</v>
+        <v>1.718569190457586</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814470307411125</v>
+        <v>0.7814400269586348</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699354954727348</v>
+        <v>0.5699246790537764</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803928931796008</v>
+        <v>0.7803852090605269</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.934036601136364</v>
+        <v>1.93578488372093</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.043777407874384</v>
+        <v>2.072767925578817</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.198143285654068</v>
+        <v>2.209818313953488</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E4" t="n">
         <v>10267</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10266</v>
+        <v>10267</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.904684638612896</v>
+        <v>6.904378348105581</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.234710966328839</v>
+        <v>7.23424881341256</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3300263277159421</v>
+        <v>0.3298704653069792</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29170518021792</v>
+        <v>1.291603820201785</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681337190772629</v>
+        <v>1.681242057833606</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679054950607878</v>
+        <v>0.8679205900474648</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379576225283746</v>
+        <v>0.7379851465999573</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472698401038137</v>
+        <v>0.8473173126918595</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.537027878787879</v>
+        <v>2.979523275622994</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.058805094888663</v>
+        <v>3.442470192638001</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.278545454545454</v>
+        <v>4.288253232024436</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.823088484848485</v>
+        <v>2.822936046511628</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301977451910169</v>
+        <v>9.301958271690813</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3695160264876842</v>
+        <v>0.3694968462683299</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247638223414878</v>
+        <v>1.247631093778848</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747198966417851</v>
+        <v>1.747188673816183</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660960146729957</v>
+        <v>0.8660989057875276</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214960188508144</v>
+        <v>0.7214993001280504</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596893772043684</v>
+        <v>0.859693478445243</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.429690556502942</v>
+        <v>4.582924471781054</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.64962277295129</v>
+        <v>5.11710950330483</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.891986020929666</v>
+        <v>6.530767602047103</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E6" t="n">
         <v>8880</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8879</v>
+        <v>8880</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734672710890866</v>
+        <v>6.734734121621622</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02361730526941</v>
+        <v>7.02353570423887</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889445943785443</v>
+        <v>0.2888015826172483</v>
       </c>
       <c r="T6" t="n">
-        <v>1.47905902306093</v>
+        <v>1.479011855533709</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907700236249394</v>
+        <v>1.907644170285079</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040236930649115</v>
+        <v>0.3040030666069015</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981494427099304</v>
+        <v>-0.1982007416369533</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790762143346099</v>
+        <v>0.2790679839404312</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.377343024306634</v>
+        <v>6.377548622187303</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.460018740357913</v>
+        <v>6.560002866454044</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.802166771855643</v>
+        <v>7.203323230598098</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E7" t="n">
+        <v>14242</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14241</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14240</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580564325842697</v>
+        <v>5.580521803244155</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567191062688369</v>
+        <v>5.567144080782505</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01337326315432661</v>
+        <v>-0.01337772246164998</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166284395403936</v>
+        <v>1.166207255452578</v>
       </c>
       <c r="U7" t="n">
-        <v>1.50966604590581</v>
+        <v>1.509610013762336</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048091498318339</v>
+        <v>0.5048164348666583</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05313041859431245</v>
+        <v>0.05314434541737012</v>
       </c>
       <c r="X7" t="n">
-        <v>0.502656472439259</v>
+        <v>0.5026637133916423</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.824804727272728</v>
+        <v>4.839656353820597</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.840965809894617</v>
+        <v>4.872673403926631</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.86</v>
+        <v>4.956195948401163</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E8" t="n">
+        <v>9040</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9039</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9038</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.873818322637751</v>
+        <v>7.873650016594754</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113709854997511</v>
+        <v>8.113608608569091</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2398915323597584</v>
+        <v>0.2399585919743354</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445909406035899</v>
+        <v>1.445995073720389</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825573144314124</v>
+        <v>1.825618907676205</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077989544907516</v>
+        <v>0.8077694105811327</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274164691104867</v>
+        <v>0.6273672294924169</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797641502963875</v>
+        <v>0.7976013337613492</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.70447698923885</v>
+        <v>4.803711869228235</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.933514943355085</v>
+        <v>4.977833893584672</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.122734883969533</v>
+        <v>5.139042222057472</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E9" t="n">
+        <v>13905</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13904</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13903</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609749334675969</v>
+        <v>7.609640031645569</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655589045309596</v>
+        <v>7.655477304727651</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04583971063362761</v>
+        <v>0.04583727308208125</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493740683139916</v>
+        <v>1.49369987597391</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941679809257262</v>
+        <v>1.94162592426774</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566612602797738</v>
+        <v>0.7566616601859117</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248713169315672</v>
+        <v>0.5248734616934903</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552418173618132</v>
+        <v>0.7552418959226064</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.131917090909091</v>
+        <v>5.231726017441861</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.277960340761254</v>
+        <v>5.304985865855739</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.318581818181818</v>
+        <v>5.373824507728946</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61568349157604</v>
+        <v>10.61559204588822</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3106218110836634</v>
+        <v>0.3105303653958473</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053206952601999</v>
+        <v>2.053270936246298</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698972587188463</v>
+        <v>2.699034184645244</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569328410149006</v>
+        <v>0.3569351725530248</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1211648655558681</v>
+        <v>-0.1212160418388373</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3367320781702318</v>
+        <v>0.336750627585136</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.651079755681819</v>
+        <v>9.658356370316705</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.952273821578263</v>
+        <v>10.12494815663505</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.24455930849478</v>
+        <v>10.40562048740598</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E11" t="n">
+        <v>13846</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13845</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13844</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242789620052008</v>
+        <v>5.24274247020585</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579701818181818</v>
+        <v>0.4579752906976745</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216361477808967</v>
+        <v>5.216299447200965</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02642814224304129</v>
+        <v>-0.02644302300488569</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16114606398535</v>
+        <v>1.161061125757097</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482639212456757</v>
+        <v>1.482578379047832</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4293855287896248</v>
+        <v>0.42940258892266</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09198971185567362</v>
+        <v>-0.09196227981769844</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275724875081928</v>
+        <v>0.4275898242948363</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.247937745738636</v>
+        <v>4.360692223837209</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.812538448105768</v>
+        <v>5.011932702781435</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.17194015625</v>
+        <v>5.346191860465116</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E12" t="n">
+        <v>4164</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4163</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4162</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.463709394521865</v>
+        <v>7.462991472495796</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205534545454546</v>
+        <v>2.205566860465116</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.637846363393764</v>
+        <v>7.63719583384909</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1741369688718986</v>
+        <v>0.1742043613532943</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9122172586765542</v>
+        <v>0.9121818573896692</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19383765886563</v>
+        <v>1.193737624908509</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8323302709236587</v>
+        <v>0.8324003952564279</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6601891159776859</v>
+        <v>0.6603381898815386</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8305046260602174</v>
+        <v>0.8305703014672633</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.856322839018202</v>
+        <v>4.857385207065317</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.13002430325225</v>
+        <v>5.124415398112168</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.560948666326228</v>
+        <v>5.478842322245161</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E13" t="n">
+        <v>6499</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6498</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6497</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.600257041711558</v>
+        <v>9.599894967682364</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02463714040462</v>
+        <v>10.02437073754589</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4243800986930606</v>
+        <v>0.4244757698635272</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690829722654695</v>
+        <v>1.690795753377176</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149251291905288</v>
+        <v>2.149161953357897</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232946225163933</v>
+        <v>0.8232907024618508</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489139788709504</v>
+        <v>0.6489118635564224</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101917540621193</v>
+        <v>0.8101709103048014</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.452248147516606</v>
+        <v>6.454810791517144</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.67069158229924</v>
+        <v>6.77063236214947</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.296681512288717</v>
+        <v>7.59094175785094</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E14" t="n">
+        <v>14086</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14085</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14084</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126517147117296</v>
+        <v>8.126358892438766</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9078666666666667</v>
+        <v>0.907890019379845</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197442474217986</v>
+        <v>8.197304544310398</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07092532710069015</v>
+        <v>0.07094565187163387</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756104604675782</v>
+        <v>1.75609515201756</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282143885684803</v>
+        <v>2.282116137975314</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808668472043119</v>
+        <v>0.7808612651243485</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654535495185462</v>
+        <v>0.5654460530642733</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804805463134755</v>
+        <v>0.7804744667239907</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.088248650977845</v>
+        <v>5.086402011194165</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.123320839761353</v>
+        <v>5.118075462216398</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.152272879083807</v>
+        <v>5.149144712984209</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.668325090909091</v>
+        <v>4.668138081395349</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82070118723857</v>
+        <v>11.82060664856587</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1431861957882083</v>
+        <v>-0.1432807344609165</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052502402544447</v>
+        <v>2.052493619554367</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697906470398924</v>
+        <v>2.697923298021468</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950141757983503</v>
+        <v>0.7950171949164744</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095190287531138</v>
+        <v>0.6095141576525331</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864667226226277</v>
+        <v>0.7864777076036035</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.684417817592457</v>
+        <v>7.681106119428045</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.555651675466887</v>
+        <v>8.889390258172906</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.98148104358864</v>
+        <v>11.00830528550993</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E16" t="n">
+        <v>9849</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9848</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9847</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.361731390271148</v>
+        <v>8.361573314378555</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623225813776211</v>
+        <v>8.623131785587692</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2614944235050617</v>
+        <v>0.2615584712091377</v>
       </c>
       <c r="T16" t="n">
-        <v>3.595603667687857</v>
+        <v>3.595864389587379</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08673292601921</v>
+        <v>11.08630318449856</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04145953319073255</v>
+        <v>0.04144028354410411</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6103704789998932</v>
+        <v>-0.6104039743041296</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02479796238998899</v>
+        <v>0.02477892464846798</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.98744688028864</v>
+        <v>12.14789466119348</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.62716394237402</v>
+        <v>12.72400291149705</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.848382032551</v>
+        <v>13.01696624954969</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E17" t="n">
+        <v>2393</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2392</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2391</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.476008992053535</v>
+        <v>6.474723035117056</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.433181818181818</v>
+        <v>1.434418604651163</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.838311536661664</v>
+        <v>6.83675686719496</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3623025446081296</v>
+        <v>0.3620338320779025</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008800965514839</v>
+        <v>2.007982706333037</v>
       </c>
       <c r="U17" t="n">
-        <v>2.546781706103376</v>
+        <v>2.546083467535185</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5377859292898063</v>
+        <v>0.5381437191136976</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05412093443222454</v>
+        <v>0.05478938332180316</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5344058294165681</v>
+        <v>0.5347642022290848</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.426872481608763</v>
+        <v>2.727259422614274</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.240136341114462</v>
+        <v>4.6032133424802</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.68716391378106</v>
+        <v>6.980152884355316</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E18" t="n">
         <v>3251</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.469318153846154</v>
+        <v>6.468675484466317</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.664118739006065</v>
+        <v>6.663479505802891</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948005851599101</v>
+        <v>0.1948040213365727</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094105196247146</v>
+        <v>1.093881276937562</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483167485328721</v>
+        <v>1.482964051451932</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6083643805745566</v>
+        <v>0.6085484940982976</v>
       </c>
       <c r="W18" t="n">
-        <v>0.231696360242638</v>
+        <v>0.2320309274309277</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6053881306268749</v>
+        <v>0.6055734876370937</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.374928938237335</v>
+        <v>4.009092665027206</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.711662201483851</v>
+        <v>5.480279323524561</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.22021272099166</v>
+        <v>7.117066895384622</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E19" t="n">
+        <v>7206</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7205</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7204</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31940401166019</v>
+        <v>10.31812234559334</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1163651490686</v>
+        <v>11.11544638464493</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7969611374084107</v>
+        <v>0.7973240390515911</v>
       </c>
       <c r="T19" t="n">
-        <v>2.059869945476142</v>
+        <v>2.060471793237813</v>
       </c>
       <c r="U19" t="n">
-        <v>2.785425302235744</v>
+        <v>2.78613320240751</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7275499513728371</v>
+        <v>0.7275915473834462</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4718707015608596</v>
+        <v>0.4719542921475283</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780376901444515</v>
+        <v>0.6780148347756503</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.132049217923993</v>
+        <v>7.17390771225855</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.18675376145489</v>
+        <v>7.248478806010093</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.356991575852421</v>
+        <v>7.395026595078187</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E20" t="n">
+        <v>10656</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10655</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10654</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85634383397887</v>
+        <v>13.85603610579172</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23284839716077</v>
+        <v>14.23257309682431</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3765045631819089</v>
+        <v>0.3765369910325809</v>
       </c>
       <c r="T20" t="n">
-        <v>1.255001254182402</v>
+        <v>1.25497744764091</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646829130967286</v>
+        <v>1.646792769488665</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935731014837976</v>
+        <v>0.8935766541714181</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790458334062449</v>
+        <v>0.7790530150663317</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887472048528354</v>
+        <v>0.8887478024158632</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.271760937272296</v>
+        <v>9.369305652797218</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.514143433421363</v>
+        <v>9.815105356885004</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.923661816431625</v>
+        <v>10.49067514659454</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16703</v>
+        <v>16704</v>
       </c>
       <c r="E21" t="n">
         <v>10251</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10250</v>
+        <v>10251</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8681669268293</v>
+        <v>130.8679310311189</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9727929241393</v>
+        <v>130.972563773137</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046259973100331</v>
+        <v>0.1046327420180781</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7974401011883291</v>
+        <v>0.7974354304346204</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046070390325553</v>
+        <v>1.046049201646916</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650217323380155</v>
+        <v>0.8650342580482414</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7309879678852436</v>
+        <v>0.7310103434542224</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642728268583821</v>
+        <v>0.8642861883089861</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5984398337426</v>
+        <v>128.6758023894909</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.8103384211233</v>
+        <v>128.9012375830087</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.1166339977195</v>
+        <v>129.4143253659274</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.132049217923993</v>
+        <v>7.17390771225855</v>
       </c>
       <c r="G2" t="n">
-        <v>7.18675376145489</v>
+        <v>7.248478806010093</v>
       </c>
       <c r="H2" t="n">
-        <v>7.356991575852421</v>
+        <v>7.395026595078187</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824804727272728</v>
+        <v>4.839656353820597</v>
       </c>
       <c r="G3" t="n">
-        <v>4.840965809894617</v>
+        <v>4.872673403926631</v>
       </c>
       <c r="H3" t="n">
-        <v>4.86</v>
+        <v>4.956195948401163</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.247937745738636</v>
+        <v>4.360692223837209</v>
       </c>
       <c r="G4" t="n">
-        <v>4.812538448105768</v>
+        <v>5.011932702781435</v>
       </c>
       <c r="H4" t="n">
-        <v>5.17194015625</v>
+        <v>5.346191860465116</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.98744688028864</v>
+        <v>12.14789466119348</v>
       </c>
       <c r="G5" t="n">
-        <v>12.62716394237402</v>
+        <v>12.72400291149705</v>
       </c>
       <c r="H5" t="n">
-        <v>12.848382032551</v>
+        <v>13.01696624954969</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.824242817050304</v>
+        <v>107.9033013560735</v>
       </c>
       <c r="G6" t="n">
-        <v>84.81775877199217</v>
+        <v>110.235278494631</v>
       </c>
       <c r="H6" t="n">
-        <v>110.1748649314524</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.684417817592457</v>
+        <v>7.681106119428045</v>
       </c>
       <c r="G7" t="n">
-        <v>8.555651675466887</v>
+        <v>8.889390258172906</v>
       </c>
       <c r="H7" t="n">
-        <v>10.98148104358864</v>
+        <v>11.00830528550993</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.452248147516606</v>
+        <v>6.454810791517144</v>
       </c>
       <c r="G8" t="n">
-        <v>6.67069158229924</v>
+        <v>6.77063236214947</v>
       </c>
       <c r="H8" t="n">
-        <v>7.296681512288717</v>
+        <v>7.59094175785094</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.856322839018202</v>
+        <v>4.857385207065317</v>
       </c>
       <c r="G9" t="n">
-        <v>5.130024303252251</v>
+        <v>5.124415398112168</v>
       </c>
       <c r="H9" t="n">
-        <v>5.560948666326228</v>
+        <v>5.478842322245161</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.70447698923885</v>
+        <v>4.803711869228235</v>
       </c>
       <c r="G10" t="n">
-        <v>4.933514943355085</v>
+        <v>4.977833893584672</v>
       </c>
       <c r="H10" t="n">
-        <v>5.122734883969533</v>
+        <v>5.139042222057472</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.271760937272296</v>
+        <v>9.369305652797218</v>
       </c>
       <c r="G11" t="n">
-        <v>9.514143433421363</v>
+        <v>9.815105356885004</v>
       </c>
       <c r="H11" t="n">
-        <v>9.923661816431625</v>
+        <v>10.49067514659454</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.426872481608763</v>
+        <v>2.727259422614274</v>
       </c>
       <c r="G12" t="n">
-        <v>3.240136341114462</v>
+        <v>4.603213342480199</v>
       </c>
       <c r="H12" t="n">
-        <v>3.68716391378106</v>
+        <v>6.980152884355316</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.088248650977845</v>
+        <v>5.086402011194165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.123320839761353</v>
+        <v>5.118075462216398</v>
       </c>
       <c r="H13" t="n">
-        <v>5.152272879083807</v>
+        <v>5.149144712984209</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.651079755681819</v>
+        <v>9.658356370316705</v>
       </c>
       <c r="G14" t="n">
-        <v>9.952273821578263</v>
+        <v>10.12494815663506</v>
       </c>
       <c r="H14" t="n">
-        <v>10.24455930849478</v>
+        <v>10.40562048740598</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.131917090909091</v>
+        <v>5.231726017441861</v>
       </c>
       <c r="G15" t="n">
-        <v>5.277960340761254</v>
+        <v>5.304985865855739</v>
       </c>
       <c r="H15" t="n">
-        <v>5.318581818181818</v>
+        <v>5.373824507728946</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.377343024306634</v>
+        <v>6.377548622187303</v>
       </c>
       <c r="G16" t="n">
-        <v>6.460018740357912</v>
+        <v>6.560002866454044</v>
       </c>
       <c r="H16" t="n">
-        <v>6.802166771855643</v>
+        <v>7.203323230598098</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.374928938237335</v>
+        <v>4.009092665027206</v>
       </c>
       <c r="G17" t="n">
-        <v>4.711662201483851</v>
+        <v>5.480279323524561</v>
       </c>
       <c r="H17" t="n">
-        <v>6.22021272099166</v>
+        <v>7.117066895384622</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.537027878787879</v>
+        <v>2.979523275622994</v>
       </c>
       <c r="G18" t="n">
-        <v>3.058805094888663</v>
+        <v>3.442470192638002</v>
       </c>
       <c r="H18" t="n">
-        <v>3.278545454545454</v>
+        <v>4.288253232024436</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.934036601136364</v>
+        <v>1.93578488372093</v>
       </c>
       <c r="G19" t="n">
-        <v>2.043777407874384</v>
+        <v>2.072767925578817</v>
       </c>
       <c r="H19" t="n">
-        <v>2.198143285654068</v>
+        <v>2.209818313953488</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.429690556502942</v>
+        <v>4.582924471781054</v>
       </c>
       <c r="G20" t="n">
-        <v>4.649622772951289</v>
+        <v>5.11710950330483</v>
       </c>
       <c r="H20" t="n">
-        <v>4.891986020929666</v>
+        <v>6.530767602047103</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5984398337426</v>
+        <v>128.6758023894909</v>
       </c>
       <c r="G21" t="n">
-        <v>128.8103384211232</v>
+        <v>128.9012375830086</v>
       </c>
       <c r="H21" t="n">
-        <v>129.1166339977195</v>
+        <v>129.4143253659274</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E2" t="n">
         <v>10040</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10039</v>
+        <v>10040</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5671230866288</v>
+        <v>102.5574142098274</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.547344106246</v>
+        <v>102.5471405404388</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01977898038281511</v>
+        <v>-0.01027366938854744</v>
       </c>
       <c r="T2" t="n">
-        <v>17.99628470404945</v>
+        <v>18.00554748112107</v>
       </c>
       <c r="U2" t="n">
-        <v>36.08763769788256</v>
+        <v>36.10139420458456</v>
       </c>
       <c r="V2" t="n">
-        <v>0.138494339019387</v>
+        <v>0.1383238495440355</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7208099438811222</v>
+        <v>-0.720142614884927</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1384933682023282</v>
+        <v>0.1383218263752586</v>
       </c>
       <c r="Y2" t="n">
-        <v>107.9033013560735</v>
+        <v>109.2754000091262</v>
       </c>
       <c r="Z2" t="n">
-        <v>110.235278494631</v>
+        <v>109.7933810593643</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.56</v>
+        <v>110.406442878382</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E3" t="n">
         <v>14634</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14633</v>
+        <v>14634</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906520979976765</v>
+        <v>4.906396166461664</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964414536278232</v>
+        <v>4.964174394499823</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0578935563014669</v>
+        <v>0.0577782280381588</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343940825146346</v>
+        <v>1.34393109136481</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718569190457586</v>
+        <v>1.718540402149516</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814400269586348</v>
+        <v>0.7814486597997008</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699246790537764</v>
+        <v>0.5699239749620836</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803852090605269</v>
+        <v>0.7803990354148286</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.93578488372093</v>
+        <v>1.937029966533054</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.072767925578817</v>
+        <v>2.100593096467845</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.209818313953488</v>
+        <v>2.235123336547924</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E4" t="n">
         <v>10267</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.23424881341256</v>
+        <v>7.234178493366916</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3298704653069792</v>
+        <v>0.3298001452613347</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291603820201785</v>
+        <v>1.291576761739584</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681242057833606</v>
+        <v>1.681220229936122</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679205900474648</v>
+        <v>0.8679246484968536</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379851465999573</v>
+        <v>0.7379919501369085</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473173126918595</v>
+        <v>0.8473379264584546</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.979523275622994</v>
+        <v>3.105709657543573</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.442470192638001</v>
+        <v>3.472548786749319</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.288253232024436</v>
+        <v>3.798187392911447</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.822936046511628</v>
+        <v>2.822783829581215</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301958271690813</v>
+        <v>9.301944263140031</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3694968462683299</v>
+        <v>0.3694828377175483</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247631093778848</v>
+        <v>1.247628776810929</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747188673816183</v>
+        <v>1.747185780539978</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8660989057875276</v>
+        <v>0.8661005036855922</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7214993001280504</v>
+        <v>0.7215002224998502</v>
       </c>
       <c r="X5" t="n">
-        <v>0.859693478445243</v>
+        <v>0.8596960680431585</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.582924471781054</v>
+        <v>4.623953756106395</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.11710950330483</v>
+        <v>5.243491810231073</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.530767602047103</v>
+        <v>6.172303993850123</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E6" t="n">
         <v>8880</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02353570423887</v>
+        <v>7.023521466121001</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2888015826172483</v>
+        <v>0.2887873444993793</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479011855533709</v>
+        <v>1.479034341757625</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907644170285079</v>
+        <v>1.907673598235712</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040030666069015</v>
+        <v>0.3040023623104022</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1982007416369533</v>
+        <v>-0.1982377096048724</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790679839404312</v>
+        <v>0.2790769604434016</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.377548622187303</v>
+        <v>6.408914930616891</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.560002866454044</v>
+        <v>6.736733743976759</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.203323230598098</v>
+        <v>7.677767808169778</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E7" t="n">
         <v>14242</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14241</v>
+        <v>14242</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580521803244155</v>
+        <v>5.580472616205589</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567144080782505</v>
+        <v>5.56708077478166</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01337772246164998</v>
+        <v>-0.01339184142392913</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166207255452578</v>
+        <v>1.166156016703371</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509610013762336</v>
+        <v>1.509580122724772</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048164348666583</v>
+        <v>0.5048178391496344</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05314434541737012</v>
+        <v>0.05312891167118428</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026637133916423</v>
+        <v>0.5026669542343054</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.839656353820597</v>
+        <v>4.849527076877674</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.872673403926631</v>
+        <v>4.908421259056679</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.956195948401163</v>
+        <v>5.099455807351048</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E8" t="n">
         <v>9040</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9039</v>
+        <v>9040</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.873650016594754</v>
+        <v>7.873471515486725</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113608608569091</v>
+        <v>8.113193314442492</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2399585919743354</v>
+        <v>0.2397217989557656</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445995073720389</v>
+        <v>1.446001570132574</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825618907676205</v>
+        <v>1.825589233127484</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077694105811327</v>
+        <v>0.807766434845109</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273672294924169</v>
+        <v>0.6273501205150592</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976013337613492</v>
+        <v>0.7976266726642918</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.803711869228235</v>
+        <v>4.89791050965523</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.977833893584672</v>
+        <v>5.016561846877805</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.139042222057472</v>
+        <v>5.177360253842846</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E9" t="n">
         <v>13905</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13904</v>
+        <v>13905</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609640031645569</v>
+        <v>7.609514203523912</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655477304727651</v>
+        <v>7.65524208911042</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04583727308208125</v>
+        <v>0.04572788558650809</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49369987597391</v>
+        <v>1.493655351936812</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94162592426774</v>
+        <v>1.941571351227811</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566616601859117</v>
+        <v>0.7566738752302762</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248734616934903</v>
+        <v>0.5248791827829323</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552418959226064</v>
+        <v>0.7552590359396116</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.231726017441861</v>
+        <v>5.271042888965482</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.304985865855739</v>
+        <v>5.359965913276012</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.373824507728946</v>
+        <v>5.719977124183006</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61559204588822</v>
+        <v>10.61549745089146</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3105303653958473</v>
+        <v>0.3104357703990908</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053270936246298</v>
+        <v>2.05333710581811</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699034184645244</v>
+        <v>2.699096567342718</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569351725530248</v>
+        <v>0.3569378482476677</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1212160418388373</v>
+        <v>-0.1212678717043878</v>
       </c>
       <c r="X10" t="n">
-        <v>0.336750627585136</v>
+        <v>0.3367698969336207</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.658356370316705</v>
+        <v>9.760650878924682</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.12494815663505</v>
+        <v>10.59618995815584</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.40562048740598</v>
+        <v>11.18921049366495</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E11" t="n">
         <v>13846</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13845</v>
+        <v>13846</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.24274247020585</v>
+        <v>5.242672938032644</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579752906976745</v>
+        <v>0.4579411764705882</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216299447200965</v>
+        <v>5.216225384877326</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02644302300488569</v>
+        <v>-0.02644755315531877</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161061125757097</v>
+        <v>1.161027729376731</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482578379047832</v>
+        <v>1.482542888354903</v>
       </c>
       <c r="V11" t="n">
-        <v>0.42940258892266</v>
+        <v>0.4294198203625418</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09196227981769844</v>
+        <v>-0.0919525534919754</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4275898242948363</v>
+        <v>0.4276087259975681</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.360692223837209</v>
+        <v>4.961676875721668</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.011932702781435</v>
+        <v>5.305281787501284</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.346191860465116</v>
+        <v>5.71375816993464</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E12" t="n">
         <v>4164</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4163</v>
+        <v>4164</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.462991472495796</v>
+        <v>7.462231868395774</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205566860465116</v>
+        <v>2.205555555555556</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.63719583384909</v>
+        <v>7.636603997410425</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1742043613532943</v>
+        <v>0.1743721290146513</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9121818573896692</v>
+        <v>0.912233694298932</v>
       </c>
       <c r="U12" t="n">
-        <v>1.193737624908509</v>
+        <v>1.193729043685657</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8324003952564279</v>
+        <v>0.8324507033901789</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6603381898815386</v>
+        <v>0.6604559348504435</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8305703014672633</v>
+        <v>0.8306119669354097</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.857385207065317</v>
+        <v>4.870944444444445</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.124415398112168</v>
+        <v>5.21061613258659</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.478842322245161</v>
+        <v>5.819550967708758</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E13" t="n">
         <v>6499</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6498</v>
+        <v>6499</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.599894967682364</v>
+        <v>9.599528773657484</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02437073754589</v>
+        <v>10.02373004166844</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4244757698635272</v>
+        <v>0.4242012680109539</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690795753377176</v>
+        <v>1.690611805793404</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149161953357897</v>
+        <v>2.149017517459068</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232907024618508</v>
+        <v>0.82330210630564</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489118635564224</v>
+        <v>0.6489282856993066</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101709103048014</v>
+        <v>0.8102125080363816</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.454810791517144</v>
+        <v>6.453596275745243</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.77063236214947</v>
+        <v>6.889726849275031</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.59094175785094</v>
+        <v>7.730220025158622</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E14" t="n">
         <v>14086</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14085</v>
+        <v>14086</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126358892438766</v>
+        <v>8.126196578162716</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.907890019379845</v>
+        <v>0.9077801984991528</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197304544310398</v>
+        <v>8.196962851354357</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07094565187163387</v>
+        <v>0.07076627319164285</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75609515201756</v>
+        <v>1.75594280282354</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282116137975314</v>
+        <v>2.281978711515041</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808612651243485</v>
+        <v>0.7808907277718476</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654460530642733</v>
+        <v>0.5654809944778427</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804744667239907</v>
+        <v>0.780507421709308</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.086402011194165</v>
+        <v>5.083402884800236</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.118075462216398</v>
+        <v>5.110715509514026</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.149144712984209</v>
+        <v>5.14531912017599</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.668138081395349</v>
+        <v>4.667951343500363</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82060664856587</v>
+        <v>11.82051182879203</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1432807344609165</v>
+        <v>-0.1433755542347523</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052493619554367</v>
+        <v>2.052484712115534</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697923298021468</v>
+        <v>2.697939721913291</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950171949164744</v>
+        <v>0.7950202948766273</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095141576525331</v>
+        <v>0.6095094033907953</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864777076036035</v>
+        <v>0.7864887912971199</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.681106119428045</v>
+        <v>7.686258212223141</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.889390258172906</v>
+        <v>9.231945204799427</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.00830528550993</v>
+        <v>11.09450918117662</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E16" t="n">
         <v>9849</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9848</v>
+        <v>9849</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.361573314378555</v>
+        <v>8.361413747588587</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623131785587692</v>
+        <v>8.623338600776723</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2615584712091377</v>
+        <v>0.2619248531881339</v>
       </c>
       <c r="T16" t="n">
-        <v>3.595864389587379</v>
+        <v>3.596024449015857</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08630318449856</v>
+        <v>11.08586038672308</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04144028354410411</v>
+        <v>0.04142821884793679</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6104039743041296</v>
+        <v>-0.6104335560580347</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02477892464846798</v>
+        <v>0.02476646520759029</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.14789466119348</v>
+        <v>12.5232010864952</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.72400291149705</v>
+        <v>12.79185688941102</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.01696624954969</v>
+        <v>12.90993559570343</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E17" t="n">
         <v>2393</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.474723035117056</v>
+        <v>6.473438152946093</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.434418604651163</v>
+        <v>1.43420116194626</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.83675686719496</v>
+        <v>6.835311418762382</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3620338320779025</v>
+        <v>0.3618732658162884</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007982706333037</v>
+        <v>2.007181957530579</v>
       </c>
       <c r="U17" t="n">
-        <v>2.546083467535185</v>
+        <v>2.545583599720219</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5381437191136976</v>
+        <v>0.5384316073814952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05478938332180316</v>
+        <v>0.05530966935881454</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5347642022290848</v>
+        <v>0.5350511792636894</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.727259422614274</v>
+        <v>2.989601897076521</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6032133424802</v>
+        <v>5.304081670313717</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.980152884355316</v>
+        <v>7.11656007651889</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E18" t="n">
         <v>3251</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.663479505802891</v>
+        <v>6.663415879351652</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948040213365727</v>
+        <v>0.1947403948853327</v>
       </c>
       <c r="T18" t="n">
-        <v>1.093881276937562</v>
+        <v>1.093884561368992</v>
       </c>
       <c r="U18" t="n">
-        <v>1.482964051451932</v>
+        <v>1.482970483670269</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6085484940982976</v>
+        <v>0.6085619252836849</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2320309274309277</v>
+        <v>0.23202426542795</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6055734876370937</v>
+        <v>0.6055931463427583</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.009092665027206</v>
+        <v>4.364644888485341</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.480279323524561</v>
+        <v>5.765634894363791</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.117066895384622</v>
+        <v>7.079646024548743</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E19" t="n">
         <v>7206</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7205</v>
+        <v>7206</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31812234559334</v>
+        <v>10.31686254510131</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11544638464493</v>
+        <v>11.114832241</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7973240390515911</v>
+        <v>0.7979696958986933</v>
       </c>
       <c r="T19" t="n">
-        <v>2.060471793237813</v>
+        <v>2.061043997784299</v>
       </c>
       <c r="U19" t="n">
-        <v>2.78613320240751</v>
+        <v>2.786847635017369</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7275915473834462</v>
+        <v>0.7276257306802797</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4719542921475283</v>
+        <v>0.4720208779034537</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780148347756503</v>
+        <v>0.67792416970471</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.17390771225855</v>
+        <v>7.140550374331551</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.248478806010093</v>
+        <v>7.257241471385896</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.395026595078187</v>
+        <v>7.639776175651321</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E20" t="n">
         <v>10656</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10655</v>
+        <v>10656</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85603610579172</v>
+        <v>13.85573430060162</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23257309682431</v>
+        <v>14.2321227822882</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3765369910325809</v>
+        <v>0.3763884816865894</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25497744764091</v>
+        <v>1.254921513879089</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646792769488665</v>
+        <v>1.646729829131617</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935766541714181</v>
+        <v>0.8935838482448097</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790530150663317</v>
+        <v>0.7790666400925333</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887478024158632</v>
+        <v>0.8887656046016235</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.369305652797218</v>
+        <v>9.504719188949673</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.815105356885004</v>
+        <v>9.769043903990008</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.49067514659454</v>
+        <v>9.996791875239811</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16704</v>
+        <v>16705</v>
       </c>
       <c r="E21" t="n">
         <v>10251</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.972563773137</v>
+        <v>130.9725294163194</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046327420180781</v>
+        <v>0.1045983852004859</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7974354304346204</v>
+        <v>0.7974424656864207</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046049201646916</v>
+        <v>1.046060057190094</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650342580482414</v>
+        <v>0.8650340695071622</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7310103434542224</v>
+        <v>0.7310047604587422</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642861883089861</v>
+        <v>0.8642890237445365</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.6758023894909</v>
+        <v>128.6879053905733</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9012375830087</v>
+        <v>129.1837975417482</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.4143253659274</v>
+        <v>130.7500193058576</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.17390771225855</v>
+        <v>7.140550374331551</v>
       </c>
       <c r="G2" t="n">
-        <v>7.248478806010093</v>
+        <v>7.257241471385894</v>
       </c>
       <c r="H2" t="n">
-        <v>7.395026595078187</v>
+        <v>7.639776175651321</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.839656353820597</v>
+        <v>4.849527076877674</v>
       </c>
       <c r="G3" t="n">
-        <v>4.872673403926631</v>
+        <v>4.908421259056679</v>
       </c>
       <c r="H3" t="n">
-        <v>4.956195948401163</v>
+        <v>5.099455807351048</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.360692223837209</v>
+        <v>4.961676875721668</v>
       </c>
       <c r="G4" t="n">
-        <v>5.011932702781435</v>
+        <v>5.305281787501283</v>
       </c>
       <c r="H4" t="n">
-        <v>5.346191860465116</v>
+        <v>5.71375816993464</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.14789466119348</v>
+        <v>12.5232010864952</v>
       </c>
       <c r="G5" t="n">
-        <v>12.72400291149705</v>
+        <v>12.79185688941102</v>
       </c>
       <c r="H5" t="n">
-        <v>13.01696624954969</v>
+        <v>12.90993559570343</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>107.9033013560735</v>
+        <v>109.2754000091262</v>
       </c>
       <c r="G6" t="n">
-        <v>110.235278494631</v>
+        <v>109.7933810593643</v>
       </c>
       <c r="H6" t="n">
-        <v>111.56</v>
+        <v>110.406442878382</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.681106119428045</v>
+        <v>7.686258212223141</v>
       </c>
       <c r="G7" t="n">
-        <v>8.889390258172906</v>
+        <v>9.231945204799427</v>
       </c>
       <c r="H7" t="n">
-        <v>11.00830528550993</v>
+        <v>11.09450918117662</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.454810791517144</v>
+        <v>6.453596275745243</v>
       </c>
       <c r="G8" t="n">
-        <v>6.77063236214947</v>
+        <v>6.889726849275033</v>
       </c>
       <c r="H8" t="n">
-        <v>7.59094175785094</v>
+        <v>7.730220025158622</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.857385207065317</v>
+        <v>4.870944444444445</v>
       </c>
       <c r="G9" t="n">
-        <v>5.124415398112168</v>
+        <v>5.21061613258659</v>
       </c>
       <c r="H9" t="n">
-        <v>5.478842322245161</v>
+        <v>5.819550967708758</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.803711869228235</v>
+        <v>4.89791050965523</v>
       </c>
       <c r="G10" t="n">
-        <v>4.977833893584672</v>
+        <v>5.016561846877804</v>
       </c>
       <c r="H10" t="n">
-        <v>5.139042222057472</v>
+        <v>5.177360253842846</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.369305652797218</v>
+        <v>9.504719188949673</v>
       </c>
       <c r="G11" t="n">
-        <v>9.815105356885004</v>
+        <v>9.769043903990008</v>
       </c>
       <c r="H11" t="n">
-        <v>10.49067514659454</v>
+        <v>9.996791875239811</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.727259422614274</v>
+        <v>2.989601897076521</v>
       </c>
       <c r="G12" t="n">
-        <v>4.603213342480199</v>
+        <v>5.304081670313717</v>
       </c>
       <c r="H12" t="n">
-        <v>6.980152884355316</v>
+        <v>7.11656007651889</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.086402011194165</v>
+        <v>5.083402884800236</v>
       </c>
       <c r="G13" t="n">
-        <v>5.118075462216398</v>
+        <v>5.110715509514026</v>
       </c>
       <c r="H13" t="n">
-        <v>5.149144712984209</v>
+        <v>5.14531912017599</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.658356370316705</v>
+        <v>9.760650878924682</v>
       </c>
       <c r="G14" t="n">
-        <v>10.12494815663506</v>
+        <v>10.59618995815584</v>
       </c>
       <c r="H14" t="n">
-        <v>10.40562048740598</v>
+        <v>11.18921049366495</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.231726017441861</v>
+        <v>5.271042888965482</v>
       </c>
       <c r="G15" t="n">
-        <v>5.304985865855739</v>
+        <v>5.359965913276012</v>
       </c>
       <c r="H15" t="n">
-        <v>5.373824507728946</v>
+        <v>5.719977124183006</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.377548622187303</v>
+        <v>6.408914930616891</v>
       </c>
       <c r="G16" t="n">
-        <v>6.560002866454044</v>
+        <v>6.736733743976759</v>
       </c>
       <c r="H16" t="n">
-        <v>7.203323230598098</v>
+        <v>7.677767808169778</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.009092665027206</v>
+        <v>4.364644888485341</v>
       </c>
       <c r="G17" t="n">
-        <v>5.480279323524561</v>
+        <v>5.765634894363791</v>
       </c>
       <c r="H17" t="n">
-        <v>7.117066895384622</v>
+        <v>7.079646024548743</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.979523275622994</v>
+        <v>3.105709657543573</v>
       </c>
       <c r="G18" t="n">
-        <v>3.442470192638002</v>
+        <v>3.472548786749318</v>
       </c>
       <c r="H18" t="n">
-        <v>4.288253232024436</v>
+        <v>3.798187392911447</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.93578488372093</v>
+        <v>1.937029966533054</v>
       </c>
       <c r="G19" t="n">
-        <v>2.072767925578817</v>
+        <v>2.100593096467845</v>
       </c>
       <c r="H19" t="n">
-        <v>2.209818313953488</v>
+        <v>2.235123336547924</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.582924471781054</v>
+        <v>4.623953756106395</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11710950330483</v>
+        <v>5.243491810231073</v>
       </c>
       <c r="H20" t="n">
-        <v>6.530767602047103</v>
+        <v>6.172303993850123</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.6758023894909</v>
+        <v>128.6879053905733</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9012375830086</v>
+        <v>129.1837975417482</v>
       </c>
       <c r="H21" t="n">
-        <v>129.4143253659274</v>
+        <v>130.7500193058576</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E2" t="n">
-        <v>10040</v>
+        <v>10042</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10040</v>
+        <v>10041</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5574142098274</v>
+        <v>102.5476933240381</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5471405404388</v>
+        <v>102.5223663111282</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01027366938854744</v>
+        <v>-0.02532701290996149</v>
       </c>
       <c r="T2" t="n">
-        <v>18.00554748112107</v>
+        <v>18.02944360578205</v>
       </c>
       <c r="U2" t="n">
-        <v>36.10139420458456</v>
+        <v>36.14053444904201</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1383238495440355</v>
+        <v>0.1384084713389883</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.720142614884927</v>
+        <v>-0.7218899034470947</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1383218263752586</v>
+        <v>0.1384081084093249</v>
       </c>
       <c r="Y2" t="n">
-        <v>109.2754000091262</v>
+        <v>108.0808366134264</v>
       </c>
       <c r="Z2" t="n">
-        <v>109.7933810593643</v>
+        <v>109.3355929599266</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.406442878382</v>
+        <v>109.9153734623463</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E3" t="n">
-        <v>14634</v>
+        <v>14636</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14634</v>
+        <v>14635</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906396166461664</v>
+        <v>4.906245234028015</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964174394499823</v>
+        <v>4.964156157539784</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0577782280381588</v>
+        <v>0.05791092351176828</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34393109136481</v>
+        <v>1.3439167749256</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718540402149516</v>
+        <v>1.718512534141387</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814486597997008</v>
+        <v>0.7814394107591294</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699239749620836</v>
+        <v>0.5699292493286023</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803990354148286</v>
+        <v>0.7803831250560371</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.937029966533054</v>
+        <v>1.980341069059552</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.100593096467845</v>
+        <v>2.145142478669311</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.235123336547924</v>
+        <v>2.355286647314949</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E4" t="n">
-        <v>10267</v>
+        <v>10270</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10267</v>
+        <v>10269</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.904378348105581</v>
+        <v>6.903786639400137</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.234178493366916</v>
+        <v>7.234110298742468</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3298001452613347</v>
+        <v>0.330323659342332</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291576761739584</v>
+        <v>1.291733707633939</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681220229936122</v>
+        <v>1.681346475715914</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679246484968536</v>
+        <v>0.8678990417882383</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379919501369085</v>
+        <v>0.7379452276750962</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473379264584546</v>
+        <v>0.8471989676560926</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.105709657543573</v>
+        <v>3.152</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.472548786749319</v>
+        <v>3.572908681231568</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.798187392911447</v>
+        <v>4.00625</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.822783829581215</v>
+        <v>2.82263183357523</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301944263140031</v>
+        <v>9.301929773710059</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3694828377175483</v>
+        <v>0.3694683482875762</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247628776810929</v>
+        <v>1.247624501018438</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747185780539978</v>
+        <v>1.747180847593582</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661005036855922</v>
+        <v>0.8661024370054977</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215002224998502</v>
+        <v>0.7215017951117038</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596960680431585</v>
+        <v>0.8596990015772572</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.623953756106395</v>
+        <v>4.736125285792012</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.243491810231073</v>
+        <v>5.242083067321062</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.172303993850123</v>
+        <v>6.010203097500796</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E6" t="n">
-        <v>8880</v>
+        <v>8883</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8880</v>
+        <v>8882</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734734121621622</v>
+        <v>6.734735307363207</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023521466121001</v>
+        <v>7.023547752813228</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887873444993793</v>
+        <v>0.2888124454500219</v>
       </c>
       <c r="T6" t="n">
-        <v>1.479034341757625</v>
+        <v>1.478694547191166</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907673598235712</v>
+        <v>1.907353562148387</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040023623104022</v>
+        <v>0.3039724945345562</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1982377096048724</v>
+        <v>-0.1981073419029498</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790769604434016</v>
+        <v>0.2790008366105098</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.408914930616891</v>
+        <v>6.422788648648649</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.736733743976759</v>
+        <v>6.866583139154793</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.677767808169778</v>
+        <v>7.787691822961839</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E7" t="n">
-        <v>14242</v>
+        <v>14244</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14242</v>
+        <v>14243</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580472616205589</v>
+        <v>5.580411324861336</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.56708077478166</v>
+        <v>5.567013453878615</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01339184142392913</v>
+        <v>-0.01339787098271924</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166156016703371</v>
+        <v>1.166065046317307</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509580122724772</v>
+        <v>1.509508297287237</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048178391496344</v>
+        <v>0.5048344037322939</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05312891167118428</v>
+        <v>0.0531733488633076</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026669542343054</v>
+        <v>0.5026821080981632</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.849527076877674</v>
+        <v>4.868907837445574</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.908421259056679</v>
+        <v>4.944971516123691</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.099455807351048</v>
+        <v>5.258355034092284</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E8" t="n">
-        <v>9040</v>
+        <v>9042</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9040</v>
+        <v>9041</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.873471515486725</v>
+        <v>7.873272315009402</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113193314442492</v>
+        <v>8.113370374450492</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2397217989557656</v>
+        <v>0.2400980594410895</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446001570132574</v>
+        <v>1.446027299318026</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825589233127484</v>
+        <v>1.825611597662324</v>
       </c>
       <c r="V8" t="n">
-        <v>0.807766434845109</v>
+        <v>0.8077346805059106</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273501205150592</v>
+        <v>0.6273146790711057</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976266726642918</v>
+        <v>0.797543874122921</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.89791050965523</v>
+        <v>4.915916310173576</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.016561846877805</v>
+        <v>5.069291646807917</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.177360253842846</v>
+        <v>5.344074579742299</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E9" t="n">
-        <v>13905</v>
+        <v>13907</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13905</v>
+        <v>13906</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609514203523912</v>
+        <v>7.609358550266071</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65524208911042</v>
+        <v>7.655185618957847</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04572788558650809</v>
+        <v>0.04582706869177502</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493655351936812</v>
+        <v>1.493536257111375</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941571351227811</v>
+        <v>1.941490274395865</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566738752302762</v>
+        <v>0.7566771989518812</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248791827829323</v>
+        <v>0.524904674558357</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552590359396116</v>
+        <v>0.7552571716264574</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.271042888965482</v>
+        <v>5.273222309350621</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.359965913276012</v>
+        <v>5.409778775465703</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.719977124183006</v>
+        <v>5.761821480406385</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61549745089146</v>
+        <v>10.61539472349397</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3104357703990908</v>
+        <v>0.3103330430015949</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05333710581811</v>
+        <v>2.053398635395294</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699096567342718</v>
+        <v>2.69915661961345</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569378482476677</v>
+        <v>0.3569421248601958</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1212678717043878</v>
+        <v>-0.121317766496353</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3367698969336207</v>
+        <v>0.3367911261725346</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.760650878924682</v>
+        <v>9.940108546348933</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.59618995815584</v>
+        <v>10.62310375056943</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.18921049366495</v>
+        <v>11.02300353870825</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E11" t="n">
-        <v>13846</v>
+        <v>13848</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13846</v>
+        <v>13847</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242672938032644</v>
+        <v>5.242588430707013</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579411764705882</v>
+        <v>0.4579854862119013</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216225384877326</v>
+        <v>5.216166207674662</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02644755315531877</v>
+        <v>-0.02642222303235148</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161027729376731</v>
+        <v>1.160980586643262</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482542888354903</v>
+        <v>1.482484884837052</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294198203625418</v>
+        <v>0.4294350870261985</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0919525534919754</v>
+        <v>-0.09189301962571506</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276087259975681</v>
+        <v>0.4276217505786627</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.961676875721668</v>
+        <v>4.459307038698986</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.305281787501284</v>
+        <v>5.147076615041406</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.71375816993464</v>
+        <v>5.534757418000877</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E12" t="n">
-        <v>4164</v>
+        <v>4166</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4164</v>
+        <v>4165</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.462231868395774</v>
+        <v>7.461469027611044</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205555555555556</v>
+        <v>2.205631349782293</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.636603997410425</v>
+        <v>7.635874062601511</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1743721290146513</v>
+        <v>0.1744050349904667</v>
       </c>
       <c r="T12" t="n">
-        <v>0.912233694298932</v>
+        <v>0.9121441479046816</v>
       </c>
       <c r="U12" t="n">
-        <v>1.193729043685657</v>
+        <v>1.193570889938893</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8324507033901789</v>
+        <v>0.8325455813200425</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6604559348504435</v>
+        <v>0.6606603537936181</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8306119669354097</v>
+        <v>0.8307022247036171</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.870944444444445</v>
+        <v>4.861843114754299</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.21061613258659</v>
+        <v>5.214059601686155</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.819550967708758</v>
+        <v>5.691130536172471</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E13" t="n">
-        <v>6499</v>
+        <v>6501</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6499</v>
+        <v>6500</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.599528773657484</v>
+        <v>9.599138846153846</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02373004166844</v>
+        <v>10.02371243375177</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4242012680109539</v>
+        <v>0.4245735875979229</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690611805793404</v>
+        <v>1.690618636156347</v>
       </c>
       <c r="U13" t="n">
-        <v>2.149017517459068</v>
+        <v>2.14886585148143</v>
       </c>
       <c r="V13" t="n">
-        <v>0.82330210630564</v>
+        <v>0.8233049671059668</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489282856993066</v>
+        <v>0.6489501663837252</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102125080363816</v>
+        <v>0.8101582742676702</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.453596275745243</v>
+        <v>6.457357393722509</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.889726849275031</v>
+        <v>7.050523218316624</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.730220025158622</v>
+        <v>8.017237057070083</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E14" t="n">
-        <v>14086</v>
+        <v>14088</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14086</v>
+        <v>14087</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126196578162716</v>
+        <v>8.126032512245333</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9077801984991528</v>
+        <v>0.9079366231253024</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.196962851354357</v>
+        <v>8.197032572175674</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07076627319164285</v>
+        <v>0.0710000599303398</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75594280282354</v>
+        <v>1.756069671420714</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281978711515041</v>
+        <v>2.282057234003265</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808907277718476</v>
+        <v>0.7808511170616538</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654809944778427</v>
+        <v>0.5654339899464789</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780507421709308</v>
+        <v>0.780463139247301</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.083402884800236</v>
+        <v>5.083080137366573</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.110715509514026</v>
+        <v>5.107313751106307</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.14531912017599</v>
+        <v>5.139836817461203</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.667951343500363</v>
+        <v>4.667764876632801</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82051182879203</v>
+        <v>11.82041594699036</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1433755542347523</v>
+        <v>-0.1434714360364256</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052484712115534</v>
+        <v>2.052470807561265</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697939721913291</v>
+        <v>2.697954067530325</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950202948766273</v>
+        <v>0.795023773238277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095094033907953</v>
+        <v>0.6095052507083598</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7864887912971199</v>
+        <v>0.786500315113135</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.686258212223141</v>
+        <v>7.757024964845697</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.231945204799427</v>
+        <v>9.592048925933531</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.09450918117662</v>
+        <v>11.28832466681697</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E16" t="n">
-        <v>9849</v>
+        <v>9851</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9849</v>
+        <v>9850</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.361413747588587</v>
+        <v>8.361248629441624</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.623338600776723</v>
+        <v>8.622940982342991</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2619248531881339</v>
+        <v>0.2616923529013656</v>
       </c>
       <c r="T16" t="n">
-        <v>3.596024449015857</v>
+        <v>3.596418167694247</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08586038672308</v>
+        <v>11.08548095585908</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04142821884793679</v>
+        <v>0.04139678258074044</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6104335560580347</v>
+        <v>-0.6104811525224001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02476646520759029</v>
+        <v>0.0247361310642279</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5232010864952</v>
+        <v>12.70418368708677</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.79185688941102</v>
+        <v>12.82640334389768</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.90993559570343</v>
+        <v>12.92859894811067</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E17" t="n">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.473438152946093</v>
+        <v>6.472166875522139</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.43420116194626</v>
+        <v>1.43688679245283</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.835311418762382</v>
+        <v>6.83414180355654</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3618732658162884</v>
+        <v>0.3619749280344009</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007181957530579</v>
+        <v>2.006217228571935</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545583599720219</v>
+        <v>2.544656991195429</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5384316073814952</v>
+        <v>0.5387787694662571</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05530966935881454</v>
+        <v>0.05613519498728514</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5350511792636894</v>
+        <v>0.5353934273592371</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.989601897076521</v>
+        <v>3.249503706471835</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.304081670313717</v>
+        <v>5.064467461094845</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.11656007651889</v>
+        <v>7.092937256627208</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E18" t="n">
-        <v>3251</v>
+        <v>3254</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3251</v>
+        <v>3253</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.468675484466317</v>
+        <v>6.467434368275438</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.663415879351652</v>
+        <v>6.662840814437413</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1947403948853327</v>
+        <v>0.1954064461619751</v>
       </c>
       <c r="T18" t="n">
-        <v>1.093884561368992</v>
+        <v>1.093638878506104</v>
       </c>
       <c r="U18" t="n">
-        <v>1.482970483670269</v>
+        <v>1.482551815403053</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6085619252836849</v>
+        <v>0.608734584131318</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23202426542795</v>
+        <v>0.2326569287589247</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6055931463427583</v>
+        <v>0.6057032298725964</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.364644888485341</v>
+        <v>4.294132026326101</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.765634894363791</v>
+        <v>5.432668711218207</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.079646024548743</v>
+        <v>7.073083471009237</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E19" t="n">
-        <v>7206</v>
+        <v>7208</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7206</v>
+        <v>7207</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31686254510131</v>
+        <v>10.31574392951297</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.114832241</v>
+        <v>11.11361092164338</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7979696958986933</v>
+        <v>0.797866992130404</v>
       </c>
       <c r="T19" t="n">
-        <v>2.061043997784299</v>
+        <v>2.061496159004777</v>
       </c>
       <c r="U19" t="n">
-        <v>2.786847635017369</v>
+        <v>2.787159869736672</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7276257306802797</v>
+        <v>0.7276991392205859</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4720208779034537</v>
+        <v>0.4721512749043477</v>
       </c>
       <c r="X19" t="n">
-        <v>0.67792416970471</v>
+        <v>0.6780375614970793</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.140550374331551</v>
+        <v>7.07833237473772</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.257241471385896</v>
+        <v>7.193505036569746</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.639776175651321</v>
+        <v>7.281806070267995</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E20" t="n">
-        <v>10656</v>
+        <v>10658</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10656</v>
+        <v>10657</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85573430060162</v>
+        <v>13.85544545436904</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.2321227822882</v>
+        <v>14.23205234215856</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3763884816865894</v>
+        <v>0.3766068877895256</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254921513879089</v>
+        <v>1.254949558502833</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646729829131617</v>
+        <v>1.646743046302073</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935838482448097</v>
+        <v>0.8935791894020952</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790666400925333</v>
+        <v>0.7790583515615996</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887656046016235</v>
+        <v>0.8887441735946203</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.504719188949673</v>
+        <v>9.513029549108285</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.769043903990008</v>
+        <v>9.799236210654986</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.996791875239811</v>
+        <v>10.14726791084439</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16705</v>
+        <v>16706</v>
       </c>
       <c r="E21" t="n">
-        <v>10251</v>
+        <v>10254</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10251</v>
+        <v>10253</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8679310311189</v>
+        <v>130.8674505998245</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9725294163194</v>
+        <v>130.9721219031986</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045983852004859</v>
+        <v>0.1046713033741992</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7974424656864207</v>
+        <v>0.7973349624091428</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046060057190094</v>
+        <v>1.045931716963417</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650340695071622</v>
+        <v>0.8650736317079993</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7310047604587422</v>
+        <v>0.7310965380710651</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8642890237445365</v>
+        <v>0.8643208718658064</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.6879053905733</v>
+        <v>128.6853266678256</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1837975417482</v>
+        <v>129.2944915479646</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.7500193058576</v>
+        <v>130.3796551298408</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.140550374331551</v>
+        <v>7.07833237473772</v>
       </c>
       <c r="G2" t="n">
-        <v>7.257241471385894</v>
+        <v>7.193505036569745</v>
       </c>
       <c r="H2" t="n">
-        <v>7.639776175651321</v>
+        <v>7.281806070267995</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.849527076877674</v>
+        <v>4.868907837445574</v>
       </c>
       <c r="G3" t="n">
-        <v>4.908421259056679</v>
+        <v>4.944971516123692</v>
       </c>
       <c r="H3" t="n">
-        <v>5.099455807351048</v>
+        <v>5.258355034092284</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.961676875721668</v>
+        <v>4.459307038698986</v>
       </c>
       <c r="G4" t="n">
-        <v>5.305281787501283</v>
+        <v>5.147076615041407</v>
       </c>
       <c r="H4" t="n">
-        <v>5.71375816993464</v>
+        <v>5.534757418000877</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5232010864952</v>
+        <v>12.70418368708677</v>
       </c>
       <c r="G5" t="n">
-        <v>12.79185688941102</v>
+        <v>12.82640334389768</v>
       </c>
       <c r="H5" t="n">
-        <v>12.90993559570343</v>
+        <v>12.92859894811067</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>109.2754000091262</v>
+        <v>108.0808366134264</v>
       </c>
       <c r="G6" t="n">
-        <v>109.7933810593643</v>
+        <v>109.3355929599266</v>
       </c>
       <c r="H6" t="n">
-        <v>110.406442878382</v>
+        <v>109.9153734623463</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.686258212223141</v>
+        <v>7.757024964845697</v>
       </c>
       <c r="G7" t="n">
-        <v>9.231945204799427</v>
+        <v>9.592048925933531</v>
       </c>
       <c r="H7" t="n">
-        <v>11.09450918117662</v>
+        <v>11.28832466681697</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.453596275745243</v>
+        <v>6.457357393722509</v>
       </c>
       <c r="G8" t="n">
-        <v>6.889726849275033</v>
+        <v>7.050523218316624</v>
       </c>
       <c r="H8" t="n">
-        <v>7.730220025158622</v>
+        <v>8.017237057070083</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.870944444444445</v>
+        <v>4.861843114754299</v>
       </c>
       <c r="G9" t="n">
-        <v>5.21061613258659</v>
+        <v>5.214059601686156</v>
       </c>
       <c r="H9" t="n">
-        <v>5.819550967708758</v>
+        <v>5.691130536172471</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.89791050965523</v>
+        <v>4.915916310173576</v>
       </c>
       <c r="G10" t="n">
-        <v>5.016561846877804</v>
+        <v>5.069291646807917</v>
       </c>
       <c r="H10" t="n">
-        <v>5.177360253842846</v>
+        <v>5.344074579742299</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.504719188949673</v>
+        <v>9.513029549108285</v>
       </c>
       <c r="G11" t="n">
-        <v>9.769043903990008</v>
+        <v>9.799236210654986</v>
       </c>
       <c r="H11" t="n">
-        <v>9.996791875239811</v>
+        <v>10.14726791084439</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.989601897076521</v>
+        <v>3.249503706471835</v>
       </c>
       <c r="G12" t="n">
-        <v>5.304081670313717</v>
+        <v>5.064467461094845</v>
       </c>
       <c r="H12" t="n">
-        <v>7.11656007651889</v>
+        <v>7.092937256627208</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.083402884800236</v>
+        <v>5.083080137366573</v>
       </c>
       <c r="G13" t="n">
-        <v>5.110715509514026</v>
+        <v>5.107313751106307</v>
       </c>
       <c r="H13" t="n">
-        <v>5.14531912017599</v>
+        <v>5.139836817461203</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.760650878924682</v>
+        <v>9.940108546348933</v>
       </c>
       <c r="G14" t="n">
-        <v>10.59618995815584</v>
+        <v>10.62310375056944</v>
       </c>
       <c r="H14" t="n">
-        <v>11.18921049366495</v>
+        <v>11.02300353870825</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.271042888965482</v>
+        <v>5.273222309350621</v>
       </c>
       <c r="G15" t="n">
-        <v>5.359965913276012</v>
+        <v>5.409778775465704</v>
       </c>
       <c r="H15" t="n">
-        <v>5.719977124183006</v>
+        <v>5.761821480406385</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.408914930616891</v>
+        <v>6.422788648648649</v>
       </c>
       <c r="G16" t="n">
-        <v>6.736733743976759</v>
+        <v>6.866583139154793</v>
       </c>
       <c r="H16" t="n">
-        <v>7.677767808169778</v>
+        <v>7.787691822961839</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.364644888485341</v>
+        <v>4.294132026326101</v>
       </c>
       <c r="G17" t="n">
-        <v>5.765634894363791</v>
+        <v>5.432668711218207</v>
       </c>
       <c r="H17" t="n">
-        <v>7.079646024548743</v>
+        <v>7.073083471009237</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.105709657543573</v>
+        <v>3.152</v>
       </c>
       <c r="G18" t="n">
-        <v>3.472548786749318</v>
+        <v>3.572908681231568</v>
       </c>
       <c r="H18" t="n">
-        <v>3.798187392911447</v>
+        <v>4.00625</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.937029966533054</v>
+        <v>1.980341069059552</v>
       </c>
       <c r="G19" t="n">
-        <v>2.100593096467845</v>
+        <v>2.145142478669311</v>
       </c>
       <c r="H19" t="n">
-        <v>2.235123336547924</v>
+        <v>2.355286647314949</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.623953756106395</v>
+        <v>4.736125285792012</v>
       </c>
       <c r="G20" t="n">
-        <v>5.243491810231073</v>
+        <v>5.242083067321063</v>
       </c>
       <c r="H20" t="n">
-        <v>6.172303993850123</v>
+        <v>6.010203097500796</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.6879053905733</v>
+        <v>128.6853266678256</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1837975417482</v>
+        <v>129.2944915479646</v>
       </c>
       <c r="H21" t="n">
-        <v>130.7500193058576</v>
+        <v>130.3796551298408</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E2" t="n">
-        <v>10042</v>
+        <v>10044</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10041</v>
+        <v>10043</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5476933240381</v>
+        <v>102.5282215141558</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5223663111282</v>
+        <v>102.5070901784104</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02532701290996149</v>
+        <v>-0.02113133574541748</v>
       </c>
       <c r="T2" t="n">
-        <v>18.02944360578205</v>
+        <v>18.05274544894794</v>
       </c>
       <c r="U2" t="n">
-        <v>36.14053444904201</v>
+        <v>36.18007849791082</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1384084713389883</v>
+        <v>0.1384555690324496</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7218899034470947</v>
+        <v>-0.7216824725480306</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1384081084093249</v>
+        <v>0.1384551570665918</v>
       </c>
       <c r="Y2" t="n">
-        <v>108.0808366134264</v>
+        <v>107.7277405820598</v>
       </c>
       <c r="Z2" t="n">
-        <v>109.3355929599266</v>
+        <v>108.9682307298963</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.9153734623463</v>
+        <v>109.6705284099435</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E3" t="n">
-        <v>14636</v>
+        <v>14638</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14635</v>
+        <v>14637</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906245234028015</v>
+        <v>4.905908758625401</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.964156157539784</v>
+        <v>4.963852745271476</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05791092351176828</v>
+        <v>0.05794398664607451</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3439167749256</v>
+        <v>1.343798459463503</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718512534141387</v>
+        <v>1.718397513436162</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814394107591294</v>
+        <v>0.7814646116351862</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699292493286023</v>
+        <v>0.5699799652458382</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7803831250560371</v>
+        <v>0.7804074339665984</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.980341069059552</v>
+        <v>2.022659638530344</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.145142478669311</v>
+        <v>2.271372700422416</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.355286647314949</v>
+        <v>2.6324978080326</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E4" t="n">
-        <v>10270</v>
+        <v>10272</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10269</v>
+        <v>10271</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.903786639400137</v>
+        <v>6.903210495570051</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.234110298742468</v>
+        <v>7.233715178146522</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.330323659342332</v>
+        <v>0.3305046825764706</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291733707633939</v>
+        <v>1.291770464644574</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681346475715914</v>
+        <v>1.681371874508908</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678990417882383</v>
+        <v>0.8678897489438074</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379452276750962</v>
+        <v>0.7379276844796985</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471989676560926</v>
+        <v>0.8471503705292507</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.152</v>
+        <v>3.154735920516304</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.572908681231568</v>
+        <v>3.640275809376669</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.00625</v>
+        <v>3.933824879227053</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82263183357523</v>
+        <v>2.822328502415459</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301929773710059</v>
+        <v>9.3018576750856</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3694683482875762</v>
+        <v>0.3693962496631181</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247624501018438</v>
+        <v>1.247574276066752</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747180847593582</v>
+        <v>1.747133438228928</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661024370054977</v>
+        <v>0.8661131662031819</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215017951117038</v>
+        <v>0.7215169088806455</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8596990015772572</v>
+        <v>0.8597136919313064</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.736125285792012</v>
+        <v>4.652335802755899</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.242083067321062</v>
+        <v>5.238267839994539</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.010203097500796</v>
+        <v>5.932712406630359</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E6" t="n">
-        <v>8883</v>
+        <v>8885</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8882</v>
+        <v>8884</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734735307363207</v>
+        <v>6.734675427735255</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023547752813228</v>
+        <v>7.023413350749613</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2888124454500219</v>
+        <v>0.2887379230143582</v>
       </c>
       <c r="T6" t="n">
-        <v>1.478694547191166</v>
+        <v>1.478339836418155</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907353562148387</v>
+        <v>1.907089547701334</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039724945345562</v>
+        <v>0.3039774701833418</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981073419029498</v>
+        <v>-0.198038687184489</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790008366105098</v>
+        <v>0.2789933004260784</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.422788648648649</v>
+        <v>6.41110142308735</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.866583139154793</v>
+        <v>7.192456664409596</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.787691822961839</v>
+        <v>8.0867405977926</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E7" t="n">
-        <v>14244</v>
+        <v>14246</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14243</v>
+        <v>14245</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580411324861336</v>
+        <v>5.580259634959635</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567013453878615</v>
+        <v>5.566753163580637</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01339787098271924</v>
+        <v>-0.01350647137899765</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166065046317307</v>
+        <v>1.166092017013729</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509508297287237</v>
+        <v>1.509444696250746</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048344037322939</v>
+        <v>0.5048991047659097</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0531733488633076</v>
+        <v>0.05318486829537994</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5026821080981632</v>
+        <v>0.5027578605648085</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.868907837445574</v>
+        <v>4.877033126426877</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.944971516123691</v>
+        <v>5.09066415969175</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.258355034092284</v>
+        <v>5.60735727256001</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E8" t="n">
-        <v>9042</v>
+        <v>9044</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9041</v>
+        <v>9043</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.873272315009402</v>
+        <v>7.872831195399757</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113370374450492</v>
+        <v>8.113038296578839</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2400980594410895</v>
+        <v>0.2402071011790828</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446027299318026</v>
+        <v>1.445880346633606</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825611597662324</v>
+        <v>1.825488195645374</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077346805059106</v>
+        <v>0.8077310618601724</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273146790711057</v>
+        <v>0.6273193406778076</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797543874122921</v>
+        <v>0.7975198443754241</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.915916310173576</v>
+        <v>4.922594387826002</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.069291646807917</v>
+        <v>5.177121624670015</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.344074579742299</v>
+        <v>5.721012325398857</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E9" t="n">
-        <v>13907</v>
+        <v>13909</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13906</v>
+        <v>13908</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609358550266071</v>
+        <v>7.609022864538396</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.655185618957847</v>
+        <v>7.654701683670623</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04582706869177502</v>
+        <v>0.04567881913222786</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493536257111375</v>
+        <v>1.493462820020793</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941490274395865</v>
+        <v>1.941539676894646</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566771989518812</v>
+        <v>0.7566434635543293</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524904674558357</v>
+        <v>0.524859133324479</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552571716264574</v>
+        <v>0.7552196512671678</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.273222309350621</v>
+        <v>4.457051701975837</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.409778775465703</v>
+        <v>4.867559780779048</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.761821480406385</v>
+        <v>5.436740957792837</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61539472349397</v>
+        <v>10.61512994333149</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3103330430015949</v>
+        <v>0.3100682628391209</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053398635395294</v>
+        <v>2.053455852296611</v>
       </c>
       <c r="U10" t="n">
-        <v>2.69915661961345</v>
+        <v>2.699209789474196</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569421248601958</v>
+        <v>0.3569773070591263</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.121317766496353</v>
+        <v>-0.121361943922949</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3367911261725346</v>
+        <v>0.3368583535400224</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.940108546348933</v>
+        <v>10.22503199170241</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.62310375056943</v>
+        <v>10.78225780060895</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.02300353870825</v>
+        <v>11.01601843328336</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E11" t="n">
-        <v>13848</v>
+        <v>13850</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13847</v>
+        <v>13849</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242588430707013</v>
+        <v>5.242425048739981</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579854862119013</v>
+        <v>0.4579956521739131</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216166207674662</v>
+        <v>5.216030421747012</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02642222303235148</v>
+        <v>-0.02639462699296871</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160980586643262</v>
+        <v>1.160958872432106</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482484884837052</v>
+        <v>1.482440925598357</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294350870261985</v>
+        <v>0.429469595694961</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09189301962571506</v>
+        <v>-0.09188557678762255</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276217505786627</v>
+        <v>0.4276606433403746</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.459307038698986</v>
+        <v>4.472471369863138</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.147076615041406</v>
+        <v>5.097208221479042</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.534757418000877</v>
+        <v>5.580293701467484</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E12" t="n">
-        <v>4166</v>
+        <v>4168</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4165</v>
+        <v>4167</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.461469027611044</v>
+        <v>7.45992344612431</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205631349782293</v>
+        <v>2.205695652173913</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.635874062601511</v>
+        <v>7.63451876749722</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1744050349904667</v>
+        <v>0.17459532137291</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9121441479046816</v>
+        <v>0.9120337774542844</v>
       </c>
       <c r="U12" t="n">
-        <v>1.193570889938893</v>
+        <v>1.193336641309525</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8325455813200425</v>
+        <v>0.8327130711231108</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6606603537936181</v>
+        <v>0.6610325135154342</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8307022247036171</v>
+        <v>0.8308554520699303</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.861843114754299</v>
+        <v>4.85783834383356</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.214059601686155</v>
+        <v>5.300256993600946</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.691130536172471</v>
+        <v>5.990656666280034</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E13" t="n">
-        <v>6501</v>
+        <v>6503</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6500</v>
+        <v>6502</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.599138846153846</v>
+        <v>9.598351661027376</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02371243375177</v>
+        <v>10.02311612253515</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4245735875979229</v>
+        <v>0.424764461507771</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690618636156347</v>
+        <v>1.690466669627031</v>
       </c>
       <c r="U13" t="n">
-        <v>2.14886585148143</v>
+        <v>2.148608448055885</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233049671059668</v>
+        <v>0.8233147539255123</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489501663837252</v>
+        <v>0.6489800334080175</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101582742676702</v>
+        <v>0.8101323682304246</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.457357393722509</v>
+        <v>6.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.050523218316624</v>
+        <v>7.404563882669379</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.017237057070083</v>
+        <v>8.296343987450658</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E14" t="n">
-        <v>14088</v>
+        <v>14090</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14087</v>
+        <v>14089</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.126032512245333</v>
+        <v>8.125701611186033</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9079366231253024</v>
+        <v>0.9079830917874396</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197032572175674</v>
+        <v>8.196756827476161</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0710000599303398</v>
+        <v>0.07105521629012984</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756069671420714</v>
+        <v>1.756036717980245</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282057234003265</v>
+        <v>2.281995848874587</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808511170616538</v>
+        <v>0.7808418343208191</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654339899464789</v>
+        <v>0.5654236459049331</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780463139247301</v>
+        <v>0.780452668117</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.083080137366573</v>
+        <v>5.074027516363095</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.107313751106307</v>
+        <v>5.095582724125314</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.139836817461203</v>
+        <v>5.118602561655213</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.667764876632801</v>
+        <v>4.667392753623188</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82041594699036</v>
+        <v>11.82022553768695</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1434714360364256</v>
+        <v>-0.1436618453398296</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052470807561265</v>
+        <v>2.052442984315693</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697954067530325</v>
+        <v>2.697983520199011</v>
       </c>
       <c r="V15" t="n">
-        <v>0.795023773238277</v>
+        <v>0.795030537800929</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095052507083598</v>
+        <v>0.6094967248587986</v>
       </c>
       <c r="X15" t="n">
-        <v>0.786500315113135</v>
+        <v>0.7865230517878731</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.757024964845697</v>
+        <v>8.005718780777642</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.592048925933531</v>
+        <v>10.30846893907205</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.28832466681697</v>
+        <v>11.38814600928627</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E16" t="n">
-        <v>9851</v>
+        <v>9853</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9850</v>
+        <v>9852</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.361248629441624</v>
+        <v>8.360899208282582</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622940982342991</v>
+        <v>8.622771510672308</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2616923529013656</v>
+        <v>0.2618723023897261</v>
       </c>
       <c r="T16" t="n">
-        <v>3.596418167694247</v>
+        <v>3.59703404606171</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08548095585908</v>
+        <v>11.08470139157754</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04139678258074044</v>
+        <v>0.04134673026737449</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6104811525224001</v>
+        <v>-0.6105689124582978</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0247361310642279</v>
+        <v>0.02468665725427532</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.70418368708677</v>
+        <v>12.8276134115311</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.82640334389768</v>
+        <v>12.84499749776546</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.92859894811067</v>
+        <v>12.86276570129292</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E17" t="n">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.472166875522139</v>
+        <v>6.469534641068448</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.43688679245283</v>
+        <v>1.439347826086957</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.83414180355654</v>
+        <v>6.83338649720656</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3619749280344009</v>
+        <v>0.3638518561381128</v>
       </c>
       <c r="T17" t="n">
-        <v>2.006217228571935</v>
+        <v>2.006608735516815</v>
       </c>
       <c r="U17" t="n">
-        <v>2.544656991195429</v>
+        <v>2.544854276920609</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5387787694662571</v>
+        <v>0.5387670473186593</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05613519498728514</v>
+        <v>0.05634224096928886</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5353934273592371</v>
+        <v>0.5353462625152356</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.249503706471835</v>
+        <v>2.329491619622479</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.064467461094845</v>
+        <v>4.25539817496866</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.092937256627208</v>
+        <v>7.05928996214752</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E18" t="n">
-        <v>3254</v>
+        <v>3256</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3253</v>
+        <v>3255</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.467434368275438</v>
+        <v>6.466216282642089</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.662840814437413</v>
+        <v>6.662743723966659</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1954064461619751</v>
+        <v>0.1965274413245693</v>
       </c>
       <c r="T18" t="n">
-        <v>1.093638878506104</v>
+        <v>1.094147675502901</v>
       </c>
       <c r="U18" t="n">
-        <v>1.482551815403053</v>
+        <v>1.482949219113952</v>
       </c>
       <c r="V18" t="n">
-        <v>0.608734584131318</v>
+        <v>0.6085205537713276</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2326569287589247</v>
+        <v>0.2324205682218572</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6057032298725964</v>
+        <v>0.6054320178086114</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.294132026326101</v>
+        <v>3.423136341721245</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.432668711218207</v>
+        <v>4.796402808879628</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.073083471009237</v>
+        <v>6.188053353408289</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E19" t="n">
-        <v>7208</v>
+        <v>7210</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7207</v>
+        <v>7209</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31574392951297</v>
+        <v>10.31359987515606</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11361092164338</v>
+        <v>11.11174772930512</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.797866992130404</v>
+        <v>0.7981478541490623</v>
       </c>
       <c r="T19" t="n">
-        <v>2.061496159004777</v>
+        <v>2.062282139478092</v>
       </c>
       <c r="U19" t="n">
-        <v>2.787159869736672</v>
+        <v>2.78773968345362</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7276991392205859</v>
+        <v>0.7278326930611699</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4721512749043477</v>
+        <v>0.4723791659924667</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780375614970793</v>
+        <v>0.6781490622671591</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.07833237473772</v>
+        <v>7.04677911613746</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.193505036569746</v>
+        <v>7.172104384371917</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.281806070267995</v>
+        <v>7.357110204121458</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E20" t="n">
-        <v>10658</v>
+        <v>10660</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10657</v>
+        <v>10659</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85544545436904</v>
+        <v>13.85485854275362</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,37 +2216,37 @@
         <v>7.490515759312321</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23205234215856</v>
+        <v>14.23150975018812</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3766068877895256</v>
+        <v>0.3766512074344964</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254949558502833</v>
+        <v>1.254934151707108</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646743046302073</v>
+        <v>1.646689233515754</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935791894020952</v>
+        <v>0.8935819527689697</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790583515615996</v>
+        <v>0.7790643779636197</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887441735946203</v>
+        <v>0.888742379928471</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.513029549108285</v>
+        <v>9.437029040330454</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.799236210654986</v>
+        <v>9.71235377189215</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.14726791084439</v>
+        <v>10.06859900854597</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16706</v>
+        <v>16708</v>
       </c>
       <c r="E21" t="n">
-        <v>10254</v>
+        <v>10256</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10253</v>
+        <v>10255</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8674505998245</v>
+        <v>130.8669976596782</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9721219031986</v>
+        <v>130.971735698397</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046713033741992</v>
+        <v>0.1047380387188036</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7973349624091428</v>
+        <v>0.7972011485002319</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045931716963417</v>
+        <v>1.045824806325638</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8650736317079993</v>
+        <v>0.8651065672800066</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7310965380710651</v>
+        <v>0.7311686152228927</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643208718658064</v>
+        <v>0.8643490824905443</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.6853266678256</v>
+        <v>128.7965938962764</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2944915479646</v>
+        <v>129.4711211537139</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.3796551298408</v>
+        <v>131.0517741041349</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.07833237473772</v>
+        <v>7.04677911613746</v>
       </c>
       <c r="G2" t="n">
-        <v>7.193505036569745</v>
+        <v>7.172104384371918</v>
       </c>
       <c r="H2" t="n">
-        <v>7.281806070267995</v>
+        <v>7.357110204121458</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.868907837445574</v>
+        <v>4.877033126426877</v>
       </c>
       <c r="G3" t="n">
-        <v>4.944971516123692</v>
+        <v>5.090664159691751</v>
       </c>
       <c r="H3" t="n">
-        <v>5.258355034092284</v>
+        <v>5.60735727256001</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.459307038698986</v>
+        <v>4.472471369863138</v>
       </c>
       <c r="G4" t="n">
-        <v>5.147076615041407</v>
+        <v>5.097208221479042</v>
       </c>
       <c r="H4" t="n">
-        <v>5.534757418000877</v>
+        <v>5.580293701467484</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.70418368708677</v>
+        <v>12.8276134115311</v>
       </c>
       <c r="G5" t="n">
-        <v>12.82640334389768</v>
+        <v>12.84499749776546</v>
       </c>
       <c r="H5" t="n">
-        <v>12.92859894811067</v>
+        <v>12.86276570129292</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>108.0808366134264</v>
+        <v>107.7277405820598</v>
       </c>
       <c r="G6" t="n">
-        <v>109.3355929599266</v>
+        <v>108.9682307298962</v>
       </c>
       <c r="H6" t="n">
-        <v>109.9153734623463</v>
+        <v>109.6705284099435</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.757024964845697</v>
+        <v>8.005718780777642</v>
       </c>
       <c r="G7" t="n">
-        <v>9.592048925933531</v>
+        <v>10.30846893907205</v>
       </c>
       <c r="H7" t="n">
-        <v>11.28832466681697</v>
+        <v>11.38814600928627</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.457357393722509</v>
+        <v>6.52</v>
       </c>
       <c r="G8" t="n">
-        <v>7.050523218316624</v>
+        <v>7.404563882669381</v>
       </c>
       <c r="H8" t="n">
-        <v>8.017237057070083</v>
+        <v>8.296343987450658</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.861843114754299</v>
+        <v>4.85783834383356</v>
       </c>
       <c r="G9" t="n">
-        <v>5.214059601686156</v>
+        <v>5.300256993600946</v>
       </c>
       <c r="H9" t="n">
-        <v>5.691130536172471</v>
+        <v>5.990656666280034</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.915916310173576</v>
+        <v>4.922594387826002</v>
       </c>
       <c r="G10" t="n">
-        <v>5.069291646807917</v>
+        <v>5.177121624670015</v>
       </c>
       <c r="H10" t="n">
-        <v>5.344074579742299</v>
+        <v>5.721012325398857</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.513029549108285</v>
+        <v>9.437029040330454</v>
       </c>
       <c r="G11" t="n">
-        <v>9.799236210654986</v>
+        <v>9.71235377189215</v>
       </c>
       <c r="H11" t="n">
-        <v>10.14726791084439</v>
+        <v>10.06859900854597</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>3.249503706471835</v>
+        <v>2.329491619622479</v>
       </c>
       <c r="G12" t="n">
-        <v>5.064467461094845</v>
+        <v>4.25539817496866</v>
       </c>
       <c r="H12" t="n">
-        <v>7.092937256627208</v>
+        <v>7.05928996214752</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.083080137366573</v>
+        <v>5.074027516363095</v>
       </c>
       <c r="G13" t="n">
-        <v>5.107313751106307</v>
+        <v>5.095582724125313</v>
       </c>
       <c r="H13" t="n">
-        <v>5.139836817461203</v>
+        <v>5.118602561655213</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.940108546348933</v>
+        <v>10.22503199170241</v>
       </c>
       <c r="G14" t="n">
-        <v>10.62310375056944</v>
+        <v>10.78225780060895</v>
       </c>
       <c r="H14" t="n">
-        <v>11.02300353870825</v>
+        <v>11.01601843328336</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.273222309350621</v>
+        <v>4.457051701975837</v>
       </c>
       <c r="G15" t="n">
-        <v>5.409778775465704</v>
+        <v>4.867559780779048</v>
       </c>
       <c r="H15" t="n">
-        <v>5.761821480406385</v>
+        <v>5.436740957792837</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.422788648648649</v>
+        <v>6.41110142308735</v>
       </c>
       <c r="G16" t="n">
-        <v>6.866583139154793</v>
+        <v>7.192456664409596</v>
       </c>
       <c r="H16" t="n">
-        <v>7.787691822961839</v>
+        <v>8.0867405977926</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.294132026326101</v>
+        <v>3.423136341721245</v>
       </c>
       <c r="G17" t="n">
-        <v>5.432668711218207</v>
+        <v>4.796402808879628</v>
       </c>
       <c r="H17" t="n">
-        <v>7.073083471009237</v>
+        <v>6.188053353408289</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.152</v>
+        <v>3.154735920516304</v>
       </c>
       <c r="G18" t="n">
-        <v>3.572908681231568</v>
+        <v>3.640275809376669</v>
       </c>
       <c r="H18" t="n">
-        <v>4.00625</v>
+        <v>3.933824879227053</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>1.980341069059552</v>
+        <v>2.022659638530344</v>
       </c>
       <c r="G19" t="n">
-        <v>2.145142478669311</v>
+        <v>2.271372700422416</v>
       </c>
       <c r="H19" t="n">
-        <v>2.355286647314949</v>
+        <v>2.6324978080326</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.736125285792012</v>
+        <v>4.652335802755899</v>
       </c>
       <c r="G20" t="n">
-        <v>5.242083067321063</v>
+        <v>5.238267839994538</v>
       </c>
       <c r="H20" t="n">
-        <v>6.010203097500796</v>
+        <v>5.932712406630359</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.6853266678256</v>
+        <v>128.7965938962764</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2944915479646</v>
+        <v>129.4711211537139</v>
       </c>
       <c r="H21" t="n">
-        <v>130.3796551298408</v>
+        <v>131.0517741041349</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E2" t="n">
+        <v>10045</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10044</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10043</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5282215141558</v>
+        <v>102.5184636267091</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843123209169055</v>
+        <v>1.843151862464183</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5070901784104</v>
+        <v>102.4958357216216</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02113133574541748</v>
+        <v>-0.02262790508752608</v>
       </c>
       <c r="T2" t="n">
-        <v>18.05274544894794</v>
+        <v>18.07277041387713</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18007849791082</v>
+        <v>36.2083696291042</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1384555690324496</v>
+        <v>0.1381071439858041</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7216824725480306</v>
+        <v>-0.7223812603346198</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1384551570665918</v>
+        <v>0.138106729898692</v>
       </c>
       <c r="Y2" t="n">
-        <v>107.7277405820598</v>
+        <v>6.084879405439972</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.9682307298963</v>
+        <v>100.9980246532898</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.6705284099435</v>
+        <v>110.0942012336522</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E3" t="n">
+        <v>14639</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14638</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14637</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.905908758625401</v>
+        <v>4.905727831670993</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.963852745271476</v>
+        <v>4.963631550123377</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05794398664607451</v>
+        <v>0.05790371845238466</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343798459463503</v>
+        <v>1.343702751855295</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718397513436162</v>
+        <v>1.71831762165666</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814646116351862</v>
+        <v>0.7814879917374702</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5699799652458382</v>
+        <v>0.5700205769558857</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804074339665984</v>
+        <v>0.7804323422069606</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.022659638530344</v>
+        <v>2.576784425619431</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.271372700422416</v>
+        <v>2.75356247792186</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.6324978080326</v>
+        <v>3.171716332378224</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E4" t="n">
+        <v>10273</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10272</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10271</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.903210495570051</v>
+        <v>6.902919343847352</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.233715178146522</v>
+        <v>7.233360362166946</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3305046825764706</v>
+        <v>0.3304410183195957</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291770464644574</v>
+        <v>1.291708130655043</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681371874508908</v>
+        <v>1.681293121005618</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678897489438074</v>
+        <v>0.8679005169595447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379276844796985</v>
+        <v>0.737947874013682</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471503705292507</v>
+        <v>0.847172276780244</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.154735920516304</v>
+        <v>3.485260267430755</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.640275809376669</v>
+        <v>3.663141904210948</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.933824879227053</v>
+        <v>3.91325129681344</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.822328502415459</v>
+        <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.3018576750856</v>
+        <v>9.301788018998815</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3693962496631181</v>
+        <v>0.3693265935763317</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247574276066752</v>
+        <v>1.247528190403433</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747133438228928</v>
+        <v>1.74708608498406</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661131662031819</v>
+        <v>0.8661227675082804</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215169088806455</v>
+        <v>0.7215320043496115</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597136919313064</v>
+        <v>0.8597267686048375</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.652335802755899</v>
+        <v>5.397957634625131</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.238267839994539</v>
+        <v>5.760261937992381</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.932712406630359</v>
+        <v>6.124418628794484</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E6" t="n">
+        <v>8886</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8885</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8884</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734675427735255</v>
+        <v>6.734615531795161</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023413350749613</v>
+        <v>7.023320467023683</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887379230143582</v>
+        <v>0.2887049352285225</v>
       </c>
       <c r="T6" t="n">
-        <v>1.478339836418155</v>
+        <v>1.478187976844278</v>
       </c>
       <c r="U6" t="n">
-        <v>1.907089547701334</v>
+        <v>1.906957545441712</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039774701833418</v>
+        <v>0.3039948069548916</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.198038687184489</v>
+        <v>-0.1979951007380882</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789933004260784</v>
+        <v>0.2790073830336446</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.41110142308735</v>
+        <v>6.881352415904541</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.192456664409596</v>
+        <v>7.760073567057695</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.0867405977926</v>
+        <v>8.230579627560878</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E7" t="n">
+        <v>14247</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14246</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14245</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580259634959635</v>
+        <v>5.580172574757827</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566753163580637</v>
+        <v>5.566657837623135</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01350647137899765</v>
+        <v>-0.01351473713469113</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166092017013729</v>
+        <v>1.166061947964387</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509444696250746</v>
+        <v>1.509408788093766</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5048991047659097</v>
+        <v>0.5049119592341417</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05318486829537994</v>
+        <v>0.05320593530802298</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5027578605648085</v>
+        <v>0.5027709990020339</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.877033126426877</v>
+        <v>5.098115173003299</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.09066415969175</v>
+        <v>5.353276272731931</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.60735727256001</v>
+        <v>5.809628378908342</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E8" t="n">
+        <v>9045</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9044</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9043</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.872831195399757</v>
+        <v>7.872586245024325</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6453438395415473</v>
+        <v>0.645365329512894</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.113038296578839</v>
+        <v>8.112764326936837</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2402071011790828</v>
+        <v>0.2401780819125101</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445880346633606</v>
+        <v>1.445777228634437</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825488195645374</v>
+        <v>1.825384538024951</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077310618601724</v>
+        <v>0.8077432681995783</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273193406778076</v>
+        <v>0.6273430717512127</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975198443754241</v>
+        <v>0.797532410781701</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.922594387826002</v>
+        <v>5.081550239256321</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.177121624670015</v>
+        <v>5.431360314061421</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.721012325398857</v>
+        <v>5.981528502152191</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E9" t="n">
+        <v>13910</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13909</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13908</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.609022864538396</v>
+        <v>7.60883870156014</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.654701683670623</v>
+        <v>7.654453705115104</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04567881913222786</v>
+        <v>0.04561500355496394</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493462820020793</v>
+        <v>1.49338114182788</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941539676894646</v>
+        <v>1.941463465217138</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566434635543293</v>
+        <v>0.7566641977288195</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524859133324479</v>
+        <v>0.5248905241227972</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552196512671678</v>
+        <v>0.7552428132713578</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.457051701975837</v>
+        <v>4.784552657958819</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.867559780779048</v>
+        <v>5.389648574690169</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.436740957792837</v>
+        <v>6.035700896938059</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61512994333149</v>
+        <v>10.61494844283996</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3100682628391209</v>
+        <v>0.3098867623475863</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053455852296611</v>
+        <v>2.053436694227355</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699209789474196</v>
+        <v>2.699183528451742</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569773070591263</v>
+        <v>0.3570197199458106</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.121361943922949</v>
+        <v>-0.1213401242273839</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3368583535400224</v>
+        <v>0.3369168649342661</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.22503199170241</v>
+        <v>10.31221565761658</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.78225780060895</v>
+        <v>10.8687881814096</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.01601843328336</v>
+        <v>11.12977101809581</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E11" t="n">
+        <v>13851</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13850</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13849</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242425048739981</v>
+        <v>5.242321444043322</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579956521739131</v>
+        <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216030421747012</v>
+        <v>5.215898609476869</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02639462699296871</v>
+        <v>-0.02642283456645324</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160958872432106</v>
+        <v>1.160979437247967</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482440925598357</v>
+        <v>1.48244874999797</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429469595694961</v>
+        <v>0.4294782350164643</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09188557678762255</v>
+        <v>-0.09189529448819411</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276606433403746</v>
+        <v>0.4276711210441666</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.472471369863138</v>
+        <v>4.169449702551851</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.097208221479042</v>
+        <v>4.739725518451614</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.580293701467484</v>
+        <v>5.101406676676977</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E12" t="n">
+        <v>4169</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4168</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4167</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.45992344612431</v>
+        <v>7.459238483685221</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205695652173913</v>
+        <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.63451876749722</v>
+        <v>7.633602274665503</v>
       </c>
       <c r="R12" t="n">
-        <v>16.78633667621756</v>
+        <v>16.74825286532928</v>
       </c>
       <c r="S12" t="n">
-        <v>0.17459532137291</v>
+        <v>0.1743637909802826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9120337774542844</v>
+        <v>0.9118295262480964</v>
       </c>
       <c r="U12" t="n">
-        <v>1.193336641309525</v>
+        <v>1.192945357315236</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8327130711231108</v>
+        <v>0.8328554502524977</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6610325135154342</v>
+        <v>0.6613311140909686</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8308554520699303</v>
+        <v>0.8310010057097683</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.85783834383356</v>
+        <v>4.222689522318817</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.300256993600946</v>
+        <v>5.188554192865136</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.990656666280034</v>
+        <v>5.972897661585301</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E13" t="n">
+        <v>6504</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6503</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6502</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.598351661027376</v>
+        <v>9.59795517453483</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02311612253515</v>
+        <v>10.02267353686519</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.424764461507771</v>
+        <v>0.4247183623303621</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690466669627031</v>
+        <v>1.690209725468332</v>
       </c>
       <c r="U13" t="n">
-        <v>2.148608448055885</v>
+        <v>2.148402412303055</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233147539255123</v>
+        <v>0.8233351514215483</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6489800334080175</v>
+        <v>0.6490206561114238</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101323682304246</v>
+        <v>0.8101519507590041</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.52</v>
+        <v>6.714062243243538</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.404563882669379</v>
+        <v>7.470257947596752</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.296343987450658</v>
+        <v>8.404015125257589</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E14" t="n">
+        <v>14091</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14090</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14089</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.125701611186033</v>
+        <v>8.125535841022003</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9079830917874396</v>
+        <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.196756827476161</v>
+        <v>8.196515398155281</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07105521629012984</v>
+        <v>0.07097955713328045</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756036717980245</v>
+        <v>1.75588420254984</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281995848874587</v>
+        <v>2.281849331733018</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808418343208191</v>
+        <v>0.780865978853185</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5654236459049331</v>
+        <v>0.565462648201543</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780452668117</v>
+        <v>0.7804781562651737</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.074027516363095</v>
+        <v>7.097135661894368</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.095582724125314</v>
+        <v>7.174286831041369</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.118602561655213</v>
+        <v>7.277034337250829</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.667392753623188</v>
+        <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82022553768695</v>
+        <v>11.82012879219055</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1436618453398296</v>
+        <v>-0.1437585908362349</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052442984315693</v>
+        <v>2.052429253974986</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697983520199011</v>
+        <v>2.698000123924439</v>
       </c>
       <c r="V15" t="n">
-        <v>0.795030537800929</v>
+        <v>0.7950336976343112</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094967248587986</v>
+        <v>0.6094919184327685</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865230517878731</v>
+        <v>0.7865342834116523</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.005718780777642</v>
+        <v>7.735714212462462</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.30846893907205</v>
+        <v>8.788540746328469</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.38814600928627</v>
+        <v>9.329391009975955</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E16" t="n">
+        <v>9854</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9853</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9852</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360899208282582</v>
+        <v>8.360735715010657</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622771510672308</v>
+        <v>8.622658279170189</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2618723023897261</v>
+        <v>0.2619225641595323</v>
       </c>
       <c r="T16" t="n">
-        <v>3.59703404606171</v>
+        <v>3.597401462170467</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08470139157754</v>
+        <v>11.08431937375612</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04134673026737449</v>
+        <v>0.04131859380535303</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6105689124582978</v>
+        <v>-0.6106158074844188</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02468665725427532</v>
+        <v>0.02465880428052913</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.8276134115311</v>
+        <v>11.74611463710226</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.84499749776546</v>
+        <v>11.75664706341954</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.86276570129292</v>
+        <v>11.7714352319618</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E17" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2397</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2396</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.469534641068448</v>
+        <v>6.468116395494368</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.439347826086957</v>
+        <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.83338649720656</v>
+        <v>6.832469573841053</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3638518561381128</v>
+        <v>0.3643531783466843</v>
       </c>
       <c r="T17" t="n">
-        <v>2.006608735516815</v>
+        <v>2.007337608381943</v>
       </c>
       <c r="U17" t="n">
-        <v>2.544854276920609</v>
+        <v>2.545594698074465</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5387670473186593</v>
+        <v>0.5386467493794241</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05634224096928886</v>
+        <v>0.0560621100040769</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5353462625152356</v>
+        <v>0.5352160115133131</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.329491619622479</v>
+        <v>2.796325003762721</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.25539817496866</v>
+        <v>5.221056892276668</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.05928996214752</v>
+        <v>7.378180550910325</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E18" t="n">
+        <v>3257</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3256</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3255</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.466216282642089</v>
+        <v>6.465524877149877</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.662743723966659</v>
+        <v>6.662077033936975</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1965274413245693</v>
+        <v>0.1965521567870986</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094147675502901</v>
+        <v>1.094282493177828</v>
       </c>
       <c r="U18" t="n">
-        <v>1.482949219113952</v>
+        <v>1.482964319254482</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6085205537713276</v>
+        <v>0.6086027727445059</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2324205682218572</v>
+        <v>0.2325860339545245</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6054320178086114</v>
+        <v>0.6055119864602612</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.423136341721245</v>
+        <v>2.350986500807899</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.796402808879628</v>
+        <v>4.865574730022947</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.188053353408289</v>
+        <v>6.660532358132271</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E19" t="n">
+        <v>7211</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7210</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7209</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31359987515606</v>
+        <v>10.31253765603329</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11174772930512</v>
+        <v>11.11076403727022</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7981478541490623</v>
+        <v>0.7982263812369342</v>
       </c>
       <c r="T19" t="n">
-        <v>2.062282139478092</v>
+        <v>2.062675005785243</v>
       </c>
       <c r="U19" t="n">
-        <v>2.78773968345362</v>
+        <v>2.788014019829423</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7278326930611699</v>
+        <v>0.7278922526780486</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4723791659924667</v>
+        <v>0.4724934587423321</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6781490622671591</v>
+        <v>0.678187502038692</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.04677911613746</v>
+        <v>8.86690262910068</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.172104384371917</v>
+        <v>9.155721093673058</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.357110204121458</v>
+        <v>9.342323839974595</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E20" t="n">
+        <v>10661</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10660</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10659</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85485854275362</v>
+        <v>13.85455531962578</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490515759312321</v>
+        <v>7.490716332378224</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23150975018812</v>
+        <v>14.23113414722645</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3766512074344964</v>
+        <v>0.3765788276006634</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254934151707108</v>
+        <v>1.25490456743891</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646689233515754</v>
+        <v>1.646633466959064</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935819527689697</v>
+        <v>0.8935878675449844</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790643779636197</v>
+        <v>0.7790762586206252</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888742379928471</v>
+        <v>0.888752778291637</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.437029040330454</v>
+        <v>10.2583709114474</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.71235377189215</v>
+        <v>10.42652374302666</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.06859900854597</v>
+        <v>10.61119334527235</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="E21" t="n">
+        <v>10257</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10256</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10255</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8669976596782</v>
+        <v>130.8668302457098</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.971735698397</v>
+        <v>130.9714839833445</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1047380387188036</v>
+        <v>0.1046537376347076</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7972011485002319</v>
+        <v>0.7971536587135867</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045824806325638</v>
+        <v>1.04576998869083</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651065672800066</v>
+        <v>0.8651190378987902</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311686152228927</v>
+        <v>0.7311895764873657</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643490824905443</v>
+        <v>0.8643649301797645</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.7965938962764</v>
+        <v>128.5613582564121</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.4711211537139</v>
+        <v>129.0622637788122</v>
       </c>
       <c r="AA21" t="n">
-        <v>131.0517741041349</v>
+        <v>129.7913342861734</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04677911613746</v>
+        <v>8.86690262910068</v>
       </c>
       <c r="G2" t="n">
-        <v>7.172104384371918</v>
+        <v>9.155721093673058</v>
       </c>
       <c r="H2" t="n">
-        <v>7.357110204121458</v>
+        <v>9.342323839974595</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.877033126426877</v>
+        <v>5.098115173003299</v>
       </c>
       <c r="G3" t="n">
-        <v>5.090664159691751</v>
+        <v>5.35327627273193</v>
       </c>
       <c r="H3" t="n">
-        <v>5.60735727256001</v>
+        <v>5.809628378908342</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.472471369863138</v>
+        <v>4.169449702551851</v>
       </c>
       <c r="G4" t="n">
-        <v>5.097208221479042</v>
+        <v>4.739725518451614</v>
       </c>
       <c r="H4" t="n">
-        <v>5.580293701467484</v>
+        <v>5.101406676676977</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8276134115311</v>
+        <v>11.74611463710226</v>
       </c>
       <c r="G5" t="n">
-        <v>12.84499749776546</v>
+        <v>11.75664706341954</v>
       </c>
       <c r="H5" t="n">
-        <v>12.86276570129292</v>
+        <v>11.7714352319618</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>107.7277405820598</v>
+        <v>6.084879405439972</v>
       </c>
       <c r="G6" t="n">
-        <v>108.9682307298962</v>
+        <v>100.9980246532898</v>
       </c>
       <c r="H6" t="n">
-        <v>109.6705284099435</v>
+        <v>110.0942012336522</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.005718780777642</v>
+        <v>7.735714212462462</v>
       </c>
       <c r="G7" t="n">
-        <v>10.30846893907205</v>
+        <v>8.788540746328469</v>
       </c>
       <c r="H7" t="n">
-        <v>11.38814600928627</v>
+        <v>9.329391009975955</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.52</v>
+        <v>6.714062243243538</v>
       </c>
       <c r="G8" t="n">
-        <v>7.404563882669381</v>
+        <v>7.470257947596752</v>
       </c>
       <c r="H8" t="n">
-        <v>8.296343987450658</v>
+        <v>8.404015125257589</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.85783834383356</v>
+        <v>4.222689522318817</v>
       </c>
       <c r="G9" t="n">
-        <v>5.300256993600946</v>
+        <v>5.188554192865136</v>
       </c>
       <c r="H9" t="n">
-        <v>5.990656666280034</v>
+        <v>5.972897661585301</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.922594387826002</v>
+        <v>5.081550239256321</v>
       </c>
       <c r="G10" t="n">
-        <v>5.177121624670015</v>
+        <v>5.431360314061422</v>
       </c>
       <c r="H10" t="n">
-        <v>5.721012325398857</v>
+        <v>5.981528502152191</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.437029040330454</v>
+        <v>10.2583709114474</v>
       </c>
       <c r="G11" t="n">
-        <v>9.71235377189215</v>
+        <v>10.42652374302666</v>
       </c>
       <c r="H11" t="n">
-        <v>10.06859900854597</v>
+        <v>10.61119334527235</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.329491619622479</v>
+        <v>2.796325003762721</v>
       </c>
       <c r="G12" t="n">
-        <v>4.25539817496866</v>
+        <v>5.221056892276668</v>
       </c>
       <c r="H12" t="n">
-        <v>7.05928996214752</v>
+        <v>7.378180550910325</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.074027516363095</v>
+        <v>7.097135661894368</v>
       </c>
       <c r="G13" t="n">
-        <v>5.095582724125313</v>
+        <v>7.174286831041369</v>
       </c>
       <c r="H13" t="n">
-        <v>5.118602561655213</v>
+        <v>7.277034337250829</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.22503199170241</v>
+        <v>10.31221565761658</v>
       </c>
       <c r="G14" t="n">
-        <v>10.78225780060895</v>
+        <v>10.8687881814096</v>
       </c>
       <c r="H14" t="n">
-        <v>11.01601843328336</v>
+        <v>11.12977101809581</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.457051701975837</v>
+        <v>4.784552657958819</v>
       </c>
       <c r="G15" t="n">
-        <v>4.867559780779048</v>
+        <v>5.389648574690169</v>
       </c>
       <c r="H15" t="n">
-        <v>5.436740957792837</v>
+        <v>6.035700896938059</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.41110142308735</v>
+        <v>6.881352415904541</v>
       </c>
       <c r="G16" t="n">
-        <v>7.192456664409596</v>
+        <v>7.760073567057695</v>
       </c>
       <c r="H16" t="n">
-        <v>8.0867405977926</v>
+        <v>8.230579627560878</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.423136341721245</v>
+        <v>2.350986500807899</v>
       </c>
       <c r="G17" t="n">
-        <v>4.796402808879628</v>
+        <v>4.865574730022947</v>
       </c>
       <c r="H17" t="n">
-        <v>6.188053353408289</v>
+        <v>6.660532358132271</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.154735920516304</v>
+        <v>3.485260267430755</v>
       </c>
       <c r="G18" t="n">
-        <v>3.640275809376669</v>
+        <v>3.663141904210949</v>
       </c>
       <c r="H18" t="n">
-        <v>3.933824879227053</v>
+        <v>3.91325129681344</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.022659638530344</v>
+        <v>2.576784425619431</v>
       </c>
       <c r="G19" t="n">
-        <v>2.271372700422416</v>
+        <v>2.75356247792186</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6324978080326</v>
+        <v>3.171716332378224</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.652335802755899</v>
+        <v>5.397957634625131</v>
       </c>
       <c r="G20" t="n">
-        <v>5.238267839994538</v>
+        <v>5.760261937992381</v>
       </c>
       <c r="H20" t="n">
-        <v>5.932712406630359</v>
+        <v>6.124418628794484</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.7965938962764</v>
+        <v>128.5613582564121</v>
       </c>
       <c r="G21" t="n">
-        <v>129.4711211537139</v>
+        <v>129.0622637788122</v>
       </c>
       <c r="H21" t="n">
-        <v>131.0517741041349</v>
+        <v>129.7913342861734</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E2" t="n">
+        <v>10046</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10045</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10044</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5184636267091</v>
+        <v>102.5086897627344</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843151862464183</v>
+        <v>1.843163922691482</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4958357216216</v>
+        <v>102.4877289231725</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02262790508752608</v>
+        <v>-0.02096083956184495</v>
       </c>
       <c r="T2" t="n">
-        <v>18.07277041387713</v>
+        <v>18.08135116756673</v>
       </c>
       <c r="U2" t="n">
-        <v>36.2083696291042</v>
+        <v>36.22277827955663</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1381071439858041</v>
+        <v>0.1381369499183128</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7223812603346198</v>
+        <v>-0.7217534265063714</v>
       </c>
       <c r="X2" t="n">
-        <v>0.138106729898692</v>
+        <v>0.1381361643952786</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.084879405439972</v>
+        <v>3.195998523304893</v>
       </c>
       <c r="Z2" t="n">
-        <v>100.9980246532898</v>
+        <v>72.69806339079817</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.0942012336522</v>
+        <v>108.992440932082</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E3" t="n">
+        <v>14640</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14639</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14638</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.905727831670993</v>
+        <v>4.905539586037297</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.963631550123377</v>
+        <v>4.963439030684142</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05790371845238466</v>
+        <v>0.05789944464684475</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343702751855295</v>
+        <v>1.343630986772322</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71831762165666</v>
+        <v>1.718249030208196</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7814879917374702</v>
+        <v>0.7815073879384358</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5700205769558857</v>
+        <v>0.5700580117739327</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804323422069606</v>
+        <v>0.780451817860539</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.576784425619431</v>
+        <v>2.575683115949291</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.75356247792186</v>
+        <v>2.815523310390457</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.171716332378224</v>
+        <v>3.292699895423228</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E4" t="n">
+        <v>10274</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10273</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10272</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.902919343847352</v>
+        <v>6.902618027839969</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.233360362166946</v>
+        <v>7.233045342052499</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3304410183195957</v>
+        <v>0.3304273142125294</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291708130655043</v>
+        <v>1.291606556613961</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681293121005618</v>
+        <v>1.681215570776326</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679005169595447</v>
+        <v>0.8679117792427328</v>
       </c>
       <c r="W4" t="n">
-        <v>0.737947874013682</v>
+        <v>0.7379691956016246</v>
       </c>
       <c r="X4" t="n">
-        <v>0.847172276780244</v>
+        <v>0.847183559040825</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.485260267430755</v>
+        <v>3.373944911792491</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.663141904210948</v>
+        <v>3.628758448229059</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.91325129681344</v>
+        <v>3.796535433070864</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301788018998815</v>
+        <v>9.301754232493224</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3693265935763317</v>
+        <v>0.3692928070707411</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247528190403433</v>
+        <v>1.247540474477104</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74708608498406</v>
+        <v>1.747098455558361</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661227675082804</v>
+        <v>0.8661217731686136</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215320043496115</v>
+        <v>0.7215280608447596</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597267686048375</v>
+        <v>0.8597277214641974</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.397957634625131</v>
+        <v>5.410453097829273</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.760261937992381</v>
+        <v>5.627783393855916</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.124418628794484</v>
+        <v>6.07576594628576</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E6" t="n">
+        <v>8887</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8886</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8885</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734615531795161</v>
+        <v>6.734550866531622</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023320467023683</v>
+        <v>7.023238040698858</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887049352285225</v>
+        <v>0.288687174167235</v>
       </c>
       <c r="T6" t="n">
-        <v>1.478187976844278</v>
+        <v>1.478081114748293</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906957545441712</v>
+        <v>1.906826174560106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039948069548916</v>
+        <v>0.3040120897716512</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979951007380882</v>
+        <v>-0.1979501965356598</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790073830336446</v>
+        <v>0.2790202224930473</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.881352415904541</v>
+        <v>6.984640806073701</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.760073567057695</v>
+        <v>7.890827296970116</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.230579627560878</v>
+        <v>8.232811099011345</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E7" t="n">
+        <v>14248</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14247</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14246</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.580172574757827</v>
+        <v>5.58008394749772</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566657837623135</v>
+        <v>5.566549844477544</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01351473713469113</v>
+        <v>-0.01353410302017514</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166061947964387</v>
+        <v>1.166044389907948</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509408788093766</v>
+        <v>1.509375511947841</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049119592341417</v>
+        <v>0.5049274605398346</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05320593530802298</v>
+        <v>0.05322525290621205</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5027709990020339</v>
+        <v>0.5027874510717738</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.098115173003299</v>
+        <v>5.093324887556476</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.353276272731931</v>
+        <v>5.419779648273668</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.809628378908342</v>
+        <v>5.825990222150717</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E8" t="n">
+        <v>9046</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9045</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9044</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.872586245024325</v>
+        <v>7.872324212271973</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.645365329512894</v>
+        <v>0.6453758052970652</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.112764326936837</v>
+        <v>8.112529487301757</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2401780819125101</v>
+        <v>0.2402052750297819</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445777228634437</v>
+        <v>1.445658463217855</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825384538024951</v>
+        <v>1.825290874928292</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077432681995783</v>
+        <v>0.8077537444191355</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273430717512127</v>
+        <v>0.6273659955300204</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797532410781701</v>
+        <v>0.7975367868479017</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.081550239256321</v>
+        <v>5.083129417435471</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.431360314061421</v>
+        <v>5.514422163825038</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.981528502152191</v>
+        <v>6.000375894910294</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E9" t="n">
+        <v>13911</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13910</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13909</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.60883870156014</v>
+        <v>7.608646477354421</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.654453705115104</v>
+        <v>7.654258202361451</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04561500355496394</v>
+        <v>0.04561172500702868</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49338114182788</v>
+        <v>1.493316307463918</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941463465217138</v>
+        <v>1.941374617075847</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566641977288195</v>
+        <v>0.7566850542546987</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5248905241227972</v>
+        <v>0.5249306308246202</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552428132713578</v>
+        <v>0.7552636932841756</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.784552657958819</v>
+        <v>4.562579895711838</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.389648574690169</v>
+        <v>5.267595033141085</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.035700896938059</v>
+        <v>5.875887190372271</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61494844283996</v>
+        <v>10.61480772721761</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3098867623475863</v>
+        <v>0.3097460467252384</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053436694227355</v>
+        <v>2.053514516487536</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699183528451742</v>
+        <v>2.699262425655478</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570197199458106</v>
+        <v>0.3570134680155506</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1213401242273839</v>
+        <v>-0.1214056787866098</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3369168649342661</v>
+        <v>0.336928407514531</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.31221565761658</v>
+        <v>10.14634416873292</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.8687881814096</v>
+        <v>10.82801862134508</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12977101809581</v>
+        <v>11.12988560101565</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E11" t="n">
+        <v>13852</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13851</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13850</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242321444043322</v>
+        <v>5.242202512453975</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215898609476869</v>
+        <v>5.215818322088285</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02642283456645324</v>
+        <v>-0.02638419036568983</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160979437247967</v>
+        <v>1.161002840447008</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48244874999797</v>
+        <v>1.482449521917145</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294782350164643</v>
+        <v>0.4294793822666691</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09189529448819411</v>
+        <v>-0.09186898492889228</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276711210441666</v>
+        <v>0.4276705934410079</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.169449702551851</v>
+        <v>4.351018864063778</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.739725518451614</v>
+        <v>4.697221600823958</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.101406676676977</v>
+        <v>5.068312135099768</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E12" t="n">
+        <v>4170</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4169</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4168</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.459238483685221</v>
+        <v>7.458591628687935</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.633602274665503</v>
+        <v>7.632626690774893</v>
       </c>
       <c r="R12" t="n">
-        <v>16.74825286532928</v>
+        <v>16.71954688618462</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1743637909802826</v>
+        <v>0.1740350620869572</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9118295262480964</v>
+        <v>0.9116687038648507</v>
       </c>
       <c r="U12" t="n">
-        <v>1.192945357315236</v>
+        <v>1.192581339994439</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8328554502524977</v>
+        <v>0.8329935528828176</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6613311140909686</v>
+        <v>0.6615970414522849</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8310010057097683</v>
+        <v>0.8311493363854973</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.222689522318817</v>
+        <v>4.275378762835659</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.188554192865136</v>
+        <v>5.303194217891669</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.972897661585301</v>
+        <v>5.711220596898687</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E13" t="n">
+        <v>6505</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6504</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6503</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.59795517453483</v>
+        <v>9.597548816113161</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02267353686519</v>
+        <v>10.02230484559988</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4247183623303621</v>
+        <v>0.4247560294867179</v>
       </c>
       <c r="T13" t="n">
-        <v>1.690209725468332</v>
+        <v>1.689962504568925</v>
       </c>
       <c r="U13" t="n">
-        <v>2.148402412303055</v>
+        <v>2.148213451306789</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233351514215483</v>
+        <v>0.8233527370110068</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6490206561114238</v>
+        <v>0.6490570918227834</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101519507590041</v>
+        <v>0.8101594189348503</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.714062243243538</v>
+        <v>6.79014828746559</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.470257947596752</v>
+        <v>7.640634818074607</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.404015125257589</v>
+        <v>8.426156169726454</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E14" t="n">
         <v>14091</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14090</v>
+        <v>14091</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.125535841022003</v>
+        <v>8.125369384713649</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.196515398155281</v>
+        <v>8.19626140270657</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07097955713328045</v>
+        <v>0.07089201799292272</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75588420254984</v>
+        <v>1.755761135485836</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281849331733018</v>
+        <v>2.281697537812075</v>
       </c>
       <c r="V14" t="n">
-        <v>0.780865978853185</v>
+        <v>0.7808930495555663</v>
       </c>
       <c r="W14" t="n">
-        <v>0.565462648201543</v>
+        <v>0.5655037804617162</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804781562651737</v>
+        <v>0.7805070208931474</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.097135661894368</v>
+        <v>7.030227343984911</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.174286831041369</v>
+        <v>7.142985321414332</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.277034337250829</v>
+        <v>7.216727718606776</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82012879219055</v>
+        <v>11.82011046450289</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1437585908362349</v>
+        <v>-0.1437769185238974</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052429253974986</v>
+        <v>2.052433414016837</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698000123924439</v>
+        <v>2.698038652756682</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950336976343112</v>
+        <v>0.7950300513034012</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094919184327685</v>
+        <v>0.6094807650398075</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865342834116523</v>
+        <v>0.7865344333560893</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.735714212462462</v>
+        <v>7.937573252745636</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.788540746328469</v>
+        <v>8.951413783045769</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.329391009975955</v>
+        <v>9.350377006687815</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E16" t="n">
+        <v>9855</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9854</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9853</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360735715010657</v>
+        <v>8.360564136391314</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622658279170189</v>
+        <v>8.622580144662289</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2619225641595323</v>
+        <v>0.2620160082709749</v>
       </c>
       <c r="T16" t="n">
-        <v>3.597401462170467</v>
+        <v>3.597776445842202</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08431937375612</v>
+        <v>11.08391264922742</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04131859380535303</v>
+        <v>0.04129533138489254</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6106158074844188</v>
+        <v>-0.6106549381764756</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02465880428052913</v>
+        <v>0.0246355709800693</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.74611463710226</v>
+        <v>11.70398550430534</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.75664706341954</v>
+        <v>11.75594914413503</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.7714352319618</v>
+        <v>11.80598106826156</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E17" t="n">
+        <v>2399</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2398</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2397</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.468116395494368</v>
+        <v>6.466620100083402</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.832469573841053</v>
+        <v>6.831509189695512</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3643531783466843</v>
+        <v>0.3648890896121103</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007337608381943</v>
+        <v>2.008198714426105</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545594698074465</v>
+        <v>2.546500177214118</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5386467493794241</v>
+        <v>0.5384747492989371</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0560621100040769</v>
+        <v>0.05573487178878789</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5352160115133131</v>
+        <v>0.5350339654275511</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.796325003762721</v>
+        <v>2.415091642044829</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.221056892276668</v>
+        <v>3.760603507153424</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.378180550910325</v>
+        <v>6.268754501328679</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E18" t="n">
+        <v>3258</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3257</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3256</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.465524877149877</v>
+        <v>6.464694197113908</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.662077033936975</v>
+        <v>6.66143026083748</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1965521567870986</v>
+        <v>0.1967360637235711</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094282493177828</v>
+        <v>1.094745962921072</v>
       </c>
       <c r="U18" t="n">
-        <v>1.482964319254482</v>
+        <v>1.483369119684093</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6086027727445059</v>
+        <v>0.6085398845975843</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2325860339545245</v>
+        <v>0.2325330829892854</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6055119864602612</v>
+        <v>0.6054349837338986</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.350986500807899</v>
+        <v>2.180169919841252</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.865574730022947</v>
+        <v>3.854104688512279</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.660532358132271</v>
+        <v>6.744077538879209</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E19" t="n">
+        <v>7212</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7211</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7210</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31253765603329</v>
+        <v>10.31146186381917</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.11076403727022</v>
+        <v>11.1100087757747</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7982263812369342</v>
+        <v>0.7985469119555323</v>
       </c>
       <c r="T19" t="n">
-        <v>2.062675005785243</v>
+        <v>2.063370473205482</v>
       </c>
       <c r="U19" t="n">
-        <v>2.788014019829423</v>
+        <v>2.788902338009248</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7278922526780486</v>
+        <v>0.7278248705702448</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4724934587423321</v>
+        <v>0.4723828663029549</v>
       </c>
       <c r="X19" t="n">
-        <v>0.678187502038692</v>
+        <v>0.6780814911626232</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.86690262910068</v>
+        <v>8.545750961362389</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.155721093673058</v>
+        <v>9.05615338103391</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.342323839974595</v>
+        <v>9.312278226862441</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E20" t="n">
+        <v>10662</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10661</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10660</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85455531962578</v>
+        <v>13.85423995940445</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490716332378224</v>
+        <v>7.490787401574804</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23113414722645</v>
+        <v>14.23078985204206</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3765788276006634</v>
+        <v>0.3765498926376142</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25490456743891</v>
+        <v>1.25479661207881</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646633466959064</v>
+        <v>1.646554729413534</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935878675449844</v>
+        <v>0.8935976062243716</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790762586206252</v>
+        <v>0.7790957472698938</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888752778291637</v>
+        <v>0.8887636494205045</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.2583709114474</v>
+        <v>10.19172798884501</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.42652374302666</v>
+        <v>10.39092754957436</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.61119334527235</v>
+        <v>10.50065941318999</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="E21" t="n">
+        <v>10258</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10257</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10256</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8668302457098</v>
+        <v>130.8667067368627</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9714839833445</v>
+        <v>130.9713009783523</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046537376347076</v>
+        <v>0.1045942414896884</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971536587135867</v>
+        <v>0.7971508316704989</v>
       </c>
       <c r="U21" t="n">
-        <v>1.04576998869083</v>
+        <v>1.045724056501088</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651190378987902</v>
+        <v>0.865123613207081</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311895764873657</v>
+        <v>0.7311973192258173</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643649301797645</v>
+        <v>0.8643713027674768</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5613582564121</v>
+        <v>128.8056198459666</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.0622637788122</v>
+        <v>129.1213968814506</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.7913342861734</v>
+        <v>129.4966889279661</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.86690262910068</v>
+        <v>8.545750961362389</v>
       </c>
       <c r="G2" t="n">
-        <v>9.155721093673058</v>
+        <v>9.05615338103391</v>
       </c>
       <c r="H2" t="n">
-        <v>9.342323839974595</v>
+        <v>9.312278226862441</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.098115173003299</v>
+        <v>5.093324887556476</v>
       </c>
       <c r="G3" t="n">
-        <v>5.35327627273193</v>
+        <v>5.419779648273669</v>
       </c>
       <c r="H3" t="n">
-        <v>5.809628378908342</v>
+        <v>5.825990222150717</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.169449702551851</v>
+        <v>4.351018864063778</v>
       </c>
       <c r="G4" t="n">
-        <v>4.739725518451614</v>
+        <v>4.697221600823958</v>
       </c>
       <c r="H4" t="n">
-        <v>5.101406676676977</v>
+        <v>5.068312135099768</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.74611463710226</v>
+        <v>11.70398550430534</v>
       </c>
       <c r="G5" t="n">
-        <v>11.75664706341954</v>
+        <v>11.75594914413503</v>
       </c>
       <c r="H5" t="n">
-        <v>11.7714352319618</v>
+        <v>11.80598106826156</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.084879405439972</v>
+        <v>3.195998523304893</v>
       </c>
       <c r="G6" t="n">
-        <v>100.9980246532898</v>
+        <v>72.69806339079815</v>
       </c>
       <c r="H6" t="n">
-        <v>110.0942012336522</v>
+        <v>108.992440932082</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.735714212462462</v>
+        <v>7.937573252745636</v>
       </c>
       <c r="G7" t="n">
-        <v>8.788540746328469</v>
+        <v>8.951413783045769</v>
       </c>
       <c r="H7" t="n">
-        <v>9.329391009975955</v>
+        <v>9.350377006687815</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.714062243243538</v>
+        <v>6.79014828746559</v>
       </c>
       <c r="G8" t="n">
-        <v>7.470257947596752</v>
+        <v>7.640634818074607</v>
       </c>
       <c r="H8" t="n">
-        <v>8.404015125257589</v>
+        <v>8.426156169726454</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.222689522318817</v>
+        <v>4.275378762835659</v>
       </c>
       <c r="G9" t="n">
-        <v>5.188554192865136</v>
+        <v>5.303194217891669</v>
       </c>
       <c r="H9" t="n">
-        <v>5.972897661585301</v>
+        <v>5.711220596898687</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.081550239256321</v>
+        <v>5.083129417435471</v>
       </c>
       <c r="G10" t="n">
-        <v>5.431360314061422</v>
+        <v>5.514422163825038</v>
       </c>
       <c r="H10" t="n">
-        <v>5.981528502152191</v>
+        <v>6.000375894910294</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2583709114474</v>
+        <v>10.19172798884501</v>
       </c>
       <c r="G11" t="n">
-        <v>10.42652374302666</v>
+        <v>10.39092754957436</v>
       </c>
       <c r="H11" t="n">
-        <v>10.61119334527235</v>
+        <v>10.50065941318999</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.796325003762721</v>
+        <v>2.415091642044829</v>
       </c>
       <c r="G12" t="n">
-        <v>5.221056892276668</v>
+        <v>3.760603507153423</v>
       </c>
       <c r="H12" t="n">
-        <v>7.378180550910325</v>
+        <v>6.268754501328679</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>7.097135661894368</v>
+        <v>7.030227343984911</v>
       </c>
       <c r="G13" t="n">
-        <v>7.174286831041369</v>
+        <v>7.142985321414332</v>
       </c>
       <c r="H13" t="n">
-        <v>7.277034337250829</v>
+        <v>7.216727718606776</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.31221565761658</v>
+        <v>10.14634416873292</v>
       </c>
       <c r="G14" t="n">
-        <v>10.8687881814096</v>
+        <v>10.82801862134508</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12977101809581</v>
+        <v>11.12988560101565</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.784552657958819</v>
+        <v>4.562579895711838</v>
       </c>
       <c r="G15" t="n">
-        <v>5.389648574690169</v>
+        <v>5.267595033141085</v>
       </c>
       <c r="H15" t="n">
-        <v>6.035700896938059</v>
+        <v>5.875887190372271</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.881352415904541</v>
+        <v>6.984640806073701</v>
       </c>
       <c r="G16" t="n">
-        <v>7.760073567057695</v>
+        <v>7.890827296970116</v>
       </c>
       <c r="H16" t="n">
-        <v>8.230579627560878</v>
+        <v>8.232811099011345</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.350986500807899</v>
+        <v>2.180169919841252</v>
       </c>
       <c r="G17" t="n">
-        <v>4.865574730022947</v>
+        <v>3.854104688512279</v>
       </c>
       <c r="H17" t="n">
-        <v>6.660532358132271</v>
+        <v>6.744077538879209</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.485260267430755</v>
+        <v>3.373944911792491</v>
       </c>
       <c r="G18" t="n">
-        <v>3.663141904210949</v>
+        <v>3.628758448229059</v>
       </c>
       <c r="H18" t="n">
-        <v>3.91325129681344</v>
+        <v>3.796535433070864</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.576784425619431</v>
+        <v>2.575683115949291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.75356247792186</v>
+        <v>2.815523310390457</v>
       </c>
       <c r="H19" t="n">
-        <v>3.171716332378224</v>
+        <v>3.292699895423228</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.397957634625131</v>
+        <v>5.410453097829273</v>
       </c>
       <c r="G20" t="n">
-        <v>5.760261937992381</v>
+        <v>5.627783393855916</v>
       </c>
       <c r="H20" t="n">
-        <v>6.124418628794484</v>
+        <v>6.07576594628576</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5613582564121</v>
+        <v>128.8056198459666</v>
       </c>
       <c r="G21" t="n">
-        <v>129.0622637788122</v>
+        <v>129.1213968814506</v>
       </c>
       <c r="H21" t="n">
-        <v>129.7913342861734</v>
+        <v>129.4966889279661</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E2" t="n">
         <v>10046</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10045</v>
+        <v>10046</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5086897627344</v>
+        <v>102.5302437454377</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843163922691482</v>
+        <v>1.843147353361946</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4877289231725</v>
+        <v>102.5279418538394</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02096083956184495</v>
+        <v>-0.002301891598228207</v>
       </c>
       <c r="T2" t="n">
-        <v>18.08135116756673</v>
+        <v>18.04045081370553</v>
       </c>
       <c r="U2" t="n">
-        <v>36.22277827955663</v>
+        <v>36.12091634500973</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1381369499183128</v>
+        <v>0.1376368459734925</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7217534265063714</v>
+        <v>-0.720185865923368</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1381361643952786</v>
+        <v>0.1376328151260168</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.195998523304893</v>
+        <v>2.585419168770938</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.69806339079817</v>
+        <v>74.5449265835996</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.992440932082</v>
+        <v>110.341220699893</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E3" t="n">
+        <v>14641</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14640</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14639</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.905539586037297</v>
+        <v>4.905347267759563</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.963439030684142</v>
+        <v>4.963245032945393</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05789944464684475</v>
+        <v>0.05789776518583014</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343630986772322</v>
+        <v>1.343558355364578</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718249030208196</v>
+        <v>1.718180915604651</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7815073879384358</v>
+        <v>0.781527211460189</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5700580117739327</v>
+        <v>0.5700966305038722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.780451817860539</v>
+        <v>0.7804716108815057</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.575683115949291</v>
+        <v>2.573326374242042</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.815523310390457</v>
+        <v>2.886788808270394</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.292699895423228</v>
+        <v>3.326487487383361</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E4" t="n">
+        <v>10275</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10274</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10273</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.902618027839969</v>
+        <v>6.902303630523651</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.233045342052499</v>
+        <v>7.232716587554074</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3304273142125294</v>
+        <v>0.3304129570304223</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291606556613961</v>
+        <v>1.291488066075953</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681215570776326</v>
+        <v>1.681130939773266</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679117792427328</v>
+        <v>0.8679253310644821</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379691956016246</v>
+        <v>0.7379947383857806</v>
       </c>
       <c r="X4" t="n">
-        <v>0.847183559040825</v>
+        <v>0.8471973696406691</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.373944911792491</v>
+        <v>3.33911212446352</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.628758448229059</v>
+        <v>3.577443109924309</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.796535433070864</v>
+        <v>3.7183331698323</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301754232493224</v>
+        <v>9.301728504086201</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692928070707411</v>
+        <v>0.3692670786637192</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247540474477104</v>
+        <v>1.247545987338174</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747098455558361</v>
+        <v>1.747104865882296</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661217731686136</v>
+        <v>0.8661216756361599</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215280608447596</v>
+        <v>0.7215260173438842</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597277214641974</v>
+        <v>0.8597291400377416</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.410453097829273</v>
+        <v>5.45150823438498</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.627783393855916</v>
+        <v>5.685989901866385</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.07576594628576</v>
+        <v>6.695230097418081</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E6" t="n">
+        <v>8888</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8887</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8886</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734550866531622</v>
+        <v>6.734484527962192</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023238040698858</v>
+        <v>7.02317153053012</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.288687174167235</v>
+        <v>0.2886870025679282</v>
       </c>
       <c r="T6" t="n">
-        <v>1.478081114748293</v>
+        <v>1.477992206317002</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906826174560106</v>
+        <v>1.906703564389273</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040120897716512</v>
+        <v>0.3040217397032574</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979501965356598</v>
+        <v>-0.1979155035655085</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790202224930473</v>
+        <v>0.2790241525083796</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.984640806073701</v>
+        <v>7.290616713897065</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.890827296970116</v>
+        <v>8.003115114041904</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.232811099011345</v>
+        <v>8.221156364231579</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E7" t="n">
+        <v>14249</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14248</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14247</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.58008394749772</v>
+        <v>5.579977610892757</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566549844477544</v>
+        <v>5.56642298441991</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01353410302017514</v>
+        <v>-0.01355462647284616</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166044389907948</v>
+        <v>1.166058182376961</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509375511947841</v>
+        <v>1.50936200259793</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049274605398346</v>
+        <v>0.5049418428310046</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05322525290621205</v>
+        <v>0.05323913621601783</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5027874510717738</v>
+        <v>0.5028031264081033</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.093324887556476</v>
+        <v>5.098422601018568</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.419779648273668</v>
+        <v>5.492199052245812</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.825990222150717</v>
+        <v>5.825078793630611</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E8" t="n">
+        <v>9047</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9046</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9045</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.872324212271973</v>
+        <v>7.872056986513376</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6453758052970652</v>
+        <v>0.6453862660944206</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.112529487301757</v>
+        <v>8.112278712645585</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2402052750297819</v>
+        <v>0.240221726132208</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445658463217855</v>
+        <v>1.445538145086972</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825290874928292</v>
+        <v>1.825195335784755</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077537444191355</v>
+        <v>0.8077654089074733</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273659955300204</v>
+        <v>0.6273907303844857</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975367868479017</v>
+        <v>0.7975435263599649</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.083129417435471</v>
+        <v>5.084734888782486</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.514422163825038</v>
+        <v>5.604381395449226</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.000375894910294</v>
+        <v>6.001899220152391</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E9" t="n">
+        <v>13912</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13911</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13910</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.608646477354421</v>
+        <v>7.608451944504348</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.654258202361451</v>
+        <v>7.654077400377894</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04561172500702868</v>
+        <v>0.045625455873545</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493316307463918</v>
+        <v>1.493251245368728</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941374617075847</v>
+        <v>1.941303941942513</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7566850542546987</v>
+        <v>0.7567001298825533</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5249306308246202</v>
+        <v>0.5249625908577142</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552636932841756</v>
+        <v>0.7552779732925767</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.562579895711838</v>
+        <v>4.598759566191917</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.267595033141085</v>
+        <v>5.39427598617887</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.875887190372271</v>
+        <v>5.874442448084333</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61480772721761</v>
+        <v>10.61466111565932</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3097460467252384</v>
+        <v>0.3095994351669482</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053514516487536</v>
+        <v>2.05358577414138</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699262425655478</v>
+        <v>2.699334080163974</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570134680155506</v>
+        <v>0.3570095667556469</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1214056787866098</v>
+        <v>-0.1214652171542077</v>
       </c>
       <c r="X10" t="n">
-        <v>0.336928407514531</v>
+        <v>0.3369418713741286</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.14634416873292</v>
+        <v>10.26077299804446</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.82801862134508</v>
+        <v>10.77352954144602</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12988560101565</v>
+        <v>11.12994945046327</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E11" t="n">
+        <v>13853</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13852</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13851</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242202512453975</v>
+        <v>5.242116445278659</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215818322088285</v>
+        <v>5.215754998615396</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02638419036568983</v>
+        <v>-0.02636144666326386</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161002840447008</v>
+        <v>1.16098486428458</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482449521917145</v>
+        <v>1.482416478825449</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294793822666691</v>
+        <v>0.4294857929005313</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09186898492889228</v>
+        <v>-0.09184347511311808</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276705934410079</v>
+        <v>0.4276760682882861</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.351018864063778</v>
+        <v>4.348151241485249</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.697221600823958</v>
+        <v>4.667241232134576</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.068312135099768</v>
+        <v>4.954886118178034</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E12" t="n">
+        <v>4171</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4170</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4169</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.458591628687935</v>
+        <v>7.457922302158273</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.632626690774893</v>
+        <v>7.631555473381896</v>
       </c>
       <c r="R12" t="n">
-        <v>16.71954688618462</v>
+        <v>16.69088197424879</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1740350620869572</v>
+        <v>0.1736331712236224</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9116687038648507</v>
+        <v>0.9115686171312586</v>
       </c>
       <c r="U12" t="n">
-        <v>1.192581339994439</v>
+        <v>1.192358793810632</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8329935528828176</v>
+        <v>0.8331018295485469</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6615970414522849</v>
+        <v>0.6617924617177687</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8311493363854973</v>
+        <v>0.8312722420984352</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.275378762835659</v>
+        <v>4.639355140289004</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.303194217891669</v>
+        <v>5.301945373197839</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.711220596898687</v>
+        <v>5.616012846870846</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E13" t="n">
+        <v>6506</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6505</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6504</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.597548816113161</v>
+        <v>9.597138739431207</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02230484559988</v>
+        <v>10.02192990325002</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4247560294867179</v>
+        <v>0.4247911638188169</v>
       </c>
       <c r="T13" t="n">
-        <v>1.689962504568925</v>
+        <v>1.68969270823706</v>
       </c>
       <c r="U13" t="n">
-        <v>2.148213451306789</v>
+        <v>2.148014749230183</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233527370110068</v>
+        <v>0.8233723746157392</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6490570918227834</v>
+        <v>0.6490972535111372</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101594189348503</v>
+        <v>0.8101692378699862</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.79014828746559</v>
+        <v>6.888326850498283</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.640634818074607</v>
+        <v>7.799326393265238</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.426156169726454</v>
+        <v>8.419340893401074</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E14" t="n">
-        <v>14091</v>
+        <v>14093</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14091</v>
+        <v>14092</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.125369384713649</v>
+        <v>8.125201355378939</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.19626140270657</v>
+        <v>8.196202645131915</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07089201799292272</v>
+        <v>0.07100128975297619</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755761135485836</v>
+        <v>1.755635815746599</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281697537812075</v>
+        <v>2.281513749573867</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808930495555663</v>
+        <v>0.7809120590919048</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5655037804617162</v>
+        <v>0.5655573699564744</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805070208931474</v>
+        <v>0.7805236396317294</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.030227343984911</v>
+        <v>7.011732001226994</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.142985321414332</v>
+        <v>7.112647496878097</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.216727718606776</v>
+        <v>7.165519301347135</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82011046450289</v>
+        <v>11.82006533726962</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1437769185238974</v>
+        <v>-0.1438220457571682</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052433414016837</v>
+        <v>2.052440000014556</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698038652756682</v>
+        <v>2.698079673053898</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950300513034012</v>
+        <v>0.7950271904345805</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094807650398075</v>
+        <v>0.6094688902382019</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865344333560893</v>
+        <v>0.7865368769974287</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.937573252745636</v>
+        <v>8.064855055457832</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.951413783045769</v>
+        <v>9.095457400814064</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.350377006687815</v>
+        <v>9.364591893180734</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E16" t="n">
+        <v>9856</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9855</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9854</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360564136391314</v>
+        <v>8.360379401319127</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622580144662289</v>
+        <v>8.622503368212158</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2620160082709749</v>
+        <v>0.2621239668930304</v>
       </c>
       <c r="T16" t="n">
-        <v>3.597776445842202</v>
+        <v>3.598148026369913</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08391264922742</v>
+        <v>11.08350891850575</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04129533138489254</v>
+        <v>0.04127190321119755</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6106549381764756</v>
+        <v>-0.6106939422512674</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0246355709800693</v>
+        <v>0.02461205937865762</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.70398550430534</v>
+        <v>11.64448805938433</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.75594914413503</v>
+        <v>11.73580155058682</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.80598106826156</v>
+        <v>11.76908688583976</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2399</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2398</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.466620100083402</v>
+        <v>6.465070862859524</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.831509189695512</v>
+        <v>6.830263788315987</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3648890896121103</v>
+        <v>0.3651929254564617</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008198714426105</v>
+        <v>2.008914805789721</v>
       </c>
       <c r="U17" t="n">
-        <v>2.546500177214118</v>
+        <v>2.547154830418226</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5384747492989371</v>
+        <v>0.5384106994723721</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05573487178878789</v>
+        <v>0.05564711676675416</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5350339654275511</v>
+        <v>0.5349633336211252</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.415091642044829</v>
+        <v>2.401702087660528</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.760603507153424</v>
+        <v>3.466448024664304</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.268754501328679</v>
+        <v>4.929032997825428</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E18" t="n">
+        <v>3259</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3258</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3257</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.464694197113908</v>
+        <v>6.46379650092081</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66143026083748</v>
+        <v>6.660538117873354</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1967360637235711</v>
+        <v>0.1967416169525434</v>
       </c>
       <c r="T18" t="n">
-        <v>1.094745962921072</v>
+        <v>1.095168199514378</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483369119684093</v>
+        <v>1.483676255277605</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6085398845975843</v>
+        <v>0.6085963316141881</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2325330829892854</v>
+        <v>0.2326821659348195</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6054349837338986</v>
+        <v>0.6054859548879311</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.180169919841252</v>
+        <v>2.135342360431581</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.854104688512279</v>
+        <v>3.688029087109818</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.744077538879209</v>
+        <v>6.794720912609442</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E19" t="n">
+        <v>7213</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7212</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7211</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31146186381917</v>
+        <v>10.31034823904603</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1100087757747</v>
+        <v>11.1092550259828</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7985469119555323</v>
+        <v>0.7989067869367645</v>
       </c>
       <c r="T19" t="n">
-        <v>2.063370473205482</v>
+        <v>2.064089883106337</v>
       </c>
       <c r="U19" t="n">
-        <v>2.788902338009248</v>
+        <v>2.78989055025359</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7278248705702448</v>
+        <v>0.7277469434995637</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4723828663029549</v>
+        <v>0.4722558619615168</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6780814911626232</v>
+        <v>0.6779576581150504</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.545750961362389</v>
+        <v>8.503817163521736</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.05615338103391</v>
+        <v>8.96339011252941</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.312278226862441</v>
+        <v>9.31245705889282</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E20" t="n">
+        <v>10663</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10662</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10661</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85423995940445</v>
+        <v>13.85391340341501</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490787401574804</v>
+        <v>7.490858369098713</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23078985204206</v>
+        <v>14.23043441722587</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3765498926376142</v>
+        <v>0.3765210138108603</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25479661207881</v>
+        <v>1.254675364369952</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646554729413534</v>
+        <v>1.646471867658645</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8935976062243716</v>
+        <v>0.8936086292472429</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7790957472698938</v>
+        <v>0.7791177246010356</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887636494205045</v>
+        <v>0.8887758352382809</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19172798884501</v>
+        <v>10.17301770309609</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.39092754957436</v>
+        <v>10.35145614719687</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.50065941318999</v>
+        <v>10.45124542460042</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16710</v>
+        <v>16711</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10257</v>
+        <v>10258</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8667067368627</v>
+        <v>130.8665696042114</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9713009783523</v>
+        <v>130.9711459311471</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045942414896884</v>
+        <v>0.1045763269358029</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971508316704989</v>
+        <v>0.7971399837627707</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045724056501088</v>
+        <v>1.045697680661275</v>
       </c>
       <c r="V21" t="n">
-        <v>0.865123613207081</v>
+        <v>0.8651259200091893</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311973192258173</v>
+        <v>0.7311974195053853</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643713027674768</v>
+        <v>0.864375873963146</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.8056198459666</v>
+        <v>128.4900698028289</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1213968814506</v>
+        <v>128.9007597406214</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.4966889279661</v>
+        <v>129.1959705825173</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.545750961362389</v>
+        <v>8.503817163521736</v>
       </c>
       <c r="G2" t="n">
-        <v>9.05615338103391</v>
+        <v>8.963390112529408</v>
       </c>
       <c r="H2" t="n">
-        <v>9.312278226862441</v>
+        <v>9.31245705889282</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.093324887556476</v>
+        <v>5.098422601018568</v>
       </c>
       <c r="G3" t="n">
-        <v>5.419779648273669</v>
+        <v>5.492199052245812</v>
       </c>
       <c r="H3" t="n">
-        <v>5.825990222150717</v>
+        <v>5.825078793630611</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.351018864063778</v>
+        <v>4.348151241485249</v>
       </c>
       <c r="G4" t="n">
-        <v>4.697221600823958</v>
+        <v>4.667241232134575</v>
       </c>
       <c r="H4" t="n">
-        <v>5.068312135099768</v>
+        <v>4.954886118178034</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.70398550430534</v>
+        <v>11.64448805938433</v>
       </c>
       <c r="G5" t="n">
-        <v>11.75594914413503</v>
+        <v>11.73580155058682</v>
       </c>
       <c r="H5" t="n">
-        <v>11.80598106826156</v>
+        <v>11.76908688583976</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.195998523304893</v>
+        <v>2.585419168770938</v>
       </c>
       <c r="G6" t="n">
-        <v>72.69806339079815</v>
+        <v>74.54492658359959</v>
       </c>
       <c r="H6" t="n">
-        <v>108.992440932082</v>
+        <v>110.341220699893</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.937573252745636</v>
+        <v>8.064855055457832</v>
       </c>
       <c r="G7" t="n">
-        <v>8.951413783045769</v>
+        <v>9.095457400814066</v>
       </c>
       <c r="H7" t="n">
-        <v>9.350377006687815</v>
+        <v>9.364591893180734</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.79014828746559</v>
+        <v>6.888326850498283</v>
       </c>
       <c r="G8" t="n">
-        <v>7.640634818074607</v>
+        <v>7.79932639326524</v>
       </c>
       <c r="H8" t="n">
-        <v>8.426156169726454</v>
+        <v>8.419340893401074</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.275378762835659</v>
+        <v>4.639355140289004</v>
       </c>
       <c r="G9" t="n">
-        <v>5.303194217891669</v>
+        <v>5.301945373197838</v>
       </c>
       <c r="H9" t="n">
-        <v>5.711220596898687</v>
+        <v>5.616012846870846</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.083129417435471</v>
+        <v>5.084734888782486</v>
       </c>
       <c r="G10" t="n">
-        <v>5.514422163825038</v>
+        <v>5.604381395449226</v>
       </c>
       <c r="H10" t="n">
-        <v>6.000375894910294</v>
+        <v>6.001899220152391</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19172798884501</v>
+        <v>10.17301770309609</v>
       </c>
       <c r="G11" t="n">
-        <v>10.39092754957436</v>
+        <v>10.35145614719687</v>
       </c>
       <c r="H11" t="n">
-        <v>10.50065941318999</v>
+        <v>10.45124542460042</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.415091642044829</v>
+        <v>2.401702087660528</v>
       </c>
       <c r="G12" t="n">
-        <v>3.760603507153423</v>
+        <v>3.466448024664305</v>
       </c>
       <c r="H12" t="n">
-        <v>6.268754501328679</v>
+        <v>4.929032997825428</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>7.030227343984911</v>
+        <v>7.011732001226994</v>
       </c>
       <c r="G13" t="n">
-        <v>7.142985321414332</v>
+        <v>7.112647496878097</v>
       </c>
       <c r="H13" t="n">
-        <v>7.216727718606776</v>
+        <v>7.165519301347135</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.14634416873292</v>
+        <v>10.26077299804446</v>
       </c>
       <c r="G14" t="n">
-        <v>10.82801862134508</v>
+        <v>10.77352954144602</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12988560101565</v>
+        <v>11.12994945046327</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.562579895711838</v>
+        <v>4.598759566191917</v>
       </c>
       <c r="G15" t="n">
-        <v>5.267595033141085</v>
+        <v>5.39427598617887</v>
       </c>
       <c r="H15" t="n">
-        <v>5.875887190372271</v>
+        <v>5.874442448084333</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.984640806073701</v>
+        <v>7.290616713897065</v>
       </c>
       <c r="G16" t="n">
-        <v>7.890827296970116</v>
+        <v>8.003115114041904</v>
       </c>
       <c r="H16" t="n">
-        <v>8.232811099011345</v>
+        <v>8.221156364231579</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.180169919841252</v>
+        <v>2.135342360431581</v>
       </c>
       <c r="G17" t="n">
-        <v>3.854104688512279</v>
+        <v>3.688029087109818</v>
       </c>
       <c r="H17" t="n">
-        <v>6.744077538879209</v>
+        <v>6.794720912609442</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.373944911792491</v>
+        <v>3.33911212446352</v>
       </c>
       <c r="G18" t="n">
-        <v>3.628758448229059</v>
+        <v>3.577443109924309</v>
       </c>
       <c r="H18" t="n">
-        <v>3.796535433070864</v>
+        <v>3.7183331698323</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.575683115949291</v>
+        <v>2.573326374242042</v>
       </c>
       <c r="G19" t="n">
-        <v>2.815523310390457</v>
+        <v>2.886788808270394</v>
       </c>
       <c r="H19" t="n">
-        <v>3.292699895423228</v>
+        <v>3.326487487383361</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.410453097829273</v>
+        <v>5.45150823438498</v>
       </c>
       <c r="G20" t="n">
-        <v>5.627783393855916</v>
+        <v>5.685989901866385</v>
       </c>
       <c r="H20" t="n">
-        <v>6.07576594628576</v>
+        <v>6.695230097418081</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.8056198459666</v>
+        <v>128.4900698028289</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1213968814506</v>
+        <v>128.9007597406214</v>
       </c>
       <c r="H21" t="n">
-        <v>129.4966889279661</v>
+        <v>129.1959705825173</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E2" t="n">
         <v>10046</v>
@@ -611,40 +611,40 @@
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843147353361946</v>
+        <v>1.8431308077198</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5279418538394</v>
+        <v>102.5271071912615</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002301891598228207</v>
+        <v>-0.003136554176139228</v>
       </c>
       <c r="T2" t="n">
-        <v>18.04045081370553</v>
+        <v>18.03969209014916</v>
       </c>
       <c r="U2" t="n">
-        <v>36.12091634500973</v>
+        <v>36.12050609271207</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1376368459734925</v>
+        <v>0.1376830005416725</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.720185865923368</v>
+        <v>-0.7201467912670381</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1376328151260168</v>
+        <v>0.1376790628996316</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.585419168770938</v>
+        <v>3.212883572694635</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5449265835996</v>
+        <v>68.51293158841899</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.341220699893</v>
+        <v>111.5472681401262</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E3" t="n">
         <v>14641</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14640</v>
+        <v>14641</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.905347267759563</v>
+        <v>4.905153609726112</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.963245032945393</v>
+        <v>4.963041901910242</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05789776518583014</v>
+        <v>0.05788829218413017</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343558355364578</v>
+        <v>1.343513581747181</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718180915604651</v>
+        <v>1.718141067539953</v>
       </c>
       <c r="V3" t="n">
-        <v>0.781527211460189</v>
+        <v>0.7815422751484999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5700966305038722</v>
+        <v>0.5701215805360291</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804716108815057</v>
+        <v>0.7804876609840915</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.573326374242042</v>
+        <v>2.570493403281183</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.886788808270394</v>
+        <v>2.963326832762448</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.326487487383361</v>
+        <v>3.3346075768406</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E4" t="n">
         <v>10275</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10274</v>
+        <v>10275</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.902303630523651</v>
+        <v>6.901982238442821</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.232716587554074</v>
+        <v>7.232325064557133</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3304129570304223</v>
+        <v>0.330342826114312</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291488066075953</v>
+        <v>1.291361499762604</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681130939773266</v>
+        <v>1.681051360407462</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679253310644821</v>
+        <v>0.867939209474755</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7379947383857806</v>
+        <v>0.7380198201321988</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471973696406691</v>
+        <v>0.8472263694347271</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.33911212446352</v>
+        <v>3.363628663330951</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.577443109924309</v>
+        <v>3.586618440173581</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.7183331698323</v>
+        <v>3.709910650464618</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301728504086201</v>
+        <v>9.301720054754202</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692670786637192</v>
+        <v>0.3692586293317182</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247545987338174</v>
+        <v>1.247541277191203</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747104865882296</v>
+        <v>1.747105673782653</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661216756361599</v>
+        <v>0.8661223305860716</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215260173438842</v>
+        <v>0.7215257597986315</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597291400377416</v>
+        <v>0.8597304368236153</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.45150823438498</v>
+        <v>5.474316779829261</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.685989901866385</v>
+        <v>5.829689686972293</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.695230097418081</v>
+        <v>7.234258701517815</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E6" t="n">
         <v>8888</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8887</v>
+        <v>8888</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734484527962192</v>
+        <v>6.734423267326733</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02317153053012</v>
+        <v>7.023128363407713</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886870025679282</v>
+        <v>0.2887050960809807</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477992206317002</v>
+        <v>1.477962069627863</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906703564389273</v>
+        <v>1.90664823844298</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040217397032574</v>
+        <v>0.3040167105195632</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979155035655085</v>
+        <v>-0.1979676056072293</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790241525083796</v>
+        <v>0.2790284472558104</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.290616713897065</v>
+        <v>7.589651134394564</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.003115114041904</v>
+        <v>8.096005378020079</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.221156364231579</v>
+        <v>8.230681876141045</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E7" t="n">
         <v>14249</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14248</v>
+        <v>14249</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579977610892757</v>
+        <v>5.579853393220577</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.56642298441991</v>
+        <v>5.566366132389365</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01355462647284616</v>
+        <v>-0.01348726083121136</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166058182376961</v>
+        <v>1.166086701907378</v>
       </c>
       <c r="U7" t="n">
-        <v>1.50936200259793</v>
+        <v>1.509363648860568</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049418428310046</v>
+        <v>0.5049416056767688</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05323913621601783</v>
+        <v>0.05325712621571277</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028031264081033</v>
+        <v>0.5028011266208665</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.098422601018568</v>
+        <v>5.119873485987529</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.492199052245812</v>
+        <v>5.569245058797988</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.825078793630611</v>
+        <v>5.843349381241421</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E8" t="n">
         <v>9047</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9046</v>
+        <v>9047</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.872056986513376</v>
+        <v>7.87178484580524</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6453862660944206</v>
+        <v>0.6453752680486061</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.112278712645585</v>
+        <v>8.111902141820121</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.240221726132208</v>
+        <v>0.2401172960148817</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445538145086972</v>
+        <v>1.445426125735049</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825195335784755</v>
+        <v>1.825116170614392</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077654089074733</v>
+        <v>0.8077800024743437</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6273907303844857</v>
+        <v>0.6274097882552281</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975435263599649</v>
+        <v>0.7975732086371821</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.084734888782486</v>
+        <v>5.095354836460285</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.604381395449226</v>
+        <v>5.698106091496003</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.001899220152391</v>
+        <v>6.007627673007466</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E9" t="n">
         <v>13912</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13911</v>
+        <v>13912</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.608451944504348</v>
+        <v>7.608255103507763</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.654077400377894</v>
+        <v>7.653886080327152</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.045625455873545</v>
+        <v>0.04563097681938907</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493251245368728</v>
+        <v>1.493243267054538</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941303941942513</v>
+        <v>1.941271220528148</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567001298825533</v>
+        <v>0.7567094568015769</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5249625908577142</v>
+        <v>0.5249767331628882</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552779732925767</v>
+        <v>0.7552881799806492</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.598759566191917</v>
+        <v>4.598856542938834</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.39427598617887</v>
+        <v>5.453558971512652</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.874442448084333</v>
+        <v>5.849502099714081</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61466111565932</v>
+        <v>10.6145111148486</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3095994351669482</v>
+        <v>0.3094494343562302</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05358577414138</v>
+        <v>2.0536485906996</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699334080163974</v>
+        <v>2.699396114016111</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570095667556469</v>
+        <v>0.3570104394582558</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1214652171542077</v>
+        <v>-0.1215167629094041</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3369418713741286</v>
+        <v>0.3369600573507877</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.26077299804446</v>
+        <v>10.69256657086023</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.77352954144602</v>
+        <v>10.98809906126675</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12994945046327</v>
+        <v>11.1284894237576</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E11" t="n">
         <v>13853</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13852</v>
+        <v>13853</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242116445278659</v>
+        <v>5.242032556125027</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215754998615396</v>
+        <v>5.215706988205918</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02636144666326386</v>
+        <v>-0.02632556791910949</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16098486428458</v>
+        <v>1.160979377242914</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482416478825449</v>
+        <v>1.482396810607485</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294857929005313</v>
+        <v>0.4294890983539184</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09184347511311808</v>
+        <v>-0.0918404376012063</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276760682882861</v>
+        <v>0.4276797388001259</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.348151241485249</v>
+        <v>4.511527020824468</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.667241232134576</v>
+        <v>4.88424751968994</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.954886118178034</v>
+        <v>5.069522301368757</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E12" t="n">
         <v>4171</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4170</v>
+        <v>4171</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.457922302158273</v>
+        <v>7.45721313833613</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.631555473381896</v>
+        <v>7.630906945435354</v>
       </c>
       <c r="R12" t="n">
-        <v>16.69088197424879</v>
+        <v>16.70026018584691</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1736331712236224</v>
+        <v>0.173693807099223</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9115686171312586</v>
+        <v>0.9113884296301785</v>
       </c>
       <c r="U12" t="n">
-        <v>1.192358793810632</v>
+        <v>1.192272068249753</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8331018295485469</v>
+        <v>0.8331725600570403</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6617924617177687</v>
+        <v>0.6619292636135656</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8312722420984352</v>
+        <v>0.8313408258718645</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.639355140289004</v>
+        <v>4.834086285677477</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.301945373197839</v>
+        <v>5.305148933861103</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.616012846870846</v>
+        <v>5.616826760827032</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E13" t="n">
         <v>6506</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6505</v>
+        <v>6506</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.597138739431207</v>
+        <v>9.596725714724869</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02192990325002</v>
+        <v>10.02138074067512</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4247911638188169</v>
+        <v>0.4246550259502529</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68969270823706</v>
+        <v>1.6894565578345</v>
       </c>
       <c r="U13" t="n">
-        <v>2.148014749230183</v>
+        <v>2.147875381127933</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233723746157392</v>
+        <v>0.8233859030115462</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6490972535111372</v>
+        <v>0.6491184670849539</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101692378699862</v>
+        <v>0.810198745247848</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.888326850498283</v>
+        <v>6.987416352346806</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.799326393265238</v>
+        <v>7.960831614082723</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.419340893401074</v>
+        <v>8.464712092549288</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E14" t="n">
         <v>14093</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14092</v>
+        <v>14093</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.125201355378939</v>
+        <v>8.12503281771092</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.196202645131915</v>
+        <v>8.195948832164568</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07100128975297619</v>
+        <v>0.07091601445364687</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755635815746599</v>
+        <v>1.755515279617754</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281513749573867</v>
+        <v>2.281362176158743</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809120590919048</v>
+        <v>0.7809391922260487</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5655573699564744</v>
+        <v>0.5655987814862697</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805236396317294</v>
+        <v>0.7805525384048153</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.011732001226994</v>
+        <v>6.992381510492661</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.112647496878097</v>
+        <v>7.09225016871124</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.165519301347135</v>
+        <v>7.162150636050148</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82006533726962</v>
+        <v>11.82000700134341</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1438220457571682</v>
+        <v>-0.1438803816833692</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052440000014556</v>
+        <v>2.05245336796896</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698079673053898</v>
+        <v>2.698125519310162</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950271904345805</v>
+        <v>0.7950241581083144</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094688902382019</v>
+        <v>0.6094556181753841</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865368769974287</v>
+        <v>0.7865399023000389</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.064855055457832</v>
+        <v>8.729037946698853</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.095457400814064</v>
+        <v>9.227765320031144</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.364591893180734</v>
+        <v>9.368344323847037</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E16" t="n">
         <v>9856</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9855</v>
+        <v>9856</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360379401319127</v>
+        <v>8.360202820616884</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622503368212158</v>
+        <v>8.62274067531869</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2621239668930304</v>
+        <v>0.2625378547018068</v>
       </c>
       <c r="T16" t="n">
-        <v>3.598148026369913</v>
+        <v>3.598361764382073</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08350891850575</v>
+        <v>11.08307430268085</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04127190321119755</v>
+        <v>0.04125991007129825</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6106939422512674</v>
+        <v>-0.6107245610846974</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02461205937865762</v>
+        <v>0.02459957669536472</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.64448805938433</v>
+        <v>11.5691310325211</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.73580155058682</v>
+        <v>11.7241226572528</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.76908688583976</v>
+        <v>11.77024349782937</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E17" t="n">
         <v>2400</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.465070862859524</v>
+        <v>6.463502083333333</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.830263788315987</v>
+        <v>6.829482257176264</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3651929254564617</v>
+        <v>0.3659801738429306</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008914805789721</v>
+        <v>2.009043957823433</v>
       </c>
       <c r="U17" t="n">
-        <v>2.547154830418226</v>
+        <v>2.547065937923828</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5384106994723721</v>
+        <v>0.5385441448573199</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05564711676675416</v>
+        <v>0.05613087841703612</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5349633336211252</v>
+        <v>0.5350804882471898</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.401702087660528</v>
+        <v>2.463163727410862</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.466448024664304</v>
+        <v>3.713627157408941</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.929032997825428</v>
+        <v>6.109472782566358</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E18" t="n">
         <v>3259</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.46379650092081</v>
+        <v>6.462868671371585</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.660538117873354</v>
+        <v>6.66000006034081</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1967416169525434</v>
+        <v>0.1971313889692231</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095168199514378</v>
+        <v>1.095239278808805</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483676255277605</v>
+        <v>1.48364920688382</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6085963316141881</v>
+        <v>0.6088025132005197</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2326821659348195</v>
+        <v>0.2332245036365665</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6054859548879311</v>
+        <v>0.6056586937691475</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.135342360431581</v>
+        <v>2.230507855428687</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.688029087109818</v>
+        <v>4.041111538287335</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.794720912609442</v>
+        <v>5.806923732431195</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E19" t="n">
         <v>7213</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7212</v>
+        <v>7213</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.31034823904603</v>
+        <v>10.3092155136559</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1092550259828</v>
+        <v>11.10887082268766</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7989067869367645</v>
+        <v>0.7996553090317613</v>
       </c>
       <c r="T19" t="n">
-        <v>2.064089883106337</v>
+        <v>2.064808136603801</v>
       </c>
       <c r="U19" t="n">
-        <v>2.78989055025359</v>
+        <v>2.790994777177908</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7277469434995637</v>
+        <v>0.7276585079447959</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4722558619615168</v>
+        <v>0.4720960478582007</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6779576581150504</v>
+        <v>0.6777631889159612</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.503817163521736</v>
+        <v>8.491400641466448</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.96339011252941</v>
+        <v>8.974565242435897</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.31245705889282</v>
+        <v>9.352677225983518</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E20" t="n">
         <v>10663</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10662</v>
+        <v>10663</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85391340341501</v>
+        <v>13.85358010946364</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490858369098713</v>
+        <v>7.490729092208721</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23043441722587</v>
+        <v>14.23003789025999</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3765210138108603</v>
+        <v>0.3764577807963442</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254675364369952</v>
+        <v>1.254563737022873</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646471867658645</v>
+        <v>1.646397853206802</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936086292472429</v>
+        <v>0.8936193746469514</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7791177246010356</v>
+        <v>0.7791381841142908</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8887758352382809</v>
+        <v>0.888791157583672</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.17301770309609</v>
+        <v>10.19213548069792</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.35145614719687</v>
+        <v>10.36463638125471</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.45124542460042</v>
+        <v>10.45113622553574</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16711</v>
+        <v>16712</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9711459311471</v>
+        <v>130.971183251691</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045763269358029</v>
+        <v>0.1046136474796392</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971399837627707</v>
+        <v>0.7971505469920043</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045697680661275</v>
+        <v>1.045714974314481</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651259200091893</v>
+        <v>0.865122058806817</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311974195053853</v>
+        <v>0.731188528566574</v>
       </c>
       <c r="X21" t="n">
-        <v>0.864375873963146</v>
+        <v>0.8643717539642325</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.4900698028289</v>
+        <v>128.4043674662909</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9007597406214</v>
+        <v>128.825896289841</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.1959705825173</v>
+        <v>129.1968100041889</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.503817163521736</v>
+        <v>8.491400641466448</v>
       </c>
       <c r="G2" t="n">
-        <v>8.963390112529408</v>
+        <v>8.974565242435897</v>
       </c>
       <c r="H2" t="n">
-        <v>9.31245705889282</v>
+        <v>9.352677225983518</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.098422601018568</v>
+        <v>5.119873485987529</v>
       </c>
       <c r="G3" t="n">
-        <v>5.492199052245812</v>
+        <v>5.569245058797987</v>
       </c>
       <c r="H3" t="n">
-        <v>5.825078793630611</v>
+        <v>5.843349381241421</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.348151241485249</v>
+        <v>4.511527020824468</v>
       </c>
       <c r="G4" t="n">
-        <v>4.667241232134575</v>
+        <v>4.88424751968994</v>
       </c>
       <c r="H4" t="n">
-        <v>4.954886118178034</v>
+        <v>5.069522301368757</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.64448805938433</v>
+        <v>11.5691310325211</v>
       </c>
       <c r="G5" t="n">
-        <v>11.73580155058682</v>
+        <v>11.7241226572528</v>
       </c>
       <c r="H5" t="n">
-        <v>11.76908688583976</v>
+        <v>11.77024349782937</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.585419168770938</v>
+        <v>3.212883572694635</v>
       </c>
       <c r="G6" t="n">
-        <v>74.54492658359959</v>
+        <v>68.51293158841899</v>
       </c>
       <c r="H6" t="n">
-        <v>110.341220699893</v>
+        <v>111.5472681401262</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.064855055457832</v>
+        <v>8.729037946698853</v>
       </c>
       <c r="G7" t="n">
-        <v>9.095457400814066</v>
+        <v>9.227765320031144</v>
       </c>
       <c r="H7" t="n">
-        <v>9.364591893180734</v>
+        <v>9.368344323847037</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.888326850498283</v>
+        <v>6.987416352346806</v>
       </c>
       <c r="G8" t="n">
-        <v>7.79932639326524</v>
+        <v>7.960831614082724</v>
       </c>
       <c r="H8" t="n">
-        <v>8.419340893401074</v>
+        <v>8.464712092549288</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.639355140289004</v>
+        <v>4.834086285677477</v>
       </c>
       <c r="G9" t="n">
-        <v>5.301945373197838</v>
+        <v>5.305148933861102</v>
       </c>
       <c r="H9" t="n">
-        <v>5.616012846870846</v>
+        <v>5.616826760827032</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.084734888782486</v>
+        <v>5.095354836460285</v>
       </c>
       <c r="G10" t="n">
-        <v>5.604381395449226</v>
+        <v>5.698106091496002</v>
       </c>
       <c r="H10" t="n">
-        <v>6.001899220152391</v>
+        <v>6.007627673007466</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.17301770309609</v>
+        <v>10.19213548069792</v>
       </c>
       <c r="G11" t="n">
-        <v>10.35145614719687</v>
+        <v>10.36463638125471</v>
       </c>
       <c r="H11" t="n">
-        <v>10.45124542460042</v>
+        <v>10.45113622553574</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.401702087660528</v>
+        <v>2.463163727410862</v>
       </c>
       <c r="G12" t="n">
-        <v>3.466448024664305</v>
+        <v>3.713627157408941</v>
       </c>
       <c r="H12" t="n">
-        <v>4.929032997825428</v>
+        <v>6.109472782566358</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>7.011732001226994</v>
+        <v>6.992381510492661</v>
       </c>
       <c r="G13" t="n">
-        <v>7.112647496878097</v>
+        <v>7.09225016871124</v>
       </c>
       <c r="H13" t="n">
-        <v>7.165519301347135</v>
+        <v>7.162150636050148</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.26077299804446</v>
+        <v>10.69256657086023</v>
       </c>
       <c r="G14" t="n">
-        <v>10.77352954144602</v>
+        <v>10.98809906126675</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12994945046327</v>
+        <v>11.1284894237576</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.598759566191917</v>
+        <v>4.598856542938834</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39427598617887</v>
+        <v>5.453558971512653</v>
       </c>
       <c r="H15" t="n">
-        <v>5.874442448084333</v>
+        <v>5.849502099714081</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.290616713897065</v>
+        <v>7.589651134394564</v>
       </c>
       <c r="G16" t="n">
-        <v>8.003115114041904</v>
+        <v>8.096005378020081</v>
       </c>
       <c r="H16" t="n">
-        <v>8.221156364231579</v>
+        <v>8.230681876141045</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.135342360431581</v>
+        <v>2.230507855428687</v>
       </c>
       <c r="G17" t="n">
-        <v>3.688029087109818</v>
+        <v>4.041111538287335</v>
       </c>
       <c r="H17" t="n">
-        <v>6.794720912609442</v>
+        <v>5.806923732431195</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.33911212446352</v>
+        <v>3.363628663330951</v>
       </c>
       <c r="G18" t="n">
-        <v>3.577443109924309</v>
+        <v>3.58661844017358</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7183331698323</v>
+        <v>3.709910650464618</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.573326374242042</v>
+        <v>2.570493403281183</v>
       </c>
       <c r="G19" t="n">
-        <v>2.886788808270394</v>
+        <v>2.963326832762448</v>
       </c>
       <c r="H19" t="n">
-        <v>3.326487487383361</v>
+        <v>3.3346075768406</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.45150823438498</v>
+        <v>5.474316779829261</v>
       </c>
       <c r="G20" t="n">
-        <v>5.685989901866385</v>
+        <v>5.829689686972293</v>
       </c>
       <c r="H20" t="n">
-        <v>6.695230097418081</v>
+        <v>7.234258701517815</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.4900698028289</v>
+        <v>128.4043674662909</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9007597406214</v>
+        <v>128.825896289841</v>
       </c>
       <c r="H21" t="n">
-        <v>129.1959705825173</v>
+        <v>129.1968100041889</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E2" t="n">
-        <v>10046</v>
+        <v>10049</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10046</v>
+        <v>10048</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5302437454377</v>
+        <v>102.5106527335457</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8431308077198</v>
+        <v>1.8432</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.5271071912615</v>
+        <v>102.4876028557012</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.003136554176139228</v>
+        <v>-0.02304987784443827</v>
       </c>
       <c r="T2" t="n">
-        <v>18.03969209014916</v>
+        <v>18.08299074385301</v>
       </c>
       <c r="U2" t="n">
-        <v>36.12050609271207</v>
+        <v>36.18735538342444</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1376830005416725</v>
+        <v>0.1374277831858881</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7201467912670381</v>
+        <v>-0.7224844426403985</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1376790628996316</v>
+        <v>0.1374263725745467</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.212883572694635</v>
+        <v>2.415735973654126</v>
       </c>
       <c r="Z2" t="n">
-        <v>68.51293158841899</v>
+        <v>66.40812432011433</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.5472681401262</v>
+        <v>109.1331888888889</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E3" t="n">
-        <v>14641</v>
+        <v>14643</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14641</v>
+        <v>14642</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.905153609726112</v>
+        <v>4.90494495287529</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.963041901910242</v>
+        <v>4.962827339392356</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05788829218413017</v>
+        <v>0.05788238651706513</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343513581747181</v>
+        <v>1.343437401564336</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718141067539953</v>
+        <v>1.718053956995124</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7815422751484999</v>
+        <v>0.7815688895706301</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5701215805360291</v>
+        <v>0.5701756742911732</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7804876609840915</v>
+        <v>0.780513836306995</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.570493403281183</v>
+        <v>2.59105600062779</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.963326832762448</v>
+        <v>3.038823773585626</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.3346075768406</v>
+        <v>3.333262857142857</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E4" t="n">
         <v>10275</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.232325064557133</v>
+        <v>7.232283868961676</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.330342826114312</v>
+        <v>0.3303016305188541</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291361499762604</v>
+        <v>1.291358210226277</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681051360407462</v>
+        <v>1.681052558712387</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867939209474755</v>
+        <v>0.8679392693203314</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7380198201321988</v>
+        <v>0.7380194466370644</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472263694347271</v>
+        <v>0.8472365071532203</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.363628663330951</v>
+        <v>3.372032310469314</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.586618440173581</v>
+        <v>3.574029577365703</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.709910650464618</v>
+        <v>3.71115</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301720054754202</v>
+        <v>9.301717313584485</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692586293317182</v>
+        <v>0.3692558881620008</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247541277191203</v>
+        <v>1.247534715020695</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747105673782653</v>
+        <v>1.747104460649469</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661223305860716</v>
+        <v>0.8661232465157223</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215257597986315</v>
+        <v>0.7215261465253529</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597304368236153</v>
+        <v>0.8597316997962952</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.474316779829261</v>
+        <v>5.473490410113907</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.829689686972293</v>
+        <v>5.947096821214966</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.234258701517815</v>
+        <v>7.16461666932865</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E6" t="n">
-        <v>8888</v>
+        <v>8890</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8888</v>
+        <v>8889</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734423267326733</v>
+        <v>6.734364551693105</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023128363407713</v>
+        <v>7.023091156117709</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887050960809807</v>
+        <v>0.2887266044246053</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477962069627863</v>
+        <v>1.47789359458646</v>
       </c>
       <c r="U6" t="n">
-        <v>1.90664823844298</v>
+        <v>1.906481608560521</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040167105195632</v>
+        <v>0.3040292229169952</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979676056072293</v>
+        <v>-0.197880899432064</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790284472558104</v>
+        <v>0.2790221761062575</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.589651134394564</v>
+        <v>7.870566994791965</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.096005378020079</v>
+        <v>8.148473392167144</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.230681876141045</v>
+        <v>8.230031142837548</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E7" t="n">
-        <v>14249</v>
+        <v>14251</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14249</v>
+        <v>14250</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579853393220577</v>
+        <v>5.579728140350878</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566366132389365</v>
+        <v>5.566176305125243</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01348726083121136</v>
+        <v>-0.01355183522563468</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166086701907378</v>
+        <v>1.166124872548124</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509363648860568</v>
+        <v>1.509359450651569</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049416056767688</v>
+        <v>0.5049662913155196</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05325712621571277</v>
+        <v>0.05328390141189809</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028011266208665</v>
+        <v>0.5028276691587359</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.119873485987529</v>
+        <v>5.178411778452909</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.569245058797988</v>
+        <v>5.637512576419816</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.843349381241421</v>
+        <v>5.841472944165007</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E8" t="n">
-        <v>9047</v>
+        <v>9049</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9047</v>
+        <v>9048</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.87178484580524</v>
+        <v>7.871496187002653</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6453752680486061</v>
+        <v>0.6454071428571428</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.111902141820121</v>
+        <v>8.111726207747854</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2401172960148817</v>
+        <v>0.2402300207452002</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445426125735049</v>
+        <v>1.445242405951252</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825116170614392</v>
+        <v>1.824960583981422</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8077800024743437</v>
+        <v>0.8078018282208772</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274097882552281</v>
+        <v>0.6274635224019826</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975732086371821</v>
+        <v>0.7975727232444314</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.095354836460285</v>
+        <v>5.153079564428033</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.698106091496003</v>
+        <v>5.786669570198366</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.007627673007466</v>
+        <v>6.008919626506445</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E9" t="n">
-        <v>13912</v>
+        <v>13914</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13912</v>
+        <v>13913</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.608255103507763</v>
+        <v>7.608044993890606</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.653886080327152</v>
+        <v>7.653639165832332</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04563097681938907</v>
+        <v>0.04559417194172571</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493243267054538</v>
+        <v>1.493176372269623</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941271220528148</v>
+        <v>1.941177694055906</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567094568015769</v>
+        <v>0.75673460860256</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5249767331628882</v>
+        <v>0.5250251030392243</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7552881799806492</v>
+        <v>0.7553135574047385</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.598856542938834</v>
+        <v>4.598657974744987</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.453558971512652</v>
+        <v>5.35476573299032</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.849502099714081</v>
+        <v>5.647903633928571</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.6145111148486</v>
+        <v>10.61435855203361</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3094494343562302</v>
+        <v>0.3092968715412424</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0536485906996</v>
+        <v>2.053712769219104</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699396114016111</v>
+        <v>2.699462635481257</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570104394582558</v>
+        <v>0.3570095403864739</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1215167629094041</v>
+        <v>-0.1215720388706574</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3369600573507877</v>
+        <v>0.3369767712636494</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.69256657086023</v>
+        <v>10.57962415786088</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.98809906126675</v>
+        <v>10.93091710740923</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.1284894237576</v>
+        <v>11.11144126256653</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E11" t="n">
-        <v>13853</v>
+        <v>13855</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13853</v>
+        <v>13854</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.242032556125027</v>
+        <v>5.241988559260863</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215706988205918</v>
+        <v>5.215652659567432</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02632556791910949</v>
+        <v>-0.02633589969343205</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160979377242914</v>
+        <v>1.160900380920082</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482396810607485</v>
+        <v>1.482324896070204</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294890983539184</v>
+        <v>0.4295004263432093</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0918404376012063</v>
+        <v>-0.09180073333013539</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276797388001259</v>
+        <v>0.4276896327257725</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.511527020824468</v>
+        <v>4.352223469387755</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.88424751968994</v>
+        <v>4.815461132850266</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.069522301368757</v>
+        <v>5.049408</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E12" t="n">
-        <v>4171</v>
+        <v>4173</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4171</v>
+        <v>4172</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.45721313833613</v>
+        <v>7.456503715244487</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.630906945435354</v>
+        <v>7.629685973651911</v>
       </c>
       <c r="R12" t="n">
-        <v>16.70026018584691</v>
+        <v>16.63367500000018</v>
       </c>
       <c r="S12" t="n">
-        <v>0.173693807099223</v>
+        <v>0.1731822584074241</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9113884296301785</v>
+        <v>0.9113527687798831</v>
       </c>
       <c r="U12" t="n">
-        <v>1.192272068249753</v>
+        <v>1.1919331405955</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8331725600570403</v>
+        <v>0.8333065830861797</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6619292636135656</v>
+        <v>0.6622091151834091</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8313408258718645</v>
+        <v>0.8314872964665724</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.834086285677477</v>
+        <v>4.438455969980065</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.305148933861103</v>
+        <v>5.18886498597892</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.616826760827032</v>
+        <v>5.610226500465983</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E13" t="n">
-        <v>6506</v>
+        <v>6508</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6506</v>
+        <v>6507</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.596725714724869</v>
+        <v>9.596315890579374</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02138074067512</v>
+        <v>10.02121242292288</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4246550259502529</v>
+        <v>0.4248965323435077</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6894565578345</v>
+        <v>1.689126166920778</v>
       </c>
       <c r="U13" t="n">
-        <v>2.147875381127933</v>
+        <v>2.147617857263203</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8233859030115462</v>
+        <v>0.8234119347673137</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6491184670849539</v>
+        <v>0.6491778434753983</v>
       </c>
       <c r="X13" t="n">
-        <v>0.810198745247848</v>
+        <v>0.810185976896806</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.987416352346806</v>
+        <v>7.22191147826087</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.960831614082723</v>
+        <v>8.101204974510491</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.464712092549288</v>
+        <v>8.475847910166737</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E14" t="n">
-        <v>14093</v>
+        <v>14095</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14093</v>
+        <v>14094</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.12503281771092</v>
+        <v>8.124864303959132</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195948832164568</v>
+        <v>8.195887891104789</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07091601445364687</v>
+        <v>0.07102358714565848</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755515279617754</v>
+        <v>1.755387828073387</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281362176158743</v>
+        <v>2.281175860411726</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809391922260487</v>
+        <v>0.7809587897524509</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5655987814862697</v>
+        <v>0.5656534228528115</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805525384048153</v>
+        <v>0.7805697633249591</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.992381510492661</v>
+        <v>6.919250707850705</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.09225016871124</v>
+        <v>7.051275274002238</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.162150636050148</v>
+        <v>7.143310960388112</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82000700134341</v>
+        <v>11.81990536102549</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1438803816833692</v>
+        <v>-0.1439820220012931</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05245336796896</v>
+        <v>2.052487266773273</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698125519310162</v>
+        <v>2.698212230375453</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950241581083144</v>
+        <v>0.7950165176546687</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094556181753841</v>
+        <v>0.6094305155155486</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865399023000389</v>
+        <v>0.7865406077070156</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.729037946698853</v>
+        <v>9.050927927927926</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.227765320031144</v>
+        <v>9.299157979661409</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.368344323847037</v>
+        <v>9.427569099703199</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E16" t="n">
-        <v>9856</v>
+        <v>9858</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9856</v>
+        <v>9857</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360202820616884</v>
+        <v>8.360034391802779</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.62274067531869</v>
+        <v>8.622346981176582</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2625378547018068</v>
+        <v>0.262312589373802</v>
       </c>
       <c r="T16" t="n">
-        <v>3.598361764382073</v>
+        <v>3.598856193592692</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08307430268085</v>
+        <v>11.08267904130124</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04125991007129825</v>
+        <v>0.04122736567205571</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6107245610846974</v>
+        <v>-0.6107671870060631</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02459957669536472</v>
+        <v>0.0245673347050509</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5691310325211</v>
+        <v>11.46164281207563</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.7241226572528</v>
+        <v>11.68928702274312</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.77024349782937</v>
+        <v>11.76830391953546</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E17" t="n">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.463502083333333</v>
+        <v>6.461892961266139</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.829482257176264</v>
+        <v>6.82664572656482</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3659801738429306</v>
+        <v>0.3647527652986798</v>
       </c>
       <c r="T17" t="n">
-        <v>2.009043957823433</v>
+        <v>2.008761531035304</v>
       </c>
       <c r="U17" t="n">
-        <v>2.547065937923828</v>
+        <v>2.546819261832665</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5385441448573199</v>
+        <v>0.5389616292183751</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05613087841703612</v>
+        <v>0.05677347779337405</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5350804882471898</v>
+        <v>0.5355148881655608</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.463163727410862</v>
+        <v>2.459292567643363</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.713627157408941</v>
+        <v>3.549460086543774</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.109472782566358</v>
+        <v>4.914054968677066</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E18" t="n">
-        <v>3259</v>
+        <v>3261</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.462868671371585</v>
+        <v>6.461913803680981</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.66000006034081</v>
+        <v>6.658281729300491</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1971313889692231</v>
+        <v>0.1963679256195095</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095239278808805</v>
+        <v>1.095141377643125</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48364920688382</v>
+        <v>1.483567190862664</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6088025132005197</v>
+        <v>0.6092193167016037</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2332245036365665</v>
+        <v>0.2338669847692461</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6056586937691475</v>
+        <v>0.606119392534715</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.230507855428687</v>
+        <v>2.202736181454358</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.041111538287335</v>
+        <v>4.063987737710498</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.806923732431195</v>
+        <v>5.912731621541849</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E19" t="n">
-        <v>7213</v>
+        <v>7215</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7213</v>
+        <v>7214</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.3092155136559</v>
+        <v>10.3080383975603</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10887082268766</v>
+        <v>11.10773885998713</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7996553090317613</v>
+        <v>0.7997004624268246</v>
       </c>
       <c r="T19" t="n">
-        <v>2.064808136603801</v>
+        <v>2.06562155996134</v>
       </c>
       <c r="U19" t="n">
-        <v>2.790994777177908</v>
+        <v>2.79207666640636</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7276585079447959</v>
+        <v>0.7275704415498488</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4720960478582007</v>
+        <v>0.4719709764450009</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6777631889159612</v>
+        <v>0.6776744115750419</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.491400641466448</v>
+        <v>8.400678046776232</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.974565242435897</v>
+        <v>8.833865216810267</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.352677225983518</v>
+        <v>9.204840018581187</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E20" t="n">
-        <v>10663</v>
+        <v>10665</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10663</v>
+        <v>10664</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85358010946364</v>
+        <v>13.85322812333185</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490729092208721</v>
+        <v>7.491000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.23003789025999</v>
+        <v>14.22967875910013</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764577807963442</v>
+        <v>0.3764506357682799</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254563737022873</v>
+        <v>1.254442984700662</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646397853206802</v>
+        <v>1.646293931901184</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936193746469514</v>
+        <v>0.8936344831520683</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7791381841142908</v>
+        <v>0.7791691103956063</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888791157583672</v>
+        <v>0.8888049890802789</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19213548069792</v>
+        <v>10.19761347951584</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.36463638125471</v>
+        <v>10.35469069133724</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.45113622553574</v>
+        <v>10.45108058676723</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.971183251691</v>
+        <v>130.9712125974141</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046136474796392</v>
+        <v>0.1046429932028025</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971505469920043</v>
+        <v>0.7971619428543387</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045714974314481</v>
+        <v>1.045735083607677</v>
       </c>
       <c r="V21" t="n">
-        <v>0.865122058806817</v>
+        <v>0.8651176998212338</v>
       </c>
       <c r="W21" t="n">
-        <v>0.731188528566574</v>
+        <v>0.7311781898781136</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643717539642325</v>
+        <v>0.8643675199713352</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.4043674662909</v>
+        <v>128.1989569673261</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.825896289841</v>
+        <v>128.6846530107072</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.1968100041889</v>
+        <v>129.1409228675784</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.491400641466448</v>
+        <v>8.400678046776232</v>
       </c>
       <c r="G2" t="n">
-        <v>8.974565242435897</v>
+        <v>8.833865216810267</v>
       </c>
       <c r="H2" t="n">
-        <v>9.352677225983518</v>
+        <v>9.204840018581187</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.119873485987529</v>
+        <v>5.178411778452909</v>
       </c>
       <c r="G3" t="n">
-        <v>5.569245058797987</v>
+        <v>5.637512576419817</v>
       </c>
       <c r="H3" t="n">
-        <v>5.843349381241421</v>
+        <v>5.841472944165007</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.511527020824468</v>
+        <v>4.352223469387755</v>
       </c>
       <c r="G4" t="n">
-        <v>4.88424751968994</v>
+        <v>4.815461132850265</v>
       </c>
       <c r="H4" t="n">
-        <v>5.069522301368757</v>
+        <v>5.049408</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5691310325211</v>
+        <v>11.46164281207563</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7241226572528</v>
+        <v>11.68928702274312</v>
       </c>
       <c r="H5" t="n">
-        <v>11.77024349782937</v>
+        <v>11.76830391953546</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.212883572694635</v>
+        <v>2.415735973654126</v>
       </c>
       <c r="G6" t="n">
-        <v>68.51293158841899</v>
+        <v>66.40812432011434</v>
       </c>
       <c r="H6" t="n">
-        <v>111.5472681401262</v>
+        <v>109.1331888888889</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.729037946698853</v>
+        <v>9.050927927927926</v>
       </c>
       <c r="G7" t="n">
-        <v>9.227765320031144</v>
+        <v>9.299157979661411</v>
       </c>
       <c r="H7" t="n">
-        <v>9.368344323847037</v>
+        <v>9.427569099703199</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.987416352346806</v>
+        <v>7.22191147826087</v>
       </c>
       <c r="G8" t="n">
-        <v>7.960831614082724</v>
+        <v>8.101204974510491</v>
       </c>
       <c r="H8" t="n">
-        <v>8.464712092549288</v>
+        <v>8.475847910166737</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.834086285677477</v>
+        <v>4.438455969980065</v>
       </c>
       <c r="G9" t="n">
-        <v>5.305148933861102</v>
+        <v>5.18886498597892</v>
       </c>
       <c r="H9" t="n">
-        <v>5.616826760827032</v>
+        <v>5.610226500465983</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.095354836460285</v>
+        <v>5.153079564428033</v>
       </c>
       <c r="G10" t="n">
-        <v>5.698106091496002</v>
+        <v>5.786669570198366</v>
       </c>
       <c r="H10" t="n">
-        <v>6.007627673007466</v>
+        <v>6.008919626506445</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19213548069792</v>
+        <v>10.19761347951584</v>
       </c>
       <c r="G11" t="n">
-        <v>10.36463638125471</v>
+        <v>10.35469069133724</v>
       </c>
       <c r="H11" t="n">
-        <v>10.45113622553574</v>
+        <v>10.45108058676723</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.463163727410862</v>
+        <v>2.459292567643363</v>
       </c>
       <c r="G12" t="n">
-        <v>3.713627157408941</v>
+        <v>3.549460086543774</v>
       </c>
       <c r="H12" t="n">
-        <v>6.109472782566358</v>
+        <v>4.914054968677066</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.992381510492661</v>
+        <v>6.919250707850705</v>
       </c>
       <c r="G13" t="n">
-        <v>7.09225016871124</v>
+        <v>7.051275274002238</v>
       </c>
       <c r="H13" t="n">
-        <v>7.162150636050148</v>
+        <v>7.143310960388112</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.69256657086023</v>
+        <v>10.57962415786088</v>
       </c>
       <c r="G14" t="n">
-        <v>10.98809906126675</v>
+        <v>10.93091710740923</v>
       </c>
       <c r="H14" t="n">
-        <v>11.1284894237576</v>
+        <v>11.11144126256653</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.598856542938834</v>
+        <v>4.598657974744987</v>
       </c>
       <c r="G15" t="n">
-        <v>5.453558971512653</v>
+        <v>5.35476573299032</v>
       </c>
       <c r="H15" t="n">
-        <v>5.849502099714081</v>
+        <v>5.647903633928571</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.589651134394564</v>
+        <v>7.870566994791965</v>
       </c>
       <c r="G16" t="n">
-        <v>8.096005378020081</v>
+        <v>8.148473392167144</v>
       </c>
       <c r="H16" t="n">
-        <v>8.230681876141045</v>
+        <v>8.230031142837548</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.230507855428687</v>
+        <v>2.202736181454358</v>
       </c>
       <c r="G17" t="n">
-        <v>4.041111538287335</v>
+        <v>4.063987737710498</v>
       </c>
       <c r="H17" t="n">
-        <v>5.806923732431195</v>
+        <v>5.912731621541849</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.363628663330951</v>
+        <v>3.372032310469314</v>
       </c>
       <c r="G18" t="n">
-        <v>3.58661844017358</v>
+        <v>3.574029577365703</v>
       </c>
       <c r="H18" t="n">
-        <v>3.709910650464618</v>
+        <v>3.71115</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.570493403281183</v>
+        <v>2.59105600062779</v>
       </c>
       <c r="G19" t="n">
-        <v>2.963326832762448</v>
+        <v>3.038823773585626</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3346075768406</v>
+        <v>3.333262857142857</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.474316779829261</v>
+        <v>5.473490410113907</v>
       </c>
       <c r="G20" t="n">
-        <v>5.829689686972293</v>
+        <v>5.947096821214966</v>
       </c>
       <c r="H20" t="n">
-        <v>7.234258701517815</v>
+        <v>7.16461666932865</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.4043674662909</v>
+        <v>128.1989569673261</v>
       </c>
       <c r="G21" t="n">
-        <v>128.825896289841</v>
+        <v>128.6846530107072</v>
       </c>
       <c r="H21" t="n">
-        <v>129.1968100041889</v>
+        <v>129.1409228675784</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E2" t="n">
+        <v>10050</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10049</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10048</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5106527335457</v>
+        <v>102.5008556738647</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8432</v>
+        <v>1.84321199143469</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4876028557012</v>
+        <v>102.4755011259438</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02304987784443827</v>
+        <v>-0.02535454792096886</v>
       </c>
       <c r="T2" t="n">
-        <v>18.08299074385301</v>
+        <v>18.10080904613902</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18735538342444</v>
+        <v>36.21098716068762</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1374277831858881</v>
+        <v>0.13730402631204</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7224844426403985</v>
+        <v>-0.7227209269002317</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1374263725745467</v>
+        <v>0.1373025985073482</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.415735973654126</v>
+        <v>4.067630586302542</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.40812432011433</v>
+        <v>94.75228086932118</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.1331888888889</v>
+        <v>110.4729842937248</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E3" t="n">
+        <v>14644</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14643</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14642</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.90494495287529</v>
+        <v>4.904730690432288</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.962827339392356</v>
+        <v>4.962610388756781</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05788238651706513</v>
+        <v>0.05787969832449296</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343437401564336</v>
+        <v>1.343393949813763</v>
       </c>
       <c r="U3" t="n">
-        <v>1.718053956995124</v>
+        <v>1.717998635694552</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7815688895706301</v>
+        <v>0.7815898093477023</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5701756742911732</v>
+        <v>0.5702160724972706</v>
       </c>
       <c r="X3" t="n">
-        <v>0.780513836306995</v>
+        <v>0.780534810288442</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.59105600062779</v>
+        <v>2.681926737598145</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.038823773585626</v>
+        <v>3.112565252818547</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.333262857142857</v>
+        <v>3.333064953604568</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E4" t="n">
-        <v>10275</v>
+        <v>10278</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10275</v>
+        <v>10277</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.901982238442821</v>
+        <v>6.901282475430572</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.232283868961676</v>
+        <v>7.231610121807335</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3303016305188541</v>
+        <v>0.3303276463767614</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291358210226277</v>
+        <v>1.291110243873886</v>
       </c>
       <c r="U4" t="n">
-        <v>1.681052558712387</v>
+        <v>1.680834937125557</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679392693203314</v>
+        <v>0.8679798527202158</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7380194466370644</v>
+        <v>0.7380973507583055</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472365071532203</v>
+        <v>0.8472611931848205</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.372032310469314</v>
+        <v>3.366916488222699</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.574029577365703</v>
+        <v>3.56091867262621</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.71115</v>
+        <v>3.715852023957865</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301717313584485</v>
+        <v>9.301715671116421</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692558881620008</v>
+        <v>0.3692542456939371</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247534715020695</v>
+        <v>1.247528976425994</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747104460649469</v>
+        <v>1.747103496154962</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661232465157223</v>
+        <v>0.8661241125905236</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215261465253529</v>
+        <v>0.7215264539899995</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597316997962952</v>
+        <v>0.8597328613659049</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.473490410113907</v>
+        <v>5.474344370378662</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.947096821214966</v>
+        <v>6.110809864304646</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.16461666932865</v>
+        <v>7.183989728095663</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E6" t="n">
+        <v>8891</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8890</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8889</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734364551693105</v>
+        <v>6.734297694038245</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023091156117709</v>
+        <v>7.02305998551712</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887266044246053</v>
+        <v>0.2887622914788752</v>
       </c>
       <c r="T6" t="n">
-        <v>1.47789359458646</v>
+        <v>1.477918182791078</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906481608560521</v>
+        <v>1.906413652916855</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040292229169952</v>
+        <v>0.3040069013590891</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.197880899432064</v>
+        <v>-0.1979145670704907</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2790221761062575</v>
+        <v>0.2789972346659096</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.870566994791965</v>
+        <v>8.109815322773168</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.148473392167144</v>
+        <v>8.172816537072588</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.230031142837548</v>
+        <v>8.229877870601387</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E7" t="n">
+        <v>14252</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14251</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14250</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579728140350878</v>
+        <v>5.579600799943864</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566176305125243</v>
+        <v>5.566048773103472</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01355183522563468</v>
+        <v>-0.01355202684039129</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166124872548124</v>
+        <v>1.16616665135997</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509359450651569</v>
+        <v>1.509365448752093</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049662913155196</v>
+        <v>0.504976260099564</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05328390141189809</v>
+        <v>0.05330085289496467</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028276691587359</v>
+        <v>0.5028378077617733</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.178411778452909</v>
+        <v>5.318568573467931</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.637512576419816</v>
+        <v>5.698711389030464</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.841472944165007</v>
+        <v>5.840821762395835</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E8" t="n">
+        <v>9050</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9049</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9048</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.871496187002653</v>
+        <v>7.871199027516853</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454071428571428</v>
+        <v>0.6454175588865096</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.111726207747854</v>
+        <v>8.111435185849176</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2402300207452002</v>
+        <v>0.2402361583323235</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445242405951252</v>
+        <v>1.445071555458688</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824960583981422</v>
+        <v>1.824839300374214</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078018282208772</v>
+        <v>0.8078229254628417</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274635224019826</v>
+        <v>0.6275051627757179</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975727232444314</v>
+        <v>0.7975901793094373</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.153079564428033</v>
+        <v>5.331051149606123</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.786669570198366</v>
+        <v>5.868691200293356</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.008919626506445</v>
+        <v>6.007235847899707</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E9" t="n">
+        <v>13915</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13914</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13913</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.608044993890606</v>
+        <v>7.60783221934742</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.653639165832332</v>
+        <v>7.653442337410993</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04559417194172571</v>
+        <v>0.0456101180635728</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493176372269623</v>
+        <v>1.493149680774641</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941177694055906</v>
+        <v>1.94113611231637</v>
       </c>
       <c r="V9" t="n">
-        <v>0.75673460860256</v>
+        <v>0.7567456921172799</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250251030392243</v>
+        <v>0.5250490261735341</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553135574047385</v>
+        <v>0.7553239176334575</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.598657974744987</v>
+        <v>4.569793640453597</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.35476573299032</v>
+        <v>5.235547567416789</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.647903633928571</v>
+        <v>5.461986752800734</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61435855203361</v>
+        <v>10.6142033164755</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3092968715412424</v>
+        <v>0.3091416359831298</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053712769219104</v>
+        <v>2.053780708924853</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699462635481257</v>
+        <v>2.699535151734013</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570095403864739</v>
+        <v>0.3570061988841834</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1215720388706574</v>
+        <v>-0.1216322977479671</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3369767712636494</v>
+        <v>0.3369913957655655</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.57962415786088</v>
+        <v>10.46448620302891</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.93091710740923</v>
+        <v>10.90480539037521</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.11144126256653</v>
+        <v>11.11530424714697</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E11" t="n">
+        <v>13856</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13855</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13854</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241988559260863</v>
+        <v>5.241903428365212</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215652659567432</v>
+        <v>5.215543510106365</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02633589969343205</v>
+        <v>-0.02635991825884657</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160900380920082</v>
+        <v>1.160895298159415</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482324896070204</v>
+        <v>1.482307214084051</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295004263432093</v>
+        <v>0.429513188727555</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09180073333013539</v>
+        <v>-0.09179901916015254</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4276896327257725</v>
+        <v>0.4277039692586118</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.352223469387755</v>
+        <v>4.246297791267956</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.815461132850266</v>
+        <v>4.799804400336095</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.049408</v>
+        <v>5.06815653950675</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E12" t="n">
+        <v>4174</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4173</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4172</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.456503715244487</v>
+        <v>7.455816199376947</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.629685973651911</v>
+        <v>7.629040317091704</v>
       </c>
       <c r="R12" t="n">
-        <v>16.63367500000018</v>
+        <v>16.60513276231278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1731822584074241</v>
+        <v>0.1732241177147563</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9113527687798831</v>
+        <v>0.9112574533281755</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1919331405955</v>
+        <v>1.191602201628676</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8333065830861797</v>
+        <v>0.8334208332818538</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6622091151834091</v>
+        <v>0.6624740367373021</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8314872964665724</v>
+        <v>0.831592868853439</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.438455969980065</v>
+        <v>4.311050689557547</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.18886498597892</v>
+        <v>5.090087738243642</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.610226500465983</v>
+        <v>5.6067055578062</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E13" t="n">
+        <v>6509</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6508</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6507</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.596315890579374</v>
+        <v>9.595904655808235</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02121242292288</v>
+        <v>10.02086341305139</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4248965323435077</v>
+        <v>0.4249587572431569</v>
       </c>
       <c r="T13" t="n">
-        <v>1.689126166920778</v>
+        <v>1.688869355926071</v>
       </c>
       <c r="U13" t="n">
-        <v>2.147617857263203</v>
+        <v>2.147400579638552</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234119347673137</v>
+        <v>0.8234350116707866</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6491778434753983</v>
+        <v>0.64922428757257</v>
       </c>
       <c r="X13" t="n">
-        <v>0.810185976896806</v>
+        <v>0.8101965554539312</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.22191147826087</v>
+        <v>7.571138065045963</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.101204974510491</v>
+        <v>8.230097491675398</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.475847910166737</v>
+        <v>8.494502193532433</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E14" t="n">
+        <v>14096</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14095</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14094</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.124864303959132</v>
+        <v>8.124695814118482</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195887891104789</v>
+        <v>8.195730078865822</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07102358714565848</v>
+        <v>0.07103426474733879</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755387828073387</v>
+        <v>1.755263291546631</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281175860411726</v>
+        <v>2.281010160517434</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809587897524509</v>
+        <v>0.7809815492091059</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5656534228528115</v>
+        <v>0.5657002123847674</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805697633249591</v>
+        <v>0.7805922268437175</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.919250707850705</v>
+        <v>6.89203775756195</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.051275274002238</v>
+        <v>7.015606788891276</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.143310960388112</v>
+        <v>7.115064269816771</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81990536102549</v>
+        <v>11.81978460782879</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1439820220012931</v>
+        <v>-0.1441027751979873</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052487266773273</v>
+        <v>2.052534085994658</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698212230375453</v>
+        <v>2.698303192985759</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950165176546687</v>
+        <v>0.7950088222335779</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094305155155486</v>
+        <v>0.6094041811758959</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865406077070156</v>
+        <v>0.786541936320361</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.050927927927926</v>
+        <v>9.182005957316726</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.299157979661409</v>
+        <v>9.34025454851238</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.427569099703199</v>
+        <v>9.442735567733504</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E16" t="n">
+        <v>9859</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9858</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9857</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.360034391802779</v>
+        <v>8.35984875228241</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622346981176582</v>
+        <v>8.622217165538155</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.262312589373802</v>
+        <v>0.2623684132557443</v>
       </c>
       <c r="T16" t="n">
-        <v>3.598856193592692</v>
+        <v>3.599280260997939</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08267904130124</v>
+        <v>11.08229402268574</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04122736567205571</v>
+        <v>0.04120138954645296</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6107671870060631</v>
+        <v>-0.6108114965973224</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0245673347050509</v>
+        <v>0.02454168872393381</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.46164281207563</v>
+        <v>11.3660190923773</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.68928702274312</v>
+        <v>11.65315213957853</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.76830391953546</v>
+        <v>11.76773781303927</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E17" t="n">
+        <v>2403</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2402</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2401</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.461892961266139</v>
+        <v>6.460270607826811</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.82664572656482</v>
+        <v>6.824721293557298</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3647527652986798</v>
+        <v>0.3644506857304872</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008761531035304</v>
+        <v>2.008463242441171</v>
       </c>
       <c r="U17" t="n">
-        <v>2.546819261832665</v>
+        <v>2.54646566037916</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5389616292183751</v>
+        <v>0.5393218422050328</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05677347779337405</v>
+        <v>0.05750912187682178</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5355148881655608</v>
+        <v>0.5358762600090314</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.459292567643363</v>
+        <v>2.402894804584476</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.549460086543774</v>
+        <v>3.604950958062932</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.914054968677066</v>
+        <v>4.560671054560999</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E18" t="n">
+        <v>3262</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3261</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3260</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.461913803680981</v>
+        <v>6.460979454155168</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.658281729300491</v>
+        <v>6.657161882793937</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1963679256195095</v>
+        <v>0.1961824286387681</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095141377643125</v>
+        <v>1.095251818518168</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483567190862664</v>
+        <v>1.483663117102574</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6092193167016037</v>
+        <v>0.6094406904017209</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2338669847692461</v>
+        <v>0.2342916578230491</v>
       </c>
       <c r="X18" t="n">
-        <v>0.606119392534715</v>
+        <v>0.6063458588538084</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.202736181454358</v>
+        <v>2.135255196999283</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.063987737710498</v>
+        <v>4.193534107052736</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.912731621541849</v>
+        <v>5.912332360788759</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E19" t="n">
+        <v>7216</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7215</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7214</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.3080383975603</v>
+        <v>10.30685779625779</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10773885998713</v>
+        <v>11.10697475118651</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7997004624268246</v>
+        <v>0.800116954928715</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06562155996134</v>
+        <v>2.066397632108266</v>
       </c>
       <c r="U19" t="n">
-        <v>2.79207666640636</v>
+        <v>2.793209891890844</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7275704415498488</v>
+        <v>0.7274813212720866</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4719709764450009</v>
+        <v>0.4718287771833439</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6776744115750419</v>
+        <v>0.677526386373087</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.400678046776232</v>
+        <v>8.406918999779862</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.833865216810267</v>
+        <v>8.795153426474574</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.204840018581187</v>
+        <v>9.095846627747099</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E20" t="n">
+        <v>10666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10665</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10664</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85322812333185</v>
+        <v>13.85286987409384</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.491000000000001</v>
+        <v>7.491070663811564</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22967875910013</v>
+        <v>14.22928669984556</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764506357682799</v>
+        <v>0.3764168257517222</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254442984700662</v>
+        <v>1.254335622475113</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646293931901184</v>
+        <v>1.646200893664892</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936344831520683</v>
+        <v>0.8936490525384038</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7791691103956063</v>
+        <v>0.7791979891043024</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888049890802789</v>
+        <v>0.8888211635401654</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19761347951584</v>
+        <v>10.1912313841476</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.35469069133724</v>
+        <v>10.34990179380678</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.45108058676723</v>
+        <v>10.51439311754974</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16713</v>
+        <v>16714</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9712125974141</v>
+        <v>130.9712489058597</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046429932028025</v>
+        <v>0.1046793016483569</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971619428543387</v>
+        <v>0.7971701887248199</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045735083607677</v>
+        <v>1.045750089702775</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651176998212338</v>
+        <v>0.865114454554743</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311781898781136</v>
+        <v>0.7311704747413573</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643675199713352</v>
+        <v>0.8643640514111712</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.1989569673261</v>
+        <v>128.2259845498521</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.6846530107072</v>
+        <v>128.6321085441714</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.1409228675784</v>
+        <v>128.9958978370408</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.400678046776232</v>
+        <v>8.406918999779862</v>
       </c>
       <c r="G2" t="n">
-        <v>8.833865216810267</v>
+        <v>8.795153426474574</v>
       </c>
       <c r="H2" t="n">
-        <v>9.204840018581187</v>
+        <v>9.095846627747099</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.178411778452909</v>
+        <v>5.318568573467931</v>
       </c>
       <c r="G3" t="n">
-        <v>5.637512576419817</v>
+        <v>5.698711389030464</v>
       </c>
       <c r="H3" t="n">
-        <v>5.841472944165007</v>
+        <v>5.840821762395835</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.352223469387755</v>
+        <v>4.246297791267956</v>
       </c>
       <c r="G4" t="n">
-        <v>4.815461132850265</v>
+        <v>4.799804400336095</v>
       </c>
       <c r="H4" t="n">
-        <v>5.049408</v>
+        <v>5.06815653950675</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.46164281207563</v>
+        <v>11.3660190923773</v>
       </c>
       <c r="G5" t="n">
-        <v>11.68928702274312</v>
+        <v>11.65315213957853</v>
       </c>
       <c r="H5" t="n">
-        <v>11.76830391953546</v>
+        <v>11.76773781303927</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.415735973654126</v>
+        <v>4.067630586302542</v>
       </c>
       <c r="G6" t="n">
-        <v>66.40812432011434</v>
+        <v>94.75228086932118</v>
       </c>
       <c r="H6" t="n">
-        <v>109.1331888888889</v>
+        <v>110.4729842937248</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.050927927927926</v>
+        <v>9.182005957316726</v>
       </c>
       <c r="G7" t="n">
-        <v>9.299157979661411</v>
+        <v>9.34025454851238</v>
       </c>
       <c r="H7" t="n">
-        <v>9.427569099703199</v>
+        <v>9.442735567733504</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.22191147826087</v>
+        <v>7.571138065045963</v>
       </c>
       <c r="G8" t="n">
-        <v>8.101204974510491</v>
+        <v>8.230097491675398</v>
       </c>
       <c r="H8" t="n">
-        <v>8.475847910166737</v>
+        <v>8.494502193532433</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.438455969980065</v>
+        <v>4.311050689557547</v>
       </c>
       <c r="G9" t="n">
-        <v>5.18886498597892</v>
+        <v>5.090087738243642</v>
       </c>
       <c r="H9" t="n">
-        <v>5.610226500465983</v>
+        <v>5.6067055578062</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.153079564428033</v>
+        <v>5.331051149606123</v>
       </c>
       <c r="G10" t="n">
-        <v>5.786669570198366</v>
+        <v>5.868691200293355</v>
       </c>
       <c r="H10" t="n">
-        <v>6.008919626506445</v>
+        <v>6.007235847899707</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19761347951584</v>
+        <v>10.1912313841476</v>
       </c>
       <c r="G11" t="n">
-        <v>10.35469069133724</v>
+        <v>10.34990179380678</v>
       </c>
       <c r="H11" t="n">
-        <v>10.45108058676723</v>
+        <v>10.51439311754974</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.459292567643363</v>
+        <v>2.402894804584476</v>
       </c>
       <c r="G12" t="n">
-        <v>3.549460086543774</v>
+        <v>3.604950958062932</v>
       </c>
       <c r="H12" t="n">
-        <v>4.914054968677066</v>
+        <v>4.560671054560999</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.919250707850705</v>
+        <v>6.89203775756195</v>
       </c>
       <c r="G13" t="n">
-        <v>7.051275274002238</v>
+        <v>7.015606788891276</v>
       </c>
       <c r="H13" t="n">
-        <v>7.143310960388112</v>
+        <v>7.115064269816771</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.57962415786088</v>
+        <v>10.46448620302891</v>
       </c>
       <c r="G14" t="n">
-        <v>10.93091710740923</v>
+        <v>10.90480539037521</v>
       </c>
       <c r="H14" t="n">
-        <v>11.11144126256653</v>
+        <v>11.11530424714697</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.598657974744987</v>
+        <v>4.569793640453597</v>
       </c>
       <c r="G15" t="n">
-        <v>5.35476573299032</v>
+        <v>5.235547567416789</v>
       </c>
       <c r="H15" t="n">
-        <v>5.647903633928571</v>
+        <v>5.461986752800734</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.870566994791965</v>
+        <v>8.109815322773168</v>
       </c>
       <c r="G16" t="n">
-        <v>8.148473392167144</v>
+        <v>8.172816537072588</v>
       </c>
       <c r="H16" t="n">
-        <v>8.230031142837548</v>
+        <v>8.229877870601387</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.202736181454358</v>
+        <v>2.135255196999283</v>
       </c>
       <c r="G17" t="n">
-        <v>4.063987737710498</v>
+        <v>4.193534107052735</v>
       </c>
       <c r="H17" t="n">
-        <v>5.912731621541849</v>
+        <v>5.912332360788759</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.372032310469314</v>
+        <v>3.366916488222699</v>
       </c>
       <c r="G18" t="n">
-        <v>3.574029577365703</v>
+        <v>3.560918672626209</v>
       </c>
       <c r="H18" t="n">
-        <v>3.71115</v>
+        <v>3.715852023957865</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.59105600062779</v>
+        <v>2.681926737598145</v>
       </c>
       <c r="G19" t="n">
-        <v>3.038823773585626</v>
+        <v>3.112565252818547</v>
       </c>
       <c r="H19" t="n">
-        <v>3.333262857142857</v>
+        <v>3.333064953604568</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.473490410113907</v>
+        <v>5.474344370378662</v>
       </c>
       <c r="G20" t="n">
-        <v>5.947096821214966</v>
+        <v>6.110809864304645</v>
       </c>
       <c r="H20" t="n">
-        <v>7.16461666932865</v>
+        <v>7.183989728095663</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.1989569673261</v>
+        <v>128.2259845498521</v>
       </c>
       <c r="G21" t="n">
-        <v>128.6846530107072</v>
+        <v>128.6321085441714</v>
       </c>
       <c r="H21" t="n">
-        <v>129.1409228675784</v>
+        <v>128.9958978370408</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E2" t="n">
+        <v>10051</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10050</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10049</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.5008556738647</v>
+        <v>102.4910535986733</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84321199143469</v>
+        <v>1.843223965763195</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4755011259438</v>
+        <v>102.4649457340973</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02535454792096886</v>
+        <v>-0.02610786457599702</v>
       </c>
       <c r="T2" t="n">
-        <v>18.10080904613902</v>
+        <v>18.11992409737999</v>
       </c>
       <c r="U2" t="n">
-        <v>36.21098716068762</v>
+        <v>36.23815836466315</v>
       </c>
       <c r="V2" t="n">
-        <v>0.13730402631204</v>
+        <v>0.1369921709513979</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7227209269002317</v>
+        <v>-0.7232926736122587</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1373025985073482</v>
+        <v>0.1369906877961748</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.067630586302542</v>
+        <v>2.426517888726067</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.75228086932118</v>
+        <v>81.32508326697973</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.4729842937248</v>
+        <v>110.6671093622214</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E3" t="n">
+        <v>14645</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14644</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14643</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.904730690432288</v>
+        <v>4.90451492078667</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.962610388756781</v>
+        <v>4.962398064672456</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05787969832449296</v>
+        <v>0.05788314388578533</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343393949813763</v>
+        <v>1.343351698618804</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717998635694552</v>
+        <v>1.717942683829681</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7815898093477023</v>
+        <v>0.7816106772925174</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5702160724972706</v>
+        <v>0.5702573807864152</v>
       </c>
       <c r="X3" t="n">
-        <v>0.780534810288442</v>
+        <v>0.7805554376457259</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.681926737598145</v>
+        <v>2.773234183309558</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.112565252818547</v>
+        <v>3.176048235603063</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.333064953604568</v>
+        <v>3.332867332382311</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E4" t="n">
         <v>10278</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10277</v>
+        <v>10278</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.901282475430572</v>
+        <v>6.900921385483557</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.231610121807335</v>
+        <v>7.231220604812858</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3303276463767614</v>
+        <v>0.3302992193293012</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291110243873886</v>
+        <v>1.291023558153817</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680834937125557</v>
+        <v>1.680757678597118</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679798527202158</v>
+        <v>0.8679971767072123</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7380973507583055</v>
+        <v>0.7381284770828662</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472611931848205</v>
+        <v>0.8472861124323519</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.366916488222699</v>
+        <v>3.384422253922967</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.56091867262621</v>
+        <v>3.584769726558907</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.715852023957865</v>
+        <v>3.898211074023716</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301715671116421</v>
+        <v>9.301714434529531</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692542456939371</v>
+        <v>0.3692530091070477</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247528976425994</v>
+        <v>1.247523322008538</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747103496154962</v>
+        <v>1.747102549270336</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661241125905236</v>
+        <v>0.8661249692154483</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215264539899995</v>
+        <v>0.7215267558407468</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597328613659049</v>
+        <v>0.8597339928112556</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.474344370378662</v>
+        <v>5.51708388061628</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.110809864304646</v>
+        <v>6.302808704873478</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.183989728095663</v>
+        <v>7.313426455429751</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E6" t="n">
+        <v>8892</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8891</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8890</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734297694038245</v>
+        <v>6.734242098751547</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02305998551712</v>
+        <v>7.023097546037612</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2887622914788752</v>
+        <v>0.2888554472860655</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477918182791078</v>
+        <v>1.47793744942525</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906413652916855</v>
+        <v>1.906334437156575</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3040069013590891</v>
+        <v>0.3039890231951587</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979145670704907</v>
+        <v>-0.1979389038395178</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789972346659096</v>
+        <v>0.2789728237236755</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.109815322773168</v>
+        <v>8.070505681688999</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.172816537072588</v>
+        <v>8.173861621224043</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.229877870601387</v>
+        <v>8.229563139202945</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E7" t="n">
+        <v>14253</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14252</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14251</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579600799943864</v>
+        <v>5.579469618299186</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.566048773103472</v>
+        <v>5.565905171113432</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01355202684039129</v>
+        <v>-0.01356444718575447</v>
       </c>
       <c r="T7" t="n">
-        <v>1.16616665135997</v>
+        <v>1.166223998919997</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509365448752093</v>
+        <v>1.509385104359847</v>
       </c>
       <c r="V7" t="n">
-        <v>0.504976260099564</v>
+        <v>0.5049853479644074</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05330085289496467</v>
+        <v>0.05330624784357685</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028378077617733</v>
+        <v>0.502848061669809</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.318568573467931</v>
+        <v>5.462018544935806</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.698711389030464</v>
+        <v>5.744643251776314</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.840821762395835</v>
+        <v>5.841764162991098</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E8" t="n">
+        <v>9051</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9050</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9049</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.871199027516853</v>
+        <v>7.870895303867402</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454175588865096</v>
+        <v>0.6454279600570614</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.111435185849176</v>
+        <v>8.111160695324042</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2402361583323235</v>
+        <v>0.240265391456639</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445071555458688</v>
+        <v>1.444916785104116</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824839300374214</v>
+        <v>1.824713732392402</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078229254628417</v>
+        <v>0.8078452839347811</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275051627757179</v>
+        <v>0.6275500467530638</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7975901793094373</v>
+        <v>0.7976062873932794</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.331051149606123</v>
+        <v>5.647415633478073</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.868691200293356</v>
+        <v>5.930385915361997</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.007235847899707</v>
+        <v>6.007995864951111</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E9" t="n">
+        <v>13916</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13915</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13914</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.60783221934742</v>
+        <v>7.607629536471435</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.653442337410993</v>
+        <v>7.653270228557397</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0456101180635728</v>
+        <v>0.04564069208596246</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493149680774641</v>
+        <v>1.493146172080156</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94113611231637</v>
+        <v>1.941108391268673</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567456921172799</v>
+        <v>0.7567510073179226</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250490261735341</v>
+        <v>0.5250626785130629</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553239176334575</v>
+        <v>0.7553282211376101</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.569793640453597</v>
+        <v>4.649078233032491</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.235547567416789</v>
+        <v>5.230470332029357</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.461986752800734</v>
+        <v>5.384390972339166</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.6142033164755</v>
+        <v>10.61404979102657</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3091416359831298</v>
+        <v>0.3089881105341966</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053780708924853</v>
+        <v>2.053847599767464</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699535151734013</v>
+        <v>2.69960592590143</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570061988841834</v>
+        <v>0.3570025633749684</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1216322977479671</v>
+        <v>-0.1216911105643614</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3369913957655655</v>
+        <v>0.3370051949887702</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.46448620302891</v>
+        <v>10.37712508284341</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.90480539037521</v>
+        <v>10.89301841881361</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.11530424714697</v>
+        <v>11.12052953711931</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E11" t="n">
+        <v>13857</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13856</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13855</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241903428365212</v>
+        <v>5.241785832852194</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215543510106365</v>
+        <v>5.215422759440979</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02635991825884657</v>
+        <v>-0.02636307341121633</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160895298159415</v>
+        <v>1.160933460706538</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482307214084051</v>
+        <v>1.482322396540984</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429513188727555</v>
+        <v>0.429520440814215</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09179901916015254</v>
+        <v>-0.0917962374337149</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277039692586118</v>
+        <v>0.427712018262922</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.246297791267956</v>
+        <v>4.197651544662526</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.799804400336095</v>
+        <v>4.770120795470474</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.06815653950675</v>
+        <v>5.045346097511367</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E12" t="n">
+        <v>4175</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4174</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.455816199376947</v>
+        <v>7.455211667465262</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.629040317091704</v>
+        <v>7.62830164675193</v>
       </c>
       <c r="R12" t="n">
-        <v>16.60513276231278</v>
+        <v>16.57663124108408</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732241177147563</v>
+        <v>0.1730899792866687</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9112574533281755</v>
+        <v>0.9111401083850486</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191602201628676</v>
+        <v>1.191290664333026</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8334208332818538</v>
+        <v>0.8335234517591095</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6624740367373021</v>
+        <v>0.6626919710286336</v>
       </c>
       <c r="X12" t="n">
-        <v>0.831592868853439</v>
+        <v>0.831696190613247</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.311050689557547</v>
+        <v>4.378030200359611</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.090087738243642</v>
+        <v>4.994912139417712</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.6067055578062</v>
+        <v>5.593860745262397</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E13" t="n">
+        <v>6510</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6509</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6508</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.595904655808235</v>
+        <v>9.595490474727299</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02086341305139</v>
+        <v>10.02054263555949</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4249587572431569</v>
+        <v>0.4250521608321859</v>
       </c>
       <c r="T13" t="n">
-        <v>1.688869355926071</v>
+        <v>1.688660709577777</v>
       </c>
       <c r="U13" t="n">
-        <v>2.147400579638552</v>
+        <v>2.147182490078491</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234350116707866</v>
+        <v>0.8234586875733197</v>
       </c>
       <c r="W13" t="n">
-        <v>0.64922428757257</v>
+        <v>0.6492714350811818</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8101965554539312</v>
+        <v>0.8102051036391895</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.571138065045963</v>
+        <v>7.839978579878999</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.230097491675398</v>
+        <v>8.319354533448962</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.494502193532433</v>
+        <v>8.494758654336742</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E14" t="n">
+        <v>14097</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14096</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14095</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.124695814118482</v>
+        <v>8.124527348183882</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195730078865822</v>
+        <v>8.195573718418753</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07103426474733879</v>
+        <v>0.0710463702348717</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755263291546631</v>
+        <v>1.755140083227416</v>
       </c>
       <c r="U14" t="n">
-        <v>2.281010160517434</v>
+        <v>2.280850902659821</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809815492091059</v>
+        <v>0.7810030252095773</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5657002123847674</v>
+        <v>0.5657445480840001</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805922268437175</v>
+        <v>0.780613390853478</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.89203775756195</v>
+        <v>6.87621114400543</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.015606788891276</v>
+        <v>6.981456111879282</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.115064269816771</v>
+        <v>7.085727175358612</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81978460782879</v>
+        <v>11.81966328807603</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1441027751979873</v>
+        <v>-0.1442240949507529</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052534085994658</v>
+        <v>2.052577844041384</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698303192985759</v>
+        <v>2.698394639891543</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950088222335779</v>
+        <v>0.7950010474465888</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6094041811758959</v>
+        <v>0.6093777057342924</v>
       </c>
       <c r="X15" t="n">
-        <v>0.786541936320361</v>
+        <v>0.7865431593488502</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.182005957316726</v>
+        <v>9.276455870179927</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.34025454851238</v>
+        <v>9.362101593804628</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.442735567733504</v>
+        <v>9.444125717637942</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E16" t="n">
+        <v>9860</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9859</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9858</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.35984875228241</v>
+        <v>8.359637285728777</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622217165538155</v>
+        <v>8.622071608424301</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2623684132557443</v>
+        <v>0.2624343226955258</v>
       </c>
       <c r="T16" t="n">
-        <v>3.599280260997939</v>
+        <v>3.599741116385465</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08229402268574</v>
+        <v>11.08192104281137</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04120138954645296</v>
+        <v>0.0411748367221165</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6108114965973224</v>
+        <v>-0.6108571491391996</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02454168872393381</v>
+        <v>0.02451547150320377</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.3660190923773</v>
+        <v>11.27607336208178</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.65315213957853</v>
+        <v>11.61393117915691</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.76773781303927</v>
+        <v>11.76703357131573</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E17" t="n">
+        <v>2404</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2403</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2402</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.460270607826811</v>
+        <v>6.458628797336663</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.824721293557298</v>
+        <v>6.822690758867225</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3644506857304872</v>
+        <v>0.3640619615305619</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008463242441171</v>
+        <v>2.008269539647686</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54646566037916</v>
+        <v>2.546209102305931</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5393218422050328</v>
+        <v>0.5396725545656015</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05750912187682178</v>
+        <v>0.05819339909441512</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5358762600090314</v>
+        <v>0.5362296127065416</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.402894804584476</v>
+        <v>2.399996550806335</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.604950958062932</v>
+        <v>3.761140555564833</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.560671054560999</v>
+        <v>6.239740715078233</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E18" t="n">
+        <v>3263</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3262</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3261</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.460979454155168</v>
+        <v>6.460061005518086</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.657161882793937</v>
+        <v>6.656215976174077</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1961824286387681</v>
+        <v>0.1961549706559906</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095251818518168</v>
+        <v>1.095518372994385</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483663117102574</v>
+        <v>1.483900274258341</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6094406904017209</v>
+        <v>0.609547804868013</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2342916578230491</v>
+        <v>0.2345446315318038</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6063458588538084</v>
+        <v>0.606447271492523</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.135255196999283</v>
+        <v>2.134439055766674</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.193534107052736</v>
+        <v>4.179863892444969</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.912332360788759</v>
+        <v>6.19597913054063</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E19" t="n">
+        <v>7217</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7216</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7215</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.30685779625779</v>
+        <v>10.30567128603104</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10697475118651</v>
+        <v>11.10621277860371</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.800116954928715</v>
+        <v>0.8005414925726649</v>
       </c>
       <c r="T19" t="n">
-        <v>2.066397632108266</v>
+        <v>2.06718803726769</v>
       </c>
       <c r="U19" t="n">
-        <v>2.793209891890844</v>
+        <v>2.794339894005939</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7274813212720866</v>
+        <v>0.7273948622700332</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4718287771833439</v>
+        <v>0.4716914047012756</v>
       </c>
       <c r="X19" t="n">
-        <v>0.677526386373087</v>
+        <v>0.6773786109761513</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.406918999779862</v>
+        <v>8.350954952573586</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.795153426474574</v>
+        <v>8.808300256499805</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.095846627747099</v>
+        <v>9.075423083578681</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E20" t="n">
+        <v>10667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10666</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10665</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85286987409384</v>
+        <v>13.85250114449755</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.491070663811564</v>
+        <v>7.49114122681883</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22928669984556</v>
+        <v>14.22888147138653</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3764168257517222</v>
+        <v>0.3763803268889866</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254335622475113</v>
+        <v>1.254231797830305</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646200893664892</v>
+        <v>1.646108929291715</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936490525384038</v>
+        <v>0.8936642293792405</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7791979891043024</v>
+        <v>0.7792280428224564</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888211635401654</v>
+        <v>0.8888381935849181</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.1912313841476</v>
+        <v>10.20154892152165</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.34990179380678</v>
+        <v>10.37330560037332</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.51439311754974</v>
+        <v>10.71140452268855</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16714</v>
+        <v>16715</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9712489058597</v>
+        <v>130.9712951052367</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046793016483569</v>
+        <v>0.1047255010254007</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971701887248199</v>
+        <v>0.7971766235702236</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045750089702775</v>
+        <v>1.045759745743343</v>
       </c>
       <c r="V21" t="n">
-        <v>0.865114454554743</v>
+        <v>0.8651122917391209</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311704747413573</v>
+        <v>0.7311655101885222</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643640514111712</v>
+        <v>0.8643611691619739</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.2259845498521</v>
+        <v>128.3234730798681</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.6321085441714</v>
+        <v>128.6272545981989</v>
       </c>
       <c r="AA21" t="n">
-        <v>128.9958978370408</v>
+        <v>128.864375861423</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.406918999779862</v>
+        <v>8.350954952573586</v>
       </c>
       <c r="G2" t="n">
-        <v>8.795153426474574</v>
+        <v>8.808300256499807</v>
       </c>
       <c r="H2" t="n">
-        <v>9.095846627747099</v>
+        <v>9.075423083578681</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.318568573467931</v>
+        <v>5.462018544935806</v>
       </c>
       <c r="G3" t="n">
-        <v>5.698711389030464</v>
+        <v>5.744643251776314</v>
       </c>
       <c r="H3" t="n">
-        <v>5.840821762395835</v>
+        <v>5.841764162991098</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.246297791267956</v>
+        <v>4.197651544662526</v>
       </c>
       <c r="G4" t="n">
-        <v>4.799804400336095</v>
+        <v>4.770120795470474</v>
       </c>
       <c r="H4" t="n">
-        <v>5.06815653950675</v>
+        <v>5.045346097511367</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.3660190923773</v>
+        <v>11.27607336208178</v>
       </c>
       <c r="G5" t="n">
-        <v>11.65315213957853</v>
+        <v>11.61393117915691</v>
       </c>
       <c r="H5" t="n">
-        <v>11.76773781303927</v>
+        <v>11.76703357131573</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>4.067630586302542</v>
+        <v>2.426517888726067</v>
       </c>
       <c r="G6" t="n">
-        <v>94.75228086932118</v>
+        <v>81.32508326697975</v>
       </c>
       <c r="H6" t="n">
-        <v>110.4729842937248</v>
+        <v>110.6671093622214</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.182005957316726</v>
+        <v>9.276455870179927</v>
       </c>
       <c r="G7" t="n">
-        <v>9.34025454851238</v>
+        <v>9.362101593804628</v>
       </c>
       <c r="H7" t="n">
-        <v>9.442735567733504</v>
+        <v>9.444125717637942</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.571138065045963</v>
+        <v>7.839978579878999</v>
       </c>
       <c r="G8" t="n">
-        <v>8.230097491675398</v>
+        <v>8.319354533448962</v>
       </c>
       <c r="H8" t="n">
-        <v>8.494502193532433</v>
+        <v>8.494758654336742</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.311050689557547</v>
+        <v>4.378030200359611</v>
       </c>
       <c r="G9" t="n">
-        <v>5.090087738243642</v>
+        <v>4.994912139417712</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6067055578062</v>
+        <v>5.593860745262397</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.331051149606123</v>
+        <v>5.647415633478073</v>
       </c>
       <c r="G10" t="n">
-        <v>5.868691200293355</v>
+        <v>5.930385915361997</v>
       </c>
       <c r="H10" t="n">
-        <v>6.007235847899707</v>
+        <v>6.007995864951111</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.1912313841476</v>
+        <v>10.20154892152165</v>
       </c>
       <c r="G11" t="n">
-        <v>10.34990179380678</v>
+        <v>10.37330560037332</v>
       </c>
       <c r="H11" t="n">
-        <v>10.51439311754974</v>
+        <v>10.71140452268855</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.402894804584476</v>
+        <v>2.399996550806335</v>
       </c>
       <c r="G12" t="n">
-        <v>3.604950958062932</v>
+        <v>3.761140555564833</v>
       </c>
       <c r="H12" t="n">
-        <v>4.560671054560999</v>
+        <v>6.239740715078233</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.89203775756195</v>
+        <v>6.87621114400543</v>
       </c>
       <c r="G13" t="n">
-        <v>7.015606788891276</v>
+        <v>6.981456111879282</v>
       </c>
       <c r="H13" t="n">
-        <v>7.115064269816771</v>
+        <v>7.085727175358612</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.46448620302891</v>
+        <v>10.37712508284341</v>
       </c>
       <c r="G14" t="n">
-        <v>10.90480539037521</v>
+        <v>10.89301841881361</v>
       </c>
       <c r="H14" t="n">
-        <v>11.11530424714697</v>
+        <v>11.12052953711931</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.569793640453597</v>
+        <v>4.649078233032491</v>
       </c>
       <c r="G15" t="n">
-        <v>5.235547567416789</v>
+        <v>5.230470332029356</v>
       </c>
       <c r="H15" t="n">
-        <v>5.461986752800734</v>
+        <v>5.384390972339166</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.109815322773168</v>
+        <v>8.070505681688999</v>
       </c>
       <c r="G16" t="n">
-        <v>8.172816537072588</v>
+        <v>8.173861621224043</v>
       </c>
       <c r="H16" t="n">
-        <v>8.229877870601387</v>
+        <v>8.229563139202945</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.135255196999283</v>
+        <v>2.134439055766674</v>
       </c>
       <c r="G17" t="n">
-        <v>4.193534107052735</v>
+        <v>4.179863892444969</v>
       </c>
       <c r="H17" t="n">
-        <v>5.912332360788759</v>
+        <v>6.19597913054063</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.366916488222699</v>
+        <v>3.384422253922967</v>
       </c>
       <c r="G18" t="n">
-        <v>3.560918672626209</v>
+        <v>3.584769726558908</v>
       </c>
       <c r="H18" t="n">
-        <v>3.715852023957865</v>
+        <v>3.898211074023716</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.681926737598145</v>
+        <v>2.773234183309558</v>
       </c>
       <c r="G19" t="n">
-        <v>3.112565252818547</v>
+        <v>3.176048235603063</v>
       </c>
       <c r="H19" t="n">
-        <v>3.333064953604568</v>
+        <v>3.332867332382311</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.474344370378662</v>
+        <v>5.51708388061628</v>
       </c>
       <c r="G20" t="n">
-        <v>6.110809864304645</v>
+        <v>6.302808704873478</v>
       </c>
       <c r="H20" t="n">
-        <v>7.183989728095663</v>
+        <v>7.313426455429751</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.2259845498521</v>
+        <v>128.3234730798681</v>
       </c>
       <c r="G21" t="n">
-        <v>128.6321085441714</v>
+        <v>128.6272545981989</v>
       </c>
       <c r="H21" t="n">
-        <v>128.9958978370408</v>
+        <v>128.864375861423</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E2" t="n">
+        <v>10052</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10051</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10050</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.4910535986733</v>
+        <v>102.481249494246</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843223965763195</v>
+        <v>1.843235923022096</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4649457340973</v>
+        <v>102.459386141239</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02610786457599702</v>
+        <v>-0.02186335300705931</v>
       </c>
       <c r="T2" t="n">
-        <v>18.11992409737999</v>
+        <v>18.13403613434937</v>
       </c>
       <c r="U2" t="n">
-        <v>36.23815836466315</v>
+        <v>36.26199059882097</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1369921709513979</v>
+        <v>0.1367504683477259</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7232926736122587</v>
+        <v>-0.7235466648036573</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1369906877961748</v>
+        <v>0.1367487441465234</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.426517888726067</v>
+        <v>2.583286001619911</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.32508326697973</v>
+        <v>56.69954153317364</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.6671093622214</v>
+        <v>108.7273484550092</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E3" t="n">
+        <v>14646</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14645</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14644</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.90451492078667</v>
+        <v>4.90430310686241</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.962398064672456</v>
+        <v>4.96219728218702</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05788314388578533</v>
+        <v>0.05789417532460974</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343351698618804</v>
+        <v>1.343313385306761</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717942683829681</v>
+        <v>1.71788807469957</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816106772925174</v>
+        <v>0.7816298092199909</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5702573807864152</v>
+        <v>0.5702964681661764</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7805554376457259</v>
+        <v>0.7805739852192279</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.773234183309558</v>
+        <v>2.877116001425517</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.176048235603063</v>
+        <v>3.228692334345407</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.332867332382311</v>
+        <v>3.332669992872416</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E4" t="n">
-        <v>10278</v>
+        <v>10280</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10278</v>
+        <v>10279</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.900921385483557</v>
+        <v>6.900522181146026</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.231220604812858</v>
+        <v>7.230761736340148</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3302992193293012</v>
+        <v>0.3302395551941215</v>
       </c>
       <c r="T4" t="n">
-        <v>1.291023558153817</v>
+        <v>1.29087809953994</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680757678597118</v>
+        <v>1.680594190094582</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8679971767072123</v>
+        <v>0.8680312204465769</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7381284770828662</v>
+        <v>0.7381935888536524</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472861124323519</v>
+        <v>0.8473258202150066</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.384422253922967</v>
+        <v>3.369185727776293</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.584769726558907</v>
+        <v>3.635243421031296</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.898211074023716</v>
+        <v>4.24949572344975</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301714434529531</v>
+        <v>9.301712963166697</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692530091070477</v>
+        <v>0.3692515377442127</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247523322008538</v>
+        <v>1.247516483356742</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747102549270336</v>
+        <v>1.747101206520999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661249692154483</v>
+        <v>0.8661258883376226</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215267558407468</v>
+        <v>0.7215271838861645</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597339928112556</v>
+        <v>0.8597351939414846</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.51708388061628</v>
+        <v>5.593470215045711</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.302808704873478</v>
+        <v>6.36416627735344</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.313426455429751</v>
+        <v>7.012542743372321</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E6" t="n">
+        <v>8893</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8892</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8891</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734242098751547</v>
+        <v>6.734226439496177</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023097546037612</v>
+        <v>7.023175957557886</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2888554472860655</v>
+        <v>0.2889495180617102</v>
       </c>
       <c r="T6" t="n">
-        <v>1.47793744942525</v>
+        <v>1.47791906485628</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906334437156575</v>
+        <v>1.906235360877683</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039890231951587</v>
+        <v>0.303982465191331</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979389038395178</v>
+        <v>-0.1979482492764273</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789728237236755</v>
+        <v>0.2789601115233215</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.070505681688999</v>
+        <v>8.012608637985638</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.173861621224043</v>
+        <v>8.15778710558819</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.229563139202945</v>
+        <v>8.228725600018485</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E7" t="n">
+        <v>14254</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14253</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14252</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579469618299186</v>
+        <v>5.579327229355223</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565905171113432</v>
+        <v>5.565766053606476</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01356444718575447</v>
+        <v>-0.01356117574874807</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166223998919997</v>
+        <v>1.166299728502376</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509385104359847</v>
+        <v>1.509428598571448</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049853479644074</v>
+        <v>0.5049819211791622</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05330624784357685</v>
+        <v>0.05329893755491366</v>
       </c>
       <c r="X7" t="n">
-        <v>0.502848061669809</v>
+        <v>0.5028447358699206</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.462018544935806</v>
+        <v>5.598482185738986</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.744643251776314</v>
+        <v>5.768978471367166</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.841764162991098</v>
+        <v>5.840596562314121</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E8" t="n">
+        <v>9052</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9051</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9050</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.870895303867402</v>
+        <v>7.870598276433544</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454279600570614</v>
+        <v>0.6454383464005702</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.111160695324042</v>
+        <v>8.110910259582569</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.240265391456639</v>
+        <v>0.2403119831490253</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444916785104116</v>
+        <v>1.444784302945366</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824713732392402</v>
+        <v>1.824592651108636</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078452839347811</v>
+        <v>0.8078655327741717</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275500467530638</v>
+        <v>0.6275915897050683</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976062873932794</v>
+        <v>0.797618440077781</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.647415633478073</v>
+        <v>5.825861228001626</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.930385915361997</v>
+        <v>5.958092147533042</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.007995864951111</v>
+        <v>6.007529284571065</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E9" t="n">
+        <v>13917</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13916</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13915</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.607629536471435</v>
+        <v>7.607445027306698</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.653270228557397</v>
+        <v>7.653089893316726</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04564069208596246</v>
+        <v>0.0456448660100288</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493146172080156</v>
+        <v>1.493132284448645</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941108391268673</v>
+        <v>1.941068160304469</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567510073179226</v>
+        <v>0.7567576854375527</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250626785130629</v>
+        <v>0.525076595571804</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553282211376101</v>
+        <v>0.7553346133420235</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.649078233032491</v>
+        <v>4.757190318184698</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.230470332029357</v>
+        <v>5.137240767872029</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.384390972339166</v>
+        <v>5.247721048979731</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61404979102657</v>
+        <v>10.61390047726996</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3089881105341966</v>
+        <v>0.3088387967775917</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053847599767464</v>
+        <v>2.053914105632406</v>
       </c>
       <c r="U10" t="n">
-        <v>2.69960592590143</v>
+        <v>2.699675131142107</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3570025633749684</v>
+        <v>0.3569981007876645</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1216911105643614</v>
+        <v>-0.1217486211050827</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370051949887702</v>
+        <v>0.3370173969036646</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.37712508284341</v>
+        <v>10.43811025711857</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.89301841881361</v>
+        <v>10.87086476277097</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12052953711931</v>
+        <v>11.12145171966188</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E11" t="n">
+        <v>13858</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13857</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13856</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241785832852194</v>
+        <v>5.241651656202642</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215422759440979</v>
+        <v>5.215267419465553</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02636307341121633</v>
+        <v>-0.02638423673708869</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160933460706538</v>
+        <v>1.160998107787398</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482322396540984</v>
+        <v>1.482368182032606</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429520440814215</v>
+        <v>0.4295306123462624</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0917962374337149</v>
+        <v>-0.09180714562991987</v>
       </c>
       <c r="X11" t="n">
-        <v>0.427712018262922</v>
+        <v>0.4277243593388677</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.197651544662526</v>
+        <v>4.337533167800305</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.770120795470474</v>
+        <v>4.769623737036055</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.045346097511367</v>
+        <v>4.953531964150481</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E12" t="n">
+        <v>4176</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4175</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4174</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.455211667465262</v>
+        <v>7.454546946107785</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.62830164675193</v>
+        <v>7.627472102032335</v>
       </c>
       <c r="R12" t="n">
-        <v>16.57663124108408</v>
+        <v>16.54817034925146</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1730899792866687</v>
+        <v>0.1729251559245506</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9111401083850486</v>
+        <v>0.9111373235762088</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191290664333026</v>
+        <v>1.191115690456324</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8335234517591095</v>
+        <v>0.8336023265513358</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6626919710286336</v>
+        <v>0.6628580839697114</v>
       </c>
       <c r="X12" t="n">
-        <v>0.831696190613247</v>
+        <v>0.8317778166895997</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.378030200359611</v>
+        <v>4.521545383411976</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.994912139417712</v>
+        <v>4.923881690244353</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.593860745262397</v>
+        <v>5.504792721931376</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E13" t="n">
         <v>6510</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6509</v>
+        <v>6510</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.595490474727299</v>
+        <v>9.595077956989247</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02054263555949</v>
+        <v>10.02007202111219</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4250521608321859</v>
+        <v>0.424994064122947</v>
       </c>
       <c r="T13" t="n">
-        <v>1.688660709577777</v>
+        <v>1.68851178708555</v>
       </c>
       <c r="U13" t="n">
-        <v>2.147182490078491</v>
+        <v>2.147017245730766</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234586875733197</v>
+        <v>0.8234771766656117</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6492714350811818</v>
+        <v>0.649301096083388</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102051036391895</v>
+        <v>0.8102326557418339</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.839978579878999</v>
+        <v>8.065586442141926</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.319354533448962</v>
+        <v>8.383361521500284</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.494758654336742</v>
+        <v>8.495022117978092</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E14" t="n">
+        <v>14098</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14097</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14096</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.124527348183882</v>
+        <v>8.124358906150244</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195573718418753</v>
+        <v>8.195417961343562</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0710463702348717</v>
+        <v>0.0710590551933165</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755140083227416</v>
+        <v>1.755017873394915</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280850902659821</v>
+        <v>2.280693704494803</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810030252095773</v>
+        <v>0.7810240830539958</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5657445480840001</v>
+        <v>0.5657880988627784</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780613390853478</v>
+        <v>0.7806341290734633</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.87621114400543</v>
+        <v>6.845458311394886</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.981456111879282</v>
+        <v>6.94676594082581</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.085727175358612</v>
+        <v>7.073063921714345</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81966328807603</v>
+        <v>11.81953759033083</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1442240949507529</v>
+        <v>-0.1443497926959531</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052577844041384</v>
+        <v>2.052609239280902</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698394639891543</v>
+        <v>2.698479880073029</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7950010474465888</v>
+        <v>0.7949943160295101</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093777057342924</v>
+        <v>0.6093530264374449</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865431593488502</v>
+        <v>0.7865454471448668</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.276455870179927</v>
+        <v>9.303818961930858</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.362101593804628</v>
+        <v>9.37164030231037</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.444125717637942</v>
+        <v>9.446765737782485</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E16" t="n">
+        <v>9861</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9860</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9859</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.359637285728777</v>
+        <v>8.359405070993914</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622071608424301</v>
+        <v>8.621916695070833</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2624343226955258</v>
+        <v>0.2625116240769177</v>
       </c>
       <c r="T16" t="n">
-        <v>3.599741116385465</v>
+        <v>3.600235143452538</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08192104281137</v>
+        <v>11.08156889699253</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0411748367221165</v>
+        <v>0.04114562929006593</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6108571491391996</v>
+        <v>-0.6109069202465907</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02451547150320377</v>
+        <v>0.02448656030246354</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.27607336208178</v>
+        <v>11.26054850271443</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.61393117915691</v>
+        <v>11.55389589734752</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.76703357131573</v>
+        <v>11.76585130356167</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2404</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2403</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.458628797336663</v>
+        <v>6.456961314475874</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.822690758867225</v>
+        <v>6.820661382702284</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3640619615305619</v>
+        <v>0.3637000682264108</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008269539647686</v>
+        <v>2.008157746263673</v>
       </c>
       <c r="U17" t="n">
-        <v>2.546209102305931</v>
+        <v>2.545999193342476</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5396725545656015</v>
+        <v>0.5400169493400584</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05819339909441512</v>
+        <v>0.05887067345841435</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5362296127065416</v>
+        <v>0.5365761918165313</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.399996550806335</v>
+        <v>2.378896850394509</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.761140555564833</v>
+        <v>3.339065124335443</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.239740715078233</v>
+        <v>3.922562533813659</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E18" t="n">
+        <v>3264</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3263</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3262</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.460061005518086</v>
+        <v>6.459130095004596</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.656215976174077</v>
+        <v>6.655143025958949</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1961549706559906</v>
+        <v>0.1960129309543526</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095518372994385</v>
+        <v>1.095674811844818</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483900274258341</v>
+        <v>1.484058416695598</v>
       </c>
       <c r="V18" t="n">
-        <v>0.609547804868013</v>
+        <v>0.609737777213237</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2345446315318038</v>
+        <v>0.2348988389756635</v>
       </c>
       <c r="X18" t="n">
-        <v>0.606447271492523</v>
+        <v>0.6066426325300771</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.134439055766674</v>
+        <v>2.115538058806822</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.179863892444969</v>
+        <v>3.433021466960768</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.19597913054063</v>
+        <v>5.020324398029068</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E19" t="n">
+        <v>7218</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7217</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7216</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.30567128603104</v>
+        <v>10.30447540529306</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10621277860371</v>
+        <v>11.10543809482749</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8005414925726649</v>
+        <v>0.8009626895344254</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06718803726769</v>
+        <v>2.067978524369202</v>
       </c>
       <c r="U19" t="n">
-        <v>2.794339894005939</v>
+        <v>2.795479855084975</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7273948622700332</v>
+        <v>0.7273088515451878</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4716914047012756</v>
+        <v>0.4715560218232274</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6773786109761513</v>
+        <v>0.6772304813266351</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.350954952573586</v>
+        <v>8.328549515248374</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.808300256499805</v>
+        <v>9.302449412746499</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.075423083578681</v>
+        <v>12.59294355997376</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E20" t="n">
+        <v>10668</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>10667</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10666</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85250114449755</v>
+        <v>13.85212193749047</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.49114122681883</v>
+        <v>7.491211689237349</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22888147138653</v>
+        <v>14.22845575497522</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3763803268889866</v>
+        <v>0.376333817484747</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254231797830305</v>
+        <v>1.254125935789654</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646108929291715</v>
+        <v>1.646013889143072</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936642293792405</v>
+        <v>0.8936806244940799</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792280428224564</v>
+        <v>0.7792604257404464</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888381935849181</v>
+        <v>0.8888572368721258</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.20154892152165</v>
+        <v>10.19203103202261</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.37330560037332</v>
+        <v>10.41588037751531</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.71140452268855</v>
+        <v>10.91031824691485</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16715</v>
+        <v>16716</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9712951052367</v>
+        <v>130.971350037445</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1047255010254007</v>
+        <v>0.1047804332336818</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971766235702236</v>
+        <v>0.7971824603321637</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045759745743343</v>
+        <v>1.045765079437028</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651122917391209</v>
+        <v>0.8651110107063023</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311655101885222</v>
+        <v>0.7311627679057313</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643611691619739</v>
+        <v>0.864358756357227</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.3234730798681</v>
+        <v>128.5088281859439</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.6272545981989</v>
+        <v>128.709305883753</v>
       </c>
       <c r="AA21" t="n">
-        <v>128.864375861423</v>
+        <v>129.64772498994</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.350954952573586</v>
+        <v>8.328549515248374</v>
       </c>
       <c r="G2" t="n">
-        <v>8.808300256499807</v>
+        <v>9.302449412746499</v>
       </c>
       <c r="H2" t="n">
-        <v>9.075423083578681</v>
+        <v>12.59294355997376</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.462018544935806</v>
+        <v>5.598482185738986</v>
       </c>
       <c r="G3" t="n">
-        <v>5.744643251776314</v>
+        <v>5.768978471367167</v>
       </c>
       <c r="H3" t="n">
-        <v>5.841764162991098</v>
+        <v>5.840596562314121</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.197651544662526</v>
+        <v>4.337533167800305</v>
       </c>
       <c r="G4" t="n">
-        <v>4.770120795470474</v>
+        <v>4.769623737036055</v>
       </c>
       <c r="H4" t="n">
-        <v>5.045346097511367</v>
+        <v>4.953531964150481</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.27607336208178</v>
+        <v>11.26054850271443</v>
       </c>
       <c r="G5" t="n">
-        <v>11.61393117915691</v>
+        <v>11.55389589734752</v>
       </c>
       <c r="H5" t="n">
-        <v>11.76703357131573</v>
+        <v>11.76585130356167</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.426517888726067</v>
+        <v>2.583286001619911</v>
       </c>
       <c r="G6" t="n">
-        <v>81.32508326697975</v>
+        <v>56.69954153317364</v>
       </c>
       <c r="H6" t="n">
-        <v>110.6671093622214</v>
+        <v>108.7273484550092</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.276455870179927</v>
+        <v>9.303818961930858</v>
       </c>
       <c r="G7" t="n">
-        <v>9.362101593804628</v>
+        <v>9.37164030231037</v>
       </c>
       <c r="H7" t="n">
-        <v>9.444125717637942</v>
+        <v>9.446765737782485</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.839978579878999</v>
+        <v>8.065586442141926</v>
       </c>
       <c r="G8" t="n">
-        <v>8.319354533448962</v>
+        <v>8.383361521500284</v>
       </c>
       <c r="H8" t="n">
-        <v>8.494758654336742</v>
+        <v>8.495022117978092</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.378030200359611</v>
+        <v>4.521545383411976</v>
       </c>
       <c r="G9" t="n">
-        <v>4.994912139417712</v>
+        <v>4.923881690244353</v>
       </c>
       <c r="H9" t="n">
-        <v>5.593860745262397</v>
+        <v>5.504792721931376</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.647415633478073</v>
+        <v>5.825861228001626</v>
       </c>
       <c r="G10" t="n">
-        <v>5.930385915361997</v>
+        <v>5.958092147533042</v>
       </c>
       <c r="H10" t="n">
-        <v>6.007995864951111</v>
+        <v>6.007529284571065</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.20154892152165</v>
+        <v>10.19203103202261</v>
       </c>
       <c r="G11" t="n">
-        <v>10.37330560037332</v>
+        <v>10.41588037751531</v>
       </c>
       <c r="H11" t="n">
-        <v>10.71140452268855</v>
+        <v>10.91031824691485</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.399996550806335</v>
+        <v>2.378896850394509</v>
       </c>
       <c r="G12" t="n">
-        <v>3.761140555564833</v>
+        <v>3.339065124335443</v>
       </c>
       <c r="H12" t="n">
-        <v>6.239740715078233</v>
+        <v>3.922562533813659</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.87621114400543</v>
+        <v>6.845458311394886</v>
       </c>
       <c r="G13" t="n">
-        <v>6.981456111879282</v>
+        <v>6.946765940825811</v>
       </c>
       <c r="H13" t="n">
-        <v>7.085727175358612</v>
+        <v>7.073063921714345</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.37712508284341</v>
+        <v>10.43811025711857</v>
       </c>
       <c r="G14" t="n">
-        <v>10.89301841881361</v>
+        <v>10.87086476277097</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12052953711931</v>
+        <v>11.12145171966188</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.649078233032491</v>
+        <v>4.757190318184698</v>
       </c>
       <c r="G15" t="n">
-        <v>5.230470332029356</v>
+        <v>5.137240767872029</v>
       </c>
       <c r="H15" t="n">
-        <v>5.384390972339166</v>
+        <v>5.247721048979731</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.070505681688999</v>
+        <v>8.012608637985638</v>
       </c>
       <c r="G16" t="n">
-        <v>8.173861621224043</v>
+        <v>8.15778710558819</v>
       </c>
       <c r="H16" t="n">
-        <v>8.229563139202945</v>
+        <v>8.228725600018485</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.134439055766674</v>
+        <v>2.115538058806822</v>
       </c>
       <c r="G17" t="n">
-        <v>4.179863892444969</v>
+        <v>3.433021466960768</v>
       </c>
       <c r="H17" t="n">
-        <v>6.19597913054063</v>
+        <v>5.020324398029068</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.384422253922967</v>
+        <v>3.369185727776293</v>
       </c>
       <c r="G18" t="n">
-        <v>3.584769726558908</v>
+        <v>3.635243421031296</v>
       </c>
       <c r="H18" t="n">
-        <v>3.898211074023716</v>
+        <v>4.24949572344975</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.773234183309558</v>
+        <v>2.877116001425517</v>
       </c>
       <c r="G19" t="n">
-        <v>3.176048235603063</v>
+        <v>3.228692334345407</v>
       </c>
       <c r="H19" t="n">
-        <v>3.332867332382311</v>
+        <v>3.332669992872416</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.51708388061628</v>
+        <v>5.593470215045711</v>
       </c>
       <c r="G20" t="n">
-        <v>6.302808704873478</v>
+        <v>6.364166277353441</v>
       </c>
       <c r="H20" t="n">
-        <v>7.313426455429751</v>
+        <v>7.012542743372321</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.3234730798681</v>
+        <v>128.5088281859439</v>
       </c>
       <c r="G21" t="n">
-        <v>128.6272545981989</v>
+        <v>128.709305883753</v>
       </c>
       <c r="H21" t="n">
-        <v>128.864375861423</v>
+        <v>129.64772498994</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E2" t="n">
         <v>10052</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10051</v>
+        <v>10052</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.481249494246</v>
+        <v>102.4714473404961</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843235923022096</v>
+        <v>1.843219373219373</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.459386141239</v>
+        <v>102.4592668373628</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02186335300705931</v>
+        <v>-0.0121805031332532</v>
       </c>
       <c r="T2" t="n">
-        <v>18.13403613434937</v>
+        <v>18.1428937388648</v>
       </c>
       <c r="U2" t="n">
-        <v>36.26199059882097</v>
+        <v>36.27497469258412</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1367504683477259</v>
+        <v>0.1366153743547817</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7235466648036573</v>
+        <v>-0.7227718303496047</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1367487441465234</v>
+        <v>0.1366122539891454</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.583286001619911</v>
+        <v>2.584782049352356</v>
       </c>
       <c r="Z2" t="n">
-        <v>56.69954153317364</v>
+        <v>37.57940285659121</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.7273484550092</v>
+        <v>108.2796199243394</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E3" t="n">
         <v>14646</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14645</v>
+        <v>14646</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.90430310686241</v>
+        <v>4.904097978970367</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.96219728218702</v>
+        <v>4.96199448417351</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05789417532460974</v>
+        <v>0.05789650520314271</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343313385306761</v>
+        <v>1.343295876539647</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71788807469957</v>
+        <v>1.717855773593011</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816298092199909</v>
+        <v>0.7816439540646006</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5702964681661764</v>
+        <v>0.5703218429718049</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7805739852192279</v>
+        <v>0.7805884956591473</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.877116001425517</v>
+        <v>3.015234033605555</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.228692334345407</v>
+        <v>3.270117731004996</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.332669992872416</v>
+        <v>3.333615384615384</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E4" t="n">
         <v>10280</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10279</v>
+        <v>10280</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.900522181146026</v>
+        <v>6.90011843385214</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230761736340148</v>
+        <v>7.230360874825341</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3302395551941215</v>
+        <v>0.3302424409732014</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29087809953994</v>
+        <v>1.290827430398232</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680594190094582</v>
+        <v>1.680527533648698</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8680312204465769</v>
+        <v>0.8680506067487522</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7381935888536524</v>
+        <v>0.7382295500790974</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473258202150066</v>
+        <v>0.8473440117423383</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.369185727776293</v>
+        <v>3.365249287749288</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.635243421031296</v>
+        <v>3.647827565708281</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.24949572344975</v>
+        <v>4.239014271652785</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301712963166697</v>
+        <v>9.301710663551205</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692515377442127</v>
+        <v>0.3692492381287221</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247516483356742</v>
+        <v>1.247509177345047</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747101206520999</v>
+        <v>1.747100166194453</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661258883376226</v>
+        <v>0.8661267642600937</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215271838861645</v>
+        <v>0.7215275155241665</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597351939414846</v>
+        <v>0.8597363931055667</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.593470215045711</v>
+        <v>5.748739316239316</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.36416627735344</v>
+        <v>6.487300663300981</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.012542743372321</v>
+        <v>7.012691344401359</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E6" t="n">
         <v>8893</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8892</v>
+        <v>8893</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734226439496177</v>
+        <v>6.734223715281683</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023175957557886</v>
+        <v>7.023169735252189</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889495180617102</v>
+        <v>0.288946019970507</v>
       </c>
       <c r="T6" t="n">
-        <v>1.47791906485628</v>
+        <v>1.477921843419235</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906235360877683</v>
+        <v>1.906180360514116</v>
       </c>
       <c r="V6" t="n">
-        <v>0.303982465191331</v>
+        <v>0.3039764906945409</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979482492764273</v>
+        <v>-0.1980138099653554</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789601115233215</v>
+        <v>0.2789676084211415</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.012608637985638</v>
+        <v>8.008350402213232</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.15778710558819</v>
+        <v>8.143925373025642</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.228725600018485</v>
+        <v>8.229288873465638</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E7" t="n">
         <v>14254</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14253</v>
+        <v>14254</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579327229355223</v>
+        <v>5.579188368177354</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565766053606476</v>
+        <v>5.565695236859315</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01356117574874807</v>
+        <v>-0.01349313131803832</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166299728502376</v>
+        <v>1.166361436400764</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509428598571448</v>
+        <v>1.509470585823442</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049819211791622</v>
+        <v>0.5049635214732924</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05329893755491366</v>
+        <v>0.05328796334536745</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028447358699206</v>
+        <v>0.502824067474451</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.598482185738986</v>
+        <v>5.678638706652867</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.768978471367166</v>
+        <v>5.780611730740095</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.840596562314121</v>
+        <v>5.84112040880445</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E8" t="n">
         <v>9052</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9051</v>
+        <v>9052</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.870598276433544</v>
+        <v>7.870312085726911</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454383464005702</v>
+        <v>0.6454273504273504</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.110910259582569</v>
+        <v>8.110553266585336</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2403119831490253</v>
+        <v>0.2402411808584252</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444784302945366</v>
+        <v>1.444682879666578</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824592651108636</v>
+        <v>1.824499267859533</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078655327741717</v>
+        <v>0.8078833633962385</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275915897050683</v>
+        <v>0.6276194511196684</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797618440077781</v>
+        <v>0.7976460933093585</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.825861228001626</v>
+        <v>5.927427708115002</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.958092147533042</v>
+        <v>5.969322434371796</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.007529284571065</v>
+        <v>6.008887261086016</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E9" t="n">
         <v>13917</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13916</v>
+        <v>13917</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.607445027306698</v>
+        <v>7.60726198174894</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.653089893316726</v>
+        <v>7.65291299692453</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0456448660100288</v>
+        <v>0.04565101517559009</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493132284448645</v>
+        <v>1.493116820062977</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941068160304469</v>
+        <v>1.941037151694268</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567576854375527</v>
+        <v>0.7567626591173595</v>
       </c>
       <c r="W9" t="n">
-        <v>0.525076595571804</v>
+        <v>0.5250855564551372</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553346133420235</v>
+        <v>0.7553396930671321</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.757190318184698</v>
+        <v>4.852539637384312</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.137240767872029</v>
+        <v>5.117882451278109</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.247721048979731</v>
+        <v>5.205438991936475</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61390047726996</v>
+        <v>10.61375218928609</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3088387967775917</v>
+        <v>0.3086905087937162</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053914105632406</v>
+        <v>2.053983332408504</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699675131142107</v>
+        <v>2.699749092991873</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569981007876645</v>
+        <v>0.3569915495353474</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1217486211050827</v>
+        <v>-0.121810086085467</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370173969036646</v>
+        <v>0.3370276422472769</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.43811025711857</v>
+        <v>10.73970825032407</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.87086476277097</v>
+        <v>10.938749275768</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12145171966188</v>
+        <v>11.12211403486233</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E11" t="n">
         <v>13858</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13857</v>
+        <v>13858</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241651656202642</v>
+        <v>5.241502886419397</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215267419465553</v>
+        <v>5.215212294826596</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02638423673708869</v>
+        <v>-0.02629059159279977</v>
       </c>
       <c r="T11" t="n">
-        <v>1.160998107787398</v>
+        <v>1.161056097192928</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482368182032606</v>
+        <v>1.4824052863821</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295306123462624</v>
+        <v>0.4295227569296122</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09180714562991987</v>
+        <v>-0.09177421986101231</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277243593388677</v>
+        <v>0.4277132695693375</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.337533167800305</v>
+        <v>4.546980713214838</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.769623737036055</v>
+        <v>4.884645192510705</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.953531964150481</v>
+        <v>5.048226780626781</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E12" t="n">
         <v>4176</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4175</v>
+        <v>4176</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.454546946107785</v>
+        <v>7.453832255747126</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.627472102032335</v>
+        <v>7.626992811232903</v>
       </c>
       <c r="R12" t="n">
-        <v>16.54817034925146</v>
+        <v>16.55761680911678</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1729251559245506</v>
+        <v>0.1731605554857765</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9111373235762088</v>
+        <v>0.9111891498572894</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191115690456324</v>
+        <v>1.191155448492955</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8336023265513358</v>
+        <v>0.833628207005332</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6628580839697114</v>
+        <v>0.6629256735274464</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8317778166895997</v>
+        <v>0.8317933113941494</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.521545383411976</v>
+        <v>4.64408783966544</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.923881690244353</v>
+        <v>5.065181295510292</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.504792721931376</v>
+        <v>5.829947422048116</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E13" t="n">
         <v>6510</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02007202111219</v>
+        <v>10.01990693943905</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.424994064122947</v>
+        <v>0.4248289824498022</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68851178708555</v>
+        <v>1.688456719723413</v>
       </c>
       <c r="U13" t="n">
-        <v>2.147017245730766</v>
+        <v>2.146965640998961</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234771766656117</v>
+        <v>0.8234858009223562</v>
       </c>
       <c r="W13" t="n">
-        <v>0.649301096083388</v>
+        <v>0.649317954360072</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102326557418339</v>
+        <v>0.810256382133276</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.065586442141926</v>
+        <v>8.196163695828078</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.383361521500284</v>
+        <v>8.425028262330985</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.495022117978092</v>
+        <v>8.495150255931218</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E14" t="n">
         <v>14098</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14097</v>
+        <v>14098</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.124358906150244</v>
+        <v>8.124189778692013</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195417961343562</v>
+        <v>8.195159084932115</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0710590551933165</v>
+        <v>0.07096930624010031</v>
       </c>
       <c r="T14" t="n">
-        <v>1.755017873394915</v>
+        <v>1.754894920706352</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280693704494803</v>
+        <v>2.28055186681822</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810240830539958</v>
+        <v>0.7810490524769821</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5657880988627784</v>
+        <v>0.5658259227016826</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806341290734633</v>
+        <v>0.7806608271680746</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.845458311394886</v>
+        <v>6.782189355800746</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.94676594082581</v>
+        <v>6.912995275992285</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.073063921714345</v>
+        <v>7.045873980282384</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81953759033083</v>
+        <v>11.81941378067622</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1443497926959531</v>
+        <v>-0.1444736023505589</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052609239280902</v>
+        <v>2.052638718042515</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698479880073029</v>
+        <v>2.698564816730541</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949943160295101</v>
+        <v>0.7949875706498716</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093530264374449</v>
+        <v>0.6093284342434226</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865454471448668</v>
+        <v>0.7865476415402948</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.303818961930858</v>
+        <v>9.301067711488312</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.37164030231037</v>
+        <v>9.373720471357608</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.446765737782485</v>
+        <v>9.450910427876568</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E16" t="n">
         <v>9861</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9860</v>
+        <v>9861</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.359405070993914</v>
+        <v>8.359155663725788</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.621916695070833</v>
+        <v>8.622121898621881</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2625116240769177</v>
+        <v>0.2629662348960926</v>
       </c>
       <c r="T16" t="n">
-        <v>3.600235143452538</v>
+        <v>3.600509709056273</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08156889699253</v>
+        <v>11.08116148250483</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04114562929006593</v>
+        <v>0.04113040470840963</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6109069202465907</v>
+        <v>-0.6109388758098133</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02448656030246354</v>
+        <v>0.02447023832125261</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.26054850271443</v>
+        <v>11.25863503926013</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.55389589734752</v>
+        <v>11.52021163588361</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.76585130356167</v>
+        <v>11.74957376220426</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E17" t="n">
         <v>2405</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.456961314475874</v>
+        <v>6.45527027027027</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.820661382702284</v>
+        <v>6.819505804050389</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3637000682264108</v>
+        <v>0.3642355337801187</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008157746263673</v>
+        <v>2.007985068630572</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545999193342476</v>
+        <v>2.545683614380797</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5400169493400584</v>
+        <v>0.5403129953610699</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05887067345841435</v>
+        <v>0.05965153794956013</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5365761918165313</v>
+        <v>0.5368592328166981</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.378896850394509</v>
+        <v>2.51715973726516</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.339065124335443</v>
+        <v>3.391067825931375</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.922562533813659</v>
+        <v>3.936761757265426</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E18" t="n">
         <v>3264</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.459130095004596</v>
+        <v>6.458137714460784</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.655143025958949</v>
+        <v>6.654409252271223</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1960129309543526</v>
+        <v>0.1962715378104386</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095674811844818</v>
+        <v>1.095590254757875</v>
       </c>
       <c r="U18" t="n">
-        <v>1.484058416695598</v>
+        <v>1.483911079225976</v>
       </c>
       <c r="V18" t="n">
-        <v>0.609737777213237</v>
+        <v>0.6100862822037114</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2348988389756635</v>
+        <v>0.2356698207326436</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6066426325300771</v>
+        <v>0.6069672674954438</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.115538058806822</v>
+        <v>2.56268766361957</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.433021466960768</v>
+        <v>3.846719871133829</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.020324398029068</v>
+        <v>5.42588729788384</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E19" t="n">
         <v>7218</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7217</v>
+        <v>7218</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.30447540529306</v>
+        <v>10.30327777777778</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10543809482749</v>
+        <v>11.10503200220482</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8009626895344254</v>
+        <v>0.8017542244270459</v>
       </c>
       <c r="T19" t="n">
-        <v>2.067978524369202</v>
+        <v>2.068738631359145</v>
       </c>
       <c r="U19" t="n">
-        <v>2.795479855084975</v>
+        <v>2.796664116436333</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7273088515451878</v>
+        <v>0.7272227422947324</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4715560218232274</v>
+        <v>0.471404966679035</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6772304813266351</v>
+        <v>0.6770240850673316</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.328549515248374</v>
+        <v>8.326038470775616</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.302449412746499</v>
+        <v>8.77867547424859</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.59294355997376</v>
+        <v>9.329369449040056</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E20" t="n">
         <v>10668</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10667</v>
+        <v>10668</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85212193749047</v>
+        <v>13.8517317873276</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.491211689237349</v>
+        <v>7.491082621082621</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22845575497522</v>
+        <v>14.22805619119024</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.376333817484747</v>
+        <v>0.3763244038626359</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254125935789654</v>
+        <v>1.254069077620708</v>
       </c>
       <c r="U20" t="n">
-        <v>1.646013889143072</v>
+        <v>1.645951367927679</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936806244940799</v>
+        <v>0.8936937070278781</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792604257404464</v>
+        <v>0.7792857026864086</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888572368721258</v>
+        <v>0.8888710262909462</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19203103202261</v>
+        <v>10.19163815408793</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.41588037751531</v>
+        <v>10.43139222207029</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.91031824691485</v>
+        <v>10.9013524155967</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16716</v>
+        <v>16717</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.971350037445</v>
+        <v>130.9714092609667</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1047804332336818</v>
+        <v>0.1048396567553801</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971824603321637</v>
+        <v>0.7971867773385013</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045765079437028</v>
+        <v>1.045768523765827</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651110107063023</v>
+        <v>0.8651100513269467</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311627679057313</v>
+        <v>0.7311609970197764</v>
       </c>
       <c r="X21" t="n">
-        <v>0.864358756357227</v>
+        <v>0.8643564184186934</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5088281859439</v>
+        <v>128.5815582201242</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.709305883753</v>
+        <v>128.9586974084521</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.64772498994</v>
+        <v>129.780301144576</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.328549515248374</v>
+        <v>8.326038470775616</v>
       </c>
       <c r="G2" t="n">
-        <v>9.302449412746499</v>
+        <v>8.778675474248587</v>
       </c>
       <c r="H2" t="n">
-        <v>12.59294355997376</v>
+        <v>9.329369449040056</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.598482185738986</v>
+        <v>5.678638706652867</v>
       </c>
       <c r="G3" t="n">
-        <v>5.768978471367167</v>
+        <v>5.780611730740095</v>
       </c>
       <c r="H3" t="n">
-        <v>5.840596562314121</v>
+        <v>5.84112040880445</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.337533167800305</v>
+        <v>4.546980713214838</v>
       </c>
       <c r="G4" t="n">
-        <v>4.769623737036055</v>
+        <v>4.884645192510705</v>
       </c>
       <c r="H4" t="n">
-        <v>4.953531964150481</v>
+        <v>5.048226780626781</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.26054850271443</v>
+        <v>11.25863503926013</v>
       </c>
       <c r="G5" t="n">
-        <v>11.55389589734752</v>
+        <v>11.52021163588361</v>
       </c>
       <c r="H5" t="n">
-        <v>11.76585130356167</v>
+        <v>11.74957376220426</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.583286001619911</v>
+        <v>2.584782049352356</v>
       </c>
       <c r="G6" t="n">
-        <v>56.69954153317364</v>
+        <v>37.57940285659121</v>
       </c>
       <c r="H6" t="n">
-        <v>108.7273484550092</v>
+        <v>108.2796199243394</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.303818961930858</v>
+        <v>9.301067711488312</v>
       </c>
       <c r="G7" t="n">
-        <v>9.37164030231037</v>
+        <v>9.373720471357606</v>
       </c>
       <c r="H7" t="n">
-        <v>9.446765737782485</v>
+        <v>9.450910427876568</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.065586442141926</v>
+        <v>8.196163695828078</v>
       </c>
       <c r="G8" t="n">
-        <v>8.383361521500284</v>
+        <v>8.425028262330983</v>
       </c>
       <c r="H8" t="n">
-        <v>8.495022117978092</v>
+        <v>8.495150255931218</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.521545383411976</v>
+        <v>4.64408783966544</v>
       </c>
       <c r="G9" t="n">
-        <v>4.923881690244353</v>
+        <v>5.065181295510292</v>
       </c>
       <c r="H9" t="n">
-        <v>5.504792721931376</v>
+        <v>5.829947422048116</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.825861228001626</v>
+        <v>5.927427708115002</v>
       </c>
       <c r="G10" t="n">
-        <v>5.958092147533042</v>
+        <v>5.969322434371797</v>
       </c>
       <c r="H10" t="n">
-        <v>6.007529284571065</v>
+        <v>6.008887261086016</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19203103202261</v>
+        <v>10.19163815408793</v>
       </c>
       <c r="G11" t="n">
-        <v>10.41588037751531</v>
+        <v>10.43139222207029</v>
       </c>
       <c r="H11" t="n">
-        <v>10.91031824691485</v>
+        <v>10.9013524155967</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.378896850394509</v>
+        <v>2.51715973726516</v>
       </c>
       <c r="G12" t="n">
-        <v>3.339065124335443</v>
+        <v>3.391067825931375</v>
       </c>
       <c r="H12" t="n">
-        <v>3.922562533813659</v>
+        <v>3.936761757265426</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.845458311394886</v>
+        <v>6.782189355800746</v>
       </c>
       <c r="G13" t="n">
-        <v>6.946765940825811</v>
+        <v>6.912995275992285</v>
       </c>
       <c r="H13" t="n">
-        <v>7.073063921714345</v>
+        <v>7.045873980282384</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.43811025711857</v>
+        <v>10.73970825032407</v>
       </c>
       <c r="G14" t="n">
-        <v>10.87086476277097</v>
+        <v>10.938749275768</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12145171966188</v>
+        <v>11.12211403486233</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.757190318184698</v>
+        <v>4.852539637384312</v>
       </c>
       <c r="G15" t="n">
-        <v>5.137240767872029</v>
+        <v>5.117882451278109</v>
       </c>
       <c r="H15" t="n">
-        <v>5.247721048979731</v>
+        <v>5.205438991936475</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.012608637985638</v>
+        <v>8.008350402213232</v>
       </c>
       <c r="G16" t="n">
-        <v>8.15778710558819</v>
+        <v>8.143925373025642</v>
       </c>
       <c r="H16" t="n">
-        <v>8.228725600018485</v>
+        <v>8.229288873465638</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.115538058806822</v>
+        <v>2.56268766361957</v>
       </c>
       <c r="G17" t="n">
-        <v>3.433021466960768</v>
+        <v>3.846719871133829</v>
       </c>
       <c r="H17" t="n">
-        <v>5.020324398029068</v>
+        <v>5.42588729788384</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.369185727776293</v>
+        <v>3.365249287749288</v>
       </c>
       <c r="G18" t="n">
-        <v>3.635243421031296</v>
+        <v>3.647827565708281</v>
       </c>
       <c r="H18" t="n">
-        <v>4.24949572344975</v>
+        <v>4.239014271652785</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.877116001425517</v>
+        <v>3.015234033605555</v>
       </c>
       <c r="G19" t="n">
-        <v>3.228692334345407</v>
+        <v>3.270117731004996</v>
       </c>
       <c r="H19" t="n">
-        <v>3.332669992872416</v>
+        <v>3.333615384615384</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.593470215045711</v>
+        <v>5.748739316239316</v>
       </c>
       <c r="G20" t="n">
-        <v>6.364166277353441</v>
+        <v>6.487300663300981</v>
       </c>
       <c r="H20" t="n">
-        <v>7.012542743372321</v>
+        <v>7.012691344401359</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5088281859439</v>
+        <v>128.5815582201242</v>
       </c>
       <c r="G21" t="n">
-        <v>128.709305883753</v>
+        <v>128.9586974084521</v>
       </c>
       <c r="H21" t="n">
-        <v>129.64772498994</v>
+        <v>129.780301144576</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E2" t="n">
         <v>10052</v>
@@ -611,40 +611,40 @@
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843219373219373</v>
+        <v>1.843202846975089</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4592668373628</v>
+        <v>102.4596012280711</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0121805031332532</v>
+        <v>-0.01184611242501553</v>
       </c>
       <c r="T2" t="n">
-        <v>18.1428937388648</v>
+        <v>18.14274143832735</v>
       </c>
       <c r="U2" t="n">
-        <v>36.27497469258412</v>
+        <v>36.27540931186548</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1366153743547817</v>
+        <v>0.1366111950325576</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7227718303496047</v>
+        <v>-0.7228131124922754</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1366122539891454</v>
+        <v>0.1366081262900842</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.584782049352356</v>
+        <v>2.522384348406686</v>
       </c>
       <c r="Z2" t="n">
-        <v>37.57940285659121</v>
+        <v>37.90176348076064</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.2796199243394</v>
+        <v>111.228335691152</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E3" t="n">
         <v>14646</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.96199448417351</v>
+        <v>4.961925461972354</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05789650520314271</v>
+        <v>0.05782748300198692</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343295876539647</v>
+        <v>1.343307781178369</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717855773593011</v>
+        <v>1.717863758092034</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816439540646006</v>
+        <v>0.7816477848894594</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5703218429718049</v>
+        <v>0.5703178487217047</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7805884956591473</v>
+        <v>0.7805956529650541</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.015234033605555</v>
+        <v>3.168934726115554</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.270117731004996</v>
+        <v>3.296769091273824</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.333615384615384</v>
+        <v>3.334559430604982</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E4" t="n">
         <v>10280</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230360874825341</v>
+        <v>7.230327904556495</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3302424409732014</v>
+        <v>0.3302094707043552</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290827430398232</v>
+        <v>1.290823823992711</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680527533648698</v>
+        <v>1.680530531850472</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8680506067487522</v>
+        <v>0.8680504036127549</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7382295500790974</v>
+        <v>0.7382286160374802</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473440117423383</v>
+        <v>0.8473523580174479</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.365249287749288</v>
+        <v>3.368072323298321</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.647827565708281</v>
+        <v>3.660831642589085</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.239014271652785</v>
+        <v>4.215124555160142</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301710663551205</v>
+        <v>9.301692096725638</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692492381287221</v>
+        <v>0.3692306713031538</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247509177345047</v>
+        <v>1.247514245732</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747100166194453</v>
+        <v>1.747106002318334</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661267642600937</v>
+        <v>0.866126677085821</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215275155241665</v>
+        <v>0.7215256550668641</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597363931055667</v>
+        <v>0.8597374615236357</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.748739316239316</v>
+        <v>5.862374433539736</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.487300663300981</v>
+        <v>6.526806098946288</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.012691344401359</v>
+        <v>6.993056983338183</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E6" t="n">
         <v>8893</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023169735252189</v>
+        <v>7.023027921870774</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.288946019970507</v>
+        <v>0.2888042065890915</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477921843419235</v>
+        <v>1.477920266266384</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906180360514116</v>
+        <v>1.906167452564217</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039764906945409</v>
+        <v>0.3039822448600667</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980138099653554</v>
+        <v>-0.1979975850055355</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789676084211415</v>
+        <v>0.2789794203495075</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.008350402213232</v>
+        <v>8.001757931162066</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.143925373025642</v>
+        <v>8.114105265552622</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.229288873465638</v>
+        <v>8.216997367606787</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E7" t="n">
         <v>14254</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565695236859315</v>
+        <v>5.565629120992345</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01349313131803832</v>
+        <v>-0.01355924718501029</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166361436400764</v>
+        <v>1.166355547717553</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509470585823442</v>
+        <v>1.509465238561009</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049635214732924</v>
+        <v>0.5049788133084648</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05328796334536745</v>
+        <v>0.05329467074170724</v>
       </c>
       <c r="X7" t="n">
-        <v>0.502824067474451</v>
+        <v>0.5028414740489391</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.678638706652867</v>
+        <v>5.628062598484314</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.780611730740095</v>
+        <v>5.76838161350379</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.84112040880445</v>
+        <v>5.841494362969141</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E8" t="n">
         <v>9052</v>
@@ -1145,40 +1145,40 @@
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454273504273504</v>
+        <v>0.6454163701067616</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.110553266585336</v>
+        <v>8.110449708958203</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2402411808584252</v>
+        <v>0.2401376232312939</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444682879666578</v>
+        <v>1.444675608390023</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824499267859533</v>
+        <v>1.824494752745156</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078833633962385</v>
+        <v>0.8078878816286928</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6276194511196684</v>
+        <v>0.6276212941883055</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976460933093585</v>
+        <v>0.7976647366890171</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.927427708115002</v>
+        <v>5.928085312461491</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.969322434371796</v>
+        <v>5.969556708947666</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.008887261086016</v>
+        <v>6.006072356436264</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E9" t="n">
         <v>13917</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65291299692453</v>
+        <v>7.652836516413243</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04565101517559009</v>
+        <v>0.04557453466430292</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493116820062977</v>
+        <v>1.493111108770413</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941037151694268</v>
+        <v>1.941030857706779</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567626591173595</v>
+        <v>0.7567696259605071</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250855564551372</v>
+        <v>0.5250886363557127</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553396930671321</v>
+        <v>0.7553496057351713</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.852539637384312</v>
+        <v>4.715384060849725</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.117882451278109</v>
+        <v>4.865391714072655</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.205438991936475</v>
+        <v>5.03090020359707</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61375218928609</v>
+        <v>10.61360561539232</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3086905087937162</v>
+        <v>0.308543934899947</v>
       </c>
       <c r="T10" t="n">
-        <v>2.053983332408504</v>
+        <v>2.054048910397695</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699749092991873</v>
+        <v>2.699816026212198</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569915495353474</v>
+        <v>0.3569868010397431</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.121810086085467</v>
+        <v>-0.121865711471274</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370276422472769</v>
+        <v>0.3370388843164809</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.73970825032407</v>
+        <v>10.54511510833054</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.938749275768</v>
+        <v>10.86529382894831</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.12211403486233</v>
+        <v>11.0816394719074</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E11" t="n">
         <v>13858</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215212294826596</v>
+        <v>5.215184443993557</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02629059159279977</v>
+        <v>-0.02631844242583976</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161056097192928</v>
+        <v>1.161071350348039</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4824052863821</v>
+        <v>1.48241944118202</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295227569296122</v>
+        <v>0.4295263363963021</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09177421986101231</v>
+        <v>-0.09179506965096174</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277132695693375</v>
+        <v>0.4277188169842578</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.546980713214838</v>
+        <v>4.469938256227758</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.884645192510705</v>
+        <v>4.839516672406086</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.048226780626781</v>
+        <v>5.119829885824436</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E12" t="n">
         <v>4176</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.626992811232903</v>
+        <v>7.627035229292461</v>
       </c>
       <c r="R12" t="n">
-        <v>16.55761680911678</v>
+        <v>16.56704982206416</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1731605554857765</v>
+        <v>0.1732029735453337</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9111891498572894</v>
+        <v>0.9112163790272847</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191155448492955</v>
+        <v>1.191233862725295</v>
       </c>
       <c r="V12" t="n">
-        <v>0.833628207005332</v>
+        <v>0.8336089405882305</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6629256735274464</v>
+        <v>0.6628812925953343</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8317933113941494</v>
+        <v>0.8317739054958868</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.64408783966544</v>
+        <v>4.643792633310336</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.065181295510292</v>
+        <v>5.092167561633113</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.829947422048116</v>
+        <v>5.912929932266954</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E13" t="n">
         <v>6510</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.01990693943905</v>
+        <v>10.01975276307926</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4248289824498022</v>
+        <v>0.424674806090017</v>
       </c>
       <c r="T13" t="n">
-        <v>1.688456719723413</v>
+        <v>1.688413332970426</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146965640998961</v>
+        <v>2.146928455159332</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234858009223562</v>
+        <v>0.8234930192738594</v>
       </c>
       <c r="W13" t="n">
-        <v>0.649317954360072</v>
+        <v>0.6493301020098803</v>
       </c>
       <c r="X13" t="n">
-        <v>0.810256382133276</v>
+        <v>0.8102800691383816</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.196163695828078</v>
+        <v>8.339344952079651</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.425028262330985</v>
+        <v>8.44218698995318</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.495150255931218</v>
+        <v>8.495279701644662</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E14" t="n">
         <v>14098</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.195159084932115</v>
+        <v>8.194987203193168</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07096930624010031</v>
+        <v>0.07079742450115457</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754894920706352</v>
+        <v>1.754806717504757</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28055186681822</v>
+        <v>2.280468397782184</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810490524769821</v>
+        <v>0.7810734176504068</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5658259227016826</v>
+        <v>0.5658577039814955</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806608271680746</v>
+        <v>0.7806879401264418</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.782189355800746</v>
+        <v>6.728788846257253</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.912995275992285</v>
+        <v>6.872370950665045</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.045873980282384</v>
+        <v>7.026916266613159</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81941378067622</v>
+        <v>11.8192879519734</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1444736023505589</v>
+        <v>-0.1445994310533848</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052638718042515</v>
+        <v>2.052668496703565</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698564816730541</v>
+        <v>2.698634006504137</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949875706498716</v>
+        <v>0.794983300348481</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093284342434226</v>
+        <v>0.609308400762262</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865476415402948</v>
+        <v>0.7865522600988057</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.301067711488312</v>
+        <v>9.272217796261787</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.373720471357608</v>
+        <v>9.368485360019474</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.450910427876568</v>
+        <v>9.454811932055346</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E16" t="n">
         <v>9861</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622121898621881</v>
+        <v>8.622034819007041</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2629662348960926</v>
+        <v>0.2628791552812527</v>
       </c>
       <c r="T16" t="n">
-        <v>3.600509709056273</v>
+        <v>3.60057039225369</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08116148250483</v>
+        <v>11.08116927802863</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04113040470840963</v>
+        <v>0.04112747236389745</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6109388758098133</v>
+        <v>-0.6109411423802955</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02447023832125261</v>
+        <v>0.02446746482154383</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.25863503926013</v>
+        <v>11.2481462997944</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.52021163588361</v>
+        <v>11.46452841317645</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.74957376220426</v>
+        <v>11.71966776273508</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E17" t="n">
         <v>2405</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.819505804050389</v>
+        <v>6.819571505496429</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3642355337801187</v>
+        <v>0.3643012352261582</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007985068630572</v>
+        <v>2.008004918174887</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545683614380797</v>
+        <v>2.545700931798601</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5403129953610699</v>
+        <v>0.5403043879008051</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05965153794956013</v>
+        <v>0.05963874416600012</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5368592328166981</v>
+        <v>0.5368494991982808</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.51715973726516</v>
+        <v>2.378083338841362</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.391067825931375</v>
+        <v>3.305635908101723</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.936761757265426</v>
+        <v>5.933850278024911</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E18" t="n">
         <v>3264</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.654409252271223</v>
+        <v>6.654519934196113</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1962715378104386</v>
+        <v>0.1963822197353285</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095590254757875</v>
+        <v>1.095615976202466</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483911079225976</v>
+        <v>1.483929114965678</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6100862822037114</v>
+        <v>0.6100630454389633</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2356698207326436</v>
+        <v>0.2356512409887132</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6069672674954438</v>
+        <v>0.6069370705015587</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.56268766361957</v>
+        <v>2.122655127876211</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.846719871133829</v>
+        <v>3.903265073250705</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.42588729788384</v>
+        <v>7.313860026030051</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E19" t="n">
         <v>7218</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10503200220482</v>
+        <v>11.10492778889829</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8017542244270459</v>
+        <v>0.801650011120517</v>
       </c>
       <c r="T19" t="n">
-        <v>2.068738631359145</v>
+        <v>2.068757606624208</v>
       </c>
       <c r="U19" t="n">
-        <v>2.796664116436333</v>
+        <v>2.796696745100693</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272227422947324</v>
+        <v>0.7272134460288739</v>
       </c>
       <c r="W19" t="n">
-        <v>0.471404966679035</v>
+        <v>0.4713926323765815</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6770240850673316</v>
+        <v>0.6770346380909315</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.326038470775616</v>
+        <v>8.326496609409588</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.77867547424859</v>
+        <v>8.567866916374783</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.329369449040056</v>
+        <v>9.068943520295367</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E20" t="n">
         <v>10668</v>
@@ -2213,40 +2213,40 @@
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.491082621082621</v>
+        <v>7.490953736654804</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22805619119024</v>
+        <v>14.22802606778531</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3763244038626359</v>
+        <v>0.3762942804577138</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254069077620708</v>
+        <v>1.254068144307328</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645951367927679</v>
+        <v>1.645955819138877</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936937070278781</v>
+        <v>0.8936933909682836</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792857026864086</v>
+        <v>0.7792845089120366</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888710262909462</v>
+        <v>0.8888734179246853</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19163815408793</v>
+        <v>10.19432206956288</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.43139222207029</v>
+        <v>10.44433038122849</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.9013524155967</v>
+        <v>10.89563804793787</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16717</v>
+        <v>16718</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9714092609667</v>
+        <v>130.9714740275805</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1048396567553801</v>
+        <v>0.1049044233691283</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971867773385013</v>
+        <v>0.7971875976836983</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045768523765827</v>
+        <v>1.045766363182889</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651100513269467</v>
+        <v>0.8651103507621047</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311609970197764</v>
+        <v>0.7311621078743293</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643564184186934</v>
+        <v>0.864355030775247</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5815582201242</v>
+        <v>128.5816824953997</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9586974084521</v>
+        <v>129.0073152149784</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.780301144576</v>
+        <v>130.0768808677328</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.326038470775616</v>
+        <v>8.326496609409588</v>
       </c>
       <c r="G2" t="n">
-        <v>8.778675474248587</v>
+        <v>8.567866916374783</v>
       </c>
       <c r="H2" t="n">
-        <v>9.329369449040056</v>
+        <v>9.068943520295367</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.678638706652867</v>
+        <v>5.628062598484314</v>
       </c>
       <c r="G3" t="n">
-        <v>5.780611730740095</v>
+        <v>5.76838161350379</v>
       </c>
       <c r="H3" t="n">
-        <v>5.84112040880445</v>
+        <v>5.841494362969141</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.546980713214838</v>
+        <v>4.469938256227758</v>
       </c>
       <c r="G4" t="n">
-        <v>4.884645192510705</v>
+        <v>4.839516672406087</v>
       </c>
       <c r="H4" t="n">
-        <v>5.048226780626781</v>
+        <v>5.119829885824436</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.25863503926013</v>
+        <v>11.2481462997944</v>
       </c>
       <c r="G5" t="n">
-        <v>11.52021163588361</v>
+        <v>11.46452841317645</v>
       </c>
       <c r="H5" t="n">
-        <v>11.74957376220426</v>
+        <v>11.71966776273508</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.584782049352356</v>
+        <v>2.522384348406686</v>
       </c>
       <c r="G6" t="n">
-        <v>37.57940285659121</v>
+        <v>37.90176348076064</v>
       </c>
       <c r="H6" t="n">
-        <v>108.2796199243394</v>
+        <v>111.228335691152</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.301067711488312</v>
+        <v>9.272217796261787</v>
       </c>
       <c r="G7" t="n">
-        <v>9.373720471357606</v>
+        <v>9.368485360019474</v>
       </c>
       <c r="H7" t="n">
-        <v>9.450910427876568</v>
+        <v>9.454811932055346</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.196163695828078</v>
+        <v>8.339344952079651</v>
       </c>
       <c r="G8" t="n">
-        <v>8.425028262330983</v>
+        <v>8.44218698995318</v>
       </c>
       <c r="H8" t="n">
-        <v>8.495150255931218</v>
+        <v>8.495279701644662</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.64408783966544</v>
+        <v>4.643792633310336</v>
       </c>
       <c r="G9" t="n">
-        <v>5.065181295510292</v>
+        <v>5.092167561633112</v>
       </c>
       <c r="H9" t="n">
-        <v>5.829947422048116</v>
+        <v>5.912929932266954</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.927427708115002</v>
+        <v>5.928085312461491</v>
       </c>
       <c r="G10" t="n">
-        <v>5.969322434371797</v>
+        <v>5.969556708947666</v>
       </c>
       <c r="H10" t="n">
-        <v>6.008887261086016</v>
+        <v>6.006072356436264</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19163815408793</v>
+        <v>10.19432206956288</v>
       </c>
       <c r="G11" t="n">
-        <v>10.43139222207029</v>
+        <v>10.44433038122849</v>
       </c>
       <c r="H11" t="n">
-        <v>10.9013524155967</v>
+        <v>10.89563804793787</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.51715973726516</v>
+        <v>2.378083338841362</v>
       </c>
       <c r="G12" t="n">
-        <v>3.391067825931375</v>
+        <v>3.305635908101723</v>
       </c>
       <c r="H12" t="n">
-        <v>3.936761757265426</v>
+        <v>5.933850278024911</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.782189355800746</v>
+        <v>6.728788846257253</v>
       </c>
       <c r="G13" t="n">
-        <v>6.912995275992285</v>
+        <v>6.872370950665045</v>
       </c>
       <c r="H13" t="n">
-        <v>7.045873980282384</v>
+        <v>7.026916266613159</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.73970825032407</v>
+        <v>10.54511510833054</v>
       </c>
       <c r="G14" t="n">
-        <v>10.938749275768</v>
+        <v>10.86529382894832</v>
       </c>
       <c r="H14" t="n">
-        <v>11.12211403486233</v>
+        <v>11.0816394719074</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.852539637384312</v>
+        <v>4.715384060849725</v>
       </c>
       <c r="G15" t="n">
-        <v>5.117882451278109</v>
+        <v>4.865391714072655</v>
       </c>
       <c r="H15" t="n">
-        <v>5.205438991936475</v>
+        <v>5.03090020359707</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.008350402213232</v>
+        <v>8.001757931162066</v>
       </c>
       <c r="G16" t="n">
-        <v>8.143925373025642</v>
+        <v>8.114105265552624</v>
       </c>
       <c r="H16" t="n">
-        <v>8.229288873465638</v>
+        <v>8.216997367606787</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.56268766361957</v>
+        <v>2.122655127876211</v>
       </c>
       <c r="G17" t="n">
-        <v>3.846719871133829</v>
+        <v>3.903265073250706</v>
       </c>
       <c r="H17" t="n">
-        <v>5.42588729788384</v>
+        <v>7.313860026030051</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.365249287749288</v>
+        <v>3.368072323298321</v>
       </c>
       <c r="G18" t="n">
-        <v>3.647827565708281</v>
+        <v>3.660831642589085</v>
       </c>
       <c r="H18" t="n">
-        <v>4.239014271652785</v>
+        <v>4.215124555160142</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.015234033605555</v>
+        <v>3.168934726115554</v>
       </c>
       <c r="G19" t="n">
-        <v>3.270117731004996</v>
+        <v>3.296769091273823</v>
       </c>
       <c r="H19" t="n">
-        <v>3.333615384615384</v>
+        <v>3.334559430604982</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.748739316239316</v>
+        <v>5.862374433539736</v>
       </c>
       <c r="G20" t="n">
-        <v>6.487300663300981</v>
+        <v>6.526806098946288</v>
       </c>
       <c r="H20" t="n">
-        <v>7.012691344401359</v>
+        <v>6.993056983338183</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5815582201242</v>
+        <v>128.5816824953997</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9586974084521</v>
+        <v>129.0073152149784</v>
       </c>
       <c r="H21" t="n">
-        <v>129.780301144576</v>
+        <v>130.0768808677328</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E2" t="n">
         <v>10052</v>
@@ -611,40 +611,40 @@
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843202846975089</v>
+        <v>1.843186344238976</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4596012280711</v>
+        <v>102.4607244422094</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01184611242501553</v>
+        <v>-0.01072289828671053</v>
       </c>
       <c r="T2" t="n">
-        <v>18.14274143832735</v>
+        <v>18.14185163147563</v>
       </c>
       <c r="U2" t="n">
-        <v>36.27540931186548</v>
+        <v>36.27452885749324</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1366111950325576</v>
+        <v>0.1366191181263721</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7228131124922754</v>
+        <v>-0.7227294833915652</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1366081262900842</v>
+        <v>0.1366159450416751</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.522384348406686</v>
+        <v>2.152626476708766</v>
       </c>
       <c r="Z2" t="n">
-        <v>37.90176348076064</v>
+        <v>27.48018182084412</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.228335691152</v>
+        <v>111.0363096408297</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E3" t="n">
         <v>14646</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.961925461972354</v>
+        <v>4.961847050402432</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05782748300198692</v>
+        <v>0.05774907143206433</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343307781178369</v>
+        <v>1.343318884013162</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717863758092034</v>
+        <v>1.717868673725026</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816477848894594</v>
+        <v>0.781652855543876</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5703178487217047</v>
+        <v>0.5703153896643191</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7805956529650541</v>
+        <v>0.7806043563505936</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.168934726115554</v>
+        <v>3.276265778106192</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.296769091273824</v>
+        <v>3.307933197836745</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.334559430604982</v>
+        <v>3.33550213371266</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E4" t="n">
         <v>10280</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230327904556495</v>
+        <v>7.230300376279035</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3302094707043552</v>
+        <v>0.3301819424268952</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290823823992711</v>
+        <v>1.290825559277405</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680530531850472</v>
+        <v>1.680535527172181</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8680504036127549</v>
+        <v>0.8680499049794653</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7382286160374802</v>
+        <v>0.7382270598215168</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473523580174479</v>
+        <v>0.8473594699029596</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.368072323298321</v>
+        <v>3.367208772247723</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.660831642589085</v>
+        <v>3.729689710740335</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.215124555160142</v>
+        <v>4.258707590682788</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E5" t="n">
         <v>2722</v>
@@ -881,37 +881,37 @@
         <v>2.82217716630461</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301692096725638</v>
+        <v>9.301667357587347</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3692306713031538</v>
+        <v>0.369205932164863</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247514245732</v>
+        <v>1.247520499273013</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747106002318334</v>
+        <v>1.747112346065408</v>
       </c>
       <c r="V5" t="n">
-        <v>0.866126677085821</v>
+        <v>0.8661265481865181</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215256550668641</v>
+        <v>0.7215236327808485</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597374615236357</v>
+        <v>0.8597387832140859</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.862374433539736</v>
+        <v>6.039249573192007</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.526806098946288</v>
+        <v>6.507035203856414</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.993056983338183</v>
+        <v>7.013752386815321</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E6" t="n">
         <v>8893</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023027921870774</v>
+        <v>7.022889787697532</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2888042065890915</v>
+        <v>0.2886660724158501</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477920266266384</v>
+        <v>1.477919142633874</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906167452564217</v>
+        <v>1.906153515383275</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039822448600667</v>
+        <v>0.3039899612283271</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979975850055355</v>
+        <v>-0.1979800664522227</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789794203495075</v>
+        <v>0.2789933898146494</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.001757931162066</v>
+        <v>7.980202384921441</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.114105265552622</v>
+        <v>8.08660651538727</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.216997367606787</v>
+        <v>8.194905175444054</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E7" t="n">
         <v>14254</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565629120992345</v>
+        <v>5.565557844204818</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01355924718501029</v>
+        <v>-0.01363052397253594</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166355547717553</v>
+        <v>1.166345704451679</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509465238561009</v>
+        <v>1.509456864251476</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049788133084648</v>
+        <v>0.504995865126238</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05329467074170724</v>
+        <v>0.05330517509950194</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028414740489391</v>
+        <v>0.5028605756520448</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.628062598484314</v>
+        <v>5.620535798956852</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.76838161350379</v>
+        <v>5.746722629631958</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.841494362969141</v>
+        <v>5.8419680202165</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E8" t="n">
         <v>9052</v>
@@ -1145,40 +1145,40 @@
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454163701067616</v>
+        <v>0.6454054054054055</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.110449708958203</v>
+        <v>8.11034093791795</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2401376232312939</v>
+        <v>0.2400288521910396</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444675608390023</v>
+        <v>1.444664896385715</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824494752745156</v>
+        <v>1.824485900973142</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078878816286928</v>
+        <v>0.8078933856969033</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6276212941883055</v>
+        <v>0.627624907466344</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976647366890171</v>
+        <v>0.7976847757463237</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.928085312461491</v>
+        <v>5.927387973895619</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.969556708947666</v>
+        <v>5.964380426276763</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.006072356436264</v>
+        <v>6.006132026521935</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E9" t="n">
         <v>13917</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.652836516413243</v>
+        <v>7.65273651969283</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04557453466430292</v>
+        <v>0.04547453794389029</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493111108770413</v>
+        <v>1.493120986052457</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941030857706779</v>
+        <v>1.94104044713388</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567696259605071</v>
+        <v>0.7567746482669954</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250886363557127</v>
+        <v>0.5250839438603485</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553496057351713</v>
+        <v>0.7553586795382219</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.715384060849725</v>
+        <v>4.561328858425056</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.865391714072655</v>
+        <v>4.62200480582123</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.03090020359707</v>
+        <v>4.71022865773097</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61360561539232</v>
+        <v>10.61346102923209</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.308543934899947</v>
+        <v>0.3083993487397151</v>
       </c>
       <c r="T10" t="n">
-        <v>2.054048910397695</v>
+        <v>2.05411659876024</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699816026212198</v>
+        <v>2.699884131989016</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569868010397431</v>
+        <v>0.3569817486381488</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.121865711471274</v>
+        <v>-0.1219223127350115</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370388843164809</v>
+        <v>0.3370498807974437</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.54511510833054</v>
+        <v>10.40238193040145</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.86529382894831</v>
+        <v>10.76775388905121</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.0816394719074</v>
+        <v>10.958721076975</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E11" t="n">
         <v>13858</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215184443993557</v>
+        <v>5.215155301586217</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02631844242583976</v>
+        <v>-0.02634758483318015</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161071350348039</v>
+        <v>1.161086243757449</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48241944118202</v>
+        <v>1.48243369422369</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295263363963021</v>
+        <v>0.4295300103045526</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09179506965096174</v>
+        <v>-0.09181606435057277</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277188169842578</v>
+        <v>0.4277244769638568</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.469938256227758</v>
+        <v>4.544802223741506</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.839516672406086</v>
+        <v>4.804152504572716</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.119829885824436</v>
+        <v>5.390131325661599</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E12" t="n">
         <v>4176</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.627035229292461</v>
+        <v>7.627088161562525</v>
       </c>
       <c r="R12" t="n">
-        <v>16.56704982206416</v>
+        <v>16.57646941678532</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732029735453337</v>
+        <v>0.1732559058153977</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9112163790272847</v>
+        <v>0.9112472990334154</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191233862725295</v>
+        <v>1.191315742931739</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8336089405882305</v>
+        <v>0.8335881902317438</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6628812925953343</v>
+        <v>0.6628349468711419</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8317739054958868</v>
+        <v>0.8317525375636143</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.643792633310336</v>
+        <v>4.643606534004756</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.092167561633113</v>
+        <v>5.079908123458017</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.912929932266954</v>
+        <v>5.576068752258946</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E13" t="n">
         <v>6510</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.01975276307926</v>
+        <v>10.01958829791547</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.424674806090017</v>
+        <v>0.4245103409262185</v>
       </c>
       <c r="T13" t="n">
-        <v>1.688413332970426</v>
+        <v>1.688368118574974</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146928455159332</v>
+        <v>2.146888685923055</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8234930192738594</v>
+        <v>0.8235005292878804</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6493301020098803</v>
+        <v>0.6493430933555674</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102800691383816</v>
+        <v>0.8103046887138663</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.339344952079651</v>
+        <v>8.164612003130284</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.44218698995318</v>
+        <v>8.420681913240426</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.495279701644662</v>
+        <v>8.495244442991119</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E14" t="n">
         <v>14098</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.194987203193168</v>
+        <v>8.194815661259177</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07079742450115457</v>
+        <v>0.07062588256716462</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754806717504757</v>
+        <v>1.754720019015761</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280468397782184</v>
+        <v>2.280384990403653</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810734176504068</v>
+        <v>0.7810978112648528</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5658577039814955</v>
+        <v>0.5658894606229459</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806879401264418</v>
+        <v>0.7807150770749819</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.728788846257253</v>
+        <v>6.717039326036133</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.872370950665045</v>
+        <v>6.827568489066083</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.026916266613159</v>
+        <v>6.920607331757258</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.8192879519734</v>
+        <v>11.81916243009333</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1445994310533848</v>
+        <v>-0.1447249529334482</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052668496703565</v>
+        <v>2.052698142197533</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698634006504137</v>
+        <v>2.698697000117535</v>
       </c>
       <c r="V15" t="n">
-        <v>0.794983300348481</v>
+        <v>0.7949799782331872</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609308400762262</v>
+        <v>0.6092901608951687</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865522600988057</v>
+        <v>0.786557778124905</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.272217796261787</v>
+        <v>9.235387432991583</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.368485360019474</v>
+        <v>9.357706753125157</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.454811932055346</v>
+        <v>9.456935412405977</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E16" t="n">
         <v>9861</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.622034819007041</v>
+        <v>8.6219544514283</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2628791552812527</v>
+        <v>0.2627987877025126</v>
       </c>
       <c r="T16" t="n">
-        <v>3.60057039225369</v>
+        <v>3.600632761785126</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08116927802863</v>
+        <v>11.0811777949922</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04112747236389745</v>
+        <v>0.04112460823350876</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6109411423802955</v>
+        <v>-0.6109436187132438</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02446746482154383</v>
+        <v>0.02446476430253375</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.2481462997944</v>
+        <v>11.22423733715743</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.46452841317645</v>
+        <v>11.41121321801921</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.71966776273508</v>
+        <v>11.68819388832639</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E17" t="n">
         <v>2405</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.819571505496429</v>
+        <v>6.819645680125721</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3643012352261582</v>
+        <v>0.36437540985545</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008004918174887</v>
+        <v>2.008022843392421</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545700931798601</v>
+        <v>2.545714695105788</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5403043879008051</v>
+        <v>0.5402955041718577</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05963874416600012</v>
+        <v>0.05962857603065019</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5368494991982808</v>
+        <v>0.536839348481594</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.378083338841362</v>
+        <v>2.375644064630889</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.305635908101723</v>
+        <v>3.092505463610372</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.933850278024911</v>
+        <v>6.608509032764545</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E18" t="n">
         <v>3264</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.654519934196113</v>
+        <v>6.654628763315593</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1963822197353285</v>
+        <v>0.1964910488548093</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095615976202466</v>
+        <v>1.095637563961652</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483929114965678</v>
+        <v>1.483947781158079</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6100630454389633</v>
+        <v>0.6100401809183926</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2356512409887132</v>
+        <v>0.2356320115382119</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6069370705015587</v>
+        <v>0.606907484243032</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.122655127876211</v>
+        <v>2.109873259417139</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.903265073250705</v>
+        <v>3.669925704011194</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.313860026030051</v>
+        <v>7.355865781290819</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E19" t="n">
         <v>7218</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10492778889829</v>
+        <v>11.10482564912382</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.801650011120517</v>
+        <v>0.8015478713460413</v>
       </c>
       <c r="T19" t="n">
-        <v>2.068757606624208</v>
+        <v>2.068777552367534</v>
       </c>
       <c r="U19" t="n">
-        <v>2.796696745100693</v>
+        <v>2.796728359893468</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272134460288739</v>
+        <v>0.7272044884965926</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4713926323765815</v>
+        <v>0.4713806812010568</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6770346380909315</v>
+        <v>0.6770453446772331</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.326496609409588</v>
+        <v>8.324263605259533</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.567866916374783</v>
+        <v>8.512118500334259</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.068943520295367</v>
+        <v>9.059142362131203</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E20" t="n">
         <v>10668</v>
@@ -2213,40 +2213,40 @@
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490953736654804</v>
+        <v>7.490825035561878</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22802606778531</v>
+        <v>14.22800102705964</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3762942804577138</v>
+        <v>0.3762692397320391</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254068144307328</v>
+        <v>1.254070675129686</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645955819138877</v>
+        <v>1.645960189226345</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936933909682836</v>
+        <v>0.8936931002021843</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792845089120366</v>
+        <v>0.7792833368911709</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888734179246853</v>
+        <v>0.888875488761426</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19432206956288</v>
+        <v>10.19389280832069</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.44433038122849</v>
+        <v>10.5018274018517</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.89563804793787</v>
+        <v>10.97281040100833</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16718</v>
+        <v>16719</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9714740275805</v>
+        <v>130.9715447594343</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1049044233691283</v>
+        <v>0.1049751552229566</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971875976836983</v>
+        <v>0.7971864509082309</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045766363182889</v>
+        <v>1.045761174363429</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651103507621047</v>
+        <v>0.8651111805536315</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311621078743293</v>
+        <v>0.7311647756744699</v>
       </c>
       <c r="X21" t="n">
-        <v>0.864355030775247</v>
+        <v>0.8643538094288492</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5816824953997</v>
+        <v>128.5815595432693</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.0073152149784</v>
+        <v>128.9470386432032</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.0768808677328</v>
+        <v>129.4907520196261</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.326496609409588</v>
+        <v>8.324263605259533</v>
       </c>
       <c r="G2" t="n">
-        <v>8.567866916374783</v>
+        <v>8.512118500334259</v>
       </c>
       <c r="H2" t="n">
-        <v>9.068943520295367</v>
+        <v>9.059142362131203</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.628062598484314</v>
+        <v>5.620535798956852</v>
       </c>
       <c r="G3" t="n">
-        <v>5.76838161350379</v>
+        <v>5.746722629631958</v>
       </c>
       <c r="H3" t="n">
-        <v>5.841494362969141</v>
+        <v>5.8419680202165</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.469938256227758</v>
+        <v>4.544802223741506</v>
       </c>
       <c r="G4" t="n">
-        <v>4.839516672406087</v>
+        <v>4.804152504572715</v>
       </c>
       <c r="H4" t="n">
-        <v>5.119829885824436</v>
+        <v>5.390131325661599</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2481462997944</v>
+        <v>11.22423733715743</v>
       </c>
       <c r="G5" t="n">
-        <v>11.46452841317645</v>
+        <v>11.41121321801921</v>
       </c>
       <c r="H5" t="n">
-        <v>11.71966776273508</v>
+        <v>11.68819388832639</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.522384348406686</v>
+        <v>2.152626476708766</v>
       </c>
       <c r="G6" t="n">
-        <v>37.90176348076064</v>
+        <v>27.48018182084411</v>
       </c>
       <c r="H6" t="n">
-        <v>111.228335691152</v>
+        <v>111.0363096408297</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.272217796261787</v>
+        <v>9.235387432991583</v>
       </c>
       <c r="G7" t="n">
-        <v>9.368485360019474</v>
+        <v>9.357706753125157</v>
       </c>
       <c r="H7" t="n">
-        <v>9.454811932055346</v>
+        <v>9.456935412405977</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.339344952079651</v>
+        <v>8.164612003130284</v>
       </c>
       <c r="G8" t="n">
-        <v>8.44218698995318</v>
+        <v>8.420681913240424</v>
       </c>
       <c r="H8" t="n">
-        <v>8.495279701644662</v>
+        <v>8.495244442991119</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.643792633310336</v>
+        <v>4.643606534004756</v>
       </c>
       <c r="G9" t="n">
-        <v>5.092167561633112</v>
+        <v>5.079908123458017</v>
       </c>
       <c r="H9" t="n">
-        <v>5.912929932266954</v>
+        <v>5.576068752258946</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.928085312461491</v>
+        <v>5.927387973895619</v>
       </c>
       <c r="G10" t="n">
-        <v>5.969556708947666</v>
+        <v>5.964380426276763</v>
       </c>
       <c r="H10" t="n">
-        <v>6.006072356436264</v>
+        <v>6.006132026521935</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19432206956288</v>
+        <v>10.19389280832069</v>
       </c>
       <c r="G11" t="n">
-        <v>10.44433038122849</v>
+        <v>10.5018274018517</v>
       </c>
       <c r="H11" t="n">
-        <v>10.89563804793787</v>
+        <v>10.97281040100833</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.378083338841362</v>
+        <v>2.375644064630889</v>
       </c>
       <c r="G12" t="n">
-        <v>3.305635908101723</v>
+        <v>3.092505463610372</v>
       </c>
       <c r="H12" t="n">
-        <v>5.933850278024911</v>
+        <v>6.608509032764545</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.728788846257253</v>
+        <v>6.717039326036133</v>
       </c>
       <c r="G13" t="n">
-        <v>6.872370950665045</v>
+        <v>6.827568489066083</v>
       </c>
       <c r="H13" t="n">
-        <v>7.026916266613159</v>
+        <v>6.920607331757258</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.54511510833054</v>
+        <v>10.40238193040145</v>
       </c>
       <c r="G14" t="n">
-        <v>10.86529382894832</v>
+        <v>10.76775388905121</v>
       </c>
       <c r="H14" t="n">
-        <v>11.0816394719074</v>
+        <v>10.958721076975</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.715384060849725</v>
+        <v>4.561328858425056</v>
       </c>
       <c r="G15" t="n">
-        <v>4.865391714072655</v>
+        <v>4.62200480582123</v>
       </c>
       <c r="H15" t="n">
-        <v>5.03090020359707</v>
+        <v>4.71022865773097</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.001757931162066</v>
+        <v>7.980202384921441</v>
       </c>
       <c r="G16" t="n">
-        <v>8.114105265552624</v>
+        <v>8.08660651538727</v>
       </c>
       <c r="H16" t="n">
-        <v>8.216997367606787</v>
+        <v>8.194905175444054</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.122655127876211</v>
+        <v>2.109873259417139</v>
       </c>
       <c r="G17" t="n">
-        <v>3.903265073250706</v>
+        <v>3.669925704011194</v>
       </c>
       <c r="H17" t="n">
-        <v>7.313860026030051</v>
+        <v>7.355865781290819</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.368072323298321</v>
+        <v>3.367208772247723</v>
       </c>
       <c r="G18" t="n">
-        <v>3.660831642589085</v>
+        <v>3.729689710740335</v>
       </c>
       <c r="H18" t="n">
-        <v>4.215124555160142</v>
+        <v>4.258707590682788</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.168934726115554</v>
+        <v>3.276265778106192</v>
       </c>
       <c r="G19" t="n">
-        <v>3.296769091273823</v>
+        <v>3.307933197836745</v>
       </c>
       <c r="H19" t="n">
-        <v>3.334559430604982</v>
+        <v>3.33550213371266</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>5.862374433539736</v>
+        <v>6.039249573192007</v>
       </c>
       <c r="G20" t="n">
-        <v>6.526806098946288</v>
+        <v>6.507035203856415</v>
       </c>
       <c r="H20" t="n">
-        <v>6.993056983338183</v>
+        <v>7.013752386815321</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5816824953997</v>
+        <v>128.5815595432693</v>
       </c>
       <c r="G21" t="n">
-        <v>129.0073152149784</v>
+        <v>128.9470386432032</v>
       </c>
       <c r="H21" t="n">
-        <v>130.0768808677328</v>
+        <v>129.4907520196261</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,13 +576,13 @@
         <v>16719</v>
       </c>
       <c r="E2" t="n">
-        <v>10052</v>
+        <v>10053</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10052</v>
+        <v>10053</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,52 +599,52 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.4714473404961</v>
+        <v>102.4616526078451</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
       </c>
       <c r="P2" t="n">
-        <v>1.843186344238976</v>
+        <v>1.84321479374111</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4607244422094</v>
+        <v>102.4505437584923</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01072289828671053</v>
+        <v>-0.01110884935280095</v>
       </c>
       <c r="T2" t="n">
-        <v>18.14185163147563</v>
+        <v>18.15073891458287</v>
       </c>
       <c r="U2" t="n">
-        <v>36.27452885749324</v>
+        <v>36.28730829641553</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1366191181263721</v>
+        <v>0.1369941021218191</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7227294833915652</v>
+        <v>-0.7219413531067607</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1366159450416751</v>
+        <v>0.1369908640292691</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.152626476708766</v>
+        <v>2.157549944778347</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.48018182084412</v>
+        <v>26.18492964118096</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.0363096408297</v>
+        <v>111.0357505115546</v>
       </c>
     </row>
     <row r="3">
@@ -703,28 +703,28 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.961847050402432</v>
+        <v>4.961851841378996</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05774907143206433</v>
+        <v>0.05775386240862915</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343318884013162</v>
+        <v>1.343322976115963</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717868673725026</v>
+        <v>1.717872092765445</v>
       </c>
       <c r="V3" t="n">
-        <v>0.781652855543876</v>
+        <v>0.7816519067268722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5703153896643191</v>
+        <v>0.5703136792768668</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7806043563505936</v>
+        <v>0.7806033120456056</v>
       </c>
       <c r="Y3" t="n">
         <v>3.276265778106192</v>
@@ -783,7 +783,7 @@
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.90011843385214</v>
+        <v>6.900121108949416</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,28 +792,28 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230300376279035</v>
+        <v>7.230314430930373</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3301819424268952</v>
+        <v>0.330193321980956</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290825559277405</v>
+        <v>1.290832792546139</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680535527172181</v>
+        <v>1.68054375212551</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8680499049794653</v>
+        <v>0.8680489294380486</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7382270598215168</v>
+        <v>0.7382240802411092</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473594699029596</v>
+        <v>0.8473592973794031</v>
       </c>
       <c r="Y4" t="n">
         <v>3.367208772247723</v>
@@ -843,13 +843,13 @@
         <v>16719</v>
       </c>
       <c r="E5" t="n">
-        <v>2722</v>
+        <v>2743</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2722</v>
+        <v>2743</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,52 +866,52 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46278</v>
+        <v>46297</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.932461425422483</v>
+        <v>8.920539555231498</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82217716630461</v>
+        <v>2.837179866765359</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.301667357587347</v>
+        <v>9.305077143273566</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.369205932164863</v>
+        <v>0.3845375880420678</v>
       </c>
       <c r="T5" t="n">
-        <v>1.247520499273013</v>
+        <v>1.249290381671169</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747112346065408</v>
+        <v>1.751116660221625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661265481865181</v>
+        <v>0.8648712779127721</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7215236327808485</v>
+        <v>0.7192413271549941</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8597387832140859</v>
+        <v>0.8576762208931431</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.039249573192007</v>
+        <v>6.108769686273214</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.507035203856414</v>
+        <v>6.561570859545462</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.013752386815321</v>
+        <v>7.00785775845493</v>
       </c>
     </row>
     <row r="6">
@@ -961,7 +961,7 @@
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734223715281683</v>
+        <v>6.734220904081862</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,28 +970,28 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.022889787697532</v>
+        <v>7.02288561071244</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886660724158501</v>
+        <v>0.2886647066305782</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477919142633874</v>
+        <v>1.477918718037959</v>
       </c>
       <c r="U6" t="n">
-        <v>1.906153515383275</v>
+        <v>1.90615186319756</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039899612283271</v>
+        <v>0.3039926458994027</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979800664522227</v>
+        <v>-0.1979766534326828</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789933898146494</v>
+        <v>0.2789963054310313</v>
       </c>
       <c r="Y6" t="n">
         <v>7.980202384921441</v>
@@ -1021,13 +1021,13 @@
         <v>16719</v>
       </c>
       <c r="E7" t="n">
-        <v>14254</v>
+        <v>14258</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14254</v>
+        <v>14256</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.579188368177354</v>
+        <v>5.578931572671156</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565557844204818</v>
+        <v>5.565297808768628</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01363052397253594</v>
+        <v>-0.01363376390252781</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166345704451679</v>
+        <v>1.166494688387604</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509456864251476</v>
+        <v>1.509537706941726</v>
       </c>
       <c r="V7" t="n">
-        <v>0.504995865126238</v>
+        <v>0.5049782611339602</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05330517509950194</v>
+        <v>0.05325576037553981</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028605756520448</v>
+        <v>0.5028446691726332</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.620535798956852</v>
+        <v>5.617862731152206</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.746722629631958</v>
+        <v>5.74487893105801</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.8419680202165</v>
+        <v>5.839593161459207</v>
       </c>
     </row>
     <row r="8">
@@ -1139,7 +1139,7 @@
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.870312085726911</v>
+        <v>7.870313742819265</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,28 +1148,28 @@
         <v>0.6454054054054055</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.11034093791795</v>
+        <v>8.110351240465164</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2400288521910396</v>
+        <v>0.2400374976458977</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444664896385715</v>
+        <v>1.444668904206799</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824485900973142</v>
+        <v>1.824490818855671</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078933856969033</v>
+        <v>0.8078928561758738</v>
       </c>
       <c r="W8" t="n">
-        <v>0.627624907466344</v>
+        <v>0.627622567580989</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976847757463237</v>
+        <v>0.7976849847587307</v>
       </c>
       <c r="Y8" t="n">
         <v>5.927387973895619</v>
@@ -1228,7 +1228,7 @@
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.60726198174894</v>
+        <v>7.607262520658187</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,28 +1237,28 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65273651969283</v>
+        <v>7.652744019887385</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04547453794389029</v>
+        <v>0.0454814992291973</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493120986052457</v>
+        <v>1.493124732215565</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94104044713388</v>
+        <v>1.941045729718972</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567746482669954</v>
+        <v>0.7567740986317479</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5250839438603485</v>
+        <v>0.525081184590777</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553586795382219</v>
+        <v>0.7553584972544695</v>
       </c>
       <c r="Y9" t="n">
         <v>4.561328858425056</v>
@@ -1377,13 +1377,13 @@
         <v>16719</v>
       </c>
       <c r="E11" t="n">
-        <v>13858</v>
+        <v>13862</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13858</v>
+        <v>13860</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241502886419397</v>
+        <v>5.241259343434344</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.215155301586217</v>
+        <v>5.214871268843941</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02634758483318015</v>
+        <v>-0.02638807459040206</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161086243757449</v>
+        <v>1.161098191716506</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48243369422369</v>
+        <v>1.48240665462847</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295300103045526</v>
+        <v>0.4295745181270334</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09181606435057277</v>
+        <v>-0.09170967998923873</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277244769638568</v>
+        <v>0.4277670898092244</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.544802223741506</v>
+        <v>4.542676477605169</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.804152504572716</v>
+        <v>4.801059844223966</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.390131325661599</v>
+        <v>5.388173399962462</v>
       </c>
     </row>
     <row r="12">
@@ -1466,13 +1466,13 @@
         <v>16719</v>
       </c>
       <c r="E12" t="n">
-        <v>4176</v>
+        <v>4180</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4176</v>
+        <v>4178</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.453832255747126</v>
+        <v>7.452139420775491</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.627088161562525</v>
+        <v>7.624068436698465</v>
       </c>
       <c r="R12" t="n">
-        <v>16.57646941678532</v>
+        <v>16.4252176386914</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732559058153977</v>
+        <v>0.171929015922975</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9112472990334154</v>
+        <v>0.9115624291693747</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191315742931739</v>
+        <v>1.19104848372388</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8335881902317438</v>
+        <v>0.8338221816722003</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6628349468711419</v>
+        <v>0.6633029127310324</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8317525375636143</v>
+        <v>0.832025503215859</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.643606534004756</v>
+        <v>4.584654968918231</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.079908123458017</v>
+        <v>5.035511914090483</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.576068752258946</v>
+        <v>5.539605638327779</v>
       </c>
     </row>
     <row r="13">
@@ -1555,13 +1555,13 @@
         <v>16719</v>
       </c>
       <c r="E13" t="n">
-        <v>6510</v>
+        <v>6515</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6510</v>
+        <v>6513</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.595077956989247</v>
+        <v>9.593820819898664</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.01958829791547</v>
+        <v>10.0194743596443</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4245103409262185</v>
+        <v>0.4256535397456353</v>
       </c>
       <c r="T13" t="n">
-        <v>1.688368118574974</v>
+        <v>1.687986008904691</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146888685923055</v>
+        <v>2.146253201861295</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8235005292878804</v>
+        <v>0.8235632889035813</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6493430933555674</v>
+        <v>0.6494806851121926</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8103046887138663</v>
+        <v>0.8102234451818412</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.164612003130284</v>
+        <v>8.156944825589445</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.420681913240426</v>
+        <v>8.402928906640465</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.495244442991119</v>
+        <v>8.492128969028803</v>
       </c>
     </row>
     <row r="14">
@@ -1682,28 +1682,28 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.194815661259177</v>
+        <v>8.194821264656223</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07062588256716462</v>
+        <v>0.07063148596421016</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754720019015761</v>
+        <v>1.754724988079525</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280384990403653</v>
+        <v>2.280389438721909</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810978112648528</v>
+        <v>0.7810972674491736</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5658894606229459</v>
+        <v>0.5658877669933797</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807150770749819</v>
+        <v>0.7807145644103439</v>
       </c>
       <c r="Y14" t="n">
         <v>6.717039326036133</v>
@@ -1822,13 +1822,13 @@
         <v>16719</v>
       </c>
       <c r="E16" t="n">
-        <v>9861</v>
+        <v>9865</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9861</v>
+        <v>9863</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.359155663725788</v>
+        <v>8.358650410625572</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.6219544514283</v>
+        <v>8.621293594276102</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2627987877025126</v>
+        <v>0.2626431836505316</v>
       </c>
       <c r="T16" t="n">
-        <v>3.600632761785126</v>
+        <v>3.601772558838007</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0811777949922</v>
+        <v>11.08051114372743</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04112460823350876</v>
+        <v>0.04105417055964067</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6109436187132438</v>
+        <v>-0.6110498596751628</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02446476430253375</v>
+        <v>0.02439504523050406</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.22423733715743</v>
+        <v>11.21011135983297</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.41121321801921</v>
+        <v>11.40012777945561</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.68819388832639</v>
+        <v>11.67877199773895</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.45527027027027</v>
+        <v>6.455278586278586</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,28 +1949,28 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.819645680125721</v>
+        <v>6.819669496560548</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.36437540985545</v>
+        <v>0.3643909102819612</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008022843392421</v>
+        <v>2.008006685010011</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545714695105788</v>
+        <v>2.545692165545333</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5402955041718577</v>
+        <v>0.5402963571966212</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05962857603065019</v>
+        <v>0.05963683428246824</v>
       </c>
       <c r="X17" t="n">
-        <v>0.536839348481594</v>
+        <v>0.5368399472899019</v>
       </c>
       <c r="Y17" t="n">
         <v>2.375644064630889</v>
@@ -2029,7 +2029,7 @@
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.458137714460784</v>
+        <v>6.458156096813726</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,28 +2038,28 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.654628763315593</v>
+        <v>6.654652334962555</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1964910488548093</v>
+        <v>0.1964962381488293</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095637563961652</v>
+        <v>1.095628026901674</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483947781158079</v>
+        <v>1.483921488955519</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6100401809183926</v>
+        <v>0.6100383606136529</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2356320115382119</v>
+        <v>0.2356309249779015</v>
       </c>
       <c r="X18" t="n">
-        <v>0.606907484243032</v>
+        <v>0.6069051109679566</v>
       </c>
       <c r="Y18" t="n">
         <v>2.109873259417139</v>
@@ -2089,13 +2089,13 @@
         <v>16719</v>
       </c>
       <c r="E19" t="n">
-        <v>7218</v>
+        <v>7222</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7218</v>
+        <v>7220</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.30327777777778</v>
+        <v>10.30087243767313</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10482564912382</v>
+        <v>11.10266716766149</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8015478713460413</v>
+        <v>0.8017947299883611</v>
       </c>
       <c r="T19" t="n">
-        <v>2.068777552367534</v>
+        <v>2.07032572182269</v>
       </c>
       <c r="U19" t="n">
-        <v>2.796728359893468</v>
+        <v>2.798668739398699</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7272044884965926</v>
+        <v>0.7270970810102223</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4713806812010568</v>
+        <v>0.4712466169106744</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6770453446772331</v>
+        <v>0.6768938019796565</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.324263605259533</v>
+        <v>8.320961431092973</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.512118500334259</v>
+        <v>8.496773385012922</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.059142362131203</v>
+        <v>9.04325551592283</v>
       </c>
     </row>
     <row r="20">
@@ -2207,7 +2207,7 @@
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8517317873276</v>
+        <v>13.8517732665177</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
@@ -2216,28 +2216,28 @@
         <v>7.490825035561878</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22800102705964</v>
+        <v>14.22806791521875</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3762692397320391</v>
+        <v>0.3762946487010471</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254070675129686</v>
+        <v>1.254113768839873</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645960189226345</v>
+        <v>1.645982716442202</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936931002021843</v>
+        <v>0.8936874280095679</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792833368911709</v>
+        <v>0.7792719823652985</v>
       </c>
       <c r="X20" t="n">
-        <v>0.888875488761426</v>
+        <v>0.8888681827308492</v>
       </c>
       <c r="Y20" t="n">
         <v>10.19389280832069</v>
@@ -2413,13 +2413,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.324263605259533</v>
+        <v>8.320961431092973</v>
       </c>
       <c r="G2" t="n">
-        <v>8.512118500334259</v>
+        <v>8.496773385012922</v>
       </c>
       <c r="H2" t="n">
-        <v>9.059142362131203</v>
+        <v>9.04325551592283</v>
       </c>
     </row>
     <row r="3">
@@ -2441,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.620535798956852</v>
+        <v>5.617862731152206</v>
       </c>
       <c r="G3" t="n">
-        <v>5.746722629631958</v>
+        <v>5.74487893105801</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8419680202165</v>
+        <v>5.839593161459207</v>
       </c>
     </row>
     <row r="4">
@@ -2469,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.544802223741506</v>
+        <v>4.542676477605169</v>
       </c>
       <c r="G4" t="n">
-        <v>4.804152504572715</v>
+        <v>4.801059844223966</v>
       </c>
       <c r="H4" t="n">
-        <v>5.390131325661599</v>
+        <v>5.388173399962462</v>
       </c>
     </row>
     <row r="5">
@@ -2497,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22423733715743</v>
+        <v>11.21011135983297</v>
       </c>
       <c r="G5" t="n">
-        <v>11.41121321801921</v>
+        <v>11.40012777945561</v>
       </c>
       <c r="H5" t="n">
-        <v>11.68819388832639</v>
+        <v>11.67877199773895</v>
       </c>
     </row>
     <row r="6">
@@ -2525,13 +2525,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.152626476708766</v>
+        <v>2.157549944778347</v>
       </c>
       <c r="G6" t="n">
-        <v>27.48018182084411</v>
+        <v>26.18492964118096</v>
       </c>
       <c r="H6" t="n">
-        <v>111.0363096408297</v>
+        <v>111.0357505115546</v>
       </c>
     </row>
     <row r="7">
@@ -2581,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.164612003130284</v>
+        <v>8.156944825589445</v>
       </c>
       <c r="G8" t="n">
-        <v>8.420681913240424</v>
+        <v>8.402928906640465</v>
       </c>
       <c r="H8" t="n">
-        <v>8.495244442991119</v>
+        <v>8.492128969028803</v>
       </c>
     </row>
     <row r="9">
@@ -2609,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.643606534004756</v>
+        <v>4.584654968918231</v>
       </c>
       <c r="G9" t="n">
-        <v>5.079908123458017</v>
+        <v>5.035511914090483</v>
       </c>
       <c r="H9" t="n">
-        <v>5.576068752258946</v>
+        <v>5.539605638327779</v>
       </c>
     </row>
     <row r="10">
@@ -2724,7 +2724,7 @@
         <v>6.717039326036133</v>
       </c>
       <c r="G13" t="n">
-        <v>6.827568489066083</v>
+        <v>6.827568489066081</v>
       </c>
       <c r="H13" t="n">
         <v>6.920607331757258</v>
@@ -2917,13 +2917,13 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.039249573192007</v>
+        <v>6.108769686273214</v>
       </c>
       <c r="G20" t="n">
-        <v>6.507035203856415</v>
+        <v>6.561570859545462</v>
       </c>
       <c r="H20" t="n">
-        <v>7.013752386815321</v>
+        <v>7.00785775845493</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E2" t="n">
         <v>10053</v>
@@ -602,49 +602,49 @@
         <v>46304</v>
       </c>
       <c r="M2" t="n">
-        <v>1.78</v>
+        <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>102.4616526078451</v>
+        <v>11.56808302662555</v>
       </c>
       <c r="O2" t="n">
-        <v>118.97</v>
+        <v>65.36500000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84321479374111</v>
+        <v>0.5074366401158565</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.4505437584923</v>
+        <v>11.2582698444753</v>
       </c>
       <c r="R2" t="n">
-        <v>118.8919225199131</v>
+        <v>64.96884503982621</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01110884935280095</v>
+        <v>-0.3098131821502448</v>
       </c>
       <c r="T2" t="n">
-        <v>18.15073891458287</v>
+        <v>6.611855785763316</v>
       </c>
       <c r="U2" t="n">
-        <v>36.28730829641553</v>
+        <v>16.97472375243922</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1369941021218191</v>
+        <v>0.1525841221307083</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7219413531067607</v>
+        <v>-0.6105670823336682</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1369908640292691</v>
+        <v>0.1505918729492578</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.157549944778347</v>
+        <v>0.7381195474426202</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.18492964118096</v>
+        <v>2.616026039023854</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.0357505115546</v>
+        <v>6.191417565347168</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E3" t="n">
         <v>14646</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.961851841378996</v>
+        <v>4.961770589246938</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05775386240862915</v>
+        <v>0.05767261027657095</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343322976115963</v>
+        <v>1.343333594382426</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717872092765445</v>
+        <v>1.717878171565639</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816519067268722</v>
+        <v>0.7816567925011125</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5703136792768668</v>
+        <v>0.57031063832647</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7806033120456056</v>
+        <v>0.7806119097561228</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.276265778106192</v>
+        <v>3.251625799573561</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.307933197836745</v>
+        <v>3.306653911641673</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.33550213371266</v>
+        <v>3.336443496801705</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E4" t="n">
         <v>10280</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230314430930373</v>
+        <v>7.230292485238992</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.330193321980956</v>
+        <v>0.3301713762895755</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290832792546139</v>
+        <v>1.290838932810581</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68054375212551</v>
+        <v>1.680551640862065</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8680489294380486</v>
+        <v>0.868047981026839</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7382240802411092</v>
+        <v>0.7382216226007035</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473592973794031</v>
+        <v>0.8473649828124795</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.367208772247723</v>
+        <v>3.366340613296884</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.729689710740335</v>
+        <v>3.820118494544826</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.258707590682788</v>
+        <v>4.296610796464107</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E5" t="n">
         <v>2743</v>
@@ -881,37 +881,37 @@
         <v>2.837179866765359</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.305077143273566</v>
+        <v>9.305030705070164</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3845375880420678</v>
+        <v>0.3844911498386656</v>
       </c>
       <c r="T5" t="n">
-        <v>1.249290381671169</v>
+        <v>1.249299247227283</v>
       </c>
       <c r="U5" t="n">
-        <v>1.751116660221625</v>
+        <v>1.751128415260552</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8648712779127721</v>
+        <v>0.8648702902941177</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7192413271549941</v>
+        <v>0.7192375577428463</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8576762208931431</v>
+        <v>0.8576785603044491</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.108769686273214</v>
+        <v>6.335622842365987</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.561570859545462</v>
+        <v>6.779765906098485</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.00785775845493</v>
+        <v>7.400673597080102</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E6" t="n">
-        <v>8893</v>
+        <v>8897</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8893</v>
+        <v>8896</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734220904081862</v>
+        <v>6.734068570143885</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02288561071244</v>
+        <v>7.023114245871691</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886647066305782</v>
+        <v>0.2890456757278056</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477918718037959</v>
+        <v>1.477905995867914</v>
       </c>
       <c r="U6" t="n">
-        <v>1.90615186319756</v>
+        <v>1.905884168519949</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039926458994027</v>
+        <v>0.3039627664350392</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1979766534326828</v>
+        <v>-0.1980107576099264</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789963054310313</v>
+        <v>0.2789402913050505</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.980202384921441</v>
+        <v>7.995119385297689</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.08660651538727</v>
+        <v>8.068649629952082</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.194905175444054</v>
+        <v>8.155718036804291</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E7" t="n">
         <v>14258</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14256</v>
+        <v>14257</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.578931572671156</v>
+        <v>5.578795574103949</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565297808768628</v>
+        <v>5.565244335741485</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01363376390252781</v>
+        <v>-0.01355123836246403</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166494688387604</v>
+        <v>1.166558014972743</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509537706941726</v>
+        <v>1.5095887424729</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049782611339602</v>
+        <v>0.5049506774874986</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05325576037553981</v>
+        <v>0.05322905388369581</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5028446691726332</v>
+        <v>0.50281470409333</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.617862731152206</v>
+        <v>5.600397927729142</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.74487893105801</v>
+        <v>5.725733088036785</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.839593161459207</v>
+        <v>5.840280323729897</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E8" t="n">
-        <v>9052</v>
+        <v>9056</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9052</v>
+        <v>9055</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.870313742819265</v>
+        <v>7.869501656543346</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454054054054055</v>
+        <v>0.6454797441364606</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.110351240465164</v>
+        <v>8.110008683012152</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2400374976458977</v>
+        <v>0.2405070264688051</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444668904206799</v>
+        <v>1.444299737891028</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824490818855671</v>
+        <v>1.824103935672198</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078928561758738</v>
+        <v>0.8079367937631027</v>
       </c>
       <c r="W8" t="n">
-        <v>0.627622567580989</v>
+        <v>0.6277399808988013</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976849847587307</v>
+        <v>0.7976561983656395</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.927387973895619</v>
+        <v>5.925823643437735</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.964380426276763</v>
+        <v>5.953390312529256</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.006132026521935</v>
+        <v>6.003142612987197</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E9" t="n">
-        <v>13917</v>
+        <v>13921</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13917</v>
+        <v>13920</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.607262520658187</v>
+        <v>7.606661278735633</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.652744019887385</v>
+        <v>7.652266649809399</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0454814992291973</v>
+        <v>0.04560537107376784</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493124732215565</v>
+        <v>1.493073809258751</v>
       </c>
       <c r="U9" t="n">
-        <v>1.941045729718972</v>
+        <v>1.940901631084011</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567740986317479</v>
+        <v>0.7567993132644866</v>
       </c>
       <c r="W9" t="n">
-        <v>0.525081184590777</v>
+        <v>0.5251500047580205</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553584972544695</v>
+        <v>0.7553780775315138</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.561328858425056</v>
+        <v>4.444570053022026</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.62200480582123</v>
+        <v>4.498492076692724</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.71022865773097</v>
+        <v>4.599603617560895</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61346102923209</v>
+        <v>10.6133260134464</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3083993487397151</v>
+        <v>0.3082643329540263</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05411659876024</v>
+        <v>2.054182298536944</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699884131989016</v>
+        <v>2.699952098690571</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569817486381488</v>
+        <v>0.3569757718847842</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1219223127350115</v>
+        <v>-0.1219787998396935</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370498807974437</v>
+        <v>0.3370592926468574</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.40238193040145</v>
+        <v>10.67809419666223</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.76775388905121</v>
+        <v>10.83149045610182</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.958721076975</v>
+        <v>10.96029632316358</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E11" t="n">
         <v>13862</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13860</v>
+        <v>13861</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241259343434344</v>
+        <v>5.241141836808311</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.214871268843941</v>
+        <v>5.214823523530868</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02638807459040206</v>
+        <v>-0.0263183132774421</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161098191716506</v>
+        <v>1.161126942995118</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48240665462847</v>
+        <v>1.482412802644716</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295745181270334</v>
+        <v>0.429571868856173</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09170967998923873</v>
+        <v>-0.09169370408695476</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277670898092244</v>
+        <v>0.4277631219699053</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.542676477605169</v>
+        <v>4.701725233579128</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.801059844223966</v>
+        <v>4.85751575841558</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.388173399962462</v>
+        <v>5.202920220326937</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E12" t="n">
         <v>4180</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4178</v>
+        <v>4179</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.452139420775491</v>
+        <v>7.451298994974874</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.624068436698465</v>
+        <v>7.623489098597893</v>
       </c>
       <c r="R12" t="n">
-        <v>16.4252176386914</v>
+        <v>16.43473134328356</v>
       </c>
       <c r="S12" t="n">
-        <v>0.171929015922975</v>
+        <v>0.1721901036230179</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9115624291693747</v>
+        <v>0.9116260742350172</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19104848372388</v>
+        <v>1.191098479013898</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8338221816722003</v>
+        <v>0.833871933853335</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6633029127310324</v>
+        <v>0.6634298419598127</v>
       </c>
       <c r="X12" t="n">
-        <v>0.832025503215859</v>
+        <v>0.8320622707655608</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.584654968918231</v>
+        <v>4.584126169283526</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.035511914090483</v>
+        <v>5.114694837001774</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.539605638327779</v>
+        <v>5.687286014764908</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E13" t="n">
         <v>6515</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6513</v>
+        <v>6514</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.593820819898664</v>
+        <v>9.593373503223825</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.0194743596443</v>
+        <v>10.01906694018444</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4256535397456353</v>
+        <v>0.42569343696062</v>
       </c>
       <c r="T13" t="n">
-        <v>1.687986008904691</v>
+        <v>1.687936205348153</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146253201861295</v>
+        <v>2.146144542081087</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8235632889035813</v>
+        <v>0.8235757051936923</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6494806851121926</v>
+        <v>0.6494971263823407</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102234451818412</v>
+        <v>0.8102378512623056</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.156944825589445</v>
+        <v>8.068441089188404</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.402928906640465</v>
+        <v>8.371162494796398</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.492128969028803</v>
+        <v>8.492575186788716</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E14" t="n">
-        <v>14098</v>
+        <v>14102</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14098</v>
+        <v>14101</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.124189778692013</v>
+        <v>8.123650450322673</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.194821264656223</v>
+        <v>8.194731411604025</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07063148596421016</v>
+        <v>0.0710809612813524</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754724988079525</v>
+        <v>1.754499113461919</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280389438721909</v>
+        <v>2.280028022379507</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810972674491736</v>
+        <v>0.7811198027282905</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5658877669933797</v>
+        <v>0.5659825977777241</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807145644103439</v>
+        <v>0.7807289852972203</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.717039326036133</v>
+        <v>6.702065448124668</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.827568489066083</v>
+        <v>6.800969151157443</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.920607331757258</v>
+        <v>6.873109344364697</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81916243009333</v>
+        <v>11.81903372501387</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1447249529334482</v>
+        <v>-0.1448536580129099</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052698142197533</v>
+        <v>2.052728711159388</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698697000117535</v>
+        <v>2.698761612191607</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949799782331872</v>
+        <v>0.7949765779692634</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6092901608951687</v>
+        <v>0.6092714519587703</v>
       </c>
       <c r="X15" t="n">
-        <v>0.786557778124905</v>
+        <v>0.78656344819357</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.235387432991583</v>
+        <v>9.128971911198008</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.357706753125157</v>
+        <v>9.335294339033213</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.456935412405977</v>
+        <v>9.458578484405498</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E16" t="n">
         <v>9865</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9863</v>
+        <v>9864</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.358650410625572</v>
+        <v>8.358416869424168</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.621293594276102</v>
+        <v>8.621530391530774</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2626431836505316</v>
+        <v>0.2631135221066057</v>
       </c>
       <c r="T16" t="n">
-        <v>3.601772558838007</v>
+        <v>3.602034565769024</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08051114372743</v>
+        <v>11.08010150259243</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04105417055964067</v>
+        <v>0.04103992749104373</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6110498596751628</v>
+        <v>-0.6110826997932084</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02439504523050406</v>
+        <v>0.02437990468063245</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.21011135983297</v>
+        <v>11.21714421811913</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.40012777945561</v>
+        <v>11.35915135366602</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.67877199773895</v>
+        <v>11.64619504174045</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E17" t="n">
-        <v>2405</v>
+        <v>2409</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.455278586278586</v>
+        <v>6.449930440199335</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.819669496560548</v>
+        <v>6.811986455212473</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3643909102819612</v>
+        <v>0.3620560150131394</v>
       </c>
       <c r="T17" t="n">
-        <v>2.008006685010011</v>
+        <v>2.007371098409879</v>
       </c>
       <c r="U17" t="n">
-        <v>2.545692165545333</v>
+        <v>2.544877102197267</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5402963571966212</v>
+        <v>0.5417366769296872</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05963683428246824</v>
+        <v>0.0621896698627179</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5368399472899019</v>
+        <v>0.5383047569077344</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.375644064630889</v>
+        <v>2.083863368998019</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.092505463610372</v>
+        <v>3.787919856315079</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.608509032764545</v>
+        <v>7.326682850258627</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E18" t="n">
-        <v>3264</v>
+        <v>3266</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3264</v>
+        <v>3266</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.458156096813726</v>
+        <v>6.456043018983467</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.654652334962555</v>
+        <v>6.651667925445653</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1964962381488293</v>
+        <v>0.1956249064621876</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095628026901674</v>
+        <v>1.095374807839438</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483921488955519</v>
+        <v>1.483792128243137</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6100383606136529</v>
+        <v>0.6109910114094841</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2356309249779015</v>
+        <v>0.2372204450049546</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6069051109679566</v>
+        <v>0.6079142693757815</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.109873259417139</v>
+        <v>2.211943978544877</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.669925704011194</v>
+        <v>4.539447742708045</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.355865781290819</v>
+        <v>7.211645732150454</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E19" t="n">
         <v>7222</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7220</v>
+        <v>7221</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.30087243767313</v>
+        <v>10.29964153164382</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10266716766149</v>
+        <v>11.10224776920565</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8017947299883611</v>
+        <v>0.8026062375618287</v>
       </c>
       <c r="T19" t="n">
-        <v>2.07032572182269</v>
+        <v>2.071062277241749</v>
       </c>
       <c r="U19" t="n">
-        <v>2.798668739398699</v>
+        <v>2.799820721245586</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270970810102223</v>
+        <v>0.7270288912601822</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4712466169106744</v>
+        <v>0.4711285575408433</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6768938019796565</v>
+        <v>0.6766956386248091</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.320961431092973</v>
+        <v>8.324958610309794</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.496773385012922</v>
+        <v>8.657322808804787</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.04325551592283</v>
+        <v>10.34558565429037</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E20" t="n">
-        <v>10668</v>
+        <v>10670</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10668</v>
+        <v>10670</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>35325</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8517732665177</v>
+        <v>13.85095686103194</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490825035561878</v>
+        <v>7.491094527363185</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22806791521875</v>
+        <v>14.2272317183471</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3762946487010471</v>
+        <v>0.3762748573151617</v>
       </c>
       <c r="T20" t="n">
-        <v>1.254113768839873</v>
+        <v>1.253954439959021</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645982716442202</v>
+        <v>1.645811185995683</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8936874280095679</v>
+        <v>0.8937216973369404</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7792719823652985</v>
+        <v>0.7793404408332805</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8888681827308492</v>
+        <v>0.8889020496636623</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19389280832069</v>
+        <v>10.19645247512745</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.5018274018517</v>
+        <v>10.57264020991435</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.97281040100833</v>
+        <v>10.97858506764648</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="E21" t="n">
         <v>10258</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9715447594343</v>
+        <v>130.9716201042233</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1049751552229566</v>
+        <v>0.1050505000119313</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971864509082309</v>
+        <v>0.7971767189421469</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045761174363429</v>
+        <v>1.045743659361439</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651111805536315</v>
+        <v>0.8651149374848335</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311647756744699</v>
+        <v>0.7311737808090513</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643538094288492</v>
+        <v>0.8643551421447075</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5815595432693</v>
+        <v>128.5813334894187</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.9470386432032</v>
+        <v>129.1016232055392</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.4907520196261</v>
+        <v>129.799229204734</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.320961431092973</v>
+        <v>8.324958610309794</v>
       </c>
       <c r="G2" t="n">
-        <v>8.496773385012922</v>
+        <v>8.657322808804789</v>
       </c>
       <c r="H2" t="n">
-        <v>9.04325551592283</v>
+        <v>10.34558565429037</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.617862731152206</v>
+        <v>5.600397927729142</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74487893105801</v>
+        <v>5.725733088036785</v>
       </c>
       <c r="H3" t="n">
-        <v>5.839593161459207</v>
+        <v>5.840280323729897</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.542676477605169</v>
+        <v>4.701725233579128</v>
       </c>
       <c r="G4" t="n">
-        <v>4.801059844223966</v>
+        <v>4.85751575841558</v>
       </c>
       <c r="H4" t="n">
-        <v>5.388173399962462</v>
+        <v>5.202920220326937</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.21011135983297</v>
+        <v>11.21714421811913</v>
       </c>
       <c r="G5" t="n">
-        <v>11.40012777945561</v>
+        <v>11.35915135366602</v>
       </c>
       <c r="H5" t="n">
-        <v>11.67877199773895</v>
+        <v>11.64619504174045</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.157549944778347</v>
+        <v>0.7381195474426202</v>
       </c>
       <c r="G6" t="n">
-        <v>26.18492964118096</v>
+        <v>2.616026039023854</v>
       </c>
       <c r="H6" t="n">
-        <v>111.0357505115546</v>
+        <v>6.191417565347168</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.235387432991583</v>
+        <v>9.128971911198008</v>
       </c>
       <c r="G7" t="n">
-        <v>9.357706753125157</v>
+        <v>9.335294339033213</v>
       </c>
       <c r="H7" t="n">
-        <v>9.456935412405977</v>
+        <v>9.458578484405498</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.156944825589445</v>
+        <v>8.068441089188404</v>
       </c>
       <c r="G8" t="n">
-        <v>8.402928906640465</v>
+        <v>8.371162494796399</v>
       </c>
       <c r="H8" t="n">
-        <v>8.492128969028803</v>
+        <v>8.492575186788716</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.584654968918231</v>
+        <v>4.584126169283526</v>
       </c>
       <c r="G9" t="n">
-        <v>5.035511914090483</v>
+        <v>5.114694837001774</v>
       </c>
       <c r="H9" t="n">
-        <v>5.539605638327779</v>
+        <v>5.687286014764908</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.927387973895619</v>
+        <v>5.925823643437735</v>
       </c>
       <c r="G10" t="n">
-        <v>5.964380426276763</v>
+        <v>5.953390312529256</v>
       </c>
       <c r="H10" t="n">
-        <v>6.006132026521935</v>
+        <v>6.003142612987197</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19389280832069</v>
+        <v>10.19645247512745</v>
       </c>
       <c r="G11" t="n">
-        <v>10.5018274018517</v>
+        <v>10.57264020991435</v>
       </c>
       <c r="H11" t="n">
-        <v>10.97281040100833</v>
+        <v>10.97858506764648</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.375644064630889</v>
+        <v>2.083863368998019</v>
       </c>
       <c r="G12" t="n">
-        <v>3.092505463610372</v>
+        <v>3.787919856315079</v>
       </c>
       <c r="H12" t="n">
-        <v>6.608509032764545</v>
+        <v>7.326682850258627</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.717039326036133</v>
+        <v>6.702065448124668</v>
       </c>
       <c r="G13" t="n">
-        <v>6.827568489066081</v>
+        <v>6.800969151157443</v>
       </c>
       <c r="H13" t="n">
-        <v>6.920607331757258</v>
+        <v>6.873109344364697</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.40238193040145</v>
+        <v>10.67809419666223</v>
       </c>
       <c r="G14" t="n">
-        <v>10.76775388905121</v>
+        <v>10.83149045610182</v>
       </c>
       <c r="H14" t="n">
-        <v>10.958721076975</v>
+        <v>10.96029632316358</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.561328858425056</v>
+        <v>4.444570053022026</v>
       </c>
       <c r="G15" t="n">
-        <v>4.62200480582123</v>
+        <v>4.498492076692724</v>
       </c>
       <c r="H15" t="n">
-        <v>4.71022865773097</v>
+        <v>4.599603617560895</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.980202384921441</v>
+        <v>7.995119385297689</v>
       </c>
       <c r="G16" t="n">
-        <v>8.08660651538727</v>
+        <v>8.068649629952082</v>
       </c>
       <c r="H16" t="n">
-        <v>8.194905175444054</v>
+        <v>8.155718036804291</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.109873259417139</v>
+        <v>2.211943978544877</v>
       </c>
       <c r="G17" t="n">
-        <v>3.669925704011194</v>
+        <v>4.539447742708044</v>
       </c>
       <c r="H17" t="n">
-        <v>7.355865781290819</v>
+        <v>7.211645732150454</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.367208772247723</v>
+        <v>3.366340613296884</v>
       </c>
       <c r="G18" t="n">
-        <v>3.729689710740335</v>
+        <v>3.820118494544826</v>
       </c>
       <c r="H18" t="n">
-        <v>4.258707590682788</v>
+        <v>4.296610796464107</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.276265778106192</v>
+        <v>3.251625799573561</v>
       </c>
       <c r="G19" t="n">
-        <v>3.307933197836745</v>
+        <v>3.306653911641673</v>
       </c>
       <c r="H19" t="n">
-        <v>3.33550213371266</v>
+        <v>3.336443496801705</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.108769686273214</v>
+        <v>6.335622842365987</v>
       </c>
       <c r="G20" t="n">
-        <v>6.561570859545462</v>
+        <v>6.779765906098485</v>
       </c>
       <c r="H20" t="n">
-        <v>7.00785775845493</v>
+        <v>7.400673597080102</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5815595432693</v>
+        <v>128.5813334894187</v>
       </c>
       <c r="G21" t="n">
-        <v>128.9470386432032</v>
+        <v>129.1016232055392</v>
       </c>
       <c r="H21" t="n">
-        <v>129.4907520196261</v>
+        <v>129.799229204734</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -614,28 +614,28 @@
         <v>0.5074366401158565</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.2582698444753</v>
+        <v>11.25822521555143</v>
       </c>
       <c r="R2" t="n">
         <v>64.96884503982621</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3098131821502448</v>
+        <v>-0.3098578110741205</v>
       </c>
       <c r="T2" t="n">
-        <v>6.611855785763316</v>
+        <v>6.611867343642521</v>
       </c>
       <c r="U2" t="n">
-        <v>16.97472375243922</v>
+        <v>16.97473503300299</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1525841221307083</v>
+        <v>0.1525830773562464</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6105670823336682</v>
+        <v>-0.6105692229411936</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1505918729492578</v>
+        <v>0.1505907091411377</v>
       </c>
       <c r="Y2" t="n">
         <v>0.7381195474426202</v>
@@ -665,13 +665,13 @@
         <v>16720</v>
       </c>
       <c r="E3" t="n">
-        <v>14646</v>
+        <v>14650</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14646</v>
+        <v>14649</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.904097978970367</v>
+        <v>4.903495050856714</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.961770589246938</v>
+        <v>4.961389826340352</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05767261027657095</v>
+        <v>0.05789477548363865</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343333594382426</v>
+        <v>1.343204590099947</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717878171565639</v>
+        <v>1.717685457877018</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816567925011125</v>
+        <v>0.7816984409163134</v>
       </c>
       <c r="W3" t="n">
-        <v>0.57031063832647</v>
+        <v>0.5704300992569196</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7806119097561228</v>
+        <v>0.7806424190474319</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.251625799573561</v>
+        <v>3.248306680881308</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.306653911641673</v>
+        <v>3.304487623239891</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.336443496801705</v>
+        <v>3.331970859985785</v>
       </c>
     </row>
     <row r="4">
@@ -754,13 +754,13 @@
         <v>16720</v>
       </c>
       <c r="E4" t="n">
-        <v>10280</v>
+        <v>10282</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10280</v>
+        <v>10282</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.900121108949416</v>
+        <v>6.899267165921027</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.230292485238992</v>
+        <v>7.229454967784389</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3301713762895755</v>
+        <v>0.3301878018633619</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290838932810581</v>
+        <v>1.290686175825949</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680551640862065</v>
+        <v>1.680340587344613</v>
       </c>
       <c r="V4" t="n">
-        <v>0.868047981026839</v>
+        <v>0.8681038981159499</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7382216226007035</v>
+        <v>0.7383271940627221</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473649828124795</v>
+        <v>0.8474109573126626</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.366340613296884</v>
+        <v>3.364607752880775</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.820118494544826</v>
+        <v>3.816774927912394</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.296610796464107</v>
+        <v>4.291225396455223</v>
       </c>
     </row>
     <row r="5">
@@ -843,13 +843,13 @@
         <v>16720</v>
       </c>
       <c r="E5" t="n">
-        <v>2743</v>
+        <v>2753</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2743</v>
+        <v>2752</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46297</v>
+        <v>46306</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.920539555231498</v>
+        <v>8.911212754360465</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>2.837179866765359</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.305030705070164</v>
+        <v>9.296428509298527</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3844911498386656</v>
+        <v>0.3852157549380629</v>
       </c>
       <c r="T5" t="n">
-        <v>1.249299247227283</v>
+        <v>1.246122537479982</v>
       </c>
       <c r="U5" t="n">
-        <v>1.751128415260552</v>
+        <v>1.747999310334064</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8648702902941177</v>
+        <v>0.8652088779896112</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7192375577428463</v>
+        <v>0.7200061117803582</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8576785603044491</v>
+        <v>0.8579056377745693</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.335622842365987</v>
+        <v>6.270370416374092</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.779765906098485</v>
+        <v>6.62896660095444</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.400673597080102</v>
+        <v>7.389333575761588</v>
       </c>
     </row>
     <row r="6">
@@ -2267,13 +2267,13 @@
         <v>16720</v>
       </c>
       <c r="E21" t="n">
-        <v>10258</v>
+        <v>10268</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10258</v>
+        <v>10267</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46297</v>
+        <v>46306</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8665696042114</v>
+        <v>130.8646363105094</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9716201042233</v>
+        <v>130.9687640087528</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1050505000119313</v>
+        <v>0.1041276982434147</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7971767189421469</v>
+        <v>0.7968153782878031</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045743659361439</v>
+        <v>1.045397635041945</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8651149374848335</v>
+        <v>0.8652382297310409</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7311737808090513</v>
+        <v>0.7314097628045224</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8643551421447075</v>
+        <v>0.8645017308997879</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5813334894187</v>
+        <v>128.5452343154691</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1016232055392</v>
+        <v>129.0840906274407</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.799229204734</v>
+        <v>129.7952668784269</v>
       </c>
     </row>
   </sheetData>
@@ -2861,13 +2861,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.366340613296884</v>
+        <v>3.364607752880775</v>
       </c>
       <c r="G18" t="n">
-        <v>3.820118494544826</v>
+        <v>3.816774927912394</v>
       </c>
       <c r="H18" t="n">
-        <v>4.296610796464107</v>
+        <v>4.291225396455223</v>
       </c>
     </row>
     <row r="19">
@@ -2889,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.251625799573561</v>
+        <v>3.248306680881308</v>
       </c>
       <c r="G19" t="n">
-        <v>3.306653911641673</v>
+        <v>3.304487623239891</v>
       </c>
       <c r="H19" t="n">
-        <v>3.336443496801705</v>
+        <v>3.331970859985785</v>
       </c>
     </row>
     <row r="20">
@@ -2917,13 +2917,13 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.335622842365987</v>
+        <v>6.270370416374092</v>
       </c>
       <c r="G20" t="n">
-        <v>6.779765906098485</v>
+        <v>6.62896660095444</v>
       </c>
       <c r="H20" t="n">
-        <v>7.400673597080102</v>
+        <v>7.389333575761588</v>
       </c>
     </row>
     <row r="21">
@@ -2945,13 +2945,13 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5813334894187</v>
+        <v>128.5452343154691</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1016232055392</v>
+        <v>129.0840906274407</v>
       </c>
       <c r="H21" t="n">
-        <v>129.799229204734</v>
+        <v>129.7952668784269</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -605,46 +605,46 @@
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>11.56808302662555</v>
+        <v>8.251775788321892</v>
       </c>
       <c r="O2" t="n">
-        <v>65.36500000000001</v>
+        <v>14.02</v>
       </c>
       <c r="P2" t="n">
         <v>0.5074366401158565</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.25822521555143</v>
+        <v>8.255060878533401</v>
       </c>
       <c r="R2" t="n">
-        <v>64.96884503982621</v>
+        <v>13.94192251991311</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3098578110741205</v>
+        <v>0.003285090211510567</v>
       </c>
       <c r="T2" t="n">
-        <v>6.611867343642521</v>
+        <v>1.274375300422962</v>
       </c>
       <c r="U2" t="n">
-        <v>16.97473503300299</v>
+        <v>1.6157770037825</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1525830773562464</v>
+        <v>0.855078354691665</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6105692229411936</v>
+        <v>0.709985160038646</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1505907091411377</v>
+        <v>0.8550766209177943</v>
       </c>
       <c r="Y2" t="n">
         <v>0.7381195474426202</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.616026039023854</v>
+        <v>2.612201453866451</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.191417565347168</v>
+        <v>6.123923985561318</v>
       </c>
     </row>
     <row r="3">
@@ -2528,10 +2528,10 @@
         <v>0.7381195474426202</v>
       </c>
       <c r="G6" t="n">
-        <v>2.616026039023854</v>
+        <v>2.612201453866452</v>
       </c>
       <c r="H6" t="n">
-        <v>6.191417565347168</v>
+        <v>6.123923985561318</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E2" t="n">
         <v>10053</v>
@@ -614,37 +614,37 @@
         <v>0.5074366401158565</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.255060878533401</v>
+        <v>8.255237112359115</v>
       </c>
       <c r="R2" t="n">
         <v>13.94192251991311</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003285090211510567</v>
+        <v>0.003461324037222902</v>
       </c>
       <c r="T2" t="n">
-        <v>1.274375300422962</v>
+        <v>1.274324250522505</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6157770037825</v>
+        <v>1.615702398603979</v>
       </c>
       <c r="V2" t="n">
-        <v>0.855078354691665</v>
+        <v>0.8550784498347244</v>
       </c>
       <c r="W2" t="n">
-        <v>0.709985160038646</v>
+        <v>0.7100119410973507</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8550766209177943</v>
+        <v>0.8550769984705485</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7381195474426202</v>
+        <v>0.7399906473423282</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.612201453866451</v>
+        <v>2.725121868142763</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.123923985561318</v>
+        <v>6.457159078075587</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E3" t="n">
         <v>14650</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14649</v>
+        <v>14650</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.903495050856714</v>
+        <v>4.9032804778157</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.961389826340352</v>
+        <v>4.96118925539282</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05789477548363865</v>
+        <v>0.05790877757712041</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343204590099947</v>
+        <v>1.343228827658374</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717685457877018</v>
+        <v>1.717678697737481</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7816984409163134</v>
+        <v>0.7817073106768012</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5704300992569196</v>
+        <v>0.5704463409456247</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7806424190474319</v>
+        <v>0.7806512603189519</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.248306680881308</v>
+        <v>3.212988227497448</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.304487623239891</v>
+        <v>3.290720737693506</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.331970859985785</v>
+        <v>3.332826704545455</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E4" t="n">
         <v>10282</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.229454967784389</v>
+        <v>7.229435202245427</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3301878018633619</v>
+        <v>0.3301680363243996</v>
       </c>
       <c r="T4" t="n">
-        <v>1.290686175825949</v>
+        <v>1.29069435132817</v>
       </c>
       <c r="U4" t="n">
-        <v>1.680340587344613</v>
+        <v>1.68035145793368</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8681038981159499</v>
+        <v>0.8681024614288703</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7383271940627221</v>
+        <v>0.7383238083839304</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8474109573126626</v>
+        <v>0.8474157881526814</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.364607752880775</v>
+        <v>3.41625</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.816774927912394</v>
+        <v>3.914091746193077</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.291225396455223</v>
+        <v>4.497667463822799</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E5" t="n">
         <v>2753</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.911212754360465</v>
+        <v>8.910108063930258</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>2.837179866765359</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.296428509298527</v>
+        <v>9.295292266791217</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3852157549380629</v>
+        <v>0.3851842028609577</v>
       </c>
       <c r="T5" t="n">
-        <v>1.246122537479982</v>
+        <v>1.245841915452928</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747999310334064</v>
+        <v>1.747705060401836</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8652088779896112</v>
+        <v>0.8652505220700212</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7200061117803582</v>
+        <v>0.7200848365395346</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8579056377745693</v>
+        <v>0.8579463693640624</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.270370416374092</v>
+        <v>6.274099920167407</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.62896660095444</v>
+        <v>6.584951276266134</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.389333575761588</v>
+        <v>7.29381335372295</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E6" t="n">
         <v>8897</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8896</v>
+        <v>8897</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.734068570143885</v>
+        <v>6.733968079127796</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023114245871691</v>
+        <v>7.023103685912028</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2890456757278056</v>
+        <v>0.2891356067842329</v>
       </c>
       <c r="T6" t="n">
-        <v>1.477905995867914</v>
+        <v>1.478003924196667</v>
       </c>
       <c r="U6" t="n">
-        <v>1.905884168519949</v>
+        <v>1.905919710651539</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039627664350392</v>
+        <v>0.3039103239762186</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980107576099264</v>
+        <v>-0.1981546099362932</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2789402913050505</v>
+        <v>0.2788984459600385</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.995119385297689</v>
+        <v>8.008852809174225</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.068649629952082</v>
+        <v>8.055309847036566</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.155718036804291</v>
+        <v>8.121018444886165</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E7" t="n">
         <v>14258</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14257</v>
+        <v>14258</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.578795574103949</v>
+        <v>5.578647671482677</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565244335741485</v>
+        <v>5.565189251728154</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01355123836246403</v>
+        <v>-0.01345841975452224</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166558014972743</v>
+        <v>1.166634185042653</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5095887424729</v>
+        <v>1.509658628951165</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049506774874986</v>
+        <v>0.5049161671583374</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05322905388369581</v>
+        <v>0.05319766330141518</v>
       </c>
       <c r="X7" t="n">
-        <v>0.50281470409333</v>
+        <v>0.50277698198815</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.600397927729142</v>
+        <v>5.59973780406605</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.725733088036785</v>
+        <v>5.702184813315805</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.840280323729897</v>
+        <v>5.816366863462711</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E8" t="n">
         <v>9056</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9055</v>
+        <v>9056</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,52 +1133,52 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.869501656543346</v>
+        <v>7.869215713339222</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6454797441364606</v>
+        <v>0.64546875</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.110008683012152</v>
+        <v>8.109668109114244</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2405070264688051</v>
+        <v>0.2404523957750202</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444299737891028</v>
+        <v>1.444209211824267</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824103935672198</v>
+        <v>1.824014943606192</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079367937631027</v>
+        <v>0.8079542788301463</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6277399808988013</v>
+        <v>0.6277660318147296</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976561983656395</v>
+        <v>0.7976835319831643</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.925823643437735</v>
+        <v>5.92560636476915</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.953390312529256</v>
+        <v>5.94368607332451</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.003142612987197</v>
+        <v>5.995273969430292</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E9" t="n">
+        <v>13922</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13921</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13920</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.606661278735633</v>
+        <v>7.606436678399541</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.652266649809399</v>
+        <v>7.652034394802845</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04560537107376784</v>
+        <v>0.04559771640330485</v>
       </c>
       <c r="T9" t="n">
-        <v>1.493073809258751</v>
+        <v>1.49311348391188</v>
       </c>
       <c r="U9" t="n">
-        <v>1.940901631084011</v>
+        <v>1.940917627031356</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7567993132644866</v>
+        <v>0.7568006980126099</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5251500047580205</v>
+        <v>0.5251500980586001</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553780775315138</v>
+        <v>0.7553801242605753</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.444570053022026</v>
+        <v>4.270042273522014</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.498492076692724</v>
+        <v>4.388507274586208</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.599603617560895</v>
+        <v>4.536935506415551</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.6133260134464</v>
+        <v>10.61318902949455</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3082643329540263</v>
+        <v>0.3081273490021763</v>
       </c>
       <c r="T10" t="n">
-        <v>2.054182298536944</v>
+        <v>2.054252623430696</v>
       </c>
       <c r="U10" t="n">
-        <v>2.699952098690571</v>
+        <v>2.700026130574141</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569757718847842</v>
+        <v>0.3569680909016061</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1219787998396935</v>
+        <v>-0.1220403293332637</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370592926468574</v>
+        <v>0.3370676326308861</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.67809419666223</v>
+        <v>10.80002695445768</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.83149045610182</v>
+        <v>10.87499726878527</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.96029632316358</v>
+        <v>11.22371583120163</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E11" t="n">
         <v>13862</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13861</v>
+        <v>13862</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241141836808311</v>
+        <v>5.241023445390276</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.457961622013034</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.214823523530868</v>
+        <v>5.214775033184984</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0263183132774421</v>
+        <v>-0.02624841220529148</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161126942995118</v>
+        <v>1.161156763868057</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482412802644716</v>
+        <v>1.482419012291749</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429571868856173</v>
+        <v>0.4295697102872282</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09169370408695476</v>
+        <v>-0.0916762394222943</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277631219699053</v>
+        <v>0.4277596010562549</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.701725233579128</v>
+        <v>4.810715909090908</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.85751575841558</v>
+        <v>4.948738769737361</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.202920220326937</v>
+        <v>5.340639766280269</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E12" t="n">
         <v>4180</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4179</v>
+        <v>4180</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.451298994974874</v>
+        <v>7.450504425837321</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.205684286748733</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.623489098597893</v>
+        <v>7.622870499352369</v>
       </c>
       <c r="R12" t="n">
-        <v>16.43473134328356</v>
+        <v>16.44423153409098</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1721901036230179</v>
+        <v>0.1723660735150477</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9116260742350172</v>
+        <v>0.9115983994002237</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191098479013898</v>
+        <v>1.191081579886759</v>
       </c>
       <c r="V12" t="n">
-        <v>0.833871933853335</v>
+        <v>0.8339348613377858</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6634298419598127</v>
+        <v>0.6635694837647139</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8320622707655608</v>
+        <v>0.832116700713076</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.584126169283526</v>
+        <v>4.583444467010569</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.114694837001774</v>
+        <v>5.208747823533008</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.687286014764908</v>
+        <v>5.797684144788401</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E13" t="n">
         <v>6515</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6514</v>
+        <v>6515</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.593373503223825</v>
+        <v>9.592909439754413</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.01906694018444</v>
+        <v>10.01865982794887</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.42569343696062</v>
+        <v>0.4257503881944605</v>
       </c>
       <c r="T13" t="n">
-        <v>1.687936205348153</v>
+        <v>1.687905786884385</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146144542081087</v>
+        <v>2.146053923657314</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8235757051936923</v>
+        <v>0.8235864661073671</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6494971263823407</v>
+        <v>0.6495103430453135</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102378512623056</v>
+        <v>0.8102492284613914</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.068441089188404</v>
+        <v>7.958707233871897</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.371162494796398</v>
+        <v>8.322892115830271</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.492575186788716</v>
+        <v>8.492810957327785</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E14" t="n">
         <v>14102</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14101</v>
+        <v>14102</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.123650450322673</v>
+        <v>8.123454474542617</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9078735216027034</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.194731411604025</v>
+        <v>8.194476784575606</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0710809612813524</v>
+        <v>0.07102231003298735</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754499113461919</v>
+        <v>1.754407154454561</v>
       </c>
       <c r="U14" t="n">
-        <v>2.280028022379507</v>
+        <v>2.279905947422262</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7811198027282905</v>
+        <v>0.7811428005559753</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5659825977777241</v>
+        <v>0.5660179199230004</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807289852972203</v>
+        <v>0.7807533778503921</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.702065448124668</v>
+        <v>6.685426157855495</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.800969151157443</v>
+        <v>6.769828663870783</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.873109344364697</v>
+        <v>6.858388943221627</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.667207096307024</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81903372501387</v>
+        <v>11.81890519198269</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1448536580129099</v>
+        <v>-0.144982191044093</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052728711159388</v>
+        <v>2.052755707105932</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698761612191607</v>
+        <v>2.698820596071334</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949765779692634</v>
+        <v>0.7949740701372546</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6092714519587703</v>
+        <v>0.6092543723194037</v>
       </c>
       <c r="X15" t="n">
-        <v>0.78656344819357</v>
+        <v>0.7865700163499874</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.128971911198008</v>
+        <v>9.008017779913503</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.335294339033213</v>
+        <v>9.29871068061329</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.458578484405498</v>
+        <v>9.459178038526687</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E16" t="n">
         <v>9865</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9864</v>
+        <v>9865</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.358416869424168</v>
+        <v>8.358198073998988</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.621530391530774</v>
+        <v>8.621763961049471</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2631135221066057</v>
+        <v>0.2635658870504837</v>
       </c>
       <c r="T16" t="n">
-        <v>3.602034565769024</v>
+        <v>3.6022790730591</v>
       </c>
       <c r="U16" t="n">
-        <v>11.08010150259243</v>
+        <v>11.07968319348495</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04103992749104373</v>
+        <v>0.04102652588867763</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6110826997932084</v>
+        <v>-0.6111143877155545</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02437990468063245</v>
+        <v>0.02436569964235802</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.21714421811913</v>
+        <v>11.18441603301187</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.35915135366602</v>
+        <v>11.32073027658754</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.64619504174045</v>
+        <v>11.56938621887138</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E17" t="n">
         <v>2409</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.449930440199335</v>
+        <v>6.448116438356164</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.439127443881246</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.811986455212473</v>
+        <v>6.810591728131639</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3620560150131394</v>
+        <v>0.3624752897754737</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007371098409879</v>
+        <v>2.007050285602845</v>
       </c>
       <c r="U17" t="n">
-        <v>2.544877102197267</v>
+        <v>2.544476666570915</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5417366769296872</v>
+        <v>0.5421403098631405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0621896698627179</v>
+        <v>0.06317080183576185</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5383047569077344</v>
+        <v>0.5386966848142565</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.083863368998019</v>
+        <v>2.3767760643277</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.787919856315079</v>
+        <v>3.692858706408541</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.326682850258627</v>
+        <v>7.031546308022977</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E18" t="n">
         <v>3266</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.651667925445653</v>
+        <v>6.651749452143315</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1956249064621876</v>
+        <v>0.1957064331598488</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095374807839438</v>
+        <v>1.095370655515927</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483792128243137</v>
+        <v>1.483796692940438</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6109910114094841</v>
+        <v>0.610982299203798</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2372204450049546</v>
+        <v>0.2372157518096401</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6079142693757815</v>
+        <v>0.6079014071538985</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.211943978544877</v>
+        <v>2.584521598466888</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.539447742708045</v>
+        <v>4.451310465652154</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.211645732150454</v>
+        <v>7.045924320386113</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E19" t="n">
         <v>7222</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7221</v>
+        <v>7222</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.29964153164382</v>
+        <v>10.29839400443091</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10224776920565</v>
+        <v>11.10183289311139</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8026062375618287</v>
+        <v>0.8034388886804857</v>
       </c>
       <c r="T19" t="n">
-        <v>2.071062277241749</v>
+        <v>2.07180813421314</v>
       </c>
       <c r="U19" t="n">
-        <v>2.799820721245586</v>
+        <v>2.800996989245471</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270288912601822</v>
+        <v>0.7269610922662075</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4711285575408433</v>
+        <v>0.471011917533626</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6766956386248091</v>
+        <v>0.676492607512811</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.324958610309794</v>
+        <v>8.320266091138048</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.657322808804787</v>
+        <v>8.459022265673827</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.34558565429037</v>
+        <v>8.834604005407336</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E20" t="n">
         <v>10670</v>
@@ -2213,40 +2213,40 @@
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.491094527363185</v>
+        <v>7.490965909090909</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.2272317183471</v>
+        <v>14.22721204600435</v>
       </c>
       <c r="R20" t="n">
         <v>21.67640869875963</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3762748573151617</v>
+        <v>0.3762551849724099</v>
       </c>
       <c r="T20" t="n">
-        <v>1.253954439959021</v>
+        <v>1.253961512861545</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645811185995683</v>
+        <v>1.645819282654879</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8937216973369404</v>
+        <v>0.8937208993975021</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7793404408332805</v>
+        <v>0.7793382697341183</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8889020496636623</v>
+        <v>0.8889032489199362</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.19645247512745</v>
+        <v>10.25578255840296</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.57264020991435</v>
+        <v>10.64587257949665</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.97858506764648</v>
+        <v>11.03960826066602</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16720</v>
+        <v>16721</v>
       </c>
       <c r="E21" t="n">
         <v>10268</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10267</v>
+        <v>10268</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8646363105094</v>
+        <v>130.8644693221659</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9687640087528</v>
+        <v>130.9686058015354</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1041276982434147</v>
+        <v>0.104136479369422</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7968153782878031</v>
+        <v>0.7967888176280791</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045397635041945</v>
+        <v>1.045349881696216</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8652382297310409</v>
+        <v>0.8652487996828396</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7314097628045224</v>
+        <v>0.7314270416699367</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8645017308997879</v>
+        <v>0.8645135527303419</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.5452343154691</v>
+        <v>128.6459334203959</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.0840906274407</v>
+        <v>129.2173960799529</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.7952668784269</v>
+        <v>130.3251326759888</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.324958610309794</v>
+        <v>8.320266091138048</v>
       </c>
       <c r="G2" t="n">
-        <v>8.657322808804789</v>
+        <v>8.459022265673825</v>
       </c>
       <c r="H2" t="n">
-        <v>10.34558565429037</v>
+        <v>8.834604005407336</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.600397927729142</v>
+        <v>5.59973780406605</v>
       </c>
       <c r="G3" t="n">
-        <v>5.725733088036785</v>
+        <v>5.702184813315805</v>
       </c>
       <c r="H3" t="n">
-        <v>5.840280323729897</v>
+        <v>5.816366863462711</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.701725233579128</v>
+        <v>4.810715909090908</v>
       </c>
       <c r="G4" t="n">
-        <v>4.85751575841558</v>
+        <v>4.948738769737361</v>
       </c>
       <c r="H4" t="n">
-        <v>5.202920220326937</v>
+        <v>5.340639766280269</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.21714421811913</v>
+        <v>11.18441603301187</v>
       </c>
       <c r="G5" t="n">
-        <v>11.35915135366602</v>
+        <v>11.32073027658754</v>
       </c>
       <c r="H5" t="n">
-        <v>11.64619504174045</v>
+        <v>11.56938621887138</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7381195474426202</v>
+        <v>0.7399906473423282</v>
       </c>
       <c r="G6" t="n">
-        <v>2.612201453866452</v>
+        <v>2.725121868142763</v>
       </c>
       <c r="H6" t="n">
-        <v>6.123923985561318</v>
+        <v>6.457159078075587</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.128971911198008</v>
+        <v>9.008017779913503</v>
       </c>
       <c r="G7" t="n">
-        <v>9.335294339033213</v>
+        <v>9.298710680613292</v>
       </c>
       <c r="H7" t="n">
-        <v>9.458578484405498</v>
+        <v>9.459178038526687</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.068441089188404</v>
+        <v>7.958707233871897</v>
       </c>
       <c r="G8" t="n">
-        <v>8.371162494796399</v>
+        <v>8.322892115830273</v>
       </c>
       <c r="H8" t="n">
-        <v>8.492575186788716</v>
+        <v>8.492810957327785</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.584126169283526</v>
+        <v>4.583444467010569</v>
       </c>
       <c r="G9" t="n">
-        <v>5.114694837001774</v>
+        <v>5.208747823533007</v>
       </c>
       <c r="H9" t="n">
-        <v>5.687286014764908</v>
+        <v>5.797684144788401</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.925823643437735</v>
+        <v>5.92560636476915</v>
       </c>
       <c r="G10" t="n">
-        <v>5.953390312529256</v>
+        <v>5.943686073324511</v>
       </c>
       <c r="H10" t="n">
-        <v>6.003142612987197</v>
+        <v>5.995273969430292</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.19645247512745</v>
+        <v>10.25578255840296</v>
       </c>
       <c r="G11" t="n">
-        <v>10.57264020991435</v>
+        <v>10.64587257949665</v>
       </c>
       <c r="H11" t="n">
-        <v>10.97858506764648</v>
+        <v>11.03960826066602</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.083863368998019</v>
+        <v>2.3767760643277</v>
       </c>
       <c r="G12" t="n">
-        <v>3.787919856315079</v>
+        <v>3.692858706408541</v>
       </c>
       <c r="H12" t="n">
-        <v>7.326682850258627</v>
+        <v>7.031546308022977</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.702065448124668</v>
+        <v>6.685426157855495</v>
       </c>
       <c r="G13" t="n">
-        <v>6.800969151157443</v>
+        <v>6.769828663870785</v>
       </c>
       <c r="H13" t="n">
-        <v>6.873109344364697</v>
+        <v>6.858388943221627</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.67809419666223</v>
+        <v>10.80002695445768</v>
       </c>
       <c r="G14" t="n">
-        <v>10.83149045610182</v>
+        <v>10.87499726878527</v>
       </c>
       <c r="H14" t="n">
-        <v>10.96029632316358</v>
+        <v>11.22371583120163</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.444570053022026</v>
+        <v>4.270042273522014</v>
       </c>
       <c r="G15" t="n">
-        <v>4.498492076692724</v>
+        <v>4.388507274586208</v>
       </c>
       <c r="H15" t="n">
-        <v>4.599603617560895</v>
+        <v>4.536935506415551</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.995119385297689</v>
+        <v>8.008852809174225</v>
       </c>
       <c r="G16" t="n">
-        <v>8.068649629952082</v>
+        <v>8.055309847036566</v>
       </c>
       <c r="H16" t="n">
-        <v>8.155718036804291</v>
+        <v>8.121018444886165</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.211943978544877</v>
+        <v>2.584521598466888</v>
       </c>
       <c r="G17" t="n">
-        <v>4.539447742708044</v>
+        <v>4.451310465652154</v>
       </c>
       <c r="H17" t="n">
-        <v>7.211645732150454</v>
+        <v>7.045924320386113</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.364607752880775</v>
+        <v>3.41625</v>
       </c>
       <c r="G18" t="n">
-        <v>3.816774927912394</v>
+        <v>3.914091746193077</v>
       </c>
       <c r="H18" t="n">
-        <v>4.291225396455223</v>
+        <v>4.497667463822799</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.248306680881308</v>
+        <v>3.212988227497448</v>
       </c>
       <c r="G19" t="n">
-        <v>3.304487623239891</v>
+        <v>3.290720737693506</v>
       </c>
       <c r="H19" t="n">
-        <v>3.331970859985785</v>
+        <v>3.332826704545455</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.270370416374092</v>
+        <v>6.274099920167407</v>
       </c>
       <c r="G20" t="n">
-        <v>6.62896660095444</v>
+        <v>6.584951276266134</v>
       </c>
       <c r="H20" t="n">
-        <v>7.389333575761588</v>
+        <v>7.29381335372295</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.5452343154691</v>
+        <v>128.6459334203959</v>
       </c>
       <c r="G21" t="n">
-        <v>129.0840906274407</v>
+        <v>129.2173960799529</v>
       </c>
       <c r="H21" t="n">
-        <v>129.7952668784269</v>
+        <v>130.3251326759888</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E2" t="n">
-        <v>10053</v>
+        <v>16718</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10053</v>
+        <v>16718</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>36161</v>
+        <v>29587</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>46304</v>
@@ -605,46 +605,46 @@
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>8.251775788321892</v>
+        <v>8.295047374087808</v>
       </c>
       <c r="O2" t="n">
         <v>14.02</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5074366401158565</v>
+        <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.255237112359115</v>
+        <v>8.29321644957507</v>
       </c>
       <c r="R2" t="n">
-        <v>13.94192251991311</v>
+        <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003461324037222902</v>
+        <v>-0.001830924512737278</v>
       </c>
       <c r="T2" t="n">
-        <v>1.274324250522505</v>
+        <v>1.443086668346993</v>
       </c>
       <c r="U2" t="n">
-        <v>1.615702398603979</v>
+        <v>1.86984891303359</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8550784498347244</v>
+        <v>0.7147907532130134</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7100119410973507</v>
+        <v>0.4299318671098454</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8550769984705485</v>
+        <v>0.7147900029254963</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7399906473423282</v>
+        <v>1.201332220141341</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.725121868142763</v>
+        <v>3.563474438976533</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.457159078075587</v>
+        <v>7.947631754705206</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E3" t="n">
         <v>16721</v>
       </c>
-      <c r="E3" t="n">
-        <v>14650</v>
-      </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14650</v>
+        <v>16721</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>30317</v>
+        <v>29587</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>46307</v>
@@ -694,7 +694,7 @@
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9032804778157</v>
+        <v>4.659337300400693</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.96118925539282</v>
+        <v>4.657636596916633</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05790877757712041</v>
+        <v>-0.001700703484060991</v>
       </c>
       <c r="T3" t="n">
-        <v>1.343228827658374</v>
+        <v>1.315251430941523</v>
       </c>
       <c r="U3" t="n">
-        <v>1.717678697737481</v>
+        <v>1.682113871636588</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7817073106768012</v>
+        <v>0.8076123394085011</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5704463409456247</v>
+        <v>0.6151411785334313</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7806512603189519</v>
+        <v>0.8076118720437362</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.212988227497448</v>
+        <v>3.015220790454223</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.290720737693506</v>
+        <v>3.101890875229432</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.332826704545455</v>
+        <v>3.191440738112135</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E4" t="n">
-        <v>10282</v>
+        <v>16719</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10282</v>
+        <v>16719</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>35065</v>
+        <v>29587</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>46305</v>
@@ -783,46 +783,46 @@
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.899267165921027</v>
+        <v>6.787254919552605</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3676769446391031</v>
+        <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.229435202245427</v>
+        <v>6.786221204924502</v>
       </c>
       <c r="R4" t="n">
-        <v>12.72990889978977</v>
+        <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3301680363243996</v>
+        <v>-0.001033714628103578</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29069435132817</v>
+        <v>1.50530729864821</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68035145793368</v>
+        <v>1.961426302455191</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8681024614288703</v>
+        <v>0.7923870617494306</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7383238083839304</v>
+        <v>0.5847415093371828</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8474157881526814</v>
+        <v>0.7923869911383867</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.41625</v>
+        <v>4.71857241932015</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.914091746193077</v>
+        <v>5.389344333894572</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.497667463822799</v>
+        <v>5.882920342018993</v>
       </c>
     </row>
     <row r="5">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E5" t="n">
         <v>16721</v>
       </c>
-      <c r="E5" t="n">
-        <v>2753</v>
-      </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2753</v>
+        <v>16721</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>42370</v>
+        <v>29587</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>46307</v>
@@ -872,46 +872,46 @@
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.910108063930258</v>
+        <v>8.212131301955624</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.837179866765359</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.295292266791217</v>
+        <v>8.208052932948407</v>
       </c>
       <c r="R5" t="n">
-        <v>15.38127820602663</v>
+        <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3851842028609577</v>
+        <v>-0.004078369007218635</v>
       </c>
       <c r="T5" t="n">
-        <v>1.245841915452928</v>
+        <v>1.511469717804899</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747705060401836</v>
+        <v>2.024820701938317</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8652505220700212</v>
+        <v>0.6081618191746067</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7200848365395346</v>
+        <v>0.2162633583745835</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8579463693640624</v>
+        <v>0.6081614976815151</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.274099920167407</v>
+        <v>7.704065955104809</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.584951276266134</v>
+        <v>7.757842245031435</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.29381335372295</v>
+        <v>7.887279996160101</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E6" t="n">
         <v>16721</v>
       </c>
-      <c r="E6" t="n">
-        <v>8897</v>
-      </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8897</v>
+        <v>16721</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>36892</v>
+        <v>29587</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>46307</v>
@@ -961,46 +961,46 @@
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733968079127796</v>
+        <v>6.231434363973447</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
       </c>
       <c r="P6" t="n">
-        <v>1.616683937823834</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.023103685912028</v>
+        <v>6.229015164513297</v>
       </c>
       <c r="R6" t="n">
-        <v>10.19050035038543</v>
+        <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2891356067842329</v>
+        <v>-0.002419199460150254</v>
       </c>
       <c r="T6" t="n">
-        <v>1.478003924196667</v>
+        <v>1.390692448873571</v>
       </c>
       <c r="U6" t="n">
-        <v>1.905919710651539</v>
+        <v>1.813131605906857</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3039103239762186</v>
+        <v>0.2529671645851024</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981546099362932</v>
+        <v>-0.4946351821825803</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2788984459600385</v>
+        <v>0.2529669674110193</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.008852809174225</v>
+        <v>7.385164322684774</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.055309847036566</v>
+        <v>7.445180734139202</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.121018444886165</v>
+        <v>7.500892433375404</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E7" t="n">
         <v>16721</v>
       </c>
-      <c r="E7" t="n">
-        <v>14258</v>
-      </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14258</v>
+        <v>16721</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>31048</v>
+        <v>29587</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>46307</v>
@@ -1050,46 +1050,46 @@
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.578647671482677</v>
+        <v>5.587663925602536</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1435</v>
+        <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.565189251728154</v>
+        <v>5.585553035612183</v>
       </c>
       <c r="R7" t="n">
-        <v>9.695129642606867</v>
+        <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01345841975452224</v>
+        <v>-0.002110889990353657</v>
       </c>
       <c r="T7" t="n">
-        <v>1.166634185042653</v>
+        <v>1.144193096889641</v>
       </c>
       <c r="U7" t="n">
-        <v>1.509658628951165</v>
+        <v>1.470683637994696</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5049161671583374</v>
+        <v>0.5169370018310002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05319766330141518</v>
+        <v>0.03370468715645469</v>
       </c>
       <c r="X7" t="n">
-        <v>0.50277698198815</v>
+        <v>0.516936823075627</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.59973780406605</v>
+        <v>5.56694819020582</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.702184813315805</v>
+        <v>5.631696908637799</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.816366863462711</v>
+        <v>5.758087295954578</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E8" t="n">
         <v>16721</v>
       </c>
-      <c r="E8" t="n">
-        <v>9056</v>
-      </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9056</v>
+        <v>16721</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>36161</v>
+        <v>29587</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>46307</v>
@@ -1139,46 +1139,46 @@
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.869215713339222</v>
+        <v>7.428262514203696</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.64546875</v>
+        <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.109668109114244</v>
+        <v>7.425420982151063</v>
       </c>
       <c r="R8" t="n">
-        <v>14.26297827610371</v>
+        <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2404523957750202</v>
+        <v>-0.002841532052634024</v>
       </c>
       <c r="T8" t="n">
-        <v>1.444209211824267</v>
+        <v>1.332414065026303</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824014943606192</v>
+        <v>1.748448772981876</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079542788301463</v>
+        <v>0.7945687005807854</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6277660318147296</v>
+        <v>0.589107080941905</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7976835319831643</v>
+        <v>0.7945683321115251</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.92560636476915</v>
+        <v>5.270934776213771</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.94368607332451</v>
+        <v>5.294580462048025</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.995273969430292</v>
+        <v>5.339048224160148</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E9" t="n">
-        <v>13922</v>
+        <v>16723</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13921</v>
+        <v>16722</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1219,55 +1219,55 @@
         <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>31778</v>
+        <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.606436678399541</v>
+        <v>7.30804613682574</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.409614576033637</v>
+        <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.652034394802845</v>
+        <v>7.307374787426292</v>
       </c>
       <c r="R9" t="n">
-        <v>13.66547972483708</v>
+        <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04559771640330485</v>
+        <v>-0.0006713493994454718</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49311348391188</v>
+        <v>1.603799808416417</v>
       </c>
       <c r="U9" t="n">
-        <v>1.940917627031356</v>
+        <v>2.058482951467503</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7568006980126099</v>
+        <v>0.7320236371875345</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5251500980586001</v>
+        <v>0.4639190181239173</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7553801242605753</v>
+        <v>0.7320235147810465</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.270042273522014</v>
+        <v>3.530764014607545</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.388507274586208</v>
+        <v>3.648936733431769</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.536935506415551</v>
+        <v>3.87199248430394</v>
       </c>
     </row>
     <row r="10">
@@ -1285,16 +1285,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E10" t="n">
-        <v>3737</v>
+        <v>16344</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>3737</v>
+        <v>16344</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>37257</v>
+        <v>29587</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>45930</v>
@@ -1317,46 +1317,46 @@
         <v>3.788</v>
       </c>
       <c r="N10" t="n">
-        <v>10.30506168049237</v>
+        <v>9.344308339451786</v>
       </c>
       <c r="O10" t="n">
         <v>39.075</v>
       </c>
       <c r="P10" t="n">
-        <v>4.255</v>
+        <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61318902949455</v>
+        <v>9.314677410681369</v>
       </c>
       <c r="R10" t="n">
-        <v>14.31670311368574</v>
+        <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3081273490021763</v>
+        <v>-0.02963092877041757</v>
       </c>
       <c r="T10" t="n">
-        <v>2.054252623430696</v>
+        <v>1.492906461035962</v>
       </c>
       <c r="U10" t="n">
-        <v>2.700026130574141</v>
+        <v>2.036036188120244</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3569680909016061</v>
+        <v>0.4130044205081494</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1220403293332637</v>
+        <v>-0.1747110339119087</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3370676326308861</v>
+        <v>0.4129957184404882</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.80002695445768</v>
+        <v>9.2602580231811</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.87499726878527</v>
+        <v>9.560870163365072</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.22371583120163</v>
+        <v>10.15709878748985</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E11" t="n">
         <v>16721</v>
       </c>
-      <c r="E11" t="n">
-        <v>13862</v>
-      </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13862</v>
+        <v>16721</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>31413</v>
+        <v>29587</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>46307</v>
@@ -1406,46 +1406,46 @@
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.241023445390276</v>
+        <v>5.24948848753065</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.457961622013034</v>
+        <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.214775033184984</v>
+        <v>5.247296692761784</v>
       </c>
       <c r="R11" t="n">
-        <v>9.96782041998552</v>
+        <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02624841220529148</v>
+        <v>-0.002191794768865417</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161156763868057</v>
+        <v>1.12954028038906</v>
       </c>
       <c r="U11" t="n">
-        <v>1.482419012291749</v>
+        <v>1.437934067945386</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4295697102872282</v>
+        <v>0.3989782637394361</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0916762394222943</v>
+        <v>-0.202222509746617</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4277596010562549</v>
+        <v>0.3989781008337588</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.810715909090908</v>
+        <v>5.057753533223708</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.948738769737361</v>
+        <v>5.216131108177113</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.340639766280269</v>
+        <v>5.398563742015615</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E12" t="n">
         <v>16721</v>
       </c>
-      <c r="E12" t="n">
-        <v>4180</v>
-      </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4180</v>
+        <v>16721</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>41640</v>
+        <v>29587</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>46307</v>
@@ -1495,46 +1495,46 @@
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.450504425837321</v>
+        <v>7.47976368040189</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205684286748733</v>
+        <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.622870499352369</v>
+        <v>7.477064292336922</v>
       </c>
       <c r="R12" t="n">
-        <v>16.44423153409098</v>
+        <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1723660735150477</v>
+        <v>-0.002699388064967936</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9115983994002237</v>
+        <v>0.9377540230893352</v>
       </c>
       <c r="U12" t="n">
-        <v>1.191081579886759</v>
+        <v>1.251857411384416</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8339348613377858</v>
+        <v>0.6556236729544163</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6635694837647139</v>
+        <v>0.3113368827100843</v>
       </c>
       <c r="X12" t="n">
-        <v>0.832116700713076</v>
+        <v>0.6556234575212638</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.583444467010569</v>
+        <v>5.35867251095552</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.208747823533008</v>
+        <v>5.9991819683489</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.797684144788401</v>
+        <v>6.935410226801745</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E13" t="n">
         <v>16721</v>
       </c>
-      <c r="E13" t="n">
-        <v>6515</v>
-      </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6515</v>
+        <v>16721</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>39083</v>
+        <v>29587</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>46307</v>
@@ -1584,46 +1584,46 @@
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.592909439754413</v>
+        <v>9.158761138687879</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.866674842326559</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.01865982794887</v>
+        <v>9.155745766395588</v>
       </c>
       <c r="R13" t="n">
-        <v>16.20563653352021</v>
+        <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4257503881944605</v>
+        <v>-0.003015372292288793</v>
       </c>
       <c r="T13" t="n">
-        <v>1.687905786884385</v>
+        <v>1.195449757379269</v>
       </c>
       <c r="U13" t="n">
-        <v>2.146053923657314</v>
+        <v>1.605820244833254</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8235864661073671</v>
+        <v>0.872974410600043</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6495103430453135</v>
+        <v>0.7459342396376903</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8102492284613914</v>
+        <v>0.8729739725176947</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.958707233871897</v>
+        <v>6.918430236949858</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.322892115830271</v>
+        <v>7.138288733004247</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.492810957327785</v>
+        <v>7.247636110156989</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E14" t="n">
         <v>16721</v>
       </c>
-      <c r="E14" t="n">
-        <v>14102</v>
-      </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14102</v>
+        <v>16721</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>30682</v>
+        <v>29587</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>46307</v>
@@ -1673,46 +1673,46 @@
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.123454474542617</v>
+        <v>8.201492434662999</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9078735216027034</v>
+        <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.194476784575606</v>
+        <v>8.198658103459534</v>
       </c>
       <c r="R14" t="n">
-        <v>14.32</v>
+        <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07102231003298735</v>
+        <v>-0.002834331203464391</v>
       </c>
       <c r="T14" t="n">
-        <v>1.754407154454561</v>
+        <v>1.848076643701622</v>
       </c>
       <c r="U14" t="n">
-        <v>2.279905947422262</v>
+        <v>2.393145997193338</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7811428005559753</v>
+        <v>0.7525222525954713</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5660179199230004</v>
+        <v>0.5050305204627897</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807533778503921</v>
+        <v>0.7525220098434893</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.685426157855495</v>
+        <v>6.819823471652954</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.769828663870783</v>
+        <v>6.958496151234085</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.858388943221627</v>
+        <v>7.054849807259874</v>
       </c>
     </row>
     <row r="15">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E15" t="n">
-        <v>3099</v>
+        <v>16570</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>3099</v>
+        <v>16570</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>42370</v>
+        <v>29587</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>46156</v>
@@ -1762,46 +1762,46 @@
         <v>3.305</v>
       </c>
       <c r="N15" t="n">
-        <v>11.96388738302678</v>
+        <v>12.68310241400121</v>
       </c>
       <c r="O15" t="n">
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.667207096307024</v>
+        <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.81890519198269</v>
+        <v>12.66831092526562</v>
       </c>
       <c r="R15" t="n">
-        <v>21.32952932657494</v>
+        <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.144982191044093</v>
+        <v>-0.01479148873558549</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052755707105932</v>
+        <v>1.354472530505431</v>
       </c>
       <c r="U15" t="n">
-        <v>2.698820596071334</v>
+        <v>2.008231604541528</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949740701372546</v>
+        <v>0.7232703675191285</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6092543723194037</v>
+        <v>0.4444062961409075</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7865700163499874</v>
+        <v>0.7232421452443648</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.008017779913503</v>
+        <v>11.25072812513642</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.29871068061329</v>
+        <v>11.37054157581102</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.459178038526687</v>
+        <v>11.44773946721842</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E16" t="n">
         <v>16721</v>
       </c>
-      <c r="E16" t="n">
-        <v>9865</v>
-      </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9865</v>
+        <v>16721</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>35804</v>
+        <v>29587</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>46307</v>
@@ -1851,46 +1851,46 @@
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.358198073998988</v>
+        <v>7.562442078823036</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5268935553946416</v>
+        <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.621763961049471</v>
+        <v>7.559489837223221</v>
       </c>
       <c r="R16" t="n">
-        <v>131.7868211440985</v>
+        <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2635658870504837</v>
+        <v>-0.002952241599816564</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6022790730591</v>
+        <v>3.084986529684322</v>
       </c>
       <c r="U16" t="n">
-        <v>11.07968319348495</v>
+        <v>9.550124982051029</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04102652588867763</v>
+        <v>0.03118193978034161</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6111143877155545</v>
+        <v>-0.9376287247920223</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02436569964235802</v>
+        <v>0.03118186112086585</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.18441603301187</v>
+        <v>9.085054280682385</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.32073027658754</v>
+        <v>9.297220774442943</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.56938621887138</v>
+        <v>9.627129652235629</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E17" t="n">
-        <v>2409</v>
+        <v>15650</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2409</v>
+        <v>15650</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>43252</v>
+        <v>30317</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>46307</v>
@@ -1940,46 +1940,46 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.448116438356164</v>
+        <v>5.811154792332268</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.439127443881246</v>
+        <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.810591728131639</v>
+        <v>5.841154714084279</v>
       </c>
       <c r="R17" t="n">
-        <v>12.15775235336712</v>
+        <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3624752897754737</v>
+        <v>0.02999992175201186</v>
       </c>
       <c r="T17" t="n">
-        <v>2.007050285602845</v>
+        <v>1.220762697371513</v>
       </c>
       <c r="U17" t="n">
-        <v>2.544476666570915</v>
+        <v>1.605181806217295</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5421403098631405</v>
+        <v>0.6470182149512828</v>
       </c>
       <c r="W17" t="n">
-        <v>0.06317080183576185</v>
+        <v>0.3017221392100694</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5386966848142565</v>
+        <v>0.6467958964449754</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3767760643277</v>
+        <v>2.692257225937086</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.692858706408541</v>
+        <v>3.77316239645539</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.031546308022977</v>
+        <v>5.958147031793098</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E18" t="n">
-        <v>3266</v>
+        <v>16720</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3266</v>
+        <v>16720</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2020,55 +2020,55 @@
         <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>42370</v>
+        <v>29587</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.456043018983467</v>
+        <v>6.539704635167464</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
       </c>
       <c r="P18" t="n">
-        <v>1.826106587712805</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.651749452143315</v>
+        <v>6.536607781768517</v>
       </c>
       <c r="R18" t="n">
-        <v>14.92762307692291</v>
+        <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1957064331598488</v>
+        <v>-0.003096853398947067</v>
       </c>
       <c r="T18" t="n">
-        <v>1.095370655515927</v>
+        <v>0.800166614872042</v>
       </c>
       <c r="U18" t="n">
-        <v>1.483796692940438</v>
+        <v>1.112383703194054</v>
       </c>
       <c r="V18" t="n">
-        <v>0.610982299203798</v>
+        <v>0.2249450781135291</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2372157518096401</v>
+        <v>-0.5503367290347136</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6079014071538985</v>
+        <v>0.2249449210556443</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.584521598466888</v>
+        <v>5.729274375966947</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.451310465652154</v>
+        <v>6.382073568665969</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.045924320386113</v>
+        <v>7.007603601832613</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E19" t="n">
         <v>16721</v>
       </c>
-      <c r="E19" t="n">
-        <v>7222</v>
-      </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7222</v>
+        <v>16721</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>37987</v>
+        <v>29587</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>46307</v>
@@ -2118,46 +2118,46 @@
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.29839400443091</v>
+        <v>9.313060911428741</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>3.790455501051156</v>
+        <v>0.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.10183289311139</v>
+        <v>9.310307036325597</v>
       </c>
       <c r="R19" t="n">
-        <v>17.53862298528381</v>
+        <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8034388886804857</v>
+        <v>-0.00275387510314663</v>
       </c>
       <c r="T19" t="n">
-        <v>2.07180813421314</v>
+        <v>2.209081382760509</v>
       </c>
       <c r="U19" t="n">
-        <v>2.800996989245471</v>
+        <v>2.858467637663892</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7269610922662075</v>
+        <v>0.6220270969319809</v>
       </c>
       <c r="W19" t="n">
-        <v>0.471011917533626</v>
+        <v>0.2439841715556352</v>
       </c>
       <c r="X19" t="n">
-        <v>0.676492607512811</v>
+        <v>0.6220269701429905</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.320266091138048</v>
+        <v>8.04686663248485</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.459022265673827</v>
+        <v>8.176958223411836</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.834604005407336</v>
+        <v>8.656655481126394</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16721</v>
+        <v>16722</v>
       </c>
       <c r="E20" t="n">
-        <v>10670</v>
+        <v>16719</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10670</v>
+        <v>16719</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>35325</v>
+        <v>29587</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>46305</v>
@@ -2207,46 +2207,46 @@
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.85095686103194</v>
+        <v>13.6462557394109</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>7.490965909090909</v>
+        <v>6.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.22721204600435</v>
+        <v>13.64450439121803</v>
       </c>
       <c r="R20" t="n">
-        <v>21.67640869875963</v>
+        <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3762551849724099</v>
+        <v>-0.00175134819286917</v>
       </c>
       <c r="T20" t="n">
-        <v>1.253961512861545</v>
+        <v>1.18454962751211</v>
       </c>
       <c r="U20" t="n">
-        <v>1.645819282654879</v>
+        <v>1.566048758117</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8937208993975021</v>
+        <v>0.8952228041792467</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7793382697341183</v>
+        <v>0.7904631635182451</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8889032489199362</v>
+        <v>0.8952226910538845</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.25578255840296</v>
+        <v>10.30112429736165</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.64587257949665</v>
+        <v>10.66573974394949</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.03960826066602</v>
+        <v>10.95978693778165</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>16722</v>
+      </c>
+      <c r="E21" t="n">
         <v>16721</v>
       </c>
-      <c r="E21" t="n">
-        <v>10268</v>
-      </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10268</v>
+        <v>16721</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>36039</v>
+        <v>29587</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>46307</v>
@@ -2296,7 +2296,7 @@
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8644693221659</v>
+        <v>130.5626679624424</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9686058015354</v>
+        <v>130.5583437397036</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.104136479369422</v>
+        <v>-0.004324222738829537</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7967888176280791</v>
+        <v>0.6948246860496022</v>
       </c>
       <c r="U21" t="n">
-        <v>1.045349881696216</v>
+        <v>0.9295856662631307</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8652487996828396</v>
+        <v>0.883994647092892</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7314270416699367</v>
+        <v>0.7679508887793298</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8645135527303419</v>
+        <v>0.8839945532364396</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.6459334203959</v>
+        <v>128.7807217072433</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2173960799529</v>
+        <v>129.2691378172737</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.3251326759888</v>
+        <v>132.0326446319481</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.320266091138048</v>
+        <v>8.04686663248485</v>
       </c>
       <c r="G2" t="n">
-        <v>8.459022265673825</v>
+        <v>8.176958223411837</v>
       </c>
       <c r="H2" t="n">
-        <v>8.834604005407336</v>
+        <v>8.656655481126394</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.59973780406605</v>
+        <v>5.56694819020582</v>
       </c>
       <c r="G3" t="n">
-        <v>5.702184813315805</v>
+        <v>5.631696908637798</v>
       </c>
       <c r="H3" t="n">
-        <v>5.816366863462711</v>
+        <v>5.758087295954578</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.810715909090908</v>
+        <v>5.057753533223708</v>
       </c>
       <c r="G4" t="n">
-        <v>4.948738769737361</v>
+        <v>5.216131108177113</v>
       </c>
       <c r="H4" t="n">
-        <v>5.340639766280269</v>
+        <v>5.398563742015615</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.18441603301187</v>
+        <v>9.085054280682385</v>
       </c>
       <c r="G5" t="n">
-        <v>11.32073027658754</v>
+        <v>9.297220774442945</v>
       </c>
       <c r="H5" t="n">
-        <v>11.56938621887138</v>
+        <v>9.627129652235629</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7399906473423282</v>
+        <v>1.201332220141341</v>
       </c>
       <c r="G6" t="n">
-        <v>2.725121868142763</v>
+        <v>3.563474438976533</v>
       </c>
       <c r="H6" t="n">
-        <v>6.457159078075587</v>
+        <v>7.947631754705206</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9.008017779913503</v>
+        <v>11.25072812513642</v>
       </c>
       <c r="G7" t="n">
-        <v>9.298710680613292</v>
+        <v>11.37054157581103</v>
       </c>
       <c r="H7" t="n">
-        <v>9.459178038526687</v>
+        <v>11.44773946721842</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.958707233871897</v>
+        <v>6.918430236949858</v>
       </c>
       <c r="G8" t="n">
-        <v>8.322892115830273</v>
+        <v>7.138288733004248</v>
       </c>
       <c r="H8" t="n">
-        <v>8.492810957327785</v>
+        <v>7.247636110156989</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.583444467010569</v>
+        <v>5.35867251095552</v>
       </c>
       <c r="G9" t="n">
-        <v>5.208747823533007</v>
+        <v>5.9991819683489</v>
       </c>
       <c r="H9" t="n">
-        <v>5.797684144788401</v>
+        <v>6.935410226801745</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.92560636476915</v>
+        <v>5.270934776213771</v>
       </c>
       <c r="G10" t="n">
-        <v>5.943686073324511</v>
+        <v>5.294580462048025</v>
       </c>
       <c r="H10" t="n">
-        <v>5.995273969430292</v>
+        <v>5.339048224160148</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.25578255840296</v>
+        <v>10.30112429736165</v>
       </c>
       <c r="G11" t="n">
-        <v>10.64587257949665</v>
+        <v>10.66573974394949</v>
       </c>
       <c r="H11" t="n">
-        <v>11.03960826066602</v>
+        <v>10.95978693778165</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3767760643277</v>
+        <v>2.692257225937086</v>
       </c>
       <c r="G12" t="n">
-        <v>3.692858706408541</v>
+        <v>3.77316239645539</v>
       </c>
       <c r="H12" t="n">
-        <v>7.031546308022977</v>
+        <v>5.958147031793098</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.685426157855495</v>
+        <v>6.819823471652954</v>
       </c>
       <c r="G13" t="n">
-        <v>6.769828663870785</v>
+        <v>6.958496151234087</v>
       </c>
       <c r="H13" t="n">
-        <v>6.858388943221627</v>
+        <v>7.054849807259874</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.80002695445768</v>
+        <v>9.2602580231811</v>
       </c>
       <c r="G14" t="n">
-        <v>10.87499726878527</v>
+        <v>9.56087016336507</v>
       </c>
       <c r="H14" t="n">
-        <v>11.22371583120163</v>
+        <v>10.15709878748985</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>4.270042273522014</v>
+        <v>3.530764014607545</v>
       </c>
       <c r="G15" t="n">
-        <v>4.388507274586208</v>
+        <v>3.648936733431769</v>
       </c>
       <c r="H15" t="n">
-        <v>4.536935506415551</v>
+        <v>3.87199248430394</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8.008852809174225</v>
+        <v>7.385164322684774</v>
       </c>
       <c r="G16" t="n">
-        <v>8.055309847036566</v>
+        <v>7.445180734139202</v>
       </c>
       <c r="H16" t="n">
-        <v>8.121018444886165</v>
+        <v>7.500892433375404</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.584521598466888</v>
+        <v>5.729274375966947</v>
       </c>
       <c r="G17" t="n">
-        <v>4.451310465652154</v>
+        <v>6.382073568665969</v>
       </c>
       <c r="H17" t="n">
-        <v>7.045924320386113</v>
+        <v>7.007603601832613</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.41625</v>
+        <v>4.71857241932015</v>
       </c>
       <c r="G18" t="n">
-        <v>3.914091746193077</v>
+        <v>5.389344333894572</v>
       </c>
       <c r="H18" t="n">
-        <v>4.497667463822799</v>
+        <v>5.882920342018993</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.212988227497448</v>
+        <v>3.015220790454223</v>
       </c>
       <c r="G19" t="n">
-        <v>3.290720737693506</v>
+        <v>3.101890875229432</v>
       </c>
       <c r="H19" t="n">
-        <v>3.332826704545455</v>
+        <v>3.191440738112135</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>6.274099920167407</v>
+        <v>7.704065955104809</v>
       </c>
       <c r="G20" t="n">
-        <v>6.584951276266134</v>
+        <v>7.757842245031435</v>
       </c>
       <c r="H20" t="n">
-        <v>7.29381335372295</v>
+        <v>7.887279996160101</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.6459334203959</v>
+        <v>128.7807217072433</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2173960799529</v>
+        <v>129.2691378172737</v>
       </c>
       <c r="H21" t="n">
-        <v>130.3251326759888</v>
+        <v>132.0326446319481</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E2" t="n">
-        <v>16718</v>
+        <v>16724</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>16718</v>
+        <v>16723</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>29587</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="M2" t="n">
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>8.295047374087808</v>
+        <v>8.293712970160856</v>
       </c>
       <c r="O2" t="n">
         <v>14.02</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.29321644957507</v>
+        <v>8.290992181644594</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.001830924512737278</v>
+        <v>-0.002720788516260193</v>
       </c>
       <c r="T2" t="n">
-        <v>1.443086668346993</v>
+        <v>1.443038403589232</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86984891303359</v>
+        <v>1.869670829716475</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7147907532130134</v>
+        <v>0.7151875204089927</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4299318671098454</v>
+        <v>0.4304238596409184</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7147900029254963</v>
+        <v>0.7151873179345357</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.201332220141341</v>
+        <v>1.936004268728475</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.563474438976533</v>
+        <v>4.505230135247428</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.947631754705206</v>
+        <v>8.582764839326989</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E3" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>29587</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.659337300400693</v>
+        <v>4.659107456796028</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.657636596916633</v>
+        <v>4.657478156623318</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001700703484060991</v>
+        <v>-0.001629300172711678</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315251430941523</v>
+        <v>1.315241417466904</v>
       </c>
       <c r="U3" t="n">
-        <v>1.682113871636588</v>
+        <v>1.682091252415575</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076123394085011</v>
+        <v>0.8076055462831885</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6151411785334313</v>
+        <v>0.615139474804232</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076118720437362</v>
+        <v>0.8076051394327159</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.015220790454223</v>
+        <v>3.015534739912317</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.101890875229432</v>
+        <v>3.094301058544954</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.191440738112135</v>
+        <v>3.186190091386981</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E4" t="n">
-        <v>16719</v>
+        <v>16724</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16719</v>
+        <v>16723</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>29587</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.787254919552605</v>
+        <v>6.786214793996292</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005</v>
+        <v>0.005017730496453902</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.786221204924502</v>
+        <v>6.785281736798369</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.001033714628103578</v>
+        <v>-0.0009330571979236081</v>
       </c>
       <c r="T4" t="n">
-        <v>1.50530729864821</v>
+        <v>1.505293927780123</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961426302455191</v>
+        <v>1.961273372028814</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7923870617494306</v>
+        <v>0.7924565567892541</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5847415093371828</v>
+        <v>0.5849096366584783</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7923869911383867</v>
+        <v>0.7924565110861715</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.71857241932015</v>
+        <v>4.956699179964537</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.389344333894572</v>
+        <v>5.515386226571815</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.882920342018993</v>
+        <v>5.969271363632166</v>
       </c>
     </row>
     <row r="5">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E5" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>29587</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.212131301955624</v>
+        <v>8.211811576870179</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.208052932948407</v>
+        <v>8.207811274381951</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004078369007218635</v>
+        <v>-0.004000302488228122</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511469717804899</v>
+        <v>1.511419363352097</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024820701938317</v>
+        <v>2.024663553934491</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6081618191746067</v>
+        <v>0.6082208442220766</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2162633583745835</v>
+        <v>0.2164191594689974</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6081614976815151</v>
+        <v>0.6082205405781063</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.704065955104809</v>
+        <v>7.706076302041818</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.757842245031435</v>
+        <v>7.774321972434542</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.887279996160101</v>
+        <v>7.938162110083843</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E6" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>29587</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.231434363973447</v>
+        <v>6.231437929797285</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.229015164513297</v>
+        <v>6.229163821379482</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002419199460150254</v>
+        <v>-0.002274108417803146</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390692448873571</v>
+        <v>1.390631615130841</v>
       </c>
       <c r="U6" t="n">
-        <v>1.813131605906857</v>
+        <v>1.812989451892506</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529671645851024</v>
+        <v>0.252967989233426</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4946351821825803</v>
+        <v>-0.494579298036127</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529669674110193</v>
+        <v>0.2529678212428438</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.385164322684774</v>
+        <v>7.398661413752344</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.445180734139202</v>
+        <v>7.445158335552025</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.500892433375404</v>
+        <v>7.547730900392785</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E7" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>29587</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.587663925602536</v>
+        <v>5.587378072116246</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585553035612183</v>
+        <v>5.585251646209935</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002110889990353657</v>
+        <v>-0.002126425906311215</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144193096889641</v>
+        <v>1.144431207423169</v>
       </c>
       <c r="U7" t="n">
-        <v>1.470683637994696</v>
+        <v>1.470906935367478</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5169370018310002</v>
+        <v>0.5168876849914567</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03370468715645469</v>
+        <v>0.03359033815456547</v>
       </c>
       <c r="X7" t="n">
-        <v>0.516936823075627</v>
+        <v>0.5168874979744037</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.56694819020582</v>
+        <v>5.566021315265773</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.631696908637799</v>
+        <v>5.617956853846647</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.758087295954578</v>
+        <v>5.719687943262412</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E8" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>29587</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.428262514203696</v>
+        <v>7.427962835615619</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.425420982151063</v>
+        <v>7.425200505164883</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002841532052634024</v>
+        <v>-0.002762330450736033</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332414065026303</v>
+        <v>1.332260087691903</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748448772981876</v>
+        <v>1.748304853503128</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7945687005807854</v>
+        <v>0.7945895301979226</v>
       </c>
       <c r="W8" t="n">
-        <v>0.589107080941905</v>
+        <v>0.589167061847085</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7945683321115251</v>
+        <v>0.7945891918268901</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.270934776213771</v>
+        <v>5.259294176618367</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.294580462048025</v>
+        <v>5.288006786513674</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.339048224160148</v>
+        <v>5.352995392911047</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E9" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.30804613682574</v>
+        <v>7.307867906476111</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.307374787426292</v>
+        <v>7.307200662681892</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006713493994454718</v>
+        <v>-0.0006672437942194183</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603799808416417</v>
+        <v>1.603810318658577</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058482951467503</v>
+        <v>2.058470060228411</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320236371875345</v>
+        <v>0.732028859676587</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639190181239173</v>
+        <v>0.4639296722111108</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320235147810465</v>
+        <v>0.7320287378011829</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.530764014607545</v>
+        <v>3.534239330360674</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.648936733431769</v>
+        <v>3.698377753242114</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.87199248430394</v>
+        <v>4.056364302040642</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314677410681369</v>
+        <v>9.314621400986917</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02963092877041757</v>
+        <v>-0.02968693846486918</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492906461035962</v>
+        <v>1.492914612895512</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036036188120244</v>
+        <v>2.036061212210263</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130044205081494</v>
+        <v>0.4130069054989741</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1747110339119087</v>
+        <v>-0.1747399098773543</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4129957184404882</v>
+        <v>0.4129981511754719</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.2602580231811</v>
+        <v>9.253572983607281</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.560870163365072</v>
+        <v>9.724594649304125</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.15709878748985</v>
+        <v>10.18823556950762</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E11" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>29587</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.24948848753065</v>
+        <v>5.249283142976738</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.247296692761784</v>
+        <v>5.247066923426255</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002191794768865417</v>
+        <v>-0.002216219550483779</v>
       </c>
       <c r="T11" t="n">
-        <v>1.12954028038906</v>
+        <v>1.129601985217431</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437934067945386</v>
+        <v>1.437954416621769</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3989782637394361</v>
+        <v>0.3990064765716114</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.202222509746617</v>
+        <v>-0.2021529958904127</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3989781008337588</v>
+        <v>0.3990063129633417</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.057753533223708</v>
+        <v>5.165565179313497</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.216131108177113</v>
+        <v>5.29567860408799</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.398563742015615</v>
+        <v>5.397925086851729</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E12" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>29587</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.47976368040189</v>
+        <v>7.479435866770316</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.477064292336922</v>
+        <v>7.476564625538325</v>
       </c>
       <c r="R12" t="n">
-        <v>19.178</v>
+        <v>19.17045886524957</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002699388064967936</v>
+        <v>-0.002871241231991424</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9377540230893352</v>
+        <v>0.9377577628373318</v>
       </c>
       <c r="U12" t="n">
-        <v>1.251857411384416</v>
+        <v>1.251842204002614</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6556236729544163</v>
+        <v>0.6557600268129481</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3113368827100843</v>
+        <v>0.3115402371894636</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6556234575212638</v>
+        <v>0.6557598110287339</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.35867251095552</v>
+        <v>5.401636088424168</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.9991819683489</v>
+        <v>6.064021122620394</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.935410226801745</v>
+        <v>6.652017230542996</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E13" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>29587</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.158761138687879</v>
+        <v>9.158423279315912</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.540007092198582</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.155745766395588</v>
+        <v>9.155525212017425</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.003015372292288793</v>
+        <v>-0.002898067298488597</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195449757379269</v>
+        <v>1.195332644902652</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605820244833254</v>
+        <v>1.605681089851968</v>
       </c>
       <c r="V13" t="n">
-        <v>0.872974410600043</v>
+        <v>0.872987326411672</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7459342396376903</v>
+        <v>0.745971762595479</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8729739725176947</v>
+        <v>0.8729869319692248</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.918430236949858</v>
+        <v>6.789056919138122</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.138288733004247</v>
+        <v>7.093345791299865</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.247636110156989</v>
+        <v>7.24683186482023</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E14" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>29587</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.201492434662999</v>
+        <v>8.201126592118639</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198658103459534</v>
+        <v>8.19846841182275</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002834331203464391</v>
+        <v>-0.002658180295888574</v>
       </c>
       <c r="T14" t="n">
-        <v>1.848076643701622</v>
+        <v>1.847896678610141</v>
       </c>
       <c r="U14" t="n">
-        <v>2.393145997193338</v>
+        <v>2.392856540196177</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7525222525954713</v>
+        <v>0.7525620289943205</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5050305204627897</v>
+        <v>0.5051388896916003</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7525220098434893</v>
+        <v>0.7525618147385258</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.819823471652954</v>
+        <v>6.749079839259702</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.958496151234085</v>
+        <v>6.925735013111281</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.054849807259874</v>
+        <v>7.032845067177586</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.66831092526562</v>
+        <v>12.6682233081971</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01479148873558549</v>
+        <v>-0.01487910580410587</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354472530505431</v>
+        <v>1.354496285539119</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008231604541528</v>
+        <v>2.008241987751409</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7232703675191285</v>
+        <v>0.7232787063407977</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4444062961409075</v>
+        <v>0.4444005509261268</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232421452443648</v>
+        <v>0.7232499130273395</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.25072812513642</v>
+        <v>11.21412959466582</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.37054157581102</v>
+        <v>11.34656776943323</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.44773946721842</v>
+        <v>11.44817935682389</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E16" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>29587</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>7.562442078823036</v>
+        <v>7.562282425402141</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.559489837223221</v>
+        <v>7.559173384186376</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002952241599816564</v>
+        <v>-0.003109041215766611</v>
       </c>
       <c r="T16" t="n">
-        <v>3.084986529684322</v>
+        <v>3.085271318944356</v>
       </c>
       <c r="U16" t="n">
-        <v>9.550124982051029</v>
+        <v>9.549701376867304</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03118193978034161</v>
+        <v>0.03115141328007485</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9376287247920223</v>
+        <v>-0.937679793184</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03118186112086585</v>
+        <v>0.03115132600849646</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.085054280682385</v>
+        <v>8.770298409703527</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.297220774442943</v>
+        <v>9.188574530835657</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.627129652235629</v>
+        <v>9.383960563150339</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E17" t="n">
-        <v>15650</v>
+        <v>15653</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>15650</v>
+        <v>15652</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>30317</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>5.811154792332268</v>
+        <v>5.810678028366982</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.841154714084279</v>
+        <v>5.840494210129572</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02999992175201186</v>
+        <v>0.02981618176259057</v>
       </c>
       <c r="T17" t="n">
-        <v>1.220762697371513</v>
+        <v>1.220869319917228</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605181806217295</v>
+        <v>1.605247445053523</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6470182149512828</v>
+        <v>0.6471541936993992</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3017221392100694</v>
+        <v>0.3019123260582037</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6467958964449754</v>
+        <v>0.6469360936905784</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.692257225937086</v>
+        <v>2.81587026305898</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.77316239645539</v>
+        <v>4.018044781516917</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.958147031793098</v>
+        <v>6.574349896407034</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E18" t="n">
-        <v>16720</v>
+        <v>16724</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>16720</v>
+        <v>16723</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>29587</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.539704635167464</v>
+        <v>6.539079501285655</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.536607781768517</v>
+        <v>6.535771834272251</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.003096853398947067</v>
+        <v>-0.003307667013403661</v>
       </c>
       <c r="T18" t="n">
-        <v>0.800166614872042</v>
+        <v>0.8010993974032599</v>
       </c>
       <c r="U18" t="n">
-        <v>1.112383703194054</v>
+        <v>1.113918150075743</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2249450781135291</v>
+        <v>0.2250804607641919</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5503367290347136</v>
+        <v>-0.5506632363437638</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249449210556443</v>
+        <v>0.2250801193386048</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.729274375966947</v>
+        <v>3.907605424564287</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.382073568665969</v>
+        <v>6.334121379747596</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.007603601832613</v>
+        <v>7.13836686366895</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E19" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>29587</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>9.313060911428741</v>
+        <v>9.312079561083536</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04</v>
+        <v>0.04000709219858156</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.310307036325597</v>
+        <v>9.309116909410024</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.00275387510314663</v>
+        <v>-0.002962651673513751</v>
       </c>
       <c r="T19" t="n">
-        <v>2.209081382760509</v>
+        <v>2.210266776742288</v>
       </c>
       <c r="U19" t="n">
-        <v>2.858467637663892</v>
+        <v>2.860174108229989</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6220270969319809</v>
+        <v>0.6218505082179031</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2439841715556352</v>
+        <v>0.2435542558701362</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6220269701429905</v>
+        <v>0.621850325166263</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.04686663248485</v>
+        <v>8.028021675767274</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.176958223411836</v>
+        <v>8.235800835898131</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.656655481126394</v>
+        <v>8.543368666748211</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E20" t="n">
-        <v>16719</v>
+        <v>16724</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>16719</v>
+        <v>16723</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>29587</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.6462557394109</v>
+        <v>13.64525487096878</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.75</v>
+        <v>6.750007092198581</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64450439121803</v>
+        <v>13.64354375408909</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.00175134819286917</v>
+        <v>-0.001711116879680589</v>
       </c>
       <c r="T20" t="n">
-        <v>1.18454962751211</v>
+        <v>1.184348613314065</v>
       </c>
       <c r="U20" t="n">
-        <v>1.566048758117</v>
+        <v>1.565819209255898</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952228041792467</v>
+        <v>0.8952635421172246</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7904631635182451</v>
+        <v>0.790549431919906</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952226910538845</v>
+        <v>0.8952634114313842</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.30112429736165</v>
+        <v>10.36585407653176</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.66573974394949</v>
+        <v>10.73554834245139</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.95978693778165</v>
+        <v>11.01927181242235</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="E21" t="n">
-        <v>16721</v>
+        <v>16724</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>16721</v>
+        <v>16723</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>29587</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.5626679624424</v>
+        <v>130.5624798780123</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5583437397036</v>
+        <v>130.5580519795068</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004324222738829537</v>
+        <v>-0.004427898505483226</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6948246860496022</v>
+        <v>0.694757614417551</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9295856662631307</v>
+        <v>0.9295137654610256</v>
       </c>
       <c r="V21" t="n">
-        <v>0.883994647092892</v>
+        <v>0.8840106187988136</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7679508887793298</v>
+        <v>0.7679776088265138</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8839945532364396</v>
+        <v>0.8840104961140771</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.7807217072433</v>
+        <v>128.932525616584</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2691378172737</v>
+        <v>129.1637416739329</v>
       </c>
       <c r="AA21" t="n">
-        <v>132.0326446319481</v>
+        <v>129.8448833822063</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.04686663248485</v>
+        <v>8.028021675767274</v>
       </c>
       <c r="G2" t="n">
-        <v>8.176958223411837</v>
+        <v>8.235800835898129</v>
       </c>
       <c r="H2" t="n">
-        <v>8.656655481126394</v>
+        <v>8.543368666748211</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.56694819020582</v>
+        <v>5.566021315265773</v>
       </c>
       <c r="G3" t="n">
-        <v>5.631696908637798</v>
+        <v>5.617956853846647</v>
       </c>
       <c r="H3" t="n">
-        <v>5.758087295954578</v>
+        <v>5.719687943262412</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.057753533223708</v>
+        <v>5.165565179313497</v>
       </c>
       <c r="G4" t="n">
-        <v>5.216131108177113</v>
+        <v>5.295678604087991</v>
       </c>
       <c r="H4" t="n">
-        <v>5.398563742015615</v>
+        <v>5.397925086851729</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>9.085054280682385</v>
+        <v>8.770298409703527</v>
       </c>
       <c r="G5" t="n">
-        <v>9.297220774442945</v>
+        <v>9.188574530835655</v>
       </c>
       <c r="H5" t="n">
-        <v>9.627129652235629</v>
+        <v>9.383960563150339</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.201332220141341</v>
+        <v>1.936004268728475</v>
       </c>
       <c r="G6" t="n">
-        <v>3.563474438976533</v>
+        <v>4.505230135247428</v>
       </c>
       <c r="H6" t="n">
-        <v>7.947631754705206</v>
+        <v>8.582764839326989</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.25072812513642</v>
+        <v>11.21412959466582</v>
       </c>
       <c r="G7" t="n">
-        <v>11.37054157581103</v>
+        <v>11.34656776943324</v>
       </c>
       <c r="H7" t="n">
-        <v>11.44773946721842</v>
+        <v>11.44817935682389</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.918430236949858</v>
+        <v>6.789056919138122</v>
       </c>
       <c r="G8" t="n">
-        <v>7.138288733004248</v>
+        <v>7.093345791299865</v>
       </c>
       <c r="H8" t="n">
-        <v>7.247636110156989</v>
+        <v>7.24683186482023</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.35867251095552</v>
+        <v>5.401636088424168</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9991819683489</v>
+        <v>6.064021122620394</v>
       </c>
       <c r="H9" t="n">
-        <v>6.935410226801745</v>
+        <v>6.652017230542996</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.270934776213771</v>
+        <v>5.259294176618367</v>
       </c>
       <c r="G10" t="n">
-        <v>5.294580462048025</v>
+        <v>5.288006786513675</v>
       </c>
       <c r="H10" t="n">
-        <v>5.339048224160148</v>
+        <v>5.352995392911047</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.30112429736165</v>
+        <v>10.36585407653176</v>
       </c>
       <c r="G11" t="n">
-        <v>10.66573974394949</v>
+        <v>10.73554834245139</v>
       </c>
       <c r="H11" t="n">
-        <v>10.95978693778165</v>
+        <v>11.01927181242235</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.692257225937086</v>
+        <v>2.81587026305898</v>
       </c>
       <c r="G12" t="n">
-        <v>3.77316239645539</v>
+        <v>4.018044781516917</v>
       </c>
       <c r="H12" t="n">
-        <v>5.958147031793098</v>
+        <v>6.574349896407034</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.819823471652954</v>
+        <v>6.749079839259702</v>
       </c>
       <c r="G13" t="n">
-        <v>6.958496151234087</v>
+        <v>6.925735013111281</v>
       </c>
       <c r="H13" t="n">
-        <v>7.054849807259874</v>
+        <v>7.032845067177586</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.2602580231811</v>
+        <v>9.253572983607281</v>
       </c>
       <c r="G14" t="n">
-        <v>9.56087016336507</v>
+        <v>9.724594649304123</v>
       </c>
       <c r="H14" t="n">
-        <v>10.15709878748985</v>
+        <v>10.18823556950762</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.530764014607545</v>
+        <v>3.534239330360674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.648936733431769</v>
+        <v>3.698377753242114</v>
       </c>
       <c r="H15" t="n">
-        <v>3.87199248430394</v>
+        <v>4.056364302040642</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.385164322684774</v>
+        <v>7.398661413752344</v>
       </c>
       <c r="G16" t="n">
-        <v>7.445180734139202</v>
+        <v>7.445158335552025</v>
       </c>
       <c r="H16" t="n">
-        <v>7.500892433375404</v>
+        <v>7.547730900392785</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>5.729274375966947</v>
+        <v>3.907605424564287</v>
       </c>
       <c r="G17" t="n">
-        <v>6.382073568665969</v>
+        <v>6.334121379747597</v>
       </c>
       <c r="H17" t="n">
-        <v>7.007603601832613</v>
+        <v>7.13836686366895</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>4.71857241932015</v>
+        <v>4.956699179964537</v>
       </c>
       <c r="G18" t="n">
-        <v>5.389344333894572</v>
+        <v>5.515386226571815</v>
       </c>
       <c r="H18" t="n">
-        <v>5.882920342018993</v>
+        <v>5.969271363632166</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.015220790454223</v>
+        <v>3.015534739912317</v>
       </c>
       <c r="G19" t="n">
-        <v>3.101890875229432</v>
+        <v>3.094301058544954</v>
       </c>
       <c r="H19" t="n">
-        <v>3.191440738112135</v>
+        <v>3.186190091386981</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.704065955104809</v>
+        <v>7.706076302041818</v>
       </c>
       <c r="G20" t="n">
-        <v>7.757842245031435</v>
+        <v>7.774321972434542</v>
       </c>
       <c r="H20" t="n">
-        <v>7.887279996160101</v>
+        <v>7.938162110083843</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.7807217072433</v>
+        <v>128.932525616584</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2691378172737</v>
+        <v>129.1637416739329</v>
       </c>
       <c r="H21" t="n">
-        <v>132.0326446319481</v>
+        <v>129.8448833822063</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E2" t="n">
         <v>16724</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>29587</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M2" t="n">
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>8.293712970160856</v>
+        <v>8.293425735469983</v>
       </c>
       <c r="O2" t="n">
         <v>14.02</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.290992181644594</v>
+        <v>8.290827137411451</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002720788516260193</v>
+        <v>-0.002598598058531088</v>
       </c>
       <c r="T2" t="n">
-        <v>1.443038403589232</v>
+        <v>1.442986721554085</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869670829716475</v>
+        <v>1.869555056945618</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7151875204089927</v>
+        <v>0.7152536214860915</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4304238596409184</v>
+        <v>0.4305883554816642</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7151873179345357</v>
+        <v>0.7152534124794345</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.936004268728475</v>
+        <v>1.929010420318914</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.505230135247428</v>
+        <v>3.886006970649883</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.582764839326989</v>
+        <v>6.497010808290595</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E3" t="n">
         <v>16724</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>29587</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.659107456796028</v>
+        <v>4.658914374551543</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.657478156623318</v>
+        <v>4.657300892975284</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001629300172711678</v>
+        <v>-0.001613481576258104</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315241417466904</v>
+        <v>1.315268775019826</v>
       </c>
       <c r="U3" t="n">
-        <v>1.682091252415575</v>
+        <v>1.682092820786858</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076055462831885</v>
+        <v>0.8076098438516198</v>
       </c>
       <c r="W3" t="n">
-        <v>0.615139474804232</v>
+        <v>0.6151483811489898</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076051394327159</v>
+        <v>0.8076094438619582</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.015534739912317</v>
+        <v>3.015101318359375</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.094301058544954</v>
+        <v>3.082922778870848</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.186190091386981</v>
+        <v>3.169509657118056</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E4" t="n">
         <v>16724</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>29587</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.786214793996292</v>
+        <v>6.785946543889022</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005017730496453902</v>
+        <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.785281736798369</v>
+        <v>6.785072416378007</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0009330571979236081</v>
+        <v>-0.0008741275110141259</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505293927780123</v>
+        <v>1.505348305529155</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961273372028814</v>
+        <v>1.961322874768392</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7924565567892541</v>
+        <v>0.7924575739925822</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849096366584783</v>
+        <v>0.5849177637089453</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924565110861715</v>
+        <v>0.7924575339154788</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.956699179964537</v>
+        <v>5.155</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.515386226571815</v>
+        <v>5.517470205533761</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.969271363632166</v>
+        <v>5.894</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E5" t="n">
         <v>16724</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>29587</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.211811576870179</v>
+        <v>8.211645838316192</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207811274381951</v>
+        <v>8.207675197321215</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004000302488228122</v>
+        <v>-0.003970640994977283</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511419363352097</v>
+        <v>1.511453044485592</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024663553934491</v>
+        <v>2.024664369926787</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6082208442220766</v>
+        <v>0.608232505318486</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2164191594689974</v>
+        <v>0.2164404790926291</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6082205405781063</v>
+        <v>0.6082322059536317</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.706076302041818</v>
+        <v>7.705784005763689</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.774321972434542</v>
+        <v>7.774032221899491</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.938162110083843</v>
+        <v>7.873027661064426</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E6" t="n">
         <v>16724</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>29587</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.231437929797285</v>
+        <v>6.231432462329586</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.229163821379482</v>
+        <v>6.229127780435303</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002274108417803146</v>
+        <v>-0.002304681894283677</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390631615130841</v>
+        <v>1.390624920446646</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812989451892506</v>
+        <v>1.812969145996653</v>
       </c>
       <c r="V6" t="n">
-        <v>0.252967989233426</v>
+        <v>0.2529623501484733</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.494579298036127</v>
+        <v>-0.4946348498779916</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529678212428438</v>
+        <v>0.2529621655730845</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.398661413752344</v>
+        <v>7.389535184749352</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.445158335552025</v>
+        <v>7.44356833447129</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.547730900392785</v>
+        <v>7.544117658097203</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E7" t="n">
         <v>16724</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>29587</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.587378072116246</v>
+        <v>5.587247279359005</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585251646209935</v>
+        <v>5.585197651350427</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002126425906311215</v>
+        <v>-0.002049628008578422</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144431207423169</v>
+        <v>1.144499869583488</v>
       </c>
       <c r="U7" t="n">
-        <v>1.470906935367478</v>
+        <v>1.470974357470062</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168876849914567</v>
+        <v>0.5168570829452002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03359033815456547</v>
+        <v>0.03356744760598218</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168874979744037</v>
+        <v>0.5168569204326683</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.566021315265773</v>
+        <v>5.564938483960701</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.617956853846647</v>
+        <v>5.601044392173109</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.719687943262412</v>
+        <v>5.675203939660222</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E8" t="n">
         <v>16724</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>29587</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.427962835615619</v>
+        <v>7.4277961313083</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.425200505164883</v>
+        <v>7.42501612951447</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002762330450736033</v>
+        <v>-0.002780001793829194</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332260087691903</v>
+        <v>1.332227509052255</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748304853503128</v>
+        <v>1.748275570735534</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7945895301979226</v>
+        <v>0.7946000548909676</v>
       </c>
       <c r="W8" t="n">
-        <v>0.589167061847085</v>
+        <v>0.5891819212940135</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7945891918268901</v>
+        <v>0.794599709660991</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.259294176618367</v>
+        <v>5.255619473978736</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.288006786513674</v>
+        <v>5.294672764637895</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.352995392911047</v>
+        <v>5.426330768179955</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E9" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.307867906476111</v>
+        <v>7.307693584070797</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.307200662681892</v>
+        <v>7.307026306787803</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006672437942194183</v>
+        <v>-0.0006672772829940428</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603810318658577</v>
+        <v>1.60383129820047</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058470060228411</v>
+        <v>2.058465947493815</v>
       </c>
       <c r="V9" t="n">
-        <v>0.732028859676587</v>
+        <v>0.7320308068121653</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639296722111108</v>
+        <v>0.4639342250678157</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320287378011829</v>
+        <v>0.7320306860229217</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.534239330360674</v>
+        <v>3.551807653407749</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.698377753242114</v>
+        <v>3.776534972885674</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.056364302040642</v>
+        <v>4.218528395467617</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314621400986917</v>
+        <v>9.314569303642987</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02968693846486918</v>
+        <v>-0.02973903580879971</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492914612895512</v>
+        <v>1.492925600554938</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036061212210263</v>
+        <v>2.036087140556897</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130069054989741</v>
+        <v>0.4130088098492128</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1747399098773543</v>
+        <v>-0.1747698296630142</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4129981511754719</v>
+        <v>0.4130000041871033</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.253572983607281</v>
+        <v>9.32013302793176</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.724594649304125</v>
+        <v>9.831587737988631</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.18823556950762</v>
+        <v>10.16030257756952</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E11" t="n">
         <v>16724</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>29587</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.249283142976738</v>
+        <v>5.249190504663956</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.247066923426255</v>
+        <v>5.247023451601581</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002216219550483779</v>
+        <v>-0.002167053062373754</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129601985217431</v>
+        <v>1.129630009196181</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437954416621769</v>
+        <v>1.437965737745067</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990064765716114</v>
+        <v>0.3990024338855081</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2021529958904127</v>
+        <v>-0.2021435018856603</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990063129633417</v>
+        <v>0.3990022798822219</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.165565179313497</v>
+        <v>5.11197942223981</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.29567860408799</v>
+        <v>5.305452238718829</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.397925086851729</v>
+        <v>5.387280240885417</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E12" t="n">
         <v>16724</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>29587</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.479435866770316</v>
+        <v>7.479257713465678</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.476564625538325</v>
+        <v>7.476499643369666</v>
       </c>
       <c r="R12" t="n">
-        <v>19.17045886524957</v>
+        <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002871241231991424</v>
+        <v>-0.002758070096012555</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9377577628373318</v>
+        <v>0.937764844210684</v>
       </c>
       <c r="U12" t="n">
-        <v>1.251842204002614</v>
+        <v>1.251843764820421</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6557600268129481</v>
+        <v>0.655791308738441</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3115402371894636</v>
+        <v>0.3116578654194206</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6557598110287339</v>
+        <v>0.655791092267392</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.401636088424168</v>
+        <v>5.696247184028587</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.064021122620394</v>
+        <v>6.120041066524333</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.652017230542996</v>
+        <v>6.473679764793728</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E13" t="n">
         <v>16724</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>29587</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.158423279315912</v>
+        <v>9.158249970102847</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.540007092198582</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.155525212017425</v>
+        <v>9.155322052140637</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.002898067298488597</v>
+        <v>-0.002927917962210025</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195332644902652</v>
+        <v>1.195321606296005</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605681089851968</v>
+        <v>1.605654026850897</v>
       </c>
       <c r="V13" t="n">
-        <v>0.872987326411672</v>
+        <v>0.8729923342585195</v>
       </c>
       <c r="W13" t="n">
-        <v>0.745971762595479</v>
+        <v>0.7459777081526429</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8729869319692248</v>
+        <v>0.8729919296008528</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.789056919138122</v>
+        <v>6.732143325117774</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.093345791299865</v>
+        <v>7.040766403062895</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.24683186482023</v>
+        <v>7.247311706070747</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E14" t="n">
         <v>16724</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>29587</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.201126592118639</v>
+        <v>8.200941162401341</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.19846841182275</v>
+        <v>8.198255082231411</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002658180295888574</v>
+        <v>-0.002686080169929775</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847896678610141</v>
+        <v>1.847841056105248</v>
       </c>
       <c r="U14" t="n">
-        <v>2.392856540196177</v>
+        <v>2.392768351094911</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7525620289943205</v>
+        <v>0.7525822029900524</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5051388896916003</v>
+        <v>0.5051703685254618</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7525618147385258</v>
+        <v>0.7525819858369555</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.749079839259702</v>
+        <v>6.722037607891492</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.925735013111281</v>
+        <v>6.890553537068188</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.032845067177586</v>
+        <v>7.018170099041033</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.6682233081971</v>
+        <v>12.66813572901694</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01487910580410587</v>
+        <v>-0.01496668498427135</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354496285539119</v>
+        <v>1.354520457280145</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008241987751409</v>
+        <v>2.008252245265232</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7232787063407977</v>
+        <v>0.7232870807861977</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4444005509261268</v>
+        <v>0.4443948752320435</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232499130273395</v>
+        <v>0.7232577106597895</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.21412959466582</v>
+        <v>11.19859771207162</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.34656776943323</v>
+        <v>11.320909370396</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.44817935682389</v>
+        <v>11.43650119325176</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E16" t="n">
         <v>16724</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>29587</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>7.562282425402141</v>
+        <v>7.562191401578569</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.559173384186376</v>
+        <v>7.559278263487887</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.003109041215766611</v>
+        <v>-0.002913138090682299</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085271318944356</v>
+        <v>3.085316673624317</v>
       </c>
       <c r="U16" t="n">
-        <v>9.549701376867304</v>
+        <v>9.549464024374068</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03115141328007485</v>
+        <v>0.0311480410822383</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.937679793184</v>
+        <v>-0.9376936331072916</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03115132600849646</v>
+        <v>0.03114796448295032</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.770298409703527</v>
+        <v>8.663103770063456</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.188574530835657</v>
+        <v>9.364198589537143</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.383960563150339</v>
+        <v>10.91628986211883</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E17" t="n">
         <v>15653</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>15652</v>
+        <v>15653</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>30317</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>5.810678028366982</v>
+        <v>5.810437136651121</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.840494210129572</v>
+        <v>5.840374776433253</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02981618176259057</v>
+        <v>0.0299376397821307</v>
       </c>
       <c r="T17" t="n">
-        <v>1.220869319917228</v>
+        <v>1.220860455175188</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605247445053523</v>
+        <v>1.605218702423864</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6471541936993992</v>
+        <v>0.6472037695196429</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3019123260582037</v>
+        <v>0.3020644704090892</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6469360936905784</v>
+        <v>0.6469826959235314</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.81587026305898</v>
+        <v>2.857220458245922</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.018044781516917</v>
+        <v>4.148650128272942</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.574349896407034</v>
+        <v>5.74148922874878</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E18" t="n">
         <v>16724</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>29587</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.539079501285655</v>
+        <v>6.53886908036355</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.535771834272251</v>
+        <v>6.53575217588492</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.003307667013403661</v>
+        <v>-0.00311690447863014</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8010993974032599</v>
+        <v>0.8012565972311074</v>
       </c>
       <c r="U18" t="n">
-        <v>1.113918150075743</v>
+        <v>1.114175936222472</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2250804607641919</v>
+        <v>0.2250592662962079</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5506632363437638</v>
+        <v>-0.5500394020108816</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2250801193386048</v>
+        <v>0.225059113983698</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.907605424564287</v>
+        <v>3.997941846798508</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.334121379747596</v>
+        <v>6.365091386378873</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.13836686366895</v>
+        <v>7.096244766254888</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E19" t="n">
         <v>16724</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>29587</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>9.312079561083536</v>
+        <v>9.311611247309255</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04000709219858156</v>
+        <v>0.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.309116909410024</v>
+        <v>9.308954705812008</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.002962651673513751</v>
+        <v>-0.002656541497249401</v>
       </c>
       <c r="T19" t="n">
-        <v>2.210266776742288</v>
+        <v>2.210577728318547</v>
       </c>
       <c r="U19" t="n">
-        <v>2.860174108229989</v>
+        <v>2.860599842240195</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6218505082179031</v>
+        <v>0.6217930280170116</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2435542558701362</v>
+        <v>0.2435403616009397</v>
       </c>
       <c r="X19" t="n">
-        <v>0.621850325166263</v>
+        <v>0.6217929157271811</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.028021675767274</v>
+        <v>8.062741831470335</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.235800835898131</v>
+        <v>8.237283977886607</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.543368666748211</v>
+        <v>8.728639047089874</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E20" t="n">
         <v>16724</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>29587</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.64525487096878</v>
+        <v>13.6449926576902</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.750007092198581</v>
+        <v>6.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64354375408909</v>
+        <v>13.64331247411897</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001711116879680589</v>
+        <v>-0.001680183571228008</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184348613314065</v>
+        <v>1.184346448014881</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565819209255898</v>
+        <v>1.565807571811916</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952635421172246</v>
+        <v>0.8952682779986132</v>
       </c>
       <c r="W20" t="n">
-        <v>0.790549431919906</v>
+        <v>0.7905605941483246</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952634114313842</v>
+        <v>0.8952681413981582</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.36585407653176</v>
+        <v>10.4953608222299</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.73554834245139</v>
+        <v>10.74655684314713</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.01927181242235</v>
+        <v>10.95082468500571</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="E21" t="n">
         <v>16724</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>29587</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.5624798780123</v>
+        <v>130.5623732958622</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5580519795068</v>
+        <v>130.5579887714833</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004427898505483226</v>
+        <v>-0.004384524378993584</v>
       </c>
       <c r="T21" t="n">
-        <v>0.694757614417551</v>
+        <v>0.6947386274118682</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9295137654610256</v>
+        <v>0.9295003942484181</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840106187988136</v>
+        <v>0.8840121418869714</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7679776088265138</v>
+        <v>0.7679822472812823</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8840104961140771</v>
+        <v>0.884012028253791</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.932525616584</v>
+        <v>129.0451508605007</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1637416739329</v>
+        <v>129.1339422884002</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.8448833822063</v>
+        <v>129.5113501758282</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.028021675767274</v>
+        <v>8.062741831470335</v>
       </c>
       <c r="G2" t="n">
-        <v>8.235800835898129</v>
+        <v>8.237283977886607</v>
       </c>
       <c r="H2" t="n">
-        <v>8.543368666748211</v>
+        <v>8.728639047089874</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.566021315265773</v>
+        <v>5.564938483960701</v>
       </c>
       <c r="G3" t="n">
-        <v>5.617956853846647</v>
+        <v>5.601044392173109</v>
       </c>
       <c r="H3" t="n">
-        <v>5.719687943262412</v>
+        <v>5.675203939660222</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.165565179313497</v>
+        <v>5.11197942223981</v>
       </c>
       <c r="G4" t="n">
-        <v>5.295678604087991</v>
+        <v>5.30545223871883</v>
       </c>
       <c r="H4" t="n">
-        <v>5.397925086851729</v>
+        <v>5.387280240885417</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.770298409703527</v>
+        <v>8.663103770063456</v>
       </c>
       <c r="G5" t="n">
-        <v>9.188574530835655</v>
+        <v>9.364198589537143</v>
       </c>
       <c r="H5" t="n">
-        <v>9.383960563150339</v>
+        <v>10.91628986211883</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.936004268728475</v>
+        <v>1.929010420318914</v>
       </c>
       <c r="G6" t="n">
-        <v>4.505230135247428</v>
+        <v>3.886006970649883</v>
       </c>
       <c r="H6" t="n">
-        <v>8.582764839326989</v>
+        <v>6.497010808290595</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.21412959466582</v>
+        <v>11.19859771207162</v>
       </c>
       <c r="G7" t="n">
-        <v>11.34656776943324</v>
+        <v>11.320909370396</v>
       </c>
       <c r="H7" t="n">
-        <v>11.44817935682389</v>
+        <v>11.43650119325176</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.789056919138122</v>
+        <v>6.732143325117774</v>
       </c>
       <c r="G8" t="n">
-        <v>7.093345791299865</v>
+        <v>7.040766403062895</v>
       </c>
       <c r="H8" t="n">
-        <v>7.24683186482023</v>
+        <v>7.247311706070747</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.401636088424168</v>
+        <v>5.696247184028587</v>
       </c>
       <c r="G9" t="n">
-        <v>6.064021122620394</v>
+        <v>6.120041066524333</v>
       </c>
       <c r="H9" t="n">
-        <v>6.652017230542996</v>
+        <v>6.473679764793728</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.259294176618367</v>
+        <v>5.255619473978736</v>
       </c>
       <c r="G10" t="n">
-        <v>5.288006786513675</v>
+        <v>5.294672764637896</v>
       </c>
       <c r="H10" t="n">
-        <v>5.352995392911047</v>
+        <v>5.426330768179955</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.36585407653176</v>
+        <v>10.4953608222299</v>
       </c>
       <c r="G11" t="n">
-        <v>10.73554834245139</v>
+        <v>10.74655684314713</v>
       </c>
       <c r="H11" t="n">
-        <v>11.01927181242235</v>
+        <v>10.95082468500571</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.81587026305898</v>
+        <v>2.857220458245922</v>
       </c>
       <c r="G12" t="n">
-        <v>4.018044781516917</v>
+        <v>4.148650128272942</v>
       </c>
       <c r="H12" t="n">
-        <v>6.574349896407034</v>
+        <v>5.74148922874878</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.749079839259702</v>
+        <v>6.722037607891492</v>
       </c>
       <c r="G13" t="n">
-        <v>6.925735013111281</v>
+        <v>6.890553537068188</v>
       </c>
       <c r="H13" t="n">
-        <v>7.032845067177586</v>
+        <v>7.018170099041033</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.253572983607281</v>
+        <v>9.32013302793176</v>
       </c>
       <c r="G14" t="n">
-        <v>9.724594649304123</v>
+        <v>9.831587737988631</v>
       </c>
       <c r="H14" t="n">
-        <v>10.18823556950762</v>
+        <v>10.16030257756952</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.534239330360674</v>
+        <v>3.551807653407749</v>
       </c>
       <c r="G15" t="n">
-        <v>3.698377753242114</v>
+        <v>3.776534972885674</v>
       </c>
       <c r="H15" t="n">
-        <v>4.056364302040642</v>
+        <v>4.218528395467617</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.398661413752344</v>
+        <v>7.389535184749352</v>
       </c>
       <c r="G16" t="n">
-        <v>7.445158335552025</v>
+        <v>7.44356833447129</v>
       </c>
       <c r="H16" t="n">
-        <v>7.547730900392785</v>
+        <v>7.544117658097203</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.907605424564287</v>
+        <v>3.997941846798508</v>
       </c>
       <c r="G17" t="n">
-        <v>6.334121379747597</v>
+        <v>6.365091386378873</v>
       </c>
       <c r="H17" t="n">
-        <v>7.13836686366895</v>
+        <v>7.096244766254888</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>4.956699179964537</v>
+        <v>5.155</v>
       </c>
       <c r="G18" t="n">
-        <v>5.515386226571815</v>
+        <v>5.517470205533762</v>
       </c>
       <c r="H18" t="n">
-        <v>5.969271363632166</v>
+        <v>5.894</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.015534739912317</v>
+        <v>3.015101318359375</v>
       </c>
       <c r="G19" t="n">
-        <v>3.094301058544954</v>
+        <v>3.082922778870848</v>
       </c>
       <c r="H19" t="n">
-        <v>3.186190091386981</v>
+        <v>3.169509657118056</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.706076302041818</v>
+        <v>7.705784005763689</v>
       </c>
       <c r="G20" t="n">
-        <v>7.774321972434542</v>
+        <v>7.774032221899491</v>
       </c>
       <c r="H20" t="n">
-        <v>7.938162110083843</v>
+        <v>7.873027661064426</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.932525616584</v>
+        <v>129.0451508605007</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1637416739329</v>
+        <v>129.1339422884002</v>
       </c>
       <c r="H21" t="n">
-        <v>129.8448833822063</v>
+        <v>129.5113501758282</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E2" t="n">
         <v>16724</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.290827137411451</v>
+        <v>8.290991624549694</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002598598058531088</v>
+        <v>-0.002434110920288282</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442986721554085</v>
+        <v>1.442974056335096</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869555056945618</v>
+        <v>1.869514538468291</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7152536214860915</v>
+        <v>0.7152399286704403</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4305883554816642</v>
+        <v>0.4306130366941356</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7152534124794345</v>
+        <v>0.7152396799235168</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.929010420318914</v>
+        <v>3.629999999999998</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.886006970649883</v>
+        <v>5.577216680133183</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.497010808290595</v>
+        <v>8.049331492196044</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E3" t="n">
         <v>16724</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.657300892975284</v>
+        <v>4.657214122992665</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001613481576258104</v>
+        <v>-0.001700251558878099</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315268775019826</v>
+        <v>1.315273335732674</v>
       </c>
       <c r="U3" t="n">
-        <v>1.682092820786858</v>
+        <v>1.682094045158306</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076098438516198</v>
+        <v>0.807615680530643</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6151483811489898</v>
+        <v>0.6151478208927431</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076094438619582</v>
+        <v>0.8076152131579105</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.015101318359375</v>
+        <v>3.041842100844017</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.082922778870848</v>
+        <v>3.104696688497364</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.169509657118056</v>
+        <v>3.19009845721106</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E4" t="n">
         <v>16724</v>
@@ -792,37 +792,37 @@
         <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.785072416378007</v>
+        <v>6.784964815122803</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0008741275110141259</v>
+        <v>-0.0009817287662187916</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505348305529155</v>
+        <v>1.505325368432788</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961322874768392</v>
+        <v>1.961309839637829</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7924575739925822</v>
+        <v>0.792468698949478</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849177637089453</v>
+        <v>0.584923281039349</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924575339154788</v>
+        <v>0.7924686457785449</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.155</v>
+        <v>5.255790968675392</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.517470205533761</v>
+        <v>5.669094040746895</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.894</v>
+        <v>5.991909820585458</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E5" t="n">
         <v>16724</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207675197321215</v>
+        <v>8.207567234788815</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003970640994977283</v>
+        <v>-0.004078603527378555</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511453044485592</v>
+        <v>1.51144360058985</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024664369926787</v>
+        <v>2.024649550357443</v>
       </c>
       <c r="V5" t="n">
-        <v>0.608232505318486</v>
+        <v>0.6082560317902664</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2164404790926291</v>
+        <v>0.2164519496082663</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6082322059536317</v>
+        <v>0.6082557101825496</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.705784005763689</v>
+        <v>7.713018820521186</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.774032221899491</v>
+        <v>7.815390327218969</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.873027661064426</v>
+        <v>7.871216052808252</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E6" t="n">
         <v>16724</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.229127780435303</v>
+        <v>6.229019190807278</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002304681894283677</v>
+        <v>-0.002413271522308876</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390624920446646</v>
+        <v>1.390615085257203</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812969145996653</v>
+        <v>1.812966083427219</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529623501484733</v>
+        <v>0.2529721689297971</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4946348498779916</v>
+        <v>-0.4946298002397789</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529621655730845</v>
+        <v>0.2529719706645076</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.389535184749352</v>
+        <v>7.401218613910571</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.44356833447129</v>
+        <v>7.460444745279837</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.544117658097203</v>
+        <v>7.580828848538925</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E7" t="n">
         <v>16724</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585197651350427</v>
+        <v>5.585140339494236</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002049628008578422</v>
+        <v>-0.002106939864767811</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144499869583488</v>
+        <v>1.144500251432562</v>
       </c>
       <c r="U7" t="n">
-        <v>1.470974357470062</v>
+        <v>1.470976067983636</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168570829452002</v>
+        <v>0.5168676085864016</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03356744760598218</v>
+        <v>0.03356519998425811</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168569204326683</v>
+        <v>0.5168674301326529</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.564938483960701</v>
+        <v>5.566776519450293</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.601044392173109</v>
+        <v>5.604022943638756</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.675203939660222</v>
+        <v>5.671407109736946</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E8" t="n">
         <v>16724</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.42501612951447</v>
+        <v>7.424958325633193</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002780001793829194</v>
+        <v>-0.002837805675106529</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332227509052255</v>
+        <v>1.332236406262987</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748275570735534</v>
+        <v>1.748291228420364</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946000548909676</v>
+        <v>0.7946022076704011</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5891819212940135</v>
+        <v>0.5891745626270949</v>
       </c>
       <c r="X8" t="n">
-        <v>0.794599709660991</v>
+        <v>0.7946018404146595</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.255619473978736</v>
+        <v>5.255043474986961</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.294672764637895</v>
+        <v>5.31382114981348</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.426330768179955</v>
+        <v>5.463625150112827</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E9" t="n">
+        <v>16726</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>16725</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>16724</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.307693584070797</v>
+        <v>7.307518983557549</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.307026306787803</v>
+        <v>7.306853992737948</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006672772829940428</v>
+        <v>-0.0006649908195998431</v>
       </c>
       <c r="T9" t="n">
-        <v>1.60383129820047</v>
+        <v>1.603860140309405</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058465947493815</v>
+        <v>2.058465232167298</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320308068121653</v>
+        <v>0.732032077293832</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639342250678157</v>
+        <v>0.4639371222757747</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320306860229217</v>
+        <v>0.732031957195831</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.551807653407749</v>
+        <v>3.568963366882763</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.776534972885674</v>
+        <v>3.868939966556384</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.218528395467617</v>
+        <v>4.632022987603466</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314569303642987</v>
+        <v>9.314513825304038</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02973903580879971</v>
+        <v>-0.02979451414774928</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492925600554938</v>
+        <v>1.492933462218216</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036087140556897</v>
+        <v>2.036111495543943</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130088098492128</v>
+        <v>0.4130116623186086</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1747698296630142</v>
+        <v>-0.1747979342313637</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130000041871033</v>
+        <v>0.4130028019374888</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.32013302793176</v>
+        <v>9.474667266897182</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.831587737988631</v>
+        <v>10.0926753374135</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.16030257756952</v>
+        <v>10.52982952812425</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E11" t="n">
         <v>16724</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.247023451601581</v>
+        <v>5.246979611231493</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002167053062373754</v>
+        <v>-0.002210893432463264</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129630009196181</v>
+        <v>1.129632116877821</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437965737745067</v>
+        <v>1.437973211428029</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990024338855081</v>
+        <v>0.3990123214496907</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2021435018856603</v>
+        <v>-0.2021559979591334</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990022798822219</v>
+        <v>0.399012155660494</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.11197942223981</v>
+        <v>5.225941258071165</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.305452238718829</v>
+        <v>5.36109380012019</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.387280240885417</v>
+        <v>5.586393739646139</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E12" t="n">
         <v>16724</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.476499643369666</v>
+        <v>7.476541481909677</v>
       </c>
       <c r="R12" t="n">
         <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002758070096012555</v>
+        <v>-0.002716231556001007</v>
       </c>
       <c r="T12" t="n">
-        <v>0.937764844210684</v>
+        <v>0.937781004020774</v>
       </c>
       <c r="U12" t="n">
-        <v>1.251843764820421</v>
+        <v>1.251867993276731</v>
       </c>
       <c r="V12" t="n">
-        <v>0.655791308738441</v>
+        <v>0.6557757081161955</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3116578654194206</v>
+        <v>0.3116312205150127</v>
       </c>
       <c r="X12" t="n">
-        <v>0.655791092267392</v>
+        <v>0.6557754953956161</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.696247184028587</v>
+        <v>5.914744587448042</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.120041066524333</v>
+        <v>6.200574744756172</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.473679764793728</v>
+        <v>6.779971215705488</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E13" t="n">
         <v>16724</v>
@@ -1593,37 +1593,37 @@
         <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.155322052140637</v>
+        <v>9.155233085607605</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.002927917962210025</v>
+        <v>-0.003016884495240095</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195321606296005</v>
+        <v>1.195321883433256</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605654026850897</v>
+        <v>1.60565662891194</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8729923342585195</v>
+        <v>0.8729957574115121</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7459777081526429</v>
+        <v>0.7459768848345005</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8729919296008528</v>
+        <v>0.8729953186964767</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.732143325117774</v>
+        <v>6.701677121615242</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.040766403062895</v>
+        <v>6.990725877759735</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.247311706070747</v>
+        <v>7.248378158263614</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E14" t="n">
         <v>16724</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198255082231411</v>
+        <v>8.198112211927635</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002686080169929775</v>
+        <v>-0.002828950473705127</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847841056105248</v>
+        <v>1.847777874461837</v>
       </c>
       <c r="U14" t="n">
-        <v>2.392768351094911</v>
+        <v>2.392704335556029</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7525822029900524</v>
+        <v>0.7526051646735917</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5051703685254618</v>
+        <v>0.5051968452730022</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7525819858369555</v>
+        <v>0.7526049228297648</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.722037607891492</v>
+        <v>6.70345204933401</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.890553537068188</v>
+        <v>6.862595287109952</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.018170099041033</v>
+        <v>7.003550281282051</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.66813572901694</v>
+        <v>12.66804846036087</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01496668498427135</v>
+        <v>-0.01505395364033353</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354520457280145</v>
+        <v>1.354545086340719</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008252245265232</v>
+        <v>2.00826254275717</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7232870807861977</v>
+        <v>0.7232954464974618</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4443948752320435</v>
+        <v>0.4443891773880851</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232577106597895</v>
+        <v>0.7232654937876065</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.19859771207162</v>
+        <v>11.1900058195669</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.320909370396</v>
+        <v>11.2946209445055</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.43650119325176</v>
+        <v>11.40749120805713</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E16" t="n">
         <v>16724</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.559278263487887</v>
+        <v>7.559281888602479</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002913138090682299</v>
+        <v>-0.00290951297609054</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085316673624317</v>
+        <v>3.085345143097375</v>
       </c>
       <c r="U16" t="n">
-        <v>9.549464024374068</v>
+        <v>9.549475703753689</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0311480410822383</v>
+        <v>0.03114888629145531</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9376936331072916</v>
+        <v>-0.9376983728651067</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03114796448295032</v>
+        <v>0.03114880989540103</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.663103770063456</v>
+        <v>8.445758503856833</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.364198589537143</v>
+        <v>8.991818773270307</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.91628986211883</v>
+        <v>9.203187600054573</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E17" t="n">
         <v>15653</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.840374776433253</v>
+        <v>5.840418232043999</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0299376397821307</v>
+        <v>0.02998109539287782</v>
       </c>
       <c r="T17" t="n">
-        <v>1.220860455175188</v>
+        <v>1.220868466777434</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605218702423864</v>
+        <v>1.605224793124244</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6472037695196429</v>
+        <v>0.6471954237452189</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3020644704090892</v>
+        <v>0.3020591740289095</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6469826959235314</v>
+        <v>0.6469736834655737</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.857220458245922</v>
+        <v>2.952158556813479</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.148650128272942</v>
+        <v>4.515742322976339</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.74148922874878</v>
+        <v>5.347896302719682</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E18" t="n">
         <v>16724</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.53575217588492</v>
+        <v>6.53572968107546</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.00311690447863014</v>
+        <v>-0.003139399288090037</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8012565972311074</v>
+        <v>0.8012708674021899</v>
       </c>
       <c r="U18" t="n">
-        <v>1.114175936222472</v>
+        <v>1.114191553349774</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2250592662962079</v>
+        <v>0.2250635490857845</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5500394020108816</v>
+        <v>-0.5500828553498562</v>
       </c>
       <c r="X18" t="n">
-        <v>0.225059113983698</v>
+        <v>0.2250633898670279</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.997941846798508</v>
+        <v>3.827116121506161</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.365091386378873</v>
+        <v>6.507916117402059</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.096244766254888</v>
+        <v>6.957914987702423</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E19" t="n">
         <v>16724</v>
@@ -2127,37 +2127,37 @@
         <v>0.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.308954705812008</v>
+        <v>9.308862284657916</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.002656541497249401</v>
+        <v>-0.002748962651340662</v>
       </c>
       <c r="T19" t="n">
-        <v>2.210577728318547</v>
+        <v>2.210621731045639</v>
       </c>
       <c r="U19" t="n">
-        <v>2.860599842240195</v>
+        <v>2.860650880694867</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6217930280170116</v>
+        <v>0.6217918789750136</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2435403616009397</v>
+        <v>0.2435133680488745</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6217929157271811</v>
+        <v>0.6217917525358339</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.062741831470335</v>
+        <v>8.294807044857281</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.237283977886607</v>
+        <v>8.541200801570394</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.728639047089874</v>
+        <v>8.687394919955231</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E20" t="n">
         <v>16724</v>
@@ -2216,37 +2216,37 @@
         <v>6.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64331247411897</v>
+        <v>13.64326922530521</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001680183571228008</v>
+        <v>-0.001723432384986334</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184346448014881</v>
+        <v>1.184344204345372</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565807571811916</v>
+        <v>1.565816710342976</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952682779986132</v>
+        <v>0.8952687167785311</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7905605941483246</v>
+        <v>0.7905581494365538</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952681413981582</v>
+        <v>0.8952685927235819</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.4953608222299</v>
+        <v>10.60259825173038</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.74655684314713</v>
+        <v>10.83052356235021</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.95082468500571</v>
+        <v>11.03949463182792</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16724</v>
+        <v>16725</v>
       </c>
       <c r="E21" t="n">
         <v>16724</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5579887714833</v>
+        <v>130.5580154629931</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004384524378993584</v>
+        <v>-0.004357832869175494</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6947386274118682</v>
+        <v>0.6947528871958182</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9295003942484181</v>
+        <v>0.929517523447614</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840121418869714</v>
+        <v>0.8840079497312787</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7679822472812823</v>
+        <v>0.7679736957735096</v>
       </c>
       <c r="X21" t="n">
-        <v>0.884012028253791</v>
+        <v>0.8840078348098214</v>
       </c>
       <c r="Y21" t="n">
-        <v>129.0451508605007</v>
+        <v>129.0447498313982</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1339422884002</v>
+        <v>129.1558766116598</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5113501758282</v>
+        <v>129.602076836054</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.062741831470335</v>
+        <v>8.294807044857281</v>
       </c>
       <c r="G2" t="n">
-        <v>8.237283977886607</v>
+        <v>8.541200801570392</v>
       </c>
       <c r="H2" t="n">
-        <v>8.728639047089874</v>
+        <v>8.687394919955231</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.564938483960701</v>
+        <v>5.566776519450293</v>
       </c>
       <c r="G3" t="n">
-        <v>5.601044392173109</v>
+        <v>5.604022943638756</v>
       </c>
       <c r="H3" t="n">
-        <v>5.675203939660222</v>
+        <v>5.671407109736946</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.11197942223981</v>
+        <v>5.225941258071165</v>
       </c>
       <c r="G4" t="n">
-        <v>5.30545223871883</v>
+        <v>5.361093800120191</v>
       </c>
       <c r="H4" t="n">
-        <v>5.387280240885417</v>
+        <v>5.586393739646139</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.663103770063456</v>
+        <v>8.445758503856833</v>
       </c>
       <c r="G5" t="n">
-        <v>9.364198589537143</v>
+        <v>8.991818773270307</v>
       </c>
       <c r="H5" t="n">
-        <v>10.91628986211883</v>
+        <v>9.203187600054573</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.929010420318914</v>
+        <v>3.629999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>3.886006970649883</v>
+        <v>5.577216680133184</v>
       </c>
       <c r="H6" t="n">
-        <v>6.497010808290595</v>
+        <v>8.049331492196044</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.19859771207162</v>
+        <v>11.1900058195669</v>
       </c>
       <c r="G7" t="n">
-        <v>11.320909370396</v>
+        <v>11.2946209445055</v>
       </c>
       <c r="H7" t="n">
-        <v>11.43650119325176</v>
+        <v>11.40749120805713</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.732143325117774</v>
+        <v>6.701677121615242</v>
       </c>
       <c r="G8" t="n">
-        <v>7.040766403062895</v>
+        <v>6.990725877759734</v>
       </c>
       <c r="H8" t="n">
-        <v>7.247311706070747</v>
+        <v>7.248378158263614</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.696247184028587</v>
+        <v>5.914744587448042</v>
       </c>
       <c r="G9" t="n">
-        <v>6.120041066524333</v>
+        <v>6.200574744756171</v>
       </c>
       <c r="H9" t="n">
-        <v>6.473679764793728</v>
+        <v>6.779971215705488</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.255619473978736</v>
+        <v>5.255043474986961</v>
       </c>
       <c r="G10" t="n">
-        <v>5.294672764637896</v>
+        <v>5.31382114981348</v>
       </c>
       <c r="H10" t="n">
-        <v>5.426330768179955</v>
+        <v>5.463625150112827</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4953608222299</v>
+        <v>10.60259825173038</v>
       </c>
       <c r="G11" t="n">
-        <v>10.74655684314713</v>
+        <v>10.83052356235021</v>
       </c>
       <c r="H11" t="n">
-        <v>10.95082468500571</v>
+        <v>11.03949463182792</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.857220458245922</v>
+        <v>2.952158556813479</v>
       </c>
       <c r="G12" t="n">
-        <v>4.148650128272942</v>
+        <v>4.515742322976339</v>
       </c>
       <c r="H12" t="n">
-        <v>5.74148922874878</v>
+        <v>5.347896302719682</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.722037607891492</v>
+        <v>6.70345204933401</v>
       </c>
       <c r="G13" t="n">
-        <v>6.890553537068188</v>
+        <v>6.862595287109952</v>
       </c>
       <c r="H13" t="n">
-        <v>7.018170099041033</v>
+        <v>7.003550281282051</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.32013302793176</v>
+        <v>9.474667266897182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.831587737988631</v>
+        <v>10.0926753374135</v>
       </c>
       <c r="H14" t="n">
-        <v>10.16030257756952</v>
+        <v>10.52982952812425</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.551807653407749</v>
+        <v>3.568963366882763</v>
       </c>
       <c r="G15" t="n">
-        <v>3.776534972885674</v>
+        <v>3.868939966556384</v>
       </c>
       <c r="H15" t="n">
-        <v>4.218528395467617</v>
+        <v>4.632022987603466</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.389535184749352</v>
+        <v>7.401218613910571</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44356833447129</v>
+        <v>7.460444745279837</v>
       </c>
       <c r="H16" t="n">
-        <v>7.544117658097203</v>
+        <v>7.580828848538925</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.997941846798508</v>
+        <v>3.827116121506161</v>
       </c>
       <c r="G17" t="n">
-        <v>6.365091386378873</v>
+        <v>6.507916117402059</v>
       </c>
       <c r="H17" t="n">
-        <v>7.096244766254888</v>
+        <v>6.957914987702423</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.155</v>
+        <v>5.255790968675392</v>
       </c>
       <c r="G18" t="n">
-        <v>5.517470205533762</v>
+        <v>5.669094040746894</v>
       </c>
       <c r="H18" t="n">
-        <v>5.894</v>
+        <v>5.991909820585458</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.015101318359375</v>
+        <v>3.041842100844017</v>
       </c>
       <c r="G19" t="n">
-        <v>3.082922778870848</v>
+        <v>3.104696688497364</v>
       </c>
       <c r="H19" t="n">
-        <v>3.169509657118056</v>
+        <v>3.19009845721106</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.705784005763689</v>
+        <v>7.713018820521186</v>
       </c>
       <c r="G20" t="n">
-        <v>7.774032221899491</v>
+        <v>7.815390327218969</v>
       </c>
       <c r="H20" t="n">
-        <v>7.873027661064426</v>
+        <v>7.871216052808252</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>129.0451508605007</v>
+        <v>129.0447498313982</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1339422884002</v>
+        <v>129.1558766116598</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5113501758282</v>
+        <v>129.602076836054</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E2" t="n">
         <v>16724</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.290991624549694</v>
+        <v>8.291072741576697</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002434110920288282</v>
+        <v>-0.002352993893284601</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442974056335096</v>
+        <v>1.442981295283828</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869514538468291</v>
+        <v>1.869523089792409</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7152399286704403</v>
+        <v>0.7152296860671868</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4306130366941356</v>
+        <v>0.4306078278300084</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7152396799235168</v>
+        <v>0.715229423872964</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.629999999999998</v>
+        <v>3.179999999999998</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.577216680133183</v>
+        <v>5.101050467616219</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.049331492196044</v>
+        <v>6.019564130286609</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E3" t="n">
         <v>16724</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.657214122992665</v>
+        <v>4.657128512308641</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001700251558878099</v>
+        <v>-0.001785862242901615</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315273335732674</v>
+        <v>1.31528176650824</v>
       </c>
       <c r="U3" t="n">
-        <v>1.682094045158306</v>
+        <v>1.682098385316188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.807615680530643</v>
+        <v>0.8076207970275299</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6151478208927431</v>
+        <v>0.6151458348903809</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076152131579105</v>
+        <v>0.8076202558096103</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.041842100844017</v>
+        <v>3.03155170872823</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.104696688497364</v>
+        <v>3.106369782629619</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.19009845721106</v>
+        <v>3.256365888181175</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E4" t="n">
         <v>16724</v>
@@ -792,37 +792,37 @@
         <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.784964815122803</v>
+        <v>6.784853649519478</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0009817287662187916</v>
+        <v>-0.001092894369544308</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505325368432788</v>
+        <v>1.505295642094103</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961309839637829</v>
+        <v>1.96129073590004</v>
       </c>
       <c r="V4" t="n">
-        <v>0.792468698949478</v>
+        <v>0.7924811871784789</v>
       </c>
       <c r="W4" t="n">
-        <v>0.584923281039349</v>
+        <v>0.5849313669399275</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924686457785449</v>
+        <v>0.7924811113510947</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.255790968675392</v>
+        <v>5.38267940552017</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.669094040746895</v>
+        <v>5.754359250207028</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.991909820585458</v>
+        <v>5.963655987371727</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E5" t="n">
         <v>16724</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207567234788815</v>
+        <v>8.207458745094511</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004078603527378555</v>
+        <v>-0.004187093221681218</v>
       </c>
       <c r="T5" t="n">
-        <v>1.51144360058985</v>
+        <v>1.51143326368228</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024649550357443</v>
+        <v>2.024634283714368</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6082560317902664</v>
+        <v>0.6082797631846804</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2164519496082663</v>
+        <v>0.2164637660762728</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6082557101825496</v>
+        <v>0.6082794135684444</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.713018820521186</v>
+        <v>7.718732816790313</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.815390327218969</v>
+        <v>7.800820956274931</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.871216052808252</v>
+        <v>7.859334492330315</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E6" t="n">
         <v>16724</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.229019190807278</v>
+        <v>6.228912264374407</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002413271522308876</v>
+        <v>-0.002520197955179067</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390615085257203</v>
+        <v>1.390605992752103</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812966083427219</v>
+        <v>1.812966574570981</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529721689297971</v>
+        <v>0.2529798071212871</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4946298002397789</v>
+        <v>-0.4946306100488627</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529719706645076</v>
+        <v>0.252979594257127</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.401218613910571</v>
+        <v>7.395843756014687</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.460444745279837</v>
+        <v>7.500304072046379</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.580828848538925</v>
+        <v>7.728045883433102</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E7" t="n">
         <v>16724</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585140339494236</v>
+        <v>5.585085072768343</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002106939864767811</v>
+        <v>-0.002162206590661828</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144500251432562</v>
+        <v>1.144501762026495</v>
       </c>
       <c r="U7" t="n">
-        <v>1.470976067983636</v>
+        <v>1.470978763513866</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168676085864016</v>
+        <v>0.5168775246682564</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03356519998425811</v>
+        <v>0.03356165804137778</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168674301326529</v>
+        <v>0.5168773291242639</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.566776519450293</v>
+        <v>5.569131346619559</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.604022943638756</v>
+        <v>5.608427919258462</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.671407109736946</v>
+        <v>5.724809485516529</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E8" t="n">
         <v>16724</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.424958325633193</v>
+        <v>7.424903623382697</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002837805675106529</v>
+        <v>-0.002892507925602194</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332236406262987</v>
+        <v>1.332245889057788</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748291228420364</v>
+        <v>1.748306015913144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946022076704011</v>
+        <v>0.7946043810413673</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5891745626270949</v>
+        <v>0.5891676128651988</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946018404146595</v>
+        <v>0.7946039887887713</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.255043474986961</v>
+        <v>5.250625389153639</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.31382114981348</v>
+        <v>5.336785310031291</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.463625150112827</v>
+        <v>5.515737159530272</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E9" t="n">
         <v>16726</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.307518983557549</v>
+        <v>7.307344852325721</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306853992737948</v>
+        <v>7.306692159668392</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006649908195998431</v>
+        <v>-0.0006526926573280956</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603860140309405</v>
+        <v>1.603882505154678</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058465232167298</v>
+        <v>2.058473958950591</v>
       </c>
       <c r="V9" t="n">
-        <v>0.732032077293832</v>
+        <v>0.7320323733420944</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639371222757747</v>
+        <v>0.4639349198739898</v>
       </c>
       <c r="X9" t="n">
-        <v>0.732031957195831</v>
+        <v>0.7320322491511175</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.568963366882763</v>
+        <v>3.59244677734375</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.868939966556384</v>
+        <v>3.982421254138592</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.632022987603466</v>
+        <v>4.788508951822917</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314513825304038</v>
+        <v>9.314452622106568</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02979451414774928</v>
+        <v>-0.02985571734521955</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492933462218216</v>
+        <v>1.492945035010679</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036111495543943</v>
+        <v>2.036135348431022</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130116623186086</v>
+        <v>0.4130147348821144</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1747979342313637</v>
+        <v>-0.1748254597246059</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130028019374888</v>
+        <v>0.4130058152271443</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.474667266897182</v>
+        <v>9.646477838841717</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.0926753374135</v>
+        <v>10.17123689536868</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.52982952812425</v>
+        <v>10.68804209745896</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E11" t="n">
         <v>16724</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246979611231493</v>
+        <v>5.246933181707734</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002210893432463264</v>
+        <v>-0.002257322956221398</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129632116877821</v>
+        <v>1.129633894124199</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437973211428029</v>
+        <v>1.437979328111299</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990123214496907</v>
+        <v>0.3990233261830863</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2021559979591334</v>
+        <v>-0.2021662251637311</v>
       </c>
       <c r="X11" t="n">
-        <v>0.399012155660494</v>
+        <v>0.3990231469581623</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.225941258071165</v>
+        <v>5.007039155341398</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.36109380012019</v>
+        <v>5.367587981237514</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.586393739646139</v>
+        <v>5.655454595862315</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E12" t="n">
         <v>16724</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.476541481909677</v>
+        <v>7.476570212536712</v>
       </c>
       <c r="R12" t="n">
         <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002716231556001007</v>
+        <v>-0.002687500928964999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.937781004020774</v>
+        <v>0.9377982355350019</v>
       </c>
       <c r="U12" t="n">
-        <v>1.251867993276731</v>
+        <v>1.251893233769807</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6557757081161955</v>
+        <v>0.655762890715727</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3116312205150127</v>
+        <v>0.3116034620889431</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6557754953956161</v>
+        <v>0.6557626831372287</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.914744587448042</v>
+        <v>6.128204029304537</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.200574744756172</v>
+        <v>6.267681775369398</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.779971215705488</v>
+        <v>6.919171899615667</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E13" t="n">
         <v>16724</v>
@@ -1593,37 +1593,37 @@
         <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.155233085607605</v>
+        <v>9.155144261395233</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.003016884495240095</v>
+        <v>-0.003105708707612496</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195321883433256</v>
+        <v>1.195321341994745</v>
       </c>
       <c r="U13" t="n">
-        <v>1.60565662891194</v>
+        <v>1.605660121187994</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8729957574115121</v>
+        <v>0.8729990378315559</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7459768848345005</v>
+        <v>0.7459757798413271</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8729953186964767</v>
+        <v>0.8729985572962854</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.701677121615242</v>
+        <v>6.678564323056321</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.990725877759735</v>
+        <v>6.931711799194855</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.248378158263614</v>
+        <v>7.217242220546692</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E14" t="n">
         <v>16724</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.198112211927635</v>
+        <v>8.197970381813162</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002828950473705127</v>
+        <v>-0.002970780588176773</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847777874461837</v>
+        <v>1.847715744443566</v>
       </c>
       <c r="U14" t="n">
-        <v>2.392704335556029</v>
+        <v>2.392638596271778</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7526051646735917</v>
+        <v>0.7526284574299693</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5051968452730022</v>
+        <v>0.5052240342222609</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7526049228297648</v>
+        <v>0.7526281836770794</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.70345204933401</v>
+        <v>6.687953799028925</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.862595287109952</v>
+        <v>6.821365492583624</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.003550281282051</v>
+        <v>6.91985349825863</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.66804846036087</v>
+        <v>12.66796292070471</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01505395364033353</v>
+        <v>-0.01513949329649567</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354545086340719</v>
+        <v>1.354568953891002</v>
       </c>
       <c r="U15" t="n">
-        <v>2.00826254275717</v>
+        <v>2.008273071515818</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7232954464974618</v>
+        <v>0.7233036535064327</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4443891773880851</v>
+        <v>0.444383351548621</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232654937876065</v>
+        <v>0.7232731177370413</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.1900058195669</v>
+        <v>11.17524759984845</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.2946209445055</v>
+        <v>11.27069128822819</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.40749120805713</v>
+        <v>11.37337673674604</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E16" t="n">
         <v>16724</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.559281888602479</v>
+        <v>7.559288267954335</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.00290951297609054</v>
+        <v>-0.002903133624235135</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085345143097375</v>
+        <v>3.085372200488986</v>
       </c>
       <c r="U16" t="n">
-        <v>9.549475703753689</v>
+        <v>9.549486854878822</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03114888629145531</v>
+        <v>0.03114993900200395</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9376983728651067</v>
+        <v>-0.9377028982506483</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03114880989540103</v>
+        <v>0.03114986294180955</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.445758503856833</v>
+        <v>8.438434848754873</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.991818773270307</v>
+        <v>8.895893366944019</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.203187600054573</v>
+        <v>9.191731702551678</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E17" t="n">
         <v>15653</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.840418232043999</v>
+        <v>5.84042664687296</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02998109539287782</v>
+        <v>0.02998951022183874</v>
       </c>
       <c r="T17" t="n">
-        <v>1.220868466777434</v>
+        <v>1.220886234259734</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605224793124244</v>
+        <v>1.605242201127457</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6471954237452189</v>
+        <v>0.6471892947024358</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3020591740289095</v>
+        <v>0.302044036183951</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6469736834655737</v>
+        <v>0.6469676733674415</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.952158556813479</v>
+        <v>2.546823147722587</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.515742322976339</v>
+        <v>4.321745529723419</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.347896302719682</v>
+        <v>5.362413557757263</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E18" t="n">
         <v>16724</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.53572968107546</v>
+        <v>6.535690676867007</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.003139399288090037</v>
+        <v>-0.00317840349654368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8012708674021899</v>
+        <v>0.8012771364750939</v>
       </c>
       <c r="U18" t="n">
-        <v>1.114191553349774</v>
+        <v>1.114199789886504</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2250635490857845</v>
+        <v>0.2250752413536632</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5500828553498562</v>
+        <v>-0.5501057730636474</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2250633898670279</v>
+        <v>0.2250750729630053</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.827116121506161</v>
+        <v>3.02275514568244</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.507916117402059</v>
+        <v>6.343485884493726</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.957914987702423</v>
+        <v>6.966478100258317</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E19" t="n">
         <v>16724</v>
@@ -2127,37 +2127,37 @@
         <v>0.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.308862284657916</v>
+        <v>9.308760436963089</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.002748962651340662</v>
+        <v>-0.002850810346167172</v>
       </c>
       <c r="T19" t="n">
-        <v>2.210621731045639</v>
+        <v>2.210665029558151</v>
       </c>
       <c r="U19" t="n">
-        <v>2.860650880694867</v>
+        <v>2.860697013669233</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6217918789750136</v>
+        <v>0.6217923966904144</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2435133680488745</v>
+        <v>0.2434889685249486</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6217917525358339</v>
+        <v>0.6217922518963596</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.294807044857281</v>
+        <v>8.103254290670026</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.541200801570394</v>
+        <v>8.53183966233996</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.687394919955231</v>
+        <v>8.661649441559721</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E20" t="n">
         <v>16724</v>
@@ -2216,37 +2216,37 @@
         <v>6.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64326922530521</v>
+        <v>13.64321979319412</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001723432384986334</v>
+        <v>-0.001772864496073711</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184344204345372</v>
+        <v>1.184339577600607</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565816710342976</v>
+        <v>1.565824091086148</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952687167785311</v>
+        <v>0.8952695629225345</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7905581494365538</v>
+        <v>0.7905561749523865</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952685927235819</v>
+        <v>0.8952694496692943</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.60259825173038</v>
+        <v>10.74939040335823</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.83052356235021</v>
+        <v>10.87486576053428</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.03949463182792</v>
+        <v>11.00988287745317</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16725</v>
+        <v>16726</v>
       </c>
       <c r="E21" t="n">
         <v>16724</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5580154629931</v>
+        <v>130.5580425066872</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004357832869175494</v>
+        <v>-0.004330789175016709</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6947528871958182</v>
+        <v>0.6947667176577218</v>
       </c>
       <c r="U21" t="n">
-        <v>0.929517523447614</v>
+        <v>0.9295343112014498</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840079497312787</v>
+        <v>0.8840038261800341</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7679736957735096</v>
+        <v>0.7679653145745422</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8840078348098214</v>
+        <v>0.88400371015721</v>
       </c>
       <c r="Y21" t="n">
-        <v>129.0447498313982</v>
+        <v>129.0443697619914</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.1558766116598</v>
+        <v>129.2539376886269</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.602076836054</v>
+        <v>130.9829965712808</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.294807044857281</v>
+        <v>8.103254290670026</v>
       </c>
       <c r="G2" t="n">
-        <v>8.541200801570392</v>
+        <v>8.53183966233996</v>
       </c>
       <c r="H2" t="n">
-        <v>8.687394919955231</v>
+        <v>8.661649441559721</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.566776519450293</v>
+        <v>5.569131346619559</v>
       </c>
       <c r="G3" t="n">
-        <v>5.604022943638756</v>
+        <v>5.608427919258462</v>
       </c>
       <c r="H3" t="n">
-        <v>5.671407109736946</v>
+        <v>5.724809485516529</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.225941258071165</v>
+        <v>5.007039155341398</v>
       </c>
       <c r="G4" t="n">
-        <v>5.361093800120191</v>
+        <v>5.367587981237514</v>
       </c>
       <c r="H4" t="n">
-        <v>5.586393739646139</v>
+        <v>5.655454595862315</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.445758503856833</v>
+        <v>8.438434848754873</v>
       </c>
       <c r="G5" t="n">
-        <v>8.991818773270307</v>
+        <v>8.895893366944019</v>
       </c>
       <c r="H5" t="n">
-        <v>9.203187600054573</v>
+        <v>9.191731702551678</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.629999999999998</v>
+        <v>3.179999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>5.577216680133184</v>
+        <v>5.101050467616219</v>
       </c>
       <c r="H6" t="n">
-        <v>8.049331492196044</v>
+        <v>6.019564130286609</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.1900058195669</v>
+        <v>11.17524759984845</v>
       </c>
       <c r="G7" t="n">
-        <v>11.2946209445055</v>
+        <v>11.27069128822819</v>
       </c>
       <c r="H7" t="n">
-        <v>11.40749120805713</v>
+        <v>11.37337673674604</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.701677121615242</v>
+        <v>6.678564323056321</v>
       </c>
       <c r="G8" t="n">
-        <v>6.990725877759734</v>
+        <v>6.931711799194855</v>
       </c>
       <c r="H8" t="n">
-        <v>7.248378158263614</v>
+        <v>7.217242220546692</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.914744587448042</v>
+        <v>6.128204029304537</v>
       </c>
       <c r="G9" t="n">
-        <v>6.200574744756171</v>
+        <v>6.267681775369399</v>
       </c>
       <c r="H9" t="n">
-        <v>6.779971215705488</v>
+        <v>6.919171899615667</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.255043474986961</v>
+        <v>5.250625389153639</v>
       </c>
       <c r="G10" t="n">
-        <v>5.31382114981348</v>
+        <v>5.336785310031291</v>
       </c>
       <c r="H10" t="n">
-        <v>5.463625150112827</v>
+        <v>5.515737159530272</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.60259825173038</v>
+        <v>10.74939040335823</v>
       </c>
       <c r="G11" t="n">
-        <v>10.83052356235021</v>
+        <v>10.87486576053428</v>
       </c>
       <c r="H11" t="n">
-        <v>11.03949463182792</v>
+        <v>11.00988287745317</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.952158556813479</v>
+        <v>2.546823147722587</v>
       </c>
       <c r="G12" t="n">
-        <v>4.515742322976339</v>
+        <v>4.321745529723419</v>
       </c>
       <c r="H12" t="n">
-        <v>5.347896302719682</v>
+        <v>5.362413557757263</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.70345204933401</v>
+        <v>6.687953799028925</v>
       </c>
       <c r="G13" t="n">
-        <v>6.862595287109952</v>
+        <v>6.821365492583624</v>
       </c>
       <c r="H13" t="n">
-        <v>7.003550281282051</v>
+        <v>6.91985349825863</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.474667266897182</v>
+        <v>9.646477838841717</v>
       </c>
       <c r="G14" t="n">
-        <v>10.0926753374135</v>
+        <v>10.17123689536868</v>
       </c>
       <c r="H14" t="n">
-        <v>10.52982952812425</v>
+        <v>10.68804209745896</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.568963366882763</v>
+        <v>3.59244677734375</v>
       </c>
       <c r="G15" t="n">
-        <v>3.868939966556384</v>
+        <v>3.982421254138592</v>
       </c>
       <c r="H15" t="n">
-        <v>4.632022987603466</v>
+        <v>4.788508951822917</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.401218613910571</v>
+        <v>7.395843756014687</v>
       </c>
       <c r="G16" t="n">
-        <v>7.460444745279837</v>
+        <v>7.500304072046379</v>
       </c>
       <c r="H16" t="n">
-        <v>7.580828848538925</v>
+        <v>7.728045883433102</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.827116121506161</v>
+        <v>3.02275514568244</v>
       </c>
       <c r="G17" t="n">
-        <v>6.507916117402059</v>
+        <v>6.343485884493726</v>
       </c>
       <c r="H17" t="n">
-        <v>6.957914987702423</v>
+        <v>6.966478100258317</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.255790968675392</v>
+        <v>5.38267940552017</v>
       </c>
       <c r="G18" t="n">
-        <v>5.669094040746894</v>
+        <v>5.754359250207029</v>
       </c>
       <c r="H18" t="n">
-        <v>5.991909820585458</v>
+        <v>5.963655987371727</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.041842100844017</v>
+        <v>3.03155170872823</v>
       </c>
       <c r="G19" t="n">
-        <v>3.104696688497364</v>
+        <v>3.106369782629619</v>
       </c>
       <c r="H19" t="n">
-        <v>3.19009845721106</v>
+        <v>3.256365888181175</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.713018820521186</v>
+        <v>7.718732816790313</v>
       </c>
       <c r="G20" t="n">
-        <v>7.815390327218969</v>
+        <v>7.800820956274931</v>
       </c>
       <c r="H20" t="n">
-        <v>7.871216052808252</v>
+        <v>7.859334492330315</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>129.0447498313982</v>
+        <v>129.0443697619914</v>
       </c>
       <c r="G21" t="n">
-        <v>129.1558766116598</v>
+        <v>129.2539376886269</v>
       </c>
       <c r="H21" t="n">
-        <v>129.602076836054</v>
+        <v>130.9829965712808</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E2" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>29587</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M2" t="n">
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>8.293425735469983</v>
+        <v>8.292294476327115</v>
       </c>
       <c r="O2" t="n">
         <v>14.02</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.291072741576697</v>
+        <v>8.289611507822226</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002352993893284601</v>
+        <v>-0.002682968504889235</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442981295283828</v>
+        <v>1.442902565515809</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869523089792409</v>
+        <v>1.869447358776848</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7152296860671868</v>
+        <v>0.7154749369496423</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4306078278300084</v>
+        <v>0.4310143260599292</v>
       </c>
       <c r="X2" t="n">
-        <v>0.715229423872964</v>
+        <v>0.715474729606054</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.179999999999998</v>
+        <v>3.480652785836915</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.101050467616219</v>
+        <v>5.113951750924516</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.019564130286609</v>
+        <v>5.989999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E3" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>29587</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.658914374551543</v>
+        <v>4.658139436872309</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.657128512308641</v>
+        <v>4.656514560006923</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001785862242901615</v>
+        <v>-0.001624876865387453</v>
       </c>
       <c r="T3" t="n">
-        <v>1.31528176650824</v>
+        <v>1.315307928141964</v>
       </c>
       <c r="U3" t="n">
-        <v>1.682098385316188</v>
+        <v>1.68201745858833</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076207970275299</v>
+        <v>0.8076464196613938</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6151458348903809</v>
+        <v>0.6152222700386845</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076202558096103</v>
+        <v>0.807646016875286</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.03155170872823</v>
+        <v>3.025549548893179</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.106369782629619</v>
+        <v>3.154997101459265</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.256365888181175</v>
+        <v>3.400426072493374</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E4" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>29587</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.785946543889022</v>
+        <v>6.784784044715447</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005</v>
+        <v>0.005017667844522967</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.784853649519478</v>
+        <v>6.783826718874579</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.001092894369544308</v>
+        <v>-0.0009573258408686993</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505295642094103</v>
+        <v>1.505565124322512</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96129073590004</v>
+        <v>1.961556135045129</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7924811871784789</v>
+        <v>0.792490771740754</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849313669399275</v>
+        <v>0.5849726746419075</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924811113510947</v>
+        <v>0.7924907226937647</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.38267940552017</v>
+        <v>5.739806475733984</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.754359250207028</v>
+        <v>5.890578660421492</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.963655987371727</v>
+        <v>6.006776882729683</v>
       </c>
     </row>
     <row r="5">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E5" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>29587</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.211645838316192</v>
+        <v>8.210982036107126</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207458745094511</v>
+        <v>8.206989903832342</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004187093221681218</v>
+        <v>-0.00399213227478359</v>
       </c>
       <c r="T5" t="n">
-        <v>1.51143326368228</v>
+        <v>1.511428355756432</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024634283714368</v>
+        <v>2.024437924321379</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6082797631846804</v>
+        <v>0.6083617747266296</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2164637660762728</v>
+        <v>0.2167043461402531</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6082794135684444</v>
+        <v>0.6083614723937214</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.718732816790313</v>
+        <v>7.768235728350782</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.800820956274931</v>
+        <v>7.849724555494973</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.859334492330315</v>
+        <v>7.870797923286012</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E6" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>29587</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.231432462329586</v>
+        <v>6.231295671927308</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.228912264374407</v>
+        <v>6.22898016058854</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002520197955179067</v>
+        <v>-0.002315511338768029</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390605992752103</v>
+        <v>1.390603067644455</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812966574570981</v>
+        <v>1.812830849267718</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529798071212871</v>
+        <v>0.2529078358205874</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4946306100488627</v>
+        <v>-0.4947121821280454</v>
       </c>
       <c r="X6" t="n">
-        <v>0.252979594257127</v>
+        <v>0.2529076606918562</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.395843756014687</v>
+        <v>7.401625794574484</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.500304072046379</v>
+        <v>7.679008002052967</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.728045883433102</v>
+        <v>8.208265250468296</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E7" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>29587</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.587247279359005</v>
+        <v>5.586738910808226</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585085072768343</v>
+        <v>5.584602309271589</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002162206590661828</v>
+        <v>-0.00213660153663753</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144501762026495</v>
+        <v>1.144828772512772</v>
       </c>
       <c r="U7" t="n">
-        <v>1.470978763513866</v>
+        <v>1.471232909688278</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168775246682564</v>
+        <v>0.516828624566386</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03356165804137778</v>
+        <v>0.03346358669305027</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168773291242639</v>
+        <v>0.5168284325355674</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.569131346619559</v>
+        <v>5.565623265422556</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.608427919258462</v>
+        <v>5.654834491705734</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.724809485516529</v>
+        <v>5.807974365283955</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E8" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>29587</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4277961313083</v>
+        <v>7.427092748684839</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.424903623382697</v>
+        <v>7.424330758832232</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002892507925602194</v>
+        <v>-0.002761989852607423</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332245889057788</v>
+        <v>1.332028837854563</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748306015913144</v>
+        <v>1.748063139483447</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946043810413673</v>
+        <v>0.7946548354831341</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5891676128651988</v>
+        <v>0.5892977398185801</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946039887887713</v>
+        <v>0.7946544970287291</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.250625389153639</v>
+        <v>5.248085788160576</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.336785310031291</v>
+        <v>5.476852237854344</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.515737159530272</v>
+        <v>6.026152632801012</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E9" t="n">
-        <v>16726</v>
+        <v>16729</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.307344852325721</v>
+        <v>7.306996652319465</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306692159668392</v>
+        <v>7.306335393744883</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006526926573280956</v>
+        <v>-0.0006612585745817462</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603882505154678</v>
+        <v>1.603908561423259</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058473958950591</v>
+        <v>2.058434723811801</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320323733420944</v>
+        <v>0.7320429849416669</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639349198739898</v>
+        <v>0.4639600370103214</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320322491511175</v>
+        <v>0.7320428668037913</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.59244677734375</v>
+        <v>3.625250799444155</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.982421254138592</v>
+        <v>4.277350254679843</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.788508951822917</v>
+        <v>5.399842448770703</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314452622106568</v>
+        <v>9.314300668722758</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02985571734521955</v>
+        <v>-0.03000767072902708</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492945035010679</v>
+        <v>1.492940917044298</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036135348431022</v>
+        <v>2.036171847287712</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130147348821144</v>
+        <v>0.41302582749438</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1748254597246059</v>
+        <v>-0.174867578899488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130058152271443</v>
+        <v>0.4130167706722728</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.646477838841717</v>
+        <v>10.05316612131659</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.17123689536868</v>
+        <v>10.61757535143252</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.68804209745896</v>
+        <v>10.82906695310399</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E11" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>29587</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.249190504663956</v>
+        <v>5.248938725490197</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246933181707734</v>
+        <v>5.246721086825227</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002257322956221398</v>
+        <v>-0.002217638664969466</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129633894124199</v>
+        <v>1.129588942747579</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437979328111299</v>
+        <v>1.437867341091498</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990233261830863</v>
+        <v>0.3990452192053002</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2021662251637311</v>
+        <v>-0.2020789637542968</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990231469581623</v>
+        <v>0.3990450547203929</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.007039155341398</v>
+        <v>5.358205115503534</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.367587981237514</v>
+        <v>5.69640420519395</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.655454595862315</v>
+        <v>5.859021088357833</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E12" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>29587</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.479257713465678</v>
+        <v>7.478560108799617</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.476570212536712</v>
+        <v>7.47572318425237</v>
       </c>
       <c r="R12" t="n">
-        <v>19.178</v>
+        <v>19.17048551236861</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002687500928964999</v>
+        <v>-0.002836924547247097</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9377982355350019</v>
+        <v>0.9380198563000417</v>
       </c>
       <c r="U12" t="n">
-        <v>1.251893233769807</v>
+        <v>1.252081936689929</v>
       </c>
       <c r="V12" t="n">
-        <v>0.655762890715727</v>
+        <v>0.655900465450965</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3116034620889431</v>
+        <v>0.3118490678195501</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6557626831372287</v>
+        <v>0.6559002481624938</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.128204029304537</v>
+        <v>6.132102001582714</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.267681775369398</v>
+        <v>6.393253524144971</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.919171899615667</v>
+        <v>7.008076526170115</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E13" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>29587</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.158249970102847</v>
+        <v>9.157570241511239</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.540007067137809</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.155144261395233</v>
+        <v>9.15468233367638</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.003105708707612496</v>
+        <v>-0.002887907834856712</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195321341994745</v>
+        <v>1.195124582257917</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605660121187994</v>
+        <v>1.605419443172033</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8729990378315559</v>
+        <v>0.8730208622131944</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7459757798413271</v>
+        <v>0.7460395545986452</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8729985572962854</v>
+        <v>0.8730204705018729</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.678564323056321</v>
+        <v>6.657674060576896</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.931711799194855</v>
+        <v>6.825071812778654</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.217242220546692</v>
+        <v>7.082679261610253</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E14" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>29587</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.200941162401341</v>
+        <v>8.200209230033478</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197970381813162</v>
+        <v>8.197557040110565</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002970780588176773</v>
+        <v>-0.002652189922911107</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847715744443566</v>
+        <v>1.847389362100058</v>
       </c>
       <c r="U14" t="n">
-        <v>2.392638596271778</v>
+        <v>2.39211999020895</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7526284574299693</v>
+        <v>0.7527002146533038</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5052240342222609</v>
+        <v>0.5054160188083161</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7526281836770794</v>
+        <v>0.752700000987044</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.687953799028925</v>
+        <v>6.677106018858804</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.821365492583624</v>
+        <v>6.898328274970959</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.91985349825863</v>
+        <v>7.177118638603833</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.66796292070471</v>
+        <v>12.66779536809093</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01513949329649567</v>
+        <v>-0.01530704591027783</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354568953891002</v>
+        <v>1.354614708982712</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008273071515818</v>
+        <v>2.008296681711325</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7233036535064327</v>
+        <v>0.7233191897213604</v>
       </c>
       <c r="W15" t="n">
-        <v>0.444383351548621</v>
+        <v>0.4443702872945663</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232731177370413</v>
+        <v>0.7232874809221258</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.17524759984845</v>
+        <v>11.13539078890464</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.27069128822819</v>
+        <v>11.22413438554022</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.37337673674604</v>
+        <v>11.34292911326453</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E16" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>29587</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>7.562191401578569</v>
+        <v>7.561948469631756</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.559288267954335</v>
+        <v>7.558894428869755</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002903133624235135</v>
+        <v>-0.003054040761999935</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085372200488986</v>
+        <v>3.085527965752862</v>
       </c>
       <c r="U16" t="n">
-        <v>9.549486854878822</v>
+        <v>9.548501729642295</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03114993900200395</v>
+        <v>0.03111206154831916</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9377028982506483</v>
+        <v>-0.9377561530199923</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03114986294180955</v>
+        <v>0.03111197731963677</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.438434848754873</v>
+        <v>8.345917465376413</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.895893366944019</v>
+        <v>8.686190358598369</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.191731702551678</v>
+        <v>9.160301540648623</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E17" t="n">
-        <v>15653</v>
+        <v>15658</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>15653</v>
+        <v>15657</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>30317</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>5.810437136651121</v>
+        <v>5.809542057865491</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.84042664687296</v>
+        <v>5.839432652308895</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02998951022183874</v>
+        <v>0.02989059444340318</v>
       </c>
       <c r="T17" t="n">
-        <v>1.220886234259734</v>
+        <v>1.221189285006129</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605242201127457</v>
+        <v>1.605469541152649</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6471892947024358</v>
+        <v>0.6473163755649972</v>
       </c>
       <c r="W17" t="n">
-        <v>0.302044036183951</v>
+        <v>0.3022680379198771</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6469676733674415</v>
+        <v>0.6470962810358438</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.546823147722587</v>
+        <v>1.941752440505575</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.321745529723419</v>
+        <v>4.639238425025912</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.362413557757263</v>
+        <v>5.561913221531623</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E18" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>29587</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.53886908036355</v>
+        <v>6.538119560019129</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.535690676867007</v>
+        <v>6.534897272136416</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.00317840349654368</v>
+        <v>-0.003222287882713035</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8012771364750939</v>
+        <v>0.802448652821073</v>
       </c>
       <c r="U18" t="n">
-        <v>1.114199789886504</v>
+        <v>1.116156163993724</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2250752413536632</v>
+        <v>0.2245367709143825</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5501057730636474</v>
+        <v>-0.5512859572879589</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2250750729630053</v>
+        <v>0.224536582112792</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.02275514568244</v>
+        <v>2.73567041477494</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.343485884493726</v>
+        <v>6.073558287975115</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.966478100258317</v>
+        <v>7.035802826949652</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E19" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>29587</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>9.311611247309255</v>
+        <v>9.309706121472979</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04</v>
+        <v>0.04000706713780919</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.308760436963089</v>
+        <v>9.306737498609358</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.002850810346167172</v>
+        <v>-0.002968622863621564</v>
       </c>
       <c r="T19" t="n">
-        <v>2.210665029558151</v>
+        <v>2.212797322342242</v>
       </c>
       <c r="U19" t="n">
-        <v>2.860697013669233</v>
+        <v>2.863661892181115</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6217923966904144</v>
+        <v>0.6214756752707568</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2434889685249486</v>
+        <v>0.2428012709915862</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6217922518963596</v>
+        <v>0.6214754896346248</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.103254290670026</v>
+        <v>8.068152950041126</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.53183966233996</v>
+        <v>8.626585645738666</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.661649441559721</v>
+        <v>8.999209418999111</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E20" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>29587</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.6449926576902</v>
+        <v>13.64388329191839</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.75</v>
+        <v>6.750007067137809</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64321979319412</v>
+        <v>13.64216021774705</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001772864496073711</v>
+        <v>-0.001723074171337175</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184339577600607</v>
+        <v>1.184359545830784</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565824091086148</v>
+        <v>1.565775025786515</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952695629225345</v>
+        <v>0.8952949438663664</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7905561749523865</v>
+        <v>0.7906112519352558</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952694496692943</v>
+        <v>0.895294816765315</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.74939040335823</v>
+        <v>10.82946316961469</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.87486576053428</v>
+        <v>10.96087564393087</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.00988287745317</v>
+        <v>11.04932817549029</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16726</v>
+        <v>16728</v>
       </c>
       <c r="E21" t="n">
-        <v>16724</v>
+        <v>16729</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>16724</v>
+        <v>16728</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>29587</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.5623732958622</v>
+        <v>130.5620367647059</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5580425066872</v>
+        <v>130.5576817549811</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004330789175016709</v>
+        <v>-0.004355009724738127</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6947667176577218</v>
+        <v>0.6946102734197548</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9295343112014498</v>
+        <v>0.9293648334198327</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840038261800341</v>
+        <v>0.8840314403915163</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7679653145745422</v>
+        <v>0.7680247589479512</v>
       </c>
       <c r="X21" t="n">
-        <v>0.88400371015721</v>
+        <v>0.884031348273202</v>
       </c>
       <c r="Y21" t="n">
-        <v>129.0443697619914</v>
+        <v>129.0464384212973</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2539376886269</v>
+        <v>129.2773117035845</v>
       </c>
       <c r="AA21" t="n">
-        <v>130.9829965712808</v>
+        <v>129.9908997710432</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.103254290670026</v>
+        <v>8.068152950041126</v>
       </c>
       <c r="G2" t="n">
-        <v>8.53183966233996</v>
+        <v>8.626585645738665</v>
       </c>
       <c r="H2" t="n">
-        <v>8.661649441559721</v>
+        <v>8.999209418999111</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.569131346619559</v>
+        <v>5.565623265422556</v>
       </c>
       <c r="G3" t="n">
-        <v>5.608427919258462</v>
+        <v>5.654834491705733</v>
       </c>
       <c r="H3" t="n">
-        <v>5.724809485516529</v>
+        <v>5.807974365283955</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.007039155341398</v>
+        <v>5.358205115503534</v>
       </c>
       <c r="G4" t="n">
-        <v>5.367587981237514</v>
+        <v>5.69640420519395</v>
       </c>
       <c r="H4" t="n">
-        <v>5.655454595862315</v>
+        <v>5.859021088357833</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.438434848754873</v>
+        <v>8.345917465376413</v>
       </c>
       <c r="G5" t="n">
-        <v>8.895893366944019</v>
+        <v>8.686190358598369</v>
       </c>
       <c r="H5" t="n">
-        <v>9.191731702551678</v>
+        <v>9.160301540648623</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.179999999999998</v>
+        <v>3.480652785836915</v>
       </c>
       <c r="G6" t="n">
-        <v>5.101050467616219</v>
+        <v>5.113951750924516</v>
       </c>
       <c r="H6" t="n">
-        <v>6.019564130286609</v>
+        <v>5.989999999999997</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.17524759984845</v>
+        <v>11.13539078890464</v>
       </c>
       <c r="G7" t="n">
-        <v>11.27069128822819</v>
+        <v>11.22413438554022</v>
       </c>
       <c r="H7" t="n">
-        <v>11.37337673674604</v>
+        <v>11.34292911326453</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.678564323056321</v>
+        <v>6.657674060576896</v>
       </c>
       <c r="G8" t="n">
-        <v>6.931711799194855</v>
+        <v>6.825071812778654</v>
       </c>
       <c r="H8" t="n">
-        <v>7.217242220546692</v>
+        <v>7.082679261610253</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.128204029304537</v>
+        <v>6.132102001582714</v>
       </c>
       <c r="G9" t="n">
-        <v>6.267681775369399</v>
+        <v>6.393253524144971</v>
       </c>
       <c r="H9" t="n">
-        <v>6.919171899615667</v>
+        <v>7.008076526170115</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.250625389153639</v>
+        <v>5.248085788160576</v>
       </c>
       <c r="G10" t="n">
-        <v>5.336785310031291</v>
+        <v>5.476852237854344</v>
       </c>
       <c r="H10" t="n">
-        <v>5.515737159530272</v>
+        <v>6.026152632801012</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.74939040335823</v>
+        <v>10.82946316961469</v>
       </c>
       <c r="G11" t="n">
-        <v>10.87486576053428</v>
+        <v>10.96087564393087</v>
       </c>
       <c r="H11" t="n">
-        <v>11.00988287745317</v>
+        <v>11.04932817549029</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.546823147722587</v>
+        <v>1.941752440505575</v>
       </c>
       <c r="G12" t="n">
-        <v>4.321745529723419</v>
+        <v>4.639238425025912</v>
       </c>
       <c r="H12" t="n">
-        <v>5.362413557757263</v>
+        <v>5.561913221531623</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.687953799028925</v>
+        <v>6.677106018858804</v>
       </c>
       <c r="G13" t="n">
-        <v>6.821365492583624</v>
+        <v>6.898328274970959</v>
       </c>
       <c r="H13" t="n">
-        <v>6.91985349825863</v>
+        <v>7.177118638603833</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.646477838841717</v>
+        <v>10.05316612131659</v>
       </c>
       <c r="G14" t="n">
-        <v>10.17123689536868</v>
+        <v>10.61757535143252</v>
       </c>
       <c r="H14" t="n">
-        <v>10.68804209745896</v>
+        <v>10.82906695310399</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.59244677734375</v>
+        <v>3.625250799444155</v>
       </c>
       <c r="G15" t="n">
-        <v>3.982421254138592</v>
+        <v>4.277350254679844</v>
       </c>
       <c r="H15" t="n">
-        <v>4.788508951822917</v>
+        <v>5.399842448770703</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.395843756014687</v>
+        <v>7.401625794574484</v>
       </c>
       <c r="G16" t="n">
-        <v>7.500304072046379</v>
+        <v>7.679008002052965</v>
       </c>
       <c r="H16" t="n">
-        <v>7.728045883433102</v>
+        <v>8.208265250468296</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.02275514568244</v>
+        <v>2.73567041477494</v>
       </c>
       <c r="G17" t="n">
-        <v>6.343485884493726</v>
+        <v>6.073558287975115</v>
       </c>
       <c r="H17" t="n">
-        <v>6.966478100258317</v>
+        <v>7.035802826949652</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.38267940552017</v>
+        <v>5.739806475733984</v>
       </c>
       <c r="G18" t="n">
-        <v>5.754359250207029</v>
+        <v>5.890578660421493</v>
       </c>
       <c r="H18" t="n">
-        <v>5.963655987371727</v>
+        <v>6.006776882729683</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.03155170872823</v>
+        <v>3.025549548893179</v>
       </c>
       <c r="G19" t="n">
-        <v>3.106369782629619</v>
+        <v>3.154997101459266</v>
       </c>
       <c r="H19" t="n">
-        <v>3.256365888181175</v>
+        <v>3.400426072493374</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.718732816790313</v>
+        <v>7.768235728350782</v>
       </c>
       <c r="G20" t="n">
-        <v>7.800820956274931</v>
+        <v>7.849724555494975</v>
       </c>
       <c r="H20" t="n">
-        <v>7.859334492330315</v>
+        <v>7.870797923286012</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>129.0443697619914</v>
+        <v>129.0464384212973</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2539376886269</v>
+        <v>129.2773117035845</v>
       </c>
       <c r="H21" t="n">
-        <v>130.9829965712808</v>
+        <v>129.9908997710432</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,7 +576,7 @@
         <v>16728</v>
       </c>
       <c r="E2" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.289611507822226</v>
+        <v>8.28953207738469</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002682968504889235</v>
+        <v>-0.002762398942423798</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442902565515809</v>
+        <v>1.442897925375381</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869447358776848</v>
+        <v>1.869436724697547</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7154749369496423</v>
+        <v>0.7154856057771266</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4310143260599292</v>
+        <v>0.4310207992259594</v>
       </c>
       <c r="X2" t="n">
-        <v>0.715474729606054</v>
+        <v>0.7154853967254129</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.480652785836915</v>
+        <v>3.481401834414483</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.113951750924516</v>
+        <v>5.112054304876312</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.989999999999997</v>
+        <v>5.98890130591277</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>16728</v>
       </c>
       <c r="E3" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.656514560006923</v>
+        <v>4.656505252341908</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001624876865387453</v>
+        <v>-0.001634184530401365</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315307928141964</v>
+        <v>1.315288894859728</v>
       </c>
       <c r="U3" t="n">
-        <v>1.68201745858833</v>
+        <v>1.681996333576686</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076464196613938</v>
+        <v>0.8076508543212114</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6152222700386845</v>
+        <v>0.6152319350786523</v>
       </c>
       <c r="X3" t="n">
-        <v>0.807646016875286</v>
+        <v>0.8076504498465682</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.025549548893179</v>
+        <v>3.024990850363678</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.154997101459265</v>
+        <v>3.154364287629837</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.400426072493374</v>
+        <v>3.399877291471124</v>
       </c>
     </row>
     <row r="4">
@@ -754,7 +754,7 @@
         <v>16728</v>
       </c>
       <c r="E4" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005017667844522967</v>
+        <v>0.005035335689045934</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.783826718874579</v>
+        <v>6.783753414039783</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0009573258408686993</v>
+        <v>-0.001030630675664039</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505565124322512</v>
+        <v>1.505540647717185</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961556135045129</v>
+        <v>1.961523603728332</v>
       </c>
       <c r="V4" t="n">
-        <v>0.792490771740754</v>
+        <v>0.7925020116072128</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849726746419075</v>
+        <v>0.5849864405221726</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924907226937647</v>
+        <v>0.7925019517367774</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.739806475733984</v>
+        <v>5.739628019855266</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.890578660421492</v>
+        <v>5.890016163169793</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.006776882729683</v>
+        <v>6.005835340980197</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
         <v>16728</v>
       </c>
       <c r="E5" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.206989903832342</v>
+        <v>8.206971081473183</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00399213227478359</v>
+        <v>-0.004010954633943561</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511428355756432</v>
+        <v>1.511390299978722</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024437924321379</v>
+        <v>2.024385853968753</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6083617747266296</v>
+        <v>0.6083787766132223</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2167043461402531</v>
+        <v>0.2167446397505283</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6083614723937214</v>
+        <v>0.6083784717563476</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.768235728350782</v>
+        <v>7.767819581266283</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.849724555494973</v>
+        <v>7.849488139094395</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.870797923286012</v>
+        <v>7.87071594794935</v>
       </c>
     </row>
     <row r="6">
@@ -932,7 +932,7 @@
         <v>16728</v>
       </c>
       <c r="E6" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.22898016058854</v>
+        <v>6.228967490025398</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002315511338768029</v>
+        <v>-0.002328181901908464</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390603067644455</v>
+        <v>1.390585793547991</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812830849267718</v>
+        <v>1.812808318334617</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529078358205874</v>
+        <v>0.2529111090817976</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4947121821280454</v>
+        <v>-0.4946750280263121</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529076606918562</v>
+        <v>0.2529109422998378</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.401625794574484</v>
+        <v>7.400892479457657</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.679008002052967</v>
+        <v>7.677879475878451</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.208265250468296</v>
+        <v>8.207655268300547</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
         <v>16728</v>
       </c>
       <c r="E7" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.584602309271589</v>
+        <v>5.584503931448002</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.00213660153663753</v>
+        <v>-0.002234979360223115</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144828772512772</v>
+        <v>1.144864719266977</v>
       </c>
       <c r="U7" t="n">
-        <v>1.471232909688278</v>
+        <v>1.471259754770709</v>
       </c>
       <c r="V7" t="n">
-        <v>0.516828624566386</v>
+        <v>0.5168403384714216</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03346358669305027</v>
+        <v>0.03342831425421666</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168284325355674</v>
+        <v>0.5168401035508721</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.565623265422556</v>
+        <v>5.565342396730529</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.654834491705734</v>
+        <v>5.654521060847866</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.807974365283955</v>
+        <v>5.807804620250021</v>
       </c>
     </row>
     <row r="8">
@@ -1110,7 +1110,7 @@
         <v>16728</v>
       </c>
       <c r="E8" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.424330758832232</v>
+        <v>7.424353605801323</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002761989852607423</v>
+        <v>-0.002739142883517282</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332028837854563</v>
+        <v>1.332008337898718</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748063139483447</v>
+        <v>1.748040625553561</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946548354831341</v>
+        <v>0.7946566406831161</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5892977398185801</v>
+        <v>0.5893083189128203</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946544970287291</v>
+        <v>0.7946563092647829</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.248085788160576</v>
+        <v>5.247924949498731</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.476852237854344</v>
+        <v>5.475968028800305</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.026152632801012</v>
+        <v>6.02407364454734</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1199,7 @@
         <v>16728</v>
       </c>
       <c r="E9" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306335393744883</v>
+        <v>7.306333303357046</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006612585745817462</v>
+        <v>-0.0006633489624189984</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603908561423259</v>
+        <v>1.603895967623968</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058434723811801</v>
+        <v>2.058417178662376</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320429849416669</v>
+        <v>0.7320450092677659</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639600370103214</v>
+        <v>0.4639691748868432</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320428668037913</v>
+        <v>0.7320448991768748</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.625250799444155</v>
+        <v>3.625860439839243</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.277350254679843</v>
+        <v>4.278176372625959</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.399842448770703</v>
+        <v>5.399219691554674</v>
       </c>
     </row>
     <row r="10">
@@ -1341,13 +1341,13 @@
         <v>2.036171847287712</v>
       </c>
       <c r="V10" t="n">
-        <v>0.41302582749438</v>
+        <v>0.4130258274943795</v>
       </c>
       <c r="W10" t="n">
         <v>-0.174867578899488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130167706722728</v>
+        <v>0.4130167706722724</v>
       </c>
       <c r="Y10" t="n">
         <v>10.05316612131659</v>
@@ -1377,7 +1377,7 @@
         <v>16728</v>
       </c>
       <c r="E11" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246721086825227</v>
+        <v>5.246692852857975</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002217638664969466</v>
+        <v>-0.002245872632221577</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129588942747579</v>
+        <v>1.12957851101451</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437867341091498</v>
+        <v>1.437855439000571</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990452192053002</v>
+        <v>0.399053719380263</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2020789637542968</v>
+        <v>-0.2020590631786252</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990450547203929</v>
+        <v>0.399053551652007</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.358205115503534</v>
+        <v>5.357886051319567</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.69640420519395</v>
+        <v>5.695992925339373</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.859021088357833</v>
+        <v>5.858603730369385</v>
       </c>
     </row>
     <row r="12">
@@ -1466,7 +1466,7 @@
         <v>16728</v>
       </c>
       <c r="E12" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.47572318425237</v>
+        <v>7.475661485874838</v>
       </c>
       <c r="R12" t="n">
-        <v>19.17048551236861</v>
+        <v>19.16297102473474</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002836924547247097</v>
+        <v>-0.002898622924779691</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9380198563000417</v>
+        <v>0.9380087651489365</v>
       </c>
       <c r="U12" t="n">
-        <v>1.252081936689929</v>
+        <v>1.252061143202705</v>
       </c>
       <c r="V12" t="n">
-        <v>0.655900465450965</v>
+        <v>0.6559194718959253</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3118490678195501</v>
+        <v>0.3118719240534461</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6559002481624938</v>
+        <v>0.6559192494676868</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.132102001582714</v>
+        <v>6.130595717685527</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.393253524144971</v>
+        <v>6.391990389620993</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.008076526170115</v>
+        <v>7.007593932917814</v>
       </c>
     </row>
     <row r="13">
@@ -1555,7 +1555,7 @@
         <v>16728</v>
       </c>
       <c r="E13" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.540007067137809</v>
+        <v>1.540014134275618</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.15468233367638</v>
+        <v>9.154720838514669</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.002887907834856712</v>
+        <v>-0.00284940299656881</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195124582257917</v>
+        <v>1.195100852995391</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605419443172033</v>
+        <v>1.605398468800376</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8730208622131944</v>
+        <v>0.8730218430666935</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7460395545986452</v>
+        <v>0.7460461904046273</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8730204705018729</v>
+        <v>0.8730214611695689</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.657674060576896</v>
+        <v>6.655235977286342</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.825071812778654</v>
+        <v>6.824508991244318</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.082679261610253</v>
+        <v>7.082366181992747</v>
       </c>
     </row>
     <row r="14">
@@ -1644,7 +1644,7 @@
         <v>16728</v>
       </c>
       <c r="E14" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197557040110565</v>
+        <v>8.197590011288996</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002652189922911107</v>
+        <v>-0.002619218744480221</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847389362100058</v>
+        <v>1.847346539305811</v>
       </c>
       <c r="U14" t="n">
-        <v>2.39211999020895</v>
+        <v>2.392062309924755</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7527002146533038</v>
+        <v>0.7527073914678535</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5054160188083161</v>
+        <v>0.5054398699535518</v>
       </c>
       <c r="X14" t="n">
-        <v>0.752700000987044</v>
+        <v>0.7527071797381089</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.677106018858804</v>
+        <v>6.672739568307149</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.898328274970959</v>
+        <v>6.896785817596879</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.177118638603833</v>
+        <v>7.176576349506801</v>
       </c>
     </row>
     <row r="15">
@@ -1786,13 +1786,13 @@
         <v>2.008296681711325</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7233191897213604</v>
+        <v>0.7233191897213603</v>
       </c>
       <c r="W15" t="n">
         <v>0.4443702872945663</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232874809221258</v>
+        <v>0.7232874809221257</v>
       </c>
       <c r="Y15" t="n">
         <v>11.13539078890464</v>
@@ -1822,7 +1822,7 @@
         <v>16728</v>
       </c>
       <c r="E16" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.558894428869755</v>
+        <v>7.558761331678022</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.003054040761999935</v>
+        <v>-0.003187137953733546</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085527965752862</v>
+        <v>3.085546282745302</v>
       </c>
       <c r="U16" t="n">
-        <v>9.548501729642295</v>
+        <v>9.548506500301238</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03111206154831916</v>
+        <v>0.03110628386945425</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9377561530199923</v>
+        <v>-0.9377580893187523</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03111197731963677</v>
+        <v>0.03110619207918419</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.345917465376413</v>
+        <v>8.343290994659871</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.686190358598369</v>
+        <v>8.682229385685044</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.160301540648623</v>
+        <v>9.156321927469843</v>
       </c>
     </row>
     <row r="17">
@@ -1911,7 +1911,7 @@
         <v>16728</v>
       </c>
       <c r="E17" t="n">
-        <v>15658</v>
+        <v>15659</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.839432652308895</v>
+        <v>5.839436519377452</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02989059444340318</v>
+        <v>0.02989446151196106</v>
       </c>
       <c r="T17" t="n">
-        <v>1.221189285006129</v>
+        <v>1.221165762122915</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605469541152649</v>
+        <v>1.605446584164187</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6473163755649972</v>
+        <v>0.6473222892176045</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3022680379198771</v>
+        <v>0.3022879918457178</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6470962810358438</v>
+        <v>0.6471017889284969</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.941752440505575</v>
+        <v>1.94182854554709</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.639238425025912</v>
+        <v>4.639042293166492</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.561913221531623</v>
+        <v>5.56160051638692</v>
       </c>
     </row>
     <row r="18">
@@ -2053,7 +2053,7 @@
         <v>1.116156163993724</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2245367709143825</v>
+        <v>0.2245367709143824</v>
       </c>
       <c r="W18" t="n">
         <v>-0.5512859572879589</v>
@@ -2089,7 +2089,7 @@
         <v>16728</v>
       </c>
       <c r="E19" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -2124,40 +2124,40 @@
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04000706713780919</v>
+        <v>0.04001413427561838</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.306737498609358</v>
+        <v>9.306454828453903</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.002968622863621564</v>
+        <v>-0.003251293019074992</v>
       </c>
       <c r="T19" t="n">
-        <v>2.212797322342242</v>
+        <v>2.212946131044788</v>
       </c>
       <c r="U19" t="n">
-        <v>2.863661892181115</v>
+        <v>2.863817507336683</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6214756752707568</v>
+        <v>0.6214788555399875</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2428012709915862</v>
+        <v>0.2427189744049014</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6214754896346248</v>
+        <v>0.6214785642464755</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.068152950041126</v>
+        <v>8.067374809469122</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.626585645738666</v>
+        <v>8.625719006328469</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.999209418999111</v>
+        <v>8.997987109266765</v>
       </c>
     </row>
     <row r="20">
@@ -2178,7 +2178,7 @@
         <v>16728</v>
       </c>
       <c r="E20" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -2213,40 +2213,40 @@
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.750007067137809</v>
+        <v>6.750014134275618</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.64216021774705</v>
+        <v>13.6421221545703</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001723074171337175</v>
+        <v>-0.001761137348092203</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184359545830784</v>
+        <v>1.184345453851946</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565775025786515</v>
+        <v>1.565758615630615</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952949438663664</v>
+        <v>0.8952982704919106</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7906112519352558</v>
+        <v>0.7906156409233759</v>
       </c>
       <c r="X20" t="n">
-        <v>0.895294816765315</v>
+        <v>0.8952981500509307</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.82946316961469</v>
+        <v>10.82935148948024</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.96087564393087</v>
+        <v>10.96040310627743</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.04932817549029</v>
+        <v>11.04884747504925</v>
       </c>
     </row>
     <row r="21">
@@ -2267,7 +2267,7 @@
         <v>16728</v>
       </c>
       <c r="E21" t="n">
-        <v>16729</v>
+        <v>16730</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5576817549811</v>
+        <v>130.5577199447009</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004355009724738127</v>
+        <v>-0.004316820004956386</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6946102734197548</v>
+        <v>0.6946031285002362</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9293648334198327</v>
+        <v>0.929340277811245</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840314403915163</v>
+        <v>0.8840354732130836</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7680247589479512</v>
+        <v>0.7680370172511771</v>
       </c>
       <c r="X21" t="n">
-        <v>0.884031348273202</v>
+        <v>0.8840354015123901</v>
       </c>
       <c r="Y21" t="n">
-        <v>129.0464384212973</v>
+        <v>129.0468525727248</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.2773117035845</v>
+        <v>129.27813548613</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.9908997710432</v>
+        <v>129.9915623222426</v>
       </c>
     </row>
   </sheetData>
@@ -2413,13 +2413,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.068152950041126</v>
+        <v>8.067374809469122</v>
       </c>
       <c r="G2" t="n">
-        <v>8.626585645738665</v>
+        <v>8.62571900632847</v>
       </c>
       <c r="H2" t="n">
-        <v>8.999209418999111</v>
+        <v>8.997987109266765</v>
       </c>
     </row>
     <row r="3">
@@ -2441,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.565623265422556</v>
+        <v>5.565342396730529</v>
       </c>
       <c r="G3" t="n">
-        <v>5.654834491705733</v>
+        <v>5.654521060847865</v>
       </c>
       <c r="H3" t="n">
-        <v>5.807974365283955</v>
+        <v>5.807804620250021</v>
       </c>
     </row>
     <row r="4">
@@ -2469,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.358205115503534</v>
+        <v>5.357886051319567</v>
       </c>
       <c r="G4" t="n">
-        <v>5.69640420519395</v>
+        <v>5.695992925339373</v>
       </c>
       <c r="H4" t="n">
-        <v>5.859021088357833</v>
+        <v>5.858603730369385</v>
       </c>
     </row>
     <row r="5">
@@ -2497,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.345917465376413</v>
+        <v>8.343290994659871</v>
       </c>
       <c r="G5" t="n">
-        <v>8.686190358598369</v>
+        <v>8.682229385685044</v>
       </c>
       <c r="H5" t="n">
-        <v>9.160301540648623</v>
+        <v>9.156321927469843</v>
       </c>
     </row>
     <row r="6">
@@ -2525,13 +2525,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.480652785836915</v>
+        <v>3.481401834414483</v>
       </c>
       <c r="G6" t="n">
-        <v>5.113951750924516</v>
+        <v>5.112054304876312</v>
       </c>
       <c r="H6" t="n">
-        <v>5.989999999999997</v>
+        <v>5.98890130591277</v>
       </c>
     </row>
     <row r="7">
@@ -2581,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.657674060576896</v>
+        <v>6.655235977286342</v>
       </c>
       <c r="G8" t="n">
-        <v>6.825071812778654</v>
+        <v>6.824508991244318</v>
       </c>
       <c r="H8" t="n">
-        <v>7.082679261610253</v>
+        <v>7.082366181992747</v>
       </c>
     </row>
     <row r="9">
@@ -2609,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.132102001582714</v>
+        <v>6.130595717685527</v>
       </c>
       <c r="G9" t="n">
-        <v>6.393253524144971</v>
+        <v>6.391990389620993</v>
       </c>
       <c r="H9" t="n">
-        <v>7.008076526170115</v>
+        <v>7.007593932917814</v>
       </c>
     </row>
     <row r="10">
@@ -2637,13 +2637,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.248085788160576</v>
+        <v>5.247924949498731</v>
       </c>
       <c r="G10" t="n">
-        <v>5.476852237854344</v>
+        <v>5.475968028800305</v>
       </c>
       <c r="H10" t="n">
-        <v>6.026152632801012</v>
+        <v>6.02407364454734</v>
       </c>
     </row>
     <row r="11">
@@ -2665,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.82946316961469</v>
+        <v>10.82935148948024</v>
       </c>
       <c r="G11" t="n">
-        <v>10.96087564393087</v>
+        <v>10.96040310627742</v>
       </c>
       <c r="H11" t="n">
-        <v>11.04932817549029</v>
+        <v>11.04884747504925</v>
       </c>
     </row>
     <row r="12">
@@ -2693,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.941752440505575</v>
+        <v>1.94182854554709</v>
       </c>
       <c r="G12" t="n">
-        <v>4.639238425025912</v>
+        <v>4.639042293166493</v>
       </c>
       <c r="H12" t="n">
-        <v>5.561913221531623</v>
+        <v>5.56160051638692</v>
       </c>
     </row>
     <row r="13">
@@ -2721,13 +2721,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.677106018858804</v>
+        <v>6.672739568307149</v>
       </c>
       <c r="G13" t="n">
-        <v>6.898328274970959</v>
+        <v>6.89678581759688</v>
       </c>
       <c r="H13" t="n">
-        <v>7.177118638603833</v>
+        <v>7.176576349506801</v>
       </c>
     </row>
     <row r="14">
@@ -2777,13 +2777,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.625250799444155</v>
+        <v>3.625860439839243</v>
       </c>
       <c r="G15" t="n">
-        <v>4.277350254679844</v>
+        <v>4.278176372625959</v>
       </c>
       <c r="H15" t="n">
-        <v>5.399842448770703</v>
+        <v>5.399219691554674</v>
       </c>
     </row>
     <row r="16">
@@ -2805,13 +2805,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.401625794574484</v>
+        <v>7.400892479457657</v>
       </c>
       <c r="G16" t="n">
-        <v>7.679008002052965</v>
+        <v>7.677879475878451</v>
       </c>
       <c r="H16" t="n">
-        <v>8.208265250468296</v>
+        <v>8.207655268300547</v>
       </c>
     </row>
     <row r="17">
@@ -2861,13 +2861,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.739806475733984</v>
+        <v>5.739628019855266</v>
       </c>
       <c r="G18" t="n">
-        <v>5.890578660421493</v>
+        <v>5.890016163169793</v>
       </c>
       <c r="H18" t="n">
-        <v>6.006776882729683</v>
+        <v>6.005835340980197</v>
       </c>
     </row>
     <row r="19">
@@ -2889,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.025549548893179</v>
+        <v>3.024990850363678</v>
       </c>
       <c r="G19" t="n">
-        <v>3.154997101459266</v>
+        <v>3.154364287629837</v>
       </c>
       <c r="H19" t="n">
-        <v>3.400426072493374</v>
+        <v>3.399877291471124</v>
       </c>
     </row>
     <row r="20">
@@ -2917,13 +2917,13 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.768235728350782</v>
+        <v>7.767819581266283</v>
       </c>
       <c r="G20" t="n">
-        <v>7.849724555494975</v>
+        <v>7.849488139094395</v>
       </c>
       <c r="H20" t="n">
-        <v>7.870797923286012</v>
+        <v>7.87071594794935</v>
       </c>
     </row>
     <row r="21">
@@ -2945,13 +2945,13 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>129.0464384212973</v>
+        <v>129.0468525727248</v>
       </c>
       <c r="G21" t="n">
-        <v>129.2773117035845</v>
+        <v>129.27813548613</v>
       </c>
       <c r="H21" t="n">
-        <v>129.9908997710432</v>
+        <v>129.9915623222426</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -1199,7 +1199,7 @@
         <v>16728</v>
       </c>
       <c r="E9" t="n">
-        <v>16730</v>
+        <v>16731</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306333303357046</v>
+        <v>7.306341171005612</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006633489624189984</v>
+        <v>-0.0006554813138511792</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603895967623968</v>
+        <v>1.603883161384549</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058417178662376</v>
+        <v>2.058401285626336</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320450092677659</v>
+        <v>0.7320457598105933</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639691748868432</v>
+        <v>0.463977452241329</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320448991768748</v>
+        <v>0.7320456604044026</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.625860439839243</v>
+        <v>3.626470080234331</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.278176372625959</v>
+        <v>4.279099240915697</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.399219691554674</v>
+        <v>5.398596934338646</v>
       </c>
     </row>
     <row r="10">
@@ -2777,13 +2777,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.625860439839243</v>
+        <v>3.626470080234331</v>
       </c>
       <c r="G15" t="n">
-        <v>4.278176372625959</v>
+        <v>4.279099240915697</v>
       </c>
       <c r="H15" t="n">
-        <v>5.399219691554674</v>
+        <v>5.398596934338646</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,7 +576,7 @@
         <v>16728</v>
       </c>
       <c r="E2" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.28953207738469</v>
+        <v>8.289390229534201</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002762398942423798</v>
+        <v>-0.002904246792914488</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442897925375381</v>
+        <v>1.442880081384346</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869436724697547</v>
+        <v>1.869407691302158</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7154856057771266</v>
+        <v>0.7155061523114133</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4310207992259594</v>
+        <v>0.4310384722176237</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7154853967254129</v>
+        <v>0.7155059326100799</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.481401834414483</v>
+        <v>3.482899931569618</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.112054304876312</v>
+        <v>5.10823524910492</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.98890130591277</v>
+        <v>5.979866586513918</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>16728</v>
       </c>
       <c r="E3" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.656505252341908</v>
+        <v>4.656504211709298</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001634184530401365</v>
+        <v>-0.001635225163012137</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315288894859728</v>
+        <v>1.315250573457326</v>
       </c>
       <c r="U3" t="n">
-        <v>1.681996333576686</v>
+        <v>1.681951029925937</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076508543212114</v>
+        <v>0.8076590375817343</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6152319350786523</v>
+        <v>0.6152526618340344</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076504498465682</v>
+        <v>0.8076586429612014</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.024990850363678</v>
+        <v>3.023873453304676</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.154364287629837</v>
+        <v>3.152997758488284</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.399877291471124</v>
+        <v>3.398779729426623</v>
       </c>
     </row>
     <row r="4">
@@ -754,7 +754,7 @@
         <v>16728</v>
       </c>
       <c r="E4" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005035335689045934</v>
+        <v>0.005070671378091871</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.783753414039783</v>
+        <v>6.783629258597462</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.001030630675664039</v>
+        <v>-0.001154786117985536</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505540647717185</v>
+        <v>1.505493358562177</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961523603728332</v>
+        <v>1.961454784327027</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7925020116072128</v>
+        <v>0.7925229706936117</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849864405221726</v>
+        <v>0.5850155612359038</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7925019517367774</v>
+        <v>0.7925228880904571</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.739628019855266</v>
+        <v>5.739271108097828</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.890016163169793</v>
+        <v>5.888941951618122</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.005835340980197</v>
+        <v>6.003952257481228</v>
       </c>
     </row>
     <row r="5">
@@ -843,7 +843,7 @@
         <v>16728</v>
       </c>
       <c r="E5" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.206971081473183</v>
+        <v>8.206963533035884</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004010954633943561</v>
+        <v>-0.00401850307124196</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511390299978722</v>
+        <v>1.511335267346384</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024385853968753</v>
+        <v>2.024300328326943</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6083787766132223</v>
+        <v>0.6084000121502312</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2167446397505283</v>
+        <v>0.2168108198240568</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6083784717563476</v>
+        <v>0.6083997059293106</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.767819581266283</v>
+        <v>7.766987287097288</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.849488139094395</v>
+        <v>7.849038612956447</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.87071594794935</v>
+        <v>7.870551997276024</v>
       </c>
     </row>
     <row r="6">
@@ -932,7 +932,7 @@
         <v>16728</v>
       </c>
       <c r="E6" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.228967490025398</v>
+        <v>6.228992335348225</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002328181901908464</v>
+        <v>-0.002303336579082453</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390585793547991</v>
+        <v>1.39055856079508</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812808318334617</v>
+        <v>1.812752397025077</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529111090817976</v>
+        <v>0.2529169554995033</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4946750280263121</v>
+        <v>-0.4945828143103204</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529109422998378</v>
+        <v>0.2529168126150376</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.400892479457657</v>
+        <v>7.39885169844801</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.677879475878451</v>
+        <v>7.675815002950381</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.207655268300547</v>
+        <v>8.206435303965051</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
         <v>16728</v>
       </c>
       <c r="E7" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.584503931448002</v>
+        <v>5.584310864225876</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002234979360223115</v>
+        <v>-0.00242804658234946</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144864719266977</v>
+        <v>1.144933330626825</v>
       </c>
       <c r="U7" t="n">
-        <v>1.471259754770709</v>
+        <v>1.471310625812613</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168403384714216</v>
+        <v>0.5168641118496714</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03342831425421666</v>
+        <v>0.03336147172876558</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168401035508721</v>
+        <v>0.5168637695293843</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.565342396730529</v>
+        <v>5.564780659346474</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.654521060847866</v>
+        <v>5.653943211816227</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.807804620250021</v>
+        <v>5.807465130182155</v>
       </c>
     </row>
     <row r="8">
@@ -1110,7 +1110,7 @@
         <v>16728</v>
       </c>
       <c r="E8" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.424353605801323</v>
+        <v>7.424418781453157</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002739142883517282</v>
+        <v>-0.002673967231682818</v>
       </c>
       <c r="T8" t="n">
-        <v>1.332008337898718</v>
+        <v>1.331971158255646</v>
       </c>
       <c r="U8" t="n">
-        <v>1.748040625553561</v>
+        <v>1.747999652631679</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946566406831161</v>
+        <v>0.7946578964435457</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5893083189128203</v>
+        <v>0.5893275713726441</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946563092647829</v>
+        <v>0.7946575784789796</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.247924949498731</v>
+        <v>5.247603272175041</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.475968028800305</v>
+        <v>5.47406784253185</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.02407364454734</v>
+        <v>6.019915668039999</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1199,7 @@
         <v>16728</v>
       </c>
       <c r="E9" t="n">
-        <v>16731</v>
+        <v>16732</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306341171005612</v>
+        <v>7.306353756684057</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006554813138511792</v>
+        <v>-0.0006428956354073464</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603883161384549</v>
+        <v>1.603868202329681</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058401285626336</v>
+        <v>2.058385834776972</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320457598105933</v>
+        <v>0.732046012442143</v>
       </c>
       <c r="W9" t="n">
-        <v>0.463977452241329</v>
+        <v>0.4639854992364566</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320456604044026</v>
+        <v>0.7320459243953445</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.626470080234331</v>
+        <v>3.627079720629418</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.279099240915697</v>
+        <v>4.280040356704566</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.398596934338646</v>
+        <v>5.397974177122618</v>
       </c>
     </row>
     <row r="10">
@@ -1341,13 +1341,13 @@
         <v>2.036171847287712</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130258274943795</v>
+        <v>0.41302582749438</v>
       </c>
       <c r="W10" t="n">
         <v>-0.174867578899488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130167706722724</v>
+        <v>0.4130167706722728</v>
       </c>
       <c r="Y10" t="n">
         <v>10.05316612131659</v>
@@ -1377,7 +1377,7 @@
         <v>16728</v>
       </c>
       <c r="E11" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246692852857975</v>
+        <v>5.246704215461793</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002245872632221577</v>
+        <v>-0.00223451002840384</v>
       </c>
       <c r="T11" t="n">
-        <v>1.12957851101451</v>
+        <v>1.12954766517123</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437855439000571</v>
+        <v>1.437822204439617</v>
       </c>
       <c r="V11" t="n">
-        <v>0.399053719380263</v>
+        <v>0.3990566778531078</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2020590631786252</v>
+        <v>-0.2020034950840579</v>
       </c>
       <c r="X11" t="n">
-        <v>0.399053551652007</v>
+        <v>0.3990565195907164</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.357886051319567</v>
+        <v>5.357247922951634</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.695992925339373</v>
+        <v>5.695171412256163</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.858603730369385</v>
+        <v>5.857769014392489</v>
       </c>
     </row>
     <row r="12">
@@ -1466,7 +1466,7 @@
         <v>16728</v>
       </c>
       <c r="E12" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.475661485874838</v>
+        <v>7.475537851943113</v>
       </c>
       <c r="R12" t="n">
-        <v>19.16297102473474</v>
+        <v>19.14794204947012</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002898622924779691</v>
+        <v>-0.003022256856504576</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9380087651489365</v>
+        <v>0.9379863083445722</v>
       </c>
       <c r="U12" t="n">
-        <v>1.252061143202705</v>
+        <v>1.252022973472336</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6559194718959253</v>
+        <v>0.6559559681943433</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3118719240534461</v>
+        <v>0.3119138792932509</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6559192494676868</v>
+        <v>0.655955730739219</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.130595717685527</v>
+        <v>6.127583149891152</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.391990389620993</v>
+        <v>6.388804004704481</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.007593932917814</v>
+        <v>7.006628746413212</v>
       </c>
     </row>
     <row r="13">
@@ -1555,7 +1555,7 @@
         <v>16728</v>
       </c>
       <c r="E13" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.540014134275618</v>
+        <v>1.540028268551237</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.154720838514669</v>
+        <v>9.15481198100581</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.00284940299656881</v>
+        <v>-0.002758260505428873</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195100852995391</v>
+        <v>1.195054835497694</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605398468800376</v>
+        <v>1.605359350018476</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8730218430666935</v>
+        <v>0.8730228827287849</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7460461904046273</v>
+        <v>0.7460585664506342</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8730214611695689</v>
+        <v>0.873022514277888</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.655235977286342</v>
+        <v>6.650359810705235</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.824508991244318</v>
+        <v>6.823513443678026</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.082366181992747</v>
+        <v>7.081740022757733</v>
       </c>
     </row>
     <row r="14">
@@ -1644,7 +1644,7 @@
         <v>16728</v>
       </c>
       <c r="E14" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.197590011288996</v>
+        <v>8.19767114243662</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002619218744480221</v>
+        <v>-0.002538087596856157</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847346539305811</v>
+        <v>1.84727207882266</v>
       </c>
       <c r="U14" t="n">
-        <v>2.392062309924755</v>
+        <v>2.39195895359084</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7527073914678535</v>
+        <v>0.7527183185372361</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5054398699535518</v>
+        <v>0.5054826069821157</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7527071797381089</v>
+        <v>0.7527181069299775</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.672739568307149</v>
+        <v>6.664006667203842</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.896785817596879</v>
+        <v>6.893805417579436</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.176576349506801</v>
+        <v>7.175491771312739</v>
       </c>
     </row>
     <row r="15">
@@ -1786,13 +1786,13 @@
         <v>2.008296681711325</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7233191897213603</v>
+        <v>0.7233191897213604</v>
       </c>
       <c r="W15" t="n">
         <v>0.4443702872945663</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232874809221257</v>
+        <v>0.7232874809221258</v>
       </c>
       <c r="Y15" t="n">
         <v>11.13539078890464</v>
@@ -1822,7 +1822,7 @@
         <v>16728</v>
       </c>
       <c r="E16" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.558761331678022</v>
+        <v>7.558487486615132</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.003187137953733546</v>
+        <v>-0.003460983016623041</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085546282745302</v>
+        <v>3.085582520293729</v>
       </c>
       <c r="U16" t="n">
-        <v>9.548506500301238</v>
+        <v>9.548514665212505</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03110628386945425</v>
+        <v>0.03109512257328192</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9377580893187523</v>
+        <v>-0.937761403267299</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03110619207918419</v>
+        <v>0.0310950141499291</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.343290994659871</v>
+        <v>8.338692035484526</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.682229385685044</v>
+        <v>8.675262544113329</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.156321927469843</v>
+        <v>9.148578269258895</v>
       </c>
     </row>
     <row r="17">
@@ -1911,7 +1911,7 @@
         <v>16728</v>
       </c>
       <c r="E17" t="n">
-        <v>15659</v>
+        <v>15661</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.839436519377452</v>
+        <v>5.839488067655375</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02989446151196106</v>
+        <v>0.02994600978988345</v>
       </c>
       <c r="T17" t="n">
-        <v>1.221165762122915</v>
+        <v>1.221136968213798</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605446584164187</v>
+        <v>1.605414274315746</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6473222892176045</v>
+        <v>0.6473227981534022</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3022879918457178</v>
+        <v>0.3023160746765279</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6471017889284969</v>
+        <v>0.6471008491280938</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.94182854554709</v>
+        <v>1.94198075563012</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.639042293166492</v>
+        <v>4.638815581588007</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.56160051638692</v>
+        <v>5.560975106097513</v>
       </c>
     </row>
     <row r="18">
@@ -2000,7 +2000,7 @@
         <v>16728</v>
       </c>
       <c r="E18" t="n">
-        <v>16729</v>
+        <v>16732</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.534897272136416</v>
+        <v>6.534736801230225</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.003222287882713035</v>
+        <v>-0.003382758788904523</v>
       </c>
       <c r="T18" t="n">
-        <v>0.802448652821073</v>
+        <v>0.8025286533388163</v>
       </c>
       <c r="U18" t="n">
-        <v>1.116156163993724</v>
+        <v>1.116143378903552</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2245367709143824</v>
+        <v>0.2245971142448467</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5512859572879589</v>
+        <v>-0.5512504188608207</v>
       </c>
       <c r="X18" t="n">
-        <v>0.224536582112792</v>
+        <v>0.2245968919803644</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.73567041477494</v>
+        <v>2.736784123280819</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.073558287975115</v>
+        <v>6.072153222070804</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.035802826949652</v>
+        <v>7.035375502430478</v>
       </c>
     </row>
     <row r="19">
@@ -2142,13 +2142,13 @@
         <v>2.863817507336683</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6214788555399875</v>
+        <v>0.6214788555399877</v>
       </c>
       <c r="W19" t="n">
         <v>0.2427189744049014</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6214785642464755</v>
+        <v>0.6214785642464757</v>
       </c>
       <c r="Y19" t="n">
         <v>8.067374809469122</v>
@@ -2178,7 +2178,7 @@
         <v>16728</v>
       </c>
       <c r="E20" t="n">
-        <v>16730</v>
+        <v>16732</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -2213,40 +2213,40 @@
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.750014134275618</v>
+        <v>6.750028268551237</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.6421221545703</v>
+        <v>13.6420677657426</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001761137348092203</v>
+        <v>-0.001815526175787913</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184345453851946</v>
+        <v>1.184314864238383</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565758615630615</v>
+        <v>1.565723726421012</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8952982704919106</v>
+        <v>0.895304341468885</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7906156409233759</v>
+        <v>0.790624972085061</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8952981500509307</v>
+        <v>0.8953042269761462</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.82935148948024</v>
+        <v>10.8287098556577</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.96040310627743</v>
+        <v>10.95942382286652</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.04884747504925</v>
+        <v>11.04788607416717</v>
       </c>
     </row>
     <row r="21">
@@ -2320,13 +2320,13 @@
         <v>0.929340277811245</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840354732130836</v>
+        <v>0.8840354732130835</v>
       </c>
       <c r="W21" t="n">
         <v>0.7680370172511771</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8840354015123901</v>
+        <v>0.88403540151239</v>
       </c>
       <c r="Y21" t="n">
         <v>129.0468525727248</v>
@@ -2441,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.565342396730529</v>
+        <v>5.564780659346474</v>
       </c>
       <c r="G3" t="n">
-        <v>5.654521060847865</v>
+        <v>5.653943211816226</v>
       </c>
       <c r="H3" t="n">
-        <v>5.807804620250021</v>
+        <v>5.807465130182155</v>
       </c>
     </row>
     <row r="4">
@@ -2469,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.357886051319567</v>
+        <v>5.357247922951634</v>
       </c>
       <c r="G4" t="n">
-        <v>5.695992925339373</v>
+        <v>5.695171412256163</v>
       </c>
       <c r="H4" t="n">
-        <v>5.858603730369385</v>
+        <v>5.857769014392489</v>
       </c>
     </row>
     <row r="5">
@@ -2497,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.343290994659871</v>
+        <v>8.338692035484526</v>
       </c>
       <c r="G5" t="n">
-        <v>8.682229385685044</v>
+        <v>8.675262544113329</v>
       </c>
       <c r="H5" t="n">
-        <v>9.156321927469843</v>
+        <v>9.148578269258895</v>
       </c>
     </row>
     <row r="6">
@@ -2525,13 +2525,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.481401834414483</v>
+        <v>3.482899931569618</v>
       </c>
       <c r="G6" t="n">
-        <v>5.112054304876312</v>
+        <v>5.108235249104921</v>
       </c>
       <c r="H6" t="n">
-        <v>5.98890130591277</v>
+        <v>5.979866586513918</v>
       </c>
     </row>
     <row r="7">
@@ -2581,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.655235977286342</v>
+        <v>6.650359810705235</v>
       </c>
       <c r="G8" t="n">
-        <v>6.824508991244318</v>
+        <v>6.823513443678026</v>
       </c>
       <c r="H8" t="n">
-        <v>7.082366181992747</v>
+        <v>7.081740022757733</v>
       </c>
     </row>
     <row r="9">
@@ -2609,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.130595717685527</v>
+        <v>6.127583149891152</v>
       </c>
       <c r="G9" t="n">
-        <v>6.391990389620993</v>
+        <v>6.388804004704481</v>
       </c>
       <c r="H9" t="n">
-        <v>7.007593932917814</v>
+        <v>7.006628746413212</v>
       </c>
     </row>
     <row r="10">
@@ -2637,13 +2637,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.247924949498731</v>
+        <v>5.247603272175041</v>
       </c>
       <c r="G10" t="n">
-        <v>5.475968028800305</v>
+        <v>5.474067842531851</v>
       </c>
       <c r="H10" t="n">
-        <v>6.02407364454734</v>
+        <v>6.019915668039999</v>
       </c>
     </row>
     <row r="11">
@@ -2665,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.82935148948024</v>
+        <v>10.8287098556577</v>
       </c>
       <c r="G11" t="n">
-        <v>10.96040310627742</v>
+        <v>10.95942382286652</v>
       </c>
       <c r="H11" t="n">
-        <v>11.04884747504925</v>
+        <v>11.04788607416717</v>
       </c>
     </row>
     <row r="12">
@@ -2693,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.94182854554709</v>
+        <v>1.94198075563012</v>
       </c>
       <c r="G12" t="n">
-        <v>4.639042293166493</v>
+        <v>4.638815581588007</v>
       </c>
       <c r="H12" t="n">
-        <v>5.56160051638692</v>
+        <v>5.560975106097513</v>
       </c>
     </row>
     <row r="13">
@@ -2721,13 +2721,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.672739568307149</v>
+        <v>6.664006667203842</v>
       </c>
       <c r="G13" t="n">
-        <v>6.89678581759688</v>
+        <v>6.893805417579436</v>
       </c>
       <c r="H13" t="n">
-        <v>7.176576349506801</v>
+        <v>7.175491771312739</v>
       </c>
     </row>
     <row r="14">
@@ -2777,13 +2777,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.626470080234331</v>
+        <v>3.627079720629418</v>
       </c>
       <c r="G15" t="n">
-        <v>4.279099240915697</v>
+        <v>4.280040356704566</v>
       </c>
       <c r="H15" t="n">
-        <v>5.398596934338646</v>
+        <v>5.397974177122618</v>
       </c>
     </row>
     <row r="16">
@@ -2805,13 +2805,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.400892479457657</v>
+        <v>7.39885169844801</v>
       </c>
       <c r="G16" t="n">
-        <v>7.677879475878451</v>
+        <v>7.675815002950381</v>
       </c>
       <c r="H16" t="n">
-        <v>8.207655268300547</v>
+        <v>8.206435303965051</v>
       </c>
     </row>
     <row r="17">
@@ -2833,13 +2833,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.73567041477494</v>
+        <v>2.736784123280819</v>
       </c>
       <c r="G17" t="n">
-        <v>6.073558287975115</v>
+        <v>6.072153222070804</v>
       </c>
       <c r="H17" t="n">
-        <v>7.035802826949652</v>
+        <v>7.035375502430478</v>
       </c>
     </row>
     <row r="18">
@@ -2861,13 +2861,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.739628019855266</v>
+        <v>5.739271108097828</v>
       </c>
       <c r="G18" t="n">
-        <v>5.890016163169793</v>
+        <v>5.888941951618122</v>
       </c>
       <c r="H18" t="n">
-        <v>6.005835340980197</v>
+        <v>6.003952257481228</v>
       </c>
     </row>
     <row r="19">
@@ -2889,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.024990850363678</v>
+        <v>3.023873453304676</v>
       </c>
       <c r="G19" t="n">
-        <v>3.154364287629837</v>
+        <v>3.152997758488285</v>
       </c>
       <c r="H19" t="n">
-        <v>3.399877291471124</v>
+        <v>3.398779729426623</v>
       </c>
     </row>
     <row r="20">
@@ -2917,13 +2917,13 @@
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.767819581266283</v>
+        <v>7.766987287097288</v>
       </c>
       <c r="G20" t="n">
-        <v>7.849488139094395</v>
+        <v>7.849038612956447</v>
       </c>
       <c r="H20" t="n">
-        <v>7.87071594794935</v>
+        <v>7.870551997276024</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E2" t="n">
         <v>16732</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>29587</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M2" t="n">
         <v>0.4299999999999926</v>
       </c>
       <c r="N2" t="n">
-        <v>8.292294476327115</v>
+        <v>8.291335285680132</v>
       </c>
       <c r="O2" t="n">
         <v>14.02</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.289390229534201</v>
+        <v>8.288742581843321</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002904246792914488</v>
+        <v>-0.002592703836812156</v>
       </c>
       <c r="T2" t="n">
-        <v>1.442880081384346</v>
+        <v>1.443007949001859</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869407691302158</v>
+        <v>1.869505446230526</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7155061523114133</v>
+        <v>0.7155582480520066</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4310384722176237</v>
+        <v>0.4311997306897408</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7155059326100799</v>
+        <v>0.7155580375227273</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.482899931569618</v>
+        <v>2.802216621253404</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.10823524910492</v>
+        <v>5.979715271957803</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.979866586513918</v>
+        <v>8.819999999999988</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E3" t="n">
         <v>16732</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>29587</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.658139436872309</v>
+        <v>4.657415371742768</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.656504211709298</v>
+        <v>4.655804772908746</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001635225163012137</v>
+        <v>-0.001610598834022498</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315250573457326</v>
+        <v>1.315304711992028</v>
       </c>
       <c r="U3" t="n">
-        <v>1.681951029925937</v>
+        <v>1.68191812660116</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076590375817343</v>
+        <v>0.8076805755755192</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6152526618340344</v>
+        <v>0.6152905782275344</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076586429612014</v>
+        <v>0.8076801781011492</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.023873453304676</v>
+        <v>3.0921359375</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.152997758488284</v>
+        <v>3.450161998233005</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.398779729426623</v>
+        <v>3.9501</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E4" t="n">
         <v>16732</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>29587</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.784784044715447</v>
+        <v>6.783677982309348</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005070671378091871</v>
+        <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.783629258597462</v>
+        <v>6.782826752003447</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.001154786117985536</v>
+        <v>-0.0008512303059004796</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505493358562177</v>
+        <v>1.50581238994113</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961454784327027</v>
+        <v>1.961824277759624</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7925229706936117</v>
+        <v>0.7924918278924765</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5850155612359038</v>
+        <v>0.5849892537890696</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7925228880904571</v>
+        <v>0.7924917895016239</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.739271108097828</v>
+        <v>5.96225732421875</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.888941951618122</v>
+        <v>6.203427832575324</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.003952257481228</v>
+        <v>6.35551724137931</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E5" t="n">
         <v>16732</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>29587</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.210982036107126</v>
+        <v>8.210386235955056</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.206963533035884</v>
+        <v>8.206419211690175</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00401850307124196</v>
+        <v>-0.003967024264881666</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511335267346384</v>
+        <v>1.511429714401519</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024300328326943</v>
+        <v>2.024263595566108</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6084000121502312</v>
+        <v>0.608448962815576</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2168108198240568</v>
+        <v>0.216874840298691</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6083997059293106</v>
+        <v>0.6084486638611089</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.766987287097288</v>
+        <v>7.911622179143056</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.849038612956447</v>
+        <v>8.03884219874414</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.870551997276024</v>
+        <v>8.552275205839161</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E6" t="n">
         <v>16732</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>29587</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.231295671927308</v>
+        <v>6.231152223284724</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.228992335348225</v>
+        <v>6.228848404255319</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002303336579082453</v>
+        <v>-0.002303819029404768</v>
       </c>
       <c r="T6" t="n">
-        <v>1.39055856079508</v>
+        <v>1.390607429051103</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812752397025077</v>
+        <v>1.812735160506897</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2529169554995033</v>
+        <v>0.2528576897590764</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4945828143103204</v>
+        <v>-0.4948438334879259</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2529168126150376</v>
+        <v>0.2528575054080888</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.39885169844801</v>
+        <v>7.580549624016991</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.675815002950381</v>
+        <v>8.455777314954663</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.206435303965051</v>
+        <v>9.681999999999983</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E7" t="n">
         <v>16732</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>29587</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.586738910808226</v>
+        <v>5.586148756873057</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.584310864225876</v>
+        <v>5.584103155675217</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.00242804658234946</v>
+        <v>-0.002045601197840096</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144933330626825</v>
+        <v>1.14526439184304</v>
       </c>
       <c r="U7" t="n">
-        <v>1.471310625812613</v>
+        <v>1.47164474026035</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5168641118496714</v>
+        <v>0.5167326043552513</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03336147172876558</v>
+        <v>0.03332059282578914</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5168637695293843</v>
+        <v>0.5167324430551288</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.564780659346474</v>
+        <v>5.625377054586039</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.653943211816227</v>
+        <v>5.935152041926347</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.807465130182155</v>
+        <v>6.421768009043904</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E8" t="n">
         <v>16732</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>29587</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.427092748684839</v>
+        <v>7.426457685871385</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.424418781453157</v>
+        <v>7.423682240616782</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002673967231682818</v>
+        <v>-0.002775445254601867</v>
       </c>
       <c r="T8" t="n">
-        <v>1.331971158255646</v>
+        <v>1.331813047323601</v>
       </c>
       <c r="U8" t="n">
-        <v>1.747999652631679</v>
+        <v>1.747873741285568</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946578964435457</v>
+        <v>0.7946996369222515</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5893275713726441</v>
+        <v>0.589381825488281</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946575784789796</v>
+        <v>0.7946992928726123</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.247603272175041</v>
+        <v>5.380506043218166</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.47406784253185</v>
+        <v>6.191862108546031</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.019915668039999</v>
+        <v>7.402885444694261</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E9" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.306996652319465</v>
+        <v>7.306386265837915</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.306353756684057</v>
+        <v>7.30575016438886</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006428956354073464</v>
+        <v>-0.0006361014490556111</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603868202329681</v>
+        <v>1.603874032054569</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058385834776972</v>
+        <v>2.058319501498587</v>
       </c>
       <c r="V9" t="n">
-        <v>0.732046012442143</v>
+        <v>0.7320600033169917</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639854992364566</v>
+        <v>0.4639978433986774</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320459243953445</v>
+        <v>0.7320598923571815</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.627079720629418</v>
+        <v>4.05553418756362</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.280040356704566</v>
+        <v>5.575234422074141</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.397974177122618</v>
+        <v>7.431547561253176</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.314300668722758</v>
+        <v>9.313863410993497</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03000767072902708</v>
+        <v>-0.03044492845829038</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492940917044298</v>
+        <v>1.492859151728104</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036171847287712</v>
+        <v>2.036177836610706</v>
       </c>
       <c r="V10" t="n">
-        <v>0.41302582749438</v>
+        <v>0.4130701730088045</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.174867578899488</v>
+        <v>-0.1748744905673443</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130167706722728</v>
+        <v>0.4130607805427868</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.05316612131659</v>
+        <v>10.89777800569748</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.61757535143252</v>
+        <v>12.25610011576072</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.82906695310399</v>
+        <v>12.64009223437747</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E11" t="n">
         <v>16732</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>29587</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.248938725490197</v>
+        <v>5.248694387999044</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246704215461793</v>
+        <v>5.246532220352263</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.00223451002840384</v>
+        <v>-0.002162167646780564</v>
       </c>
       <c r="T11" t="n">
-        <v>1.12954766517123</v>
+        <v>1.129629411493649</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437822204439617</v>
+        <v>1.437831437483815</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990566778531078</v>
+        <v>0.3990208181253739</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2020034950840579</v>
+        <v>-0.2021032166180847</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990565195907164</v>
+        <v>0.3990206653092264</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.357247922951634</v>
+        <v>6.07485633837195</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.695171412256163</v>
+        <v>6.777758465023689</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.857769014392489</v>
+        <v>7.118984037943154</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E12" t="n">
         <v>16732</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>29587</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.478560108799617</v>
+        <v>7.478032422902222</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.475537851943113</v>
+        <v>7.47527626916772</v>
       </c>
       <c r="R12" t="n">
-        <v>19.14794204947012</v>
+        <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.003022256856504576</v>
+        <v>-0.002756153734503639</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9379863083445722</v>
+        <v>0.9380346545717048</v>
       </c>
       <c r="U12" t="n">
-        <v>1.252022973472336</v>
+        <v>1.252067329186231</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6559559681943433</v>
+        <v>0.6559882471125608</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3119138792932509</v>
+        <v>0.3120530197310964</v>
       </c>
       <c r="X12" t="n">
-        <v>0.655955730739219</v>
+        <v>0.655988030087689</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.127583149891152</v>
+        <v>6.127243506493507</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.388804004704481</v>
+        <v>7.132951257007671</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.006628746413212</v>
+        <v>7.881776318185681</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E13" t="n">
         <v>16732</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>29587</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.157570241511239</v>
+        <v>9.156925800860627</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>1.540028268551237</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.15481198100581</v>
+        <v>9.154000791895768</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.002758260505428873</v>
+        <v>-0.002925008964857722</v>
       </c>
       <c r="T13" t="n">
-        <v>1.195054835497694</v>
+        <v>1.194934344040643</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605359350018476</v>
+        <v>1.605213337816935</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8730228827287849</v>
+        <v>0.8730471413330211</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7460585664506342</v>
+        <v>0.7460875336566795</v>
       </c>
       <c r="X13" t="n">
-        <v>0.873022514277888</v>
+        <v>0.8730467373360059</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.650359810705235</v>
+        <v>6.537649127933112</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.823513443678026</v>
+        <v>6.663780250459621</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.081740022757733</v>
+        <v>6.790570641282565</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E14" t="n">
         <v>16732</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>29587</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.200209230033478</v>
+        <v>8.19950409395171</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.19767114243662</v>
+        <v>8.196819223358718</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002538087596856157</v>
+        <v>-0.002684870592989774</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84727207882266</v>
+        <v>1.847007943200902</v>
       </c>
       <c r="U14" t="n">
-        <v>2.39195895359084</v>
+        <v>2.39158885500926</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7527183185372361</v>
+        <v>0.7528001157403102</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5054826069821157</v>
+        <v>0.5056063426747338</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7527181069299775</v>
+        <v>0.7527998984982061</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.664006667203842</v>
+        <v>6.83897051051686</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.893805417579436</v>
+        <v>6.97698810807942</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.175491771312739</v>
+        <v>7.03504216808049</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.66779536809093</v>
+        <v>12.6674762933248</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01530704591027783</v>
+        <v>-0.01562612067640584</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354614708982712</v>
+        <v>1.354694971768305</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008296681711325</v>
+        <v>2.008340625086536</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7233191897213604</v>
+        <v>0.723350275741261</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4443702872945663</v>
+        <v>0.4443459716520703</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7232874809221258</v>
+        <v>0.7233162061606067</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.13539078890464</v>
+        <v>11.0834357666061</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.22413438554022</v>
+        <v>11.14707811754546</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.34292911326453</v>
+        <v>11.21034682178635</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E16" t="n">
         <v>16732</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>29587</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>7.561948469631756</v>
+        <v>7.561816818073154</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.558487486615132</v>
+        <v>7.558903578685837</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.003460983016623041</v>
+        <v>-0.002913239387316054</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085582520293729</v>
+        <v>3.085411085809261</v>
       </c>
       <c r="U16" t="n">
-        <v>9.548514665212505</v>
+        <v>9.547461112705511</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03109512257328192</v>
+        <v>0.03109783621703531</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.937761403267299</v>
+        <v>-0.9377940711651171</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0310950141499291</v>
+        <v>0.0310977596088855</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.338692035484526</v>
+        <v>8.668731456415809</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.675262544113329</v>
+        <v>9.117656485788411</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.148578269258895</v>
+        <v>11.11734862385321</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E17" t="n">
         <v>15661</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>15657</v>
+        <v>15661</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>30317</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>5.809542057865491</v>
+        <v>5.809095683545112</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.839488067655375</v>
+        <v>5.839041075832428</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02994600978988345</v>
+        <v>0.0299453922873161</v>
       </c>
       <c r="T17" t="n">
-        <v>1.221136968213798</v>
+        <v>1.221086914237293</v>
       </c>
       <c r="U17" t="n">
-        <v>1.605414274315746</v>
+        <v>1.605282728237122</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6473227981534022</v>
+        <v>0.6473811981841554</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3023160746765279</v>
+        <v>0.3024072083157389</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6471008491280938</v>
+        <v>0.6471603588394439</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.94198075563012</v>
+        <v>2.431824838929816</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.638815581588007</v>
+        <v>5.416847213017981</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.560975106097513</v>
+        <v>7.386010551864832</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E18" t="n">
         <v>16732</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>29587</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.538119560019129</v>
+        <v>6.537770977767153</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.534736801230225</v>
+        <v>6.5346557129751</v>
       </c>
       <c r="R18" t="n">
         <v>18.492</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.003382758788904523</v>
+        <v>-0.003115264792051784</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8025286533388163</v>
+        <v>0.802805041966657</v>
       </c>
       <c r="U18" t="n">
-        <v>1.116143378903552</v>
+        <v>1.116470756845125</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2245971142448467</v>
+        <v>0.2243160313517537</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5512504188608207</v>
+        <v>-0.5515217163148733</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2245968919803644</v>
+        <v>0.2243158796170157</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.736784123280819</v>
+        <v>3.527161089166483</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.072153222070804</v>
+        <v>6.636451359603929</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.035375502430478</v>
+        <v>7.489055916789315</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E19" t="n">
         <v>16730</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>16728</v>
+        <v>16730</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>29587</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>9.309706121472979</v>
+        <v>9.308781918708906</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04001413427561838</v>
+        <v>0.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.306454828453903</v>
+        <v>9.30586167226625</v>
       </c>
       <c r="R19" t="n">
         <v>24.588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.003251293019074992</v>
+        <v>-0.002920246442658134</v>
       </c>
       <c r="T19" t="n">
-        <v>2.212946131044788</v>
+        <v>2.213682887230797</v>
       </c>
       <c r="U19" t="n">
-        <v>2.863817507336683</v>
+        <v>2.86481159989527</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6214788555399877</v>
+        <v>0.6213506470464201</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2427189744049014</v>
+        <v>0.242602365449945</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6214785642464757</v>
+        <v>0.6213504949239903</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.067374809469122</v>
+        <v>8.491721696011592</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.625719006328469</v>
+        <v>8.926273864833442</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.997987109266765</v>
+        <v>9.395440324003362</v>
       </c>
     </row>
     <row r="20">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E20" t="n">
         <v>16732</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>29587</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="M20" t="n">
         <v>6.75</v>
       </c>
       <c r="N20" t="n">
-        <v>13.64388329191839</v>
+        <v>13.64282152206615</v>
       </c>
       <c r="O20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="P20" t="n">
-        <v>6.750028268551237</v>
+        <v>6.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.6420677657426</v>
+        <v>13.64114255933835</v>
       </c>
       <c r="R20" t="n">
         <v>22.08804784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.001815526175787913</v>
+        <v>-0.001678962727795053</v>
       </c>
       <c r="T20" t="n">
-        <v>1.184314864238383</v>
+        <v>1.184381697773823</v>
       </c>
       <c r="U20" t="n">
-        <v>1.565723726421012</v>
+        <v>1.565737989006954</v>
       </c>
       <c r="V20" t="n">
-        <v>0.895304341468885</v>
+        <v>0.8953156764601977</v>
       </c>
       <c r="W20" t="n">
-        <v>0.790624972085061</v>
+        <v>0.7906554591399361</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8953042269761462</v>
+        <v>0.8953155394629034</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.8287098556577</v>
+        <v>11.01873699939071</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.95942382286652</v>
+        <v>11.20039940844115</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.04788607416717</v>
+        <v>11.49267306155743</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16728</v>
+        <v>16732</v>
       </c>
       <c r="E21" t="n">
         <v>16730</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>16728</v>
+        <v>16730</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>29587</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.5620367647059</v>
+        <v>130.5619749551703</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.5577199447009</v>
+        <v>130.5576430985015</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.004316820004956386</v>
+        <v>-0.00433185666891084</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6946031285002362</v>
+        <v>0.6946958258845942</v>
       </c>
       <c r="U21" t="n">
-        <v>0.929340277811245</v>
+        <v>0.9294166698528092</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8840354732130835</v>
+        <v>0.8840078820994576</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7680370172511771</v>
+        <v>0.7679731493819753</v>
       </c>
       <c r="X21" t="n">
-        <v>0.88403540151239</v>
+        <v>0.8840077644259072</v>
       </c>
       <c r="Y21" t="n">
-        <v>129.0468525727248</v>
+        <v>129.2089186929838</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.27813548613</v>
+        <v>130.3877616401733</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.9915623222426</v>
+        <v>131.2373431079656</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.067374809469122</v>
+        <v>8.491721696011592</v>
       </c>
       <c r="G2" t="n">
-        <v>8.62571900632847</v>
+        <v>8.926273864833442</v>
       </c>
       <c r="H2" t="n">
-        <v>8.997987109266765</v>
+        <v>9.395440324003362</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.564780659346474</v>
+        <v>5.625377054586039</v>
       </c>
       <c r="G3" t="n">
-        <v>5.653943211816226</v>
+        <v>5.935152041926346</v>
       </c>
       <c r="H3" t="n">
-        <v>5.807465130182155</v>
+        <v>6.421768009043904</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>5.357247922951634</v>
+        <v>6.07485633837195</v>
       </c>
       <c r="G4" t="n">
-        <v>5.695171412256163</v>
+        <v>6.777758465023689</v>
       </c>
       <c r="H4" t="n">
-        <v>5.857769014392489</v>
+        <v>7.118984037943154</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8.338692035484526</v>
+        <v>8.668731456415809</v>
       </c>
       <c r="G5" t="n">
-        <v>8.675262544113329</v>
+        <v>9.117656485788411</v>
       </c>
       <c r="H5" t="n">
-        <v>9.148578269258895</v>
+        <v>11.11734862385321</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.482899931569618</v>
+        <v>2.802216621253404</v>
       </c>
       <c r="G6" t="n">
-        <v>5.108235249104921</v>
+        <v>5.979715271957803</v>
       </c>
       <c r="H6" t="n">
-        <v>5.979866586513918</v>
+        <v>8.819999999999988</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.13539078890464</v>
+        <v>11.0834357666061</v>
       </c>
       <c r="G7" t="n">
-        <v>11.22413438554022</v>
+        <v>11.14707811754546</v>
       </c>
       <c r="H7" t="n">
-        <v>11.34292911326453</v>
+        <v>11.21034682178635</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.650359810705235</v>
+        <v>6.537649127933112</v>
       </c>
       <c r="G8" t="n">
-        <v>6.823513443678026</v>
+        <v>6.663780250459621</v>
       </c>
       <c r="H8" t="n">
-        <v>7.081740022757733</v>
+        <v>6.790570641282565</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>6.127583149891152</v>
+        <v>6.127243506493507</v>
       </c>
       <c r="G9" t="n">
-        <v>6.388804004704481</v>
+        <v>7.132951257007669</v>
       </c>
       <c r="H9" t="n">
-        <v>7.006628746413212</v>
+        <v>7.881776318185681</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.247603272175041</v>
+        <v>5.380506043218166</v>
       </c>
       <c r="G10" t="n">
-        <v>5.474067842531851</v>
+        <v>6.191862108546031</v>
       </c>
       <c r="H10" t="n">
-        <v>6.019915668039999</v>
+        <v>7.402885444694261</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.8287098556577</v>
+        <v>11.01873699939071</v>
       </c>
       <c r="G11" t="n">
-        <v>10.95942382286652</v>
+        <v>11.20039940844115</v>
       </c>
       <c r="H11" t="n">
-        <v>11.04788607416717</v>
+        <v>11.49267306155743</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.94198075563012</v>
+        <v>2.431824838929816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.638815581588007</v>
+        <v>5.41684721301798</v>
       </c>
       <c r="H12" t="n">
-        <v>5.560975106097513</v>
+        <v>7.386010551864832</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6.664006667203842</v>
+        <v>6.83897051051686</v>
       </c>
       <c r="G13" t="n">
-        <v>6.893805417579436</v>
+        <v>6.97698810807942</v>
       </c>
       <c r="H13" t="n">
-        <v>7.175491771312739</v>
+        <v>7.03504216808049</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10.05316612131659</v>
+        <v>10.89777800569748</v>
       </c>
       <c r="G14" t="n">
-        <v>10.61757535143252</v>
+        <v>12.25610011576072</v>
       </c>
       <c r="H14" t="n">
-        <v>10.82906695310399</v>
+        <v>12.64009223437747</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>3.627079720629418</v>
+        <v>4.05553418756362</v>
       </c>
       <c r="G15" t="n">
-        <v>4.280040356704566</v>
+        <v>5.575234422074141</v>
       </c>
       <c r="H15" t="n">
-        <v>5.397974177122618</v>
+        <v>7.431547561253176</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>7.39885169844801</v>
+        <v>7.580549624016991</v>
       </c>
       <c r="G16" t="n">
-        <v>7.675815002950381</v>
+        <v>8.455777314954663</v>
       </c>
       <c r="H16" t="n">
-        <v>8.206435303965051</v>
+        <v>9.681999999999983</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.736784123280819</v>
+        <v>3.527161089166483</v>
       </c>
       <c r="G17" t="n">
-        <v>6.072153222070804</v>
+        <v>6.636451359603929</v>
       </c>
       <c r="H17" t="n">
-        <v>7.035375502430478</v>
+        <v>7.489055916789315</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>5.739271108097828</v>
+        <v>5.96225732421875</v>
       </c>
       <c r="G18" t="n">
-        <v>5.888941951618122</v>
+        <v>6.203427832575324</v>
       </c>
       <c r="H18" t="n">
-        <v>6.003952257481228</v>
+        <v>6.35551724137931</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>3.023873453304676</v>
+        <v>3.0921359375</v>
       </c>
       <c r="G19" t="n">
-        <v>3.152997758488285</v>
+        <v>3.450161998233005</v>
       </c>
       <c r="H19" t="n">
-        <v>3.398779729426623</v>
+        <v>3.9501</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7.766987287097288</v>
+        <v>7.911622179143056</v>
       </c>
       <c r="G20" t="n">
-        <v>7.849038612956447</v>
+        <v>8.03884219874414</v>
       </c>
       <c r="H20" t="n">
-        <v>7.870551997276024</v>
+        <v>8.552275205839161</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>129.0468525727248</v>
+        <v>129.2089186929838</v>
       </c>
       <c r="G21" t="n">
-        <v>129.27813548613</v>
+        <v>130.3877616401733</v>
       </c>
       <c r="H21" t="n">
-        <v>129.9915623222426</v>
+        <v>131.2373431079656</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E2" t="n">
         <v>16732</v>
@@ -614,37 +614,37 @@
         <v>0.4299999999999997</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.288742581843321</v>
+        <v>8.288644462359523</v>
       </c>
       <c r="R2" t="n">
         <v>14.02</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002592703836812156</v>
+        <v>-0.002690823320608705</v>
       </c>
       <c r="T2" t="n">
-        <v>1.443007949001859</v>
+        <v>1.44301535601024</v>
       </c>
       <c r="U2" t="n">
-        <v>1.869505446230526</v>
+        <v>1.869522777477908</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7155582480520066</v>
+        <v>0.7155668852205651</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4311997306897408</v>
+        <v>0.4311891845168022</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7155580375227273</v>
+        <v>0.7155666826723843</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.802216621253404</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.979715271957803</v>
+        <v>6.554903753218611</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.819999999999988</v>
+        <v>8.552073371217531</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E3" t="n">
         <v>16732</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.655804772908746</v>
+        <v>4.655720918395107</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001610598834022498</v>
+        <v>-0.001694453347661426</v>
       </c>
       <c r="T3" t="n">
-        <v>1.315304711992028</v>
+        <v>1.315312042653562</v>
       </c>
       <c r="U3" t="n">
-        <v>1.68191812660116</v>
+        <v>1.681920907570524</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8076805755755192</v>
+        <v>0.8076859372255889</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6152905782275344</v>
+        <v>0.615289306030055</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8076801781011492</v>
+        <v>0.8076854745405503</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.0921359375</v>
+        <v>3.16525117370892</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.450161998233005</v>
+        <v>3.548946922505436</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.9501</v>
+        <v>4.068491701102761</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E4" t="n">
         <v>16732</v>
@@ -792,37 +792,37 @@
         <v>0.005</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.782826752003447</v>
+        <v>6.782675022296866</v>
       </c>
       <c r="R4" t="n">
         <v>12.93</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0008512303059004796</v>
+        <v>-0.001002960012481302</v>
       </c>
       <c r="T4" t="n">
-        <v>1.50581238994113</v>
+        <v>1.505758197375539</v>
       </c>
       <c r="U4" t="n">
-        <v>1.961824277759624</v>
+        <v>1.961766601034225</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7924918278924765</v>
+        <v>0.7925135658056054</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5849892537890696</v>
+        <v>0.585013655677922</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7924917895016239</v>
+        <v>0.7925135106289101</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.96225732421875</v>
+        <v>6.000943661971831</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.203427832575324</v>
+        <v>6.261051635408537</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.35551724137931</v>
+        <v>6.356232897018425</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E5" t="n">
         <v>16732</v>
@@ -881,37 +881,37 @@
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.206419211690175</v>
+        <v>8.206299291913025</v>
       </c>
       <c r="R5" t="n">
         <v>15.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003967024264881666</v>
+        <v>-0.004086944042031287</v>
       </c>
       <c r="T5" t="n">
-        <v>1.511429714401519</v>
+        <v>1.511413082590201</v>
       </c>
       <c r="U5" t="n">
-        <v>2.024263595566108</v>
+        <v>2.024243931677668</v>
       </c>
       <c r="V5" t="n">
-        <v>0.608448962815576</v>
+        <v>0.6084746529886713</v>
       </c>
       <c r="W5" t="n">
-        <v>0.216874840298691</v>
+        <v>0.2168900549288544</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6084486638611089</v>
+        <v>0.6084743300129214</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.911622179143056</v>
+        <v>7.989767018139371</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.03884219874414</v>
+        <v>8.168480799913725</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.552275205839161</v>
+        <v>8.588741934276879</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E6" t="n">
         <v>16732</v>
@@ -970,34 +970,34 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.228848404255319</v>
+        <v>6.228731686679063</v>
       </c>
       <c r="R6" t="n">
         <v>10.6125</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002303819029404768</v>
+        <v>-0.002420536605660732</v>
       </c>
       <c r="T6" t="n">
-        <v>1.390607429051103</v>
+        <v>1.390594315704883</v>
       </c>
       <c r="U6" t="n">
-        <v>1.812735160506897</v>
+        <v>1.812725638034443</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2528576897590764</v>
+        <v>0.2528691644241804</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4948438334879259</v>
+        <v>-0.4948281284118059</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2528575054080888</v>
+        <v>0.2528689682162291</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.580549624016991</v>
+        <v>7.705861736233643</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.455777314954663</v>
+        <v>8.693809671527722</v>
       </c>
       <c r="AA6" t="n">
         <v>9.681999999999983</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E7" t="n">
         <v>16732</v>
@@ -1059,37 +1059,37 @@
         <v>1.025</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.584103155675217</v>
+        <v>5.584048401523237</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.002045601197840096</v>
+        <v>-0.002100355349820027</v>
       </c>
       <c r="T7" t="n">
-        <v>1.14526439184304</v>
+        <v>1.145268244855344</v>
       </c>
       <c r="U7" t="n">
-        <v>1.47164474026035</v>
+        <v>1.471647377200256</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5167326043552513</v>
+        <v>0.5167427396201963</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03332059282578914</v>
+        <v>0.03331712856879987</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5167324430551288</v>
+        <v>0.5167425627012467</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.625377054586039</v>
+        <v>5.687060022603066</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.935152041926347</v>
+        <v>6.060742305930991</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.421768009043904</v>
+        <v>6.728635094118587</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E8" t="n">
         <v>16732</v>
@@ -1148,37 +1148,37 @@
         <v>0.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.423682240616782</v>
+        <v>7.423620293091925</v>
       </c>
       <c r="R8" t="n">
         <v>15.14</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002775445254601867</v>
+        <v>-0.002837392779459436</v>
       </c>
       <c r="T8" t="n">
-        <v>1.331813047323601</v>
+        <v>1.331815579307454</v>
       </c>
       <c r="U8" t="n">
-        <v>1.747873741285568</v>
+        <v>1.747885804323298</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7946996369222515</v>
+        <v>0.7947028564526178</v>
       </c>
       <c r="W8" t="n">
-        <v>0.589381825488281</v>
+        <v>0.5893761576651341</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7946992928726123</v>
+        <v>0.7947024892260348</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.380506043218166</v>
+        <v>5.432715604163216</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.191862108546031</v>
+        <v>6.451061382534131</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.402885444694261</v>
+        <v>7.928997926066917</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E9" t="n">
         <v>16733</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>29587</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.306386265837915</v>
+        <v>7.306244048686229</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.30575016438886</v>
+        <v>7.305595146217722</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0006361014490556111</v>
+        <v>-0.0006489024685063552</v>
       </c>
       <c r="T9" t="n">
-        <v>1.603874032054569</v>
+        <v>1.603872839353355</v>
       </c>
       <c r="U9" t="n">
-        <v>2.058319501498587</v>
+        <v>2.058296603226462</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7320600033169917</v>
+        <v>0.7320652936973315</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4639978433986774</v>
+        <v>0.4640006852760418</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7320598923571815</v>
+        <v>0.7320651695042942</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.05553418756362</v>
+        <v>4.048160590277778</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.575234422074141</v>
+        <v>5.808116329900271</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.431547561253176</v>
+        <v>7.556862142422398</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E10" t="n">
         <v>16344</v>
@@ -1326,37 +1326,37 @@
         <v>3.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.313863410993497</v>
+        <v>9.313727392773925</v>
       </c>
       <c r="R10" t="n">
         <v>39.075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03044492845829038</v>
+        <v>-0.030580946677859</v>
       </c>
       <c r="T10" t="n">
-        <v>1.492859151728104</v>
+        <v>1.49282535659315</v>
       </c>
       <c r="U10" t="n">
-        <v>2.036177836610706</v>
+        <v>2.036159857764651</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4130701730088045</v>
+        <v>0.4130870316638049</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1748744905673443</v>
+        <v>-0.1748537430727346</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4130607805427868</v>
+        <v>0.4130775479938009</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.89777800569748</v>
+        <v>11.81120978267741</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.25610011576072</v>
+        <v>12.53944331205353</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.64009223437747</v>
+        <v>12.88523523726456</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E11" t="n">
         <v>16732</v>
@@ -1415,37 +1415,37 @@
         <v>0.438</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.246532220352263</v>
+        <v>5.246390292236303</v>
       </c>
       <c r="R11" t="n">
         <v>10.15</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002162167646780564</v>
+        <v>-0.002304095762741154</v>
       </c>
       <c r="T11" t="n">
-        <v>1.129629411493649</v>
+        <v>1.129561982365753</v>
       </c>
       <c r="U11" t="n">
-        <v>1.437831437483815</v>
+        <v>1.437750474156815</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3990208181253739</v>
+        <v>0.3990757703695976</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2021032166180847</v>
+        <v>-0.2019678411726913</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3990206653092264</v>
+        <v>0.399075602237698</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.07485633837195</v>
+        <v>6.249900576882519</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.777758465023689</v>
+        <v>7.063815013717107</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.118984037943154</v>
+        <v>7.572384987359669</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E12" t="n">
         <v>16732</v>
@@ -1504,37 +1504,37 @@
         <v>2.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.47527626916772</v>
+        <v>7.475291869893157</v>
       </c>
       <c r="R12" t="n">
         <v>19.178</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.002756153734503639</v>
+        <v>-0.002740553009065606</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9380346545717048</v>
+        <v>0.9380520073405999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.252067329186231</v>
+        <v>1.252093143441763</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6559882471125608</v>
+        <v>0.6559779986007934</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3120530197310964</v>
+        <v>0.3120246522115602</v>
       </c>
       <c r="X12" t="n">
-        <v>0.655988030087689</v>
+        <v>0.6559777874997961</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.127243506493507</v>
+        <v>6.228208178353577</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.132951257007671</v>
+        <v>7.348352006757507</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.881776318185681</v>
+        <v>8.015538681730671</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E13" t="n">
         <v>16732</v>
@@ -1593,37 +1593,37 @@
         <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.154000791895768</v>
+        <v>9.153939340205408</v>
       </c>
       <c r="R13" t="n">
         <v>16.215</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.002925008964857722</v>
+        <v>-0.002986460655217439</v>
       </c>
       <c r="T13" t="n">
-        <v>1.194934344040643</v>
+        <v>1.194951884725076</v>
       </c>
       <c r="U13" t="n">
-        <v>1.605213337816935</v>
+        <v>1.60522556942882</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8730471413330211</v>
+        <v>0.8730482875208094</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7460875336566795</v>
+        <v>0.746083664051935</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8730467373360059</v>
+        <v>0.8730478597462079</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.537649127933112</v>
+        <v>6.529314538102842</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.663780250459621</v>
+        <v>6.643183336562774</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.790570641282565</v>
+        <v>6.723993344474183</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E14" t="n">
         <v>16732</v>
@@ -1682,37 +1682,37 @@
         <v>0.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.196819223358718</v>
+        <v>8.196687362959231</v>
       </c>
       <c r="R14" t="n">
         <v>34.002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002684870592989774</v>
+        <v>-0.002816730992477369</v>
       </c>
       <c r="T14" t="n">
-        <v>1.847007943200902</v>
+        <v>1.846955170957934</v>
       </c>
       <c r="U14" t="n">
-        <v>2.39158885500926</v>
+        <v>2.391540400766723</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7528001157403102</v>
+        <v>0.7528195186233169</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5056063426747338</v>
+        <v>0.5056263755724941</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7527998984982061</v>
+        <v>0.7528192787260287</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.83897051051686</v>
+        <v>6.878274434435603</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.97698810807942</v>
+        <v>7.034333020520589</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.03504216808049</v>
+        <v>7.161640970249327</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E15" t="n">
         <v>16570</v>
@@ -1771,37 +1771,37 @@
         <v>3.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.6674762933248</v>
+        <v>12.66740152866808</v>
       </c>
       <c r="R15" t="n">
         <v>30.745</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.01562612067640584</v>
+        <v>-0.01570088533312842</v>
       </c>
       <c r="T15" t="n">
-        <v>1.354694971768305</v>
+        <v>1.354715354824284</v>
       </c>
       <c r="U15" t="n">
-        <v>2.008340625086536</v>
+        <v>2.008355380656566</v>
       </c>
       <c r="V15" t="n">
-        <v>0.723350275741261</v>
+        <v>0.7233567426610599</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4443459716520703</v>
+        <v>0.4443378066805065</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7233162061606067</v>
+        <v>0.723322085404746</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.0834357666061</v>
+        <v>11.08186940235796</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.14707811754546</v>
+        <v>11.13472826797223</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.21034682178635</v>
+        <v>11.19673258372229</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E16" t="n">
         <v>16732</v>
@@ -1860,37 +1860,37 @@
         <v>0.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.558903578685837</v>
+        <v>7.558934680407932</v>
       </c>
       <c r="R16" t="n">
         <v>131.9</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002913239387316054</v>
+        <v>-0.002882137665221537</v>
       </c>
       <c r="T16" t="n">
-        <v>3.085411085809261</v>
+        <v>3.085435671871837</v>
       </c>
       <c r="U16" t="n">
-        <v>9.547461112705511</v>
+        <v>9.547470919597462</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03109783621703531</v>
+        <v>0.03109988356647922</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9377940711651171</v>
+        <v>-0.9377980520657179</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0310977596088855</v>
+        <v>0.03109980859906336</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.668731456415809</v>
+        <v>8.672895044998345</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.117656485788411</v>
+        <v>9.473532301262212</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.11734862385321</v>
+        <v>11.88916922209595</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16732</v>
+        <v>16733</v>
       </c>
       <c r="E17" t="n">
         <v>15661</v>
@@ -1949,37 +1949,37 @@
         <v>1.413225199131064</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.839041075832428</v>
+        <v>5.838852433519982</v>
       </c>
       <c r="R17" t="n">
         <v>12.23</v>
       </c>
       <c r="S17" t="n">
-        <